--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,22 +512,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 21:05:00</t>
+          <t>2026-09-13 09:55:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>KARA HAYDARIN MASAK RAPORU PATLADI: 74 BİNDEN 222 MİLYONA</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>KARA HAYDARIN MASAK RAPORU PATLADI: 74 BİNDEN 222 MİLYONA Diriliş Postası</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Bolu</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -552,22 +552,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:01:35</t>
+          <t>2026-09-13 08:43:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Özel Harekat'tan 11 İlde Operasyon. 10 Şirkete el Konuldu</t>
+          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Özel Harekat'tan 11 İlde Operasyon. 10 Şirkete el Konuldu Kocatepe Gazetesi</t>
+          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı internethaber.com</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -575,7 +575,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
@@ -588,22 +592,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 07:53:36</t>
+          <t>2026-09-13 13:19:31</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bulgaristan'da patlama: Silah deposunda yangın çıktı</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Bulgaristan'da patlama: Silah deposunda yangın çıktı Hürriyet</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -624,7 +628,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 05:39:50</t>
+          <t>2026-09-13 10:02:22</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -634,12 +638,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Yangın ve patlama sigortasına zorunlu olarak katılmak zorunda olan kuruluşlar.</t>
+          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Yangın ve patlama sigortasına zorunlu olarak katılmak zorunda olan kuruluşlar. Vietnam.vn</t>
+          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede sondakika.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -647,20 +651,32 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Gerede Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 04:45:19</t>
+          <t>2026-09-12 17:46:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -670,12 +686,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hanoi polisi, An Khanh beldesindeki fabrika yangını hakkında bilgi verdi.</t>
+          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hanoi polisi, An Khanh beldesindeki fabrika yangını hakkında bilgi verdi. Vietnam.vn</t>
+          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı 24 Saat Gazetesi Ankara</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -683,20 +699,32 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>BOLPET PLAST GERİ DÖNÜŞÜM</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 07:32:59</t>
+          <t>2026-09-12 18:12:27</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -706,12 +734,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Yangın Güvenliği Reasürans Tesisi, 19,6 Milyar Sterlinlik 730 Riske Teminat Sağladı</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Yangın Güvenliği Reasürans Tesisi, 19,6 Milyar Sterlinlik 730 Riske Teminat Sağladı sigortahaber.com</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı Türkiye Gazetesi</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -719,7 +747,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Antalya | Bolu</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
@@ -732,22 +764,22 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 11:46:59</t>
+          <t>2026-09-12 19:11:09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın zulası patladı! Düğün altınları gizli adresten çıktı! 66 bilezik, metrelerci zincir ve dövizler el konuldu</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın zulası patladı! Düğün altınları gizli adresten çıktı! 66 bilezik, metrelerci zincir ve dövizler el konuldu SuperHaber</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı A Haber</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -755,8 +787,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Bolu | Muş | Sakarya</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
@@ -768,7 +808,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 00:58:25</t>
+          <t>2026-09-12 19:09:34</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -778,12 +818,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Deri fabrikasında korkutan yangın</t>
+          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Deri fabrikasında korkutan yangın Hürriyet</t>
+          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. Vietnam.vn</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -791,16 +831,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
@@ -812,7 +844,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:57:33</t>
+          <t>2026-09-13 05:48:46</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -822,12 +854,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Hanoi'nin An Khanh beldesinde, konut ve fabrikanın bir arada bulunduğu binada çıkan yangın söndürüldü.</t>
+          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hanoi'nin An Khanh beldesinde, konut ve fabrikanın bir arada bulunduğu binada çıkan yangın söndürüldü. Vietnam.vn</t>
+          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti Eskişehir Durum</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -835,7 +867,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
@@ -848,7 +884,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:58:45</t>
+          <t>2026-09-13 09:04:00</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -858,12 +894,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Söke'de KİPAŞ kağıt fabrikasındaki yangın itfaiyenin hızlı müdahalesiyle sınırlı kaldı</t>
+          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Söke'de KİPAŞ kağıt fabrikasındaki yangın itfaiyenin hızlı müdahalesiyle sınırlı kaldı Aksiyon.com.TR</t>
+          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Milli İrade Gazetesi</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -873,45 +909,37 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Aydın | Bursa | Düzce | İstanbul | Muş</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Söke | Maltepe | Sivaslı</t>
-        </is>
-      </c>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Batı Kipaş Kağıt Fabrikası</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:40:00</t>
+          <t>2026-09-13 03:22:15</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın düğünündeki altınlar bulundu! Hepsine el konuldu</t>
+          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın düğünündeki altınlar bulundu! Hepsine el konuldu Haber 7</t>
+          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı bolgegundemi.com</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -932,7 +960,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:33:42</t>
+          <t>2026-09-13 09:03:05</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -942,12 +970,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MASAK Hawala ve Alternatif Değer Transfer Sistemleri İçin Yeni Rehber Yayımladı</t>
+          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MASAK Hawala ve Alternatif Değer Transfer Sistemleri İçin Yeni Rehber Yayımladı FintekWins</t>
+          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı A Haber</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -955,7 +983,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
@@ -968,7 +1000,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:16:07</t>
+          <t>2026-09-13 06:08:08</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -978,12 +1010,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MASAK’ın radarına giren altınlar odunluktan çıktı haberi</t>
+          <t>15 ilde 'Ailem Güvende' operasyonu</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MASAK’ın radarına giren altınlar odunluktan çıktı haberi Finans Gündem</t>
+          <t>15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1004,7 +1036,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 06:17:00</t>
+          <t>2026-09-13 09:19:34</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1014,12 +1046,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>MASAK Şanlıurfa'da takibe aldı, TEM çökertti: DEAŞ'ın para ağlarına operasyon!</t>
+          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MASAK Şanlıurfa'da takibe aldı, TEM çökertti: DEAŞ'ın para ağlarına operasyon! Şanlıurfa Gazetesi</t>
+          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1027,11 +1059,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Şanlıurfa</t>
-        </is>
-      </c>
+      <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1044,7 +1072,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:07:00</t>
+          <t>2026-09-13 09:07:34</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1054,12 +1082,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Van'daki Düğün Sonrası Başlatılan Soruşturmada Kimler Gözaltına Alındı? MASAK Raporunda Kimlerin Adı Geçiyor?</t>
+          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı!</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Van'daki Düğün Sonrası Başlatılan Soruşturmada Kimler Gözaltına Alındı? MASAK Raporunda Kimlerin Adı Geçiyor? urfanatik.com</t>
+          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! SON TV</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1067,11 +1095,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul | Van</t>
-        </is>
-      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1084,22 +1108,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:42:18</t>
+          <t>2026-09-12 20:23:48</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11 ilde Şimşekler suç örgütüne operasyon: 64 gözaltı, dev mal varlığına el konuldu</t>
+          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11 ilde Şimşekler suç örgütüne operasyon: 64 gözaltı, dev mal varlığına el konuldu Takvim</t>
+          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1107,11 +1131,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Adana</t>
-        </is>
-      </c>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1124,7 +1144,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:08:00</t>
+          <t>2026-09-13 08:33:15</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1134,12 +1154,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MASAK ve KOM raporları skandalı ortaya çıkardı: Tepebaşı Belediyesi soruşturmasında hapis talebi</t>
+          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı!</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MASAK ve KOM raporları skandalı ortaya çıkardı: Tepebaşı Belediyesi soruşturmasında hapis talebi Yirmidort.tv</t>
+          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! SON TV</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1147,11 +1167,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Eskişehir</t>
-        </is>
-      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1164,22 +1180,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:01:00</t>
+          <t>2026-09-13 14:13:08</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Bankalar artık buna da bakacak!</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Bankalar artık buna da bakacak! Söz Sakarya</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1187,7 +1203,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Bingöl | İstanbul | Van</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1200,22 +1220,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:53:30</t>
+          <t>2026-09-13 09:05:00</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposundaki yangın beş depoyu yok etti, yakınındaki evde hasar oluştu</t>
+          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposundaki yangın beş depoyu yok etti, yakınındaki evde hasar oluştu Aksiyon.com.TR</t>
+          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı aydinlik.com.tr</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1223,16 +1243,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Antalya | Bursa | Düzce | İstanbul | Muş</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Muratpaşa | Maltepe | Sivaslı</t>
-        </is>
-      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
@@ -1244,22 +1256,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 12:42:41</t>
+          <t>2026-09-13 06:35:00</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da ev ve depoda çıkan yangına itfaiye ekipleri müdahale ediyor</t>
+          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da ev ve depoda çıkan yangına itfaiye ekipleri müdahale ediyor Son Dakika</t>
+          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Ege Telgraf</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1267,16 +1279,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Antalya</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Muratpaşa</t>
-        </is>
-      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
@@ -1288,22 +1292,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:47:00</t>
+          <t>2026-09-13 07:18:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposunda korkutan yangın! Ekipler tarafından kontrol altına alındı</t>
+          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposunda korkutan yangın! Ekipler tarafından kontrol altına alındı Şok Gazetesi</t>
+          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında KARAR</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1313,7 +1317,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Antalya</t>
+          <t>Ankara | Hatay | İstanbul | Mersin</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -1328,22 +1332,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:40:20</t>
+          <t>2026-09-13 12:22:00</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Türkiye İş Dünyası Haberleri</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1353,14 +1357,10 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir | Hatay | Sakarya | İstanbul</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Beşiktaş</t>
-        </is>
-      </c>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
@@ -1372,22 +1372,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 06:49:27</t>
+          <t>2026-09-13 10:19:26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>İnşaat konkordatoda tekstili solladı: Başvurularda düşüş</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi!</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>İnşaat konkordatoda tekstili solladı: Başvurularda düşüş Odatv</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1395,8 +1395,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
@@ -1408,22 +1416,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:16:58</t>
+          <t>2026-09-13 01:34:53</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Konkordatolar azalıyor: Şirketler toparlanıyor mu, başvurmak mı pahalılaştı?</t>
+          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Konkordatolar azalıyor: Şirketler toparlanıyor mu, başvurmak mı pahalılaştı? Para Analiz</t>
+          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi Finans Gündem</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1431,8 +1439,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
@@ -1444,22 +1460,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 16:33:36</t>
+          <t>2026-09-12 18:20:15</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>58 yıllık Türk meyve suyu şirketi iflastan kurtuldu: Her sofrada vardı</t>
+          <t>Antalya'da depo yangını / Ek fotoğraflar</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>58 yıllık Türk meyve suyu şirketi iflastan kurtuldu: Her sofrada vardı Yeniçağ Gazetesi</t>
+          <t>Antalya'da depo yangını / Ek fotoğraflar Antalya İleri</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1467,7 +1483,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1480,22 +1500,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:18:00</t>
+          <t>2026-09-13 10:20:22</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm’de Şaşırtan Gelişme: Konkordato Kararı</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm’de Şaşırtan Gelişme: Konkordato Kararı KGRT Haber</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor sondakika.com</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1505,10 +1525,14 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Sakarya</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
@@ -1520,22 +1544,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:32:59</t>
+          <t>2026-09-12 19:47:00</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Seferler ve bilet satışı sürüyor</t>
+          <t>Depo’da korkutan yangın, mahalleli seferber oldu</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Seferler ve bilet satışı sürüyor bolgegundemi.com</t>
+          <t>Depo’da korkutan yangın, mahalleli seferber oldu BursaVar</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1556,22 +1580,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 21:52:00</t>
+          <t>2026-09-12 17:42:00</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat devi şirketi iflas etti</t>
+          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne?</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat devi şirketi iflas etti Evrensel.net</t>
+          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? politikam.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1581,34 +1605,30 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Giresun | İzmir | Muğla | Bursa</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>İnegöl | Şebinkarahisar</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş</t>
-        </is>
-      </c>
+          <t>Muratpaşa</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>İzmer</t>
+          <t>Ambalaj Ticaret</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:23:16</t>
+          <t>2026-09-13 10:00:14</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1618,12 +1638,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ünlü seyahat şirketi iflas etti... Rezervasyonu olanlara acil çağrı yapıldı</t>
+          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ünlü seyahat şirketi iflas etti... Rezervasyonu olanlara acil çağrı yapıldı Turizm Aktüel</t>
+          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti Samanyolu Haber</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1631,20 +1651,32 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>İzmer</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 07:25:00</t>
+          <t>2026-09-13 06:18:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1654,12 +1686,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için iflas talebi! Mahkeme tarihi belli oldu</t>
+          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!”</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için iflas talebi! Mahkeme tarihi belli oldu bursatv.com.tr</t>
+          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1667,16 +1699,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Bursa | Iğdır</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Aralık</t>
-        </is>
-      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
       <c r="J31" s="2" t="inlineStr">
@@ -1688,7 +1712,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:20:02</t>
+          <t>2026-09-12 18:50:00</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1698,12 +1722,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat şirketi iflas etti! Alacaklılar için ek sıra cetveli hazırlandı..</t>
+          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat şirketi iflas etti! Alacaklılar için ek sıra cetveli hazırlandı.. EmlakDream</t>
+          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Yıldırım Gazetesi</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1711,7 +1735,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1724,7 +1752,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:25:12</t>
+          <t>2026-09-13 01:09:00</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1734,12 +1762,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır</t>
+          <t>Ege Gıda Meşrubat, konkordato süreci başlattı</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır Haberler</t>
+          <t>Ege Gıda Meşrubat, konkordato süreci başlattı egealternatif.com</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1747,24 +1775,28 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Kayseri</t>
-        </is>
-      </c>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Ege Gıda Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:22:00</t>
+          <t>2026-09-13 10:08:44</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1774,12 +1806,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de inşaat şirketinin iflası sonrası alacaklıların durumu belirlendi</t>
+          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de inşaat şirketinin iflası sonrası alacaklıların durumu belirlendi Ege Alternatif</t>
+          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek enerjifm.com.tr</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1787,11 +1819,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
@@ -1804,22 +1832,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 05:13:00</t>
+          <t>2026-09-12 17:51:00</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Almanya'da şirket iflasları patladı</t>
+          <t>Fabrika yangınına müdahale sürüyor</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Almanya'da şirket iflasları patladı Yeni Mesaj</t>
+          <t>Fabrika yangınına müdahale sürüyor Güneydoğu Ekspres</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1829,12 +1857,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Iğdır | Tekirdağ</t>
+          <t>Bolu</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Çerkezköy</t>
+          <t>Gerede</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
@@ -1848,22 +1876,22 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 21:29:00</t>
+          <t>2026-09-12 18:58:00</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Barnes Worldwide Travel Ltd, iflasını açıkladı ve rezervasyon sahiplerine uyarıda bulundu</t>
+          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Barnes Worldwide Travel Ltd, iflasını açıkladı ve rezervasyon sahiplerine uyarıda bulundu Ege Alternatif</t>
+          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Zonguldak Pusula Son Dakika Haberleri</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1871,7 +1899,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
@@ -1884,22 +1916,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 17:23:54</t>
+          <t>2026-09-12 17:37:21</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>İzmir’in tarihi simgelerinden Konak Pier'i işleten şirket iflas etti haberi</t>
+          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>İzmir’in tarihi simgelerinden Konak Pier'i işleten şirket iflas etti haberi Finans Gündem</t>
+          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Bursa Saati</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1909,10 +1941,14 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>İzmir</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Kocasinan</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
@@ -1924,22 +1960,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:22:58</t>
+          <t>2026-09-12 19:04:58</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>İzmirli 35 yıllık inşaat şirketinin iflas sürecinde yeni aşama</t>
+          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>İzmirli 35 yıllık inşaat şirketinin iflas sürecinde yeni aşama bolgegundemi.com</t>
+          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1947,8 +1983,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
@@ -1960,22 +2004,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:43:33</t>
+          <t>2026-09-13 14:39:00</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>İzmirli inşaat devi İzmer iflas etti, Konak Pier masada</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı!</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>İzmirli inşaat devi İzmer iflas etti, Konak Pier masada İş'te Gündem</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1996,22 +2040,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:53:00</t>
+          <t>2026-09-13 00:03:35</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Hakkari’de ihale usulsüzlüğü ortaya çıktı! 7 şüpheli tutuklandı, hesaplara el konuldu</t>
+          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Hakkari’de ihale usulsüzlüğü ortaya çıktı! 7 şüpheli tutuklandı, hesaplara el konuldu Türkgün</t>
+          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2019,11 +2063,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Hakkari</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2036,22 +2076,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:16:21</t>
+          <t>2026-09-13 10:10:48</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Kayseri Kocasinan'da avize imalathanesinin çatısında çıkan yangın söndürüldü</t>
+          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Kayseri Kocasinan'da avize imalathanesinin çatısında çıkan yangın söndürüldü Son Dakika</t>
+          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2059,16 +2099,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Kayseri</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Kocasinan</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
@@ -2080,7 +2112,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:29:36</t>
+          <t>2026-09-13 10:52:00</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2090,12 +2122,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Müşteri kılığında bankaya girdi! Çalışanların yüzüne biber atıp paralarla kaçtı</t>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama!</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Müşteri kılığında bankaya girdi! Çalışanların yüzüne biber atıp paralarla kaçtı Halk TV</t>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2116,7 +2148,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:01:00</t>
+          <t>2026-09-13 06:39:00</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2126,12 +2158,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>İzmir Hatay’da silahlı soygun: Bankadakiler rehin alındı! Başsavcılık'tan açıklama</t>
+          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>İzmir Hatay’da silahlı soygun: Bankadakiler rehin alındı! Başsavcılık'tan açıklama gazeteyenigun.com.tr</t>
+          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2139,11 +2171,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Hatay</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2156,22 +2184,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 16:13:44</t>
+          <t>2026-09-13 04:52:14</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Banka çalışanlarını rehin almıştı; eylemi 'kız çocukları farkındalığı' için yapmış</t>
+          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Banka çalışanlarını rehin almıştı; eylemi 'kız çocukları farkındalığı' için yapmış Aliağa Medya</t>
+          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı 10haber.net</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2179,35 +2207,51 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Muğla</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Marmaris</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Pusula Holding</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Pusula Yatırım Menkul Değerler A.Ş</t>
+        </is>
+      </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:24:19</t>
+          <t>2026-09-13 13:33:00</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek: 16 ilimizde turizm güvenliğini tehdit eden 164 olay ve soruşturmada 323 şüpheli hakkında adli işlem yapıldı</t>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek: 16 ilimizde turizm güvenliğini tehdit eden 164 olay ve soruşturmada 323 şüpheli hakkında adli işlem yapıldı DHA | Demirören Haber Ajansı</t>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2215,8 +2259,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Muğla</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Bodrum</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
@@ -2225,8 +2277,52 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:50:46</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J45"/>
+  <autoFilter ref="A1:J46"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2272,6 +2368,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2283,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB45"/>
+  <dimension ref="A1:AB46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2461,27 +2558,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 21:05:00</t>
+          <t>2026-09-13 09:55:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MASAK raporu</t>
+          <t>üretim tesisi yangını</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>KARA HAYDARIN MASAK RAPORU PATLADI: 74 BİNDEN 222 MİLYONA</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>KARA HAYDARIN MASAK RAPORU PATLADI: 74 BİNDEN 222 MİLYONA Diriliş Postası</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2491,44 +2588,52 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Dün yazdım. Bugün MASAK raporu ortaya çıktı. Ve artık mesele düğündeki altınlar, lüks araçlar ya da sosyal medyada sergilenen gösteriş değil. Mesele para. Van'ın köklü aşiretlerini bu tartışmanın içine kimse çekmesin. Van'da ciddi aşiret düğünleri vardır. Sofralar kurulur, tonlarca et pişer, insanlar bir araya gelir. Düğün sahibine para takılır, altın takılır. Bugün sen benim düğünümde destek olursun, yarın ben seninkinde. Bu bir gelenektir. Ama Kara Haydar meselesinin bununla ne ilgisi var? Benim gördüğüm aşiret düğünü değil. Önce kendilerine isim takan, dizi karakterlerini taklit eden, sosyal medyada kendilerine başka bir dünya kuran insanlar görüyoruz. Sonra o kurmaca karakter büyütülüyor. TikTok bunu besliyor. Gösteriş büyüyor. Lüks arabalar kadraja giriyor. Altınlar masaya diziliyor. Ve gençlere “Hayat böyle yaşanır” mesajı veriliyor. Hayır! Hayat böyle yaşanmıyor. Bu, bana göre gençlere pazarlanan tehlikeli bir illüzyon. Ve şimdi MASAK raporu önümüzde. Rakamlar küçük değil: 74 bin 281 lira. Tançalan'ın 2020'den itibaren tespit edilen ticari kâr beyanı. Karşısında: 222 milyon liradan fazla. Çiftin banka hesaplarındaki toplam transfer hacmi. Üstelik; 13 milyon liralık mal ve hizmet alımı. 7,1 milyon liralık Porsche. Milyonluk araçlar. Taşınmaz devirleri. Ve düğünde sergilenen milyonluk altınlar. Sonra “Altınlar emanetti” açıklaması geliyor. MASAK raporuna göre kuyumcu tarafının anlatımı ise farklı. Şimdi kusura bakmayın ama ben buna bakıp “Van'ın düğün geleneği” deyip geçemem. Geçmem. Çünkü Van'ın geleneğine saygım var. Ama geleneğin arkasına saklanarak açıklanması gereken rakamları da görmezden gelmem. 222 MİLYON LİRA NEREDEN GELDİ? Benim sorum bu. Dubai üzerinden mail order geliri olduğu yönündeki bilgiler rapora girmiş. Ancak MASAK incelemesinde çift adına yurt dışından Türkiye'ye finansal kanallarla fon transferi tespit edilmediği belirtiliyor. O zaman sorular daha da büyüyor. Para nerede kazanıldı? Nasıl hareket etti? Kimlerin hesapları kullanıldı? Düğündeki para ve altınların kaynağı neydi? Kimler taktı? Kimler oradaydı? Allah aşkına, düğün görüntülerini açın. Kimler var? Kimler aynı masada? Kimler birbirine altın takıyor? Kimler bu gösterinin içerisinde? Bence dosyanın en önemli taraflarından biri de burada. Çünkü mesele Van'ın örfü değil. Mesele para trafiği. ASIL TEHLİKE TİKTOK'TA Beni para kadar rahatsız eden başka bir şey daha var: Bu insanların sosyal medyada kahramanlaştırılması. Kendilerine isim takıyorlar. Dizi karakterlerini taklit ediyorlar. Kendilerini başka bir dünyanın insanı gibi gösteriyorlar. Sonra gençler bunları izliyor. Takip ediyor. Özeniyor. İşte buna itiraz ediyorum. Çünkü çalışmadan, üretmeden, alın teri dökmeden zenginleşmiş gibi görünmek başarı değildir. Bu, gençlere satılan sahte bir hayat hikâyesidir. Kimse hiçbir şey yapmadan kalıcı servet sahibi olamaz. Oluyorsa bunun bir hikâyesi vardır. Ve o hikâye anlatılmalıdır. Ben gençlere açıkça söylüyorum: Bu insanları takip ederek kendinize gelecek kuramazsınız. Bir araba kadraja giriyor diye o araba başarı değildir. Bir avuç altın gösteriliyor diye o altın servet değildir. Birileri kendisine mafya, kabadayı veya dizi karakteri görüntüsü veriyor diye güçlü değildir. Gerçek güç üretmektir. Çalışmaktır. Kendi paranı kazanmak ve o paranın hesabını verebilmektir. MASAK raporu ortada. 222 milyon liralık transfer trafiği ortada. 74 bin 281 liralık ticari kâr beyanı ortada. Lüks araçlar ortada. Porsche ortada. Taşınmaz hareketleri ortada. Düğündeki altınlar ortada. Çelişkili açıklamalar ortada. Ben kimseyi mahkeme yerine koyup suçlu ilan etmiyorum. Ama gazeteci olarak da susacak değilim. Bu dosya sonuna kadar incelenmeli. Eğer her kuruşun yasal ve açıklanabilir bir kaynağı varsa ortaya konur. Yok eğer bu gösterişli dünyanın arkasında kayıt dışı veya suçtan kaynaklanan bir para varsa, o da ortaya çıkar. Ama bir şeyi de artık açıkça söyleyelim: Kimse sosyal medyada kendisine bir karakter yazıp gerçek hayatta kahraman olamaz. Kimse üç video, iki lüks araba, birkaç kilo altın göstererek gençlere “başarı” dersi veremez. Takipçi vermeyin. Özendirmeyin. Kahramanlaştırmayın. Van'ın geleneği tertemizdir. Ben o geleneği, sosyal medyada yaratılmış birkaç yapay karakterin gösterisine kurban ettirmem. Ve benim için dosyanın özeti çok net: 74 BİNDEN 222 MİLYONA GELEN BU TABLONUN HESABI VERİLMELİ. KARA HAYDARIN MASAK RAPORU PATLADI: 74 BİNDEN 222 MİLYONA Bugün MASAK raporu ortaya çıktı. Ve artık mesele düğündeki altınlar, lüks araçlar ya da sosyal medyada sergilenen gösteriş değil. Van'ın köklü aşiretlerini bu tartışmanın içine kimse çekmesin. Van'da ciddi aşiret düğünleri vardır. Sofralar kurulur, tonlarca et pişer, insanlar bir araya gelir. Düğün sahibine para takılır, altın takılır. Bugün sen benim düğünümde destek olursun, yarın ben seninkinde. Ama Kara Haydar meselesinin bununla ne ilgisi var? Benim gördüğüm aşiret düğünü değil. Önce kendilerine isim takan, dizi karakterlerini taklit eden, sosyal medyada kendilerine başka bir dünya kuran insanlar görüyoruz. Sonra o kurmaca karakter büyütülüyor. Lüks arabalar kadraja giriyor. Altınlar masaya diziliyor. Ve gençlere “Hayat böyle yaşanır” mesajı veriliyor. Bu, bana göre gençlere pazarlanan tehlikeli bir illüzyon. Ve şimdi MASAK raporu önümüzde. Tançalan'ın 2020'den itibaren tespit edilen ticari kâr beyanı. 222 milyon liradan fazla. Çiftin banka hesaplarındaki toplam transfer hacmi. 13 milyon liralık mal ve hizmet alımı. 7,1 milyon liralık Porsche. Ve düğünde sergilenen milyonluk altınlar. Sonra “Altınlar emanetti” açıklaması geliyor. MASAK raporuna göre kuyumcu tarafının anlatımı ise farklı. Şimdi kusura bakmayın ama ben buna bakıp “Van'ın düğün geleneği” deyip geçemem. Çünkü Van'ın geleneğine saygım var. Ama geleneğin arkasına saklanarak açıklanması gereken rakamları da görmezden gelmem. 222 MİLYON LİRA NEREDEN GELDİ? Dubai üzerinden mail order geliri olduğu yönündeki bilgiler rapora girmiş. Ancak MASAK incelemesinde çift adına yurt dışından Türkiye'ye finansal kanallarla fon transferi tespit edilmediği belirtiliyor. O zaman sorular daha da büyüyor. Kimlerin hesapları kullanıldı? Düğündeki para ve altınların kaynağı neydi? Allah aşkına, düğün görüntülerini açın. Kimler birbirine altın takıyor? Kimler bu gösterinin içerisinde? Bence dosyanın en önemli taraflarından biri de burada. Çünkü mesele Van'ın örfü değil. Beni para kadar rahatsız eden başka bir şey daha var: Bu insanların sosyal medyada kahramanlaştırılması. Kendilerine isim takıyorlar. Dizi karakterlerini taklit ediyorlar. Kendilerini başka bir dünyanın insanı gibi gösteriyorlar. Sonra gençler bunları izliyor. İşte buna itiraz ediyorum. Çünkü çalışmadan, üretmeden, alın teri dökmeden zenginleşmiş gibi görünmek başarı değildir. Bu, gençlere satılan sahte bir hayat hikâyesidir. Kimse hiçbir şey yapmadan kalıcı servet sahibi olamaz. Oluyorsa bunun bir hikâyesi vardır. Ve o hikâye anlatılmalıdır. Ben gençlere açıkça söylüyorum: Bu insanları takip ederek kendinize gelecek kuramazsınız. Bir araba kadraja giriyor diye o araba başarı değildir. Bir avuç altın gösteriliyor diye o altın servet değildir. Birileri kendisine mafya, kabadayı veya dizi karakteri görüntüsü veriyor diye güçlü değildir. Kendi paranı kazanmak ve o paranın hesabını verebilmektir. 222 milyon liralık transfer trafiği ortada. 74 bin 281 liralık ticari kâr beyanı ortada. Taşınmaz hareketleri ortada. Düğündeki altınlar ortada. Çelişkili açıklamalar ortada. Ben kimseyi mahkeme yerine koyup suçlu ilan etmiyorum. Ama gazeteci olarak da susacak değilim. Bu dosya sonuna kadar incelenmeli. Eğer her kuruşun yasal ve açıklanabilir bir kaynağı varsa ortaya konur. Yok eğer bu gösterişli dünyanın arkasında kayıt dışı veya suçtan kaynaklanan bir para varsa, o da ortaya çıkar. Ama bir şeyi de artık açıkça söyleyelim: Kimse sosyal medyada kendisine bir karakter yazıp gerçek hayatta kahraman olamaz. Kimse üç video, iki lüks araba, birkaç kilo altın göstererek gençlere “başarı” dersi veremez. Van'ın geleneği tertemizdir. Ben o geleneği, sosyal medyada yaratılmış birkaç yapay karakterin gösterisine kurban ettirmem. Ve benim için dosyanın özeti çok net: 74 BİNDEN 222 MİLYONA GELEN BU TABLONUN HESABI VERİLMELİ.</t>
+          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontro... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Val... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontro...</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>KARA HAYDARIN MASAK RAPORU PATLADI: 74 BİNDEN 222 MİLYONA KARA HAYDARIN MASAK RAPORU PATLADI: 74 BİNDEN 222 MİLYONA Diriliş Postası Bugün MASAK raporu ortaya çıktı. Ve artık mesele düğündeki altınlar, lüks araçlar ya da sosyal medyada sergilenen gösteriş değil. Van'ın köklü aşiretlerini bu tartışmanın içine kimse çekmesin. Van'da ciddi aşiret düğünleri vardır. Sofralar kurulur, tonlarca et pişer, insanlar bir araya gelir. Düğün sahibine para takılır, altın takılır. Bugün sen benim düğünümde destek olursun, yarın ben seninkinde. Ama Kara Haydar meselesinin bununla ne ilgisi var? Benim gördüğüm aşiret düğünü değil. Önce kendilerine isim takan, dizi karakterlerini taklit eden, sosyal medyada kendilerine başka bir dünya kuran insanlar görüyoruz. Sonra o kurmaca karakter büyütülüyor. Lüks arabalar kadraja giriyor. Altınlar masaya diziliyor. Ve gençlere “Hayat böyle yaşanır” mesajı veriliyor. Ve şimdi MASAK raporu önümüzde. Sonra “Altınlar emanetti” açıklaması geliyor. MASAK raporuna göre kuyumcu tarafının anlatımı ise farklı. Şimdi kusura bakmayın ama ben buna bakıp “Van'ın düğün geleneği” deyip geçemem. Çünkü Van'ın geleneğine saygım var. Ama geleneğin arkasına saklanarak açıklanması gereken rakamları da görmezden gelmem. Ancak MASAK incelemesinde çift adına yurt dışından Türkiye'ye finansal kanallarla fon transferi tespit edilmediği belirtiliyor. Allah aşkına, düğün görüntülerini açın. Çünkü mesele Van'ın örfü değil. ASIL TEHLİKE TİKTOK'TA Beni para kadar rahatsız eden başka bir şey daha var: Bu insanların sosyal medyada kahramanlaştırılması. Kendilerini başka bir dünyanın insanı gibi gösteriyorlar. Çünkü çalışmadan, üretmeden, alın teri dökmeden zenginleşmiş gibi görünmek başarı değildir. Ben gençlere açıkça söylüyorum: Bu insanları takip ederek kendinize gelecek kuramazsınız. Bir araba kadraja giriyor diye o araba başarı değildir. Taşınmaz hareketleri ortada. Bu dosya sonuna kadar incelenmeli. Eğer her kuruşun yasal ve açıklanabilir bir kaynağı varsa ortaya konur. Yok eğer bu gösterişli dünyanın arkasında kayıt dışı veya suçtan kaynaklanan bir para varsa, o da ortaya çıkar. Ama bir şeyi de artık açıkça söyleyelim: Kimse sosyal medyada kendisine bir karakter yazıp gerçek hayatta kahraman olamaz. Van'ın geleneği tertemizdir. Ve benim için dosyanın özeti çok net: 74 BİNDEN 222 MİLYONA GELEN BU TABLONUN HESABI VERİLMELİ. KARA HAYDARIN MASAK RAPORU PATLADI: 74 BİNDEN 222 MİLYONA Bugün MASAK raporu ortaya çıktı. Beni para kadar rahatsız eden başka bir şey daha var: Bu insanların sosyal medyada kahramanlaştırılması.</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontro... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNYjNKUklrbEhzeFU5c2NxS05TbU1kV1ZfRkEtZ19TNVZETXZSZFlLWlgtUGQwYUVpTzR6eERuMEc0YzlKSkdQcVh4M3RUSUVlWjRVMERRMGxSSlNaNnBUd2sxNDZjN2QtZkZ1Y3F4QnY0dDFlcm9POHdVRHBYNlU3dnY2aVJIa2tJNkw4QWxxMFpTc1VxMkE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.bolugundem.com/haber/28691580/boluda-5-saatlik-yangin-kabusu-geri-donusum-fabrikasi-alevlere-teslim-oldu-3-kisi-yaralandi</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Van</t>
+          <t>Bolu</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Geri dönüşüm fabrikası</t>
+        </is>
+      </c>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr"/>
@@ -2542,7 +2647,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="n">
-        <v>79.75</v>
+        <v>128.01</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -2551,27 +2656,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:01:35</t>
+          <t>2026-09-13 08:43:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MASAK raporu</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Özel Harekat'tan 11 İlde Operasyon. 10 Şirkete el Konuldu</t>
+          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Özel Harekat'tan 11 İlde Operasyon. 10 Şirkete el Konuldu Kocatepe Gazetesi</t>
+          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı internethaber.com</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2581,35 +2686,35 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>el konuldu, şirket</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>kuruluş, masak</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Özel Harekat'tan 11 İlde Operasyon. 10 Şirkete el Konuldu Kocatepe Gazetesi</t>
+          <t>MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar... MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar... MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar... HABERLER GÜNCEL Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar... Yayınlama Tarihi: 13.09.2026 11:43 Güncelleme Tarihi: 13.09.2026 12:36 MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. 1 10 SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. 2 10 “Bankacılık Transfer”lerinde yer alan 45.135 işlemde 13.040 para girişi, 32.095 para çıkışı tespit edilmiştir. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. 3 10 4 10 5 10 6 10 7 10 8 10 9 10 10 10 masak LGBT MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. “Bankacılık Transfer”lerinde yer alan 45.135 işlemde 13.040 para girişi, 32.095 para çıkışı tespit edilmiştir. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. 1 10 SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. 2 10 “Bankacılık Transfer”lerinde yer alan 45.135 işlemde 13.040 para girişi, 32.095 para çıkışı tespit edilmiştir. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. 3 10 4 10 5 10 6 10 7 10 8 10 9 10 10 10 MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. 1 10 SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. 2 10 “Bankacılık Transfer”lerinde yer alan 45.135 işlemde 13.040 para girişi, 32.095 para çıkışı tespit edilmiştir. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. 3 10 Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar...</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Özel Harekat'tan 11 İlde Operasyon. 10 Şirkete el Konuldu Özel Harekat'tan 11 İlde Operasyon. 10 Şirkete el Konuldu Kocatepe Gazetesi Özel Harekat'tan 11 İlde Operasyon. 10 Şirkete el Konuldu Kocatepe Gazetesi</t>
+          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı internethaber.com MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. HABERLER GÜNCEL Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Yayınlama Tarihi: 13.09.2026 11:43 Güncelleme Tarihi: 13.09.2026 12:36 MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. 1 10 SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. 3 10 4 10 5 10 6 10 7 10 8 10 9 10 10 10 masak LGBT MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. 3 10 4 10 5 10 6 10 7 10 8 10 9 10 10 10 MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. 3 10 Yabancı kuruluşlardan LGBT derneklerine para transferleri!</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQTF9LVmg1SWV4d3hTaEhQOVFnWUhsWTI2VTFMT1h2OGxWVEU5NGpVdXRQN1NwRnNVaGdqdDBWNk5yQktGaWZWZG44QU1SNnIwUW5sYjNBLUNRMk80dmdaVzVOd29jSVNLUkNRYjAybXFDZ3p3RXEtcDRjVVBWVkRrQUxqMVN2b2NRVjNqYjEwNTFiRlZvanpMMEVsejVWdw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>https://www.internethaber.com/yabanci-kuruluslardan-lgbt-derneklerine-para-transferleri-masak-tek-tek-acikladi-foto-galerisi-2459238.htm</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
@@ -2618,7 +2723,7 @@
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
@@ -2632,7 +2737,7 @@
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="n">
-        <v>56</v>
+        <v>106.25</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>2</v>
@@ -2641,27 +2746,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 07:53:36</t>
+          <t>2026-09-13 13:19:31</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>para aklama</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Bulgaristan'da patlama: Silah deposunda yangın çıktı</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Bulgaristan'da patlama: Silah deposunda yangın çıktı Hürriyet</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2671,48 +2776,44 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı. Patlamanın nedeni henüz bilinmiyor. En Son Haberler - Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı. Patlamanın nedeni henüz bilinmiyor. Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı. Patlamanın nedeni henüz bilinmiyor. HABER MERKEZİ/İHA Oluşturulma Tarihi: Eylül 12, 2026 10:53 2dk okuma Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı. Patlamanın nedeni henüz bilinmiyor. Haberlerimizi Google’da Takip Edin Gelişmelerden anında haberdar olun. Google’da tercih edilen kaynak olarak ekleyin Haberin Devamı Bulgaristan'ın Gabrovo bölgesinde gece saatlerinde silah deposunda patlama meydana geldi. Tsareva Livada köyü yakınlarında özel silah şirketi EMCO'ya ait depoda yaşanan patlamanın ardından yangın çıktı. Gabrovo Valisi Kristina Sidorova, alevlerin depolama alanı içinde yayıldığını belirterek, "Yangın fabrikanın depolama alanının sınırları içinde. Depodan depoya yayılıyor" dedi. ALEVLER DEPOLAR ARASINDA YAYILDI Yerel basında yer alan haberlere göre yangın, EMCO'nun tesislerinden birinde çıktı. Patlamanın ardından başlayan yangının depolama alanındaki diğer bölümlere yayıldığı bildirildi. Şirketin aynı zamanda geçtiğimiz ay başka bir tesisinde de patlama yaşadığı aktarıldı. EMCO'NUN SAHİBİ DAHA ÖNCE DE GÜNDEMDEYDİ EMCO, Bulgar iş insanı Emilian Gebrev'e ait. Gebrev ve şirketi, geçmiş yıllarda Bulgaristan'daki mühimmat deposu patlamalarıyla ilgili soruşturmaların merkezinde yer aldı. Haberin Devamı Bulgar savcılar, Gebrev'in tesislerinin geçmişte Rus ajanlar tarafından düzenlendiği öne sürülen saldırıların hedefi olduğunu açıklamıştı. BULGARİSTAN'DAN 6 RUS VATANDAŞINA TUTUKLAMA EMRİ Bulgaristan, 2024 yılında EMCO'ya ait silah depolarının imha edilmesine karıştıkları iddiasıyla 6 Rus vatandaşı hakkında tutuklama emri çıkarmıştı. Söz konusu depolarda 2011-2020 yılları arasında Ukrayna ve Gürcistan'a ihraç edilmek üzere mühimmat bulunduğu belirtilmişti. Dönemin Bulgar savcıları, ülkedeki mühimmat deposu patlamaları ile 2015 yılında Emilian Gebrev'e yönelik zehirleme girişimi ve 2014'te Çekya'daki mühimmat deposu patlamaları arasında bağlantı olabileceğini öne sürmüştü. RUSYA İDDİALARI REDDETTİ Bulgaristan 'daki patlamalarla ilgili soruşturmalarda Rusya'nın rolü bulunduğuna yönelik iddialar Moskova tarafından kabul edilmedi. Rusya, Bulgar makamlarının ortaya attığı suçlamaları reddetti. Gözden Kaçmasın NATO’yu alarma geçiren hamle! Putin neyi test etti? Denizin yüzlerce metre altında ne oldu? Haberi görüntüle Haberle ilgili daha fazlası: #Bulgaristan #Patlama #Silah Deposu HABER MERKEZİ/İHA Oluşturulma Tarihi: Eylül 12, 2026 10:53 2dk okuma Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı. Patlamanın nedeni henüz bilinmiyor. Haberlerimizi Google’da Takip Edin Gelişmelerden anında haberdar olun. Google’da tercih edilen kaynak olarak ekleyin Haberin Devamı Bulgaristan'ın Gabrovo bölgesinde gece saatlerinde silah deposunda patlama meydana geldi. Tsareva Livada köyü yakınlarında özel silah şirketi EMCO'ya ait depoda yaşanan patlamanın ardından yangın çıktı. Gabrovo Valisi Kristina Sidorova, alevlerin depolama alanı içinde yayıldığını belirterek, "Yangın fabrikanın depolama alanının sınırları içinde. Depodan depoya yayılıyor" dedi. ALEVLER DEPOLAR ARASINDA YAYILDI Yerel basında yer alan haberlere göre yangın, EMCO'nun tesislerinden birinde çıktı. Patlamanın ardından başlayan yangının depolama alanındaki diğer bölümlere yayıldığı bildirildi. Şirketin aynı zamanda geçtiğimiz ay başka bir tesisinde de patlama yaşadığı aktarıldı. EMCO'NUN SAHİBİ DAHA ÖNCE DE GÜNDEMDEYDİ EMCO, Bulgar iş insanı Emilian Gebrev'e ait. Gebrev ve şirketi, geçmiş yıllarda Bulgaristan'daki mühimmat deposu patlamalarıyla ilgili soruşturmaların merkezinde yer aldı. Haberin Devamı Bulgar savcılar, Gebrev'in tesislerinin geçmişte Rus ajanlar tarafından düzenlendiği öne sürülen saldırıların hedefi olduğunu açıklamıştı. BULGARİSTAN'DAN 6 RUS VATANDAŞINA TUTUKLAMA EMRİ Bulgaristan, 2024 yılında EMCO'ya ait silah depolarının imha edilmesine karıştıkları iddiasıyla 6 Rus vatandaşı hakkında tutuklama emri çıkarmıştı. Söz konusu depolarda 2011-2020 yılları arasında Ukrayna ve Gürcistan'a ihraç edilmek üzere mühimmat bulunduğu belirtilmişti. Dönemin Bulgar savcıları, ülkedeki mühimmat deposu patlamaları ile 2015 yılında Emilian Gebrev'e yönelik zehirleme girişimi ve 2014'te Çekya'daki mühimmat deposu patlamaları arasında bağlantı olabileceğini öne sürmüştü. RUSYA İDDİALARI REDDETTİ Bulgaristan 'daki patlamalarla ilgili soruşturmalarda Rusya'nın rolü bulunduğuna yönelik iddialar Moskova tarafından kabul edilmedi. Rusya, Bulgar makamlarının ortaya attığı suçlamaları reddetti. Gözden Kaçmasın NATO’yu alarma geçiren hamle! Putin neyi test etti? Denizin yüzlerce metre altında ne oldu? Haberi görüntüle Haberlerimizi Google’da Takip Edin Gelişmelerden anında haberdar olun. Gözden Kaçmasın NATO’yu alarma geçiren hamle! Putin neyi test etti? Denizin yüzlerce metre altında ne oldu? Haberi görüntüle × GÜNDEM DÜNYA BİGPARA ANASAYFA BORSA DÖVİZ ALTIN VİOP&amp;VARANT ANALİZ KOBİ KRİPTO PARALAR SPOR ARENA ANASAYFA FUTBOL BASKETBOL VOLEYBOL CANLI SKOR KELEBEK ANASAYFA EKRANDA HAYAT SEYAHAT STİL FAKİR HAUSGERATE İLE LEZZETLİ TARİFLER SAĞLIK YAŞAM ANASAYFA CUMARTESİ PAZAR LEZZETLİ HAYAT ÇOCUKLA HAYAT SEYAHAT YAZARLAR RESMİ İLANLAR ASTROLOJİ TÜMÜ EKONOMİ TV REHBERİ MAHMURE HÜRRİYET AİLE VİDEO ASTROLOJİ HESAPLAMA ARAÇLARI BULMACA EN İYİ ON LEZİZZ TEKNOLOJİ FOTO GALERİ RAMAZAN KİTAP SANAT HAVA DURUMU AV</t>
+          <t>Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bunlar da ilginizi çekebilir Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Bunlar da ilginizi çekebilir Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 Etiket: Kara para aklama Yorum (0) En popüler En yeni Duygularınızı paylaşmak için lütfen bir yorum bırakın! İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html Duygularınızı paylaşmak için lütfen bir yorum bırakın! Ana sayfa Ekonomi Yatırım - Finans Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. ÇİN - "Bu benim param, neden gönderemiyorum?", görünüşte basit bir soru olsa da, bankaların "kara para aklama karşıtı" ve "dolandırıcılık karşıtı" bahanesiyle büyük nakit işlemlerine yönelik kısıtlamaları giderek sıkılaştırması nedeniyle birçok Çin vatandaşı için baş ağrısı yaratıyor. VietNamNet•13/09/2026 Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bunlar da ilginizi çekebilir Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Bunlar da ilginizi çekebilir Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 Etiket: Kara para aklama Yorum (0) En popüler En yeni Duygularınızı paylaşmak için lütfen bir yorum bırakın! İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bunlar da ilginizi çekebilir Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Bunlar da ilginizi çekebilir Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Bulgaristan'da patlama: Silah deposunda yangın çıktı Bulgaristan'da patlama: Silah deposunda yangın çıktı Hürriyet Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı. Patlamanın nedeni henüz bilinmiyor. En Son Haberler - Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı. HABER MERKEZİ/İHA Oluşturulma Tarihi: Eylül 12, 2026 10:53 2dk okuma Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı. Google’da tercih edilen kaynak olarak ekleyin Haberin Devamı Bulgaristan'ın Gabrovo bölgesinde gece saatlerinde silah deposunda patlama meydana geldi. Tsareva Livada köyü yakınlarında özel silah şirketi EMCO'ya ait depoda yaşanan patlamanın ardından yangın çıktı. Gabrovo Valisi Kristina Sidorova, alevlerin depolama alanı içinde yayıldığını belirterek, "Yangın fabrikanın depolama alanının sınırları içinde. Depodan depoya yayılıyor" dedi. ALEVLER DEPOLAR ARASINDA YAYILDI Yerel basında yer alan haberlere göre yangın, EMCO'nun tesislerinden birinde çıktı. Patlamanın ardından başlayan yangının depolama alanındaki diğer bölümlere yayıldığı bildirildi. Şirketin aynı zamanda geçtiğimiz ay başka bir tesisinde de patlama yaşadığı aktarıldı. Gebrev ve şirketi, geçmiş yıllarda Bulgaristan'daki mühimmat deposu patlamalarıyla ilgili soruşturmaların merkezinde yer aldı. BULGARİSTAN'DAN 6 RUS VATANDAŞINA TUTUKLAMA EMRİ Bulgaristan, 2024 yılında EMCO'ya ait silah depolarının imha edilmesine karıştıkları iddiasıyla 6 Rus vatandaşı hakkında tutuklama emri çıkarmıştı. Söz konusu depolarda 2011-2020 yılları arasında Ukrayna ve Gürcistan'a ihraç edilmek üzere mühimmat bulunduğu belirtilmişti. Dönemin Bulgar savcıları, ülkedeki mühimmat deposu patlamaları ile 2015 yılında Emilian Gebrev'e yönelik zehirleme girişimi ve 2014'te Çekya'daki mühimmat deposu patlamaları arasında bağlantı olabileceğini öne sürmüştü. RUSYA İDDİALARI REDDETTİ Bulgaristan 'daki patlamalarla ilgili soruşturmalarda Rusya'nın rolü bulunduğuna yönelik iddialar Moskova tarafından kabul edilmedi. Gözden Kaçmasın NATO’yu alarma geçiren hamle! Haberi görüntüle Haberle ilgili daha fazlası: #Bulgaristan #Patlama #Silah Deposu HABER MERKEZİ/İHA Oluşturulma Tarihi: Eylül 12, 2026 10:53 2dk okuma Bulgaristan'ın Gabrovo bölgesindeki bir silah deposunda patlamanın ardından yangın çıktı.</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ana sayfa Ekonomi Yatırım - Finans Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. ÇİN - "Bu benim param, neden gönderemiyorum?", görünüşte basit bir soru olsa da, bankaların "kara para aklama karşıtı" ve "dolandırıcılık karşıtı" bahanesiyle büyük nakit işlemlerine yönelik kısıtlamaları giderek sıkılaştırması nedeniyle birçok Çin vatandaşı için baş ağrısı yaratıyor. VietNamNet•13/09/2026 Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. Fotoğraf: Baidu Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.hurriyet.com.tr/dunya/bulgaristanda-patlama-silah-deposunda-yangin-cikti-43304219</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWUdoUHJCRWZaZEdNanVFWHRsZFp3QnNMNWlEeWI0X3p4MEJSalFXY1YxcDN2cUNETm5tdl90cGpaVVJtSkp2WXRJajd6THVlNk9pOU5PODNLTl9KQXhhbV9QMTAxNmdrVTYtS09EZXR4N0lfci10azVOUjRINFJ2OE53enFLM3NpbXc4dlRDUkpTcF9aekFrNVNuaWRfUEhvNk5POXVJMkxhRlJaSkFfNA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>daki mühimmat deposu | ülkedeki mühimmat deposu | Silah Deposu</t>
-        </is>
-      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr"/>
@@ -2726,7 +2827,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="n">
-        <v>88.25</v>
+        <v>90.5</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>3</v>
@@ -2735,7 +2836,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 05:39:50</t>
+          <t>2026-09-13 10:02:22</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -2750,12 +2851,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Yangın ve patlama sigortasına zorunlu olarak katılmak zorunda olan kuruluşlar.</t>
+          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Yangın ve patlama sigortasına zorunlu olarak katılmak zorunda olan kuruluşlar. Vietnam.vn</t>
+          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede sondakika.com</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2765,54 +2866,90 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>kuruluş</t>
+          <t>tesis</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Yangın ve patlama sigortasına zorunlu olarak katılmak zorunda olan kuruluşlar. Vietnam.vn</t>
+          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Son Güncelleme: 13.09.2026 13:02 Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Gün ağarınca ortaya çıkan hasarın boyutu ise dronla görüntülendi. Gerede ilçesi Karma Organize Sanayi Bölgesi'ndeki geri dönüşüm tesisinde, dün saat 19.00 sıralarında yangın çıktı. Tesisi saran alevleri fark edenlerin ihbarı üzerine adrese itfaiye, AFAD ve jandarma ekipleri sevk edildi. Yangında yaralanan 2 işçi, sağlıkçıların olay yerindeki ilk müdahalesi sonrası ambulanslarla kaldırıldıkları hastanede tedaviye alındı. Yangın, ekiplerin 5 saatlik çalışması sonrası kontrol altına alındı. Gece boyu süren soğutma çalışmaları sonrası yangın, sabaha karşı tamamen söndürüldü. Hasarın boyutu da gün ağarınca ortaya çıktı. Tesiste oluşan hasar dronla görüntülendi. Yangının çıkış nedeninin belirlenmesi için soruşturma sürüyor. Kaynak: DHA BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Gün ağarınca ortaya çıkan hasarın boyutu ise dronla görüntülendi. Gerede ilçesi Karma Organize Sanayi Bölgesi'ndeki geri dönüşüm tesisinde, dün saat 19.00 sıralarında yangın çıktı. Tesisi saran alevleri fark edenlerin ihbarı üzerine adrese itfaiye, AFAD ve jandarma ekipleri sevk edildi. Yangında yaralanan 2 işçi, sağlıkçıların olay yerindeki ilk müdahalesi sonrası ambulanslarla kaldırıldıkları hastanede tedaviye alındı. Yangın, ekiplerin 5 saatlik çalışması sonrası kontrol altına alındı. Gece boyu süren soğutma çalışmaları sonrası yangın, sabaha karşı tamamen söndürüldü. Hasarın boyutu da gün ağarınca ortaya çıktı. Tesiste oluşan hasar dronla görüntülendi. Yangının çıkış nedeninin belirlenmesi için soruşturma sürüyor. Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Gün ağarınca ortaya çıkan hasarın boyutu ise dronla görüntülendi. Gerede ilçesi Karma Organize Sanayi Bölgesi'ndeki geri dönüşüm tesisinde, dün saat 19.00 sıralarında yangın çıktı. Tesisi saran alevleri fark edenlerin ihbarı üzerine adrese itfaiye, AFAD ve jandarma ekipleri sevk edildi. Yangında yaralanan 2 işçi, sağlıkçıların olay yerindeki ilk müdahalesi sonrası ambulanslarla kaldırıldıkları hastanede tedaviye alındı. Yangın, ekiplerin 5 saatlik çalışması sonrası kontrol altına alındı. Gece boyu süren soğutma çalışmaları sonrası yangın, sabaha karşı tamamen söndürüldü. Hasarın boyutu da gün ağarınca ortaya çıktı. Tesiste oluşan hasar dronla görüntülendi. Yangının çıkış nedeninin belirlenmesi için soruşturma sürüyor.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Yangın ve patlama sigortasına zorunlu olarak katılmak zorunda olan kuruluşlar. Yangın ve patlama sigortasına zorunlu olarak katılmak zorunda olan kuruluşlar. Vietnam.vn Yangın ve patlama sigortasına zorunlu olarak katılmak zorunda olan kuruluşlar.</t>
+          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede sondakika.com Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Son Güncelleme: 13.09.2026 13:02 Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Gün ağarınca ortaya çıkan hasarın boyutu ise dronla görüntülendi. Gerede ilçesi Karma Organize Sanayi Bölgesi'ndeki geri dönüşüm tesisinde, dün saat 19.00 sıralarında yangın çıktı. Tesisi saran alevleri fark edenlerin ihbarı üzerine adrese itfaiye, AFAD ve jandarma ekipleri sevk edildi. Yangında yaralanan 2 işçi, sağlıkçıların olay yerindeki ilk müdahalesi sonrası ambulanslarla kaldırıldıkları hastanede tedaviye alındı. Yangın, ekiplerin 5 saatlik çalışması sonrası kontrol altına alındı. Gece boyu süren soğutma çalışmaları sonrası yangın, sabaha karşı tamamen söndürüldü. Hasarın boyutu da gün ağarınca ortaya çıktı. Tesiste oluşan hasar dronla görüntülendi. Yangının çıkış nedeninin belirlenmesi için soruşturma sürüyor. Kaynak: DHA BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPTDAzYkNKWjI2MzM3LUdfT3g3TkU3eGVhd252amFIMTBtMTRWQjVoWWUzVUtLM1VSUnluRTdTUm9vRURmeFFYX0RpcDdkWnRQOXRKaGc4STlIc1h3RlVfLUZpNWdMZ0ZIZm0wdldCYU1uSFluT2piSTZmTjlVdE9VNmpGejdmUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
+          <t>https://www.sondakika.com/amp/haber-bolu-gerede-de-geri-donusum-tesisi-yangini-sondu-2-20233092/</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Gerede ilçesi Karma Organize Sanayi</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>de geri dönüşüm tesisi</t>
+        </is>
+      </c>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
+          <t>firma yok</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>de geri dönüşüm tesisi Gerede ilçesi Karma Organize Sanayi Gerede Bolu Türkiye</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Gerede Organize Sanayi Bölgesi | Gerede Deri İhtisas OSB | Gerede Deri Sanayi Sitesi | Gerede Ticaret Ve Sanayi Odası</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Gerede Organize Sanayi Bölgesi</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>38.46153846153846 | 47.82608695652174 | 51.06382978723404 | 38.46153846153846</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>Depo</t>
+        </is>
+      </c>
       <c r="AA5" s="2" t="n">
-        <v>78.14</v>
+        <v>192</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>4</v>
@@ -2821,12 +2958,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 04:45:19</t>
+          <t>2026-09-12 17:46:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2836,12 +2973,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hanoi polisi, An Khanh beldesindeki fabrika yangını hakkında bilgi verdi.</t>
+          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Hanoi polisi, An Khanh beldesindeki fabrika yangını hakkında bilgi verdi. Vietnam.vn</t>
+          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı 24 Saat Gazetesi Ankara</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -2851,58 +2988,86 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo, fabrika</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>fabrika | depo</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Hanoi polisi, An Khanh beldesindeki fabrika yangını hakkında bilgi verdi. Vietnam.vn</t>
+          <t>www.24saatgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.24saatgazetesi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.24saatgazetesi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Hanoi polisi, An Khanh beldesindeki fabrika yangını hakkında bilgi verdi. Hanoi polisi, An Khanh beldesindeki fabrika yangını hakkında bilgi verdi. Vietnam.vn Hanoi polisi, An Khanh beldesindeki fabrika yangını hakkında bilgi verdi.</t>
+          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı 24 Saat Gazetesi Ankara www.24saatgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.24saatgazetesi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>browser_error</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOU1VmRFhhblhaN0c1SFhKbmppcnNBek5WTmd3ZmhLbC15Mno3T3N3ZGRGMVE1Z2RqbTd1VXBCd0F6by1ROTlvVXpXeGhqTnhsSnBTWmN4M09vUjhYaWExZHJkeWU2MjhERl9GT3Fwa2x1M0F6OG1SSjh5VjZNb1g5WFhPUDhFVmphZmxuUnQ1VzE?oc=5&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>https://www.24saatgazetesi.com/son-dakika-bolu-geredede-fabrika-yangini-geri-donusum-deposu-alev-aldi-1-isci-yaralandi</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Geri dönüşüm deposu</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr"/>
-      <c r="V6" s="2" t="inlineStr"/>
-      <c r="W6" s="2" t="inlineStr"/>
+          <t>firma yok</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>Geri dönüşüm deposu Gerede Bolu Türkiye</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>BOLPET PLAST GERİ DÖNÜŞÜM</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>BOLPET PLAST GERİ DÖNÜŞÜM</t>
+        </is>
+      </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>77.41935483870968</t>
+        </is>
+      </c>
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="n">
-        <v>74.34</v>
+        <v>191.27</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>5</v>
@@ -2911,7 +3076,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 07:32:59</t>
+          <t>2026-09-12 18:12:27</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -2926,12 +3091,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Yangın Güvenliği Reasürans Tesisi, 19,6 Milyar Sterlinlik 730 Riske Teminat Sağladı</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Yangın Güvenliği Reasürans Tesisi, 19,6 Milyar Sterlinlik 730 Riske Teminat Sağladı sigortahaber.com</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı Türkiye Gazetesi</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -2941,44 +3106,52 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>fabrika, tesis</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Yangın Güvenliği Reasürans Tesisi, 19,6 Milyar Sterlinlik 730 Riske Teminat Sağladı sigortahaber.com</t>
+          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangın kısa sürede büyüyerek tesisi sardı. Zaman zaman patlamaların da yaşandığı yangın 4 saatin ardından kontrol altına alınırken, 2 fabrika işçisinin hafif şekilde yaralandığı öğrenildi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangın kısa sürede büyüyerek tesisi sardı. Zaman zaman patlamaların da yaşandığı yangın 4 saatin ardından kontrol altına alınırken, 2 fabrika işçisinin hafif şekilde yaralandığı öğrenildi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangın kısa sürede büyüyerek tesisi sardı. Zaman zaman patlamaların da yaşandığı yangın 4 saatin ardından kontrol altına alınırken, 2 fabrika işçisinin hafif şekilde yaralandığı öğrenildi. Giriş: 12 Eylül, 2026 - 21:12 | Güncelleme: 12 Eylül, 2026 - 23:15 Boluda geri dönüşüm fabrikası yanıyor! Alevler tüm tesisi sardı ÖNERİLEN HABERLER 3. SAYFA Antalya'da orman yangını! Ekipler bölgeye 2 saatte ulaşabildi 3. SAYFA Antalya'da orman yangını! Ekipler bölgeye 2 saatte ulaşabildi Editör : SİNEM GÖNEN | Kaynak: İHLAS HABER AJANSI Yayın Tarihi | 12 Eylül, 2026 - 21:12 Haberle İlgili Daha Fazlası 3. Sayfa Haber Verin Editör masamıza bilgi ve materyal göndermek için tıklayın Kaçırmayın Ücretsiz üye olun, gündemi şekillendiren gelişmeleri önce siz duyun Ev almak isteyenlere 3 milyon TL'ye kadar faizsiz ... Kaydet Togg'un yeni modeli T6X'e sürpriz talip! Piyasaya ... Kaydet Kâr payı oranlarında son durum: 500 bin TL’nin ayl... Kaydet Çiftçinin imdadına TMO yetişti! Tüccarın 2 katına ... Kaydet Alman Meclisi'ne Türkiye önerisi! "Ankara'nın hare... Kaydet İsmail Kapan Siyonist İsrail için alan daralıyor!.. Kaydet Rahim Er Yunanistan’ı düşman görmek! Kaydet Sevil Nuriyeva Siyasetin sabrı, devletin aklı Kaydet İsa Karakaş "Yarın bana kim bakacak?" sorusuna devlet sigortası! Kaydet Sadık Söztutan Evlat Kaydet 'Practical magic' yeniden geldi Kaydet Şampiyonlar Ligi'nde puan durumu belli oldu Kaydet 4.1 milyar liralık tarımsal destek ödemesi hesaplara yatıyor Kaydet TCBM ANKETİ YAYINLANDI! Kaydet Cari dengede temmuzda fazla verdi Kaydet Bize Haber Verin Editör masasıyla bilgi ve materyal paylaşma</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Yangın Güvenliği Reasürans Tesisi, 19,6 Milyar Sterlinlik 730 Riske Teminat Sağladı Yangın Güvenliği Reasürans Tesisi, 19,6 Milyar Sterlinlik 730 Riske Teminat Sağladı sigortahaber.com Yangın Güvenliği Reasürans Tesisi, 19,6 Milyar Sterlinlik 730 Riske Teminat Sağladı sigortahaber.com</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı Türkiye Gazetesi Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangın kısa sürede büyüyerek tesisi sardı. Zaman zaman patlamaların da yaşandığı yangın 4 saatin ardından kontrol altına alınırken, 2 fabrika işçisinin hafif şekilde yaralandığı öğrenildi. Giriş: 12 Eylül, 2026 - 21:12 | Güncelleme: 12 Eylül, 2026 - 23:15 Boluda geri dönüşüm fabrikası yanıyor! Alevler tüm tesisi sardı ÖNERİLEN HABERLER 3. SAYFA Antalya'da orman yangını! Ekipler bölgeye 2 saatte ulaşabildi 3. Ekipler bölgeye 2 saatte ulaşabildi Editör : SİNEM GÖNEN | Kaynak: İHLAS HABER AJANSI Yayın Tarihi | 12 Eylül, 2026 - 21:12 Haberle İlgili Daha Fazlası 3. Kaydet Kâr payı oranlarında son durum: 500 bin TL’nin ayl... Kaydet Sevil Nuriyeva Siyasetin sabrı, devletin aklı Kaydet İsa Karakaş "Yarın bana kim bakacak?" sorusuna devlet sigortası!</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNOURrUGwzV1FnOW9fMURfWGhDNXBmdVJ6U2RMckxWZElvWEN2Q01SOXU4bGk5Tk1hSTlmdEZ6aEJ3ZFpwZ3B3aWxCMEYwZFpEa3NySmFLQUtSa1hVWGI0SjJmZzRrWWRTemkyNms0V3JTYlRmTElhenJBUWp6eDBHbU5LNGdSaUtaYUFzWkFuRHdUTHFVaXp6SGxHZ3BRZFJiYVRvUnNxTnJvZ21TLXJ0eGtfQnRMREJoLXRB?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>https://www.turkiyegazetesi.com.tr/3-sayfa/boluda-geri-donusum-fabrikasi-yaniyor-alevler-tum-tesisi-sardi-1815590</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Antalya | Bolu</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Yangın Güvenliği Reasürans Tesisi | Güvenliği Reasürans Tesisi</t>
+          <t>geri dönüşüm fabrikası | Alevler tüm tesisi | sürede büyüyerek tesisi</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr"/>
@@ -2992,7 +3165,7 @@
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="n">
-        <v>107.5</v>
+        <v>118.75</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>6</v>
@@ -3001,27 +3174,27 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 11:46:59</t>
+          <t>2026-09-12 19:11:09</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>para aklama</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın zulası patladı! Düğün altınları gizli adresten çıktı! 66 bilezik, metrelerci zincir ve dövizler el konuldu</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın zulası patladı! Düğün altınları gizli adresten çıktı! 66 bilezik, metrelerci zincir ve dövizler el konuldu SuperHaber</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı A Haber</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -3031,18 +3204,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>www.superhaber.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.superhaber.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.superhaber.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Bolu’nun Gerede ilçesindeki geri dönüşüm fabrikasında yangın çıktı. Bölgeye çok sayıda itfaiye ekipleri sevk edilirken, alevler kontrol altına alındı. 1 fabrika işçisi hafif şekilde yaralandı. Bolu’nun Gerede ilçesindeki geri dönüşüm fabrikasında yangın çıktı. Bölgeye çok sayıda itfaiye ekipleri sevk edilirken, alevler kontrol altına alındı. 1 fabrika işçisi hafif şekilde yaralandı. Bolu’nun Gerede ilçesindeki geri dönüşüm fabrikasında yangın çıktı. Bölgeye çok sayıda itfaiye ekipleri sevk edilirken, alevler kontrol altına alındı. 1 fabrika işçisi hafif şekilde yaralandı. Giriş Tarihi: 12 Eylül 2026 22:11 Son Güncelleme: 13 Eylül 2026 00:13 İHA | ahaber.com.tr Haber Merkezi Giriş Tarihi: 12 Eylül 2026 22:11 Son Güncelleme: 13 Eylül 2026 00:13 İHA | ahaber.com.tr Haber Merkezi Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında bilinmeyen nedenle yangın çıktı. Alevler kısa sürede fabrikanın büyük bölümüne yayılırken, olayda 1 işçi yaralandı. Yangın ekiplerin yoğun çalışmasının ardından kontrol altına alındı. Bolu 'nun Gerede Karma Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren geri dönüşüm tesisinde saat 19.00 sıralarında henüz belirlenemeyen nedenle yangın çıktı. Tesis içerisinde başlayan yangın, kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. (Foto: İHA) 1 İŞÇİ YARALANDI Durumun bildirilmesi üzerine olay yerine çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Olay yerine gelen itfaiye ekipleri, alevleri kontrol altına alabilmek amacıyla yoğun çalışma başlattı. Çıkan yangında 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi ambulansta yapılan tedavinin ardından hastaneye kaldırıldı. Foto: İHA YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Alevlerin tamamen sardığı fabrikada zaman zaman patlamaların da meydana geldiği bildirildi. Öte yandan, yangının boyutu ve ekiplerin bölgedeki müdahale çalışmaları yangının 4'üncü saatinde dronla da görüntülendi. Ayrıca, Bolu Valisi Abdulaziz Aydın ve Gerede Kaymakamı Fatih Kaya fabrikada incelemelerde bulunarak yetkililerden bilgi aldı. KONTROL ALTINA ALINDI Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır. Bölgede soğutma çalışmaları ile gerekli güvenlik tedbirleri aralıksız sürdürülmektedir." denildi. Bolu 'nun Gerede Karma Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren geri dönüşüm tesisinde saat 19.00 sıralarında henüz belirlenemeyen nedenle yangın çıktı. Tesis içerisinde başlayan yangın, kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. (Foto: İHA) 1 İŞÇİ YARALANDI Durumun bildirilmesi üzerine olay yerine çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Olay yerine gelen itfaiye ekipleri, alevleri kontrol altına alabilmek amacıyla yoğun çalışma başlattı. Çıkan yangında 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi ambulansta yapılan tedavinin ardından hastaneye kaldırıldı. Foto: İHA YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Alevlerin tamamen sardığı fabrikada zaman zaman patlamaların da meydana geldiği bildirildi. Öte yandan, yangının boyutu ve ekiplerin bölgedeki müdahale çalışmaları yangının 4'üncü saatinde dronla da görüntülendi. Ayrıca, Bolu Valisi Abdulaziz Aydın ve Gerede Kaymakamı Fatih Kaya fabrikada incelemelerde bulunarak yetkililerden bilgi aldı. KONTROL ALTINA ALINDI Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır. Bölgede soğutma çalışmaları ile gerekli güvenlik tedbirleri aralıksız sürdürülmektedir." denildi. Önceki Haber Sakarya'da akran zorbalığı: 15 yaşındaki çocuğu depoya kilitleyip dakikalarca dövdüler Sonraki Haber Muş'ta kahreden olay: 13 yaşındaki çocuk gölette boğuldu Önceki Haber Sakarya'da akran zorbalığı: 15 yaşındaki çocuğu depoya kilitleyip dakikalarca dövdüler Sonraki Haber Muş'ta kahreden olay: 13 yaşındaki çocuk gölette boğuldu Mobil uygulamalarımızı indirin Bolu'da geri dönüşüm fabrikasında yangın! Alevler kontrol altına alındı: 1 işçi yaralı Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. (Foto: İHA) Durumun bildirilmesi üzerine olay yerine çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Olay yerine gelen itfaiye ekipleri, alevleri kontrol altına alabilmek amacıyla yoğun çalışma başlattı. Çıkan yangında 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi ambulansta yapılan tedavinin ardından hastaneye kaldırıldı. YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Alevlerin tamamen sardığı fabrikada zaman zaman patlamaların da meydana geldiği bildirildi. Öte yandan, yangının boyutu ve ekiplerin bölgedeki müdahale çalışmaları yangının 4'üncü saatinde dronla da görüntülendi. Ayrıca, Bolu Valisi Abdulaziz Aydın ve Gerede Kaymakamı Fatih Kaya fabrikada incelemelerde bulunarak yetkililerden bilgi aldı. Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır. Bölgede soğutma çalışmaları ile gerekli güvenlik tedbirleri aralıksız sürdürülmektedir." denildi.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın zulası patladı! Düğün altınları gizli adresten çıktı! 66 bilezik, metrelerci zincir ve dövizler el konuldu Vanlı Kara Haydar'ın zulası patladı! Düğün altınları gizli adresten çıktı! 66 bilezik, metrelerci zincir ve dövizler el konuldu SuperHaber www.superhaber.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.superhaber.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.superhaber.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı A Haber Bolu’nun Gerede ilçesindeki geri dönüşüm fabrikasında yangın çıktı. Bölgeye çok sayıda itfaiye ekipleri sevk edilirken, alevler kontrol altına alındı. 1 fabrika işçisi hafif şekilde yaralandı. Giriş Tarihi: 12 Eylül 2026 22:11 Son Güncelleme: 13 Eylül 2026 00:13 İHA | ahaber.com.tr Haber Merkezi Giriş Tarihi: 12 Eylül 2026 22:11 Son Güncelleme: 13 Eylül 2026 00:13 İHA | ahaber.com.tr Haber Merkezi Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında bilinmeyen nedenle yangın çıktı. Alevler kısa sürede fabrikanın büyük bölümüne yayılırken, olayda 1 işçi yaralandı. Yangın ekiplerin yoğun çalışmasının ardından kontrol altına alındı. Bolu 'nun Gerede Karma Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren geri dönüşüm tesisinde saat 19.00 sıralarında henüz belirlenemeyen nedenle yangın çıktı. Tesis içerisinde başlayan yangın, kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. Olay yerine gelen itfaiye ekipleri, alevleri kontrol altına alabilmek amacıyla yoğun çalışma başlattı. Çıkan yangında 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi ambulansta yapılan tedavinin ardından hastaneye kaldırıldı. Foto: İHA YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Alevlerin tamamen sardığı fabrikada zaman zaman patlamaların da meydana geldiği bildirildi. Öte yandan, yangının boyutu ve ekiplerin bölgedeki müdahale çalışmaları yangının 4'üncü saatinde dronla da görüntülendi. Ayrıca, Bolu Valisi Abdulaziz Aydın ve Gerede Kaymakamı Fatih Kaya fabrikada incelemelerde bulunarak yetkililerden bilgi aldı. KONTROL ALTINA ALINDI Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır. Önceki Haber Sakarya'da akran zorbalığı: 15 yaşındaki çocuğu depoya kilitleyip dakikalarca dövdüler Sonraki Haber Muş'ta kahreden olay: 13 yaşındaki çocuk gölette boğuldu Önceki Haber Sakarya'da akran zorbalığı: 15 yaşındaki çocuğu depoya kilitleyip dakikalarca dövdüler Sonraki Haber Muş'ta kahreden olay: 13 yaşındaki çocuk gölette boğuldu Mobil uygulamalarımızı indirin Bolu'da geri dönüşüm fabrikasında yangın! Alevler kontrol altına alındı: 1 işçi yaralı Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -3052,19 +3229,31 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.superhaber.com/amp/vanli-kara-haydarin-zulasi-patladi-dugun-altinlari-gizli-adresten-cikti-66-bilezik-584777</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
+          <t>https://www.ahaber.com.tr/yasam/2026/09/12/boluda-geri-donusum-fabrikasinda-yangin</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Bolu | Muş | Sakarya</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>nun Gerede Karma Organize Sanayi</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr"/>
@@ -3078,7 +3267,7 @@
       <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="n">
-        <v>119.4</v>
+        <v>126.75</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>7</v>
@@ -3087,12 +3276,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 00:58:25</t>
+          <t>2026-09-12 19:09:34</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3102,12 +3291,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Deri fabrikasında korkutan yangın</t>
+          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Deri fabrikasında korkutan yangın Hürriyet</t>
+          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. Vietnam.vn</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -3127,46 +3316,34 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. Son Dakika Haberleri İnternet - Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. İHA Oluşturulma Tarihi: Eylül 12, 2026 03:58 Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. Haberlerimizi Google’da Takip Edin Gelişmelerden anında haberdar olun. Google’da tercih edilen kaynak olarak ekleyin Haberin Devamı Yangın , Gerede Deri İhtisas Organize Sanayi Bölgesi’nde faaliyet gösteren deri fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikanın baca kısmında çıkan yangını fark edenlerin ihbarı üzerine bölgeye itfaiye ve jandarma ekipleri sevk edildi. İtfaiye ekipleri, alevlere müdahale ederek yangının büyümesini önledi. Yangın, fabrikanın diğer bölümlerine sıçramadan kontrol altına alındı. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. Haberlerimizi Google’da Takip Edin Gelişmelerden anında haberdar olun. Deri fabrikasında korkutan yangın Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. Güncelleme Tarihi: Eylül 12, 2026 03:58 Yangın , Gerede Deri İhtisas Organize Sanayi Bölgesi’nde faaliyet gösteren deri fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikanın baca kısmında çıkan yangını fark edenlerin ihbarı üzerine bölgeye itfaiye ve jandarma ekipleri sevk edildi. İtfaiye ekipleri, alevlere müdahale ederek yangının büyümesini önledi. Yangın, fabrikanın diğer bölümlerine sıçramadan kontrol altına alındı. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı.</t>
+          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. Vietnam.vn</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Deri fabrikasında korkutan yangın Deri fabrikasında korkutan yangın Hürriyet Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. Son Dakika Haberleri İnternet - Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. İHA Oluşturulma Tarihi: Eylül 12, 2026 03:58 Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. Google’da tercih edilen kaynak olarak ekleyin Haberin Devamı Yangın , Gerede Deri İhtisas Organize Sanayi Bölgesi’nde faaliyet gösteren deri fabrikasında meydana geldi. Edinilen bilgilere göre, fabrikanın baca kısmında çıkan yangını fark edenlerin ihbarı üzerine bölgeye itfaiye ve jandarma ekipleri sevk edildi. İtfaiye ekipleri, alevlere müdahale ederek yangının büyümesini önledi. Yangın, fabrikanın diğer bölümlerine sıçramadan kontrol altına alındı. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. Deri fabrikasında korkutan yangın Bolu’nun Gerede ilçesinde deri üretimi yapan fabrikanın bacasında çıkan yangın, itfaiye ekiplerinin müdahalesiyle fabrikaya sıçramadan kontrol altına alındı. Güncelleme Tarihi: Eylül 12, 2026 03:58 Yangın , Gerede Deri İhtisas Organize Sanayi Bölgesi’nde faaliyet gösteren deri fabrikasında meydana geldi.</t>
+          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. Vietnam.vn An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.hurriyet.com.tr/gundem/deri-fabrikasinda-korkutan-yangin-43304133</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Gerede Deri İhtisas Organize Sanayi</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZUNZRWJSaW1nVkNPSkJxUW5VV2NtcXBHX0tjWEdoWm5kSG1rM3NLaW9QeE54V3ZucEp6Mm13eERSRThmbG12U2cxdG9NTDJWdTBaUTRvM2dGMU5DOVRsUGxndUtGUGNGczg0VVhtSjkxWDAyVFBRNS1QbTRLcWdSQ3RxRFlPVXpCYmo4eE9aS1FQMUU?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr"/>
@@ -3180,7 +3357,7 @@
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="n">
-        <v>100</v>
+        <v>103.22</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>8</v>
@@ -3189,12 +3366,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 20:57:33</t>
+          <t>2026-09-13 05:48:46</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3204,12 +3381,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hanoi'nin An Khanh beldesinde, konut ve fabrikanın bir arada bulunduğu binada çıkan yangın söndürüldü.</t>
+          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Hanoi'nin An Khanh beldesinde, konut ve fabrikanın bir arada bulunduğu binada çıkan yangın söndürüldü. Vietnam.vn</t>
+          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti Eskişehir Durum</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3219,35 +3396,35 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>tesis</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Hanoi'nin An Khanh beldesinde, konut ve fabrikanın bir arada bulunduğu binada çıkan yangın söndürüldü. Vietnam.vn</t>
+          <t>Eskişehir’de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle diğer alanlara sıçramadan kontrol altına alınarak söndürüldü. Eskişehir’de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle diğer alanlara sıçramadan kontrol altına alınarak söndürüldü. Eskişehir’de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle diğer alanlara sıçramadan kontrol altına alınarak söndürüldü.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Hanoi'nin An Khanh beldesinde, konut ve fabrikanın bir arada bulunduğu binada çıkan yangın söndürüldü. Hanoi'nin An Khanh beldesinde, konut ve fabrikanın bir arada bulunduğu binada çıkan yangın söndürüldü. Vietnam.vn Hanoi'nin An Khanh beldesinde, konut ve fabrikanın bir arada bulunduğu binada çıkan yangın söndürüldü.</t>
+          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti Eskişehir Durum Eskişehir’de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle diğer alanlara sıçramadan kontrol altına alınarak söndürüldü.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNN3ZROWlMcnBUeU0tT0JHc0t4R2lSMkpFMHh4ZldWWHF4QnRaNXl0blV1MnA3ZENydnFqMkN6U3RDS1hIMGJRWklqZHlWbGNYWDlteFNfYWtpQUNXLWpOQjlXc0ZJbHFaU3BRM3VobmVYbzFZNllaWG1JeWNmRC1ZeGQyVHV0WGdWQVB2djQydmRaY09tWDROTHdR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>https://eskisehirdurum.com/eskisehir-gundem/eskisehirde-tesis-yangini-ekipler-hizla-mudahale-etti/804268</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
@@ -3256,7 +3433,7 @@
       <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr"/>
@@ -3270,7 +3447,7 @@
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="n">
-        <v>96.38</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>9</v>
@@ -3279,12 +3456,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:58:45</t>
+          <t>2026-09-13 09:04:00</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3294,12 +3471,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Söke'de KİPAŞ kağıt fabrikasındaki yangın itfaiyenin hızlı müdahalesiyle sınırlı kaldı</t>
+          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Söke'de KİPAŞ kağıt fabrikasındaki yangın itfaiyenin hızlı müdahalesiyle sınırlı kaldı Aksiyon.com.TR</t>
+          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Milli İrade Gazetesi</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3309,22 +3486,18 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>tesis</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Söke’deki KİPAŞ kağıt fabrikasında çıkan yangına Aydın Büyükşehir Belediyesi itfaiye ekipleri hızlı müdahale etti ve yangın kontrol altına alındı. Söke’deki KİPAŞ kağıt fabrikasında çıkan yangına Aydın Büyükşehir Belediyesi itfaiye ekipleri hızlı müdahale etti ve yangın kontrol altına alındı. Söke’deki KİPAŞ kağıt fabrikasında çıkan yangına Aydın Büyükşehir Belediyesi itfaiye ekipleri hızlı müdahale etti ve yangın kontrol altına alındı. yangının tespiti ve müdahale: Aydın’ın Söke ilçesinde faaliyet gösteren KİPAŞ Kağıt Fabrikası nda henüz belirlenemeyen bir nedenle yangın çıktı. Olayın fark edilmesi üzerine durum yetkililere bildirildi ve Aydın Büyükşehir Belediyesi İtfaiye Daire Başkanlığı ekipleri kısa sürede bölgeye sevk edilerek müdahaleye başladı. İtfaiye ekipleri, hızlı erişim ve koordineli söndürme çalışmalarıyla alevlere anında müdahale etti. Ekiplerin zamanında ve sistemli söndürme çalışmaları yangının yayılmasını engelledi. müdahalenin etkisi ve soğutma çalışmaları: Müdahale sonucunda yangın kontrol altına alınırken, olay yerinde soğutma çalışmaları sürüyor. Ekipler, alevlerin yeniden parlamasını önlemek ve çevre güvenliğini sağlamak için bölgedeki sıcak noktaları tespit edip soğutma uygulamalarına devam ediyor. Yetkililer ve itfaiye ekipleri olay yerindeki çalışmalarını halen sürdürüyor. Yangının çıkış nedeniyle ilgili inceleme devam ederken, fabrikanın çevresinde olası risklere karşı alınan önlemlerle yangının daha geniş bir alana yayılmasının önüne geçildi. SÖKE’DEKİ KAĞIT FABRİKASI YANGININA İTFAİYEDEN HIZLI MÜDAHALE 1 Anlaşmazlık yaşamlarını aldı: Maltepe'de öldürülen ev sahipleri defnedildi Anlaşmazlık yaşamlarını aldı: Maltepe'de öldürülen ev sahipleri defnedildi 2 Kars çevre yolunda sert çarpışma: 6 kişi hastaneye kaldırıldı Kars çevre yolunda sert çarpışma: 6 kişi hastaneye kaldırıldı 3 Düzce'de bir haftada suç çözüm oranı yüzde 99'a çıktı Düzce'de bir haftada suç çözüm oranı yüzde 99'a çıktı 4 Muş’ta kayıp Suat Balkaya için Karasu Nehri çevresinde kapsamlı arama Muş’ta kayıp Suat Balkaya için Karasu Nehri çevresinde kapsamlı arama 5 Ezgi Apartmanı davasında bilirkişi raporları kolon kesme iddiasını reddetti Ezgi Apartmanı davasında bilirkişi raporları kolon kesme iddiasını reddetti 6 Samsun'da cadde kenarında çocuk otomobilin çarpmasıyla hafif yaralandı Samsun'da cadde kenarında çocuk otomobilin çarpmasıyla hafif yaralandı 7 Sivaslı'da meşelik yangını yoğun müdahaleyle kontrol altına alındı Sivaslı'da meşelik yangını yoğun müdahaleyle kontrol altına alındı Söke'de KİPAŞ kağıt fabrikasındaki yangın itfaiyenin hızlı müdahalesiyle sınırlı kaldı yangının tespiti ve müdahale: Söke’deki KİPAŞ kağıt fabrikasında çıkan yangına Aydın Büyükşehir Belediyesi itfaiye ekipleri hızlı müdahale etti ve yangın kontrol altına alındı. Aydın’ın Söke ilçesinde faaliyet gösteren KİPAŞ Kağıt Fabrikası nda henüz belirlenemeyen bir nedenle yangın çıktı. Olayın fark edilmesi üzerine durum yetkililere bildirildi ve Aydın Büyükşehir Belediyesi İtfaiye Daire Başkanlığı ekipleri kısa sürede bölgeye sevk edilerek müdahaleye başladı. İtfaiye ekipleri, hızlı erişim ve koordineli söndürme çalışmalarıyla alevlere anında müdahale etti. Ekiplerin zamanında ve sistemli söndürme çalışmaları yangının yayılmasını engelledi. Müdahale sonucunda yangın kontrol altına alınırken, olay yerinde soğutma çalışmaları sürüyor. Ekipler, alevlerin yeniden parlamasını önlemek ve çevre güvenliğini sağlamak için bölgedeki sıcak noktaları tespit edip soğutma uygulamalarına devam ediyor. Yetkililer ve itfaiye ekipleri olay yerindeki çalışmalarını halen sürdürüyor. Yangının çıkış nedeniyle ilgili inceleme devam ederken, fabrikanın çevresinde olası risklere karşı alınan önlemlerle yangının daha geniş bir alana yayılmasının önüne geçildi. SÖKE’DEKİ KAĞIT FABRİKASI YANGININA İTFAİYEDEN HIZLI MÜDAHALE Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. aksiyon.com.tr Gündem'deyim ama spesifik olarak eğitim ve sağlık politikalarındaki güncel gelişmelere odaklanıyorum. Öğrenmeye açık, meraklı ve enerjik bir yapım var. 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
+          <t>Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. ASAYİŞ Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 13.09.2026 - 12:04 Eskişehir’de faaliyet gösteren bir geri dönüşüm tesisinde çıkan yangın, Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekiplerinin müdahalesiyle çevre alanlara sıçramadan kontrol altına alınarak söndürüldü. Yangının çıkış nedeninin belirlenmesi amacıyla inceleme başlatıldı. Eskişehir'de sanayi alanında faaliyet yürüten bir geri dönüşüm tesisinde henüz belirlenemeyen bir sebepten dolayı yangın meydana geldi. Dumanları Görenler İhbar Etti Tesis içerisindeki malzemelerin alev almasıyla birlikte yükselen yoğun dumanları fark eden çevredeki vatandaşlar ve tesis çalışanları durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine bölgeye kısa sürede polis ve itfaiye ekipleri sevk edildi. Alevler Sıçramadan Kontrol Altına Alındı Olay yerine ulaşan Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekipler, yangına çok yönlü olarak müdahalede bulundu. İtfaiye personelinin yürüttüğü yoğun ve koordineli çalışma neticesinde alevler tesisin diğer bölümlerine ve çevredeki yapılara sıçramadan söndürüldü. Yangın sonrası soğutma çalışmaları tamamlanırken, olayda yaralanan ya da dumandan etkilenen kimsenin olmadığı öğrenildi. Çıkış Nedeni Araştırılıyor Yangının ardından tesis içerisinde oluşan maddi hasarın tespiti yapılırken, yangının çıkış kaynağı ve sebebinin netleştirilmesi amacıyla yetkililer tarafından geniş çaplı inceleme başlatıldı. Kaynak: Haber Merkezi Bunlar</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Söke'de KİPAŞ kağıt fabrikasındaki yangın itfaiyenin hızlı müdahalesiyle sınırlı kaldı Söke'de KİPAŞ kağıt fabrikasındaki yangın itfaiyenin hızlı müdahalesiyle sınırlı kaldı Aksiyon.com.TR Söke’deki KİPAŞ kağıt fabrikasında çıkan yangına Aydın Büyükşehir Belediyesi itfaiye ekipleri hızlı müdahale etti ve yangın kontrol altına alındı. yangının tespiti ve müdahale: Aydın’ın Söke ilçesinde faaliyet gösteren KİPAŞ Kağıt Fabrikası nda henüz belirlenemeyen bir nedenle yangın çıktı. Olayın fark edilmesi üzerine durum yetkililere bildirildi ve Aydın Büyükşehir Belediyesi İtfaiye Daire Başkanlığı ekipleri kısa sürede bölgeye sevk edilerek müdahaleye başladı. İtfaiye ekipleri, hızlı erişim ve koordineli söndürme çalışmalarıyla alevlere anında müdahale etti. Ekiplerin zamanında ve sistemli söndürme çalışmaları yangının yayılmasını engelledi. müdahalenin etkisi ve soğutma çalışmaları: Müdahale sonucunda yangın kontrol altına alınırken, olay yerinde soğutma çalışmaları sürüyor. Ekipler, alevlerin yeniden parlamasını önlemek ve çevre güvenliğini sağlamak için bölgedeki sıcak noktaları tespit edip soğutma uygulamalarına devam ediyor. Yetkililer ve itfaiye ekipleri olay yerindeki çalışmalarını halen sürdürüyor. Yangının çıkış nedeniyle ilgili inceleme devam ederken, fabrikanın çevresinde olası risklere karşı alınan önlemlerle yangının daha geniş bir alana yayılmasının önüne geçildi. SÖKE’DEKİ KAĞIT FABRİKASI YANGININA İTFAİYEDEN HIZLI MÜDAHALE 1 Anlaşmazlık yaşamlarını aldı: Maltepe'de öldürülen ev sahipleri defnedildi Anlaşmazlık yaşamlarını aldı: Maltepe'de öldürülen ev sahipleri defnedildi 2 Kars çevre yolunda sert çarpışma: 6 kişi hastaneye kaldırıldı Kars çevre yolunda sert çarpışma: 6 kişi hastaneye kaldırıldı 3 Düzce'de bir haftada suç çözüm oranı yüzde 99'a çıktı Düzce'de bir haftada suç çözüm oranı yüzde 99'a çıktı 4 Muş’ta kayıp Suat Balkaya için Karasu Nehri çevresinde kapsamlı arama Muş’ta kayıp Suat Balkaya için Karasu Nehri çevresinde kapsamlı arama 5 Ezgi Apartmanı davasında bilirkişi raporları kolon kesme iddiasını reddetti Ezgi Apartmanı davasında bilirkişi raporları kolon kesme iddiasını reddetti 6 Samsun'da cadde kenarında çocuk otomobilin çarpmasıyla hafif yaralandı Samsun'da cadde kenarında çocuk otomobilin çarpmasıyla hafif yaralandı 7 Sivaslı'da meşelik yangını yoğun müdahaleyle kontrol altına alındı Sivaslı'da meşelik yangını yoğun müdahaleyle kontrol altına alındı Söke'de KİPAŞ kağıt fabrikasındaki yangın itfaiyenin hızlı müdahalesiyle sınırlı kaldı yangının tespiti ve müdahale: Söke’deki KİPAŞ kağıt fabrikasında çıkan yangına Aydın Büyükşehir Belediyesi itfaiye ekipleri hızlı müdahale etti ve yangın kontrol altına alındı. Aydın’ın Söke ilçesinde faaliyet gösteren KİPAŞ Kağıt Fabrikası nda henüz belirlenemeyen bir nedenle yangın çıktı. Müdahale sonucunda yangın kontrol altına alınırken, olay yerinde soğutma çalışmaları sürüyor. SÖKE’DEKİ KAĞIT FABRİKASI YANGININA İTFAİYEDEN HIZLI MÜDAHALE Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? TRT 1, 2 Ocak yayın planını değiştirdi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
+          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Milli İrade Gazetesi Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. ASAYİŞ Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü.</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -3334,61 +3507,37 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.aksiyon.com.tr/soke-de-kipas-kagit-fabrikasindaki-yangin-itfaiyenin-hizli-mudahalesiyle-sinirli-kaldi-353390</t>
+          <t>https://www.milliirade.com/geri-donusum-tesisinde-cikan-yangin-itfaiye-ekiplerince-sonduruldu</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Aydın | Bursa | Düzce | İstanbul | Muş</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Söke | Maltepe | Sivaslı</t>
-        </is>
-      </c>
+          <t>Eskişehir</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>KİPAŞ Kağıt Fabrikası</t>
-        </is>
-      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>KİPAŞ Kağıt Fabrikası Söke Aydın Türkiye</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Batı Kipaş Kağıt Fabrikası</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Batı Kipaş Kağıt Fabrikası</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>87.5</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="n">
-        <v>193.25</v>
+        <v>95.75</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>10</v>
@@ -3397,7 +3546,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:40:00</t>
+          <t>2026-09-13 03:22:15</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3407,17 +3556,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın düğünündeki altınlar bulundu! Hepsine el konuldu</t>
+          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın düğünündeki altınlar bulundu! Hepsine el konuldu Haber 7</t>
+          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı bolgegundemi.com</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3427,28 +3576,32 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın düğünündeki altınlar bulundu! Hepsine el konuldu Haber 7</t>
+          <t>www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Vanlı Kara Haydar'ın düğünündeki altınlar bulundu! Hepsine el konuldu Vanlı Kara Haydar'ın düğünündeki altınlar bulundu! Hepsine el konuldu Haber 7 Vanlı Kara Haydar'ın düğünündeki altınlar bulundu! Hepsine el konuldu Haber 7</t>
+          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı bolgegundemi.com www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQUVRsTE5OcERjaGZvMXp6dlppZ0JzNWlvWFNWeHdVY1VLSVZ4ci1mMHlKUUZZOGFnNkN4VVQxQlpaZ0U5Q1V5TGtuRDNUOE1TQl9RZlJ6NEhYS3ktMzJ5dEZCdW5rNWZTcmctTEV4c05nU1c2elpzc1o3c0tTQU55cktJNzNUQ2lDQUI3TTBSWEk2NUFpU01BRXBORm1lb2VQNkY0MXdtWFJ0MDRXYnd3Y9IBuAFBVV95cUxPYzFnUFZxenh1Y3NpWDBvZDdHbTJHaUs0ZDR6V19RM1AzUTI4a2NxTy1ta1F6ZUVwd1RCaEpfYTA5eGRFTzFIZDRjN1prem5rSWJLaHNyT0lpZkpuVE1ET0tyU0gyWk5nd2ZfUkViaGY0VjlJVHI1WVJtczFWaEpTT3cyZHVuMk0wdlV3Y0ZSa1VBcENXWEM5dG9sVXZNQVNONzVUb1lFaEwwa3JIc1V4WDJDUWFrQWF0?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.bolgegundemi.com/ekonomi/otomatik-finansal-paylasimda-banka-ve-elden-yatirim-farki-176836.html</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
@@ -3474,7 +3627,7 @@
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="n">
-        <v>62.52</v>
+        <v>50.46</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>11</v>
@@ -3483,7 +3636,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:33:42</t>
+          <t>2026-09-13 09:03:05</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -3498,12 +3651,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MASAK Hawala ve Alternatif Değer Transfer Sistemleri İçin Yeni Rehber Yayımladı</t>
+          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MASAK Hawala ve Alternatif Değer Transfer Sistemleri İçin Yeni Rehber Yayımladı FintekWins</t>
+          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı A Haber</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -3519,25 +3672,29 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>MASAK Hawala ve Alternatif Değer Transfer Sistemleri İçin Yeni Rehber Yayımladı FintekWins</t>
+          <t>İstanbul Cumhuriyet Başsavcılığının soruşturmasında MASAK verileri incelendi; 6 derneğe 2011-2026 döneminde yurt dışı bağlantılı milyonluk para girişleri ve 209 kurumsal transfer tespit edildi. İstanbul Cumhuriyet Başsavcılığının soruşturmasında MASAK verileri incelendi; 6 derneğe 2011-2026 döneminde yurt dışı bağlantılı milyonluk para girişleri ve 209 kurumsal transfer tespit edildi. İstanbul Cumhuriyet Başsavcılığının soruşturmasında MASAK verileri incelendi; 6 derneğe 2011-2026 döneminde yurt dışı bağlantılı milyonluk para girişleri ve 209 kurumsal transfer tespit edildi. AYNI KAYNAKLAR BİRDEN FAZLA DERNEĞİ FONLADI Üç dosyanın birlikte incelenmesi, bazı yabancı kaynakların birden fazla derneğe düzenli olarak para gönderdiğini ortaya koydu. EED/FEDEM'in HEVİ, LİSTAG ve SPoD'a 16 işlemde toplam 315 bin 278,23 euro gönderdiği belirlendi. İşlemlerin transfer tarihlerindeki toplam TL karşılığı yaklaşık 11,38 milyon lira olarak hesaplandı. ILGA-Europe'un HEVİ, Lambdaİstanbul, LİSTAG ve SPoD'a 37 işlemde toplam 234 bin 221,17 euro aktardığı kaydedildi. Bu işlemlerin TL karşılığının yaklaşık 7,69 milyon lira olduğu belirtildi. Diğer ortak finansman kaynakları ise şöyle sıralandı: Almanya Federal Cumhuriyeti ve Başkonsolosluğu: LİSTAG ve SPoD'a 9 işlemde 104 bin 98,92 euro Hollanda Dışişleri Bakanlığı: LİSTAG ve SPoD'a en az 5 işlemde 89 bin 687 euro ve 276 bin 500 lira ABD Dışişleri Bakanlığı: Pozitif- z ve SPoD'a 6 işlemde 45 bin 984,02 dolar Fransa Büyükelçiliği: HEVİ, Pozitif İz ve SPoD'a 4 işlemde 25 bin 706 euro German Marshall Fund: LİSTAG, Pozitif Yaşam ve SPoD'a 3 işlemde 63 bin 347 dolar International AIDS Society: Pozitif İz ve SPoD'a 6 işlemde 32 bin 320 dolar SWIFT KAYITLARINDA 3,3 MİLYON DOLARI AŞAN TRAFİK MASAK Veri İnceleme Tutanağındaki GİB SWIFT kayıtlarında, derneklerin farklı yıllara yayılan yurt dışı bağlantılı hesap hareketlerinin dolar karşılıklarına da yer verildi. Dernek İncelenen dönem Rapordaki toplam dolar karşılığı SPoD2012-2026 1.570.692,44 dolar HEVİ2018-2026 762.939,21 dolar Pozitif Yaşam-2011-20255 18.525,92 dolar LİSTAG2020-2026 314.220,89 dolar Lambdaİstanbul-2012-2026 103.650,93 dolar Pozitif İz-2022-2026 89.138,41 dolar Toplam3.359.167,80 dolar Böylece 6 derneğe ait GİB SWIFT kayıtlarında yer alan para hareketlerinin dolar karşılığı toplamı 3 milyon 359 bin 167,80 dolara ulaştı. Bu toplam, farklı yıllarda ve farklı para birimleriyle gerçekleştirilen işlemlerin tutanaktaki dolar karşılıklarından oluşuyor. 2021-2026 dönemine ilişkin 67,4 milyon liralık bankacılık analiziyle aynı kapsamı taşımadığı için iki rakamın birbirine eklenmemesi gerekiyor. PARA TRAFİĞİ 2011'E KADAR UZANDI SWIFT kayıtları, yurt dışı bağlantılı finansmanın yalnızca son yıllarla sınırlı olmadığını ortaya koydu. Pozitif Yaşam Derneğinin 2011, Lambdaİstanbul ile SPoD'un 2012 yılına kadar uzanan transfer kayıtları bulunduğu belirlendi. Eski kayıtlarda Pozitif Yaşam'a Avrupa Komisyonundan 47 bin 996,94 dolar, UNDP'den 2 bin 500 dolar ve Deutsche Gesellschaft bağlantılı kayıtlardan 5 işlemde 124 bin 786,02 dolar gönderildiği görüldü. SPoD'a ABD Dışişleri Bakanlığından farklı yıllarda 9 işlemle 113 bin 591,62 dolar, ILGA-Europe'tan 15 işlemle 61 bin 403,14 dolar ve EED/FEDEM'den 9 işlemle 167 bin 207,74 dolar aktarıldığı kaydedildi. MASAK TUTANAĞINDA ÇARPICI DEĞERLENDİRME MASAK verileri üzerinde hazırlanan inceleme tutanağında, söz konusu derneklere yurt dışı bağlantılı kişi ve kuruluşlar tarafından maddi destek sağlandığı belirtildi. Tutanakta, bu kaynaklar aracılığıyla cinsiyet değiştirmek isteyen kişilerin ameliyat masraflarının karşılandığı yönünde değerlendirmeye yer verildi. Derneklerin faaliyetleri dışında toplumsal yapının bozulmasına, toplum içerisinde görüş ayrılıklarının oluşmasına, aileler arasında kaygı meydana gelmesine, kamu düzeni ile toplumsal değerlere zarar verilmesine yönelik çalışmalar yürüttüğü iddiası da soruşturma kapsamında kayda geçirildi. Söz konusu ifadeler, soruşturma dosyasındaki inceleme ve değerlendirmeleri yansıtıyor. DERNEK HESAPLARINA MÜKERRER PARA AKIŞI Gerçek kişilerden yapılan para girişlerinin incelendiği ayrı analizde, gönderenlerin T.C. kimlik numarası kayıtları esas alındı ve aynı kişiye ait isim farklılıkları birleştirildi. En fazla işlem yapan isim, Lambdaİstanbul ile SPoD'a toplam 72 kez para gönderen Abdullah İkbal Arslanbaş oldu. Arslanbaş adına 37'si Lambda İstanbul'a, 35'i SPoD'a olmak üzere toplam 11 bin 535 liralık transfer kaydı bulundu. En fazla mükerrer işlem yapan kişiler şöyle sıralandı: Gönderen İşlem Toplam Dernek Abdullah İkbal Arslanbaş 72 11.535 TL Lambdaİstanbul ve SPoD Yasemin Öz 56 3.010 TL Lambdaİstanbul ve SPoD Aslı Meleş 54 25.324 TL LİSTAG Anıl Birkan 44 39.550 TL Pozitif İz Günseli Dum 40 5.680 TL LİSTAG Abdulkadir Öner Ceylan 38 21.146 TL Lambdaİstanbul ve LİSTAG Mesude Demirağ 36 46.600 TL LİSTAG Serpil Bilgin 33 7.510 TL LİSTAG Rezan Bekiroğlu 30 6.000 TL LİSTAG Cüneyt Orhan Yurtsever 28 8.400 TL LİSTAG Figen Yılmaz 27 21.800 TL LİSTAG Hasan Metehan Özkan 25 26.528,64 TL LİSTAG ve SPoD Can Candan 21 20.250 TL LİSTAG Osman Elbek 20 20.000 TL LİSTAG Yağmur Arığ 20 11.000 TL LİSTAG ve SPoD BİRDEN FAZLA DERNEĞE PARA GÖNDERENLER Aynı gerçek kişilerin birden fazla derneğin hesabında görülmesi de incelemede dikkat çeken başlıklardan biri oldu. Necla İclal Küneralp'in Lambda İstanbul'a 20 bin, LİSTAG'a 40 bin olmak üzere toplam 60 bin lira gönderdiği belirlendi. Turgay Bayındır'ın Lambdaİstanbul ve SPoD'a 19 işlemle toplam 52 bin 670 lira, Esra Banu Çırak'ın Lambdaİstanbul ile LİSTAG'a 40 bin lira aktardığı kaydedildi. Mihael Nahmias'ın Pozitif Yaşam ile Pozitif İz'e toplam 40 bin lira, Hasan Metehan Özkan'ın LİSTAG ile SPoD'a 25 işlemle 26 bin 528,64 lira gönderdiği tespit edildi. Abdulkadir Öner Ceylan'ın iki derneğe 38 işlemle 21 bin 146 lira, Abdullah İkbal Arslanbaş'ın ise iki derneğe 72 işlemle toplam 11 bin 535 lira aktardığı belirtildi. HEARTSTOPPER'IN YAZARI DA KAYITLARDA Gerçek kişilerden gelen transferler ile açık kaynak kayıtlarının karşılaştırıldığı analizde uluslararası alanda tanınan isimlerin de bulunduğu görüldü. MASAK kaydında karşı tarafın doğrudan "ALICE OSEMAN AUTHOR" olarak yer aldığı belirtildi. İngiltere'deki TSB Bank PLC London üzerinden Lambda İstanbul'a 663,37 sterlin gönderildiği ve işlem açıklamasında "DONATION OTHER" ifadesinin bulunduğu kaydedildi. İşlemin transfer tarihindeki TL karşılığı 12 bin 277,72 lira olarak hesaplandı. "Author" ibaresi, İngiltere bağlantısı ve ayırt edici isim nedeniyle kaydın, Heartstopper serisinin yaratıcısı, yazar ve senarist Alice Oseman ile eşleşme seviyesinin son derece yüksek olduğu değerlendirildi. SWIFT inceleme tutanağında aynı isme ait 2022 tarihli işlemin dolar karşılığı ise 904,10 dolar olarak yer aldı. TANINMIŞ İSİMLERİN TRANSFERLERİ Belgesel yönetmeni ve akademisyen Can Candan adına LİSTAG'a 21 ayrı işlemle toplam 20 bin 250 lira gönderildiği belirlendi. İşlem açıklamalarında düzenli şekilde "bağış", bir işlemde ise "aidat" ifadesinin bulunduğu kaydedildi. Oyuncu Ayça Damgacı adına LİSTAG hesabına tek işlemle 28 bin 513 lira aktarıldı. Ancak bu işlem "bağış" değil, "iade" açıklamasıyla kayıtlara geçti. Derya Seyhan Arman adına Lambda İstanbul'a 12 ayrı işlemle toplam 6 bin lira gönderildiği belirtildi. Banka kayıtlarında karşı tarafın "Derya Arman" , işlem açıklamalarında ise "Seyhan Arman" olarak yer aldığı aktarıldı. Hekim Osman Elbek adına LİSTAG'a 20 ayrı işlemle toplam 20 bin lira gönderildiği ve işlemlerde "bağış" açıklamasının bulunduğu kaydedildi. Çevirmen Amy Marie Spangler adına Lambda İstanbul'a 12 işlemle toplam 19 bin 700 lira gönderildi. Bazı işlemlerin açıklamasında doğrudan "bağış" ifadesinin yer aldığı belirtildi. Akademisyen Şemsa Özar adına SPoD'a "bağış" açıklamasıyla 5 bin liralık işlem bulunduğu kaydedildi. Ancak analizde, banka kaydındaki kişi ile kamuoyunca tanınan ismin aynı olduğunu gösteren ikinci bir kişisel tanımlayıcı bulunmadığı için bu eşleşmenin ihtiyatla değerlendirilmesi gerektiği vurgulandı. DERNEK YÖNETİCİLERİNDEN DERNEK HESAPLARINA PARA Bazı transfer sahiplerinin para gönderdikleri derneklerde yönetici veya çalışan olarak görev yaptığına ilişkin açık kaynak kayıtlarına da ulaşıldı. SPoD'un eski iletişim koordinatörü olarak eşleştirilen Erkan Çıvak adına iki bağış işleminde toplam 72 bin 830 lira para girişi bulundu. SPoD'un eski yönetim kurulu başkanı olduğu belirtilen Müge Akbasan adına 15 işlemle 49 bin 119,50 lira aktarıldı. Bu tutarın en az 35 bin 869,50 liralık bölümünün bağış veya aidat açıklaması taşıdığı kaydedildi. Derneğin yönetiminde sayman olarak yer aldığı belirtilen Ali Erdoğan adına 5 işlemle 39 bin 275,18 lira, Anıl Kocaoğulları adına ise 6 işlemle 24 bin 120 lira para girişi tespit edildi. SPoD'un denetleme kurulunda yer aldığı belirtilen Abdullah İkbal Arslanbaş, 72 işlemle gerçek kişiler arasındaki en yüksek transfer sayısına ulaştı. HER PARA GİRİŞİ BAĞIŞ DEĞİL Belgelerde, hesaplara giren brüt tutarların tamamının bağış olarak değerlendirilmemesi gerektiğine dikkat çekildi. HEVİ bağlantılı Osman Doğan adına 9 işlemle 101 bin 406,68 liralık brüt para girişi bulundu. Ancak bu tutarın 100 bin 206,68 liralık bölümünün huzur hakkı iadesi niteliğinde olduğu, bağış ve aidat olarak değerlendirilen kısmın yaklaşık bin 200 lira olduğu belirtildi. Zafer Rıfat Irmak adına görünen 93 bin 237,41 liralık para girişinin de 89 bin 853,41 liralık bölümünün huzur hakkı iadesi olduğu kaydedildi. Furkan Yurt adına görünen 61 bin liralık iki işlemin 60 bin liralık kısmının "maaş avans iadesi" açıklaması taşıdığı tespit edildi. Ayça Damgacı adına kaydedilen 28 bin 513 liralık işlem ile Selim Gültepe adına görünen 45 bin liralık işlemin de iade niteliğinde olduğu belirtildi. SORUŞTURMADA PARA TRAFİĞİ MERCEK ALTINDA Üç dosyanın birlikte değerlendirilmesi sonucunda, 6 derneğe uzanan yabancı finansman ağında uluslararası kuruluşların yanı sıra ABD Dışişleri Bakanlığı, Hollanda Dışişleri Bakanlığı, Almanya ve Fransa'nın diplomatik temsilcilikleri gibi yabancı kamu kurumlarının da bulunduğu tespit edildi. MASAK Veri İnceleme Tutanağında yer alan değerlendirmeler ile para transferlerinin hangi faaliyetlerde kullanıldığına ilişkin iddialar, İstanbul Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında inceleniyor. Belgelerde adı geçen kişiler ile kuruluşlar hakkındaki kayıtlar para transferlerini gösterirken, söz konusu hareketler tek başına suçun kesinleştiği anlamına gelmiyor. Dosyadaki iddia ve değerlendirmelere ilişkin adli süreç devam ediyor. Sosyal medyadaki sapkın içeriklere erişim engeli kararı! SOSYAL MEDYADAKİ SAPKIN İÇERİKLERE ERİŞİM ENGELİ KARARI! #MASAK LGBTİ Dernekleri Raporu #İstanbul Cumhuriyet Başsavcılığı LGBTİ Soruşturması Giriş Tarihi: 13 Eylül 2026 12:03 Son Güncelleme: 13 Eylül 2026 13:15 ahaber.com.tr Haber Merkezi Giriş Tarihi: 13 Eylül 2026 12:03 Son Güncelleme: 13 Eylül 2026 13:15 ahaber.com.tr Haber Merkezi İstanbul Cumhuriyet Başsavcılığının soruşturması kapsamında incelenen MASAK verileri, 6 LGBT derneğinin yurt dışı bağlantılı para trafiğini ortaya çıkardı. GİB SWIFT kayıtlarında derneklere gönderilen paranın dolar karşılığı 3 milyon 359 bin doları aşarken, 2021-2026 dönemindeki 209 yabancı kurumsal transferin işlem tarihlerindeki TL karşılığı 67,4 milyon liraya ulaştı. Para trafiğinde yabancı devlet kurumları, diplomatik misyonlar, uluslararası kuruluşlar ve bazı tanınmış isimler yer aldı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında gönderilen Mali Suçları Araştırma Kurulu verileri üzerinde yapılan inceleme, İstanbul merkezli 6 LGBT derneğinin yurt içi ve yurt dışı bağlantılı hesap hareketlerini gözler önüne serdi. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu'nun 226'ncı maddesi kapsamında yürütülen araştırmada; Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği, Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği, Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin hesapları mercek altına alındı. BAKAN GÜRLEK DUYURMUŞTU: İZMİR'DEKİ "AİLEM GÜVENDE" OPERASYONUNDAN GÖRÜNTÜLER! ahaber.com.tr'nin ulaştığı MASAK Veri İnceleme Tutanağı ile bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte incelendi. Belgelerde yabancı kuruluşlardan gelen fonlar, GİB SWIFT kayıtları, gerçek kişilerden yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketleri ayrıntılı şekilde sıralandı. 45 BİN 135 İŞLEM SATIRI İNCELENDİ "Bankacılık Transfer" tablosunda toplam 45 bin 135 işlem satırı bulunduğu belirtildi. Bu işlemlerin 13 bin 40'ının para girişi, 32 bin 95'inin ise para çıkışı olduğu kaydedildi. Para girişlerinden 218'inin doğrudan SWIFT alma işlemi olduğu tespit edildi. Gönderen adı, ülke bilgisi, SWIFT niteliği, banka ve işlem açıklamalarının birlikte değerlendirilmesi sonucunda 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan toplam 209 para girişi belirlendi. Bu işlemlerin transfer tarihlerindeki TL karşılıklarının toplamı yaklaşık 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde söz konusu rakamın paranın bugünkü değerini göstermediği, farklı tarihlerde gerçekleştirilen işlemlerin MASAK kayıtlarında bulunan TL karşılıklarının aritmetik toplamından oluştuğu vurgulandı. PARANIN YÜZDE 78'İ İKİ DERNEĞE GİTTİ 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinde SPoD ile HEVİ'nin belirgin şekilde öne çıktığı görüldü. Dernek İşlem sayısı Yabancı kaynak TL karşılığı SPoD 129 25 33.924.428,57 TL HEVİ 34 8 18.874.570,54 TL LİSTAG 19 8 8.231.662,68 TL Pozitif Yaşam 11 5 2.729.693,32 TL Lambda İstanbul 9 3 2.056.884,74 TL Pozitif-İz 7 3 1.577.322,83 TL Yabancı kurumsal para girişlerinin yaklaşık yüzde 50,3'ü SPoD'a, yüzde 28'i HEVİ'ye ve yüzde 12,2'si LİSTAG'a yöneldi. SPoD ile HEVİ'ye yapılan transferlerin işlem tarihlerindeki toplam TL karşılığı yaklaşık 52,8 milyon liraya ulaştı. Böylece iki dernek, 6 derneğe yönelen yabancı kurumsal finansmanın yaklaşık yüzde 78'ini aldı. SPoD'A 25 YABANCI KAYNAKTAN 33,9 MİLYON LİRA Yabancı kaynak çeşitliliği ve işlem hacmi bakımından ilk sırada SPoD yer aldı. Derneğin hesaplarına 25 farklı yabancı kaynaktan 129 işlemle yaklaşık 33 milyon 924 bin lira karşılığında para gönderildiği belirlendi. SPoD'a yapılan dikkat çekici transferler şöyle sıralandı: Women Win: 7 işlemde 320 bin 500 dolar Rainbow Railroad USA Inc: 3 işlemde 149 bin 794,86 dolar ILGA-Europe: 17 işlemde 104 bin 169,48 euro New Venture Fund: Tek işlemde 86 bin 400 dolar EED/FEDEM: 7 işlemde 76 bin 347,96 euro Regnbågsfonden: 6 işlemde 51 bin 840,34 euro ve 505 bin 84,50 İsveç kronu King Baudouin Foundation: Tek işlemde 25 bin dolar Almanya Federal Cumhuriyeti ve Başkonsolosluğu: 3 işlemde 42 bin 685 euro ABD Dışişleri Bakanlığı: 4 işlemde 38 bin 916,22 dolar Turkish Philanthropy Funds: 2 işlemde 23 bin 230,28 dolar German Marshall Fund: Tek işlemde 24 bin 839 dolar Fransa Büyükelçiliği: Tek işlemde 6 bin 505 euro OutRight Action International: 2 işlemde 6 bin 987 dolar International AIDS Society: 2 işlemde 2 bin 240 dolar ARACI BANKALARIN ARKASINDAKİ KAYNAK İncelemede, bazı banka kayıtlarında aracı finans kuruluşlarının gönderen olarak görünmesi nedeniyle gerçek fon sağlayıcısının ilk bakışta anlaşılamadığı tespit edildi. UK Online Giving Foundation kaynaklı çok sayıda işlemin karşı taraf bölümünde Bank of America veya Citibank Europe PLC'nin bulunduğu, ancak işlem açıklamalarında açıkça "UK ONLINE GIVING FOUNDATION" ve "POP GRANT DONATION FROM UKOGF" ifadelerinin yer aldığı kaydedildi. Bu nedenle 53 işlem aracı bankalara değil, nihai fon sağlayıcısı olarak değerlendirilen UK Online Giving Foundation'a atfedildi. Bu kapsamdaki son işlemin 27 Ağustos 2026 tarihinde gerçekleştirildiği belirtildi. HEVİ'YE 18,87 MİLYON LİRALIK YABANCI FON HEVİ'nin hesaplarına 8 yabancı kaynaktan 34 işlemle yaklaşık 18 milyon 874 bin lira karşılığında para gönderildiği belirlendi. Derneğin en büyük yabancı finansman kaynağının European Endowment for Democracy ve FEDEM kayıtları olduğu görüldü. Aynı finansman kaynağının farklı yazımlarla kaydedildiği belirtilirken 7 işlemde toplam 213 bin 930,27 euro gönderildiği tespit edildi. Bu işlemlerin transfer tarihlerindeki TL karşılığı 8 milyon 790 bin lirayı aştı. HEVİ'ye para gönderen diğer kaynaklar şöyle sıralandı: Wellspring Philanthropic Fund: 6 işlemde 200 bin 49 dolar ILGA-Europe: 11 işlemde 78 bin 910,98 euro Global Fund for Women: Tek işlemde 45 bin dolar Rosa-Luxemburg-Stiftung: 3 işlemde 19 bin 267,26 euro Fransa Büyükelçiliği: 2 işlemde 8 bin 361 euro Norveç Helsinki Komitesi: 3 işlemde 22 bin 453,12 dolar Front Line: Tek işlemde bin 815 euro LİSTAG'A YABANCI DEVLET VE DİPLOMATİK MİSYON PARASI LİSTAG'a 2021 sonrasında 8 farklı yabancı kaynaktan 19 işlemle yaklaşık 8 milyon 231 bin lira karşılığında para gönderildiği tespit edildi. Hollanda Dışişleri Bakanlığından 4 işlemde 89 bin 687 euro, Almanya Federal Cumhuriyeti ve Başkonsolosluğu bağlantılı kayıtlardan 6 işlemde 61 bin 413,92 euro gönderildiği belirlendi. Belgelerde adı eksik şekilde "Embassy of the Kingdom of..." olarak görünen kaynaktan 2 işlemle 38 bin 256 euro, European Endowment for Democracy'den ise 2 işlemle 25 bin euro aktarıldığı kaydedildi. LİSTAG'a yönelen finansmanın önemli bir bölümünün yabancı devlet kurumları ve diplomatik temsilciliklerle bağlantılı olduğu değerlendirmesine yer verildi. POZİTİF YAŞAM'A 2,73 MİLYON LİRA Pozitif Yaşam Derneğine 5 farklı kaynaktan 11 işlemle yaklaşık 2 milyon 729 bin lira karşılığında yabancı kurumsal para girişi tespit edildi. Charities Aid Foundation tarafından 2 işlemde 114 bin 310,30 euro, Gilead Sciences tarafından tek işlemde 33 bin dolar gönderildi. Bu iki kaynağın transfer tarihlerindeki toplam TL karşılığı 2,6 milyon lirayı aştı. German Marshall Fund'dan 13 bin 644 dolar, UK Online Giving Foundation üzerinden 6 işlemde toplam 4 bin 494,53 lira ve Posithiva Gruppen'den 195 euro aktarıldığı kaydedildi. POZİTİF İZ'E ABD VE FRANSA BAĞLANTILI TRANSFERLER Pozitif İz Derneğine 7 işlemle yaklaşık 1 milyon 577 bin lira karşılığında para gönderildiği belirlendi. International AIDS Society adına farklı yazımlarla görünen 4 transferin toplamı 30 bin 80 dolara ulaştı. Fransa Büyükelçiliğinden 10 bin 840 euro, ABD Dışişleri Bakanlığından ise 2 işlemde 7 bin 67,80 dolar gönderildiği tespit edildi. LAMBDA İSTANBUL'A ILGA-EUROPE'TAN 7 TRANSFER Lambda İstanbul'a 3 yabancı kurumsal kaynaktan 9 işlemle yaklaşık 2 milyon 56 bin lira karşılığında para girişi tespit edildi. ILGA-Europe tarafından 7 işlemde toplam 45 bin 532,01 euro gönderildi. Urgent Action Fund for Feminist kaynaklı kayıttan 6 bin dolar, IFLRY'den ise 300 euro aktarıldığı belirtildi. 3 Ağustos 2026 tarihinde İngiltere bağlantılı bir banka üzerinden "VACHINA" adına 500 euroluk transfer yapıldığı da görüldü. Ancak karşı tarafın tüzel bir kuruluş olup olmadığı kesinleştirilemediği için bu işlem kurumsal yabancı kaynak toplamına dahil edilmedi. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında gönderilen Mali Suçları Araştırma Kurulu verileri üzerinde yapılan inceleme, İstanbul merkezli 6 LGBT derneğinin yurt içi ve yurt dışı bağlantılı hesap hareketlerini gözler önüne serdi. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu'nun 226'ncı maddesi kapsamında yürütülen araştırmada; Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği, Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği, Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin hesapları mercek altına alındı. BAKAN GÜRLEK DUYURMUŞTU: İZMİR'DEKİ "AİLEM GÜVENDE" OPERASYONUNDAN GÖRÜNTÜLER! ahaber.com.tr'nin ulaştığı MASAK Veri İnceleme Tutanağı ile bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte incelendi. Belgelerde yabancı kuruluşlardan gelen fonlar, GİB SWIFT kayıtları, gerçek kişilerden yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketleri ayrıntılı şekilde sıralandı. 45 BİN 135 İŞLEM SATIRI İNCELENDİ "Bankacılık Transfer" tablosunda toplam 45 bin 135 işlem satırı bulunduğu belirtildi. Bu işlemlerin 13 bin 40'ının para girişi, 32 bin 95'inin ise para çıkışı olduğu kaydedildi. Para girişlerinden 218'inin doğrudan SWIFT alma işlemi olduğu tespit edildi. Gönderen adı, ülke bilgisi, SWIFT niteliği, banka ve işlem açıklamalarının birlikte değerlendirilmesi sonucunda 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan toplam 209 para girişi belirlendi. Bu işlemlerin transfer tarihlerindeki TL karşılıklarının toplamı yaklaşık 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde söz konusu rakamın paranın bugünkü değerini göstermediği, farklı tarihlerde gerçekleştirilen işlemlerin MASAK kayıtlarında bulunan TL karşılıklarının aritmetik toplamından oluştuğu vurgulandı. PARANIN YÜZDE 78'İ İKİ DERNEĞE GİTTİ 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinde SPoD ile HEVİ'nin belirgin şekilde öne çıktığı görüldü. Dernek İşlem sayısı Yabancı kaynak TL karşılığı SPoD 129 25 33.924.428,57 TL HEVİ 34 8 18.874.570,54 TL LİSTAG 19 8 8.231.662,68 TL Pozitif Yaşam 11 5 2.729.693,32 TL Lambda İstanbul 9 3 2.056.884,74 TL Pozitif-İz 7 3 1.577.322,83 TL Yabancı kurumsal para girişlerinin yaklaşık yüzde 50,3'ü SPoD'a, yüzde 28'i HEVİ'ye ve yüzde 12,2'si LİSTAG'a yöneldi. SPoD ile HEVİ'ye yapılan transferlerin işlem tarihlerindeki toplam TL karşılığı yaklaşık 52,8 milyon liraya ulaştı. Böylece iki dernek, 6 derneğe yönelen yabancı kurumsal finansmanın yaklaşık yüzde 78'ini aldı. SPoD'A 25 YABANCI KAYNAKTAN 33,9 MİLYON LİRA Yabancı kaynak çeşitliliği ve işlem hacmi bakımından ilk sırada SPoD yer aldı. Derneğin hesaplarına 25 farklı yabancı kaynaktan 129 işlemle yaklaşık 33 milyon 924 bin lira karşılığında para gönderildiği belirlendi. SPoD'a yapılan dikkat çekici transferler şöyle sıralandı: Women Win: 7 işlemde 320 bin 500 dolar Rainbow Railroad USA Inc: 3 işlemde 149 bin 794,86 dolar ILGA-Europe: 17 işlemde 104 bin 169,48 euro New Venture Fund: Tek işlemde 86 bin 400 dolar EED/FEDEM: 7 işlemde 76 bin 347,96 euro Regnbågsfonden: 6 işlemde 51 bin 840,34 euro ve 505 bin 84,50 İsveç kronu King Baudouin Foundation: Tek işlemde 25 bin dolar Almanya Federal Cumhuriyeti ve Başkonsolosluğu: 3 işlemde 42 bin 685 euro ABD Dışişleri Bakanlığı: 4 işlemde 38 bin 916,22 dolar Turkish Philanthropy Funds: 2 işlemde 23 bin 230,28 dolar German Marshall Fund: Tek işlemde 24 bin 839 dolar Fransa Büyükelçiliği: Tek işlemde 6 bin 505 euro OutRight Action International: 2 işlemde 6 bin 987 dolar International AIDS Society: 2 işlemde 2 bin 240 dolar ARACI BANKALARIN ARKASINDAKİ KAYNAK İncelemede, bazı banka kayıtlarında aracı finans kuruluşlarının gönderen olarak görünmesi nedeniyle gerçek fon sağlayıcısının ilk bakışta anlaşılamadığı tespit edildi. UK Online Giving Foundation kaynaklı çok sayıda işlemin karşı taraf bölümünde Bank of America veya Citibank Europe PLC'nin bulunduğu, ancak işlem açıklamalarında açıkça "UK ONLINE GIVING FOUNDATION" ve "POP GRANT DONATION FROM UKOGF" ifadelerinin yer aldığı kaydedildi. Bu nedenle 53 işlem aracı bankalara değil, nihai fon sağlayıcısı olarak değerlendirilen UK Online Giving Foundation'a atfedildi. Bu kapsamdaki son işlemin 27 Ağustos 2026 tarihinde gerçekleştirildiği belirtildi. HEVİ'YE 18,87 MİLYON LİRALIK YABANCI FON HEVİ'nin hesaplarına 8 yabancı kaynaktan 34 işlemle yaklaşık 18 milyon 874 bin lira karşılığında para gönderildiği belirlendi. Derneğin en büyük yabancı finansman kaynağının European Endowment for Democracy ve FEDEM kayıtları olduğu görüldü. Aynı finansman kaynağının farklı yazımlarla kaydedildiği belirtilirken 7 işlemde toplam 213 bin 930,27 euro gönderildiği tespit edildi. Bu işlemlerin transfer tarihlerindeki TL karşılığı 8 milyon 790 bin lirayı aştı. HEVİ'ye para gönderen diğer kaynaklar şöyle sıralandı: Wellspring Philanthropic Fund: 6 işlemde 200 bin 49 dolar ILGA-Europe: 11 işlemde 78 bin 910,98 euro Global Fund for Women: Tek işlemde 45 bin dolar Rosa-Luxemburg-Stiftung: 3 işlemde 19 bin 267,26 euro Fransa Büyükelçiliği: 2 işlemde 8 bin 361 euro Norveç Helsinki Komitesi: 3 işlemde 22 bin 453,12 dolar Front Line: Tek işlemde bin 815 euro LİSTAG'A YABANCI DEVLET VE DİPLOMATİK MİSYON PARASI LİSTAG'a 2021 sonrasında 8 farklı yabancı kaynaktan 19 işlemle yaklaşık 8 milyon 231 bin lira karşılığında para gönderildiği tespit edildi. Hollanda Dışişleri Bakanlığından 4 işlemde 89 bin 687 euro, Almanya Federal Cumhuriyeti ve Başkonsolosluğu bağlantılı kayıtlardan 6 işlemde 61 bin 413,92 euro gönderildiği belirlendi. Belgelerde adı eksik şekilde "Embassy of the Kingdom of..." olarak görünen kaynaktan 2 işlemle 38 bin 256 euro, European Endowment for Democracy'den ise 2 işlemle 25 bin euro aktarıldığı kaydedildi. LİSTAG'a yönelen finansmanın önemli bir bölümünün yabancı devlet kurumları ve diplomatik temsilciliklerle bağlantılı olduğu değerlendirmesine yer verildi. POZİTİF YAŞAM'A 2,73 MİLYON LİRA Pozitif Yaşam Derneğine 5 farklı kaynaktan 11 işlemle yaklaşık 2 milyon 729 bin lira karşılığında yabancı kurumsal para girişi tespit edildi. Charities Aid Foundation tarafından 2 işlemde 114 bin 310,30 euro, Gilead Sciences tarafından tek işlemde 33 bin dolar gönderildi. Bu iki kaynağın transfer tarihlerindeki toplam TL karşılığı 2,6 milyon lirayı aştı. German Marshall Fund'dan 13 bin 644 dolar, UK Online Giving Foundation üzerinden 6 işlemde toplam 4 bin 494,53 lira ve Posithiva Gruppen'den 195 euro aktarıldığı kaydedildi. POZİTİF İZ'E ABD VE FRANSA BAĞLANTILI TRANSFERLER Pozitif İz Derneğine 7 işlemle yaklaşık 1 milyon 577 bin lira karşılığında para gönderildiği belirlendi. International AIDS Society adına farklı yazımlarla görünen 4 transferin toplamı 30 bin 80 dolara ulaştı. Fransa Büyükelçiliğinden 10 bin 840 euro, ABD Dışişleri Bakanlığından ise 2 işlemde 7 bin 67,80 dolar gönderildiği tespit edildi. LAMBDA İSTANBUL'A ILGA-EUROPE'TAN 7 TRANSFER Lambda İstanbul'a 3 yabancı kurumsal kaynaktan 9 işlemle yaklaşık 2 milyon 56 bin lira karşılığında para girişi tespit edildi. ILGA-Europe tarafından 7 işlemde toplam 45 bin 532,01 euro gönderildi. Urgent Action Fund for Feminist kaynaklı kayıttan 6 bin dolar, IFLRY'den ise 300 euro aktarıldığı belirtildi. 3 Ağustos 2026 tarihinde İngiltere bağlantılı bir banka üzerinden "VACHINA" adına 500 euroluk transfer yapıldığı da görüldü. Ancak karşı tarafın tüzel bir kuruluş olup olmadığı kesinleştirilemediği için bu işlem kurumsal yabancı kaynak toplamına dahil edilmedi. AYNI KAYNAKLAR BİRDEN FAZLA DERNEĞİ FONLADI Üç dosyanın birlikte incelenmesi, bazı yabancı kaynakların birden fazla derneğe düzenli olarak para gönderdiğini ortaya koydu. EED/FEDEM'in HEVİ, LİSTAG ve SPoD'a 16 işlemde toplam 315 bin 278,23 euro gönderdiği belirlendi. İşlemlerin transfer tarihlerindeki toplam TL karşılığı yaklaşık 11,38 milyon lira olarak hesaplandı. ILGA-Europe'un HEVİ, Lambdaİstanbul, LİSTAG ve SPoD'a 37 işlemde toplam 234 bin 221,17 euro aktardığı kaydedildi. Bu işlemlerin TL karşılığının yaklaşık 7,69 milyon lira olduğu belirtildi. Diğer ortak finansman kaynakları ise şöyle sıralandı: Almanya Federal Cumhuriyeti ve Başkonsolosluğu: LİSTAG ve SPoD'a 9 işlemde 104 bin 98,92 euro Hollanda Dışişleri Bakanlığı: LİSTAG ve SPoD'a en az 5 işlemde 89 bin 687 euro ve 276 bin 500 lira ABD Dışişleri Bakanlığı: Pozitif- z ve SPoD'a 6 işlemde 45 bin 984,02 dolar Fransa Büyükelçiliği: HEVİ, Pozitif İz ve SPoD'a 4 işlemde 25 bin 706 euro German Marshall Fund: LİSTAG, Pozitif Yaşam ve SPoD'a 3 işlemde 63 bin 347 dolar International AIDS Society: Pozitif İz ve SPoD'a 6 işlemde 32 bin 320 dolar SWIFT KAYITLARINDA 3,3 MİLYON DOLARI AŞAN TRAFİK MASAK Veri İnceleme Tutanağındaki GİB SWIFT kayıtlarında, derneklerin farklı yıllara yayılan yurt dışı bağlantılı hesap hareketlerinin dolar karşılıklarına da yer verildi. Dernek İncelenen dönem Rapordaki toplam dolar karşılığı SPoD2012-2026 1.570.692,44 dolar HEVİ2018-2026 762.939,21 dolar Pozitif Yaşam-2011-20255 18.525,92 dolar LİSTAG2020-2026 314.220,89 dolar Lambdaİstanbul-2012-2026 103.650,93 dolar Pozitif İz-2022-2026 89.138,41 dolar Toplam3.359.167,80 dolar Böylece 6 derneğe ait GİB SWIFT kayıtlarında yer alan para hareketlerinin dolar karşılığı toplamı 3 milyon 359 bin 167,80 dolara ulaştı. Bu toplam, farklı yıllarda ve farklı para birimleriyle gerçekleştirilen işlemlerin tutanaktaki dolar karşılıklarından oluşuyor. 2021-2026 dönemine ilişkin 67,4 milyon liralık bankacılık analiziyle aynı kapsamı taşımadığı için iki rakamın birbirine eklenmemesi gerekiyor. PARA TRAFİĞİ 2011'E KADAR UZANDI SWIFT kayıtları, yurt dışı bağlantılı finansmanın yalnızca son yıllarla sınırlı olmadığını ortaya koydu. Pozitif Yaşam Derneğinin 2011, Lambdaİstanbul ile SPoD'un 2012 yılına kadar uzanan transfer kayıtları bulunduğu belirlendi. Eski kayıtlarda Pozitif Yaşam'a Avrupa Komisyonundan 47 bin 996,94 dolar, UNDP'den 2 bin 500 dolar ve Deutsche Gesellschaft bağlantılı kayıtlardan 5 işlemde 124 bin 786,02 dolar gönderildiği görüldü. SPoD'a ABD Dışişleri Bakanlığından farklı yıllarda 9 işlemle 113 bin 591,62 dolar, ILGA-Europe'tan 15 işlemle 61 bin 403,14 dolar ve EED/FEDEM'den 9 işlemle 167 bin 207,74 dolar aktarıldığı kaydedildi. MASAK TUTANAĞINDA ÇARPICI DEĞERLENDİRME MASAK verileri üzerinde hazırlanan inceleme tutanağında, söz konusu derneklere yurt dışı bağlantılı kişi ve kuruluşlar tarafından maddi destek sağlandığı belirtildi. Tutanakta, bu kaynaklar aracılığıyla cinsiyet değiştirmek isteyen kişilerin ameliyat masraflarının karşılandığı yönünde değerlendirmeye yer verildi. Derneklerin faaliyetleri dışında toplumsal yapının bozulmasına, toplum içerisinde görüş ayrılıklarının oluşmasına, aileler arasında kaygı meydana gelmesine, kamu düzeni ile toplumsal değerlere zarar verilmesine yönelik çalışmalar yürüttüğü iddiası da soruşturma kapsamında kayda geçirildi. Söz konusu ifadeler, soruşturma dosyasındaki inceleme ve değerlendirmeleri yansıtıyor. DERNEK HESAPLARINA MÜKERRER PARA AKIŞI Gerçek kişilerden yapılan para girişlerinin incelendiği ayrı analizde, gönderenlerin T.C. kimlik numarası kayıtları esas alındı ve aynı kişiye ait isim farklılıkları birleştirildi. En fazla işlem yapan isim, Lambdaİstanbul ile SPoD'a toplam 72 kez para gönderen Abdullah İkbal Arslanbaş oldu. Arslanbaş adına 37'si Lambda İstanbul'a, 35'i SPoD'a olmak üzere toplam 11 bin 535 liralık transfer kaydı bulundu. En fazla mükerrer işlem yapan kişiler şöyle sıralandı: Gönderen İşlem Toplam Dernek Abdullah İkbal Arslanbaş 72 11.535 TL Lambdaİstanbul ve SPoD Yasemin Öz 56 3.010 TL Lambdaİstanbul ve SPoD Aslı Meleş 54 25.324 TL LİSTAG Anıl Birkan 44 39.550 TL Pozitif İz Günseli Dum 40 5.680 TL LİSTAG Abdulkadir Öner Ceylan 38 21.146 TL Lambdaİstanbul ve LİSTAG Mesude Demirağ 36 46.600 TL LİSTAG Serpil Bilgin 33 7.510 TL LİSTAG Rezan Bekiroğlu 30 6.000 TL LİSTAG Cüneyt Orhan Yurtsever 28 8.400 TL LİSTAG Figen Yılmaz 27 21.800 TL LİSTAG Hasan Metehan Özkan 25 26.528,64 TL LİSTAG ve SPoD Can Candan 21 20.250 TL LİSTAG Osman Elbek 20 20.000 TL LİSTAG Yağmur Arığ 20 11.000 TL LİSTAG ve SPoD BİRDEN FAZLA DERNEĞE PARA GÖNDERENLER Aynı gerçek kişilerin birden fazla derneğin hesabında görülmesi de incelemede dikkat çeken başlıklardan biri oldu. Necla İclal Küneralp'in Lambda İstanbul'a 20 bin, LİSTAG'a 40 bin olmak üzere toplam 60 bin lira gönderdiği belirlendi. Turgay Bayındır'ın Lambdaİstanbul ve SPoD'a 19 işlemle toplam 52 bin 670 lira, Esra Banu Çırak'ın Lambdaİstanbul ile LİSTAG'a 40 bin lira aktardığı kaydedildi. Mihael Nahmias'ın Pozitif Yaşam ile Pozitif İz'e toplam 40 bin lira, Hasan Metehan Özkan'ın LİSTAG ile SPoD'a 25 işlemle 26 bin 528,64 lira gönderdiği tespit edildi. Abdulkadir Öner Ceylan'ın iki derneğe 38 işlemle 21 bin 146 lira, Abdullah İkbal Arslanbaş'ın ise iki derneğe 72 işlemle toplam 11 bin 535 lira aktardığı belirtildi. HEARTSTOPPER'IN YAZARI DA KAYITLARDA Gerçek kişilerden gelen transferler ile açık kaynak kayıtlarının karşılaştırıldığı analizde uluslararası alanda tanınan isimlerin de bulunduğu görüldü. MASAK kaydında karşı tarafın doğrudan "ALICE OSEMAN AUTHOR" olarak yer aldığı belirtildi. İngiltere'deki TSB Bank PLC London üzerinden Lambda İstanbul'a 663,37 sterlin gönderildiği ve işlem açıklamasında "DONATION OTHER" ifadesinin bulunduğu kaydedildi. İşlemin transfer tarihindeki TL karşılığı 12 bin 277,72 lira olarak hesaplandı. "Author" ibaresi, İngiltere bağlantısı ve ayırt edici isim nedeniyle kaydın</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>MASAK Hawala ve Alternatif Değer Transfer Sistemleri İçin Yeni Rehber Yayımladı MASAK Hawala ve Alternatif Değer Transfer Sistemleri İçin Yeni Rehber Yayımladı FintekWins MASAK Hawala ve Alternatif Değer Transfer Sistemleri İçin Yeni Rehber Yayımladı FintekWins</t>
+          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı A Haber İstanbul Cumhuriyet Başsavcılığının soruşturmasında MASAK verileri incelendi; 6 derneğe 2011-2026 döneminde yurt dışı bağlantılı milyonluk para girişleri ve 209 kurumsal transfer tespit edildi. AYNI KAYNAKLAR BİRDEN FAZLA DERNEĞİ FONLADI Üç dosyanın birlikte incelenmesi, bazı yabancı kaynakların birden fazla derneğe düzenli olarak para gönderdiğini ortaya koydu. EED/FEDEM'in HEVİ, LİSTAG ve SPoD'a 16 işlemde toplam 315 bin 278,23 euro gönderdiği belirlendi. İşlemlerin transfer tarihlerindeki toplam TL karşılığı yaklaşık 11,38 milyon lira olarak hesaplandı. ILGA-Europe'un HEVİ, Lambdaİstanbul, LİSTAG ve SPoD'a 37 işlemde toplam 234 bin 221,17 euro aktardığı kaydedildi. Bu işlemlerin TL karşılığının yaklaşık 7,69 milyon lira olduğu belirtildi. Diğer ortak finansman kaynakları ise şöyle sıralandı: Almanya Federal Cumhuriyeti ve Başkonsolosluğu: LİSTAG ve SPoD'a 9 işlemde 104 bin 98,92 euro Hollanda Dışişleri Bakanlığı: LİSTAG ve SPoD'a en az 5 işlemde 89 bin 687 euro ve 276 bin 500 lira ABD Dışişleri Bakanlığı: Pozitif- z ve SPoD'a 6 işlemde 45 bin 984,02 dolar Fransa Büyükelçiliği: HEVİ, Pozitif İz ve SPoD'a 4 işlemde 25 bin 706 euro German Marshall Fund: LİSTAG, Pozitif Yaşam ve SPoD'a 3 işlemde 63 bin 347 dolar International AIDS Society: Pozitif İz ve SPoD'a 6 işlemde 32 bin 320 dolar SWIFT KAYITLARINDA 3,3 MİLYON DOLARI AŞAN TRAFİK MASAK Veri İnceleme Tutanağındaki GİB SWIFT kayıtlarında, derneklerin farklı yıllara yayılan yurt dışı bağlantılı hesap hareketlerinin dolar karşılıklarına da yer verildi. Dernek İncelenen dönem Rapordaki toplam dolar karşılığı SPoD2012-2026 1.570.692,44 dolar HEVİ2018-2026 762.939,21 dolar Pozitif Yaşam-2011-20255 18.525,92 dolar LİSTAG2020-2026 314.220,89 dolar Lambdaİstanbul-2012-2026 103.650,93 dolar Pozitif İz-2022-2026 89.138,41 dolar Toplam3.359.167,80 dolar Böylece 6 derneğe ait GİB SWIFT kayıtlarında yer alan para hareketlerinin dolar karşılığı toplamı 3 milyon 359 bin 167,80 dolara ulaştı. Bu toplam, farklı yıllarda ve farklı para birimleriyle gerçekleştirilen işlemlerin tutanaktaki dolar karşılıklarından oluşuyor. 2021-2026 dönemine ilişkin 67,4 milyon liralık bankacılık analiziyle aynı kapsamı taşımadığı için iki rakamın birbirine eklenmemesi gerekiyor. PARA TRAFİĞİ 2011'E KADAR UZANDI SWIFT kayıtları, yurt dışı bağlantılı finansmanın yalnızca son yıllarla sınırlı olmadığını ortaya koydu. Pozitif Yaşam Derneğinin 2011, Lambdaİstanbul ile SPoD'un 2012 yılına kadar uzanan transfer kayıtları bulunduğu belirlendi. Eski kayıtlarda Pozitif Yaşam'a Avrupa Komisyonundan 47 bin 996,94 dolar, UNDP'den 2 bin 500 dolar ve Deutsche Gesellschaft bağlantılı kayıtlardan 5 işlemde 124 bin 786,02 dolar gönderildiği görüldü. SPoD'a ABD Dışişleri Bakanlığından farklı yıllarda 9 işlemle 113 bin 591,62 dolar, ILGA-Europe'tan 15 işlemle 61 bin 403,14 dolar ve EED/FEDEM'den 9 işlemle 167 bin 207,74 dolar aktarıldığı kaydedildi. MASAK TUTANAĞINDA ÇARPICI DEĞERLENDİRME MASAK verileri üzerinde hazırlanan inceleme tutanağında, söz konusu derneklere yurt dışı bağlantılı kişi ve kuruluşlar tarafından maddi destek sağlandığı belirtildi. Tutanakta, bu kaynaklar aracılığıyla cinsiyet değiştirmek isteyen kişilerin ameliyat masraflarının karşılandığı yönünde değerlendirmeye yer verildi. Derneklerin faaliyetleri dışında toplumsal yapının bozulmasına, toplum içerisinde görüş ayrılıklarının oluşmasına, aileler arasında kaygı meydana gelmesine, kamu düzeni ile toplumsal değerlere zarar verilmesine yönelik çalışmalar yürüttüğü iddiası da soruşturma kapsamında kayda geçirildi. Söz konusu ifadeler, soruşturma dosyasındaki inceleme ve değerlendirmeleri yansıtıyor. kimlik numarası kayıtları esas alındı ve aynı kişiye ait isim farklılıkları birleştirildi. En fazla işlem yapan isim, Lambdaİstanbul ile SPoD'a toplam 72 kez para gönderen Abdullah İkbal Arslanbaş oldu. Arslanbaş adına 37'si Lambda İstanbul'a, 35'i SPoD'a olmak üzere toplam 11 bin 535 liralık transfer kaydı bulundu. En fazla mükerrer işlem yapan kişiler şöyle sıralandı: Gönderen İşlem Toplam Dernek Abdullah İkbal Arslanbaş 72 11.535 TL Lambdaİstanbul ve SPoD Yasemin Öz 56 3.010 TL Lambdaİstanbul ve SPoD Aslı Meleş 54 25.324 TL LİSTAG Anıl Birkan 44 39.550 TL Pozitif İz Günseli Dum 40 5.680 TL LİSTAG Abdulkadir Öner Ceylan 38 21.146 TL Lambdaİstanbul ve LİSTAG Mesude Demirağ 36 46.600 TL LİSTAG Serpil Bilgin 33 7.510 TL LİSTAG Rezan Bekiroğlu 30 6.000 TL LİSTAG Cüneyt Orhan Yurtsever 28 8.400 TL LİSTAG Figen Yılmaz 27 21.800 TL LİSTAG Hasan Metehan Özkan 25 26.528,64 TL LİSTAG ve SPoD Can Candan 21 20.250 TL LİSTAG Osman Elbek 20 20.000 TL LİSTAG Yağmur Arığ 20 11.000 TL LİSTAG ve SPoD BİRDEN FAZLA DERNEĞE PARA GÖNDERENLER Aynı gerçek kişilerin birden fazla derneğin hesabında görülmesi de incelemede dikkat çeken başlıklardan biri oldu. Necla İclal Küneralp'in Lambda İstanbul'a 20 bin, LİSTAG'a 40 bin olmak üzere toplam 60 bin lira gönderdiği belirlendi. Abdulkadir Öner Ceylan'ın iki derneğe 38 işlemle 21 bin 146 lira, Abdullah İkbal Arslanbaş'ın ise iki derneğe 72 işlemle toplam 11 bin 535 lira aktardığı belirtildi. HEARTSTOPPER'IN YAZARI DA KAYITLARDA Gerçek kişilerden gelen transferler ile açık kaynak kayıtlarının karşılaştırıldığı analizde uluslararası alanda tanınan isimlerin de bulunduğu görüldü. MASAK kaydında karşı tarafın doğrudan "ALICE OSEMAN AUTHOR" olarak yer aldığı belirtildi. İngiltere'deki TSB Bank PLC London üzerinden Lambda İstanbul'a 663,37 sterlin gönderildiği ve işlem açıklamasında "DONATION OTHER" ifadesinin bulunduğu kaydedildi. SWIFT inceleme tutanağında aynı isme ait 2022 tarihli işlemin dolar karşılığı ise 904,10 dolar olarak yer aldı. Ancak bu işlem "bağış" değil, "iade" açıklamasıyla kayıtlara geçti. Derya Seyhan Arman adına Lambda İstanbul'a 12 ayrı işlemle toplam 6 bin lira gönderildiği belirtildi. Hekim Osman Elbek adına LİSTAG'a 20 ayrı işlemle toplam 20 bin lira gönderildiği ve işlemlerde "bağış" açıklamasının bulunduğu kaydedildi. Çevirmen Amy Marie Spangler adına Lambda İstanbul'a 12 işlemle toplam 19 bin 700 lira gönderildi. Bazı işlemlerin açıklamasında doğrudan "bağış" ifadesinin yer aldığı belirtildi. Akademisyen Şemsa Özar adına SPoD'a "bağış" açıklamasıyla 5 bin liralık işlem bulunduğu kaydedildi. DERNEK YÖNETİCİLERİNDEN DERNEK HESAPLARINA PARA Bazı transfer sahiplerinin para gönderdikleri derneklerde yönetici veya çalışan olarak görev yaptığına ilişkin açık kaynak kayıtlarına da ulaşıldı. SPoD'un eski yönetim kurulu başkanı olduğu belirtilen Müge Akbasan adına 15 işlemle 49 bin 119,50 lira aktarıldı. Bu tutarın en az 35 bin 869,50 liralık bölümünün bağış veya aidat açıklaması taşıdığı kaydedildi. SPoD'un denetleme kurulunda yer aldığı belirtilen Abdullah İkbal Arslanbaş, 72 işlemle gerçek kişiler arasındaki en yüksek transfer sayısına ulaştı. Ancak bu tutarın 100 bin 206,68 liralık bölümünün huzur hakkı iadesi niteliğinde olduğu, bağış ve aidat olarak değerlendirilen kısmın yaklaşık bin 200 lira olduğu belirtildi. Furkan Yurt adına görünen 61 bin liralık iki işlemin 60 bin liralık kısmının "maaş avans iadesi" açıklaması taşıdığı tespit edildi. SORUŞTURMADA PARA TRAFİĞİ MERCEK ALTINDA Üç dosyanın birlikte değerlendirilmesi sonucunda, 6 derneğe uzanan yabancı finansman ağında uluslararası kuruluşların yanı sıra ABD Dışişleri Bakanlığı, Hollanda Dışişleri Bakanlığı, Almanya ve Fransa'nın diplomatik temsilcilikleri gibi yabancı kamu kurumlarının da bulunduğu tespit edildi. MASAK Veri İnceleme Tutanağında yer alan değerlendirmeler ile para transferlerinin hangi faaliyetlerde kullanıldığına ilişkin iddialar, İstanbul Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında inceleniyor. Belgelerde adı geçen kişiler ile kuruluşlar hakkındaki kayıtlar para transferlerini gösterirken, söz konusu hareketler tek başına suçun kesinleştiği anlamına gelmiyor. #MASAK LGBTİ Dernekleri Raporu #İstanbul Cumhuriyet Başsavcılığı LGBTİ Soruşturması Giriş Tarihi: 13 Eylül 2026 12:03 Son Güncelleme: 13 Eylül 2026 13:15 ahaber.com.tr Haber Merkezi Giriş Tarihi: 13 Eylül 2026 12:03 Son Güncelleme: 13 Eylül 2026 13:15 ahaber.com.tr Haber Merkezi İstanbul Cumhuriyet Başsavcılığının soruşturması kapsamında incelenen MASAK verileri, 6 LGBT derneğinin yurt dışı bağlantılı para trafiğini ortaya çıkardı. GİB SWIFT kayıtlarında derneklere gönderilen paranın dolar karşılığı 3 milyon 359 bin doları aşarken, 2021-2026 dönemindeki 209 yabancı kurumsal transferin işlem tarihlerindeki TL karşılığı 67,4 milyon liraya ulaştı. Para trafiğinde yabancı devlet kurumları, diplomatik misyonlar, uluslararası kuruluşlar ve bazı tanınmış isimler yer aldı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında gönderilen Mali Suçları Araştırma Kurulu verileri üzerinde yapılan inceleme, İstanbul merkezli 6 LGBT derneğinin yurt içi ve yurt dışı bağlantılı hesap hareketlerini gözler önüne serdi. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu'nun 226'ncı maddesi kapsamında yürütülen araştırmada; Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği, Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği, Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin hesapları mercek altına alındı. BAKAN GÜRLEK DUYURMUŞTU: İZMİR'DEKİ "AİLEM GÜVENDE" OPERASYONUNDAN GÖRÜNTÜLER! ahaber.com.tr'nin ulaştığı MASAK Veri İnceleme Tutanağı ile bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte incelendi. Bu işlemlerin transfer tarihlerindeki TL karşılıklarının toplamı yaklaşık 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde söz konusu rakamın paranın bugünkü değerini göstermediği, farklı tarihlerde gerçekleştirilen işlemlerin MASAK kayıtlarında bulunan TL karşılıklarının aritmetik toplamından oluştuğu vurgulandı. PARANIN YÜZDE 78'İ İKİ DERNEĞE GİTTİ 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinde SPoD ile HEVİ'nin belirgin şekilde öne çıktığı görüldü. Dernek İşlem sayısı Yabancı kaynak TL karşılığı SPoD 129 25 33.924.428,57 TL HEVİ 34 8 18.874.570,54 TL LİSTAG 19 8 8.231.662,68 TL Pozitif Yaşam 11 5 2.729.693,32 TL Lambda İstanbul 9 3 2.056.884,74 TL Pozitif-İz 7 3 1.577.322,83 TL Yabancı kurumsal para girişlerinin yaklaşık yüzde 50,3'ü SPoD'a, yüzde 28'i HEVİ'ye ve yüzde 12,2'si LİSTAG'a yöneldi. SPoD ile HEVİ'ye yapılan transferlerin işlem tarihlerindeki toplam TL karşılığı yaklaşık 52,8 milyon liraya ulaştı. Böylece iki dernek, 6 derneğe yönelen yabancı kurumsal finansmanın yaklaşık yüzde 78'ini aldı. SPoD'A 25 YABANCI KAYNAKTAN 33,9 MİLYON LİRA Yabancı kaynak çeşitliliği ve işlem hacmi bakımından ilk sırada SPoD yer aldı. Derneğin hesaplarına 25 farklı yabancı kaynaktan 129 işlemle yaklaşık 33 milyon 924 bin lira karşılığında para gönderildiği belirlendi. SPoD'a yapılan dikkat çekici transferler şöyle sıralandı: Women Win: 7 işlemde 320 bin 500 dolar Rainbow Railroad USA Inc: 3 işlemde 149 bin 794,86 dolar ILGA-Europe: 17 işlemde 104 bin 169,48 euro New Venture Fund: Tek işlemde 86 bin 400 dolar EED/FEDEM: 7 işlemde 76 bin 347,96 euro Regnbågsfonden: 6 işlemde 51 bin 840,34 euro ve 505 bin 84,50 İsveç kronu King Baudouin Foundation: Tek işlemde 25 bin dolar Almanya Federal Cumhuriyeti ve Başkonsolosluğu: 3 işlemde 42 bin 685 euro ABD Dışişleri Bakanlığı: 4 işlemde 38 bin 916,22 dolar Turkish Philanthropy Funds: 2 işlemde 23 bin 230,28 dolar German Marshall Fund: Tek işlemde 24 bin 839 dolar Fransa Büyükelçiliği: Tek işlemde 6 bin 505 euro OutRight Action International: 2 işlemde 6 bin 987 dolar International AIDS Society: 2 işlemde 2 bin 240 dolar ARACI BANKALARIN ARKASINDAKİ KAYNAK İncelemede, bazı banka kayıtlarında aracı finans kuruluşlarının gönderen olarak görünmesi nedeniyle gerçek fon sağlayıcısının ilk bakışta anlaşılamadığı tespit edildi. HEVİ'YE 18,87 MİLYON LİRALIK YABANCI FON HEVİ'nin hesaplarına 8 yabancı kaynaktan 34 işlemle yaklaşık 18 milyon 874 bin lira karşılığında para gönderildiği belirlendi. Bu işlemlerin transfer tarihlerindeki TL karşılığı 8 milyon 790 bin lirayı aştı. HEVİ'ye para gönderen diğer kaynaklar şöyle sıralandı: Wellspring Philanthropic Fund: 6 işlemde 200 bin 49 dolar ILGA-Europe: 11 işlemde 78 bin 910,98 euro Global Fund for Women: Tek işlemde 45 bin dolar Rosa-Luxemburg-Stiftung: 3 işlemde 19 bin 267,26 euro Fransa Büyükelçiliği: 2 işlemde 8 bin 361 euro Norveç Helsinki Komitesi: 3 işlemde 22 bin 453,12 dolar Front Line: Tek işlemde bin 815 euro LİSTAG'A YABANCI DEVLET VE DİPLOMATİK MİSYON PARASI LİSTAG'a 2021 sonrasında 8 farklı yabancı kaynaktan 19 işlemle yaklaşık 8 milyon 231 bin lira karşılığında para gönderildiği tespit edildi. Belgelerde adı eksik şekilde "Embassy of the Kingdom of..." olarak görünen kaynaktan 2 işlemle 38 bin 256 euro, European Endowment for Democracy'den ise 2 işlemle 25 bin euro aktarıldığı kaydedildi. POZİTİF YAŞAM'A 2,73 MİLYON LİRA Pozitif Yaşam Derneğine 5 farklı kaynaktan 11 işlemle yaklaşık 2 milyon 729 bin lira karşılığında yabancı kurumsal para girişi tespit edildi. Charities Aid Foundation tarafından 2 işlemde 114 bin 310,30 euro, Gilead Sciences tarafından tek işlemde 33 bin dolar gönderildi. Bu iki kaynağın transfer tarihlerindeki toplam TL karşılığı 2,6 milyon lirayı aştı. German Marshall Fund'dan 13 bin 644 dolar, UK Online Giving Foundation üzerinden 6 işlemde toplam 4 bin 494,53 lira ve Posithiva Gruppen'den 195 euro aktarıldığı kaydedildi. POZİTİF İZ'E ABD VE FRANSA BAĞLANTILI TRANSFERLER Pozitif İz Derneğine 7 işlemle yaklaşık 1 milyon 577 bin lira karşılığında para gönderildiği belirlendi. International AIDS Society adına farklı yazımlarla görünen 4 transferin toplamı 30 bin 80 dolara ulaştı. Fransa Büyükelçiliğinden 10 bin 840 euro, ABD Dışişleri Bakanlığından ise 2 işlemde 7 bin 67,80 dolar gönderildiği tespit edildi. LAMBDA İSTANBUL'A ILGA-EUROPE'TAN 7 TRANSFER Lambda İstanbul'a 3 yabancı kurumsal kaynaktan 9 işlemle yaklaşık 2 milyon 56 bin lira karşılığında para girişi tespit edildi. Urgent Action Fund for Feminist kaynaklı kayıttan 6 bin dolar, IFLRY'den ise 300 euro aktarıldığı belirtildi. #MASAK LGBTİ Dernekleri Raporu #İstanbul Cumhuriyet Başsavcılığı LGBTİ Soruşturması Sonraki Haber Babülmendep krizi piyasaları alt üst etti! Petrol fiyatlarında artış altını baskıladı Mobil uygulamalarımızı indirin Günün Manşetleri İçin Tıklayın AYNI KAYNAKLAR BİRDEN FAZLA DERNEĞİ FONLADI Üç dosyanın birlikte incelenmesi, bazı yabancı kaynakların birden fazla derneğe düzenli olarak para gönderdiğini ortaya koydu.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPd1IteTZUTl8zSnBwWVVubGNhVi13a0ZPcFVBdVNPSXFFaC02QTFCUjdqWkwzakVkYWpBV2xRWEF5Z1RHODlwVjdfRGVCb3hmNW5hYnM0U2MzZ3JQaUZfRmktZUF5WHlJM3dmVW9qdnhOeWZFaG5kaG5JSkVUaXdYLVBiV0VhX1BpWnNxcWJjRWd0NGtjY0tRN2hRbmpVMEFJMUV6c3ZpdTUyYWc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>https://www.ahaber.com.tr/ozel-haberler/2026/09/13/lgbti-derneklerinin-karanlik-para-agi-desifre-oldu</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -3546,7 +3703,7 @@
       <c r="S13" s="2" t="inlineStr"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr"/>
@@ -3560,7 +3717,7 @@
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>115</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>12</v>
@@ -3569,7 +3726,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:16:07</t>
+          <t>2026-09-13 06:08:08</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -3584,12 +3741,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MASAK’ın radarına giren altınlar odunluktan çıktı haberi</t>
+          <t>15 ilde 'Ailem Güvende' operasyonu</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>MASAK’ın radarına giren altınlar odunluktan çıktı haberi Finans Gündem</t>
+          <t>15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -3605,12 +3762,12 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>MASAK’ın radarına giren altınlar odunluktan çıktı haberi Finans Gündem</t>
+          <t>15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>MASAK’ın radarına giren altınlar odunluktan çıktı haberi MASAK’ın radarına giren altınlar odunluktan çıktı haberi Finans Gündem MASAK’ın radarına giren altınlar odunluktan çıktı haberi Finans Gündem</t>
+          <t>15 ilde 'Ailem Güvende' operasyonu 15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv 15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -3620,7 +3777,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNemFzNHlYNFJha0Z2enNZVzlfMXdkR0FXMkxpZjIzd0pGYWNLTzJtQXJmY1I4cU5SbjdFNXZBOWZqNXZVSUxJaG5JRUFQVVcyOFdFb1g0TXZ2MHNzdldTTWs5Z3RCZXlqbVJYNktIa2hGWFJCRXp2TW1zNmY3Y1NzNUVRX1ZOc1ExeDFESU5YZ29uYVFMOXBZMHdR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.odatv.com/guncel/15-ilde-ailem-guvende-operasyonu-masak-lgbti-derneklerinin-fonlarini-desifre-etti-120162459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr"/>
@@ -3646,7 +3803,7 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="n">
-        <v>44.2</v>
+        <v>56.92</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>13</v>
@@ -3655,7 +3812,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 06:17:00</t>
+          <t>2026-09-13 09:19:34</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -3670,12 +3827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MASAK Şanlıurfa'da takibe aldı, TEM çökertti: DEAŞ'ın para ağlarına operasyon!</t>
+          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>MASAK Şanlıurfa'da takibe aldı, TEM çökertti: DEAŞ'ın para ağlarına operasyon! Şanlıurfa Gazetesi</t>
+          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -3691,29 +3848,25 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Şanlıurfa İl Emniyet Müdürlüğü ve Şanlıurfa Cumhuriyet Başsavcılığı koordinesinde, MASAK ve HTS incelemeleri neticesinde DEAŞ terör örgütüne operadsyon düzenlendi. 16,5 milyon liralık işlem hacmi ile fon sağladıkları tespit edilen 8 şahıs yakalandı, milyonlarca liralık altın, döviz ele geçirildi. Şanlıurfa İl Emniyet Müdürlüğü ve Şanlıurfa Cumhuriyet Başsavcılığı koordinesinde, MASAK ve HTS incelemeleri neticesinde DEAŞ terör örgütüne operadsyon düzenlendi. 16,5 milyon liralık işlem hacmi ile fon sağladıkları tespit edilen 8 şahıs yakalandı, milyonlarca liralık altın, döviz ele geçirildi. Şanlıurfa İl Emniyet Müdürlüğü ve Şanlıurfa Cumhuriyet Başsavcılığı koordinesinde, MASAK ve HTS incelemeleri neticesinde DEAŞ terör örgütüne operadsyon düzenlendi. 16,5 milyon liralık işlem hacmi ile fon sağladıkları tespit edilen 8 şahıs yakalandı, milyonlarca liralık altın, döviz ele geçirildi. MASAK Şanlıurfa'da takibe aldı, TEM çökertti: DEAŞ'ın para ağlarına operasyon! Şanlıurfa İl Emniyet Müdürlüğü ve Şanlıurfa Cumhuriyet Başsavcılığı koordinesinde, MASAK ve HTS incelemeleri neticesinde DEAŞ terör örgütüne operadsyon düzenlendi. 16,5 milyon liralık işlem hacmi ile fon sağladıkları tespit edilen 8 şahıs yakalandı, milyonlarca liralık altın, döviz ele geçirildi. 12.09.2026 - 09:17 Yayınlanma 12.09.2026 - 09:55 Güncelleme — Payl</t>
+          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>MASAK Şanlıurfa'da takibe aldı, TEM çökertti: DEAŞ'ın para ağlarına operasyon! MASAK Şanlıurfa'da takibe aldı, TEM çökertti: DEAŞ'ın para ağlarına operasyon! Şanlıurfa Gazetesi Şanlıurfa İl Emniyet Müdürlüğü ve Şanlıurfa Cumhuriyet Başsavcılığı koordinesinde, MASAK ve HTS incelemeleri neticesinde DEAŞ terör örgütüne operadsyon düzenlendi. 16,5 milyon liralık işlem hacmi ile fon sağladıkları tespit edilen 8 şahıs yakalandı, milyonlarca liralık altın, döviz ele geçirildi. MASAK Şanlıurfa'da takibe aldı, TEM çökertti: DEAŞ'ın para ağlarına operasyon! 12.09.2026 - 09:17 Yayınlanma 12.09.2026 - 09:55 Güncelleme — Payl</t>
+          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.sanliurfagazetesi.com/masak-sanliurfada-takibe-aldi-tem-cokertti-deasin-para-aglarina-operasyon</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Şanlıurfa</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTFd3TlNFT0JUb01yMmphNFBGcUc5dWl5NEkyZ25WcW5NdUwxbkVQQ0k0WERtUTJ3N3JfX3hlZnRqSWhBZjNSeWpNM0tFWkQxQVFRXzduUHk2UjdaQlVrdTFtbmJCN2tPdnVHYXNuSWhzX2V1SFlGTVRVNU16RWpOekxPMzRXWGRWSE5Kdms1M09Ld0NMTFBQckc2Q2JSVTV5bnZDaHhXY0ZIbFc2M1lHNmFKQXBrT2c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -3722,7 +3875,7 @@
       <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr"/>
@@ -3736,7 +3889,7 @@
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="n">
-        <v>102.62</v>
+        <v>86.98</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>14</v>
@@ -3745,7 +3898,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:07:00</t>
+          <t>2026-09-13 09:07:34</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -3760,12 +3913,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Van'daki Düğün Sonrası Başlatılan Soruşturmada Kimler Gözaltına Alındı? MASAK Raporunda Kimlerin Adı Geçiyor?</t>
+          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı!</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Van'daki Düğün Sonrası Başlatılan Soruşturmada Kimler Gözaltına Alındı? MASAK Raporunda Kimlerin Adı Geçiyor? urfanatik.com</t>
+          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! SON TV</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -3781,29 +3934,25 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Van'da gerçekleştirilen düğünün görüntülerinin sosyal medyada gündem olmasının ardından Mehmet Fatih Tançalan hakkında başlatılan soruşturmada yeni gelişmeler yaşandı. “Suçtan kaynaklanan malvarlığı değerlerini aklama” suçlamasıyla tutuklanan Tançalan'ın eşi Çağla Öz Tançalan hakkında gözaltı kararı verildiği, MASAK raporunda adı geçen annesi N.O.'nun ise İstanbul'da gözaltına alındığı bildirildi. Van'da gerçekleştirilen düğünün görüntülerinin sosyal medyada gündem olmasının ardından Mehmet Fatih Tançalan hakkında başlatılan soruşturmada yeni gelişmeler yaşandı. “Suçtan kaynaklanan malvarlığı değerlerini aklama” suçlamasıyla tutuklanan Tançalan'ın eşi Çağla Öz Tançalan hakkında gözaltı kararı verildiği, MASAK raporunda adı geçen annesi N.O.'nun ise İstanbul'da gözaltına alındığı bildirildi. Van'da gerçekleştirilen düğünün görüntülerinin sosyal medyada gündem olmasının ardından Mehmet Fatih Tançalan hakkında başlatılan soruşturmada yeni gelişmeler yaşandı. “Suçtan kaynaklanan malvarlığı değerlerini aklama” suçlamasıyla tutuklanan Tançalan'ın eşi Çağla Öz Tançalan hakkında gözaltı kararı verildiği, MASAK raporunda adı geçen annesi N.O.'nun ise İstanbul'da gözaltına alındığı bildirildi. Van'daki Düğün Sonrası Başlatılan Soruşturmada Kimler Gözaltına Alındı? MASAK Raporunda Kimlerin Adı Geçiyor? Van'da gerçekleştirilen düğünün görüntülerinin sosyal medyada gündem olmasının ardından Mehmet Fatih Tançalan hakkında başlatılan soruşturmada yeni gelişmeler yaşandı. “Suçtan kaynaklanan malvarlığı değerlerini aklama” suçlamasıyla tutuklanan Tançalan'ın eşi Çağla Öz Tançalan hakkında gözaltı kararı verildiği, MASAK raporunda adı geçen annesi N.O.'nun ise İstanbul'da gözaltına alındığı bildirildi. Haber Merkezi Editör 12.09.2026 - 17:07 Yayınlanma — Paylaşım 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Haberlerimizi Google’da Takip Edin Gelişmelerden anında haberdar olun. Google’da tercih edilen kaynak olarak ekleyin Van'da gerçekleştirilen düğünün görüntülerinin sosyal medyada gündem olmasının ardından Mehmet Fatih Tançalan hakkında başlatılan soruşturmada yeni gelişmeler yaşandı. “Suçtan kaynaklanan malvarlığı değerlerini aklama” suçlamasıyla tutuklanan Tançalan'ın eşi Çağla Öz Tançalan hakkında gözaltı kararı verildiği , MASAK raporunda adı geçen annesi N.O.'nun ise İstanbul'da gözaltına alındığı bildirildi. Van'daki Düğünün Ardından Soruşturma Başlatıldı Sosyal medya ünlüsü Çağla Öz ile “Vanlı Kara Haydar” ismiyle tanınan Mehmet Fatih Tançalan'ın Van'da gerçekleştirilen düğününden görüntüler sosyal medya platformlarında geniş yankı uyandırdı. Paylaşımların ardından Van Cumhuriyet Başsavcılığı , Mehmet Fatih Tançalan hakkında soruşturma başlattı. Tançalan, yürütülen soruşturma kapsamında gözaltına alındı. Mehmet Fatih Tançalan Tutuklandı Emniyetteki ve savcılıktaki işlemlerinin tamamlanmasının ardından Mehmet Fatih Tançalan, “suçtan kaynaklanan malvarlığı değerlerini aklama” suçlamasıyla adliyeye sevk edildi. Tançalan, çıkarıldığı nöbetçi sulh ceza hakimliği tarafından tutuklandı. Soruşturmanın devamında başka isimler hakkında da işlem yapıldığı bildirildi. Çağla Öz Tançalan Hakkında Gözaltı Kararı Soruşturma kapsamında Tançalan'ın eşi, sosyal medya ünlüsü Çağla Öz Tançalan hakkında da gözaltı kararı verildi. Çağla Öz Tançalan'ın arandığı bildirildi. Soruşturmanın bu aşamasında hakkında gözaltı kararı bulunması, kendisine yöneltilen olası suçlamalar bakımından kesinleşmiş bir hüküm anlamına gelmiyor. MASAK Raporunda Adı Geçen Kayınvalide Gözaltında Soruşturma kapsamında hazırlanan MASAK raporunda ismi geçtiği belirtilen N.O. , İstanbul'da gözaltına alındı. N.O.'nun Mehmet Fatih Tançalan'ın kayınvalidesi olduğu belirtildi. Raporda adı geçen M.S.T.'nin de Muradiye ilçesinde gözaltına alındığı kaydedildi. Soruşturmada Gözler Yeni Gelişmelerde Düğün görüntülerinin sosyal medyada yayılmasının ardından başlayan süreçte Mehmet Fatih Tançalan tutuklanırken , Çağla Öz Tançalan hakkında gözaltı kararı verildiği bildirildi. MASAK raporunda isimlerinin geçtiği belirtilen N.O. ve M.S.T. gözaltına alınırken , Çağla Öz Tançalan'ın aranmasına devam edildiği aktarıldı. Muhabir: Haber Merkezi Editörün Seçtiği Ceylanpınar Hava Durumu (Güncel) Editörün Seçtiği Halfeti Hava Durumu (Güncel) Editörün Seçtiği 12 Eylül Şanlıurfa Cenaze İlanları 2026: Güncel Bugün Vefat Edenlerin Bilgileri Editör Hakkında Haber Merkezi Bunlar</t>
+          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! SON TV</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Van'daki Düğün Sonrası Başlatılan Soruşturmada Kimler Gözaltına Alındı? MASAK Raporunda Kimlerin Adı Geçiyor? Van'daki Düğün Sonrası Başlatılan Soruşturmada Kimler Gözaltına Alındı? MASAK Raporunda Kimlerin Adı Geçiyor? urfanatik.com Van'da gerçekleştirilen düğünün görüntülerinin sosyal medyada gündem olmasının ardından Mehmet Fatih Tançalan hakkında başlatılan soruşturmada yeni gelişmeler yaşandı. “Suçtan kaynaklanan malvarlığı değerlerini aklama” suçlamasıyla tutuklanan Tançalan'ın eşi Çağla Öz Tançalan hakkında gözaltı kararı verildiği, MASAK raporunda adı geçen annesi N.O.'nun ise İstanbul'da gözaltına alındığı bildirildi. Van'daki Düğün Sonrası Başlatılan Soruşturmada Kimler Gözaltına Alındı? MASAK Raporunda Kimlerin Adı Geçiyor?</t>
+          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! SON TV Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı!</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.urfanatik.com/vandaki-dugun-sonrasi-baslatilan-sorusturmada-kimler-gozaltina-alindi-masak-raporunda-kimlerin-adi-geciyor</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul | Van</t>
-        </is>
-      </c>
+          <t>https://www.son.tv/dunyaca-unlu-yazar-ile-oyuncu-ve-akademisyenlerin-lgbt-derneklerine-para-transferleri-masak-kayitlarinda-cikti/</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
@@ -3812,7 +3961,7 @@
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr"/>
@@ -3826,7 +3975,7 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="n">
-        <v>126.25</v>
+        <v>102.18</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>15</v>
@@ -3835,27 +3984,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:42:18</t>
+          <t>2026-09-12 20:23:48</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>gözaltı</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11 ilde Şimşekler suç örgütüne operasyon: 64 gözaltı, dev mal varlığına el konuldu</t>
+          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11 ilde Şimşekler suç örgütüne operasyon: 64 gözaltı, dev mal varlığına el konuldu Takvim</t>
+          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -3865,35 +4014,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>el konuldu, mal varlığı</t>
+          <t>masak</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Adana merkezli 11 ilde Halim Şimşek’in liderliğini yaptığı Şimşekler Suç Örgütüne operasyon düzenlendi. 64 şüpheli gözaltına alınırken 10 şirket ve çok sayıda araca el konuldu. Adana merkezli 11 ilde Halim Şimşek’in liderliğini yaptığı Şimşekler Suç Örgütüne operasyon düzenlendi. 64 şüpheli gözaltına alınırken 10 şirket ve çok sayıda araca el konuldu. Adana merkezli 11 ilde Halim Şimşek’in liderliğini yaptığı Şimşekler Suç Örgütüne operasyon düzenlendi. 64 şüpheli gözaltına alınırken 10 şirket ve çok sayıda araca el konuldu. Adana merkezli 11 ilde "Şimşekler" suç örgütüne dev operasyon: Şafak baskınında 64 gözaltı! Giriş Tarihi: 12 Eylül 2026 11:42 Güncelleme Tarihi: 12 Eylül 2026 11:55 Facebook X NSosyal Linki Kopyala Yazı Boyutu Takvim'i Google'a ekleyin, doğru kaynaktan haberi alın! Adana Cumhuriyet Başsavcılığı koordinesinde yürütülen soruşturma kapsamında, liderliğini yurt dışında firari bulunan Halim Şimşek'in yaptığı "Şimşekler Suç Örgütü"ne yönelik 11 ilde eş zamanlı operasyon düzenlendi. Aylar süren takibin ardından 12 Eylül 2026'da gerçekleştirilen baskınlarda 64 şüpheli gözaltına alınırken; cinayet, haraç ve el bombalı eylemlerle anılan örgütün 10 şirket ile çok sayıda taşınmaz ve aracına el konuldu. Emirhan Ceylan Takvim.com.tr Güncel Ertuğrul Kaya’nın Trabzonluları hedef alan videolu açıklamasına soruşturma 11.09.2026 Cuma Alişan'ın Çağla Şıkel'e çorba şakası boşa çıktı: Eğlenceli anları sosyal medyadan</t>
+          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11 ilde Şimşekler suç örgütüne operasyon: 64 gözaltı, dev mal varlığına el konuldu 11 ilde Şimşekler suç örgütüne operasyon: 64 gözaltı, dev mal varlığına el konuldu Takvim Adana merkezli 11 ilde Halim Şimşek’in liderliğini yaptığı Şimşekler Suç Örgütüne operasyon düzenlendi. 64 şüpheli gözaltına alınırken 10 şirket ve çok sayıda araca el konuldu. Adana merkezli 11 ilde "Şimşekler" suç örgütüne dev operasyon: Şafak baskınında 64 gözaltı! Giriş Tarihi: 12 Eylül 2026 11:42 Güncelleme Tarihi: 12 Eylül 2026 11:55 Facebook X NSosyal Linki Kopyala Yazı Boyutu Takvim'i Google'a ekleyin, doğru kaynaktan haberi alın! Adana Cumhuriyet Başsavcılığı koordinesinde yürütülen soruşturma kapsamında, liderliğini yurt dışında firari bulunan Halim Şimşek'in yaptığı "Şimşekler Suç Örgütü"ne yönelik 11 ilde eş zamanlı operasyon düzenlendi. Aylar süren takibin ardından 12 Eylül 2026'da gerçekleştirilen baskınlarda 64 şüpheli gözaltına alınırken; cinayet, haraç ve el bombalı eylemlerle anılan örgütün 10 şirket ile çok sayıda taşınmaz ve aracına el konuldu. Emirhan Ceylan Takvim.com.tr Güncel Ertuğrul Kaya’nın Trabzonluları hedef alan videolu açıklamasına soruşturma 11.09.2026 Cuma Alişan'ın Çağla Şıkel'e çorba şakası boşa çıktı: Eğlenceli anları sosyal medyadan</t>
+          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.takvim.com.tr/video/guncel/adanada-simsekler-suc-orgutune-operasyon-11-ilde-64-gozalti</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Adana</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOd0N2UGZsdGF5RFhyX081cE5HLWdsQ0hEbXpHVExlS1FKS3k0OFVkMmJ0NWhJVU9wTTlpZzZNRjFtLXdvaUxZT2hMY2VoakFrdlVDaGV3TWFrTUNiSWI1cEtHRkNrYVpwM2JkY05SOVVWcVZFVzdyRlJNVnhrZmtMaGxLUTVFWExWSHJ6Y2xZUmpRZi01eEJUWjlhX2Ywc2FBajVpU3Z4SQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
@@ -3902,7 +4047,7 @@
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr"/>
@@ -3916,7 +4061,7 @@
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="n">
-        <v>103.64</v>
+        <v>53.16</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>16</v>
@@ -3925,7 +4070,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:08:00</t>
+          <t>2026-09-13 08:33:15</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -3940,12 +4085,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MASAK ve KOM raporları skandalı ortaya çıkardı: Tepebaşı Belediyesi soruşturmasında hapis talebi</t>
+          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı!</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>MASAK ve KOM raporları skandalı ortaya çıkardı: Tepebaşı Belediyesi soruşturmasında hapis talebi Yirmidort.tv</t>
+          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! SON TV</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -3961,29 +4106,25 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Haberin devamı için tıklayınız... Eskişehir Cumhuriyet Başsavcılığı, Tepebaşı Belediyesi'nin doğrudan temin ihalelerinde usulsüzlük yapılarak kamunun zarara uğratıldığı iddiasıyla yürütülen soruşturmayı tamamladı. Aralarında belediye personeli ve şirket yetkililerinin de bulunduğu 22 şüpheli hakkında hazırlanan iddianamede; sahte teklifler, paravan şirketler ve kripto varlıklar üzerinden milyonlarca liralık fonun sistem dışına çıkarıldığı tespit edilirken, 13'ü tutuklu 22 sanık hakkında Haberin devamı için tıklayınız...</t>
+          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! SON TV</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>MASAK ve KOM raporları skandalı ortaya çıkardı: Tepebaşı Belediyesi soruşturmasında hapis talebi MASAK ve KOM raporları skandalı ortaya çıkardı: Tepebaşı Belediyesi soruşturmasında hapis talebi Yirmidort.tv Eskişehir Cumhuriyet Başsavcılığı, Tepebaşı Belediyesi'nin doğrudan temin ihalelerinde usulsüzlük yapılarak kamunun zarara uğratıldığı iddiasıyla yürütülen soruşturmayı tamamladı. Aralarında belediye personeli ve şirket yetkililerinin de bulunduğu 22 şüpheli hakkında hazırlanan iddianamede; sahte teklifler, paravan şirketler ve kripto varlıklar üzerinden milyonlarca liralık fonun sistem dışına çıkarıldığı tespit edilirken, 13'ü tutuklu 22 sanık hakkında Haberin devamı için tıklayınız...</t>
+          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! SON TV MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı!</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.yirmidort.tv/gundem/masak-ve-kom-raporlari-skandali-ortaya-cikardi-tepebasi-belediyesi-sorusturmasinda-hapis-talebi-291222</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Eskişehir</t>
-        </is>
-      </c>
+          <t>https://www.son.tv/flas-gelisme-masak-incelemesinde-dikkat-ceken-para-trafigi-6-dernege-yurt-disindan-33-milyon-dolari-asan-transfer-ortaya-cikti/</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -3992,7 +4133,7 @@
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr"/>
@@ -4006,7 +4147,7 @@
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="n">
-        <v>106.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>17</v>
@@ -4015,27 +4156,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:01:00</t>
+          <t>2026-09-13 14:13:08</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>borç krizi</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Bankalar artık buna da bakacak!</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Bankalar artık buna da bakacak! Söz Sakarya</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -4045,35 +4186,35 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Bankalar artık buna da bakacak! Söz Sakarya</t>
+          <t>"Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. Mersin limanı’nda 350 kilogram kokain ele geçirildi Bingöl'de otomobil ile tır çarpıştı: 5 yaralı Van’da Düğün altınları için MASAK incelemesi Yayınlanma: 13 Eylül 2026 Pazar 17:13 Kaynak: Necmi Ertuş "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. Van Cumhuriyet Başsavcılığı tarafından Mehmet Fatih Tançalan hakkında sosyal medya platformlarında yapılan paylaşımlar nedeniyle "suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan soruşturma başlatıldı. Soruşturma kapsamında dün İstanbul'da gözaltına alınan Çağla Öz Tançalan'ın İstanbul Emniyet Müdürlüğü Mali Suçlarla Mücadele Şubesindeki işlemleri tamamlandı. Tançalan, işlemlerinin ardından Van Emniyet Müdürlüğüne götürüldü. Soruşturma kapsamında Van İl Emniyet Müdürlüğü Asayiş Şubesi ekipleri, Mehmet Fatih Tançalan'ı 8 Eylül'de Van'ın Muradiye ilçesindeki evinde gözaltına aldı. Emniyetteki işlemlerinin ardından adliyeye sevk edilen Tançalan, çıkarıldığı hakimlikçe "suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan tutuklandı. Tançalan'ın sosyal medyaya yansıyan görüntüleri ile düğününde takıldığı belirtilen yüksek miktardaki altınlara ilişkin de mali araştırma başlatıldı ve Mali Suçları Araştırma Kurulundan (MASAK) inceleme talep edildi. Tançalan'ın düğününde eşi Çağla Öz Tançalan'a takılan ziynet eşyaları ve paralar, Muradiye'de bir ev ve eklentisinde yapılan aramada ele geçirildi. Aramanın gerçekleştirildiği evin sahibi de gözaltına alındı. HABERE YORUM KAT YASAL UYARI: Yazılan yoruml</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Bankalar artık buna da bakacak! Bankalar artık buna da bakacak! Söz Sakarya Bankalar artık buna da bakacak!</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. Mersin limanı’nda 350 kilogram kokain ele geçirildi Bingöl'de otomobil ile tır çarpıştı: 5 yaralı Van’da Düğün altınları için MASAK incelemesi Yayınlanma: 13 Eylül 2026 Pazar 17:13 Kaynak: Necmi Ertuş "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. Van Cumhuriyet Başsavcılığı tarafından Mehmet Fatih Tançalan hakkında sosyal medya platformlarında yapılan pay</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9pdl9FdDVyWXJZeXhta3B0YURqMUY2QWdBWFJSQXd1dVRzOTBzeThuVlQ5NXRHS01Bd1NoWkY2TDVjVmUzZVBjOEhCRFNDaThnOW1kWkI4YlhCZTVPbFJYdksxdm16QnVPNUswbVdNUDhsNzU2NjZB0gF8QVVfeXFMUGstUjB5RFpSdkFXMUp3Qk5XWnVWNEpfZlF2NEVHRVJjUDlSTkl3N2QwNk51MFEwYnJKVE01SjlXekxlS1gyZHVHLXNpdmptbWV6bDF2NzdodWlxLVVVaDE4VWplM01ZWmliV3A2Q3dWRURwd2VnWmVNSEc4Mg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>https://www.hakkarihabertv.com/vanda-dugun-altinlari-icin-masak-incelemesi-88464h.htm</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Bingöl | İstanbul | Van</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -4082,7 +4223,7 @@
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr"/>
@@ -4096,7 +4237,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="n">
-        <v>24.68</v>
+        <v>70.25</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>18</v>
@@ -4105,27 +4246,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:53:30</t>
+          <t>2026-09-13 09:05:00</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposundaki yangın beş depoyu yok etti, yakınındaki evde hasar oluştu</t>
+          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposundaki yangın beş depoyu yok etti, yakınındaki evde hasar oluştu Aksiyon.com.TR</t>
+          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı aydinlik.com.tr</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -4135,22 +4276,18 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Antalya’nın Muratpaşa ilçesinde ambalaj depolarında çıkan yangın, yaklaşık iki saatte kontrol altına alındı; beş depodaki ürünler ve bir ev hasar gördü. Antalya’nın Muratpaşa ilçesinde ambalaj depolarında çıkan yangın, yaklaşık iki saatte kontrol altına alındı; beş depodaki ürünler ve bir ev hasar gördü. Antalya’nın Muratpaşa ilçesinde ambalaj depolarında çıkan yangın, yaklaşık iki saatte kontrol altına alındı; beş depodaki ürünler ve bir ev hasar gördü. yangın kısa sürede yayıldı, soğutma çalışmaları sürüyor Yangın, saat 14.45 sıralarında Muratpaşa ilçesi Yenigöl Mahallesi Lavanta Sokak'ta ambalaj ürünlerinin bulunduğu bir depoda başladı. Alevler kısa sürede yoğun dumanla birlikte büyüyerek bitişikteki diğer depolara ve yakınındaki bir eve sıçradı. Depolarda bulunan yanıcı malzemelerin yoğunluğu alevlerin çabuk yayılmasına neden oldu. itfaiye müdahalesi ve bölge halkının katkısı: İhbar üzerine bölgeye Antalya Büyükşehir Belediyesi İtfaiye Daire Başkanlığına bağlı çok sayıda ekip ile polis sevk edildi. İtfaiye ekipleri yangının daha geniş bir alana yayılmasını önlemek için farklı noktalardan müdahalede bulundu; bazı noktalarda alevler çatıya kadar ulaştı. Ekiplerin müdahalesiyle eve sıçrayan alevler kısa sürede söndürüldü, ancak yapının bir bölümü zarar gördü. Bölgedeki vatandaşlar da söndürme çalışmalarına destek vererek itfaiye hortumlarının taşınmasına yardım etti ve depo önündeki bir kamyoneti iterek tehlike alanından uzaklaştırdı. zarar ve depo sahibinin açıklaması: Yaklaşık iki saat süren yoğun müdahalelerin ardından yangın büyük ölçüde kontrol altına alınırken soğutma çalışmaları devam ediyor. Yangında beş depodaki ürünler yanarak kullanılamaz hale geldi. Depoların sahibi Arif Ordu bölgeye gelerek yaptığı açıklamada, "Haber üzerine geldik, depoların hepsi bizim, kiradalar. Perişanız. 1 dönümde AVM ambalaj ürünleri, 1 dönümde otel ürünleri bir kısımda da izolasyon ürünleri bulunuyordu. Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. İtfaiye yetkilileri, soğutma çalışmaları tamamlanana ve bölgedeki risk tamamen ortadan kalkana kadar nöbet ve kontrollerin sürdürüleceğini bildirdi. ANTALYA’DA AMBALAJ ÜRÜNLERİNİN BULUNDUĞU BİR DEPODA ÇIKAN YANGIN, ÇEVREDEKİ DEPOLAR İLE YAKINDAKİ BİR EVE SIÇRADI. 1 Anlaşmazlık yaşamlarını aldı: Maltepe'de öldürülen ev sahipleri defnedildi Anlaşmazlık yaşamlarını aldı: Maltepe'de öldürülen ev sahipleri defnedildi 2 Kars çevre yolunda sert çarpışma: 6 kişi hastaneye kaldırıldı Kars çevre yolunda sert çarpışma: 6 kişi hastaneye kaldırıldı 3 Düzce'de bir haftada suç çözüm oranı yüzde 99'a çıktı Düzce'de bir haftada suç çözüm oranı yüzde 99'a çıktı 4 Muş’ta kayıp Suat Balkaya için Karasu Nehri çevresinde kapsamlı arama Muş’ta kayıp Suat Balkaya için Karasu Nehri çevresinde kapsamlı arama 5 Ezgi Apartmanı davasında bilirkişi raporları kolon kesme iddiasını reddetti Ezgi Apartmanı davasında bilirkişi raporları kolon kesme iddiasını reddetti 6 Samsun'da cadde kenarında çocuk otomobilin çarpmasıyla hafif yaralandı Samsun'da cadde kenarında çocuk otomobilin çarpmasıyla hafif yaralandı 7 Sivaslı'da meşelik yangını yoğun müdahaleyle kontrol altına alındı Sivaslı'da meşelik yangını yoğun müdahaleyle kontrol altına alındı Antalya'da ambalaj deposundaki yangın beş depoyu yok etti, yakınındaki evde hasar oluştu yangın kısa sürede yayıldı, soğutma çalışmaları sürüyor Antalya’nın Muratpaşa ilçesinde ambalaj depolarında çıkan yangın, yaklaşık iki saatte kontrol altına alındı; beş depodaki ürünler ve bir ev hasar gördü. Yangın, saat 14.45 sıralarında Muratpaşa ilçesi Yenigöl Mahallesi Lavanta Sokak'ta ambalaj ürünlerinin bulunduğu bir depoda başladı. Alevler kısa sürede yoğun dumanla birlikte büyüyerek bitişikteki diğer depolara ve yakınındaki bir eve sıçradı. Depolarda bulunan yanıcı malzemelerin yoğunluğu alevlerin çabuk yayılmasına neden oldu. İhbar üzerine bölgeye Antalya Büyükşehir Belediyesi İtfaiye Daire Başkanlığına bağlı çok sayıda ekip ile polis sevk edildi. İtfaiye ekipleri yangının daha geniş bir alana yayılmasını önlemek için farklı noktalardan müdahalede bulundu; bazı noktalarda alevler çatıya kadar ulaştı. Ekiplerin müdahalesiyle eve sıçrayan alevler kısa sürede söndürüldü, ancak yapının bir bölümü zarar gördü. Bölgedeki vatandaşlar da söndürme çalışmalarına destek vererek itfaiye hortumlarının taşınmasına yardım etti ve depo önündeki bir kamyoneti iterek tehlike alanından uzaklaştırdı. Yaklaşık iki saat süren yoğun müdahalelerin ardından yangın büyük ölçüde kontrol altına alınırken soğutma çalışmaları devam ediyor. Yangında beş depodaki ürünler yanarak kullanılamaz hale geldi. Depoların sahibi Arif Ordu bölgeye gelerek yaptığı açıklamada, "Haber üzerine geldik, depoların hepsi bizim, kiradalar. Perişanız. 1 dönümde AVM ambalaj ürünleri, 1 dönümde otel ürünleri bir kısımda da izolasyon ürünleri bulunuyordu. Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. İtfaiye yetkilileri, soğutma çalışmaları tamamlanana ve bölgedeki risk tamamen ortadan kalkana kadar nöbet ve kontrollerin sürdürüleceğini bildirdi. ANTALYA’DA AMBALAJ ÜRÜNLERİNİN BULUNDUĞU BİR DEPODA ÇIKAN YANGIN, ÇEVREDEKİ DEPOLAR İLE YAKINDAKİ BİR EVE SIÇRADI. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. aksiyon.com.tr Gündem'deyim ama spesifik olarak eğitim ve sağlık politikalarındaki güncel gelişmelere odaklanıyorum. Öğrenmeye açık, meraklı ve enerjik bir yapım var. 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
+          <t>Vatan Partisi’nin dikkat çektiği küresel fon ağı MASAK raporuyla belgelendi. 6 LGBTİ+ derneğine Batı’dan 3,3 milyon doları aşkın kaynak aktarıldığı saptandı. 37 yabancı kurumdan sağlanan bu finansmanın cinsiyet değiştirme ameliyatları dahil çeşitli faaliyetlerde kullanıldığı belirlendi.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposundaki yangın beş depoyu yok etti, yakınındaki evde hasar oluştu Antalya'da ambalaj deposundaki yangın beş depoyu yok etti, yakınındaki evde hasar oluştu Aksiyon.com.TR Antalya’nın Muratpaşa ilçesinde ambalaj depolarında çıkan yangın, yaklaşık iki saatte kontrol altına alındı; beş depodaki ürünler ve bir ev hasar gördü. yangın kısa sürede yayıldı, soğutma çalışmaları sürüyor Yangın, saat 14.45 sıralarında Muratpaşa ilçesi Yenigöl Mahallesi Lavanta Sokak'ta ambalaj ürünlerinin bulunduğu bir depoda başladı. Alevler kısa sürede yoğun dumanla birlikte büyüyerek bitişikteki diğer depolara ve yakınındaki bir eve sıçradı. Depolarda bulunan yanıcı malzemelerin yoğunluğu alevlerin çabuk yayılmasına neden oldu. itfaiye müdahalesi ve bölge halkının katkısı: İhbar üzerine bölgeye Antalya Büyükşehir Belediyesi İtfaiye Daire Başkanlığına bağlı çok sayıda ekip ile polis sevk edildi. İtfaiye ekipleri yangının daha geniş bir alana yayılmasını önlemek için farklı noktalardan müdahalede bulundu; bazı noktalarda alevler çatıya kadar ulaştı. Ekiplerin müdahalesiyle eve sıçrayan alevler kısa sürede söndürüldü, ancak yapının bir bölümü zarar gördü. Bölgedeki vatandaşlar da söndürme çalışmalarına destek vererek itfaiye hortumlarının taşınmasına yardım etti ve depo önündeki bir kamyoneti iterek tehlike alanından uzaklaştırdı. zarar ve depo sahibinin açıklaması: Yaklaşık iki saat süren yoğun müdahalelerin ardından yangın büyük ölçüde kontrol altına alınırken soğutma çalışmaları devam ediyor. Yangında beş depodaki ürünler yanarak kullanılamaz hale geldi. Depoların sahibi Arif Ordu bölgeye gelerek yaptığı açıklamada, "Haber üzerine geldik, depoların hepsi bizim, kiradalar. 1 dönümde AVM ambalaj ürünleri, 1 dönümde otel ürünleri bir kısımda da izolasyon ürünleri bulunuyordu. Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. ANTALYA’DA AMBALAJ ÜRÜNLERİNİN BULUNDUĞU BİR DEPODA ÇIKAN YANGIN, ÇEVREDEKİ DEPOLAR İLE YAKINDAKİ BİR EVE SIÇRADI. 1 Anlaşmazlık yaşamlarını aldı: Maltepe'de öldürülen ev sahipleri defnedildi Anlaşmazlık yaşamlarını aldı: Maltepe'de öldürülen ev sahipleri defnedildi 2 Kars çevre yolunda sert çarpışma: 6 kişi hastaneye kaldırıldı Kars çevre yolunda sert çarpışma: 6 kişi hastaneye kaldırıldı 3 Düzce'de bir haftada suç çözüm oranı yüzde 99'a çıktı Düzce'de bir haftada suç çözüm oranı yüzde 99'a çıktı 4 Muş’ta kayıp Suat Balkaya için Karasu Nehri çevresinde kapsamlı arama Muş’ta kayıp Suat Balkaya için Karasu Nehri çevresinde kapsamlı arama 5 Ezgi Apartmanı davasında bilirkişi raporları kolon kesme iddiasını reddetti Ezgi Apartmanı davasında bilirkişi raporları kolon kesme iddiasını reddetti 6 Samsun'da cadde kenarında çocuk otomobilin çarpmasıyla hafif yaralandı Samsun'da cadde kenarında çocuk otomobilin çarpmasıyla hafif yaralandı 7 Sivaslı'da meşelik yangını yoğun müdahaleyle kontrol altına alındı Sivaslı'da meşelik yangını yoğun müdahaleyle kontrol altına alındı Antalya'da ambalaj deposundaki yangın beş depoyu yok etti, yakınındaki evde hasar oluştu yangın kısa sürede yayıldı, soğutma çalışmaları sürüyor Antalya’nın Muratpaşa ilçesinde ambalaj depolarında çıkan yangın, yaklaşık iki saatte kontrol altına alındı; beş depodaki ürünler ve bir ev hasar gördü. Yangın, saat 14.45 sıralarında Muratpaşa ilçesi Yenigöl Mahallesi Lavanta Sokak'ta ambalaj ürünlerinin bulunduğu bir depoda başladı. İhbar üzerine bölgeye Antalya Büyükşehir Belediyesi İtfaiye Daire Başkanlığına bağlı çok sayıda ekip ile polis sevk edildi. Yaklaşık iki saat süren yoğun müdahalelerin ardından yangın büyük ölçüde kontrol altına alınırken soğutma çalışmaları devam ediyor. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
+          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı aydinlik.com.tr Vatan Partisi’nin dikkat çektiği küresel fon ağı MASAK raporuyla belgelendi. 6 LGBTİ+ derneğine Batı’dan 3,3 milyon doları aşkın kaynak aktarıldığı saptandı. 37 yabancı kurumdan sağlanan bu finansmanın cinsiyet değiştirme ameliyatları dahil çeşitli faaliyetlerde kullanıldığı belirlendi.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -4160,31 +4297,19 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.aksiyon.com.tr/antalya-da-ambalaj-deposundaki-yangin-bes-depoyu-yok-etti-yakinindaki-evde-hasar-olustu-353386</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Antalya | Bursa | Düzce | İstanbul | Muş</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>Muratpaşa | Maltepe | Sivaslı</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>sıralarında Muratpaşa ilçesi Yenigöl Mahallesi</t>
-        </is>
-      </c>
+          <t>https://www.aydinlik.com.tr/haber/vatan-partisi-uyarmisti-masak-belgeledi-iste-lgbti-derneklerinin-kuresel-fon-carki-589932</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr"/>
@@ -4198,7 +4323,7 @@
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="n">
-        <v>150.75</v>
+        <v>86.62</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>19</v>
@@ -4207,27 +4332,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 12:42:41</t>
+          <t>2026-09-13 06:35:00</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da ev ve depoda çıkan yangına itfaiye ekipleri müdahale ediyor</t>
+          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da ev ve depoda çıkan yangına itfaiye ekipleri müdahale ediyor Son Dakika</t>
+          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Ege Telgraf</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -4237,44 +4362,32 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>işletme, masak</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da ev ve depoda çıkan yangına itfaiye ekipleri müdahale ediyor Son Dakika</t>
+          <t>Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Gündem Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 13.09.2026 - 09:35 Okunma Süresi: 1 Dk Adalet Bakanı Akın Gürlek, İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonlarına ilişkin açıklamalarda bulundu. 5 il merkezli olarak 15 ili kapsayan operasyonlarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığı bildirildi. 162 ŞÜPHELİ HAKKINDA ADLİ SÜREÇ Emniyet ve Jandarma birimlerinin katılımıyla gerçekleştirilen operasyonlarda, 162 şüpheli hakkında adli işlem uygulandı. Soruşturmaların; fuhşa aracılık veya yer temini, müstehcen içeriklerin üretilmesi ve yayılması ile çocukların bu tür içeriklere maruz bırakılmasına yönelik faaliyetler üzerinde yoğunlaştığı belirtildi. Dolar 48 TL’yi aştı, Euro 56 TL seviyesinde! 13 Eylül güncel döviz kurları: Dolar kaç TL? Euro ne kadar? İçeriği Görüntüle Faaliyetlere ortam sağladığı değerlendirilen bazı işletmeler ile soruşturmaya konu edilen 9 dernek de incelemeye alındı. Toplam 13 işletme hakkında da adli işlem gerçekleştirildi. 15 İLDE EŞ ZAMANLI OPERASYON DÜZENLENDİ Soruşturma sürecinde gizli soruşturmacı görevlendirilmesinin yanı sıra teknik ve fiziki takip yapıldığı bildirildi. Tanık ifadeleri, dijital incelemeler ve görüntü kayıtlarından da yararlanıldığı aktarıldı. Elde edilen deliller doğrultusunda 15 ilde eş zamanlı gözaltı, arama ve el koyma işlemleri gerçekleştirildi. Operasyonlarda uyuşturucu maddeler ile çok sayıda dijital materyale el konuldu. SOSYAL MEDYA HESAPLARINA ERİŞİM ENGELİ Soruşturmalar kapsamında çok sayıda sosyal medya hesabı ve internet sitesi hakkında da erişimin engellenmesi tedbirinin uygulandığı açıklandı. MASAK'TAN FON HAREKETLERİNE İNCELEME Operasyonların mali boyutuna ilişkin yapılan incelemelerde ise MASAK'ın bazı derneklere yönelik para hareketlerini mercek altına aldığı belirtildi. Yapılan incelemelerde, bazı derneklere yurt dışında bulunan kamu kurumları ve yabancı kuruluşlardan yüksek miktarlarda fon aktarıldığının tespit edildiği aktarıldı. Söz konusu fonların kaynağı ile soruşturma kapsamında incelenen faaliyetler arasında herhangi bir bağlantı bulunup bulunmadığının araştırıldığı kaydedildi. Adalet Bakanı Akın Gürlek, açıklamasında çocukları, gençleri ve aileleri hedef alan suç yapılanmaları, istismar ağları ve yasa dışı faaliyetlere karşı müsamaha gösterilmeyeceğini ifade etti. Kaynak: HABER MERKEZİ Editörün Seçtiği Aydın’da ayakta kalan üç kuleden biri! Zindanından hamamına eksiksiz Ege’nin 200 yıllık az bilinen tarihi şatosu Editörün Seçtiği Ne Efes ne Bergama! 5 bin yıllık değişimin tanığı: İzmir’in kayıp ada kentinde binlerce boncuk bulundu Editörün Seçtiği Ne Efes ne Bergama! İZBAN’dan inip kralların tepesine çıkılıyor: İzmir’de üç saraylı antik kenti çoğu kişi bilmiyor Editör Hakkında Kader Ergin Bunlar da ilgini</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da ev ve depoda çıkan yangına itfaiye ekipleri müdahale ediyor Antalya Muratpaşa'da ev ve depoda çıkan yangına itfaiye ekipleri müdahale ediyor Son Dakika Antalya Muratpaşa'da ev ve depoda çıkan yangına itfaiye ekipleri müdahale ediyor Son Dakika</t>
+          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Ege Telgraf Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Gündem Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcjhNaGZxc2wyLXZobzladXRmNnhzWTg5MFZYSzUyc0xUWF9FX3NfZVpBaFE4X094b1lNd093WHF6RFotWnVIT0lMMFBDckNxdWR2TFlRb1I3OWRTQVk2T1JNVkJJOE51cy1HTGpqRzYwVHZNMkZfSHRlTm4xVjNfR2dFMmEwMEJLYTBtT1hTWGNfNmtGRTdTSVZpQWVzZFl0eVHSAZwBQVVfeXFMTnhjY3N1RXhSMWZNdTYxeGt1ZEFaR1NyLUNEeHMyUW1WSWk3TzNvZ1RQNGZHcG1oMUt0MmJMY3FZMmdyWVRxenRmVjdoZHRVYXNIYjZNcFFKcHUxSmRqQVBUcDVqT0xtc3RPVkhFUXdtY24zSmg5d3hFc2tpUUVKdlZSQU1tQnNqZHBFNVhlSEZPVnpxdEN6allZU1R4?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Antalya</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Muratpaşa</t>
-        </is>
-      </c>
+          <t>https://www.egetelgraf.com/bakan-gurlek-duyurdu-9-dernek-ve-13-isletme-mercek-altinda-masak-harekete-gecti</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
@@ -4282,7 +4395,7 @@
       <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr"/>
@@ -4296,7 +4409,7 @@
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="n">
-        <v>107.66</v>
+        <v>94.75</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>20</v>
@@ -4305,27 +4418,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 13:47:00</t>
+          <t>2026-09-13 07:18:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposunda korkutan yangın! Ekipler tarafından kontrol altına alındı</t>
+          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposunda korkutan yangın! Ekipler tarafından kontrol altına alındı Şok Gazetesi</t>
+          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında KARAR</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -4335,41 +4448,41 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposunda korkutan yangın! Ekipler tarafından kontrol altına alındı Şok Gazetesi</t>
+          <t>İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonları 15 ili kapsadı. Fuhuş, müstehcenlik, uyuşturucu ve çocukların korunmasına ilişkin soruşturmalar kapsamında 162 şüpheli, 9 dernek ve 13 işletme hakkında adli işlem başlatıldı. Operasyonlarda çok sayıda uyuşturucu madde ve dijital materyale el konulurken, bazı sosyal medya hesapları ile internet siteleri hakkında da erişim engeli tedbiri uygulandı. İSTANBUL’DA 54 ADRESE OPERASYON İstanbul merkezli çalışmada İstanbul’un yanı sıra Ankara, Çanakkale, İzmir, Antalya, Ordu, Elazığ, Balıkesir, Aydın, Kırşehir, Iğdır ve Hatay’da operasyonlar düzenlendi. 38 şüpheliye yönelik adreslerde arama, yakalama ve el koyma işlemleri gerçekleştirilirken, İstanbul’da 10 işletme ile 6 LGBTİ+ derneğinin de aralarında bulunduğu toplam 54 iş yeri, ev ve dernekte arama yapıldı. UYUŞTURUCU, KAÇAK ALKOL VE RUHSATSIZ SİLAH ELE GEÇİRİLDİ Aramalarda 25 gram uyuşturucu ve uyarıcı madde, 10 gram kokain, 9 gram esrar, uyuşturucu olduğu değerlendirilen 10 sentetik hap, 7 enjektör ve iğnesi, yaklaşık 2 bin şişe kaçak alkol, ruhsatsız tabanca, 5 kamera kayıt cihazı ve 26 cep telefonu ele geçirildi. İstanbul'daki operasyonlarda 26 şüpheli gözaltına alınırken, diğer şüphelilerin yakalanmasına yönelik çalışmaların sürdüğü belirtildi. Bir işletme ise ruhsat faaliyetlerine aykırı hareket ettiği gerekçesiyle mühürlendi. MASAK İNCELEMESİNDE YÜKSEK TUTARLI FON AKTARIMI TESPİT EDİLDİ “Ailem Güvende” operasyonları kapsamında yürütülen soruşturmanın mali boyutunda MASAK incelemeleri dikkat çekti. Adalet Bakanı Akın Gürlek, bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığının tespit edildiğini açıkladı. Gürlek, söz konusu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısının araştırıldığını bildirdi. Gürlek'in açıklaması şöyle: "Cumhurbaşkanımız Recep Tayyip Erdoğan’ın ortaya koyduğu 2026-2035 Aile ve Nüfus On Yılı vizyonu ve 2026/4 Sayılı Cumhurbaşkanlığı Genelgesi doğrultusunda; çocuklarımızı, aile kurumunu ve toplum düzenini korumaya yönelik çalışmalarımızı kararlılıkla sürdürüyoruz. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımızın koordinasyonunda, Emniyet ve Jandarma teşkilatlarımızla birlikte başlatılan "Ailem Güvende" operasyonlarında, 5 il merkezli ve toplam 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletmeye yönelik adli işlemler gerçekleştirilmektedir. Soruşturmalarda; fuhşa aracılık veya yer temin eden kişiler, bu faaliyetlere ortam sağladığı değerlendirilen işletmeler, müstehcen içerik üreten ve yayan şüpheliler ile çocukların bu içeriklere maruz bırakılmasına yönelik faaliyetler incelenmiştir. Gizli soruşturmacı görevlendirilmesi, teknik ve fiziki takip, tanık beyanları, dijital incelemeler ve görüntü kayıtları sonucunda eş zamanlı gözaltı, arama ve el koyma işlemleri yapılmış; uyuşturucu maddeler ile çok sayıda dijital materyale el konulmuş, çok sayıda sosyal medya hesabı ve internet sitesine erişimin engellenmesi tedbiri uygulanmıştır. Soruşturmaların mali boyutunda ise LGBT ve ahlaksızlığı teşvik eden derneklere ilişkin; MASAK incelemelerinde bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığı tespit edilmiştir. Bu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısı araştırılmaktadır. Soruşturmaları titizlikle yürüten İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımıza, operasyonlarda görev alan Emniyet ve Jandarma teşkilatlarımızın kıymetli mensuplarına ve katkı sunan tüm kamu görevlilerimize teşekkür ediyorum. Anayasamızın aile ve çocukların korunmasına ilişkin devlete yüklediği sorumluluk çerçevesinde, çocuklarımızı, gençlerimizi ve ailelerimizi hedef alan hiçbir suç yapılanmasına, istismar ağına ve yasa dışı faaliyete müsamaha göstermeyeceğiz" ERİŞİM ENGELİ GETİRİLDİĞİ BELİRTİLEN 73 SİTE VE HESAP Soruşturma kapsamında erişim engeli getirildiği belirtilen site ve sosyal medya hesapları arasında LGBTİ+ alanında faaliyet gösteren dernek, oluşum ve platformların yanı sıra bazı akademik öğrenci toplulukları, medya platformları ve kişiler de yer aldı. Kaos GL SPoD LGBTİ+ Pembe Hayat LGBTİ+ Dayanışma Derneği ÜniKuir Derneği Lambdaistanbul LGBTİ+ Dayanışma Derneği 17 Mayıs Derneği HEVİ LGBTİ+ Derneği Kırmızı Şemsiye Derneği Genç LGBTİ+ Derneği Özgür Renkler Derneği Muamma LGBTİ+ Derneği Mersin 7 Renk Derneği Queer Adana Antalya BİZ Derneği Keskesor LGBTİ+ Cinsel Şiddetle Mücadele Derneği CETAD Velvele GZone Ayı Sözlük Boysan'ın Evi LGBTI News Turkey İstanbul LGBTİ+ Onur Haftası İstanbul Trans Onur Haftası Ankara Onur Haftası İzmir Onur Haftası ODTÜ LGBTİ+ Dayanışması Boğaziçi Üniversitesi LGBTİ+ Çalışmaları Kulübü Bilkent Renkli Düşün İstanbul Üniversitesi Radar Queer Deer – Hacettepe Üniversitesi Enes Hocaoğulları Yasemin Öz Ali Erol Ali Özbaş Zeynep Esmeray Özadikti Buse Kılıçkaya Şevval Kılıç Levent Pişkin Yıldız Tar İlker Hepkaner Mert Bell Mika Can Raun Seyhan Arman Kuir Tıp Öğrencileri Ağı Renkli Güvercin LGBTIQ GoFor Hormon Hakkım Kolektifi Kuir Baykuş GALA Derneği ÜniKuir2 Kuir Konya Eşitlik İçin Eğitimciler Kapsama Alanı Aşko Anlat Sportif Lezbon Arya'ya Ne Oldu Aforgütü Direnişin Renkleri Pozitif Dayanışma Bodrum Kadın Platformu Barış İçin LGBTİ+ Sivil Alan Araştırmaları Demos Araştırma Eşitlik İçin Kadın Platformu Qlub ÜniKuir Derste Zengiinn All Inclusive Mag LISTAG Boğaziçi LGBTİA İnter Dayanışma LGBT Türkiye 19:19 İstanbul'da yarın ulaşım ücretsiz: Sadece okul saatleri içerisinde 19:15 Trump, İran'la savaşın bitimine dair tarih verdi: Ara seçimler... 18:35 Suudi Arabistan'dan 'güvenlik' mesajı: İzin vermeyeceğiz 18:14 Trabzonspor’da Şenol Güneş sesleri 18:07 Yaz bitti mi, yağışlar başlıyor mu? Meteoroloji'den yeni hafta için 11 illik uyarı 18:04 Formula 1’in ilk Madrid yarışında tarihi zafer 17:54 TOKİ kiralık konut başvurusu ücretli mi? Bekarlar başvuru yapabilecek mi? Kiralık evler satın alınabilecek mi? 17:49 Osimhen için karar verildi: Dönüş tarihi belli oldu 17:38 Katılımevim’de yönetim değişti, Tera ile devir süreci sürüyor 17:38 Ankara’da yarın bazı yollar trafiğe kapatılacak 17:35 Irak, İran sınırındaki 3 sınır kapısını yeniden açıyor 17:34 Ünlülere yönelik uyuşturucu soruşturmasında yeni operasyon: Oyuncu Çağla Boz gözaltına alındı 17:32 Toprak Razgatlıoğlu San Marino’da 12. oldu 17:20 Uzaklaştırma kararı engel olmadı: Uzman çavuş eşini öldürüp intihar etti 17:13 Almanya'da aşırı sağ ve AfD’ye karşı protestolar artıyor MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. 13/09/2026 10:18 KAYNAK: Anadolu Ajansı (AA) İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonları 15 ili kapsadı. Fuhuş, müstehcenlik, uyuşturucu ve çocukların korunmasına ilişkin soruşturmalar kapsamında 162 şüpheli, 9 dernek ve 13 işletme hakkında adli işlem başlatıldı. Operasyonlarda çok sayıda uyuşturucu madde ve dijital materyale el konulurken, bazı sosyal medya hesapları ile internet siteleri hakkında da erişim engeli tedbiri uygulandı. İSTANBUL’DA 54 ADRESE OPERASYON İstanbul merkezli çalışmada İstanbul’un yanı sıra Ankara, Çanakkale, İzmir, Antalya, Ordu, Elazığ, Balıkesir, Aydın, Kırşehir, Iğdır ve Hatay’da operasyonlar düzenlendi. 38 şüpheliye yönelik adreslerde arama, yakalama ve el koyma işlemleri gerçekleştirilirken, İstanbul’da 10 işletme ile 6 LGBTİ+ derneğinin de aralarında bulunduğu toplam 54 iş yeri, ev ve dernekte arama yapıldı. UYUŞTURUCU, KAÇAK ALKOL VE RUHSATSIZ SİLAH ELE GEÇİRİLDİ Aramalarda 25 gram uyuşturucu ve uyarıcı madde, 10 gram kokain, 9 gram esrar, uyuşturucu olduğu değerlendirilen 10 sentetik hap, 7 enjektör ve iğnesi, yaklaşık 2 bin şişe kaçak alkol, ruhsatsız tabanca, 5 kamera kayıt cihazı ve 26 cep telefonu ele geçirildi. İstanbul'daki operasyonlarda 26 şüpheli gözaltına alınırken, diğer şüphelilerin yakalanmasına yönelik çalışmaların sürdüğü belirtildi. Bir işletme ise ruhsat faaliyetlerine aykırı hareket ettiği gerekçesiyle mühürlendi. MASAK İNCELEMESİNDE YÜKSEK TUTARLI FON AKTARIMI TESPİT EDİLDİ “Ailem Güvende” operasyonları kapsamında yürütülen soruşturmanın mali boyutunda MASAK incelemeleri dikkat çekti. Adalet Bakanı Akın Gürlek, bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığının tespit edildiğini açıkladı. Gürlek, söz konusu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısının araştırıldığını bildirdi. Gürlek'in açıklaması şöyle: "Cumhurbaşkanımız Recep Tayyip Erdoğan’ın ortaya koyduğu 2026-2035 Aile ve Nüfus On Yılı vizyonu ve 2026/4 Sayılı Cumhurbaşkanlığı Genelgesi doğrultusunda; çocuklarımızı, aile kurumunu ve toplum düzenini korumaya yönelik çalışmalarımızı kararlılıkla sürdürüyoruz. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımızın koordinasyonunda, Emniyet ve Jandarma teşkilatlarımızla birlikte başlatılan "Ailem Güvende" operasyonlarında, 5 il merkezli ve toplam 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletmeye yönelik adli işlemler gerçekleştirilmektedir. Soruşturmalarda; fuhşa aracılık veya yer temin eden kişiler, bu faaliyetlere ortam sağladığı değerlendirilen işletmeler, müstehcen içerik üreten ve yayan şüpheliler ile çocukların bu içeriklere maruz bırakılmasına yönelik faaliyetler incelenmiştir. Gizli soruşturmacı görevlendirilmesi, teknik ve fiziki takip, tanık beyanları, dijital incelemeler ve görüntü kayıtları sonucunda eş zamanlı gözaltı, arama ve el koyma işlemleri yapılmış; uyuşturucu maddeler ile çok sayıda dijital materyale el konulmuş, çok sayıda sosyal medya hesabı ve internet sitesine erişimin engellenmesi tedbiri uygulanmıştır. Soruşturmaların mali boyutunda ise LGBT ve ahlaksızlığı teşvik eden derneklere ilişkin; MASAK incelemelerinde bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığı tespit edilmiştir. Bu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısı araştırılmaktadır. Soruşturmaları titizlikle yürüten İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımıza, operasyonlarda görev alan Emniyet ve Jandarma teşkilatlarımızın kıymetli mensuplarına ve katkı sunan tüm kamu görevlilerimize teşekkür ediyorum. Anayasamızın aile ve çocukların korunmasına ilişkin devlete yüklediği sorumluluk çerçevesinde, çocuklarımızı, gençlerimizi ve ailelerimizi hedef alan hiçbir suç yapılanmasına, istismar ağına ve yasa dışı faaliyete müsamaha göstermeyeceğiz" ERİŞİM ENGELİ GETİRİLDİĞİ BELİRTİLEN 73 SİTE VE HESAP Soruşturma kapsamında erişim engeli getirildiği belirtilen site ve sosyal medya hesapları arasında LGBTİ+ alanında faaliyet gösteren dernek, oluşum ve platformların yanı sıra bazı akademik öğrenci toplulukları, medya platformları ve kişiler de yer aldı. Kaos GL SPoD LGBTİ+ Pembe Hayat LGBTİ+ Dayanışma Derneği ÜniKuir Derneği Lambdaistanbul LGBTİ+ Dayanışma Derneği 17 Mayıs Derneği HEVİ LGBTİ+ Derneği Kırmızı Şemsiye Derneği Genç LGBTİ+ Derneği Özgür Renkler Derneği Muamma LGBTİ+ Derneği Mersin 7 Renk Derneği Queer Adana Antalya BİZ Derneği Keskesor LGBTİ+ Cinsel Şiddetle Mücadele Derneği CETAD Velvele GZone Ayı Sözlük Boysan'ın Evi LGBTI News Turkey İstanbul LGBTİ+ Onur Haftası İstanbul Trans Onur Haftası Ankara Onur Haftası İzmir Onur Haftası ODTÜ LGBTİ+ Dayanışması Boğaziçi Üniversitesi LGBTİ+ Çalışmaları Kulübü Bilkent Renkli Düşün İstanbul Üniversitesi Radar Queer Deer – Hacettepe Üniversitesi Enes Hocaoğulları Yasemin Öz Ali Erol Ali Özbaş Zeynep Esmeray Özadikti Buse Kılıçkaya Şevval Kılıç Levent Pişkin Yıldız Tar İlker Hepkaner Mert Bell Mika Can Raun Seyhan Arman Kuir Tıp Öğrencileri Ağı Renkli Güvercin LGBTIQ GoFor Hormon Hakkım Kolektifi Kuir Baykuş GALA Derneği ÜniKuir2 Kuir Konya Eşitlik İçin Eğitimciler Kapsama Alanı Aşko Anlat Sportif Lezbon Arya'ya Ne Oldu Aforgütü Direnişin Renkleri Pozitif Dayanışma Bodrum Kadın Platformu Barış İçin LGBTİ+ Sivil Alan Araştırmaları Demos Araştırma Eşitlik İçin Kadın Platformu Qlub ÜniKuir Derste Zengiinn All Inclusive Mag LISTAG Boğaziçi LGBTİA İnter Dayanışma LGBT Türkiye YORUMLAR Diğer Haberler İstanbul'da yarın ulaşım ücretsiz Yaz bitti mi, yağışlar başlıyor mu? Meteoroloji'den yeni hafta için</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da ambalaj deposunda korkutan yangın! Ekipler tarafından kontrol altına alındı Antalya'da ambalaj deposunda korkutan yangın! Ekipler tarafından kontrol altına alındı Şok Gazetesi Antalya'da ambalaj deposunda korkutan yangın! Ekipler tarafından kontrol altına alındı Şok Gazetesi</t>
+          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında KARAR İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonları 15 ili kapsadı. Fuhuş, müstehcenlik, uyuşturucu ve çocukların korunmasına ilişkin soruşturmalar kapsamında 162 şüpheli, 9 dernek ve 13 işletme hakkında adli işlem başlatıldı. Operasyonlarda çok sayıda uyuşturucu madde ve dijital materyale el konulurken, bazı sosyal medya hesapları ile internet siteleri hakkında da erişim engeli tedbiri uygulandı. İSTANBUL’DA 54 ADRESE OPERASYON İstanbul merkezli çalışmada İstanbul’un yanı sıra Ankara, Çanakkale, İzmir, Antalya, Ordu, Elazığ, Balıkesir, Aydın, Kırşehir, Iğdır ve Hatay’da operasyonlar düzenlendi. 38 şüpheliye yönelik adreslerde arama, yakalama ve el koyma işlemleri gerçekleştirilirken, İstanbul’da 10 işletme ile 6 LGBTİ+ derneğinin de aralarında bulunduğu toplam 54 iş yeri, ev ve dernekte arama yapıldı. İstanbul'daki operasyonlarda 26 şüpheli gözaltına alınırken, diğer şüphelilerin yakalanmasına yönelik çalışmaların sürdüğü belirtildi. MASAK İNCELEMESİNDE YÜKSEK TUTARLI FON AKTARIMI TESPİT EDİLDİ “Ailem Güvende” operasyonları kapsamında yürütülen soruşturmanın mali boyutunda MASAK incelemeleri dikkat çekti. Adalet Bakanı Akın Gürlek, bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığının tespit edildiğini açıkladı. Gürlek, söz konusu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısının araştırıldığını bildirdi. Gürlek'in açıklaması şöyle: "Cumhurbaşkanımız Recep Tayyip Erdoğan’ın ortaya koyduğu 2026-2035 Aile ve Nüfus On Yılı vizyonu ve 2026/4 Sayılı Cumhurbaşkanlığı Genelgesi doğrultusunda; çocuklarımızı, aile kurumunu ve toplum düzenini korumaya yönelik çalışmalarımızı kararlılıkla sürdürüyoruz. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımızın koordinasyonunda, Emniyet ve Jandarma teşkilatlarımızla birlikte başlatılan "Ailem Güvende" operasyonlarında, 5 il merkezli ve toplam 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletmeye yönelik adli işlemler gerçekleştirilmektedir. Soruşturmalarda; fuhşa aracılık veya yer temin eden kişiler, bu faaliyetlere ortam sağladığı değerlendirilen işletmeler, müstehcen içerik üreten ve yayan şüpheliler ile çocukların bu içeriklere maruz bırakılmasına yönelik faaliyetler incelenmiştir. Gizli soruşturmacı görevlendirilmesi, teknik ve fiziki takip, tanık beyanları, dijital incelemeler ve görüntü kayıtları sonucunda eş zamanlı gözaltı, arama ve el koyma işlemleri yapılmış; uyuşturucu maddeler ile çok sayıda dijital materyale el konulmuş, çok sayıda sosyal medya hesabı ve internet sitesine erişimin engellenmesi tedbiri uygulanmıştır. Soruşturmaların mali boyutunda ise LGBT ve ahlaksızlığı teşvik eden derneklere ilişkin; MASAK incelemelerinde bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığı tespit edilmiştir. Bu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısı araştırılmaktadır. Soruşturmaları titizlikle yürüten İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımıza, operasyonlarda görev alan Emniyet ve Jandarma teşkilatlarımızın kıymetli mensuplarına ve katkı sunan tüm kamu görevlilerimize teşekkür ediyorum. Anayasamızın aile ve çocukların korunmasına ilişkin devlete yüklediği sorumluluk çerçevesinde, çocuklarımızı, gençlerimizi ve ailelerimizi hedef alan hiçbir suç yapılanmasına, istismar ağına ve yasa dışı faaliyete müsamaha göstermeyeceğiz" ERİŞİM ENGELİ GETİRİLDİĞİ BELİRTİLEN 73 SİTE VE HESAP Soruşturma kapsamında erişim engeli getirildiği belirtilen site ve sosyal medya hesapları arasında LGBTİ+ alanında faaliyet gösteren dernek, oluşum ve platformların yanı sıra bazı akademik öğrenci toplulukları, medya platformları ve kişiler de yer aldı. Kaos GL SPoD LGBTİ+ Pembe Hayat LGBTİ+ Dayanışma Derneği ÜniKuir Derneği Lambdaistanbul LGBTİ+ Dayanışma Derneği 17 Mayıs Derneği HEVİ LGBTİ+ Derneği Kırmızı Şemsiye Derneği Genç LGBTİ+ Derneği Özgür Renkler Derneği Muamma LGBTİ+ Derneği Mersin 7 Renk Derneği Queer Adana Antalya BİZ Derneği Keskesor LGBTİ+ Cinsel Şiddetle Mücadele Derneği CETAD Velvele GZone Ayı Sözlük Boysan'ın Evi LGBTI News Turkey İstanbul LGBTİ+ Onur Haftası İstanbul Trans Onur Haftası Ankara Onur Haftası İzmir Onur Haftası ODTÜ LGBTİ+ Dayanışması Boğaziçi Üniversitesi LGBTİ+ Çalışmaları Kulübü Bilkent Renkli Düşün İstanbul Üniversitesi Radar Queer Deer – Hacettepe Üniversitesi Enes Hocaoğulları Yasemin Öz Ali Erol Ali Özbaş Zeynep Esmeray Özadikti Buse Kılıçkaya Şevval Kılıç Levent Pişkin Yıldız Tar İlker Hepkaner Mert Bell Mika Can Raun Seyhan Arman Kuir Tıp Öğrencileri Ağı Renkli Güvercin LGBTIQ GoFor Hormon Hakkım Kolektifi Kuir Baykuş GALA Derneği ÜniKuir2 Kuir Konya Eşitlik İçin Eğitimciler Kapsama Alanı Aşko Anlat Sportif Lezbon Arya'ya Ne Oldu Aforgütü Direnişin Renkleri Pozitif Dayanışma Bodrum Kadın Platformu Barış İçin LGBTİ+ Sivil Alan Araştırmaları Demos Araştırma Eşitlik İçin Kadın Platformu Qlub ÜniKuir Derste Zengiinn All Inclusive Mag LISTAG Boğaziçi LGBTİA İnter Dayanışma LGBT Türkiye 19:19 İstanbul'da yarın ulaşım ücretsiz: Sadece okul saatleri içerisinde 19:15 Trump, İran'la savaşın bitimine dair tarih verdi: Ara seçimler... 18:35 Suudi Arabistan'dan 'güvenlik' mesajı: İzin vermeyeceğiz 18:14 Trabzonspor’da Şenol Güneş sesleri 18:07 Yaz bitti mi, yağışlar başlıyor mu? Meteoroloji'den yeni hafta için 11 illik uyarı 18:04 Formula 1’in ilk Madrid yarışında tarihi zafer 17:54 TOKİ kiralık konut başvurusu ücretli mi? Bekarlar başvuru yapabilecek mi? 17:49 Osimhen için karar verildi: Dönüş tarihi belli oldu 17:38 Katılımevim’de yönetim değişti, Tera ile devir süreci sürüyor 17:38 Ankara’da yarın bazı yollar trafiğe kapatılacak 17:35 Irak, İran sınırındaki 3 sınır kapısını yeniden açıyor 17:34 Ünlülere yönelik uyuşturucu soruşturmasında yeni operasyon: Oyuncu Çağla Boz gözaltına alındı 17:32 Toprak Razgatlıoğlu San Marino’da 12. oldu 17:20 Uzaklaştırma kararı engel olmadı: Uzman çavuş eşini öldürüp intihar etti 17:13 Almanya'da aşırı sağ ve AfD’ye karşı protestolar artıyor MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. 13/09/2026 10:18 KAYNAK: Anadolu Ajansı (AA) İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonları 15 ili kapsadı.</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOTWx0OE1FeUQ4Y2w2Y2JLa0o4WjRmdDJhVVNzZFNMRGhjYkRGaUJkZVp3T19DR210OEVFdFhpM1QzRHVzVExLbTk5bmhveUJsZU5OM1c5V1F1RE1aUk9ZSTgwdEJFeXB2UXBWWXpnT2hLcGs5TVE0OTFUMHl0aERRaW9ESE55V2JMWlpyemF2eXlzbndhazlMRklCQnJ6eUNLUWdJemR0VjhpUC1GdzJCdnNocXRIUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.karar.com/guncel-haberler/ailem-guvende-operasyonunda-yeni-gelisme-15-ilde-9-dernek-ve-13-2071591</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Antalya</t>
+          <t>Ankara | Hatay | İstanbul | Mersin</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Levent</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr"/>
@@ -4390,7 +4503,7 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="n">
-        <v>94.73999999999999</v>
+        <v>141</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>21</v>
@@ -4399,27 +4512,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:40:20</t>
+          <t>2026-09-13 12:22:00</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Türkiye İş Dünyası Haberleri</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -4429,22 +4542,18 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>banka, turizm</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>masak, para transferi</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde 0 Sakarya Asliye Ticaret Mahkemesi, Sınırlı Sorumlu 37 Nolu Sakarya VİB Otobüsçüler Karayolu Yolcu Taşıma Kooperatifi ile Yönetim Kurulu Başkanı Suat Akın hakkında 28 Ağustos 2026’dan itibaren 3 aylık geçici mühlet kararı verdi. Sürecin başarıya ulaşıp ulaşamayacağını değerlendirmek üzere üç kişilik konkordato komiser heyeti görevlendirildi. KONKORDATONUN GEREKÇESİ BANKA BORÇLARI Şirket tarafından yapılan açıklamada, konkordato sürecinin mali yapının güçlendirilmesi ve bankalara olan finansal yükümlülüklerin sürdürülebilir bir ödeme planına bağlanması amacıyla başlatıldığı belirtildi. Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde sürdüğü bildirildi. VERGİ KAYITLARI MALİ TABLOYA İŞARET EDİYOR Şirketin 2024 ve 2025 yıllarında vergiye esas matrah bildirmediği bilgisi de mali tabloya ilişkin dikkat çeken göstergeler arasında yer alıyor. Ancak bu veri tek başına şirketin toplam zararını veya borç miktarını ortaya koymuyor. VİB Turizm’in konkordato başvurusunun, büyüme hedeflerinin konuşulduğu bir dönemin ardından gelmesi de dikkat çekiyor. 2024 sonunda şirketin 54 araçla 45 şehir ve 500 şubede hizmet verdiği, 2025’te filo büyütme ve yeni hatlar açma hedeflerinin bulunduğu açıklanmıştı. OTOBÜS İŞLETMECİLERİNDE MALİYET BASKISI ARTIYOR VİB Turizm’in açıklamasında konkordatonun temel nedeni banka borçlarının yeniden yapılandırılması olarak gösterilirken, şehirlerarası otobüs taşımacılığında artan işletme maliyetleri de sektörün önemli sorunları arasında bulunuyor. Akaryakıt, bakım, yedek parça ve sigorta giderlerindeki yükselişler işletmecilerin maliyetlerini artırıyor. Nitekim Ankara EGO’nun ağustos ayındaki açıklamasında, motorin fiyatının yıl başından bu yana yaklaşık 50 liradan 80,90 liraya yükseldiği, yedek parça maliyetlerinin yüzde 31,90, zorunlu trafik sigortası maliyetlerinin ise yüzde 54,73 arttığı belirtilmişti. “İFLAS ETTİ” DEMEK İÇİN HENÜZ ERKEN Mahkemenin verdiği karar bir iflas kararı değil, 3 aylık geçici konkordato mühleti niteliğinde. Görevlendirilen komiser heyeti, şirketin mali yapısını ve konkordato projesinin uygulanabilirliğini inceleyecek. Bu nedenle mevcut aşamada VİB Turizm’in faaliyetlerinin sona erdiğini söylemek yerine, şirketin borçlarını yeniden yapılandırmak üzere konkordato korumasına girdiğini belirtmek daha doğru. KOMİSER HEYETİ ŞİRKETİN GELECEĞİNİ İNCELEYECEK Sakarya Asliye Ticaret Mahkemesi’nin 2026/728 Esas sayılı dosyası kapsamında Prof. Dr. Ali Taş, Prof. Dr. Habib Yıldız ve Prof. Dr. Selahattin Karabınar geçici konkordato komiseri olarak görevlendirildi. Önümüzdeki süreçte şirketin borçluluk düzeyi, banka yükümlülükleri, nakit akışı ve filo finansmanı başta olmak üzere mali yapısı değerlendirilecek. Konkordato projesinin uygulanabilirliği yapılacak incelemelerin ardından netleşecek. Anasayfa / Şirket Haberleri / VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Türkiye'de İş Dünyası Şirket Haberleri VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Güncelleme: 12/09/2026 12:40 VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Sakarya’nın 29 yıllık şehirlerarası ulaşım markası VİB Turizm, bankalara yönelik finansal yükümlülüklerini yeniden yapılandırmak amacıyla konkordato sürecine girdi. Mahkeme şirkete 3 aylık geçici mühlet verirken, sefer ve bilet satışlarının devam ettiği bildirildi. 12/09/2026 12:40 0 Sakarya Asliye Ticaret Mahkemesi, Sınırlı Sorumlu 37 Nolu Sakarya VİB Otobüsçüler Karayolu Yolcu Taşıma Kooperatifi ile Yönetim Kurulu Başkanı Suat Akın hakkında 28 Ağustos 2026’dan itibaren 3 aylık geçici mühlet kararı verdi. Sürecin başarıya ulaşıp ulaşamayacağını değerlendirmek üzere üç kişilik konkordato komiser heyeti görevlendirildi. KONKORDATONUN GEREKÇESİ BANKA BORÇLARI Şirket tarafından yapılan açıklamada, konkordato sürecinin mali yapının güçlendirilmesi ve bankalara olan finansal yükümlülüklerin sürdürülebilir bir ödeme planına bağlanması amacıyla başlatıldığı belirtildi. Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde sürdüğü bildirildi. VERGİ KAYITLARI MALİ TABLOYA İŞARET EDİYOR Şirketin 2024 ve 2025 yıllarında vergiye esas matrah bildirmediği bilgisi de mali tabloya ilişkin dikkat çeken göstergeler arasında yer alıyor. Ancak bu veri tek başına şirketin toplam zararını veya borç miktarını ortaya koymuyor. VİB Turizm’in konkordato başvurusunun, büyüme hedeflerinin konuşulduğu bir dönemin ardından gelmesi de dikkat çekiyor. 2024 sonunda şirketin 54 araçla 45 şehir ve 500 şubede hizmet verdiği, 2025’te filo büyütme ve yeni hatlar açma hedeflerinin bulunduğu açıklanmıştı. OTOBÜS İŞLETMECİLERİNDE MALİYET BASKISI ARTIYOR VİB Turizm’in açıklamasında konkordatonun temel nedeni banka borçlarının yeniden yapılandırılması olarak gösterilirken, şehirlerarası otobüs taşımacılığında artan işletme maliyetleri de sektörün önemli sorunları arasında bulunuyor. Akaryakıt, bakım, yedek parça ve sigorta giderlerindeki yükselişler işletmecilerin maliyetlerini artırıyor. Nitekim Ankara EGO’nun ağustos ayındaki açıklamasında, motorin fiyatının yıl başından bu yana yaklaşık 50 liradan 80,90 liraya yükseldiği, yedek parça maliyetlerinin yüzde 31,90, zorunlu trafik sigortası maliyetlerinin ise yüzde 54,73 arttığı belirtilmişti. “İFLAS ETTİ” DEMEK İÇİN HENÜZ ERKEN Mahkemenin verdiği karar bir iflas kararı değil, 3 aylık geçici konkordato mühleti niteliğinde. Görevlendirilen komiser heyeti, şirketin mali yapısını ve konkordato projesinin uygulanabilirliğini inceleyecek. Bu nedenle mevcut aşamada VİB Turizm’in faaliyetlerinin sona erdiğini söylemek yerine, şirketin borçlarını yeniden yapılandırmak üzere konkordato korumasına girdiğini belirtmek daha doğru. KOMİSER HEYETİ ŞİRKETİN GELECEĞİNİ İNCELEYECEK Sakarya Asliye Ticaret Mahkemesi’nin 2026/728 Esas sayılı dosyası kapsamında Prof. Dr. Ali Taş, Prof. Dr. Habib Yıldız ve Prof. Dr. Selahattin Karabınar geçici konkordato komiseri olarak görevlendirildi. Önümüzdeki süreçte şirketin borçluluk düzeyi, banka yükümlülükleri, nakit akışı ve filo finansmanı başta olmak üzere mali yapısı değerlendirilecek. Konkordato projesinin uygulanabilirliği yapılacak incelemelerin ardından netleşecek. banka borçları finansal yapılandırma konkordato otobüs sektörü Sakarya VİB şehirlerarası taşımacılık VİB Turizm VİB Turizm konkordato Limak dünyanın en büyük müteahhitleri arasında 10 basamak yükseldi Tüpraş meslek yüksekokulu öğrencilerini rafinericilik staj programıyla destekliyor Enerjisa Enerji’nin tiyatrosu Hatay’da 3 binden fazla çocuğa ulaştı Auran Kozmetik üreticinin yedi yıllık emeğine sahip çıktı Ar-Ge’de hem yatırım hem istihdam öne çıktı Tasarruf finansmanda rekabet ve alternatifler artıyor SON DAKİKA HABERLERİ GÜNDEM KORİDORU 8 gün önce Resmi Gazete’de yayımlandı: Diyanet ve Dışişleri’nde kritik atamalar gerçekleşti EKONOMİ 10 gün önce KOSGEB’den KOBİ’lere 27,1 milyar liralık dev can suyu ALMANYA'DA İŞ DÜNYASI 10 gün önce Almanya’da Trilya yağına zararlı mineral yağ engeli: Raflardan toplatılıyor EKONOMİ 10 gün önce Eskişehir’de stratejik adım: Nadir elementler için dev kamulaştırma SPOR 10 gün önce Beşiktaş’ta beklenen ayrılık EKONOMİ 10 gün önce AFSİAD Başkanı Sayın’dan bankalara faiz ve teminat çağrısı EMLAK 10 gün önce Eylül ayı kira artış oranı için gözler TÜİK’te KATEGORİNİN POPÜLERLERİ 1 V ORMAN RESORT’TA ÖMÜR BOYU LÜKS TATİL İMKANI 2 Turkcell Tumbara nedir, ücretli mi? 3 Sabancı Holding CFO’su Köstem enerji ve bankacılık sektörünün geleceğini değerlendirdi 4 Yeni inci üretim hacmini 3 yıl içinde yüzde 40 artırmayı hedefliyor 5 İş Kadınları Girişim Derneği İŞKAGİD: “Bir Kadın Tek Başına Çoğunluktur” Limak dünyanın en büyük müteahhitleri arasında 10 basamak yükseldi Tüpraş meslek yüksekokulu öğrencilerini rafinericilik staj programıyla destekliyor VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Enerjisa Enerji’nin tiyatrosu Hatay’da 3 binden fazla çocuğa ulaştı Auran Kozmetik üreticinin yedi yıllık emeğine sahip çıktı VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Sakarya’nın 29 yıllık şehirlerarası ulaşım markası VİB Turizm, bankalara yönelik finansal yükümlülüklerini yeniden yapılandırmak amacıyla konkordato sürecine girdi. Mahkeme şirkete 3 aylık geçici mühlet verirken, sefer ve bilet satışlarının devam ettiği bildirildi. Sakarya Asliye Ticaret Mahkemesi, Sınırlı Sorumlu 37 Nolu Sakarya VİB Otobüsçüler Karayolu Yolcu Taşıma Kooperatifi ile Yönetim Kurulu Başkanı Suat Akın hakkında 28 Ağustos 2026’dan itibaren 3 aylık geçici mühlet kararı verdi. Sürecin başarıya ulaşıp ulaşamayacağını değerlendirmek üzere üç kişilik konkordato komiser heyeti görevlendirildi. Şirket tarafından yapılan açıklamada, konkordato sürecinin mali yapının güçlendirilmesi ve bankalara olan finansal yükümlülüklerin sürdürülebilir bir ödeme planına bağlanması amacıyla başlatıldığı belirtildi. Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde sürdüğü bildirildi. Şirketin 2024 ve 2025 yıllarında vergiye esas matrah bildirmediği bilgisi de mali tabloya ilişkin dikkat çeken göstergeler arasında yer alıyor. Ancak bu veri tek başına şirketin toplam zararını veya borç miktarını ortaya koymuyor. VİB Turizm’in konkordato başvurusunun, büyüme hedeflerinin konuşulduğu bir dönemin ardından gelmesi de dikkat çekiyor. 2024 sonunda şirketin 54 araçla 45 şehir ve 500 şubede hizmet verdiği, 2025’te filo büyütme ve yeni hatlar açma hedeflerinin bulunduğu açıklanmıştı. VİB Turizm’in açıklamasında konkordatonun temel nedeni banka borçlarının yeniden yapılandırılması olarak gösterilirken, şehirlerarası otobüs taşımacılığında artan işletme maliyetleri de sektörün önemli sorunları arasında bulunuyor. Akaryakıt, bakım, yedek parça ve sigorta giderlerindeki yükselişler işletmecilerin maliyetlerini artırıyor. Nitekim Ankara EGO’nun ağustos ayındaki açıklamasında, motorin fiyatının yıl başından bu yana yaklaşık 50 liradan 80,90 liraya yükseldiği, yedek parça maliyetlerinin yüzde 31,90, zorunlu trafik sigortası maliyetlerinin ise yüzde 54,73 arttığı belirtilmişti. Mahkemenin verdiği karar bir iflas kararı değil, 3 aylık geçici konkordato mühleti niteliğinde. Görevlendirilen komiser heyeti, şirketin mali yapısını ve konkordato projesinin uygulanabilirliğini inceleyecek. Bu nedenle mevcut aşamada VİB Turizm’in faaliyetlerinin sona erdiğini söylemek yerine, şirketin borçlarını yeniden yapılandırmak üzere konkordato korumasına girdiğini belirtmek daha doğru. Sakarya Asliye Ticaret Mahkemesi’nin 2026/728 Esas sayılı dosyası kapsamında Prof. Dr. Ali Taş, Prof. Dr. Habib Yıldız ve Prof. Dr. Selahattin Karabınar geçici konkordato komiseri olarak görevlendirildi. Önümüzdeki süreçte şirketin borçluluk düzeyi, banka yükümlülükleri, nakit akışı ve filo finansmanı başta olmak üzere mali yapısı değerlendirilecek. Konkordato projesinin uygulanabilirliği yapılacak incelemelerin ardından netleşecek. Limak dünyanın en büyük müteahhitleri arasında 10 basamak yükseldi Tüpraş meslek yüksekokulu öğrencilerini rafinericilik staj programıyla destekliyor Enerjisa Enerji’nin tiyatrosu Hatay’da 3 binden fazla çocuğa ulaştı Auran Kozmetik üreticinin yedi yıllık emeğine sahip çıktı</t>
+          <t>İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Gündem 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sevda Ecem Karapolat 13.09.2026 - 15:22 1 İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Soruşturma belgelerine dayandırılan bilgilere göre, 2021-2026 döneminde yabancı ve uluslararası kurumsal kaynaklardan yapılan 209 transferin işlem tarihlerindeki toplam karşılığı yaklaşık 67,4 milyon lira olarak hesaplandı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında, İstanbul merkezli 6 derneğin yurt içi ve yurt dışı bağlantılı para hareketleri incelemeye alındı. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu’nun 226’ncı maddesi kapsamında yürütülen araştırmada, MASAK Veri İnceleme Tutanağı ve bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte değerlendirildi. HANGİ DERNEKLERİN HESAPLARI İNCELENDİ? İnceleme kapsamında şu derneklerin hesap hareketleri ele alındı: Yemen’de çatışmalar şiddetlendi: İran destekli Husiler operasyon görüntülerini paylaştı İçeriği Görüntüle Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği (HEVİ) Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği Pozitif Yaşam Derneği Pozitif İz Derneği Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneği (SPoD) Belgelerde, yabancı kuruluşlardan gelen fonların yanı sıra GİB SWIFT kayıtları, gerçek kişiler tarafından yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketlerinin sıralandığı belirtildi. 45 BİN 135 İŞLEM KAYDI DEĞERLENDİRİLDİ İncelemeye ilişkin aktarılan bilgilere göre, “Bankacılık Transfer” tablosunda toplam 45 bin 135 işlem satırı bulunuyor. Bunların 13 bin 40’ını para girişleri , 32 bin 95’ini ise para çıkışları oluşturuyor. Para girişlerinin 218’inin doğrudan SWIFT alma işlemi olduğu kaydedildi. Gönderen adı, ülke bilgisi, işlemin SWIFT niteliği, banka ve açıklama bilgilerinin birlikte değerlendirilmesiyle yabancı kurumsal kaynaklardan gelen transferler ayrıca sınıflandırıldı. 37 KURUMSAL KAYNAKTAN 209 PARA GİRİŞİ 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan 209 para girişi belirlendiği aktarıldı. Bu işlemlerin gerçekleştirildikleri tarihlerdeki TL karşılıklarının toplamı 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde bu tutarın paranın bugünkü değerini ifade etmediği vurgulandı. Rakamın, farklı tarihlerde yapılan transferlerin MASAK kayıtlarındaki TL karşılıklarının aritmetik toplamından oluştuğu belirtildi. GİB SWIFT kayıtlarına ilişkin değerlendirmede ise derneklere gönderilen paranın dolar karşılığının 3 milyon 359 bin doları aştığı bilgisine yer verildi. YABANCI KURUMSAL GİRİŞLERİN YÜZDE 78’İ İKİ DERNEĞE Aktarılan inceleme bulgularına göre, 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinin yüzde 78’i SPoD ve HEVİ’ye yöneldi. Para hareketlerinde yabancı devlet kurumları, diplomatik misyonlar ve uluslararası kuruluşların yanı sıra gerçek kişilerden yapılan transferlerin de bulunduğu belirtildi. Paylaşılan bilgilerde, bu transferlerin suç oluşturduğuna ilişkin kesinleşmiş bir yargı kararına yer verilmedi. Kaynak: Haber Merkezi Editörün Seçtiği Benzine gece yarısı büyük zam geliyor: Ankara'da 80 liranın üzerine çıkacak! Editörün Seçtiği Kaşif Kozinoğlu'nun mezarı bugün açılacaktı: Feth-i kabir işlemi ertelendi! Editörün Seçtiği Kredi kartı limiti düşürülecek mi? İşte 2026 düzenlemesinin ayrıntıları... Editör Hakkında Sevda Ecem Karapolat Bunlar da ilginizi çekebilir Yemen’de çat</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Türkiye İş Dünyası Haberleri Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde 0 Sakarya Asliye Ticaret Mahkemesi, Sınırlı Sorumlu 37 Nolu Sakarya VİB Otobüsçüler Karayolu Yolcu Taşıma Kooperatifi ile Yönetim Kurulu Başkanı Suat Akın hakkında 28 Ağustos 2026’dan itibaren 3 aylık geçici mühlet kararı verdi. Sürecin başarıya ulaşıp ulaşamayacağını değerlendirmek üzere üç kişilik konkordato komiser heyeti görevlendirildi. KONKORDATONUN GEREKÇESİ BANKA BORÇLARI Şirket tarafından yapılan açıklamada, konkordato sürecinin mali yapının güçlendirilmesi ve bankalara olan finansal yükümlülüklerin sürdürülebilir bir ödeme planına bağlanması amacıyla başlatıldığı belirtildi. Konkordato kararının faaliyetlerin durduğu anlamına gelmediği vurgulanırken, VİB Turizm’in seferleri, bilet satışları ve operasyonlarının mevcut şekilde sürdüğü bildirildi. VERGİ KAYITLARI MALİ TABLOYA İŞARET EDİYOR Şirketin 2024 ve 2025 yıllarında vergiye esas matrah bildirmediği bilgisi de mali tabloya ilişkin dikkat çeken göstergeler arasında yer alıyor. Ancak bu veri tek başına şirketin toplam zararını veya borç miktarını ortaya koymuyor. VİB Turizm’in konkordato başvurusunun, büyüme hedeflerinin konuşulduğu bir dönemin ardından gelmesi de dikkat çekiyor. 2024 sonunda şirketin 54 araçla 45 şehir ve 500 şubede hizmet verdiği, 2025’te filo büyütme ve yeni hatlar açma hedeflerinin bulunduğu açıklanmıştı. OTOBÜS İŞLETMECİLERİNDE MALİYET BASKISI ARTIYOR VİB Turizm’in açıklamasında konkordatonun temel nedeni banka borçlarının yeniden yapılandırılması olarak gösterilirken, şehirlerarası otobüs taşımacılığında artan işletme maliyetleri de sektörün önemli sorunları arasında bulunuyor. Akaryakıt, bakım, yedek parça ve sigorta giderlerindeki yükselişler işletmecilerin maliyetlerini artırıyor. Nitekim Ankara EGO’nun ağustos ayındaki açıklamasında, motorin fiyatının yıl başından bu yana yaklaşık 50 liradan 80,90 liraya yükseldiği, yedek parça maliyetlerinin yüzde 31,90, zorunlu trafik sigortası maliyetlerinin ise yüzde 54,73 arttığı belirtilmişti. “İFLAS ETTİ” DEMEK İÇİN HENÜZ ERKEN Mahkemenin verdiği karar bir iflas kararı değil, 3 aylık geçici konkordato mühleti niteliğinde. Görevlendirilen komiser heyeti, şirketin mali yapısını ve konkordato projesinin uygulanabilirliğini inceleyecek. Bu nedenle mevcut aşamada VİB Turizm’in faaliyetlerinin sona erdiğini söylemek yerine, şirketin borçlarını yeniden yapılandırmak üzere konkordato korumasına girdiğini belirtmek daha doğru. KOMİSER HEYETİ ŞİRKETİN GELECEĞİNİ İNCELEYECEK Sakarya Asliye Ticaret Mahkemesi’nin 2026/728 Esas sayılı dosyası kapsamında Prof. Selahattin Karabınar geçici konkordato komiseri olarak görevlendirildi. Önümüzdeki süreçte şirketin borçluluk düzeyi, banka yükümlülükleri, nakit akışı ve filo finansmanı başta olmak üzere mali yapısı değerlendirilecek. Konkordato projesinin uygulanabilirliği yapılacak incelemelerin ardından netleşecek. Anasayfa / Şirket Haberleri / VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Türkiye'de İş Dünyası Şirket Haberleri VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Güncelleme: 12/09/2026 12:40 VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Sakarya’nın 29 yıllık şehirlerarası ulaşım markası VİB Turizm, bankalara yönelik finansal yükümlülüklerini yeniden yapılandırmak amacıyla konkordato sürecine girdi. Mahkeme şirkete 3 aylık geçici mühlet verirken, sefer ve bilet satışlarının devam ettiği bildirildi. 12/09/2026 12:40 0 Sakarya Asliye Ticaret Mahkemesi, Sınırlı Sorumlu 37 Nolu Sakarya VİB Otobüsçüler Karayolu Yolcu Taşıma Kooperatifi ile Yönetim Kurulu Başkanı Suat Akın hakkında 28 Ağustos 2026’dan itibaren 3 aylık geçici mühlet kararı verdi. banka borçları finansal yapılandırma konkordato otobüs sektörü Sakarya VİB şehirlerarası taşımacılık VİB Turizm VİB Turizm konkordato Limak dünyanın en büyük müteahhitleri arasında 10 basamak yükseldi Tüpraş meslek yüksekokulu öğrencilerini rafinericilik staj programıyla destekliyor Enerjisa Enerji’nin tiyatrosu Hatay’da 3 binden fazla çocuğa ulaştı Auran Kozmetik üreticinin yedi yıllık emeğine sahip çıktı Ar-Ge’de hem yatırım hem istihdam öne çıktı Tasarruf finansmanda rekabet ve alternatifler artıyor SON DAKİKA HABERLERİ GÜNDEM KORİDORU 8 gün önce Resmi Gazete’de yayımlandı: Diyanet ve Dışişleri’nde kritik atamalar gerçekleşti EKONOMİ 10 gün önce KOSGEB’den KOBİ’lere 27,1 milyar liralık dev can suyu ALMANYA'DA İŞ DÜNYASI 10 gün önce Almanya’da Trilya yağına zararlı mineral yağ engeli: Raflardan toplatılıyor EKONOMİ 10 gün önce Eskişehir’de stratejik adım: Nadir elementler için dev kamulaştırma SPOR 10 gün önce Beşiktaş’ta beklenen ayrılık EKONOMİ 10 gün önce AFSİAD Başkanı Sayın’dan bankalara faiz ve teminat çağrısı EMLAK 10 gün önce Eylül ayı kira artış oranı için gözler TÜİK’te KATEGORİNİN POPÜLERLERİ 1 V ORMAN RESORT’TA ÖMÜR BOYU LÜKS TATİL İMKANI 2 Turkcell Tumbara nedir, ücretli mi? 3 Sabancı Holding CFO’su Köstem enerji ve bankacılık sektörünün geleceğini değerlendirdi 4 Yeni inci üretim hacmini 3 yıl içinde yüzde 40 artırmayı hedefliyor 5 İş Kadınları Girişim Derneği İŞKAGİD: “Bir Kadın Tek Başına Çoğunluktur” Limak dünyanın en büyük müteahhitleri arasında 10 basamak yükseldi Tüpraş meslek yüksekokulu öğrencilerini rafinericilik staj programıyla destekliyor VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Enerjisa Enerji’nin tiyatrosu Hatay’da 3 binden fazla çocuğa ulaştı Auran Kozmetik üreticinin yedi yıllık emeğine sahip çıktı VİB Turizm konkordato ilan etti: Banka borçlarını yeniden yapılandıracak Sakarya’nın 29 yıllık şehirlerarası ulaşım markası VİB Turizm, bankalara yönelik finansal yükümlülüklerini yeniden yapılandırmak amacıyla konkordato sürecine girdi. Sakarya Asliye Ticaret Mahkemesi, Sınırlı Sorumlu 37 Nolu Sakarya VİB Otobüsçüler Karayolu Yolcu Taşıma Kooperatifi ile Yönetim Kurulu Başkanı Suat Akın hakkında 28 Ağustos 2026’dan itibaren 3 aylık geçici mühlet kararı verdi. Şirket tarafından yapılan açıklamada, konkordato sürecinin mali yapının güçlendirilmesi ve bankalara olan finansal yükümlülüklerin sürdürülebilir bir ödeme planına bağlanması amacıyla başlatıldığı belirtildi. Şirketin 2024 ve 2025 yıllarında vergiye esas matrah bildirmediği bilgisi de mali tabloya ilişkin dikkat çeken göstergeler arasında yer alıyor. VİB Turizm’in açıklamasında konkordatonun temel nedeni banka borçlarının yeniden yapılandırılması olarak gösterilirken, şehirlerarası otobüs taşımacılığında artan işletme maliyetleri de sektörün önemli sorunları arasında bulunuyor. Mahkemenin verdiği karar bir iflas kararı değil, 3 aylık geçici konkordato mühleti niteliğinde. Sakarya Asliye Ticaret Mahkemesi’nin 2026/728 Esas sayılı dosyası kapsamında Prof. Limak dünyanın en büyük müteahhitleri arasında 10 basamak yükseldi Tüpraş meslek yüksekokulu öğrencilerini rafinericilik staj programıyla destekliyor Enerjisa Enerji’nin tiyatrosu Hatay’da 3 binden fazla çocuğa ulaştı Auran Kozmetik üreticinin yedi yıllık emeğine sahip çıktı</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Gündem 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sevda Ecem Karapolat 13.09.2026 - 15:22 1 İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Soruşturma belgelerine dayandırılan bilgilere göre, 2021-2026 döneminde yabancı ve uluslararası kurumsal kaynaklardan yapılan 209 transferin işlem tarihlerindeki toplam karşılığı yaklaşık 67,4 milyon lira olarak hesaplandı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında, İstanbul merkezli 6 derneğin yurt içi ve yurt dışı bağlantılı para hareketleri incelemeye alındı. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu’nun 226’ncı maddesi kapsamında yürütülen araştırmada, MASAK Veri İnceleme Tutanağı ve bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte değerlendirildi. HANGİ DERNEKLERİN HESAPLARI İNCELENDİ? İnceleme kapsamında şu derneklerin hesap hareketleri ele alındı: Yemen’de çatışmalar şiddetlendi: İran destekli Husiler operasyon görüntülerini paylaştı İçeriği Görüntüle Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği (HEVİ) Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği Pozitif Yaşam Derneği Pozitif İz Derneği Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneği (SPoD) Belgelerde, yabancı kuruluşlardan gelen fonların yanı sıra GİB SWIFT kayıtları, gerçek kişiler tarafından yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketlerinin sıralandığı belirtildi. 45 BİN 135 İŞLEM KAYDI DEĞERLENDİRİLDİ İncelemeye ilişkin aktarılan bilgilere göre, “Bankacılık Transfer” tablosunda toplam 45 bin 135 işlem satırı bulunuyor. Bunların 13 bin 40’ını para girişleri , 32 bin 95’ini ise para çıkışları oluşturuyor. Para girişlerinin 218’inin doğrudan SWIFT alma işlemi olduğu kaydedildi. 37 KURUMSAL KAYNAKTAN 209 PARA GİRİŞİ 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan 209 para girişi belirlendiği aktarıldı. Rakamın, farklı tarihlerde yapılan transferlerin MASAK kayıtlarındaki TL karşılıklarının aritmetik toplamından oluştuğu belirtildi. GİB SWIFT kayıtlarına ilişkin değerlendirmede ise derneklere gönderilen paranın dolar karşılığının 3 milyon 359 bin doları aştığı bilgisine yer verildi. YABANCI KURUMSAL GİRİŞLERİN YÜZDE 78’İ İKİ DERNEĞE Aktarılan inceleme bulgularına göre, 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinin yüzde 78’i SPoD ve HEVİ’ye yöneldi. Para hareketlerinde yabancı devlet kurumları, diplomatik misyonlar ve uluslararası kuruluşların yanı sıra gerçek kişilerden yapılan transferlerin de bulunduğu belirtildi. Editörün Seçtiği Kaşif Kozinoğlu'nun mezarı bugün açılacaktı: Feth-i kabir işlemi ertelendi!</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -4454,19 +4563,15 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://turkiyedeisdunyasi.com/vib-turizm-konkordato-ilan-etti-banka-borclarini-yeniden-yapilandiracak-132591/</t>
+          <t>https://www.ankaranethaber.com/6-lgbt-dernegine-yurt-disindan-para-transferi-masak-incelemesinde-209-islem-belirlendi</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir | Hatay | Sakarya | İstanbul</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Beşiktaş</t>
-        </is>
-      </c>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -4474,7 +4579,7 @@
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr"/>
@@ -4488,7 +4593,7 @@
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="n">
-        <v>110.25</v>
+        <v>111</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>22</v>
@@ -4497,27 +4602,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 06:49:27</t>
+          <t>2026-09-13 10:19:26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>İnşaat konkordatoda tekstili solladı: Başvurularda düşüş</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi!</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>İnşaat konkordatoda tekstili solladı: Başvurularda düşüş Odatv</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -4527,32 +4632,44 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>tekstil</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>İnşaat konkordatoda tekstili solladı: Başvurularda düşüş Odatv</t>
+          <t>Ad Haberler - Gündem Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>İnşaat konkordatoda tekstili solladı: Başvurularda düşüş İnşaat konkordatoda tekstili solladı: Başvurularda düşüş Odatv İnşaat konkordatoda tekstili solladı: Başvurularda düşüş Odatv</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi Ad Haberler - Gündem Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.odatv.com/ekonomi/konkordato-basvurularinda-son-durum-insaat-tekstili-solladi-120162360</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>https://www.sozcu.com.tr/amp/bolu-daki-depo-yangininda-son-durum-hasarin-boyutu-havadan-goruntulendi-p357811</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -4560,7 +4677,7 @@
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr"/>
@@ -4574,7 +4691,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="n">
-        <v>52.12</v>
+        <v>117.5</v>
       </c>
       <c r="AB24" s="2" t="n">
         <v>23</v>
@@ -4583,27 +4700,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:16:58</t>
+          <t>2026-09-13 01:34:53</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Konkordatolar azalıyor: Şirketler toparlanıyor mu, başvurmak mı pahalılaştı?</t>
+          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Konkordatolar azalıyor: Şirketler toparlanıyor mu, başvurmak mı pahalılaştı? Para Analiz</t>
+          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi Finans Gündem</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -4613,36 +4730,44 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>depo, fabrika</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika | depo</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Konkordatolar azalıyor: Şirketler toparlanıyor mu, başvurmak mı pahalılaştı? Para Analiz</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda çıkan yangın kontrol altına alındı. Soğutma çalışmaları sürerken Valilik, olayda hafif yaralanan 2 kişinin tedavi edildiğini ve incelemelerin devam ettiğini açıkladı Bolu Gerede'deki geri dönüşüm deposunda çıkan yangın kontrol altına alındı. Soğutma çalışmaları...</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Konkordatolar azalıyor: Şirketler toparlanıyor mu, başvurmak mı pahalılaştı? Konkordatolar azalıyor: Şirketler toparlanıyor mu, başvurmak mı pahalılaştı? Para Analiz Konkordatolar azalıyor: Şirketler toparlanıyor mu, başvurmak mı pahalılaştı?</t>
+          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi Finans Gündem Bolu Gerede'deki geri dönüşüm deposunda çıkan yangın kontrol altına alındı. Soğutma çalışmaları sürerken Valilik, olayda hafif yaralanan 2 kişinin tedavi edildiğini ve incelemelerin devam ettiğini açıkladı Bolu Gerede'deki geri dönüşüm deposunda çıkan yangın kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPclVNMEl5VUV3NEZZbDZkamsxUkMzMkRoN0xoWGtrZGtVRVY1RERoeUtjNElGZzdEMkRlY2dqZXgzbGpPS28wbGFaN2dYeDBLRFlNeC1qVWduZlJLMUlKREM2QnFFOUtSLXFnaGpfbHV4T2p4bHE4Sno0dFN2R09XODVrRFNfcDFUU1pNelVORFctNWt3dzc2V2ZKWnpUUXNWcGtqWm9jQ0M0bVVEWkE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>https://www.finansingundemi.com/haber/bolu-geredede-fabrika-deposundaki-yangin-kontrol-altina-alindi-2-yarali/1908123</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -4650,7 +4775,7 @@
       <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr"/>
@@ -4664,7 +4789,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="n">
-        <v>76.88</v>
+        <v>100.54</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>24</v>
@@ -4673,27 +4798,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 16:33:36</t>
+          <t>2026-09-12 18:20:15</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>58 yıllık Türk meyve suyu şirketi iflastan kurtuldu: Her sofrada vardı</t>
+          <t>Antalya'da depo yangını / Ek fotoğraflar</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58 yıllık Türk meyve suyu şirketi iflastan kurtuldu: Her sofrada vardı Yeniçağ Gazetesi</t>
+          <t>Antalya'da depo yangını / Ek fotoğraflar Antalya İleri</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4703,35 +4828,39 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Türkiye'nin meyve suyu sektöründe uzun yıllardır faaliyet gösteren köklü şirketlerinden biri için yaklaşık iki yıldır devam eden kritik süreç sona erdi. Mahkeme, şirket hakkında iflas kararı verilmesine yer olmadığına hükmederken uygulanan tedbirler de kaldırıldı.</t>
+          <t>Antalya'da depo yangını / Ek fotoğraflar Antalya İleri</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>58 yıllık Türk meyve suyu şirketi iflastan kurtuldu: Her sofrada vardı 58 yıllık Türk meyve suyu şirketi iflastan kurtuldu: Her sofrada vardı Yeniçağ Gazetesi Türkiye'nin meyve suyu sektöründe uzun yıllardır faaliyet gösteren köklü şirketlerinden biri için yaklaşık iki yıldır devam eden kritik süreç sona erdi. Mahkeme, şirket hakkında iflas kararı verilmesine yer olmadığına hükmederken uygulanan tedbirler de kaldırıldı.</t>
+          <t>Antalya'da depo yangını / Ek fotoğraflar Antalya'da depo yangını / Ek fotoğraflar Antalya İleri Antalya'da depo yangını / Ek fotoğraflar Antalya İleri</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.yenicaggazetesi.com/58-yillik-turk-meyve-suyu-sirketi-iflastan-kurtuldu-her-sofrada-vardi-1070868h.htm</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE90d2U5TV9WcVhEeWsyNVEwRDI0QWZQaUg4ZXZNWnNmbzhCVUlpZ1R5X2VURWZvWjA3aWlYd0hid185U0wwSVZBby1GbW1RX2JWOHdkcHViQ0tFdXdYS3V4MGhJOWc5UmRza1AyaVJuYUx3QUxxdVZEOGh5eExiUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Antalya</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
@@ -4740,7 +4869,7 @@
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr"/>
@@ -4754,7 +4883,7 @@
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="n">
-        <v>75.39</v>
+        <v>52.04</v>
       </c>
       <c r="AB26" s="2" t="n">
         <v>25</v>
@@ -4763,27 +4892,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:18:00</t>
+          <t>2026-09-13 10:20:22</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm’de Şaşırtan Gelişme: Konkordato Kararı</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm’de Şaşırtan Gelişme: Konkordato Kararı KGRT Haber</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor sondakika.com</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4793,18 +4922,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>turizm</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Sakarya’nın uzun yıllardır şehirlerarası yolcu taşımacılığında faaliyet gösteren markalarından VİB Turizm, mali yapısını yeniden düzenlemek amacıyla konkordato başvurusunda bulundu. Mahkeme, şirket ve yönetim kurulu başkanı hakkında 3 aylık geçici mühlet kararı verirken, faaliyetlerin devam ettiği bildirildi. Sakarya’nın uzun yıllardır şehirlerarası yolcu taşımacılığında faaliyet gösteren markalarından VİB Turizm, mali yapısını yeniden düzenlemek amacıyla konkordato başvurusunda bulundu. Mahkeme, şirket ve yönetim kurulu başkanı hakkında 3 aylık geçici mühlet kararı verirken, faaliyetlerin devam ettiği bildirildi. Sakarya’nın uzun yıllardır şehirlerarası yolcu taşımacılığında faaliyet gösteren markalarından VİB Turizm, mali yapısını yeniden düzenlemek amacıyla konkordato başvurusunda bulundu. Mahkeme, şirket ve yönetim kurulu başkanı hakkında 3 aylık geçici mühlet kararı verirken, faaliyetlerin devam ettiği bildirildi. Gündem Asayiş Politika Karaman Vefat Dünya Genel VİB Turizm’de Şaşırtan Gelişme: Konkordato Kararı Sakarya’nın uzun yıllardır şehirlerarası yolcu taşımacılığında faaliyet gösteren markalarından VİB Turizm, mali yapısını yeniden düzenlemek amacıyla konkordato başvurusunda bulundu. Mahkeme, şirket ve yönetim kurulu başkanı hakkında 3 aylık geçici mühlet kararı verirken, faaliyetlerin devam ettiği bildirildi. Hatice Kübra Sarı Editör 12.09.2026 - 13:18 Yayınlanma — Paylaşım 2 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sedat Şahin’e Yönelik Saldırı Planı Çökertildi İçeriği Görüntüle Sakarya Asliye Ticaret Mahkemesi, Sınırlı Sorumlu 37 Nolu Sakarya VİB Otobüsçüler Karayolu Yolcu Taşıma Kooperatifi ile Yönetim Kurulu Başkanı Suat Akın hakkında 28 Ağustos 2026 tarihinden itibaren geçerli olmak üzere 3 aylık geçici mühlet uygulanmasına karar verdi. Mahkeme tarafından konkordato sürecini takip etmek ve şirketin mali durumunu incelemek üzere üç kişilik komiser heyeti de görevlendirildi. Banka borçları yeniden yapılandırılacak VİB Turizm yönetimi tarafından yapılan açıklamada, konkordato sürecinin temel amacının bankalara yönelik finansal yükümlülüklerin yeniden yapılandırılması olduğu belirtildi. Şirketin açıklamasında, mali yapının daha sağlıklı hale getirilmesi ve borçların sürdürülebilir bir ödeme planına bağlanmasının hedeflendiği ifade edildi. Konkordato kararının şirketin faaliyetlerini durdurmadığına da dikkat çekildi. Buna göre VİB Turizm’in seferleri, bilet satışları ve diğer operasyonları devam ediyor. Son iki yılın verileri dikkat çekiyor Şirketin mali durumuna ilişkin kamuoyuna yansıyan bilgiler arasında 2024 ve 2025 yıllarına ait vergi kayıtları da bulunuyor. VİB Turizm’in bu iki yılda vergiye esas matrah bildirmediği belirtiliyor. Ancak söz konusu verinin tek başına şirketin toplam borcunu ya da zarar miktarını ortaya koymadığına dikkat çekiliyor. Şirketin mali tablosunun konkordato sürecindeki incelemeler sonucunda daha net ortaya çıkması bekleniyor. Büyüme planlarının ardından konkordato geldi VİB Turizm’in konkordato sürecine girmesi, şirketin daha önce açıkladığı büyüme hedeflerinin ardından gelmesi nedeniyle de dikkat çekti. 2024 yılı sonunda şirketin 54 araçla 45 şehirde ve 500 şubeyle hizmet verdiği açıklanmış, 2025 yılı için filonun genişletilmesi ve yeni güzergâhların devreye alınması hedeflenmişti. Şimdi ise şirketin önündeki en önemli gündem maddesini mevcut finansal yükümlülüklerin yeniden düzenlenmesi oluşturuyor. Otobüs sektöründe maliyetler yükseldi VİB Turizm’in konkordato gerekçesinde banka borçlarının yeniden yapılandırılması öne çıkarken, şehirlerarası taşımacılık sektöründe artan işletme maliyetleri de dikkat çekiyor. Akaryakıt başta olmak üzere bakım, yedek parça ve sigorta giderlerindeki yükselişler otobüs işletmecilerinin maliyetlerini artıran unsurlar arasında yer alıyor. VİB Turizm için kritik 3 ay Mahkemenin verdiği karar şirket açısından doğrudan iflas anlamına gelmiyor. Verilen karar, 3 aylık geçici konkordato mühletini kapsıyor. Bu süreçte görevlendirilen komiser heyetinin şirketin borçlarını, gelir-gider dengesini, nakit akışını ve konkordato projesinin uygulanabilirliğini incelemesi bekleniyor. Yaklaşık 29 yıldır yolcu taşımacılığı sektöründe faaliyet gösteren VİB Turizm’in bundan sonraki süreçte mali yapısını nasıl toparlayacağı ve konkordato sürecinin nasıl sonuçlanacağı yapılacak incelemelerin ardından belli olacak. Kaynak: HATİCE KÜBRA SARI Editörün Seçtiği Takla atan otomobilden mısır tarlasına fırlayan şahıs hayatını kaybetti Editörün Seçtiği Karaman’da domuz saldırısına uğrayan genç çoban ölümden döndü Editörün Seçtiği Karaman’da üniversite bölgesinde denetimler arttı Editör Hakkında Hatice Kübra Sarı Bunlar da ilgin</t>
+          <t>Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Güncelleme: 13.09.2026 13:20 Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Kaynak: AA Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm’de Şaşırtan Gelişme: Konkordato Kararı VİB Turizm’de Şaşırtan Gelişme: Konkordato Kararı KGRT Haber Sakarya’nın uzun yıllardır şehirlerarası yolcu taşımacılığında faaliyet gösteren markalarından VİB Turizm, mali yapısını yeniden düzenlemek amacıyla konkordato başvurusunda bulundu. Mahkeme, şirket ve yönetim kurulu başkanı hakkında 3 aylık geçici mühlet kararı verirken, faaliyetlerin devam ettiği bildirildi. Gündem Asayiş Politika Karaman Vefat Dünya Genel VİB Turizm’de Şaşırtan Gelişme: Konkordato Kararı Sakarya’nın uzun yıllardır şehirlerarası yolcu taşımacılığında faaliyet gösteren markalarından VİB Turizm, mali yapısını yeniden düzenlemek amacıyla konkordato başvurusunda bulundu. Hatice Kübra Sarı Editör 12.09.2026 - 13:18 Yayınlanma — Payla</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor sondakika.com Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Güncelleme: 13.09.2026 13:20 Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Kaynak: AA Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -4814,15 +4947,19 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.kgrthaber.com/vib-turizmde-sasirtan-gelisme-konkordato-karari</t>
+          <t>https://www.sondakika.com/amp/haber-bolu-gerede-deki-geri-donusum-deposunda-yangin-son-20233164/</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Sakarya</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
@@ -4830,7 +4967,7 @@
       <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr"/>
@@ -4844,7 +4981,7 @@
       <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="n">
-        <v>62.5</v>
+        <v>122.5</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>26</v>
@@ -4853,27 +4990,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:32:59</t>
+          <t>2026-09-12 19:47:00</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Seferler ve bilet satışı sürüyor</t>
+          <t>Depo’da korkutan yangın, mahalleli seferber oldu</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Seferler ve bilet satışı sürüyor bolgegundemi.com</t>
+          <t>Depo’da korkutan yangın, mahalleli seferber oldu BursaVar</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -4883,28 +5020,32 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>turizm</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Depo’da korkutan yangın, mahalleli seferber oldu BursaVar</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm konkordato ilan etti: Seferler ve bilet satışı sürüyor VİB Turizm konkordato ilan etti: Seferler ve bilet satışı sürüyor bolgegundemi.com www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Depo’da korkutan yangın, mahalleli seferber oldu Depo’da korkutan yangın, mahalleli seferber oldu BursaVar Depo’da korkutan yangın, mahalleli seferber oldu BursaVar</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.bolgegundemi.com/gundem/vib-turizm-konkordato-ilan-etti-seferler-ve-bilet-satisi-suruyor-175965.html</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOYnkydTM5a0phbkY3cjNoSFV5MnBubnBoMXNTRHFla2ZaRGpOeU12OGx5RnZlT0d4c09sSVFFcTFTSEVXVVBJQUhXWkxjOWFGVVlyNGxMN20wTG5OSmlFX1p1enY3cjNmV0dWc1pfTkUxaklLNHNjaFJTYkw0Ym1NWXNNVHpLQ0RVNHpMS2Z4SdIBlAFBVV95cUxPTFJZc2NOUm9ReWY3eGEzeWhwOXJGbXZ4R25DOEdpd1RtNzdDYWY2TGFlYXpFbnRVZExMSlVzT3pacTVST2JucVJsb0YxM2h1allEcWg2Wk4xeDJacktzVjRndHkzQkFkUTRYMkIwMEdoU3dJdGlRYnBRYkpWNGZRWVJMS2NuWFczaTAwNHVjMG1hVS11?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
@@ -4930,7 +5071,7 @@
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="n">
-        <v>74.45999999999999</v>
+        <v>46.82</v>
       </c>
       <c r="AB28" s="2" t="n">
         <v>27</v>
@@ -4939,27 +5080,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 21:52:00</t>
+          <t>2026-09-12 17:42:00</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat devi şirketi iflas etti</t>
+          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne?</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat devi şirketi iflas etti Evrensel.net</t>
+          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? politikam.com</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -4969,22 +5110,22 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>inşaat, şirket</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>İzmir merkezli İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında mahkeme tarafından iflas kararı verildi. Alacaklılar için ek sıra cetveli hazırlandı. 11.09.2026 13:51 Deştin köylülerinden bilirkişi heyeti hakkında suç duyurusu: Çimento davasındaki bilirkişi raporunu şirket danışmanı mı hazırladı? Muğla'da çimento fabrikasına karşı direnen yöre halkı, lehte görüş bildiren bilirkişi raporunun dijital künyesinde şirket danışmanının adının çıkması üzerine 9 bilirkişi ve şirket yetkilileri hakkında suç duyurusunda bulundu. Fotoğraf: Deştin Çevre Platformu Özer Akdemir ozerakdemir@gmail.com İçerik yükleniyor... Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin İzmir merkezli İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında mahkeme tarafından iflas kararı verildi. Alacaklılar için ek sıra cetveli hazırlandı. Fotoğraf: Josue Isai Ramos Figueroa/Unsplash Batı Nil virüsü Avrupa’da 15 ülkede görülürken toplam yerel vaka sayısı 1.086’ya ulaştı. Hollanda’da ağustos ayından bu yana 18 vaka tespit edilirken 3 kişi hayatını kaybetti. Fotoğraf: DHA Bursa İnegöl'de iddiaya göre dengesini kaybederek 4 katlı binanın en üst katındaki dairenin balkonundan düşen Merve Emin, yaşamını yitirdi. Fotoğraf: DHA Giresun'un Şebinkarahisar ilçesinde mevsimlik tarım işçilerini taşıyan minibüs ile kamyonet çarpıştı, 23 kişi yaralandı. Mahmut Ahmet Yeles/AA Rusya Devlet Başkanı Vladimir Putin, Avrupalı askeri birliklerin Ukrayna'da konuşlanmasının kendilerine karşı savaş açılması anlamına geleceğini söyledi. Kremlin Basın Servisi Muğla'da çimento fabrikasına karşı direnen yöre halkı, lehte görüş bildiren bilirkişi raporunun dijital künyesinde şirket danışmanının adının çıkması üzerine 9 bilirkişi ve şirket yetkilileri hakkında suç duyurusunda bulundu. Fotoğraf: Deştin Çevre Platformu Körfez ülkelerinin dışişleri bakanlarının, Hürmüz Boğazı’ndan ticari gemi geçişlerinin yeniden başlaması için İran Dışişleri Bakanı Abbas Arakçi ile görüşmesi bekleniyor. Görüşme, Umman'ın girişimiyle 14 Eylül'de Salalah kentinde yapılacak. Fotoğraf: DHA İçerik yükleniyor... (Haber Merkezi) Devamını Oku İçerik yükleniyor... (DHA) İçerik yükleniyor... (AA) Özer Akdemir ozerakdemir@gmail.com İçerik yükleniyor... İçerik yükleniyor... (Dış Haberler) 35 yıllık inşaat şirketi iflas etti İzmir merkezli İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında mahkeme tarafından iflas kararı verildi. Alacaklılar için ek sıra cetveli hazırlandı. Sivrisineklerden bulaşıyor, çoğu belirti vermiyor: Batı Nil virüsü Avrupa’da yayılıyor? Batı Nil virüsü Avrupa’da 15 ülkede görülürken toplam yerel vaka sayısı 1.086’ya ulaştı. Hollanda’da ağustos ayından bu yana 18 vaka tespit edilirken 3 kişi hayatını kaybetti. İnegöl'de balkondan düşen kadın yaşamını yitirdi Bursa İnegöl'de iddiaya göre dengesini kaybederek 4 katlı binanın en üst katındaki dairenin balkonundan düşen Merve Emin, yaşamını yitirdi. Giresun'da tarım işçilerini taşıyan minibüs kaza yaptı: 23 yaralı Giresun'un Şebinkarahisar ilçesinde mevsimlik tarım işçilerini taşıyan minibüs ile kamyonet çarpıştı, 23 kişi yaralandı. Putin: Ukrayna'ya Avrupa askerinin konuşlandırılması savaş ilanı olur Rusya Devlet Başkanı Vladimir Putin, Avrupalı askeri birliklerin Ukrayna'da konuşlanmasının kendilerine karşı savaş açılması anlamına geleceğini söyledi. Deştin köylülerinden bilirkişi heyeti hakkında suç duyurusu: Çimento davasındaki bilirkişi raporunu şirket danışmanı mı hazırladı? Muğla'da çimento fabrikasına karşı direnen yöre halkı, lehte görüş bildiren bilirkişi raporunun dijital künyesinde şirket danışmanının adının çıkması üzerine 9 bilirkişi ve şirket yetkilileri hakkında suç duyurusunda bulundu. Körfez ülkeleri Hürmüz için İran'la görüşecek Körfez ülkelerinin dışişleri bakanlarının, Hürmüz Boğazı’ndan ticari gemi geçişlerinin yeniden başlaması için İran Dışişleri Bakanı Abbas Arakçi ile görüşmesi bekleniyor. Görüşme, Umman'ın girişimiyle 14 Eylül'de Salalah kentinde yapılacak. Fotoğraf: Josue Isai Ramos Figueroa/Unsplash İzmir merkezli İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında İzmir 3. Asliye Ticaret Mahkemesi tarafından iflas kararı verildi. Mahkeme kararının ardından şirketin alacaklıları için ek sıra cetveli hazırlandı. Yaklaşık 35 yıldır faaliyet gösteren İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş.’nin iflasına, İzmir 3. Asliye Ticaret Mahkemesi’nin 23 Ocak 2026 tarihli ve 2023/829 Esas sayılı kararıyla hükmedildi. İflas kararının ardından hazırlanan ilan İzmir İflas Müdürlüğü tarafından yayımlandı. İlanda, şirketin borçları nedeniyle iflas masasına alacak kaydı yaptıranların kayıt, kabul, ret ve sıralarını gösteren 8 Eylül 2026 tarihli ek sıra cetvelinin İzmir İflas Müdürlüğü divanhanesine asıldığı belirtildi. İlanda, sıra cetvelinde gösterilen alacakların esasına ilişkin itirazların en geç 15 gün içerisinde İzmir Asliye Ticaret Mahkemelerinde, alacağın sırasına ilişkin itirazların ise en geç 7 gün içerisinde İzmir İcra Hukuk Mahkemelerinde dava yoluyla yapılabileceği bildirildi. İzmir İflas Müdürlüğü, duyurunun İcra ve İflas Kanunu’nun ilgili maddeleri kapsamında yapıldığını belirtti. 31 yıldır emeğin sesi olan Evrensel, gücünü sadece okurlarından alıyor. Emeğin sesinin daha gür çıkması için sen de güç ver. Fotoğraf: Deştin Çevre Platformu Özer Akdemir ozerakdemir@gmail.com Önemli haberlerden ve gelişmelerden haberdar olmak ister misiniz?</t>
+          <t>Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Olay yerinden ilk detaylar haberimizde. Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Olay yerinden ilk detaylar haberimizde. Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Olay yerinden ilk detaylar haberimizde. Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Olay yerinden ilk detaylar haberimizde. Kevser Yoldaş Editör 12.09.2026 - 20:42 Yayınlanma — Paylaşım 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Antalya’nın Muratpaşa ilçesinde akşam saatlerinde hareketli dakikalar yaşandı. Yenigöl Mahallesi Lavanta Sokak üzerinde bulunan bir ambalaj deposunda henüz belirlenemeyen bir nedenle yangın çıktı. Depoda bulunan plastik ve ambalaj malzemelerinin tutuşmasıyla alevler kısa sürede büyüyerek kontrolden çıktı. Rüzgarın ve yanıcı maddelerin etkisiyle şiddetini artıran alevler, deponun hemen bitişiğinde yer alan müstakil bir eve sıçradı. İtfaiye, Polis ve Sağlık Ekipleri Alarmda Sokaktan yükselen dumanları ve alevleri gören mahalle sakinlerinin ihbarı üzerine bölgeye çok sayıda itfaiye, polis ve 112 Acil Sağlık ekibi sevk edildi. Olay yerine kısa sürede ulaşan emniyet güçleri çevrede güvenlik önlemleri alarak sokağı trafiğe ve yaya geçişine kapatırken, sağlık ekipleri de olası yaralanma ve dumandan etkilenme ihtimallerine karşı hazır bekletilmeye başlandı. Söndürme Çalışmaları Devam Ediyor İtfaiye ekipleri, hem ambalaj deposunu saran alevleri kontrol altına almak hem de eve sıçrayan yangının diğer yapılara yayılmasını önlemek için yoğun bir çalışma yürütüyor. Yangının çıkış nedeninin belirlenmesi amacıyla söndürme işlemlerinin tamamlanmasının ardından inceleme başlatılacak. Kaynak: Anadolu Ajansı Editör Kevser Yoldaş Bu</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat devi şirketi iflas etti 35 yıllık inşaat devi şirketi iflas etti Evrensel.net İzmir merkezli İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında mahkeme tarafından iflas kararı verildi. Alacaklılar için ek sıra cetveli hazırlandı. 11.09.2026 13:51 Deştin köylülerinden bilirkişi heyeti hakkında suç duyurusu: Çimento davasındaki bilirkişi raporunu şirket danışmanı mı hazırladı? Muğla'da çimento fabrikasına karşı direnen yöre halkı, lehte görüş bildiren bilirkişi raporunun dijital künyesinde şirket danışmanının adının çıkması üzerine 9 bilirkişi ve şirket yetkilileri hakkında suç duyurusunda bulundu. Fotoğraf: Deştin Çevre Platformu Özer Akdemir ozerakdemir@gmail.com İçerik yükleniyor... Evrensel'i, Google'da tercih edilen kaynak olarak ekleyin İzmir merkezli İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında mahkeme tarafından iflas kararı verildi. Fotoğraf: Josue Isai Ramos Figueroa/Unsplash Batı Nil virüsü Avrupa’da 15 ülkede görülürken toplam yerel vaka sayısı 1.086’ya ulaştı. Hollanda’da ağustos ayından bu yana 18 vaka tespit edilirken 3 kişi hayatını kaybetti. Fotoğraf: DHA Bursa İnegöl'de iddiaya göre dengesini kaybederek 4 katlı binanın en üst katındaki dairenin balkonundan düşen Merve Emin, yaşamını yitirdi. Fotoğraf: DHA Giresun'un Şebinkarahisar ilçesinde mevsimlik tarım işçilerini taşıyan minibüs ile kamyonet çarpıştı, 23 kişi yaralandı. Mahmut Ahmet Yeles/AA Rusya Devlet Başkanı Vladimir Putin, Avrupalı askeri birliklerin Ukrayna'da konuşlanmasının kendilerine karşı savaş açılması anlamına geleceğini söyledi. Kremlin Basın Servisi Muğla'da çimento fabrikasına karşı direnen yöre halkı, lehte görüş bildiren bilirkişi raporunun dijital künyesinde şirket danışmanının adının çıkması üzerine 9 bilirkişi ve şirket yetkilileri hakkında suç duyurusunda bulundu. Fotoğraf: Deştin Çevre Platformu Körfez ülkelerinin dışişleri bakanlarının, Hürmüz Boğazı’ndan ticari gemi geçişlerinin yeniden başlaması için İran Dışişleri Bakanı Abbas Arakçi ile görüşmesi bekleniyor. (Dış Haberler) 35 yıllık inşaat şirketi iflas etti İzmir merkezli İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında mahkeme tarafından iflas kararı verildi. Sivrisineklerden bulaşıyor, çoğu belirti vermiyor: Batı Nil virüsü Avrupa’da yayılıyor? Batı Nil virüsü Avrupa’da 15 ülkede görülürken toplam yerel vaka sayısı 1.086’ya ulaştı. İnegöl'de balkondan düşen kadın yaşamını yitirdi Bursa İnegöl'de iddiaya göre dengesini kaybederek 4 katlı binanın en üst katındaki dairenin balkonundan düşen Merve Emin, yaşamını yitirdi. Giresun'da tarım işçilerini taşıyan minibüs kaza yaptı: 23 yaralı Giresun'un Şebinkarahisar ilçesinde mevsimlik tarım işçilerini taşıyan minibüs ile kamyonet çarpıştı, 23 kişi yaralandı. Putin: Ukrayna'ya Avrupa askerinin konuşlandırılması savaş ilanı olur Rusya Devlet Başkanı Vladimir Putin, Avrupalı askeri birliklerin Ukrayna'da konuşlanmasının kendilerine karşı savaş açılması anlamına geleceğini söyledi. Deştin köylülerinden bilirkişi heyeti hakkında suç duyurusu: Çimento davasındaki bilirkişi raporunu şirket danışmanı mı hazırladı? Körfez ülkeleri Hürmüz için İran'la görüşecek Körfez ülkelerinin dışişleri bakanlarının, Hürmüz Boğazı’ndan ticari gemi geçişlerinin yeniden başlaması için İran Dışişleri Bakanı Abbas Arakçi ile görüşmesi bekleniyor. Fotoğraf: Josue Isai Ramos Figueroa/Unsplash İzmir merkezli İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında İzmir 3. Asliye Ticaret Mahkemesi tarafından iflas kararı verildi. Mahkeme kararının ardından şirketin alacaklıları için ek sıra cetveli hazırlandı. Yaklaşık 35 yıldır faaliyet gösteren İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş.’nin iflasına, İzmir 3. Asliye Ticaret Mahkemesi’nin 23 Ocak 2026 tarihli ve 2023/829 Esas sayılı kararıyla hükmedildi. İflas kararının ardından hazırlanan ilan İzmir İflas Müdürlüğü tarafından yayımlandı. İlanda, şirketin borçları nedeniyle iflas masasına alacak kaydı yaptıranların kayıt, kabul, ret ve sıralarını gösteren 8 Eylül 2026 tarihli ek sıra cetvelinin İzmir İflas Müdürlüğü divanhanesine asıldığı belirtildi. İlanda, sıra cetvelinde gösterilen alacakların esasına ilişkin itirazların en geç 15 gün içerisinde İzmir Asliye Ticaret Mahkemelerinde, alacağın sırasına ilişkin itirazların ise en geç 7 gün içerisinde İzmir İcra Hukuk Mahkemelerinde dava yoluyla yapılabileceği bildirildi. İzmir İflas Müdürlüğü, duyurunun İcra ve İflas Kanunu’nun ilgili maddeleri kapsamında yapıldığını belirtti. Emeğin sesinin daha gür çıkması için sen de güç ver.</t>
+          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? politikam.com Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Kevser Yoldaş Editör 12.09.2026 - 20:42 Yayınlanma —</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -4994,69 +5135,61 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.evrensel.net/haber/6000200/35-yillik-insaat-sirketi-iflas-etti</t>
+          <t>https://www.politikam.com/antalya-muratpasada-yangin-panigi-ambalaj-deposu-ve-yanindaki-ev-alevlere-teslim-oldu-son-durum-ne</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Giresun | İzmir | Muğla | Bursa</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>İnegöl | Şebinkarahisar</t>
+          <t>Muratpaşa</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş:65:body | İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş:raw_legal</t>
-        </is>
-      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Ambalaj Deposu</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>faaliyet/tesis yok</t>
+          <t>firma yok</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş İnegöl Giresun Türkiye</t>
+          <t>Ambalaj Deposu Muratpaşa Antalya Türkiye</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>İzmer</t>
+          <t>Ambalaj Ticaret | Balcı Ambalaj | Doğuş Ambalaj | Gürbüz Ambalaj toptan parekende | Antalya Ambalaj</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>İzmer</t>
+          <t>Ambalaj Ticaret</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>İrma Mermer | İnegöl İnci Mezar</t>
-        </is>
-      </c>
+          <t>66.66666666666666 | 70.0 | 81.48148148148148 | 66.66666666666666 | 66.66666666666666</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="n">
-        <v>173.25</v>
+        <v>205</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>28</v>
@@ -5065,7 +5198,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:23:16</t>
+          <t>2026-09-13 10:00:14</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -5080,12 +5213,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ünlü seyahat şirketi iflas etti... Rezervasyonu olanlara acil çağrı yapıldı</t>
+          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Ünlü seyahat şirketi iflas etti... Rezervasyonu olanlara acil çağrı yapıldı Turizm Aktüel</t>
+          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti Samanyolu Haber</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -5095,7 +5228,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>turizm, şirket</t>
+          <t>inşaat, şirket</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -5105,48 +5238,80 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Ünlü seyahat şirketi iflas etti... Rezervasyonu olanlara acil çağrı yapıldı Turizm Aktüel</t>
+          <t>Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler İzmir’de 35 yıldır faaliyet gösteren İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında iflas kararı verildi. Şirketin iflasına, İzmir 3. Asliye Ticaret Mahkemesi tarafından hükmedildi. Mahkemenin 23 Ocak 2026 tarihli kararıyla iflasına karar verilen şirketin alacaklılarına ilişkin ek sıra cetveli de hazırlandı. Ege’de Son Söz’de yer alan habere göre, İzmir İflas Dairesi tarafından yayımlanan ilana göre, iflas masasına alacak kaydı yaptıranların kayıt, kabul, ret ve sıralarını gösteren 8 Eylül 2026 tarihli ek sıra cetveli, aynı gün İzmir İflas Müdürlüğü divanhanesine asıldı. İlanda, sıra cetvelinde yer alan alacakların esasına ilişkin itirazların en geç 15 gün içerisinde İzmir Asliye Ticaret Mahkemelerinde yapılabileceği belirtildi. Alacakların sırasına ilişkin itirazların ise en geç 7 gün içerisinde İzmir İcra Hukuk Mahkemelerinde dava açılarak yapılabileceği bildirildi. İzmir İflas Dairesi, söz konusu sürelere ilişkin duyuruyu İcra ve İflas Kanunu’nun ilgili maddeleri kapsamında tebliğ ve ilan etti. İFLAS DUYURUSU Duyuru şu şekilde: “İzmi</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Ünlü seyahat şirketi iflas etti... Rezervasyonu olanlara acil çağrı yapıldı Ünlü seyahat şirketi iflas etti... Rezervasyonu olanlara acil çağrı yapıldı Turizm Aktüel Ünlü seyahat şirketi iflas etti... Rezervasyonu olanlara acil çağrı yapıldı Turizm Aktüel</t>
+          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti Samanyolu Haber Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler İzmir’de 35 yıldır faaliyet gösteren İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında iflas kararı verildi. Şirketin iflasına, İzmir 3. Asliye Ticaret Mahkemesi tarafından hükmedildi. Mahkemenin 23 Ocak 2026 tarihli kararıyla iflasına karar verilen şirketin alacaklılarına ilişkin ek sıra cetveli de hazırlandı. Ege’de Son Söz’de yer alan habere göre, İzmir İflas Dairesi tarafından yayımlanan ilana göre, iflas masasına alacak kaydı yaptıranların kayıt, kabul, ret ve sıralarını gösteren 8 Eylül 2026 tarihli ek sıra cetveli, aynı gün İzmir İflas Müdürlüğü divanhanesine asıldı. İlanda, sıra cetvelinde yer alan alacakların esasına ilişkin itirazların en geç 15 gün içerisinde İzmir Asliye Ticaret Mahkemelerinde yapılabileceği belirtildi. Alacakların sırasına ilişkin itirazların ise en geç 7 gün içerisinde İzmir İcra Hukuk Mahkemelerinde dava açılarak yapılabileceği bildirildi. İzmir İflas Dairesi, söz konusu sürelere ilişkin duyuruyu İcra ve İflas Kanunu’nun ilgili maddeleri kapsamında tebliğ ve ilan etti.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQRDRKYmdRczNHek5TeXl4MVl4ZTcwZ2luYUFBSG0zdkJ4MURrYVhtWWd2bGE5dWVrT3pOSUpLVXZ4QWVpQndzZ19NaW1oU1RXT0thMkxsRjF0ekdvMm5rNjNQdmdEU1pjUTJNMGJNTmFSdjlVbkp0U1ExRHVFSHlQT3hna2VOTFhiQy1uTTg2VEItR1Y2ZW9fQkVLVlNjRUhGeFJKaFhnOGh3Yzg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>https://www.samanyoluhaber.com/alacaklilar-kapiya-dayandi-35-yillik-turk-insaat-sirketi-iflas-etti-haberi/1492579</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr"/>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş:57:body | İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr"/>
-      <c r="V30" s="2" t="inlineStr"/>
-      <c r="W30" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş İzmir Türkiye</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>İzmer</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>İzmer</t>
+        </is>
+      </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y30" s="2" t="inlineStr"/>
-      <c r="Z30" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>İzmer Ege Yapı Kimyasalları | İz-Mer Mermer Granit</t>
+        </is>
+      </c>
       <c r="AA30" s="2" t="n">
-        <v>76.64</v>
+        <v>180.38</v>
       </c>
       <c r="AB30" s="2" t="n">
         <v>29</v>
@@ -5155,7 +5320,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 07:25:00</t>
+          <t>2026-09-13 06:18:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -5170,12 +5335,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için iflas talebi! Mahkeme tarihi belli oldu</t>
+          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!”</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için iflas talebi! Mahkeme tarihi belli oldu bursatv.com.tr</t>
+          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -5185,7 +5350,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>firma</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -5195,34 +5360,26 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Bursa Bursa’da bir şirket için iflas talebi! Mahkeme tarihi belli oldu Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’ndeki davanın duruşma tarihi belli olurken, alacaklılar için 15 günlük itiraz süresi başlatıldı. 12.09.2026 - 10:25 12.09.2026 - 10:25 Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi, hakkında açılan iflas talebi davasıyla gündeme geldi. Şirket aleyhine NAKLOG Lojistik ve Servis Hizmetleri Sanayi ve Ticaret Anonim Şirketi tarafından iflas talebiyle dava açılırken, dosyanın Bursa 1. Asliye Ticaret Mahkemesi’nde görüleceği bildirildi. Dava dosyasının esas numarası ise 2026/497 olarak açıklandı. İflas davasında duruşma tarihi belli oldu Mahkeme tarafından yayımlanan ilana göre dava, kambiyo senetlerine mahsus takipten doğan iflas talebine ilişkin olarak yürütülüyor. Dosya kapsamında yapılacak duruşmanın tarihi de belli oldu. Buna göre ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkındaki iflas talebinin değerlendirileceği duruşma, 9 Aralık 2026 Çarşamba günü saat 14.20’de Bursa 1. Asliye Ticaret Mahkemesi’nde yapılacak. Alacaklılara 15 günlük başvuru süresi Dava sürecinde şirketten alacağı bulunan kişilere de önemli bir süre tanındı. Mahkeme ilanında, ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi’nden alacağı bulunanların, ilanın yayımlandığı tarihten itibaren 15 gün içerisinde mahkemeye başvurarak davaya müdahil olabilecekleri belirtildi. Alacaklıların aynı süre içerisinde açılan iflas talebine itiraz etme hakkının da bulunduğu bildirildi. Böylece Bursa’da faaliyet gösteren şirket hakkında açılan iflas talebi davasında hem duruşma tarihi hem de alacaklıların başvurabileceği süre netleşmiş oldu. Davanın 9 Aralık’ta yapılacak duruşmasında, şirket hakkındaki iflas talebine ilişkin yargı sürecinin ilerlemesi bekleniyor. Bursa’da spor seferberliği! 35 bin 884 çocuk ve genç katıldı İçeriği Görüntüle Bursa-Yalova yolunu kullanacaklar dikkat! Trafik akışı değişti İçeriği Görüntüle Bursa’da benzine 2,95 TL zam geliyor! Yeni fiyatlar belli oldu İçeriği Görüntüle Bursa’da yakalanınca kontrolden çıktı! Kameralara tükürdü, polis aracına saldırdı İçeriği Görüntüle Bursa'nın vergi rekortmenleri açıklandı! Zirvedeki isim merak konusu oldu... İçeriği Görüntüle #bursa #burshaber Bunlar</t>
+          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için iflas talebi! Mahkeme tarihi belli oldu Bursa’da bir şirket için iflas talebi! Mahkeme tarihi belli oldu bursatv.com.tr Bursa Bursa’da bir şirket için iflas talebi! Mahkeme tarihi belli oldu Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Asliye Ticaret Mahkemesi’ndeki davanın duruşma tarihi belli olurken, alacaklılar için 15 günlük itiraz süresi başlatıldı. 12.09.2026 - 10:25 12.09.2026 - 10:25 Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi, hakkında açılan iflas talebi davasıyla gündeme geldi. Şirket aleyhine NAKLOG Lojistik ve Servis Hizmetleri Sanayi ve Ticaret Anonim Şirketi tarafından iflas talebiyle dava açılırken, dosyanın Bursa 1. Asliye Ticaret Mahkemesi’nde görüleceği bildirildi. Dava dosyasının esas numarası ise 2026/497 olarak açıklandı. İflas davasında duruşma tarihi belli oldu Mahkeme tarafından yayımlanan ilana göre dava, kambiyo senetlerine mahsus takipten doğan iflas talebine ilişkin olarak yürütülüyor. Dosya kapsamında yapılacak duruşmanın tarihi de belli oldu. Buna göre ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkındaki iflas talebinin değerlendirileceği duruşma, 9 Aralık 2026 Çarşamba günü saat 14.20’de Bursa 1. Asliye Ticaret Mahkemesi’nde yapılacak. Alacaklılara 15 günlük başvuru süresi Dava sürecinde şirketten alacağı bulunan kişilere de önemli bir süre tanındı. Mahkeme ilanında, ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi’nden alacağı bulunanların, ilanın yayımlandığı tarihten itibaren 15 gün içerisinde mahkemeye başvurarak davaya müdahil olabilecekleri belirtildi. Alacaklıların aynı süre içerisinde açılan iflas talebine itiraz etme hakkının da bulunduğu bildirildi. Böylece Bursa’da faaliyet gösteren şirket hakkında açılan iflas talebi davasında hem duruşma tarihi hem de alacaklıların başvurabileceği süre netleşmiş oldu. Davanın 9 Aralık’ta yapılacak duruşmasında, şirket hakkındaki iflas talebine ilişkin yargı sürecinin ilerlemesi bekleniyor. Bursa’da spor seferberliği! 35 bin 884 çocuk ve genç katıldı İçeriği Görüntüle Bursa-Yalova yolunu kullanacaklar dikkat! Trafik akışı değişti İçeriği Görüntüle Bursa’da benzine 2,95 TL zam geliyor! Yeni fiyatlar belli oldu İçeriği Görüntüle Bursa’da yakalanınca kontrolden çıktı! Kameralara tükürdü, polis aracına saldırdı İçeriği Görüntüle Bursa'nın vergi rekortmenleri açıklandı! İçeriği Görüntüle #bursa #burshaber Bunlar</t>
+          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQNXFvOFRuR1c3bVJBN1ViMV90UEJZUW1OQjRQOTA5V1phaUxGbXRnX0RycWtZYVZybnp4RV9rTnNsN2ROM2FFOXJ1TGc1Nlp2Qzc1MzJ6NExEeS02bUJmbHoyWmdSRUhfLUwtakRfYXhMNTI3c2FoUmppLVNwMXZHQTAwNkd2dUo5Z3hVSTN0dUF6T2NTNnlVStIBmAFBVV95cUxQNXFvOFRuR1c3bVJBN1ViMV90UEJZUW1OQjRQOTA5V1phaUxGbXRnX0RycWtZYVZybnp4RV9rTnNsN2ROM2FFOXJ1TGc1Nlp2Qzc1MzJ6NExEeS02bUJmbHoyWmdSRUhfLUwtakRfYXhMNTI3c2FoUmppLVNwMXZHQTAwNkd2dUo5Z3hVSTN0dUF6T2NTNnlVSg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Bursa | Iğdır</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Aralık</t>
-        </is>
-      </c>
+          <t>https://www.yeniankara.com.tr/ekonomi/ekonomist-sirinden-faiz-degerlendirmesi-bircok-firmada-iflas-var-182562</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr"/>
@@ -5230,7 +5387,7 @@
       <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr"/>
@@ -5244,7 +5401,7 @@
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="n">
-        <v>102.75</v>
+        <v>61.56</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>30</v>
@@ -5253,7 +5410,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:20:02</t>
+          <t>2026-09-12 18:50:00</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5268,12 +5425,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat şirketi iflas etti! Alacaklılar için ek sıra cetveli hazırlandı..</t>
+          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat şirketi iflas etti! Alacaklılar için ek sıra cetveli hazırlandı.. EmlakDream</t>
+          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Yıldırım Gazetesi</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -5283,7 +5440,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>inşaat, şirket</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -5293,25 +5450,29 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat şirketi iflas etti! Alacaklılar için ek sıra cetveli hazırlandı.. EmlakDream</t>
+          <t>Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı. Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı. Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı. BURSA Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>35 yıllık inşaat şirketi iflas etti! Alacaklılar için ek sıra cetveli hazırlandı.. 35 yıllık inşaat şirketi iflas etti! Alacaklılar için ek sıra cetveli hazırlandı.. EmlakDream 35 yıllık inşaat şirketi iflas etti! Alacaklılar için ek sıra cetveli hazırlandı..</t>
+          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Yıldırım Gazetesi Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı. BURSA Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNUTZDdW1lZnR0c09PNHVLQXVGSmNkVWtla1BEdHp1YmVXQ0txX3pzM1BkYnlYbHhfVjk4bVc4RjVlQ3lrU21vNUwxVnBXblZrRFlOb3B4VjI5Z0t5U1kwSm1nX1NIZy1lWUJZNlBkemtPRmRCQmc4ZmwtNzNUUVdES2poQW5hZjloanljdUprUTNIMEpJczQzX2V6dmYyLTBGQlA0WTFsSEZxQXc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>https://www.yildirimgazetesi.com/bursada-bir-sirket-icin-daha-iflas-talebi-mahkeme-tarihi-belli-oldu</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
@@ -5320,7 +5481,7 @@
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
@@ -5334,7 +5495,7 @@
       <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr"/>
       <c r="AA32" s="2" t="n">
-        <v>81.18000000000001</v>
+        <v>94.36</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>31</v>
@@ -5343,12 +5504,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:25:12</t>
+          <t>2026-09-13 01:09:00</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -5358,12 +5519,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır</t>
+          <t>Ege Gıda Meşrubat, konkordato süreci başlattı</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır Haberler</t>
+          <t>Ege Gıda Meşrubat, konkordato süreci başlattı egealternatif.com</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -5373,22 +5534,18 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>gıda</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır 11 Eylül 2026 21:26 Güncel Haberler Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. (ANKARA) - Saadet Partisi Genel Başkanı Mahmut Arıkan , Kayseri 'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. Saadet Partisi Genel Başkanı Mahmut Arıkan, sosyal medya hesabından yaptığı açıklamada, Kayseri'de faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasını uygulanan ekonomi politikalarının sonucu olarak değerlendirdi. Arıkan, şunları kaydetti: "Yüksek faiz, düşük üretim, kapanan fabrikalar... 1953'ten bu yana Kayseri'mizde üretim yapan Orta Anadolu Mensucat'ın; artan maliyetler, ağırlaşan finansman yükü ve daralan talep nedeniyle üretimini sonlandırması, uygulanan yanlış ekonomi politikalarının acı bir sonucudur. Fabrikalar kapanıyor, tezgahlar duruyor, üretim ve istihdam Türkiye'den uzaklaşıyor. Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır! İktidar ise bu acı ve müflis tablo karşısında dahi istatistik oyunlarıyla 'ekonomiyi düzeltiyoruz' diyerek milletimizi rakamlarla inandırmaya çalışıyor. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz. Ekonominin gerçeği tablolarınızda değil; kapanan fabrikalarda, duran tezgahlarda ve işini kaybeden insanlarımızdadır! Bizler üreten Türkiye'yi, Saadet Partimizin iktidarında Türkiye Kalkınma Planı ile yeniden inşa edeceğiz." Kaynak: ANKA / Güncel Mahmut Arıkan , Kayseri , Ekonomi , Güncel , Sp , İflas , Kayseri , Mahmut Arıkan , Sp , Ekonomi , Güncel , Haberler AK PARTİ AVRUPA BİRLİĞİ AZERBAYCAN BASKETBOL BELEDİYE BEŞİKTAŞ CHP ÇEVRE DEM DİPLOMASİ DOĞA DONALD TRUMP DEVLET BAHÇELİ EĞİTİM EKREM İMAMOĞLU ELON MUSK EMEKLİ EMLAK ENERJİ ENFLASYON ESNAF FENERBAHÇE FİKSTÜR FİLİSTİN FUTBOL GALATASARAY GASTRONOMİ GAZZE GÜNCEL GÜVENLİK GÖÇMEN HAKAN FİDAN HASTANE HAYVAN HAKLARI HIRSIZLIK HUKUK IRAK İNSAN HAKLARI İRAN İSRAİL İSTANBUL İŞÇİ İTFAİYE JANDARMA JOSE MOURINHO KAZA KRİPTO KÜLTÜR SANAT MAÇ SONUÇLARI MAHKEME MEDYA MHP MOTOSİKLET MÜZİK NARKOTİK OKAN BURUK OPERASYON ORTA DOĞU OTOMOBİL ÖĞRETMEN ÖZGÜR ÖZEL POLİS PUAN DURUMU RECEP TAYYİP ERDOĞAN RUSYA SAĞLIK SANAT SAVAŞ SAVUNMA SİVİL TOPLUM SUÇ SÜPER LİG SURİYE TARIM TBMM TERÖR TRABZONSPOR TRAFİK TURİZM UEFA UKRAYNA ULAŞIM ULUSLARARASI İLİŞKİLER ÜMİT ÖZDAĞ ÜNİVERSİTE VLADİMİR PUTİN YANGIN YARGI YAŞAM YATIRIM YEMEK TARİFİ YEREL YÖNETİM EKONOMİ MAGAZİN SPOR KRİPTO PARA SON DAKİKA KADIN POLİTİKA FİNANS 3.SAYFA TEKNOLOJİ DÜNYA RESMİ İLANLAR YEREL HABERLER KÜLTÜR-SANAT SAĞLIK OTOMOBİL ENERJİ BELEDİYE HABERLERİ AK PARTİ AVRUPA BİRLİĞİ AZERBAYCAN BASKETBOL BELEDİYE BEŞİKTAŞ CHP ÇEVRE DEM DİPLOMASİ DOĞA DONALD TRUMP DEVLET BAHÇELİ EĞİTİM EKREM İMAMOĞLU ELON MUSK EMEKLİ EMLAK ENERJİ ENFLASYON ESNAF FENERBAHÇE FİKSTÜR FİLİSTİN FUTBOL GALATASARAY GASTRONOMİ GAZZE GÜNCEL GÜVENLİK GÖÇMEN HAKAN FİDAN HASTANE HAYVAN HAKLARI HIRSIZLIK HUKUK IRAK İNSAN HAKLARI İRAN İSRAİL İSTANBUL İŞÇİ İTFAİYE JANDARMA JOSE MOURINHO KAZA KRİPTO KÜLTÜR SANAT MAÇ SONUÇLARI MAHKEME MEDYA MHP MOTOSİKLET MÜZİK NARKOTİK OKAN BURUK OPERASYON ORTA DOĞU OTOMOBİL ÖĞRETMEN ÖZGÜR ÖZEL POLİS PUAN DURUMU RECEP TAYYİP ERDOĞAN RUSYA SAĞLIK SANAT SAVAŞ SAVUNMA SİVİL TOPLUM SUÇ SÜPER LİG SURİYE TARIM TBMM TERÖR TRABZONSPOR TRAFİK TURİZM UEFA UKRAYNA ULAŞIM ULUSLARARASI İLİŞKİLER ÜMİT ÖZDAĞ ÜNİVERSİTE VLADİMİR PUTİN YANGIN YARGI YAŞAM YATIRIM YEMEK TARİFİ YEREL YÖNETİM Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır 11 Eylül 2026 21:26 Güncel Haberler Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. (ANKARA) - Saadet Partisi Genel Başkanı Mahmut Arıkan , Kayseri 'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. Saadet Partisi Genel Başkanı Mahmut Arıkan, sosyal medya hesabından yaptığı açıklamada, Kayseri'de faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasını uygulanan ekonomi politikalarının sonucu olarak değerlendirdi. Arıkan, şunları kaydetti: "Yüksek faiz, düşük üretim, kapanan fabrikalar... 1953'ten bu yana Kayseri'mizde üretim yapan Orta Anadolu Mensucat'ın; artan maliyetler, ağırlaşan finansman yükü ve daralan talep nedeniyle üretimini sonlandırması, uygulanan yanlış ekonomi politikalarının acı bir sonucudur. Fabrikalar kapanıyor, tezgahlar duruyor, üretim ve istihdam Türkiye'den uzaklaşıyor. Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır! İktidar ise bu acı ve müflis tablo karşısında dahi istatistik oyunlarıyla 'ekonomiyi düzeltiyoruz' diyerek milletimizi rakamlarla inandırmaya çalışıyor. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz. Ekonominin gerçeği tablolarınızda değil; kapanan fabrikalarda, duran tezgahlarda ve işini kaybeden insanlarımızdadır! Bizler üreten Türkiye'yi, Saadet Partimizin iktidarında Türkiye Kalkınma Planı ile yeniden inşa edeceğiz." Kaynak: ANKA / Güncel Mahmut Arıkan , Kayseri , Ekonomi , Güncel , Sp , İflas , Kayseri , Mahmut Arıkan , Sp , Ekonomi , Güncel , Haberler AK PARTİ AVRUPA BİRLİĞİ AZERBAYCAN BASKETBOL BELEDİYE BEŞİKTAŞ CHP ÇEVRE DEM DİPLOMASİ DOĞA DONALD TRUMP DEVLET BAHÇELİ EĞİTİM EKREM İMAMOĞLU ELON MUSK EMEKLİ EMLAK ENERJİ ENFLASYON ESNAF FENERBAHÇE FİKSTÜR FİLİSTİN FUTBOL GALATASARAY GASTRONOMİ GAZZE GÜNCEL GÜVENLİK GÖÇMEN HAKAN FİDAN HASTANE HAYVAN HAKLARI HIRSIZLIK HUKUK IRAK İNSAN HAKLARI İRAN İSRAİL İSTANBUL İŞÇİ İTFAİYE JANDARMA JOSE MOURINHO KAZA KRİPTO KÜLTÜR SANAT MAÇ SONUÇLARI MAHKEME MEDYA MHP MOTOSİKLET MÜZİK NARKOTİK OKAN BURUK OPERASYON ORTA DOĞU OTOMOBİL ÖĞRETMEN ÖZGÜR ÖZEL POLİS PUAN DURUMU RECEP TAYYİP ERDOĞAN RUSYA SAĞLIK SANAT SAVAŞ SAVUNMA SİVİL TOPLUM SUÇ SÜPER LİG SURİYE TARIM TBMM TERÖR TRABZONSPOR TRAFİK TURİZM UEFA UKRAYNA ULAŞIM ULUSLARARASI İLİŞKİLER ÜMİT ÖZDAĞ ÜNİVERSİTE VLADİMİR PUTİN YANGIN YARGI YAŞAM YATIRIM YEMEK TARİFİ YEREL YÖNETİM Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. (ANKARA) - Saadet Partisi Genel Başkanı Mahmut Arıkan , Kayseri 'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. Saadet Partisi Genel Başkanı Mahmut Arıkan, sosyal medya hesabından yaptığı açıklamada, Kayseri'de faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasını uygulanan ekonomi politikalarının sonucu olarak değerlendirdi. Arıkan, şunları kaydetti: "Yüksek faiz, düşük üretim, kapanan fabrikalar... 1953'ten bu yana Kayseri'mizde üretim yapan Orta Anadolu Mensucat'ın; artan maliyetler, ağırlaşan finansman yükü ve daralan talep nedeniyle üretimini sonlandırması, uygulanan yanlış ekonomi politikalarının acı bir sonucudur. Fabrikalar kapanıyor, tezgahlar duruyor, üretim ve istihdam Türkiye'den uzaklaşıyor. Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır! İktidar ise bu acı ve müflis tablo karşısında dahi istatistik oyunlarıyla 'ekonomiyi düzeltiyoruz' diyerek milletimizi rakamlarla inandırmaya çalışıyor. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz. Ekonominin gerçeği tablolarınızda değil; kapanan fabrikalarda, duran tezgahlarda ve işini kaybeden insanlarımızdadır! Bizler üreten Türkiye'yi, Saadet Partimizin iktidarında Türkiye Kalkınma Planı ile yeniden inşa edeceğiz."</t>
+          <t>Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi, Edirne 2’nci Asliye Hukuk Mahkemesi tarafından konkordato ilan etti ve 3 aylık geçici mühlet aldı. Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi, Edirne 2’nci Asliye Hukuk Mahkemesi tarafından konkordato ilan etti ve 3 aylık geçici mühlet aldı. Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi, Edirne 2’nci Asliye Hukuk Mahkemesi tarafından konkordato ilan etti ve 3 aylık geçici mühlet aldı.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır Haberler Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz" açıklamasını yaptı. Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır 11 Eylül 2026 21:26 Güncel Haberler Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. (ANKARA) - Saadet Partisi Genel Başkanı Mahmut Arıkan , Kayseri 'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Saadet Partisi Genel Başkanı Mahmut Arıkan, sosyal medya hesabından yaptığı açıklamada, Kayseri'de faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasını uygulanan ekonomi politikalarının sonucu olarak değerlendirdi. Arıkan, şunları kaydetti: "Yüksek faiz, düşük üretim, kapanan fabrikalar... 1953'ten bu yana Kayseri'mizde üretim yapan Orta Anadolu Mensucat'ın; artan maliyetler, ağırlaşan finansman yükü ve daralan talep nedeniyle üretimini sonlandırması, uygulanan yanlış ekonomi politikalarının acı bir sonucudur. Fabrikalar kapanıyor, tezgahlar duruyor, üretim ve istihdam Türkiye'den uzaklaşıyor. Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır! Rakamları makyajlayarak kapanan fabrikaların bacasını tüttüremez, duran tezgahı çalıştıramaz, kaybedilen istihdamı geri getiremezsiniz. Bizler üreten Türkiye'yi, Saadet Partimizin iktidarında Türkiye Kalkınma Planı ile yeniden inşa edeceğiz." Kaynak: ANKA / Güncel Mahmut Arıkan , Kayseri , Ekonomi , Güncel , Sp , İflas , Kayseri , Mahmut Arıkan , Sp , Ekonomi , Güncel , Haberler AK PARTİ AVRUPA BİRLİĞİ AZERBAYCAN BASKETBOL BELEDİYE BEŞİKTAŞ CHP ÇEVRE DEM DİPLOMASİ DOĞA DONALD TRUMP DEVLET BAHÇELİ EĞİTİM EKREM İMAMOĞLU ELON MUSK EMEKLİ EMLAK ENERJİ ENFLASYON ESNAF FENERBAHÇE FİKSTÜR FİLİSTİN FUTBOL GALATASARAY GASTRONOMİ GAZZE GÜNCEL GÜVENLİK GÖÇMEN HAKAN FİDAN HASTANE HAYVAN HAKLARI HIRSIZLIK HUKUK IRAK İNSAN HAKLARI İRAN İSRAİL İSTANBUL İŞÇİ İTFAİYE JANDARMA JOSE MOURINHO KAZA KRİPTO KÜLTÜR SANAT MAÇ SONUÇLARI MAHKEME MEDYA MHP MOTOSİKLET MÜZİK NARKOTİK OKAN BURUK OPERASYON ORTA DOĞU OTOMOBİL ÖĞRETMEN ÖZGÜR ÖZEL POLİS PUAN DURUMU RECEP TAYYİP ERDOĞAN RUSYA SAĞLIK SANAT SAVAŞ SAVUNMA SİVİL TOPLUM SUÇ SÜPER LİG SURİYE TARIM TBMM TERÖR TRABZONSPOR TRAFİK TURİZM UEFA UKRAYNA ULAŞIM ULUSLARARASI İLİŞKİLER ÜMİT ÖZDAĞ ÜNİVERSİTE VLADİMİR PUTİN YANGIN YARGI YAŞAM YATIRIM YEMEK TARİFİ YEREL YÖNETİM EKONOMİ MAGAZİN SPOR KRİPTO PARA SON DAKİKA KADIN POLİTİKA FİNANS 3.SAYFA TEKNOLOJİ DÜNYA RESMİ İLANLAR YEREL HABERLER KÜLTÜR-SANAT SAĞLIK OTOMOBİL ENERJİ BELEDİYE HABERLERİ AK PARTİ AVRUPA BİRLİĞİ AZERBAYCAN BASKETBOL BELEDİYE BEŞİKTAŞ CHP ÇEVRE DEM DİPLOMASİ DOĞA DONALD TRUMP DEVLET BAHÇELİ EĞİTİM EKREM İMAMOĞLU ELON MUSK EMEKLİ EMLAK ENERJİ ENFLASYON ESNAF FENERBAHÇE FİKSTÜR FİLİSTİN FUTBOL GALATASARAY GASTRONOMİ GAZZE GÜNCEL GÜVENLİK GÖÇMEN HAKAN FİDAN HASTANE HAYVAN HAKLARI HIRSIZLIK HUKUK IRAK İNSAN HAKLARI İRAN İSRAİL İSTANBUL İŞÇİ İTFAİYE JANDARMA JOSE MOURINHO KAZA KRİPTO KÜLTÜR SANAT MAÇ SONUÇLARI MAHKEME MEDYA MHP MOTOSİKLET MÜZİK NARKOTİK OKAN BURUK OPERASYON ORTA DOĞU OTOMOBİL ÖĞRETMEN ÖZGÜR ÖZEL POLİS PUAN DURUMU RECEP TAYYİP ERDOĞAN RUSYA SAĞLIK SANAT SAVAŞ SAVUNMA SİVİL TOPLUM SUÇ SÜPER LİG SURİYE TARIM TBMM TERÖR TRABZONSPOR TRAFİK TURİZM UEFA UKRAYNA ULAŞIM ULUSLARARASI İLİŞKİLER ÜMİT ÖZDAĞ ÜNİVERSİTE VLADİMİR PUTİN YANGIN YARGI YAŞAM YATIRIM YEMEK TARİFİ YEREL YÖNETİM Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır 11 Eylül 2026 21:26 Güncel Haberler Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır. Bizler üreten Türkiye'yi, Saadet Partimizin iktidarında Türkiye Kalkınma Planı ile yeniden inşa edeceğiz." Kaynak: ANKA / Güncel Mahmut Arıkan , Kayseri , Ekonomi , Güncel , Sp , İflas , Kayseri , Mahmut Arıkan , Sp , Ekonomi , Güncel , Haberler AK PARTİ AVRUPA BİRLİĞİ AZERBAYCAN BASKETBOL BELEDİYE BEŞİKTAŞ CHP ÇEVRE DEM DİPLOMASİ DOĞA DONALD TRUMP DEVLET BAHÇELİ EĞİTİM EKREM İMAMOĞLU ELON MUSK EMEKLİ EMLAK ENERJİ ENFLASYON ESNAF FENERBAHÇE FİKSTÜR FİLİSTİN FUTBOL GALATASARAY GASTRONOMİ GAZZE GÜNCEL GÜVENLİK GÖÇMEN HAKAN FİDAN HASTANE HAYVAN HAKLARI HIRSIZLIK HUKUK IRAK İNSAN HAKLARI İRAN İSRAİL İSTANBUL İŞÇİ İTFAİYE JANDARMA JOSE MOURINHO KAZA KRİPTO KÜLTÜR SANAT MAÇ SONUÇLARI MAHKEME MEDYA MHP MOTOSİKLET MÜZİK NARKOTİK OKAN BURUK OPERASYON ORTA DOĞU OTOMOBİL ÖĞRETMEN ÖZGÜR ÖZEL POLİS PUAN DURUMU RECEP TAYYİP ERDOĞAN RUSYA SAĞLIK SANAT SAVAŞ SAVUNMA SİVİL TOPLUM SUÇ SÜPER LİG SURİYE TARIM TBMM TERÖR TRABZONSPOR TRAFİK TURİZM UEFA UKRAYNA ULAŞIM ULUSLARARASI İLİŞKİLER ÜMİT ÖZDAĞ ÜNİVERSİTE VLADİMİR PUTİN YANGIN YARGI YAŞAM YATIRIM YEMEK TARİFİ YEREL YÖNETİM Mahmut Arıkan: Bir ülke fabrikalarını kaybediyorsa iflas eden uygulanan ekonomi politikasıdır Saadet Partisi Genel Başkanı Mahmut Arıkan, Kayseri'de 1953 yılından bu yana faaliyet gösteren Orta Anadolu Mensucat'ın üretimini sonlandırmasına ilişkin, "Bir ülke fabrikalarını ve üreticisini kaybediyorsa, iflas eden yalnızca şirketler değil; uygulanan ekonomi politikasıdır.</t>
+          <t>Ege Gıda Meşrubat, konkordato süreci başlattı Ege Gıda Meşrubat, konkordato süreci başlattı egealternatif.com Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi, Edirne 2’nci Asliye Hukuk Mahkemesi tarafından konkordato ilan etti ve 3 aylık geçici mühlet aldı.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -5398,37 +5555,57 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.haberler.com/amp/mahmut-arikan-bir-ulke-fabrikalarini-kaybediyorsa-20229804-haberi/</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Kayseri</t>
-        </is>
-      </c>
+          <t>https://www.egealternatif.com/haber/ege-gida-mesrubat-konkordato-sureci-baslatti_92480/</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>Ege Gıda:292:body+summary+title | Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi:raw_legal</t>
+        </is>
+      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr"/>
-      <c r="V33" s="2" t="inlineStr"/>
-      <c r="W33" s="2" t="inlineStr"/>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi Türkiye</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Ege Gıda Sanayi ve Ticaret Limited Şirketi | EGE EXPORT GIDA SANAYİ VE TİCARET LİMİTED ṢİRKETİ | EGE GRUP GIDA DIS TICARET ANONIM SIRKETI | Ege Gıda Meşrubat San</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Ege Gıda Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>100.0 | 67.3076923076923 | 75.0 | 100</t>
+        </is>
+      </c>
       <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" s="2" t="n">
-        <v>103</v>
+        <v>156.8</v>
       </c>
       <c r="AB33" s="2" t="n">
         <v>32</v>
@@ -5437,12 +5614,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:22:00</t>
+          <t>2026-09-13 10:08:44</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>tasfiye</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5452,12 +5629,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de inşaat şirketinin iflası sonrası alacaklıların durumu belirlendi</t>
+          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de inşaat şirketinin iflası sonrası alacaklıların durumu belirlendi Ege Alternatif</t>
+          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek enerjifm.com.tr</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5467,22 +5644,18 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>inşaat, şirket</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>enerji</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de 35 yıllık bir inşaat şirketinin iflası sonrası alacaklıların durumları belirlendi. İflas masasına başvuranların kayıtları askıya alındı ve itiraz süreleri açıklandı. İzmir'de 35 yıllık bir inşaat şirketinin iflası sonrası alacaklıların durumları belirlendi. İflas masasına başvuranların kayıtları askıya alındı ve itiraz süreleri açıklandı. İzmir'de 35 yıllık bir inşaat şirketinin iflası sonrası alacaklıların durumları belirlendi. İflas masasına başvuranların kayıtları askıya alındı ve itiraz süreleri açıklandı.</t>
+          <t>2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. Resmi Gazete'de yayımlanan "2027-2029 Dönemi Bütçe Çağrısı" ile ka 2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. Resmi Gazete'de yayımlanan "2027-2029 Dönemi Bütçe Çağrısı" ile ka 2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. Resmi Gazete'de yayımlanan "2027-2029 Dönemi Bütçe Çağrısı" ile kamu idarelerinin yeni dönem bütçe çalışmalarında izleyeceği...Devamı için tıklayınız Şarkı İsteği Gönder DJ'e şarkı isteğinizi iletin İsteğiniz Alındı! DJ en kısa sürede isteğinizi değerlendirecektir. Kapat CANLI Yükleniyor... Enerji FM 100.5 Alemin En kral Radyosu Dinle Kamuda ihtiyaç fazlası araçlar tasfiye edilecek İçerikle ilgili telif hakkı ihlali veya başka bir itirazınız varsa aşağıdaki formu doldurun. En kısa sürede değerlendirip gerekli işlemi yapacağız. DJ'e şarkı isteğinizi iletin DJ en kısa sürede isteğinizi değerlendirecektir.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de inşaat şirketinin iflası sonrası alacaklıların durumu belirlendi İzmir'de inşaat şirketinin iflası sonrası alacaklıların durumu belirlendi Ege Alternatif İzmir'de 35 yıllık bir inşaat şirketinin iflası sonrası alacaklıların durumları belirlendi. İflas masasına başvuranların kayıtları askıya alındı ve itiraz süreleri açıklandı.</t>
+          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek Kamuda ihtiyaç fazlası araçlar tasfiye edilecek enerjifm.com.tr 2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. Resmi Gazete'de yayımlanan "2027-2029 Dönemi Bütçe Çağrısı" ile ka 2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. DJ en kısa sürede isteğinizi değerlendirecektir. Enerji FM 100.5 Alemin En kral Radyosu Dinle Kamuda ihtiyaç fazlası araçlar tasfiye edilecek İçerikle ilgili telif hakkı ihlali veya başka bir itirazınız varsa aşağıdaki formu doldurun. En kısa sürede değerlendirip gerekli işlemi yapacağız. DJ'e şarkı isteğinizi iletin DJ en kısa sürede isteğinizi değerlendirecektir.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -5492,14 +5665,10 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.egealternatif.com/haber/izmir-de-insaat-sirketinin-iflasi-sonrasi-alacaklilarin-durumu-belirlendi_92375/</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+          <t>https://enerjifm.com.tr/haber/23335/kamuda-ihtiyac-fazlasi-araclar-tasfiye-edilecek</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
@@ -5508,7 +5677,7 @@
       <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr"/>
@@ -5522,7 +5691,7 @@
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="n">
-        <v>89.73999999999999</v>
+        <v>57</v>
       </c>
       <c r="AB34" s="2" t="n">
         <v>33</v>
@@ -5531,27 +5700,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 05:13:00</t>
+          <t>2026-09-12 17:51:00</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Almanya'da şirket iflasları patladı</t>
+          <t>Fabrika yangınına müdahale sürüyor</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Almanya'da şirket iflasları patladı Yeni Mesaj</t>
+          <t>Fabrika yangınına müdahale sürüyor Güneydoğu Ekspres</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -5561,22 +5730,22 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Almanya'da kurumsal iflaslar, ekonomideki toparlanma sinyallerine rağmen yılın ilk yarısında son 13 yılın en yüksek seviyesine ulaştı. Almanya Federal İstatistik Ofisi (Destatis), Haziran ayına ve yılın ilk yarısına ilişkin resmi iflas başvurusu verilerini açıkladı. Almanya'da kurumsal iflaslar, ekonomideki toparlanma sinyallerine rağmen yılın ilk yarısında son 13 yılın en yüksek seviyesine ulaştı. Almanya Federal İstatistik Ofisi (Destatis), Haziran ayına ve yılın ilk yarısına ilişkin resmi iflas başvurusu verilerini açıkladı. Almanya'da kurumsal iflaslar, ekonomideki toparlanma sinyallerine rağmen yılın ilk yarısında son 13 yılın en yüksek seviyesine ulaştı. Almanya Federal İstatistik Ofisi (Destatis), Haziran ayına ve yılın ilk yarısına ilişkin resmi iflas başvurusu verilerini açıkladı. Almanya'da kurumsal iflaslar, ekonomideki toparlanma sinyallerine rağmen yılın ilk yarısında son 13 yılın en yüksek seviyesine ulaştı. Almanya Federal İstatistik Ofisi (Destatis), Haziran ayına ve yılın ilk yarısına ilişkin resmi iflas başvurusu verilerini açıkladı. Buna göre, ülkede bu yılın ilk yarısında 12 bin 812 işletme iflas başvurusunda bulundu. Kurumsal iflaslar, 2025'in aynı dönemine kıyasla yüzde 6.7 arttı. Söz konusu miktar, 13 bin 253 iflasın kaydedildiği 2013'ten bu yana ilk yarıyıllar bazında görülen en yüksek seviye olarak kayıtlara geçti. Uzmanlar, uzun süredir durgun seyreden iç konjonktürü, enerji ve iş gücü maliyetlerindeki artışı ve yoğun bürokrasiyi iflas dalgasının temel nedenleri olarak gösteriyor. Sadece Haziran ayında kurumsal iflas başvuruları, geçen yılın aynı ayına göre yüzde 15.8 artarak 2 bin 266'ya ulaştı ve son 14 yılın en yüksek Haziran ayı seviyesini gördü. Yeni eğitimin öğretim döneminin başlamasından önce açıklamalar yapan Palandöken, "İlk, orta ve lisede yaklaşık 18 milyon öğrenci eğitim görüyor. Dolayısıyla 1 milyon 200 binin üzerinde öğretmenimiz var. Ülkemizde yaklaşık 75 bini aşkın okulumuz var. Yeni eğitim öğretim yılında 30 bine yakın güvenlik görevlisi görev yapacak. Dolayısıyla biz aileleri, başta tabii ki çevredeki esnafları uyararak öğrencilerimizi, kötü alışkanlıklardan uzak tutmak için gerekli tedbirleri almalarını istiyoruz. Bununla birlikte ailelerin de eğitim döneminde çocukların okul aile birlikleriyle ve öğretmenleriyle temasını geliştirmesi lazım" dedi. "Okul çevrelerinde kötü alışkanlıklara karşı tedbir alınmalı" Okul çevrelerinin güvenliği konusunda uyarılarda bulunan Türkiye Esnaf ve Sanatkarları Konfederasyonu (TESK) Genel Başkanı Bendevi Palandöken, "Korsan satıcıların veya illegal örgütlerin ürünlerini satan, bağımlılık kazandıran içeriklerden uzak tutulması lazım. En önemlisi çocuklarımızı kontrol etmemiz. Bunların geleceğini daha güvenli, daha emin, gözümüz gibi koruduğumuz; sınıflara yeni başlayandan liseyi bitirip üniversiteye gidinceye kadarki ebeveynlik görevlerimizi de harfiyen yerine getirmemiz lazım. Gidiş geliş saatleri başta olmak üzere, çevresindeki arkadaşları, okuldaki hareketleri mercek altında olması lazım. Hem çevredeki esnaflarımızla birlikte hem de servis araçlarımızla, onların bakımlarıyla güvenli bir şekilde öğrencileri indirip bindiren araçlarda bulunması gereken eğitici ablalarının, koruyucu ablalarının çok dikkatli bir şekilde; evlerinin bulunduğu caddenin, sokağın ve trafik akışını iyi hesap edip indirilip bindirilmesine de dikkat etmesi lazım" diye konuştu. "Servis şoförlerimizin yeterlilikleri ve araçların bakımı önemli" Yeni eğitim-öğretim döneminde servis şoförlerinin mesleki yeterliliklerinin ve araç bakımlarının çok önemli olduğuna işaret eden Palandöken, "İnşallah 2026-2027 öğretim yılı başarılı bir şekilde neticelenir. Kazasız belasız ve çocuklarımızın yetişmesindeki, eve geliş gidiş saatlerindeki, beslenmeleri, harcadıkları zamanların, kimlerle birlikte olduklarının da kontrol edilmesi lazım. En önemlisi kolluk kuvvetleri. Hem yerel yönetimler hem de emniyet güçlerinin çok sık takip etmesi çok önemli. Çocukları taşıyan servis araçlarının bakımlı aynı zamanda da can güvenlikleriyle ilgili bütün sorunlar halledilmiş bir vaziyette, servisleri yapılmış, okula getirip götürmelerinde ilgili Oda belgesine dayanan, sertifikaları olan şoförlerimizin bu konuda uyarılmasıyla ilgili tedbirler alındı. Bizim umudumuz inşallah bu sene çok daha dikkatli ve çok daha disiplinli bir şekilde okul hayatlarını idame ettirecek yavrularımıza hepimiz birlikte, toplum olarak da sahip çıkacağız. Onların yetişmeleri, toplumun refaha ermesi, daha iyi neticeleri alması için, hepimize gerekli olan bir uygulama olacak inşallah" ifadelerini kullandı. Tekirdağ'ın Çerkezköy ilçesine bağlı Kızılpınar Mahallesi'nde şehidin ailesinin yaşadığı evin önüne Türk bayrağı asılırken, acı haberin ardından yakınları ve vatandaşlar taziye için evin önünde bir araya geldi. Çerkezköy Kaymakamı Nazmi Günlü, Çerkezköy Tugay Komutanı Tuğgeneral Günal Budak, şehidin ailesini ziyaret ederek başsağlığı dileklerini iletti. Şehidin ailesi Yüksekova'ya uğurlanacak Çerkezköy Kaymakamı Nazmi Günlü, şehidin ailesinin isteği doğrultusunda cenaze töreninin memleketleri Hakkari Yüksekova'da gerçekleştirileceğini açıkladı. Günlü, "Iğdır'da meydana gelen askeri araç kazası neticesinde bir şehidimiz var. Şehidimizin anne ve babası ilçemizde ikamet ediyorlar. Şehit haberini aldığımız andan itibaren biz de onlarla beraber olmaya, onların acısını paylaş</t>
+          <t>Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Bolu Fabrika yangınına müdahale sürüyor Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Ali Abbas YILMAZ 12.09.2026 - 20:51 Okunma Süresi: 1 Dk Trafik ışıklarında feci kaza yaşandı İçeriği Görüntüle Bolu’nun Gerede ilçesinde organize sanayi bölgesinde faaliyet gösteren bir geri dönüşüm fabrikasında henüz belirlenemeyen nedenle yangın çıktı. Haber verilmesi üzerine bölgeye itfaiye ekipleri sevk edildi. Yangın nedeniyle bölgede yoğun duman oluşurken, fabrikadan patlama sesleri duyuluyor. Ekiplerin yangını söndürme çalışmaları sürüyor. Kaynak: MA Editörün Seçtiği Sabahattin Ali’nin öyküleri Kürtçeye çevrildi Editörün Seçtiği Köyden kente geliyor, sabah saatlerinde tükeniyor Editörün Seçtiği Gastronomi araştırmacısı Mehmet Kudat: Diyarbakır tandır kültür yeniden canlandırılmalı Editör Hakkında Ali Abbas YILMAZ B</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Almanya'da şirket iflasları patladı Almanya'da şirket iflasları patladı Yeni Mesaj Almanya'da kurumsal iflaslar, ekonomideki toparlanma sinyallerine rağmen yılın ilk yarısında son 13 yılın en yüksek seviyesine ulaştı. Almanya Federal İstatistik Ofisi (Destatis), Haziran ayına ve yılın ilk yarısına ilişkin resmi iflas başvurusu verilerini açıkladı. Buna göre, ülkede bu yılın ilk yarısında 12 bin 812 işletme iflas başvurusunda bulundu. Kurumsal iflaslar, 2025'in aynı dönemine kıyasla yüzde 6.7 arttı. Söz konusu miktar, 13 bin 253 iflasın kaydedildiği 2013'ten bu yana ilk yarıyıllar bazında görülen en yüksek seviye olarak kayıtlara geçti. Uzmanlar, uzun süredir durgun seyreden iç konjonktürü, enerji ve iş gücü maliyetlerindeki artışı ve yoğun bürokrasiyi iflas dalgasının temel nedenleri olarak gösteriyor. Sadece Haziran ayında kurumsal iflas başvuruları, geçen yılın aynı ayına göre yüzde 15.8 artarak 2 bin 266'ya ulaştı ve son 14 yılın en yüksek Haziran ayı seviyesini gördü. Yeni eğitimin öğretim döneminin başlamasından önce açıklamalar yapan Palandöken, "İlk, orta ve lisede yaklaşık 18 milyon öğrenci eğitim görüyor. Ülkemizde yaklaşık 75 bini aşkın okulumuz var. Dolayısıyla biz aileleri, başta tabii ki çevredeki esnafları uyararak öğrencilerimizi, kötü alışkanlıklardan uzak tutmak için gerekli tedbirleri almalarını istiyoruz. Bununla birlikte ailelerin de eğitim döneminde çocukların okul aile birlikleriyle ve öğretmenleriyle temasını geliştirmesi lazım" dedi. "Okul çevrelerinde kötü alışkanlıklara karşı tedbir alınmalı" Okul çevrelerinin güvenliği konusunda uyarılarda bulunan Türkiye Esnaf ve Sanatkarları Konfederasyonu (TESK) Genel Başkanı Bendevi Palandöken, "Korsan satıcıların veya illegal örgütlerin ürünlerini satan, bağımlılık kazandıran içeriklerden uzak tutulması lazım. Bunların geleceğini daha güvenli, daha emin, gözümüz gibi koruduğumuz; sınıflara yeni başlayandan liseyi bitirip üniversiteye gidinceye kadarki ebeveynlik görevlerimizi de harfiyen yerine getirmemiz lazım. Gidiş geliş saatleri başta olmak üzere, çevresindeki arkadaşları, okuldaki hareketleri mercek altında olması lazım. Hem çevredeki esnaflarımızla birlikte hem de servis araçlarımızla, onların bakımlarıyla güvenli bir şekilde öğrencileri indirip bindiren araçlarda bulunması gereken eğitici ablalarının, koruyucu ablalarının çok dikkatli bir şekilde; evlerinin bulunduğu caddenin, sokağın ve trafik akışını iyi hesap edip indirilip bindirilmesine de dikkat etmesi lazım" diye konuştu. "Servis şoförlerimizin yeterlilikleri ve araçların bakımı önemli" Yeni eğitim-öğretim döneminde servis şoförlerinin mesleki yeterliliklerinin ve araç bakımlarının çok önemli olduğuna işaret eden Palandöken, "İnşallah 2026-2027 öğretim yılı başarılı bir şekilde neticelenir. Kazasız belasız ve çocuklarımızın yetişmesindeki, eve geliş gidiş saatlerindeki, beslenmeleri, harcadıkları zamanların, kimlerle birlikte olduklarının da kontrol edilmesi lazım. Çocukları taşıyan servis araçlarının bakımlı aynı zamanda da can güvenlikleriyle ilgili bütün sorunlar halledilmiş bir vaziyette, servisleri yapılmış, okula getirip götürmelerinde ilgili Oda belgesine dayanan, sertifikaları olan şoförlerimizin bu konuda uyarılmasıyla ilgili tedbirler alındı. Bizim umudumuz inşallah bu sene çok daha dikkatli ve çok daha disiplinli bir şekilde okul hayatlarını idame ettirecek yavrularımıza hepimiz birlikte, toplum olarak da sahip çıkacağız. Onların yetişmeleri, toplumun refaha ermesi, daha iyi neticeleri alması için, hepimize gerekli olan bir uygulama olacak inşallah" ifadelerini kullandı. Tekirdağ'ın Çerkezköy ilçesine bağlı Kızılpınar Mahallesi'nde şehidin ailesinin yaşadığı evin önüne Türk bayrağı asılırken, acı haberin ardından yakınları ve vatandaşlar taziye için evin önünde bir araya geldi. Çerkezköy Kaymakamı Nazmi Günlü, Çerkezköy Tugay Komutanı Tuğgeneral Günal Budak, şehidin ailesini ziyaret ederek başsağlığı dileklerini iletti. Günlü, "Iğdır'da meydana gelen askeri araç kazası neticesinde bir şehidimiz var. Şehidimizin anne ve babası ilçemizde ikamet ediyorlar.</t>
+          <t>Fabrika yangınına müdahale sürüyor Fabrika yangınına müdahale sürüyor Güneydoğu Ekspres Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Bolu Fabrika yangınına müdahale sürüyor Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5586,24 +5755,20 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.yenimesaj.com.tr/almanyada-sirket-iflaslari-patladi-H1616544.htm</t>
+          <t>https://www.guneydoguekspres.com/fabrika-yanginina-mudahale-suruyor-1</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Iğdır | Tekirdağ</t>
+          <t>Bolu</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Çerkezköy</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Çerkezköy ilçesine bağlı Kızılpınar Mahallesi</t>
-        </is>
-      </c>
+          <t>Gerede</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr"/>
@@ -5624,7 +5789,7 @@
       <c r="Y35" s="2" t="inlineStr"/>
       <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" s="2" t="n">
-        <v>102</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>34</v>
@@ -5633,27 +5798,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 21:29:00</t>
+          <t>2026-09-12 18:58:00</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Barnes Worldwide Travel Ltd, iflasını açıkladı ve rezervasyon sahiplerine uyarıda bulundu</t>
+          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Barnes Worldwide Travel Ltd, iflasını açıkladı ve rezervasyon sahiplerine uyarıda bulundu Ege Alternatif</t>
+          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Zonguldak Pusula Son Dakika Haberleri</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5663,18 +5828,22 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>ltd</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Barnes Worldwide Travel Ltd, İngiltere'de iflas ettiğini duyurdu. Rezervasyon sahiplerine, tatil planlarının iptal edilmemesi için dikkat etmeleri gereken adımlar hatırlatıldı. Barnes Worldwide Travel Ltd, İngiltere'de iflas ettiğini duyurdu. Rezervasyon sahiplerine, tatil planlarının iptal edilmemesi için dikkat etmeleri gereken adımlar hatırlatıldı. Barnes Worldwide Travel Ltd, İngiltere'de iflas ettiğini duyurdu. Rezervasyon sahiplerine, tatil planlarının iptal edilmemesi için dikkat etmeleri gereken adımlar hatırlatıldı.</t>
+          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Barnes Worldwide Travel Ltd, iflasını açıkladı ve rezervasyon sahiplerine uyarıda bulundu Barnes Worldwide Travel Ltd, iflasını açıkladı ve rezervasyon sahiplerine uyarıda bulundu Ege Alternatif Barnes Worldwide Travel Ltd, İngiltere'de iflas ettiğini duyurdu. Rezervasyon sahiplerine, tatil planlarının iptal edilmemesi için dikkat etmeleri gereken adımlar hatırlatıldı.</t>
+          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Zonguldak Pusula Son Dakika Haberleri Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -5684,10 +5853,14 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.egealternatif.com/haber/barnes-worldwide-travel-ltd-iflasini-acikladi-ve-rezervasyon-sahiplerine-uyarida-bulundu_92308/</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>https://www.pusulagazetesi.com.tr/fabrika-yangininda-yaklasik-4-saat-geride-kaldi-1-yarali</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
@@ -5696,7 +5869,7 @@
       <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr"/>
@@ -5710,7 +5883,7 @@
       <c r="Y36" s="2" t="inlineStr"/>
       <c r="Z36" s="2" t="inlineStr"/>
       <c r="AA36" s="2" t="n">
-        <v>91.8</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="AB36" s="2" t="n">
         <v>35</v>
@@ -5719,27 +5892,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 17:23:54</t>
+          <t>2026-09-12 17:37:21</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>usulsüzlük</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>İzmir’in tarihi simgelerinden Konak Pier'i işleten şirket iflas etti haberi</t>
+          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>İzmir’in tarihi simgelerinden Konak Pier'i işleten şirket iflas etti haberi Finans Gündem</t>
+          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Bursa Saati</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5749,48 +5922,60 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>imalat, imalathane</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>üretim tesisi</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>İzmir’in tarihi simgelerinden Konak Pier'i işleten şirket iflas etti haberi Finans Gündem</t>
+          <t>Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Asayiş Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. 12.09.2026 - 20:37 12.09.2026 - 20:37 Loading... Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Edinilen bilgiye göre, ilçeye bağlı Sanayi Mahallesi Osman Kavuncu Bulvarı üzerinde bulunan bir avize imalathanesinin çatısında henüz bilinmeyen bir sebeple yangın çıktı. İhbar üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin müdahalesiyle yangın söndürülürken, iş yerinin çatısında hasar meydana geldi. Olayla ilgili soruşturma başlatıldı. B</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>İzmir’in tarihi simgelerinden Konak Pier'i işleten şirket iflas etti haberi İzmir’in tarihi simgelerinden Konak Pier'i işleten şirket iflas etti haberi Finans Gündem İzmir’in tarihi simgelerinden Konak Pier'i işleten şirket iflas etti haberi Finans Gündem</t>
+          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Bursa Saati Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Asayiş Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. 12.09.2026 - 20:37 12.09.2026 - 20:37 Loading... Edinilen bilgiye göre, ilçeye bağlı Sanayi Mahallesi Osman Kavuncu Bulvarı üzerinde bulunan bir avize imalathanesinin çatısında henüz bilinmeyen bir sebeple yangın çıktı. İhbar üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin müdahalesiyle yangın söndürülürken, iş yerinin çatısında hasar meydana geldi. Olayla ilgili soruşturma başlatıldı.</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxORVpEYk1nVlBJa09FZC1NM2h3N2Q3bEZQZFJlLWY3MFRNQjdldXlkQ3Q1Tjg4M1cyVU5lSWF6cnhuMGhtLVdWbGs4MW41REJzTDJJTl93Y1ZnWlgzWVpuQXZhTDB5R2ZnWXJqSV9YbXh0RUNKRkJaV0JVMENzMjcyWE52aEpabFVtUFdkel9Dd3ZMVy1mNFNQUXl1Vnc2UlE4SU5TUGdxUUY5WWJ4ZWd0a1Fn?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.bursasaati.com.tr/kayseride-avize-imalathanesinin-catisinda-cikan-yangin-sonduruldu/amp</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>İzmir</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
+          <t>Kayseri</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Kocasinan</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>ilçeye bağlı Sanayi Mahallesi</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Sanayi Mahallesi Osman Kavuncu Bulvarı</t>
+        </is>
+      </c>
       <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr"/>
@@ -5804,7 +5989,7 @@
       <c r="Y37" s="2" t="inlineStr"/>
       <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="n">
-        <v>76.64</v>
+        <v>134.72</v>
       </c>
       <c r="AB37" s="2" t="n">
         <v>36</v>
@@ -5813,27 +5998,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:22:58</t>
+          <t>2026-09-12 19:04:58</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>yolsuzluk</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>İzmirli 35 yıllık inşaat şirketinin iflas sürecinde yeni aşama</t>
+          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>İzmirli 35 yıllık inşaat şirketinin iflas sürecinde yeni aşama bolgegundemi.com</t>
+          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -5843,22 +6028,18 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>inşaat, şirket</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>tesis</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. yangın sürüyor, söndürme çalışmaları devam ediyorBolu'nun Gerede ilçesinde bulunan Gerede Karma Organize Sanayi Bölgesi (OSB) içindeki geri dönüşüm tesisinde saat 19.00 civarında henüz belirlenemeyen nedenle yangın başladı. Kısa sürede fabrikaya yayılan alevler, ekiplerin yoğun çalışmasına rağmen yaklaşık 4 saattir kontrol… HABERİN DEVAMI Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>İzmirli 35 yıllık inşaat şirketinin iflas sürecinde yeni aşama İzmirli 35 yıllık inşaat şirketinin iflas sürecinde yeni aşama bolgegundemi.com www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Aksiyon.com.TR Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. yangın sürüyor, söndürme çalışmaları devam ediyorBolu'nun Gerede ilçesinde bulunan Gerede Karma Organize Sanayi Bölgesi (OSB) içindeki geri dönüşüm tesisinde saat 19.00 civarında henüz belirlenemeyen nedenle yangın başladı. Kısa sürede fabrikaya yayılan alevler, ekiplerin yoğun çalışmasına rağmen yaklaşık 4 saattir kontrol… HABERİN DEVAMI Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -5868,11 +6049,19 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.bolgegundemi.com/ekonomi/izmirli-35-yillik-insaat-sirketinin-iflas-surecinde-yeni-asama-175956.html</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>https://www.aksiyon.com.tr/gerede-de-geri-donusum-tesisinde-cikan-yangin-mudahale-suresini-4-saate-tasidi-353480/amp</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -5880,7 +6069,7 @@
       <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr"/>
@@ -5894,7 +6083,7 @@
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="n">
-        <v>64.20999999999999</v>
+        <v>117.63</v>
       </c>
       <c r="AB38" s="2" t="n">
         <v>37</v>
@@ -5903,27 +6092,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:43:33</t>
+          <t>2026-09-13 14:39:00</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>İzmirli inşaat devi İzmer iflas etti, Konak Pier masada</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı!</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>İzmirli inşaat devi İzmer iflas etti, Konak Pier masada İş'te Gündem</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5933,28 +6122,28 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>inşaat</t>
+          <t>turizm</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>İzmirli inşaat devi İzmer iflas etti, Konak Pier masada İş'te Gündem</t>
+          <t>Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. VİB Turizm'den dolandırıcılık uyarısı! Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Haber Merkezi Editör 13.09.2026 - 17:39 Yayınlanma — P</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>İzmirli inşaat devi İzmer iflas etti, Konak Pier masada İzmirli inşaat devi İzmer iflas etti, Konak Pier masada İş'te Gündem İzmirli inşaat devi İzmer iflas etti, Konak Pier masada İş'te Gündem</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı! VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. VİB Turizm'den dolandırıcılık uyarısı!</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNSXlJeUdvNUhjTk9BbGFvVUpNbUF5bm1VV1lqdTRQNW1idkpraklyNzZfZ1VSRjhaV1dNcUJoSkEtUk9SRGt4R2N1THFXcDJSZW1tZEY4R2o4WHhhYXc1SzltYmQtSjBZZDY2N3UtTFVqWmVhVlRuZUNjR1R5QlhDM1ZhUFZrR3dHQTdnU0lDSnhKOFJPVkQxRzRn?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.bizimsakarya.com.tr/vib-turizmden-dolandiricilik-uyarisi</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
@@ -5980,7 +6169,7 @@
       <c r="Y39" s="2" t="inlineStr"/>
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="n">
-        <v>53.18</v>
+        <v>54.14</v>
       </c>
       <c r="AB39" s="2" t="n">
         <v>38</v>
@@ -5989,27 +6178,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:53:00</t>
+          <t>2026-09-13 00:03:35</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>usulsüzlük</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Hakkari’de ihale usulsüzlüğü ortaya çıktı! 7 şüpheli tutuklandı, hesaplara el konuldu</t>
+          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Hakkari’de ihale usulsüzlüğü ortaya çıktı! 7 şüpheli tutuklandı, hesaplara el konuldu Türkgün</t>
+          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -6019,35 +6208,31 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
+          <t>enerji</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>www.turkgun.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.turkgun.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.turkgun.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Hakkari’de ihale usulsüzlüğü ortaya çıktı! 7 şüpheli tutuklandı, hesaplara el konuldu Hakkari’de ihale usulsüzlüğü ortaya çıktı! 7 şüpheli tutuklandı, hesaplara el konuldu Türkgün www.turkgun.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.turkgun.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.turkgun.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://www.turkgun.com/gundem/hakkaride-ihale-usulsuzlugu-ortaya-cikti-7-supheli-tutuklandi-hesaplara-el-konuldu/398941</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Hakkari</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOa0FHZTR5WWlLWURTM3dxOVl2T1pPNTJVWGRscEloTnBweGxJZDdzNXlqX09SUUdiTnRlMTZHUkV1UkNiZ1R0MFV0Wm1Dd3k0Q2x4VmFhOHdTRWxhNEx1STV6eXNKaTdNRjVzSDVOTlFza2N1ZEs2RjkyRk5MYlc4Tk5aWDVKOGtRem5yVjNlQy1zVUJ0d2twZjhZQmQ2VHhPT3JoT1BULS1kTkR2czdWT3Q2ei1FNjlBYzVlUmNCZUQyY0ZPZVJn?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
@@ -6056,7 +6241,7 @@
       <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr"/>
@@ -6070,7 +6255,7 @@
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="n">
-        <v>87.06</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AB40" s="2" t="n">
         <v>39</v>
@@ -6079,27 +6264,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 14:16:21</t>
+          <t>2026-09-13 10:10:48</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>bankaya soruşturma</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Kayseri Kocasinan'da avize imalathanesinin çatısında çıkan yangın söndürüldü</t>
+          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Kayseri Kocasinan'da avize imalathanesinin çatısında çıkan yangın söndürüldü Son Dakika</t>
+          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6109,22 +6294,22 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>imalat, imalathane</t>
+          <t>banka, banka hesabı</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>üretim tesisi</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Kayseri Kocasinan'da avize imalathanesinin çatısında çıkan yangın söndürüldü Son Dakika</t>
+          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Kayseri Kocasinan'da avize imalathanesinin çatısında çıkan yangın söndürüldü Kayseri Kocasinan'da avize imalathanesinin çatısında çıkan yangın söndürüldü Son Dakika Kayseri Kocasinan'da avize imalathanesinin çatısında çıkan yangın söndürüldü Son Dakika</t>
+          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -6134,19 +6319,11 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOMjI4RFJucjBlMlJXV2QzWmROaGI0SzNmbEpGWHRYZGUzVHYteUt2a1dqTWtMRHdXWWM2eGtzUDc1WU1xVG5xckIxVXRsZ1V4cUR3d2FJT2J3bFlPU19Vbmlqam1oWVBrd19GWGoyOWN3aFhFMDdwNXJqTzMxV3NPQnZyaFBHWHVnSXFaTlpFbDZxRVNFYkJxaUlIczB5Z2Ra0gGcAUFVX3lxTE1YOG5aR0E5SDh4U25RNWE3cGY5NFpPSDU3OEFxckFCbzNneXdFMldnQVhmYUo1RmpfckNxNGlBLXlaQS1pcDd4bnZJNmZ2UVdLSTBLUFBaZUhOMEpWc3hGd0ROV09lOXNzY2N5bGNVeV9wSDZzNmExb1JtNkFvSFVjVFRsclllakh4bE1Kc0g3YnF0cnRsOEpVc3RQdQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Kayseri</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>Kocasinan</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPeXNpNGNCMnJGZDc4ZFk5SWZ4Nmx0TEhETXNqc2EycnhaVGx6VWNSUWtDelJSTmRMOW5yZ3Z2RGxDYkkxeUdiTVZ4R2JSUjdId1hzak50cklfdkxTVS1tTVVxN1Zaakl0dWRmcElXdnBTZEVxNHQxRFRCTHpTTktjdTg5azFadm80TW1uZXNIVzg3VE9KNzg4NHFpdGlaN215c2w4eWdyVVprMG9DZmQySnBR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr"/>
@@ -6154,7 +6331,7 @@
       <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr"/>
@@ -6168,7 +6345,7 @@
       <c r="Y41" s="2" t="inlineStr"/>
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="n">
-        <v>104.62</v>
+        <v>65.88</v>
       </c>
       <c r="AB41" s="2" t="n">
         <v>40</v>
@@ -6177,12 +6354,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 09:29:36</t>
+          <t>2026-09-13 10:52:00</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>banka hesabına bloke</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -6192,12 +6369,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Müşteri kılığında bankaya girdi! Çalışanların yüzüne biber atıp paralarla kaçtı</t>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama!</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Müşteri kılığında bankaya girdi! Çalışanların yüzüne biber atıp paralarla kaçtı Halk TV</t>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6217,12 +6394,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Hindistan’da bir bankaya müşteri gibi giren 28 yaşındaki Suraj Borkar, çalışanların yüzüne biber tozu atıp 4 bin 200 dolarla kaçtı. Ancak banka çalışanlarının başlattığı kovalamacaya polis de katılınca şüpheli yaklaşık 30 dakika içinde yakalandı. Hindistan’da bir bankaya müşteri gibi giren 28 yaşındaki Suraj Borkar, çalışanların yüzüne biber tozu atıp 4 bin 200 dolarla kaçtı. Ancak banka çalışanlarının başlattığı kovalamacaya polis de katılınca şüpheli yaklaşık 30 dakika içinde yakalandı. Hindistan’da bir bankaya müşteri gibi giren 28 yaşındaki Suraj Borkar, çalışanların yüzüne biber tozu atıp 4 bin 200 dolarla kaçtı. Ancak banka çalışanlarının başlattığı kovalamacaya polis de katılınca şüpheli yaklaşık 30 dakika içinde yakalandı.</t>
+          <t>Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Emekli Maaşlarına Ek Zam: Seyyanen Zam İçin Gözler Kritik Kararda! İçeriği Görüntüle Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Vatandaşların hukuki süreçlerde en sık karşılaştığı ve kafa karışıklığı yaşadığı konuların başında, maaşın işveren tarafından bankaya yatırılmasından sonraki hukuki statüsü gelmektedir. Maaş kesintisi doğrudan işyeri üzerinden icra dairesi kanalıyla yapılırken, banka hesaplarına uygulanan e-haciz işlemleri Doğrudan banka blokajı olarak gerçekleşmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Bu durum, banka hesabında bloke bulunan vatandaşların işlem türünü doğru tespit etmesini zorunlu kılmaktadır. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. Uygulanan işlemin bir maaş haczi mi yoksa banka mevduat haczi mi olduğunun icra dosyasından doğrulanması gerekmektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Akseki Aksu Alanya Demre Döşemealtı Elmalı Finike Gazipaşa Gündoğmuş İbradı Kaş Kemer Kepez Konyaaltı Korkuteli Kumluca Manavgat Muratpaşa Serik 30 ° C Web sitemizden ayrılıyorsunuz Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor. Sayfada Kal Devam Et Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. Vatandaşların hukuki süreçlerde en sık karşılaştığı ve kafa karışıklığı yaşadığı konuların başında, maaşın işveren tarafından bankaya yatırılmasından sonraki hukuki statüsü gelmektedir. Maaş kesintisi doğrudan işyeri üzerinden icra dairesi kanalıyla yapılırken, banka hesaplarına uygulanan e-haciz işlemleri Doğrudan banka blokajı olarak gerçekleşmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Bu durum, banka hesabında bloke bulunan vatandaşların işlem türünü doğru tespit etmesini zorunlu kılmaktadır. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. Uygulanan işlemin bir maaş haczi mi yoksa banka mevduat haczi mi olduğunun icra dosyasından doğrulanması gerekmektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Antalya Hakkında'nın sponsor olduğu yayıncılar Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Müşteri kılığında bankaya girdi! Çalışanların yüzüne biber atıp paralarla kaçtı Müşteri kılığında bankaya girdi! Çalışanların yüzüne biber atıp paralarla kaçtı Halk TV Hindistan’da bir bankaya müşteri gibi giren 28 yaşındaki Suraj Borkar, çalışanların yüzüne biber tozu atıp 4 bin 200 dolarla kaçtı. Ancak banka çalışanlarının başlattığı kovalamacaya polis de katılınca şüpheli yaklaşık 30 dakika içinde yakalandı.</t>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Emekli Maaşlarına Ek Zam: Seyyanen Zam İçin Gözler Kritik Kararda! İçeriği Görüntüle Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Akseki Aksu Alanya Demre Döşemealtı Elmalı Finike Gazipaşa Gündoğmuş İbradı Kaş Kemer Kepez Konyaaltı Korkuteli Kumluca Manavgat Muratpaşa Serik 30 ° C Web sitemizden ayrılıyorsunuz Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor. Sayfada Kal Devam Et Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Antalya Hakkında'nın sponsor olduğu yayıncılar Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -6232,7 +6409,7 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://halktv.com.tr/dunya/musteri-kiliginda-bankaya-girdi-calisanlarin-yuzune-biber-atip-paralarla-kacti-1054613h</t>
+          <t>https://www.antalyahakkinda.com/maasiniz-hesaba-yatinca-bu-para-kesilecek-bankalardan-kritik-uygulama</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr"/>
@@ -6258,7 +6435,7 @@
       <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr"/>
       <c r="AA42" s="2" t="n">
-        <v>74.65000000000001</v>
+        <v>79.25</v>
       </c>
       <c r="AB42" s="2" t="n">
         <v>41</v>
@@ -6267,12 +6444,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 18:01:00</t>
+          <t>2026-09-13 06:39:00</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>şüpheli işlem</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -6282,12 +6459,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>İzmir Hatay’da silahlı soygun: Bankadakiler rehin alındı! Başsavcılık'tan açıklama</t>
+          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>İzmir Hatay’da silahlı soygun: Bankadakiler rehin alındı! Başsavcılık'tan açıklama gazeteyenigun.com.tr</t>
+          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -6297,22 +6474,18 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>finansal kuruluş</t>
-        </is>
-      </c>
+          <t>şüpheli işlem</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>İzmir Hatay’da silahlı soygun: Bankadakiler rehin alındı! Başsavcılık'tan açıklama gazeteyenigun.com.tr</t>
+          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>İzmir Hatay’da silahlı soygun: Bankadakiler rehin alındı! Başsavcılık'tan açıklama İzmir Hatay’da silahlı soygun: Bankadakiler rehin alındı! Başsavcılık'tan açıklama gazeteyenigun.com.tr İzmir Hatay’da silahlı soygun: Bankadakiler rehin alındı! Başsavcılık'tan açıklama gazeteyenigun.com.tr</t>
+          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -6322,14 +6495,10 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxPUGNfMUtZaW5hNENXVlU3elVhc2hxeEROcHVxZmZMXzNSTWtQVmJXdERkbWh3S1dxakFnRldrSzViTVd5YUhpTHJGRHozS1ZUUlpvUnF2aVNDSTN2Wm5OaXdSalNXMHhFcHJtVF9BZm9SMDJIVWJHeC0xOEJ0d3FEYUNRZGxYaHdpOU9rOHctNmFuR0RaRkwwSGtkVHpPb2lBcS12RXQwSXhuc3dKajVqQ0FwQjZxWGZKZWFwVHR1Q0lPa0Vn0gHKAUFVX3lxTE55cUFjWHpDVmNHQlotWkpNRTM5Zlg5RXRzNGMyN2dnYXZqblB6aENobFp6d2ZnUFphS1g0OVM0T3RuT29ESGNaUjB5aVFkeFMyejlZNE11X2JOWFN5RWh1bXh5WDE5Z2p5dkxYeWlxbEJEY1ZHQjBZMGtBVEV2TGhLZjhjZWpHMVp4NUVndTgyN1Y2eGlLU0ZnX3MxLWxxQUxla2ZfSTdSMWdYdHE5RzdaWVpCU1V4XzZsMjNGR0I2TkhpcFZjZGJNblE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Hatay</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOXzhXNnZwbnFrUHFHNnZac2ZnMmZoUXNLYnJnVkN5SlczZmZKeEQ4cEZNTEVhQjFrYUl5TF9YMDRyaWY4SkhFaWpTNlplWnJKZVFNOVJxcUxTdXRibVpqMnR5QjRyNWRxOVJaZ2Y1end0d3EyeVJtYksyOG00b2F1cVBPMmNTeVJMNjgtUG5aSGFYa3U3TUxVaVZsb0RJSUVVZTFxT2pCNDZETUxWTmktUHJoMERFdVBSNzNjV3ZDRG0yUdIBxwFBVV95cUxObmxnU2JUTWwyZ0I4Mm1oTEc2cDBaZGREUW5LcHMxVG0tOW13OGhjTm1KOTFBLWsxUm1TNEtnWmhOX0VpMHd0SkNJMjhaVzlka2tFeHBBRHlaeEQ1cDVUbE9RcVNoWlZpQWxzQlJBajFrWG1GZC01WDJvaDNLMWVDb0xSRTFRV0RocmJ1cldmWlhrQ3ZiZUpzZGoyQW9tNmpLOEtuWmpGOXNuMENUdG1iSjBqVWZnLUEwY3g4cXhIek43dDFkTlo4?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
@@ -6338,7 +6507,7 @@
       <c r="S43" s="2" t="inlineStr"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr"/>
@@ -6352,7 +6521,7 @@
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="n">
-        <v>83.78</v>
+        <v>82.98</v>
       </c>
       <c r="AB43" s="2" t="n">
         <v>42</v>
@@ -6361,27 +6530,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 16:13:44</t>
+          <t>2026-09-13 04:52:14</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>soruşturma</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Banka çalışanlarını rehin almıştı; eylemi 'kız çocukları farkındalığı' için yapmış</t>
+          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Banka çalışanlarını rehin almıştı; eylemi 'kız çocukları farkındalığı' için yapmış Aliağa Medya</t>
+          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı 10haber.net</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -6391,58 +6560,90 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>holding</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Banka çalışanlarını rehin almıştı; eylemi 'kız çocukları farkındalığı' için yapmış Aliağa Medya</t>
+          <t>Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini […] Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini […] Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini bu sarsıntıya bağladı. Ancak dün ortaya çıkan ve henüz bütün boyutları bilinmeyen bir gelişme, gerçeğin farklı olabileceğini ima ediyor. Cumartesi günü İstanbul Cumhuriyet Başsavcılığı’nın Tera tarafından devralınmak üzere olan, hatta devir görüşmelerinin tamamlandığı açıklanan Pusula Holding’in en azından bazı yöneticileri ve patronları hakkında soruşturma yürüttüğü ortaya çıktı. Buna göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, Pusula Holding’in bir parçası olan KatılımEvim yönetim kurulu üyesi Serdar Turhan ve tamamen ayrı bir şirket olan Destek Yatırım’ın hakim ortağı Altunç Kumova savcılık tarafından soruşturuluyor, hatta iddiaya göre bu isimler hakkında tedbir kararları alınmış durumda. Gazeteci İsmail Saymaz’ın sosyal medyadan yazdığına göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, cep telefonunu Türkiye’de bırakarak Marmaris’ten bir tekneyle Yunanistan’a geçti. Bu gelişme sonrası Katılımevim Yönetim Kurulu üyesi Serdar Turhan ve Destek Yatırım’ın sahibi Altunç Kumova için de yurt dışı çıkış yas ağı getirildi ve tedbir uygulandı. Savcılıktan henüz bir açıklama yapılmadığı için, Pusula ile ilgili bir soruşturma olup olmadığı, varsa bunun kapsamı ve konusu hakkında pek az bilgi var. Ancak cumartesi günü çıkan bu haberler üstüne gerek Tera Holding, gerekse Pusula Holding açıklamalar yaparak devralınma sürecinin bu soruşturmadan bağımsız olarak devam ettiğini bildirdiler. Günün 10 Haberi Yok artık daha neler… 11 aylık bebeklerini satmışlar, ‘Kayboldu’ demişler Şimşek vergi denetimini anlattı: ‘Büyük ve yüksek gelirli mükellefler mercek altında’ Özgür Özel’den seçim mesajı: ‘Butlancılar ve darbeciler otokratın safında’ Yapay zeka devleri birden insafa geldi: Evet, gelişme hızımızı yavaşlatmalıyız “Kıyamet” ne kadar yakın? Dünyanın sonunu yapay zeka mı siyaset mi getirecek? Kahve erkeklerde testosteronu arttırıyormuş Bermuda Şeytan Üçgeni’nin büyük gizemi: Batık şehir izine rastlandı Nurgül Yeşilçay: Şehirde gençler yaşasın, biz değil Trabzonspor’da Burak Yılmaz iddiası: Galatasaray derbisinde takımın başında olabilir İspanya, üç yazıyla Arda Güler’i göklere çıkardı: ‘Mourinho’ya kendisini 15 dakikada hatırlattı’ Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini bu sarsıntıya bağladı. Ancak dün ortaya çıkan ve henüz bütün boyutları bilinmeyen bir gelişme, gerçeğin farklı olabileceğini ima ediyor. Cumartesi günü İstanbul Cumhuriyet Başsavcılığı’nın Tera tarafından devralınmak üzere olan, hatta devir görüşmelerinin tamamlandığı açıklanan Pusula Holding’in en azından bazı yöneticileri ve patronları hakkında soruşturma yürüttüğü ortaya çıktı. Buna göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, Pusula Holding’in bir parçası olan KatılımEvim yönetim kurulu üyesi Serdar Turhan ve tamamen ayrı bir şirket olan Destek Yatırım’ın hakim ortağı Altunç Kumova savcılık tarafından soruşturuluyor, hatta iddiaya göre bu isimler hakkında tedbir kararları alınmış durumda. Gazeteci İsmail Saymaz’ın sosyal medyadan yazdığına göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, cep telefonunu Türkiye’de bırakarak Marmaris’ten bir tekneyle Yunanistan’a geçti. Bu gelişme sonrası Katılımevim Yönetim Kurulu üyesi Serdar Turhan ve Destek Yatırım’ın sahibi Altunç Kumova için de yurt dışı çıkış yas ağı getirildi ve tedbir uygulandı. Savcılıktan henüz bir açıklama yapılmadığı için, Pusula ile ilgili bir soruşturma olup olmadığı, varsa bunun kapsamı ve konusu hakkında pek az bilgi var. Ancak cumartesi günü çıkan bu haberler üstüne gerek Tera Holding, gerekse Pusula Holding açıklamalar yaparak devralınma sürecinin bu soruşturmadan bağımsız olarak devam ettiğini bildirdiler. Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı İstanbul’da Cumhuriyet Savcılığı’nın Pusula Holding ve ona bağlı şirketler için soruşturma yürüttüğü, holdinge bağlı bazı şirketlerin patronlarının yurt dışına kaçtığı ortaya çıktı. Tam da bugünlerde Terra Holding, Pusula’yı satın almak için görüşmeleri tamamlamıştı. 10Haber bültenine üye olun, gündem özeti her sabah mailinize gelsin. Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini bu sarsıntıya bağladı. Ancak dün ortaya çıkan ve henüz bütün boyutları bilinmeyen bir gelişme, gerçeğin farklı olabileceğini ima ediyor. Cumartesi günü İstanbul Cumhuriyet Başsavcılığı’nın Tera tarafından devralınmak üzere olan, hatta devir görüşmelerinin tamamlandığı açıklanan Pusula Holding’in en azından bazı yöneticileri ve patronları hakkında soruşturma yürüttüğü ortaya çıktı. Buna göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, Pusula Holding’in bir parçası olan KatılımEvim yönetim kurulu üyesi Serdar Turhan ve tamamen ayrı bir şirket olan Destek Yatırım’ın hakim ortağı Altunç Kumova savcılık tarafından soruşturuluyor, hatta iddiaya göre bu isimler hakkında tedbir kararları alınmış durumda. Gazeteci İsmail Saymaz’ın sosyal medyadan yazdığına göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, cep telefonunu Türkiye’de bırakarak Marmaris’ten bir tekneyle Yunanistan’a geçti. Bu gelişme sonrası Katılımevim Yönetim Kurulu üyesi Serdar Turhan ve Destek Yatırım’ın sahibi Altunç Kumova için de yurt dışı çıkış yas ağı getirildi ve tedbir uygulandı. Savcılıktan henüz bir açıklama yapılmadığı için, Pusula ile ilgili bir soruşturma olup olmadığı, varsa bunun kapsamı ve konusu hakkında pek az bilgi var. Ancak cumartesi günü çıkan bu haberler üstüne gerek Tera Holding, gerekse Pusula Holding açıklamalar yaparak devralınma sürecinin bu soruşturmadan bağımsız olarak devam ettiğini bildirdiler.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Banka çalışanlarını rehin almıştı; eylemi 'kız çocukları farkındalığı' için yapmış Banka çalışanlarını rehin almıştı; eylemi 'kız çocukları farkındalığı' için yapmış Aliağa Medya Banka çalışanlarını rehin almıştı; eylemi 'kız çocukları farkındalığı' için yapmış Aliağa Medya</t>
+          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı » Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı 10haber.net Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini […] Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini bu sarsıntıya bağladı. Ancak dün ortaya çıkan ve henüz bütün boyutları bilinmeyen bir gelişme, gerçeğin farklı olabileceğini ima ediyor. Cumartesi günü İstanbul Cumhuriyet Başsavcılığı’nın Tera tarafından devralınmak üzere olan, hatta devir görüşmelerinin tamamlandığı açıklanan Pusula Holding’in en azından bazı yöneticileri ve patronları hakkında soruşturma yürüttüğü ortaya çıktı. Buna göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, Pusula Holding’in bir parçası olan KatılımEvim yönetim kurulu üyesi Serdar Turhan ve tamamen ayrı bir şirket olan Destek Yatırım’ın hakim ortağı Altunç Kumova savcılık tarafından soruşturuluyor, hatta iddiaya göre bu isimler hakkında tedbir kararları alınmış durumda. Gazeteci İsmail Saymaz’ın sosyal medyadan yazdığına göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, cep telefonunu Türkiye’de bırakarak Marmaris’ten bir tekneyle Yunanistan’a geçti. Bu gelişme sonrası Katılımevim Yönetim Kurulu üyesi Serdar Turhan ve Destek Yatırım’ın sahibi Altunç Kumova için de yurt dışı çıkış yas ağı getirildi ve tedbir uygulandı. Savcılıktan henüz bir açıklama yapılmadığı için, Pusula ile ilgili bir soruşturma olup olmadığı, varsa bunun kapsamı ve konusu hakkında pek az bilgi var. Ancak cumartesi günü çıkan bu haberler üstüne gerek Tera Holding, gerekse Pusula Holding açıklamalar yaparak devralınma sürecinin bu soruşturmadan bağımsız olarak devam ettiğini bildirdiler. Günün 10 Haberi Yok artık daha neler… 11 aylık bebeklerini satmışlar, ‘Kayboldu’ demişler Şimşek vergi denetimini anlattı: ‘Büyük ve yüksek gelirli mükellefler mercek altında’ Özgür Özel’den seçim mesajı: ‘Butlancılar ve darbeciler otokratın safında’ Yapay zeka devleri birden insafa geldi: Evet, gelişme hızımızı yavaşlatmalıyız “Kıyamet” ne kadar yakın? Dünyanın sonunu yapay zeka mı siyaset mi getirecek? Kahve erkeklerde testosteronu arttırıyormuş Bermuda Şeytan Üçgeni’nin büyük gizemi: Batık şehir izine rastlandı Nurgül Yeşilçay: Şehirde gençler yaşasın, biz değil Trabzonspor’da Burak Yılmaz iddiası: Galatasaray derbisinde takımın başında olabilir İspanya, üç yazıyla Arda Güler’i göklere çıkardı: ‘Mourinho’ya kendisini 15 dakikada hatırlattı’ Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı İstanbul’da Cumhuriyet Savcılığı’nın Pusula Holding ve ona bağlı şirketler için soruşturma yürüttüğü, holdinge bağlı bazı şirketlerin patronlarının yurt dışına kaçtığı ortaya çıktı. Tam da bugünlerde Terra Holding, Pusula’yı satın almak için görüşmeleri tamamlamıştı.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxONzVKdkFOX0VJZVBSa0czLTNJN0R5Q3E1OUtMUjIwTlJlWTNyTGJnbzV6V2N1b3N2TU0xVWRpOV91OUphZVp5T1FCU1FNY0cwN3FfRGozQjdFYTVQMXJCLV9TYWUzb3RpcXRyLU1Mazl1SFVjZ0htY1o1bnhTb3daMFJZQy1pd2loQzMzblhZRWNvZy0waGp4TnJHYU15MVJpSWR6VjhjTnBjX1o1aWtIcmEtZEs?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>https://10haber.net/ekonomi/piyasa-fena-karisti-tam-tera-grubu-pusulayi-aliyordu-savcilik-pusula-holdinge-sorusturma-baslatti-patronlari-kacti-736955/</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Muğla</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Marmaris</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Pusula Holding</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Pusula Holding:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr"/>
-      <c r="V44" s="2" t="inlineStr"/>
-      <c r="W44" s="2" t="inlineStr"/>
+          <t>faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>Pusula Holding Marmaris İstanbul Türkiye</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Pusula Yatırım Menkul Değerler A.Ş | Pusula Portföy Yönetimi A.Ş | Pusula Uluslararası Ticaret A.Ş | Pusula Enerji | Pusula</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Pusula Yatırım Menkul Değerler A.Ş</t>
+        </is>
+      </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>100 | 100 | 100 | 100 | 100.0</t>
+        </is>
+      </c>
       <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" s="2" t="n">
-        <v>71.7</v>
+        <v>258.75</v>
       </c>
       <c r="AB44" s="2" t="n">
         <v>43</v>
@@ -6451,27 +6652,27 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 10:24:19</t>
+          <t>2026-09-13 13:33:00</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>şüpheli işlem</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek: 16 ilimizde turizm güvenliğini tehdit eden 164 olay ve soruşturmada 323 şüpheli hakkında adli işlem yapıldı</t>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek: 16 ilimizde turizm güvenliğini tehdit eden 164 olay ve soruşturmada 323 şüpheli hakkında adli işlem yapıldı DHA | Demirören Haber Ajansı</t>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6481,40 +6682,52 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>turizm</t>
+          <t>sanayi</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek: 16 ilimizde turizm güvenliğini tehdit eden 164 olay ve soruşturmada 323 şüpheli hakkında adli işlem yapıldı DHA | Demirören Haber Ajansı</t>
+          <t>Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. +1 Haber albümü için resme tıklayın Bugün öğleden sonra Konacık Sanayi Sitesi'ndeki otluk alanda yangın başladı. Alevleri fark eden sanayi esnafı, hortum ve yangın tüpleriyle alevlere müdahale etti. İhbarın ardından Bodrum İtfaiye Grup Amirliği ekipleri de olay yerine geldi. Vatandaşlar ve ekiplerin müdahalesiyle yangın büyümeden söndürüldü. Yangının otluk alana atılan sigara izmaritinden çıktığı sanılıyor. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 - Asayiş Sanayideki Yangın Büyümeden Söndürüldü Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. +1 Haber albümü için resme tıklayın Bugün öğleden sonra Konacık Sanayi Sitesi'ndeki otluk alanda yangın başladı. Alevleri fark eden sanayi esnafı, hortum ve yangın tüpleriyle alevlere müdahale etti. İhbarın ardından Bodrum İtfaiye Grup Amirliği ekipleri de olay yerine geldi. Vatandaşlar ve ekiplerin müdahalesiyle yangın büyümeden söndürüldü. Yangının otluk alana atılan sigara izmaritinden çıktığı sanılıyor. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 Muğla / Bodrum - Asayiş Yazdır GİRİŞ YAP Yorum yazarak Bodrum Kent Tv Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yoruml</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek: 16 ilimizde turizm güvenliğini tehdit eden 164 olay ve soruşturmada 323 şüpheli hakkında adli işlem yapıldı Bakan Gürlek: 16 ilimizde turizm güvenliğini tehdit eden 164 olay ve soruşturmada 323 şüpheli hakkında adli işlem yapıldı DHA | Demirören Haber Ajansı Bakan Gürlek: 16 ilimizde turizm güvenliğini tehdit eden 164 olay ve soruşturmada 323 şüpheli hakkında adli işlem yapıldı DHA | Demirören Haber Ajansı</t>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. +1 Haber albümü için resme tıklayın Bugün öğleden sonra Konacık Sanayi Sitesi'ndeki otluk alanda yangın başladı. Alevleri fark eden sanayi esnafı, hortum ve yangın tüpleriyle alevlere müdahale etti. İhbarın ardından Bodrum İtfaiye Grup Amirliği ekipleri de olay yerine geldi. Vatandaşlar ve ekiplerin müdahalesiyle yangın büyümeden söndürüldü. Yangının otluk alana atılan sigara izmaritinden çıktığı sanılıyor. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 - Asayiş Sanayideki Yangın Büyümeden Söndürüldü Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 Muğla / Bodrum - Asayiş Yazdır GİRİŞ YAP Yorum yazarak Bodrum Kent Tv Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxPcmlSdUdBWVRlMjVvV2JfOHIxbXR5cjhsQnczNkgyWnhJVEpEWEI4Q0Npa2lHUHEtbGxhQWNobWc0YWQtM2lzTjhuUjI2VVd5X0M1MjVqWVVHR3ZXYkhzU1gtU0hNV0lEYlhXMzhSUml4VjE3aEdjeTdSelA1RzhVOXlKdzZuTGo4YkJtcFhTLUI5aXhvRHFVOUVQeEtSYV9Ia3FFVXlvMWhnbko4RjBWX05pdkxJODhOT0ZCR1YtZERLY2RDa3UtZFhZbjlMNkZHTEtGTWw0cjdDVklGM09iMzdRMDdhTnVrNzdRcE9RdGlqdw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
+          <t>https://kenttv.net/haber/28692971/sanayideki-yangin-buyumeden-sonduruldu</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Muğla</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Bodrum</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>da sanayi sitesi</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr"/>
@@ -6528,14 +6741,124 @@
       <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="n">
-        <v>115.5</v>
+        <v>105.25</v>
       </c>
       <c r="AB45" s="2" t="n">
         <v>44</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:50:46</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>soruşturma</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>ticaret</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>browser_failed</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPczREcWt4bVUtWHhXU0d2Qzh0cklpYTJpbDR1RkdPQ05kOGNfUWRvT1gzNHE3NFY2V1R3a0RyeHFsbER3bXBMRkJCd2NoLUVHNjNTV1VLcGlzZHJxcEVOcV9uVzlfNmwycTdIVnY1STE4blpLcXVKUzR4elVIUnRkWmxKbjhVdXFCcXBDb3c2Y1VJUnVXSkRPNmlYRDEwZlp6a040aEVnLUQxc082WWVES2FQVGpUTF9Ca3N4UjQ5SGxZcDdmRnZFOGlR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret:161:body+summary</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Türkiye</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi | İstanbul Ticaret Merkezi | İstanbul Ticaret İş Güvenliği ve Endüstriyel Ürünler San. A.Ş | İstanbul Ticaret Üniversitesi Küçükyalı Kampüsü | İstanbul Ticaret Borsası</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>100.0 | 100.0 | 100.0 | 100.0 | 100.0</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="n">
+        <v>200.96</v>
+      </c>
+      <c r="AB46" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB45"/>
+  <autoFilter ref="A1:AB46"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -6581,6 +6904,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:55:00</t>
+          <t>2026-09-13 20:42:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
+          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
+          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Bursada Bugün</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -537,10 +537,14 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Bursa | Düzce</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Orhangazi</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
@@ -552,22 +556,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 08:43:00</t>
+          <t>2026-09-13 23:31:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı</t>
+          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı internethaber.com</t>
+          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce Postası</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -577,7 +581,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Düzce</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
@@ -592,22 +596,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:19:31</t>
+          <t>2026-09-14 06:03:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
+          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
+          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Ege Alternatif</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -615,7 +619,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -628,22 +636,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:02:22</t>
+          <t>2026-09-14 06:49:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede sondakika.com</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği egetelgraf.com</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -651,47 +659,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Gerede Organize Sanayi Bölgesi</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 17:46:00</t>
+          <t>2026-09-13 13:19:31</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı 24 Saat Gazetesi Ankara</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -699,47 +695,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>BOLPET PLAST GERİ DÖNÜŞÜM</t>
-        </is>
-      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 18:12:27</t>
+          <t>2026-09-13 14:33:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı</t>
+          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı Türkiye Gazetesi</t>
+          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı surmelihaber.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -747,11 +731,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Antalya | Bolu</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
@@ -764,7 +744,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:11:09</t>
+          <t>2026-09-13 19:18:13</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -774,12 +754,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti!</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı A Haber</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! duzcegazeteefsane.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -789,14 +769,10 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Bolu | Muş | Sakarya</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
@@ -808,7 +784,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:09:34</t>
+          <t>2026-09-13 21:12:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -818,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı.</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. Vietnam.vn</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -831,20 +807,32 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Nova Orman Ürünleri - Bolu Fabrika</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 05:48:46</t>
+          <t>2026-09-13 19:45:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -854,12 +842,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti Eskişehir Durum</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir</t>
+          <t>Bolu</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -884,7 +872,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:04:00</t>
+          <t>2026-09-13 11:41:26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -894,12 +882,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü</t>
+          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Milli İrade Gazetesi</t>
+          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü kocatepegazetesi.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -909,10 +897,14 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>Ankara | Eskişehir | Manisa</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Demirci</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
@@ -924,22 +916,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 03:22:15</t>
+          <t>2026-09-14 09:11:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı bolgegundemi.com</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -947,35 +939,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Antalya | Bursa</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Alanya</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Toptancı Hali</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:03:05</t>
+          <t>2026-09-13 20:07:54</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı A Haber</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Turizm Aktüel</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -985,7 +989,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1000,22 +1004,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 06:08:08</t>
+          <t>2026-09-13 10:20:22</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15 ilde 'Ailem Güvende' operasyonu</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Dakika</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1023,8 +1027,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
@@ -1036,22 +1048,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:19:34</t>
+          <t>2026-09-13 10:19:26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi!</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1059,8 +1071,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
@@ -1072,22 +1092,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:07:34</t>
+          <t>2026-09-14 06:55:51</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı!</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! SON TV</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1095,8 +1115,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Bilecik</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Bozüyük</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
@@ -1108,22 +1136,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 20:23:48</t>
+          <t>2026-09-14 06:45:32</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı aksiyon.com.tr</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1131,8 +1159,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Adana | Aydın | Bartın | Bilecik | Düzce</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Köşk | Bozüyük | Mudurnu | Maltepe</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
@@ -1144,7 +1180,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 08:33:15</t>
+          <t>2026-09-13 14:13:08</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1154,12 +1190,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı!</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! SON TV</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1167,7 +1203,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Van</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1180,7 +1220,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:13:08</t>
+          <t>2026-09-13 11:13:44</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1190,12 +1230,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi</t>
+          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv</t>
+          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1203,11 +1243,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Bingöl | İstanbul | Van</t>
-        </is>
-      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1220,7 +1256,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:05:00</t>
+          <t>2026-09-13 12:22:00</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1230,12 +1266,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı aydinlik.com.tr</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1243,7 +1279,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1256,22 +1296,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 06:35:00</t>
+          <t>2026-09-14 07:21:29</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti</t>
+          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Ege Telgraf</t>
+          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursada Bugün</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1279,35 +1319,51 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Orhangazi</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Cargill Türkiye Bursa Orhangazi Mısır İşleme Tesisi</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 07:18:00</t>
+          <t>2026-09-14 08:57:35</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında KARAR</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1315,11 +1371,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Ankara | Hatay | İstanbul | Mersin</t>
-        </is>
-      </c>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1332,22 +1384,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:22:00</t>
+          <t>2026-09-14 06:00:38</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1357,10 +1409,14 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>Çorum | Eskişehir | Kilis | Aydın | İstanbul</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Söke | Beşiktaş | Çerkezköy</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
@@ -1372,22 +1428,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:19:26</t>
+          <t>2026-09-14 09:46:30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi!</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1395,16 +1451,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
@@ -1416,22 +1464,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 01:34:53</t>
+          <t>2026-09-14 06:22:37</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi Finans Gündem</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1439,16 +1487,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
@@ -1460,22 +1500,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 18:20:15</t>
+          <t>2026-09-13 15:39:00</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da depo yangını / Ek fotoğraflar</t>
+          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da depo yangını / Ek fotoğraflar Antalya İleri</t>
+          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı İstiklal Gazetesi</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1485,7 +1525,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Antalya</t>
+          <t>Kayseri</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1500,22 +1540,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:20:22</t>
+          <t>2026-09-14 07:27:00</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı!</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor sondakika.com</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1525,41 +1565,45 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t>Kahramanmaraş</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:47:00</t>
+          <t>2026-09-13 20:52:25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Depo’da korkutan yangın, mahalleli seferber oldu</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Depo’da korkutan yangın, mahalleli seferber oldu BursaVar</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1580,22 +1624,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 17:42:00</t>
+          <t>2026-09-13 14:39:00</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne?</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı!</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? politikam.com</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1603,32 +1647,20 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Antalya</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Muratpaşa</t>
-        </is>
-      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>Ambalaj Ticaret</t>
-        </is>
-      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:00:14</t>
+          <t>2026-09-14 08:14:01</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1638,12 +1670,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti</t>
+          <t>AirBaltic'te finansal kriz: ABD'de iflas koruması başvurusunda bulundu</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti Samanyolu Haber</t>
+          <t>AirBaltic'te finansal kriz: ABD'de iflas koruması başvurusunda bulundu İstanbul Ticaret Gazetesi</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1651,20 +1683,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş</t>
+          <t>İstanbul Ticaret</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>İzmer</t>
+          <t>İstanbul Ticaret Üniversitesi</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -1676,7 +1704,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 06:18:00</t>
+          <t>2026-09-14 09:58:46</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1686,12 +1714,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!”</t>
+          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara</t>
+          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1699,7 +1727,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Kahramanmaraş</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1712,7 +1744,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 18:50:00</t>
+          <t>2026-09-14 07:12:00</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1722,12 +1754,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Yıldırım Gazetesi</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1737,10 +1769,14 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Gebze</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
@@ -1752,7 +1788,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 01:09:00</t>
+          <t>2026-09-14 08:07:27</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1762,12 +1798,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ege Gıda Meşrubat, konkordato süreci başlattı</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak?</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Ege Gıda Meşrubat, konkordato süreci başlattı egealternatif.com</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1777,26 +1813,18 @@
       </c>
       <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Ege Gıda Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:08:44</t>
+          <t>2026-09-14 07:23:36</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1806,12 +1834,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı...</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek enerjifm.com.tr</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1819,8 +1847,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Kestel</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
@@ -1832,22 +1868,22 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 17:51:00</t>
+          <t>2026-09-14 09:53:53</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınına müdahale sürüyor</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınına müdahale sürüyor Güneydoğu Ekspres</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1855,16 +1891,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
@@ -1876,7 +1904,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 18:58:00</t>
+          <t>2026-09-13 20:36:11</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1886,12 +1914,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı</t>
+          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Zonguldak Pusula Son Dakika Haberleri</t>
+          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor aksiyon.com.tr</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1901,10 +1929,14 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>Adana | Bilecik | Düzce | Iğdır | Zonguldak</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Köşk | Mudurnu</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
@@ -1916,7 +1948,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 17:37:21</t>
+          <t>2026-09-13 20:44:00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1926,12 +1958,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü</t>
+          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Bursa Saati</t>
+          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Cumhuriyet</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1941,14 +1973,10 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Kayseri</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Kocasinan</t>
-        </is>
-      </c>
+          <t>Bolu | Düzce</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
@@ -1960,7 +1988,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:04:58</t>
+          <t>2026-09-13 21:48:26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1970,12 +1998,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Aksiyon.com.TR</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1988,11 +2016,7 @@
           <t>Bolu</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
@@ -2004,22 +2028,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:39:00</t>
+          <t>2026-09-13 20:36:42</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı!</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2040,22 +2064,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 00:03:35</t>
+          <t>2026-09-13 19:48:24</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada aksiyon.com.tr</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2063,8 +2087,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Adana | Aydın | Bartın | Düzce | Iğdır</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Köşk | Mudurnu | Maltepe</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
@@ -2076,22 +2108,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:10:48</t>
+          <t>2026-09-14 07:27:59</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı duzcegazeteefsane.com</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2099,7 +2131,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2112,22 +2148,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:52:00</t>
+          <t>2026-09-13 14:06:00</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama!</t>
+          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com</t>
+          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı yeniadimgazetesi.com</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2135,7 +2171,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2148,22 +2188,22 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 06:39:00</t>
+          <t>2026-09-14 07:51:05</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2184,22 +2224,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 04:52:14</t>
+          <t>2026-09-14 06:20:02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı</t>
+          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı 10haber.net</t>
+          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2209,22 +2249,22 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>İstanbul | Muğla</t>
+          <t>Bursa</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Marmaris</t>
+          <t>Nilüfer</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Pusula Holding</t>
+          <t>Tarım AŞ</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Pusula Yatırım Menkul Değerler A.Ş</t>
+          <t>TARIM PEYZAJ A.Ş. Bursa Tarım Hayvancılık Peyzaj Çevre İnş. San. Tic. A.Ş</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -2236,7 +2276,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:33:00</t>
+          <t>2026-09-14 09:20:28</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2246,12 +2286,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Sanayideki Yangın Büyümeden Söndürüldü</t>
+          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV</t>
+          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı aksiyon.com.tr</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2261,12 +2301,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Muğla</t>
+          <t>Adana | Bilecik | Bursa | Düzce | Iğdır</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Bodrum</t>
+          <t>Köşk | Mudurnu | Kızıltepe</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
@@ -2280,49 +2320,205 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>2026-09-13 22:01:00</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 08:43:00</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Diğer</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 10:52:00</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama!</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:23:00</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası Samsun Gazetesi</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Samsun | Muğla</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Marmaris</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>2026-09-13 11:50:46</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>İstanbul Ticaret</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>İstanbul Ticaret Üniversitesi</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J46"/>
+  <autoFilter ref="A1:J50"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2369,6 +2565,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2380,7 +2580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB46"/>
+  <dimension ref="A1:AB50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2558,7 +2758,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:55:00</t>
+          <t>2026-09-13 20:42:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2573,12 +2773,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
+          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
+          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Bursada Bugün</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2598,12 +2798,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontro... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Val... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontro...</t>
+          <t>Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Düzce'de fabrika yangını için çok sayıda ekip sevk edildi Ahşap malzemeler alevlerin kısa sürede büyümesine neden oldu Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Yangın, Düzce merkeze bağlı Hacıdayı mevkisinde faaliyet gösteren ahşap kapı fabrikasında meydana geldi. Fabrikadan yükselen alevleri ve dumanları görenlerin durumu yetkililere bildirmesi üzerine bölgeye geniş kapsamlı ekip sevkiyatı yapıldı. İlk belirlemelere göre henüz çıkış nedeni netleşmeyen yangın, fabrikada bulunan ahşap ve diğer yanıcı malzemelerin etkisiyle kısa süre içerisinde geniş bir alana yayıldı. Alevlerin büyümesi üzerine yangına müdahale için kent merkezinin yanı sıra ilçelerden ve çevre illerden de itfaiye ekipleri bölgeye gönderildi. İhbarın ardından olay yerine ulaşan itfaiye ekipleri, fabrikadaki yangının daha fazla alana yayılmasını önlemek amacıyla çalışma başlattı. Yangının üretim yapılan bölümde bulunan yanıcı malzemeler nedeniyle hızlı şekilde büyümesi, müdahalenin kapsamının genişletilmesine neden oldu. Bölgeye sevk edilen ekipler, farklı noktalardan alevlere müdahale ederek yangını kontrol altına almaya çalışıyor. Düzce fabrika yangını nedeniyle ekiplerin bölgede yoğun çalışması sürerken, çevrede de güvenlik tedbirleri alındı. Yangının çıkış noktası ve büyüklüğünün net olarak belirlenmesine yönelik çalışmalar da devam ediyor. İtfaiye ekiplerinin müdahalesinin ardından yangının çıkış nedeninin belirlenmesi için gerekli incelemelerin yapılması bekleniyor. Yangının meydana geldiği fabrikanın ahşap kapı imalatı yapılan bir tesis olması nedeniyle içeride bulunan malzemelerin alevlerin yayılma hızını artırdığı belirtildi. Yangının başlamasının ardından kısa süre içerisinde yoğun duman ve alevlerin yükselmesi üzerine bölgeye daha fazla ekip takviyesi gerçekleştirildi. İtfaiye ekipleri, bir yandan alevleri bastırmaya çalışırken diğer yandan yangının fabrikanın diğer bölümlerine ve çevredeki alanlara sıçramaması için müdahalelerini sürdürüyor. Çalışmalar sırasında ekiplerin koordineli şekilde hareket ettiği görüldü. Diğer Güncel Haberler için tıklayın Türkiye bu olayı konuşuyor: 11 aylık Büşra'dan 4 gündür haber yok! Anne "satıldı" dedi, baba reddetti Cezaevinden çıkan Fatma Soydaş'ın son hali şaşırttı! İlk görüntüsü ortaya çıktı Bursa'da gözler bu toplantıda! Nilüfer'de tartışma yaratan imar planı gündemde... Bursa Orhangazi'de dev operasyon! 8 ton ele geçirildi... Kurtlar Vadisi sahneleri yeniden gündemde: Plakadaki detay dikkat çekti! Bursa'da vicdanları sızlatan görüntü!</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontro... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı.</t>
+          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Bursada Bugün Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Düzce'de fabrika yangını için çok sayıda ekip sevk edildi Ahşap malzemeler alevlerin kısa sürede büyümesine neden oldu Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yangın, Düzce merkeze bağlı Hacıdayı mevkisinde faaliyet gösteren ahşap kapı fabrikasında meydana geldi. Fabrikadan yükselen alevleri ve dumanları görenlerin durumu yetkililere bildirmesi üzerine bölgeye geniş kapsamlı ekip sevkiyatı yapıldı. İlk belirlemelere göre henüz çıkış nedeni netleşmeyen yangın, fabrikada bulunan ahşap ve diğer yanıcı malzemelerin etkisiyle kısa süre içerisinde geniş bir alana yayıldı. Alevlerin büyümesi üzerine yangına müdahale için kent merkezinin yanı sıra ilçelerden ve çevre illerden de itfaiye ekipleri bölgeye gönderildi. İhbarın ardından olay yerine ulaşan itfaiye ekipleri, fabrikadaki yangının daha fazla alana yayılmasını önlemek amacıyla çalışma başlattı. Yangının üretim yapılan bölümde bulunan yanıcı malzemeler nedeniyle hızlı şekilde büyümesi, müdahalenin kapsamının genişletilmesine neden oldu. Bölgeye sevk edilen ekipler, farklı noktalardan alevlere müdahale ederek yangını kontrol altına almaya çalışıyor. Düzce fabrika yangını nedeniyle ekiplerin bölgede yoğun çalışması sürerken, çevrede de güvenlik tedbirleri alındı. Yangının çıkış noktası ve büyüklüğünün net olarak belirlenmesine yönelik çalışmalar da devam ediyor. İtfaiye ekiplerinin müdahalesinin ardından yangının çıkış nedeninin belirlenmesi için gerekli incelemelerin yapılması bekleniyor. Yangının meydana geldiği fabrikanın ahşap kapı imalatı yapılan bir tesis olması nedeniyle içeride bulunan malzemelerin alevlerin yayılma hızını artırdığı belirtildi. Yangının başlamasının ardından kısa süre içerisinde yoğun duman ve alevlerin yükselmesi üzerine bölgeye daha fazla ekip takviyesi gerçekleştirildi. İtfaiye ekipleri, bir yandan alevleri bastırmaya çalışırken diğer yandan yangının fabrikanın diğer bölümlerine ve çevredeki alanlara sıçramaması için müdahalelerini sürdürüyor. Çalışmalar sırasında ekiplerin koordineli şekilde hareket ettiği görüldü. Anne "satıldı" dedi, baba reddetti Cezaevinden çıkan Fatma Soydaş'ın son hali şaşırttı! İlk görüntüsü ortaya çıktı Bursa'da gözler bu toplantıda! Bursa Orhangazi'de dev operasyon! Bursa'da vicdanları sızlatan görüntü!</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -2613,27 +2813,27 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bolugundem.com/haber/28691580/boluda-5-saatlik-yangin-kabusu-geri-donusum-fabrikasi-alevlere-teslim-oldu-3-kisi-yaralandi</t>
+          <t>https://www.bursadabugun.com/haber/duzce-de-ahsap-kapi-fabrikasinda-yangin-panigi-alevler-kisa-surede-buyudu-1948671.html</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Bursa | Düzce</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Orhangazi</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Geri dönüşüm fabrikası</t>
-        </is>
-      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr"/>
@@ -2647,7 +2847,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="n">
-        <v>128.01</v>
+        <v>118</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -2656,27 +2856,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 08:43:00</t>
+          <t>2026-09-13 23:31:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı</t>
+          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı internethaber.com</t>
+          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce Postası</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2686,18 +2886,22 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>kuruluş, masak</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar... MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar... MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar... HABERLER GÜNCEL Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar... Yayınlama Tarihi: 13.09.2026 11:43 Güncelleme Tarihi: 13.09.2026 12:36 MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. 1 10 SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. 2 10 “Bankacılık Transfer”lerinde yer alan 45.135 işlemde 13.040 para girişi, 32.095 para çıkışı tespit edilmiştir. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. 3 10 4 10 5 10 6 10 7 10 8 10 9 10 10 10 masak LGBT MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. “Bankacılık Transfer”lerinde yer alan 45.135 işlemde 13.040 para girişi, 32.095 para çıkışı tespit edilmiştir. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. 1 10 SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. 2 10 “Bankacılık Transfer”lerinde yer alan 45.135 işlemde 13.040 para girişi, 32.095 para çıkışı tespit edilmiştir. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. 3 10 4 10 5 10 6 10 7 10 8 10 9 10 10 10 MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. 1 10 SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. 2 10 “Bankacılık Transfer”lerinde yer alan 45.135 işlemde 13.040 para girişi, 32.095 para çıkışı tespit edilmiştir. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. 3 10 Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. İşte detaylar...</t>
+          <t>Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci hastaneye kaldırıldı. Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci h... Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci hastaneye kaldırıldı. Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale eden bir itfaiye eri, üzerine çatı düşmesi sonucu yaralandı. D-100 kara yolu üzerinde bulunan Düzce Door isimli fabrikada çıkan yangın kısa sürede fabrikayı sardı. Yangına müdahale eden itfaiye ekiplerinin çalışmaları sırasında bir itfaiye erinin üzerine yanan çatı düştü. Çatı parçalarının altında kalan itfaiye eri yaralandı. Olay yerinde sağlık ekipleri tarafından ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci hastaneye kaldırıldı. Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale eden bir itfaiye eri, üzerine çatı düşmesi sonucu yaralandı. D-100 kara yolu üzerinde bulunan Düzce Door isimli fabrikada çıkan yangın kısa sürede fabrikayı sardı. Yangına müdahale eden itfaiye ekiplerinin çalışmaları sırasında bir itfaiye erinin üzerine yanan çatı düştü. Çatı parçalarının altında kalan itfaiye eri yaralandı. Olay yerinde sağlık ekipleri tarafından ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. 14 Eyl 2026 - 02:31 İHA Düzce - Asayiş Yazdır Mahreç İhlas Haber Ajansı Yorum yazarak Düzce Postası Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yo</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı internethaber.com MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Büyükelçilikler ve yabancı vakıflardan alınan maddi desteklerin, cinsiyet geçiş ameliyatları dahil çeşitli faaliyetlerde kullanıldığı ve bu finansal hareketlerin soruşturma kapsamında değerlendirildiği belirtildi. HABERLER GÜNCEL Yabancı kuruluşlardan LGBT derneklerine para transferleri! MASAK tek tek açıkladı MASAK raporuna göre İstanbul merkezli 6 derneğin (Hak Eşitlik, Lambda İstanbul, LGBTİ+ Aileleri, Pozitif Yaşam, Pozitif İz ve SPoD) yurt dışı fonları incelendi. Yayınlama Tarihi: 13.09.2026 11:43 Güncelleme Tarihi: 13.09.2026 12:36 MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. Tutanakta; Hak Eşitlik Varoluş İçin Derneği, Lambda İstanbul, LGBTİ+ Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin çeşitli yabancı kişi, vakıf, kuruluş, büyükelçilik ve kamu kurumlarından maddi destek aldığı; bu kaynakların bir bölümünün cinsiyet geçiş sürecindeki kişilerin ameliyat masrafları dâhil çeşitli faaliyetlerde kullanıldığı ve söz konusu faaliyetlerin soruşturma kapsamında değerlendirildiği belirtildi. 1 10 SWIFT kayıtlarında altı derneğe farklı dönemlerde toplam 3 milyon 359 bin 167 dolar aktarıldığı tespit edildi. En yüksek tutarın 1 milyon 570 bin 692 dolarla Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğine, ardından 762 bin 939 dolarla Hak Eşitlik Varoluş İçin Derneğine ve 518 bin 525 dolarla Pozitif Yaşam Derneğine gönderildiği görüldü. LGBTİ+ Aileleri ve Yakınları Derneğine 314 bin 220 dolar, Lambda İstanbul’a 103 bin 650 dolar, Pozitif İz Derneğine ise 89 bin 138 dolar aktarıldığı; transferler arasında ABD Dışişleri Bakanlığı bağlantılı ödemeler, Fransa Büyükelçiliği, Hollanda ve Almanya bağlantılı kamu kurumları, ILGA Europe, European Endowment for Democracy, German Marshall Fund, çeşitli uluslararası vakıf ve kuruluşların bulunduğu kaydedildi. Para girişlerinin 218’i doğrudan SWIFT alma işlemidir. Gönderen adı, ülke/uyruk bilgisi, SWIFT niteliği, banka ve özellikle işlem açıklaması birlikte değerlendirildiğinde; 2021–2026 döneminde yabancı veya uluslararası nitelikte olduğu dosya içeriğinden anlaşılabilen 37 farklı kurumsal kaynak/kamu misyonundan toplam 209 para girişi tespit edilmiştir. 3 10 4 10 5 10 6 10 7 10 8 10 9 10 10 10 masak LGBT MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. 3 10 4 10 5 10 6 10 7 10 8 10 9 10 10 10 MASAK Veri İnceleme Tutanağı’na göre, İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında İstanbul merkezli 6 derneğin yurt dışı para hareketleri incelendi. 3 10 Yabancı kuruluşlardan LGBT derneklerine para transferleri!</t>
+          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce Postası Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci hastaneye kaldırıldı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci h... Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale eden bir itfaiye eri, üzerine çatı düşmesi sonucu yaralandı. D-100 kara yolu üzerinde bulunan Düzce Door isimli fabrikada çıkan yangın kısa sürede fabrikayı sardı. Yangına müdahale eden itfaiye ekiplerinin çalışmaları sırasında bir itfaiye erinin üzerine yanan çatı düştü. Çatı parçalarının altında kalan itfaiye eri yaralandı. Olay yerinde sağlık ekipleri tarafından ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. 14 Eyl 2026 - 02:31 İHA Düzce - Asayiş Yazdır Mahreç İhlas Haber Ajansı Yorum yazarak Düzce Postası Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -2707,12 +2911,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.internethaber.com/yabanci-kuruluslardan-lgbt-derneklerine-para-transferleri-masak-tek-tek-acikladi-foto-galerisi-2459238.htm</t>
+          <t>https://www.duzcepostasi.com/haber/28694684/duzcede-fabrikadaki-yanginda-uzerine-cati-dusen-itfaiyeci-yaralandi</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Düzce</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
@@ -2737,7 +2941,7 @@
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="n">
-        <v>106.25</v>
+        <v>95.5</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>2</v>
@@ -2746,27 +2950,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:19:31</t>
+          <t>2026-09-14 06:03:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>para aklama</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
+          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
+          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Ege Alternatif</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2776,44 +2980,52 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bunlar da ilginizi çekebilir Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Bunlar da ilginizi çekebilir Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 Etiket: Kara para aklama Yorum (0) En popüler En yeni Duygularınızı paylaşmak için lütfen bir yorum bırakın! İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html Duygularınızı paylaşmak için lütfen bir yorum bırakın! Ana sayfa Ekonomi Yatırım - Finans Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. ÇİN - "Bu benim param, neden gönderemiyorum?", görünüşte basit bir soru olsa da, bankaların "kara para aklama karşıtı" ve "dolandırıcılık karşıtı" bahanesiyle büyük nakit işlemlerine yönelik kısıtlamaları giderek sıkılaştırması nedeniyle birçok Çin vatandaşı için baş ağrısı yaratıyor. VietNamNet•13/09/2026 Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bunlar da ilginizi çekebilir Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Bunlar da ilginizi çekebilir Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 Etiket: Kara para aklama Yorum (0) En popüler En yeni Duygularınızı paylaşmak için lütfen bir yorum bırakın! İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bunlar da ilginizi çekebilir Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Bunlar da ilginizi çekebilir Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Banka çalışanları, müşterilere fon kaynağını beyan eden bir formu doldurma konusunda rehberlik ediyor; bu işlem, Çin'de büyük finansal işlemler gerçekleştirirken birçok kişi için bir kabusa dönüşmüş durumda. Fotoğraf: Baidu Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Bu nedenle, banka fonlarının kaynağını kanıtlayan belgeler istediğinde, birçoğu zor durumda kalıyor. Bu yük banka çalışanlarının omuzlarına düşüyor. Sadece müşterilerin hayal kırıklığına uğradığını düşünüyorsanız, karşıdaki banka çalışanlarına bakın. Banka çalışanları da önemli bir baskı altında. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Çin'deki Zhengzhou Üniversitesi'nden Profesör Zhao Ming şöyle bir benzetme kullandı: "Bu, taksi şoförlerinin yolcuların aranan suçlular olup olmadığını kontrol etmesine benziyor. Sıkı kontroller şikayetlere yol açarken, gevşek kontroller iş kayıplarına neden oluyor." Son zamanlarda, Guangdong'da tanınmış bir avukat olan Zhu Xiaoyun, sosyal medyada Shandong'daki bir bankanın çalışanları tarafından "sorguya çekildiğini" ve sadece 40.000 RMB (yaklaşık 156 milyon VND) çektiği için polisin çağrıldığını paylaştı. Olay, kamuoyunda hızla büyük tepkiye yol açarak, merkez bankasının daha önce düzenlemeleri değiştirmesine rağmen süregelen pratik sorunları bir kez daha gündeme getirdi. Özellikle, 28 Kasım 2025 tarihinde Çin Halk Bankası (PBoC), Çin Mali Davranışlar Devlet İdaresi ve Çin Menkul Kıymetler Düzenleme Komisyonu, 1 Ocak 2026'dan itibaren geçerli olmak üzere yeni düzenlemeler yayınladı. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ancak, gerekenden fazla bilgi istendiğinde, müşteriler iş birliğine açık olmalı, ancak aynı zamanda personelden belirli düzenlemeleri talep ederek veya yardım için çağrı merkezini arayarak haklarını korumalıdırlar. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. Baidu'ya göre, Beijing Business Today, The Paper Kaynak: https://vietnamnet.vn/nguoi-dan-ong-mang-hai-vali-tien-gui-ngan-hang-muon-dem-ve-cung-khong-duoc-2553059.html</t>
+          <t>Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. ASAYİŞ Yayınlanma : 14 Eylül 2026 09:03 Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'de bir kapı imalat fabrikasında çıkan yangın tamamen söndürüldü. Yangının ardından fabrikanın durumu havadan görüntülendi. Yangın anında büyük hasar oluştu Düzce Gökçeköy mevkisinde bulunan Düzce Door isimli fabrikada, dün akşam 21.30 sıralarında başlayan yangın, içerideki kimyasal, ahşap ve plastik maddelerin etkisiyle hızla yayıldı ve tüm tesisi sardı. Yangın, 4 saatlik bir mücadelenin ardından kontrol altına alındı ve sabaha karşı tamamen söndürüldü. Detaylı inceleme yapılacak Fabrikanın son hali havadan görüntülenirken, yangının etkisiyle tamamen kullanılmaz hale geldiği ve bazı bölümlerden hala dumanların yükseldiği görüldü. İlerleyen saatlerde, yangının çıkış nedeni hakkında detaylı bir inceleme yapılması planlanıyor. #Düzce #Yangın İHA Pay</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. 18 Nisan'da, Çin'in Zhejiang eyaletine bağlı Ningbo şehrinde Li soyadlı bir adam, faiz kazanmak amacıyla 1 milyon yuan (yaklaşık 3,9 milyar VND) değerinde nakit parayla dolu iki bavulu bir banka şubesine götürdü. Bu para, 10 yıldır işlettiği bakkal dükkanından biriktirdiği paraydı. Ancak Bay Li, sıcak bir karşılama yerine "inanılmaz" bir taleple karşılaştı: Banka çalışanı ona her banknotun kaynağını, alındığı zamanı, yeri ve işlem yöntemini belirtmesini isteyen bir kağıt verdi. Günlük satışlardan elde edilen para, yoğun sezonlarda biriktirilen bozuk paralar veya akrabalar tarafından emanet edilen paralar gibi kalemlerin ayrıntılı bir hesabı verilemiyordu. Bay Li'nin bankaya getirdiği 1 milyon yuanın tamamı, gişenin üzerinde yığınlar halinde duruyordu. Fotoğraf: Baidu Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi. Bu tuhaf durum, Çin finans forumlarında hemen büyük yankı uyandırdı. Tartışmanın özünde, teorik düzenlemeler ile gerçek hayattaki uygulama arasındaki uçurum yatıyor. Kara para aklama karşıtı düzenlemelere göre, suç riskini önlemek için 50.000 RMB'yi (yaklaşık 195 milyon VND) aşan nakit işlemlerinin menşeinin doğrulanması gerekiyor. Sorun şu ki, banka çalışanları noter onaylı iş sözleşmeleri, maaş bordroları veya satış faturaları gibi belgelere ihtiyaç duyuyor. Karşı tarafta çiftçiler, küçük esnaf veya tamirciler oturuyor. Nakit parayla geçiniyorlar ve iş sözleşmesi veya fatura olmadan sadece defterlerde kayıt tutuyorlar. Birçok banka, "dolandırıcılık yapmama" hedefini çalışan performans değerlendirmeleri ve primleriyle ilişkilendirmiştir. Çalışanlardan, yasa dışı bir işlem gerçekleşmesi durumunda ağır cezalardan "kendilerini korumak" için sorular sormaları ve hatta yetkilileri aramaları istenmektedir. Bu durum ironik bir sonuca yol açıyor: Bazen, zorunlu eşiğin altında kalan 40.000 RMB (yaklaşık 156 milyon VND) gibi küçük bir miktar bile reddediliyor veya sorgulanıyor; bu da her iki taraf için de zaman kaybına ve hayal kırıklığına neden oluyor. Bu düzenleme, 50.000 RMB'yi aşan mevduatlar için fonların kaynağını kaydetme zorunluluğunu resmen kaldırıyor ve bunun yerine "tüm işlemleri sorgulamak" yerine, gerçekten usulsüzlük belirtileri gösteren işlemlere odaklanan risk tabanlı bir yönetim modeline geçişi sağlıyor. Ayrıca, büyük meblağlardaki paralar için, faturalar ve sözleşmeler gibi yasal kökenlerini kanıtlayan eksiksiz belgeleri saklamak, haklarınızı korumanın ve gereksiz sorunlardan kaçınmanın en iyi yoludur. İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. Çinli finans uzmanları, vatandaşlara mevcut sıkı denetim sürecinin öncelikle yaşlıları hedef alan mali dolandırıcılığı önlemeyi amaçladığını anlamaları gerektiğini tavsiye ediyor. Ana sayfa Ekonomi Yatırım - Finans Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. ÇİN - "Bu benim param, neden gönderemiyorum?", görünüşte basit bir soru olsa da, bankaların "kara para aklama karşıtı" ve "dolandırıcılık karşıtı" bahanesiyle büyük nakit işlemlerine yönelik kısıtlamaları giderek sıkılaştırması nedeniyle birçok Çin vatandaşı için baş ağrısı yaratıyor. VietNamNet•13/09/2026 Vietnam.vn'i takip et Google Vietnam.vn'i ekle Google 0 İki bavul dolusu nakit para ve "çıkmaz sokak" bir soru. Fotoğraf: Baidu Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Bay Li parasını geri çekme isteğini dile getirdiğinde, işlemin banka doğrulaması için geçici olarak askıya alınacağı kendisine bildirildi.</t>
+          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Ege Alternatif Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. ASAYİŞ Yayınlanma : 14 Eylül 2026 09:03 Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'de bir kapı imalat fabrikasında çıkan yangın tamamen söndürüldü. Yangının ardından fabrikanın durumu havadan görüntülendi. Yangın anında büyük hasar oluştu Düzce Gökçeköy mevkisinde bulunan Düzce Door isimli fabrikada, dün akşam 21.30 sıralarında başlayan yangın, içerideki kimyasal, ahşap ve plastik maddelerin etkisiyle hızla yayıldı ve tüm tesisi sardı. Yangın, 4 saatlik bir mücadelenin ardından kontrol altına alındı ve sabaha karşı tamamen söndürüldü. Detaylı inceleme yapılacak Fabrikanın son hali havadan görüntülenirken, yangının etkisiyle tamamen kullanılmaz hale geldiği ve bazı bölümlerden hala dumanların yükseldiği görüldü. İlerleyen saatlerde, yangının çıkış nedeni hakkında detaylı bir inceleme yapılması planlanıyor.</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article_dom</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWUdoUHJCRWZaZEdNanVFWHRsZFp3QnNMNWlEeWI0X3p4MEJSalFXY1YxcDN2cUNETm5tdl90cGpaVVJtSkp2WXRJajd6THVlNk9pOU5PODNLTl9KQXhhbV9QMTAxNmdrVTYtS09EZXR4N0lfci10azVOUjRINFJ2OE53enFLM3NpbXc4dlRDUkpTcF9aekFrNVNuaWRfUEhvNk5POXVJMkxhRlJaSkFfNA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>https://www.egealternatif.com/haber/duzce-deki-kapi-fabrikasindaki-yangin-havadan-goruntulendi_92660/</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>ve tüm tesisi</t>
+        </is>
+      </c>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr"/>
@@ -2827,7 +3039,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="n">
-        <v>90.5</v>
+        <v>104.25</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>3</v>
@@ -2836,27 +3048,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:02:22</t>
+          <t>2026-09-14 06:49:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>MASAK raporu</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede sondakika.com</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği egetelgraf.com</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2866,18 +3078,18 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
+          <t>masak</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Son Güncelleme: 13.09.2026 13:02 Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Gün ağarınca ortaya çıkan hasarın boyutu ise dronla görüntülendi. Gerede ilçesi Karma Organize Sanayi Bölgesi'ndeki geri dönüşüm tesisinde, dün saat 19.00 sıralarında yangın çıktı. Tesisi saran alevleri fark edenlerin ihbarı üzerine adrese itfaiye, AFAD ve jandarma ekipleri sevk edildi. Yangında yaralanan 2 işçi, sağlıkçıların olay yerindeki ilk müdahalesi sonrası ambulanslarla kaldırıldıkları hastanede tedaviye alındı. Yangın, ekiplerin 5 saatlik çalışması sonrası kontrol altına alındı. Gece boyu süren soğutma çalışmaları sonrası yangın, sabaha karşı tamamen söndürüldü. Hasarın boyutu da gün ağarınca ortaya çıktı. Tesiste oluşan hasar dronla görüntülendi. Yangının çıkış nedeninin belirlenmesi için soruşturma sürüyor. Kaynak: DHA BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Gün ağarınca ortaya çıkan hasarın boyutu ise dronla görüntülendi. Gerede ilçesi Karma Organize Sanayi Bölgesi'ndeki geri dönüşüm tesisinde, dün saat 19.00 sıralarında yangın çıktı. Tesisi saran alevleri fark edenlerin ihbarı üzerine adrese itfaiye, AFAD ve jandarma ekipleri sevk edildi. Yangında yaralanan 2 işçi, sağlıkçıların olay yerindeki ilk müdahalesi sonrası ambulanslarla kaldırıldıkları hastanede tedaviye alındı. Yangın, ekiplerin 5 saatlik çalışması sonrası kontrol altına alındı. Gece boyu süren soğutma çalışmaları sonrası yangın, sabaha karşı tamamen söndürüldü. Hasarın boyutu da gün ağarınca ortaya çıktı. Tesiste oluşan hasar dronla görüntülendi. Yangının çıkış nedeninin belirlenmesi için soruşturma sürüyor. Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Gün ağarınca ortaya çıkan hasarın boyutu ise dronla görüntülendi. Gerede ilçesi Karma Organize Sanayi Bölgesi'ndeki geri dönüşüm tesisinde, dün saat 19.00 sıralarında yangın çıktı. Tesisi saran alevleri fark edenlerin ihbarı üzerine adrese itfaiye, AFAD ve jandarma ekipleri sevk edildi. Yangında yaralanan 2 işçi, sağlıkçıların olay yerindeki ilk müdahalesi sonrası ambulanslarla kaldırıldıkları hastanede tedaviye alındı. Yangın, ekiplerin 5 saatlik çalışması sonrası kontrol altına alındı. Gece boyu süren soğutma çalışmaları sonrası yangın, sabaha karşı tamamen söndürüldü. Hasarın boyutu da gün ağarınca ortaya çıktı. Tesiste oluşan hasar dronla görüntülendi. Yangının çıkış nedeninin belirlenmesi için soruşturma sürüyor.</t>
+          <t>8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Güncel 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 14.09.2026 - 09:49 Okunma Süresi: 1 Dk İçişleri Bakanlığı, yasa dışı bahis organizasyonlarına yönelik 8 ilde kapsamlı operasyonlar gerçekleştirildiğini açıkladı. Mali Suçları Araştırma Kurulu (MASAK) raporları doğrultusunda yürütülen çalışmalarda, hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edilen 177 şüpheli hakkında adli işlem başlatıldı. 8 İLDE EŞ ZAMANLI OPERASYON Yasa dışı bahis suçuna yönelik operasyonlar 8 ilde düzenlendi. Ekiplerin çalışmaları kapsamında şüphelilerin banka hesapları ve para hareketleri mercek altına alındı. İzmirliler dikkat! Termometreler önce yükselecek, ardından sıcaklık hızla düşecek İçeriği Görüntüle MASAK RAPORLARI HAREKETLİLİĞİ ORTAYA ÇIKARDI Operasyonların önemli dayanaklarından biri MASAK tarafından hazırlanan raporlar oldu. Yapılan incelemelerde, şüphelilerin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği bulunduğu belirlendi. 177 ŞÜPHELİ HAKKINDA ADLİ İŞLEM Soruşturma kapsamında yasa dışı bahis faaliyetleriyle bağlantılı olduğu değerlendirilen 177 şüpheli hakkında adli işlem başlatıldı. Güvenlik güçlerinin operasyonlarla yasa dışı bahis ağlarına yönelik mücadelesini sürdürdüğü bildirildi. Kaynak: HABER MERKEZİ Editörün Seçtiği Aydın’da ayakta kalan üç kuleden biri! Zindanından hamamına eksiksiz Ege’nin 200 yıllık az bilinen tarihi şatosu Editörün Seçtiği Ne Efes ne Bergama! 5 bin yıllık değişimin tanığı: İzmir’in kayıp ada kentinde binlerce boncuk bulundu Editörün Seçtiği Ne Efes ne Bergama! İZBAN’dan inip kralların tepesine çıkılıyor: İzmir’de üç saraylı antik kenti çoğu kişi bilmiyor Editör Hakkında Kader Ergin Bunlar da ilgi</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede sondakika.com Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. Yangında yaralanan 2 işçinin hastanedeki tedavisi sürerken, tesisteki hasarın boyutu dronla görüntülendi. Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Son Güncelleme: 13.09.2026 13:02 Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü. BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Gün ağarınca ortaya çıkan hasarın boyutu ise dronla görüntülendi. Gerede ilçesi Karma Organize Sanayi Bölgesi'ndeki geri dönüşüm tesisinde, dün saat 19.00 sıralarında yangın çıktı. Tesisi saran alevleri fark edenlerin ihbarı üzerine adrese itfaiye, AFAD ve jandarma ekipleri sevk edildi. Yangında yaralanan 2 işçi, sağlıkçıların olay yerindeki ilk müdahalesi sonrası ambulanslarla kaldırıldıkları hastanede tedaviye alındı. Yangın, ekiplerin 5 saatlik çalışması sonrası kontrol altına alındı. Gece boyu süren soğutma çalışmaları sonrası yangın, sabaha karşı tamamen söndürüldü. Hasarın boyutu da gün ağarınca ortaya çıktı. Tesiste oluşan hasar dronla görüntülendi. Yangının çıkış nedeninin belirlenmesi için soruşturma sürüyor. Kaynak: DHA BOLU'nun Gerede ilçesinde dün, 5 saatte kontrol altına alınan geri dönüşüm tesisindeki yangın, sabaha karşı tamamen söndürüldü. Bolu Gerede'de geri dönüşüm tesisi yangını söndü, 2 işçi hastanede Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde dün akşam çıkan ve 5 saatte kontrol altına alınan yangın, sabaha karşı tamamen söndürüldü.</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği egetelgraf.com 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Güncel 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2887,69 +3099,33 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.sondakika.com/amp/haber-bolu-gerede-de-geri-donusum-tesisi-yangini-sondu-2-20233092/</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Gerede ilçesi Karma Organize Sanayi</t>
-        </is>
-      </c>
+          <t>https://www.egetelgraf.com/8-ilde-yasa-disi-bahis-operasyonu-masak-raporu-ortaya-cikardi-17-milyar-750-milyon-tllik-para-trafigi</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>de geri dönüşüm tesisi</t>
-        </is>
-      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>de geri dönüşüm tesisi Gerede ilçesi Karma Organize Sanayi Gerede Bolu Türkiye</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gerede Organize Sanayi Bölgesi | Gerede Deri İhtisas OSB | Gerede Deri Sanayi Sitesi | Gerede Ticaret Ve Sanayi Odası</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Gerede Organize Sanayi Bölgesi</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>38.46153846153846 | 47.82608695652174 | 51.06382978723404 | 38.46153846153846</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>Depo</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="n">
-        <v>192</v>
+        <v>112.75</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>4</v>
@@ -2958,27 +3134,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 17:46:00</t>
+          <t>2026-09-13 13:19:31</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>para aklama</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı 24 Saat Gazetesi Ankara</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -2988,86 +3164,58 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>depo, fabrika</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>fabrika | depo</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>www.24saatgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.24saatgazetesi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.24saatgazetesi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı SON DAKİKA: Bolu Gerede'de fabrika yangını... Geri dönüşüm deposu alev aldı, 1 işçi yaralandı 24 Saat Gazetesi Ankara www.24saatgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.24saatgazetesi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı.</t>
+          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://www.24saatgazetesi.com/son-dakika-bolu-geredede-fabrika-yangini-geri-donusum-deposu-alev-aldi-1-isci-yaralandi</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWUdoUHJCRWZaZEdNanVFWHRsZFp3QnNMNWlEeWI0X3p4MEJSalFXY1YxcDN2cUNETm5tdl90cGpaVVJtSkp2WXRJajd6THVlNk9pOU5PODNLTl9KQXhhbV9QMTAxNmdrVTYtS09EZXR4N0lfci10azVOUjRINFJ2OE53enFLM3NpbXc4dlRDUkpTcF9aekFrNVNuaWRfUEhvNk5POXVJMkxhRlJaSkFfNA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Geri dönüşüm deposu</t>
-        </is>
-      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>Geri dönüşüm deposu Gerede Bolu Türkiye</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>BOLPET PLAST GERİ DÖNÜŞÜM</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>BOLPET PLAST GERİ DÖNÜŞÜM</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>77.41935483870968</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="n">
-        <v>191.27</v>
+        <v>76.5</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>5</v>
@@ -3076,27 +3224,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 18:12:27</t>
+          <t>2026-09-13 14:33:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>para aklama</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı</t>
+          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı Türkiye Gazetesi</t>
+          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı surmelihaber.com</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3106,22 +3254,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>fabrika, tesis</t>
+          <t>banka, banka hesabı</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangın kısa sürede büyüyerek tesisi sardı. Zaman zaman patlamaların da yaşandığı yangın 4 saatin ardından kontrol altına alınırken, 2 fabrika işçisinin hafif şekilde yaralandığı öğrenildi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangın kısa sürede büyüyerek tesisi sardı. Zaman zaman patlamaların da yaşandığı yangın 4 saatin ardından kontrol altına alınırken, 2 fabrika işçisinin hafif şekilde yaralandığı öğrenildi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangın kısa sürede büyüyerek tesisi sardı. Zaman zaman patlamaların da yaşandığı yangın 4 saatin ardından kontrol altına alınırken, 2 fabrika işçisinin hafif şekilde yaralandığı öğrenildi. Giriş: 12 Eylül, 2026 - 21:12 | Güncelleme: 12 Eylül, 2026 - 23:15 Boluda geri dönüşüm fabrikası yanıyor! Alevler tüm tesisi sardı ÖNERİLEN HABERLER 3. SAYFA Antalya'da orman yangını! Ekipler bölgeye 2 saatte ulaşabildi 3. SAYFA Antalya'da orman yangını! Ekipler bölgeye 2 saatte ulaşabildi Editör : SİNEM GÖNEN | Kaynak: İHLAS HABER AJANSI Yayın Tarihi | 12 Eylül, 2026 - 21:12 Haberle İlgili Daha Fazlası 3. Sayfa Haber Verin Editör masamıza bilgi ve materyal göndermek için tıklayın Kaçırmayın Ücretsiz üye olun, gündemi şekillendiren gelişmeleri önce siz duyun Ev almak isteyenlere 3 milyon TL'ye kadar faizsiz ... Kaydet Togg'un yeni modeli T6X'e sürpriz talip! Piyasaya ... Kaydet Kâr payı oranlarında son durum: 500 bin TL’nin ayl... Kaydet Çiftçinin imdadına TMO yetişti! Tüccarın 2 katına ... Kaydet Alman Meclisi'ne Türkiye önerisi! "Ankara'nın hare... Kaydet İsmail Kapan Siyonist İsrail için alan daralıyor!.. Kaydet Rahim Er Yunanistan’ı düşman görmek! Kaydet Sevil Nuriyeva Siyasetin sabrı, devletin aklı Kaydet İsa Karakaş "Yarın bana kim bakacak?" sorusuna devlet sigortası! Kaydet Sadık Söztutan Evlat Kaydet 'Practical magic' yeniden geldi Kaydet Şampiyonlar Ligi'nde puan durumu belli oldu Kaydet 4.1 milyar liralık tarımsal destek ödemesi hesaplara yatıyor Kaydet TCBM ANKETİ YAYINLANDI! Kaydet Cari dengede temmuzda fazla verdi Kaydet Bize Haber Verin Editör masasıyla bilgi ve materyal paylaşma</t>
+          <t>Yozgat Bozok Üniversitesi Ziraat Fakültesi Dekanlığı, son dönemde üniversite öğrencilerini hedef alan banka hesabı ve IBAN dolandırıcılığı vakalarındaki artışa dikkat çekerek öğrencilere yasal uyarıda bulundu. Yozgat Bozok Üniversitesi Ziraat Fakültesi Dekanlığı, son dönemde üniversite öğrencilerini hedef alan banka hesabı ve IBAN dolandırıcılığı vakalarındaki artışa dikkat çekerek öğrencilere yasal uyarıda bulundu. Yozgat Bozok Üniversitesi Ziraat Fakültesi Dekanlığı, son dönemde üniversite öğrencilerini hedef alan banka hesabı ve IBAN dolandırıcılığı vakalarındaki artışa dikkat çekerek öğrencilere yasal uyarıda bulundu.</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı Bolu'da geri dönüşüm fabrikasında yangın! Alevler tüm tesisi sardı Türkiye Gazetesi Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangın kısa sürede büyüyerek tesisi sardı. Zaman zaman patlamaların da yaşandığı yangın 4 saatin ardından kontrol altına alınırken, 2 fabrika işçisinin hafif şekilde yaralandığı öğrenildi. Giriş: 12 Eylül, 2026 - 21:12 | Güncelleme: 12 Eylül, 2026 - 23:15 Boluda geri dönüşüm fabrikası yanıyor! Alevler tüm tesisi sardı ÖNERİLEN HABERLER 3. SAYFA Antalya'da orman yangını! Ekipler bölgeye 2 saatte ulaşabildi 3. Ekipler bölgeye 2 saatte ulaşabildi Editör : SİNEM GÖNEN | Kaynak: İHLAS HABER AJANSI Yayın Tarihi | 12 Eylül, 2026 - 21:12 Haberle İlgili Daha Fazlası 3. Kaydet Kâr payı oranlarında son durum: 500 bin TL’nin ayl... Kaydet Sevil Nuriyeva Siyasetin sabrı, devletin aklı Kaydet İsa Karakaş "Yarın bana kim bakacak?" sorusuna devlet sigortası!</t>
+          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı surmelihaber.com Yozgat Bozok Üniversitesi Ziraat Fakültesi Dekanlığı, son dönemde üniversite öğrencilerini hedef alan banka hesabı ve IBAN dolandırıcılığı vakalarındaki artışa dikkat çekerek öğrencilere yasal uyarıda bulundu.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -3131,27 +3279,19 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://www.turkiyegazetesi.com.tr/3-sayfa/boluda-geri-donusum-fabrikasi-yaniyor-alevler-tum-tesisi-sardi-1815590</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Antalya | Bolu</t>
-        </is>
-      </c>
+          <t>https://surmelihaber.com/gundem/yozgat-bozok-universitesinden-banka-hesabi-dolandiriciligi-uyarisi-25494h</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>geri dönüşüm fabrikası | Alevler tüm tesisi | sürede büyüyerek tesisi</t>
-        </is>
-      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr"/>
@@ -3165,7 +3305,7 @@
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
       <c r="AA7" s="2" t="n">
-        <v>118.75</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>6</v>
@@ -3174,7 +3314,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:11:09</t>
+          <t>2026-09-13 19:18:13</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3189,12 +3329,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti!</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı A Haber</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! duzcegazeteefsane.com</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -3214,12 +3354,12 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Bolu’nun Gerede ilçesindeki geri dönüşüm fabrikasında yangın çıktı. Bölgeye çok sayıda itfaiye ekipleri sevk edilirken, alevler kontrol altına alındı. 1 fabrika işçisi hafif şekilde yaralandı. Bolu’nun Gerede ilçesindeki geri dönüşüm fabrikasında yangın çıktı. Bölgeye çok sayıda itfaiye ekipleri sevk edilirken, alevler kontrol altına alındı. 1 fabrika işçisi hafif şekilde yaralandı. Bolu’nun Gerede ilçesindeki geri dönüşüm fabrikasında yangın çıktı. Bölgeye çok sayıda itfaiye ekipleri sevk edilirken, alevler kontrol altına alındı. 1 fabrika işçisi hafif şekilde yaralandı. Giriş Tarihi: 12 Eylül 2026 22:11 Son Güncelleme: 13 Eylül 2026 00:13 İHA | ahaber.com.tr Haber Merkezi Giriş Tarihi: 12 Eylül 2026 22:11 Son Güncelleme: 13 Eylül 2026 00:13 İHA | ahaber.com.tr Haber Merkezi Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında bilinmeyen nedenle yangın çıktı. Alevler kısa sürede fabrikanın büyük bölümüne yayılırken, olayda 1 işçi yaralandı. Yangın ekiplerin yoğun çalışmasının ardından kontrol altına alındı. Bolu 'nun Gerede Karma Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren geri dönüşüm tesisinde saat 19.00 sıralarında henüz belirlenemeyen nedenle yangın çıktı. Tesis içerisinde başlayan yangın, kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. (Foto: İHA) 1 İŞÇİ YARALANDI Durumun bildirilmesi üzerine olay yerine çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Olay yerine gelen itfaiye ekipleri, alevleri kontrol altına alabilmek amacıyla yoğun çalışma başlattı. Çıkan yangında 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi ambulansta yapılan tedavinin ardından hastaneye kaldırıldı. Foto: İHA YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Alevlerin tamamen sardığı fabrikada zaman zaman patlamaların da meydana geldiği bildirildi. Öte yandan, yangının boyutu ve ekiplerin bölgedeki müdahale çalışmaları yangının 4'üncü saatinde dronla da görüntülendi. Ayrıca, Bolu Valisi Abdulaziz Aydın ve Gerede Kaymakamı Fatih Kaya fabrikada incelemelerde bulunarak yetkililerden bilgi aldı. KONTROL ALTINA ALINDI Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır. Bölgede soğutma çalışmaları ile gerekli güvenlik tedbirleri aralıksız sürdürülmektedir." denildi. Bolu 'nun Gerede Karma Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren geri dönüşüm tesisinde saat 19.00 sıralarında henüz belirlenemeyen nedenle yangın çıktı. Tesis içerisinde başlayan yangın, kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. (Foto: İHA) 1 İŞÇİ YARALANDI Durumun bildirilmesi üzerine olay yerine çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Olay yerine gelen itfaiye ekipleri, alevleri kontrol altına alabilmek amacıyla yoğun çalışma başlattı. Çıkan yangında 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi ambulansta yapılan tedavinin ardından hastaneye kaldırıldı. Foto: İHA YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Alevlerin tamamen sardığı fabrikada zaman zaman patlamaların da meydana geldiği bildirildi. Öte yandan, yangının boyutu ve ekiplerin bölgedeki müdahale çalışmaları yangının 4'üncü saatinde dronla da görüntülendi. Ayrıca, Bolu Valisi Abdulaziz Aydın ve Gerede Kaymakamı Fatih Kaya fabrikada incelemelerde bulunarak yetkililerden bilgi aldı. KONTROL ALTINA ALINDI Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır. Bölgede soğutma çalışmaları ile gerekli güvenlik tedbirleri aralıksız sürdürülmektedir." denildi. Önceki Haber Sakarya'da akran zorbalığı: 15 yaşındaki çocuğu depoya kilitleyip dakikalarca dövdüler Sonraki Haber Muş'ta kahreden olay: 13 yaşındaki çocuk gölette boğuldu Önceki Haber Sakarya'da akran zorbalığı: 15 yaşındaki çocuğu depoya kilitleyip dakikalarca dövdüler Sonraki Haber Muş'ta kahreden olay: 13 yaşındaki çocuk gölette boğuldu Mobil uygulamalarımızı indirin Bolu'da geri dönüşüm fabrikasında yangın! Alevler kontrol altına alındı: 1 işçi yaralı Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. (Foto: İHA) Durumun bildirilmesi üzerine olay yerine çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Olay yerine gelen itfaiye ekipleri, alevleri kontrol altına alabilmek amacıyla yoğun çalışma başlattı. Çıkan yangında 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi ambulansta yapılan tedavinin ardından hastaneye kaldırıldı. YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Alevlerin tamamen sardığı fabrikada zaman zaman patlamaların da meydana geldiği bildirildi. Öte yandan, yangının boyutu ve ekiplerin bölgedeki müdahale çalışmaları yangının 4'üncü saatinde dronla da görüntülendi. Ayrıca, Bolu Valisi Abdulaziz Aydın ve Gerede Kaymakamı Fatih Kaya fabrikada incelemelerde bulunarak yetkililerden bilgi aldı. Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır. Bölgede soğutma çalışmaları ile gerekli güvenlik tedbirleri aralıksız sürdürülmektedir." denildi.</t>
+          <t>Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı Bolu'da geri dönüşüm fabrikasında yangın! Alevler kısa sürede yayıldı A Haber Bolu’nun Gerede ilçesindeki geri dönüşüm fabrikasında yangın çıktı. Bölgeye çok sayıda itfaiye ekipleri sevk edilirken, alevler kontrol altına alındı. 1 fabrika işçisi hafif şekilde yaralandı. Giriş Tarihi: 12 Eylül 2026 22:11 Son Güncelleme: 13 Eylül 2026 00:13 İHA | ahaber.com.tr Haber Merkezi Giriş Tarihi: 12 Eylül 2026 22:11 Son Güncelleme: 13 Eylül 2026 00:13 İHA | ahaber.com.tr Haber Merkezi Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında bilinmeyen nedenle yangın çıktı. Alevler kısa sürede fabrikanın büyük bölümüne yayılırken, olayda 1 işçi yaralandı. Yangın ekiplerin yoğun çalışmasının ardından kontrol altına alındı. Bolu 'nun Gerede Karma Organize Sanayi Bölgesi'nde (OSB) faaliyet gösteren geri dönüşüm tesisinde saat 19.00 sıralarında henüz belirlenemeyen nedenle yangın çıktı. Tesis içerisinde başlayan yangın, kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. Olay yerine gelen itfaiye ekipleri, alevleri kontrol altına alabilmek amacıyla yoğun çalışma başlattı. Çıkan yangında 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi ambulansta yapılan tedavinin ardından hastaneye kaldırıldı. Foto: İHA YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Alevlerin tamamen sardığı fabrikada zaman zaman patlamaların da meydana geldiği bildirildi. Öte yandan, yangının boyutu ve ekiplerin bölgedeki müdahale çalışmaları yangının 4'üncü saatinde dronla da görüntülendi. Ayrıca, Bolu Valisi Abdulaziz Aydın ve Gerede Kaymakamı Fatih Kaya fabrikada incelemelerde bulunarak yetkililerden bilgi aldı. KONTROL ALTINA ALINDI Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır. Önceki Haber Sakarya'da akran zorbalığı: 15 yaşındaki çocuğu depoya kilitleyip dakikalarca dövdüler Sonraki Haber Muş'ta kahreden olay: 13 yaşındaki çocuk gölette boğuldu Önceki Haber Sakarya'da akran zorbalığı: 15 yaşındaki çocuğu depoya kilitleyip dakikalarca dövdüler Sonraki Haber Muş'ta kahreden olay: 13 yaşındaki çocuk gölette boğuldu Mobil uygulamalarımızı indirin Bolu'da geri dönüşüm fabrikasında yangın! Alevler kontrol altına alındı: 1 işçi yaralı Bolu'nun Gerede ilçesinde bulunan geri dönüşüm fabrikasındaki yangın fabrikanın büyük bir bölümüne yayıldı. YANGIN DRONLA GÖRÜNTÜLENDİ Jandarma ekipleri ise bölgede güvenlik önlemi aldı. Bolu Valiliği yangına ilişkin yaptığı açıklamada "Gerede ilçemize bağlı Yazıkara köyü mülki sınırları içerisinde faaliyet gösteren bir fabrikanın deposunda, bugün saat 18.40 sıralarında meydana gelen yangın, ekiplerimizin yoğun ve koordineli müdahalesi sonucunda kontrol altına alınmıştır.</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! duzcegazeteefsane.com Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -3229,31 +3369,27 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.ahaber.com.tr/yasam/2026/09/12/boluda-geri-donusum-fabrikasinda-yangin</t>
+          <t>https://www.duzcegazeteefsane.com/asayis-duzce-haberleri/15389-duzcede-gece-yarisi-korku-dolu-anlar:-fabrikada-cikan-yangin-gokyuzunu-alevlere-teslim-etti!</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Bolu | Muş | Sakarya</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>nun Gerede Karma Organize Sanayi</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Kısa sürede tüm tesisi</t>
+        </is>
+      </c>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr"/>
@@ -3267,7 +3403,7 @@
       <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" s="2" t="n">
-        <v>126.75</v>
+        <v>130.07</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>7</v>
@@ -3276,7 +3412,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:09:34</t>
+          <t>2026-09-13 21:12:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3291,12 +3427,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı.</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. Vietnam.vn</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -3316,48 +3452,84 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. Vietnam.vn</t>
+          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Val... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. 5 SAAT SÜREN ZORLU MÜCADELE Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı 5 SAAT SÜREN ZORLU MÜCADELE BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. 13 Eyl 2026 - 12:55 Bolu - Asayiş Yazdır Yorum yazarak Bolu Gündem Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yorumlarda</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı. Vietnam.vn An Khanh beldesindeki bir fabrikada çıkan yangın, 50'den fazla subay ve asker tarafından kontrol altına alındı.</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. 5 SAAT SÜREN ZORLU MÜCADELE Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı 5 SAAT SÜREN ZORLU MÜCADELE BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. 13 Eyl 2026 - 12:55 Bolu - Asayiş Yazdır Yorum yazarak Bolu Gündem Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQZUNZRWJSaW1nVkNPSkJxUW5VV2NtcXBHX0tjWEdoWm5kSG1rM3NLaW9QeE54V3ZucEp6Mm13eERSRThmbG12U2cxdG9NTDJWdTBaUTRvM2dGMU5DOVRsUGxndUtGUGNGczg0VVhtSjkxWDAyVFBRNS1QbTRLcWdSQ3RxRFlPVXpCYmo4eE9aS1FQMUU?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
+          <t>https://www.bolugundem.com/haber/28691580/boluda-5-saatlik-yangin-kabusu-geri-donusum-fabrikasi-alevlere-teslim-oldu-3-kisi-yaralandi</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>00 sıralarında Karma Organize Sanayi</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Geri dönüşüm fabrikası | başlayan ve tesisi</t>
+        </is>
+      </c>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr"/>
-      <c r="V9" s="2" t="inlineStr"/>
-      <c r="W9" s="2" t="inlineStr"/>
+          <t>firma yok</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>Geri dönüşüm fabrikası 00 sıralarında Karma Organize Sanayi Gerede Bolu Türkiye</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Nova Orman Ürünleri - Bolu Fabrika | İlamet Metal Ltd Şti | An-Ker-San Kereste Fabrikası Gerede OSB</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Nova Orman Ürünleri - Bolu Fabrika</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr"/>
-      <c r="Z9" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>51.851851851851855 | 35.8974358974359 | 58.064516129032256</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>Gerede Organize Sanayi Bölgesi | Gerede Deri İhtisas OSB</t>
+        </is>
+      </c>
       <c r="AA9" s="2" t="n">
-        <v>103.22</v>
+        <v>220.5</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>8</v>
@@ -3366,12 +3538,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 05:48:46</t>
+          <t>2026-09-13 19:45:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3381,12 +3553,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti Eskişehir Durum</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3396,18 +3568,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir’de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle diğer alanlara sıçramadan kontrol altına alınarak söndürüldü. Eskişehir’de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle diğer alanlara sıçramadan kontrol altına alınarak söndürüldü. Eskişehir’de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle diğer alanlara sıçramadan kontrol altına alınarak söndürüldü.</t>
+          <t>Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. 13 Eylül 2026 - 22:45 - Güncellenme: 13 Eylül 2026 - 23:29 G: 13 Eylül 2026 - 23:29 Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. Editör Haber Merkezi 0 Paylaşım 0 Paylaşım Google Kaynaklara Ekle A − A + Düzce'de Door Kapı Fabrikası'nda çıkan yangın fabrikanın geniş bir bölümüne yayıldı. Yangının büyüklüğü nedeniyle Düzce'nin ilçelerinden itfaiye ekipleri bölgeye yönlendirilirken, Bolu'dan da takviye ekip sevk edildi. Edinilen bilgilere göre yangın saat 21.40 sıralarında henüz belirlenemeyen bir nedenle çıktı. Kısa sürede yayılan alevlerin ardından bölgeye çok sayıda itfaiye, sağlık ve güvenlik ekibi gönderildi. Bolu'dan takviye ekip sevk edildi Yangının geniş bir alana yayılması üzerine Düzce'nin ilçelerindeki itfaiye ekipleri de bölgeye yönlendirildi. Söndürme çalışmalarına destek amacıyla Bolu'dan takviye ekip sevk edildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. Yangının boyutu dronla görüntülendi Door Kapı Fabrikası'ndaki yangın dronla havadan görüntülendi. Havadan kaydedilen görüntülerde fabrikanın büyük bölümünü saran alevler ile bölgeden yükselen yoğun duman yer aldı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Yangının çıkış nedeninin, söndürme çalışmalarının ardından yapılacak incelemeyle belirlenmesi bekleniyor. Düzce / Merkez #düzce yangın #düzce fabrika yangını #düzce door yangın Y</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti Eskişehir’de Tesis Yangını: Ekipler Hızla Müdahale Etti Eskişehir Durum Eskişehir’de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle diğer alanlara sıçramadan kontrol altına alınarak söndürüldü.</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. 13 Eylül 2026 - 22:45 - Güncellenme: 13 Eylül 2026 - 23:29 G: 13 Eylül 2026 - 23:29 Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -3417,23 +3593,27 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://eskisehirdurum.com/eskisehir-gundem/eskisehirde-tesis-yangini-ekipler-hizla-mudahale-etti/804268</t>
+          <t>https://www.duzcehurhaber.com/duzcede-kapi-fabrikasinda-buyuk-yangin-alevler-sehrin-ust-kesimlerinden-goruldu-4205470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir</t>
+          <t>Bolu</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>deki Door Kapı Fabrikası</t>
+        </is>
+      </c>
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr"/>
@@ -3447,7 +3627,7 @@
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="n">
-        <v>67.73999999999999</v>
+        <v>119.25</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>9</v>
@@ -3456,7 +3636,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:04:00</t>
+          <t>2026-09-13 11:41:26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -3471,12 +3651,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü</t>
+          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Milli İrade Gazetesi</t>
+          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü kocatepegazetesi.com</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3492,12 +3672,12 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. ASAYİŞ Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 13.09.2026 - 12:04 Eskişehir’de faaliyet gösteren bir geri dönüşüm tesisinde çıkan yangın, Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekiplerinin müdahalesiyle çevre alanlara sıçramadan kontrol altına alınarak söndürüldü. Yangının çıkış nedeninin belirlenmesi amacıyla inceleme başlatıldı. Eskişehir'de sanayi alanında faaliyet yürüten bir geri dönüşüm tesisinde henüz belirlenemeyen bir sebepten dolayı yangın meydana geldi. Dumanları Görenler İhbar Etti Tesis içerisindeki malzemelerin alev almasıyla birlikte yükselen yoğun dumanları fark eden çevredeki vatandaşlar ve tesis çalışanları durumu 112 Acil Çağrı Merkezi'ne bildirdi. İhbar üzerine bölgeye kısa sürede polis ve itfaiye ekipleri sevk edildi. Alevler Sıçramadan Kontrol Altına Alındı Olay yerine ulaşan Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekipler, yangına çok yönlü olarak müdahalede bulundu. İtfaiye personelinin yürüttüğü yoğun ve koordineli çalışma neticesinde alevler tesisin diğer bölümlerine ve çevredeki yapılara sıçramadan söndürüldü. Yangın sonrası soğutma çalışmaları tamamlanırken, olayda yaralanan ya da dumandan etkilenen kimsenin olmadığı öğrenildi. Çıkış Nedeni Araştırılıyor Yangının ardından tesis içerisinde oluşan maddi hasarın tespiti yapılırken, yangının çıkış kaynağı ve sebebinin netleştirilmesi amacıyla yetkililer tarafından geniş çaplı inceleme başlatıldı. Kaynak: Haber Merkezi Bunlar</t>
+          <t>Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Haberler Asayiş Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. asayiş PAYLAŞ 13.09.2026 14:41 Güncelleme: 13.09.2026 14:41 İHA İhlas Haber Ajansı TAKİP ET Kocatepe Gazetesi kaynağını Google'da tercih edilen kaynak olarak ekleyin! Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. asayiş İHA PAYLAŞ İlk Yorum Yazan Sen Ol! Kocatepe Gazetesi - Bizi Sosyal Medyada Takip Edin! Facebook X.com Instagram Bakmadan Geçme Başkan Demirci’den ‘Öğretmen Emeği’ Vurgusu Başkan Arslan Takdir Etti; Taleplerini Gündeme Getirdi Bilgi Ailesinin Acı Günü: Hasibe Bilgi Vefat Etti Afyon'un Komşusu O İlde Milletvekili Vali'den Şikayetçi: Vekil Ankara'dan Koruma Talep Etti Afyon'da Seçim Gündemi Hareketleniyor. Ticaret Borsası'nda Mühsürler'e Muhalif Hareketlenme Okullar Açılırken Önemli Uyarı: Bu Ürünler Denetlenmeli Haberler Asayiş Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. asayiş PAYLAŞ 13.09.2026 14:41 Güncelleme: 13.09.2026 14:41 İHA İhlas Haber Ajansı TAKİP ET Kocatepe Gazetesi kaynağını Google'da tercih edilen kaynak olarak ekleyin! Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. asayiş İHA PAYLAŞ İlk Yorum Yazan Sen Ol! Kocatepe Gazetesi - Bizi Sosyal Medyada Takip Edin! Facebook X.com Instagram Bakmadan Geçme Başkan Demirci’den ‘Öğretmen Emeği’ Vurgusu Başkan Arslan Takdir Etti; Taleplerini Gündeme Getirdi Bilgi Ailesinin Acı Günü: Hasibe Bilgi Vefat Etti Afyon'un Komşusu O İlde Milletvekili Vali'den Şikayetçi: Vekil Ankara'dan Koruma Talep Etti Afyon'da Seçim Gündemi Hareketleniyor. Ticaret Borsası'nda Mühsürler'e Muhalif Hareketlenme Okullar Açılırken Önemli Uyarı: Bu Ürünler Denetlenmeli Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü https://www.kocatepegazetesi.com/geri-donusum-tesisinde-korkutan-yangin-alevler-buyumeden-sonduruldu/409832/ Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. Yukarıdaki arama formları aracılığı ile Kocatepe Gazetesi arşivinde kelime, içerik, konu araması yapabilir veya gün-ay-yıl formatında tarih girerek tarihe göre haberleri listeleyebilirsiniz.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Milli İrade Gazetesi Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü. ASAYİŞ Geri Dönüşüm Tesisinde Çıkan Yangın İtfaiye Ekiplerince Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, Büyükşehir Belediyesi itfaiye ekiplerinin hızlı müdahalesiyle büyümeden kontrol altına alınarak söndürüldü.</t>
+          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü kocatepegazetesi.com Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Haberler Asayiş Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. Facebook X.com Instagram Bakmadan Geçme Başkan Demirci’den ‘Öğretmen Emeği’ Vurgusu Başkan Arslan Takdir Etti; Taleplerini Gündeme Getirdi Bilgi Ailesinin Acı Günü: Hasibe Bilgi Vefat Etti Afyon'un Komşusu O İlde Milletvekili Vali'den Şikayetçi: Vekil Ankara'dan Koruma Talep Etti Afyon'da Seçim Gündemi Hareketleniyor. Ticaret Borsası'nda Mühsürler'e Muhalif Hareketlenme Okullar Açılırken Önemli Uyarı: Bu Ürünler Denetlenmeli Haberler Asayiş Geri Dönüşüm Tesisinde Korkutan Yangın! Ticaret Borsası'nda Mühsürler'e Muhalif Hareketlenme Okullar Açılırken Önemli Uyarı: Bu Ürünler Denetlenmeli Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü https://www.kocatepegazetesi.com/geri-donusum-tesisinde-korkutan-yangin-alevler-buyumeden-sonduruldu/409832/ Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Geri Dönüşüm Tesisinde Korkutan Yangın!</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -3507,15 +3687,19 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.milliirade.com/geri-donusum-tesisinde-cikan-yangin-itfaiye-ekiplerince-sonduruldu</t>
+          <t>https://www.kocatepegazetesi.com/geri-donusum-tesisinde-korkutan-yangin-alevler-buyumeden-sonduruldu/409832/</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>Ankara | Eskişehir | Manisa</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Demirci</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -3523,7 +3707,7 @@
       <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr"/>
@@ -3537,7 +3721,7 @@
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="n">
-        <v>95.75</v>
+        <v>115.25</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>10</v>
@@ -3546,27 +3730,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 03:22:15</t>
+          <t>2026-09-14 09:11:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>kara para</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı bolgegundemi.com</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3576,22 +3760,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Demirtaş Mahallesi'nde saman deposu yangını Alanya'nın Demirtaş Mahallesi'ndeki bir depolama alanında çıkan yangında çok sayıda saman balyası yandı. İtfaiyenin müdahalesiyle alevler söndürüldü. 14.09.2026 - 12:11 Yayınlanma Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Alanya’da 75 bin öğrenci derslere başlıyor İçeriği Görüntüle Alanya'nın Demirtaş Mahallesi'nde yer alan bir saman depolama alanında henüz belirlenemeyen bir nedenle yangın çıktı. Çevredekilerin ihbarı üzerine, olay yerine hızla Antalya Büyükşehir Belediyesi Alanya İtfaiye Müdürlüğü ekipleri sevk edildi. İtfaiye personelinin zamanında müdahalesi sayesinde alevler daha geniş bir alana yayılmadan kontrol altına alındı. Yerel haber kaynaklarının aktardığına göre, söndürme işlemlerinin ardından depolama alanında bulunan çok sayıda saman balyası yandı. SOĞUTMA VE İNCELEME SÜRECİ BAŞLADI Bölgede alevlerin tamamen bastırılmasının ardından itfaiye ekipleri tarafından bir süre daha soğutma çalışmaları gerçekleştirildi. Yangının tam olarak hangi sebeple başladığını tespit etmek amacıyla ilgili birimler tarafından resmi inceleme süreci başlatıldı. TARIMSAL DEPOLAMADA GÜVENLİK ÖNLEMİ Saman balyası gibi kuru tarım ürünlerinin istiflendiği alanlar, materyalin yapısı gereği yüksek tutuşma potansiyeli barındırıyor. Bu tür depolama noktalarında yeterli havalandırmanın sağlanması ve temel yangın söndürme teçhizatının bulundurulması, olası maddi kayıpların büyümesini engellemek için standart bir gereksinim olarak öne çıkıyor. Kaynak: Haber Merkezi Editörün Seçtiği Antalya S Tipi Cezaevi'nde işkence iddiası Meclis'e taşındı Editörün Seçtiği 5 milyon TL’de mevduat ve konut hesabı değişti Editörün Seçtiği 10 Yaşındaki İki Arkadaş Limonata Satarak Harçlık Biriktiriyor Bunlar da</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı Otomatik Finansal Paylaşımda Banka Ve Elden Yatırım Farkı bolgegundemi.com www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Demirtaş Mahallesi'nde saman deposu yangını Alanya'nın Demirtaş Mahallesi'ndeki bir depolama alanında çıkan yangında çok sayıda saman balyası yandı. İtfaiyenin müdahalesiyle alevler söndürüldü. 14.09.2026 - 12:11 Yayınlanma P</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -3601,33 +3785,65 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bolgegundemi.com/ekonomi/otomatik-finansal-paylasimda-banka-ve-elden-yatirim-farki-176836.html</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
+          <t>https://www.yenialanya.com/demirtas-mahallesinde-saman-deposu-yangini</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Antalya | Bursa</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Alanya</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş | Demirtaş Mahallesi | saman deposu yangını Demirtaş Mahallesi | Yeni Alanya Alanya Demirtaş Mahallesi | nın Demirtaş Mahallesi</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>nde saman deposu</t>
+        </is>
+      </c>
       <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr"/>
-      <c r="V12" s="2" t="inlineStr"/>
-      <c r="W12" s="2" t="inlineStr"/>
+          <t>firma yok</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>nde saman deposu Demirtaş Alanya Antalya Türkiye</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Toptancı Hali</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Toptancı Hali</t>
+        </is>
+      </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>36.8421052631579</t>
+        </is>
+      </c>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="n">
-        <v>50.46</v>
+        <v>174.25</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>11</v>
@@ -3636,27 +3852,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:03:05</t>
+          <t>2026-09-13 20:07:54</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı A Haber</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Turizm Aktüel</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -3666,18 +3882,22 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>depo, turizm</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Cumhuriyet Başsavcılığının soruşturmasında MASAK verileri incelendi; 6 derneğe 2011-2026 döneminde yurt dışı bağlantılı milyonluk para girişleri ve 209 kurumsal transfer tespit edildi. İstanbul Cumhuriyet Başsavcılığının soruşturmasında MASAK verileri incelendi; 6 derneğe 2011-2026 döneminde yurt dışı bağlantılı milyonluk para girişleri ve 209 kurumsal transfer tespit edildi. İstanbul Cumhuriyet Başsavcılığının soruşturmasında MASAK verileri incelendi; 6 derneğe 2011-2026 döneminde yurt dışı bağlantılı milyonluk para girişleri ve 209 kurumsal transfer tespit edildi. AYNI KAYNAKLAR BİRDEN FAZLA DERNEĞİ FONLADI Üç dosyanın birlikte incelenmesi, bazı yabancı kaynakların birden fazla derneğe düzenli olarak para gönderdiğini ortaya koydu. EED/FEDEM'in HEVİ, LİSTAG ve SPoD'a 16 işlemde toplam 315 bin 278,23 euro gönderdiği belirlendi. İşlemlerin transfer tarihlerindeki toplam TL karşılığı yaklaşık 11,38 milyon lira olarak hesaplandı. ILGA-Europe'un HEVİ, Lambdaİstanbul, LİSTAG ve SPoD'a 37 işlemde toplam 234 bin 221,17 euro aktardığı kaydedildi. Bu işlemlerin TL karşılığının yaklaşık 7,69 milyon lira olduğu belirtildi. Diğer ortak finansman kaynakları ise şöyle sıralandı: Almanya Federal Cumhuriyeti ve Başkonsolosluğu: LİSTAG ve SPoD'a 9 işlemde 104 bin 98,92 euro Hollanda Dışişleri Bakanlığı: LİSTAG ve SPoD'a en az 5 işlemde 89 bin 687 euro ve 276 bin 500 lira ABD Dışişleri Bakanlığı: Pozitif- z ve SPoD'a 6 işlemde 45 bin 984,02 dolar Fransa Büyükelçiliği: HEVİ, Pozitif İz ve SPoD'a 4 işlemde 25 bin 706 euro German Marshall Fund: LİSTAG, Pozitif Yaşam ve SPoD'a 3 işlemde 63 bin 347 dolar International AIDS Society: Pozitif İz ve SPoD'a 6 işlemde 32 bin 320 dolar SWIFT KAYITLARINDA 3,3 MİLYON DOLARI AŞAN TRAFİK MASAK Veri İnceleme Tutanağındaki GİB SWIFT kayıtlarında, derneklerin farklı yıllara yayılan yurt dışı bağlantılı hesap hareketlerinin dolar karşılıklarına da yer verildi. Dernek İncelenen dönem Rapordaki toplam dolar karşılığı SPoD2012-2026 1.570.692,44 dolar HEVİ2018-2026 762.939,21 dolar Pozitif Yaşam-2011-20255 18.525,92 dolar LİSTAG2020-2026 314.220,89 dolar Lambdaİstanbul-2012-2026 103.650,93 dolar Pozitif İz-2022-2026 89.138,41 dolar Toplam3.359.167,80 dolar Böylece 6 derneğe ait GİB SWIFT kayıtlarında yer alan para hareketlerinin dolar karşılığı toplamı 3 milyon 359 bin 167,80 dolara ulaştı. Bu toplam, farklı yıllarda ve farklı para birimleriyle gerçekleştirilen işlemlerin tutanaktaki dolar karşılıklarından oluşuyor. 2021-2026 dönemine ilişkin 67,4 milyon liralık bankacılık analiziyle aynı kapsamı taşımadığı için iki rakamın birbirine eklenmemesi gerekiyor. PARA TRAFİĞİ 2011'E KADAR UZANDI SWIFT kayıtları, yurt dışı bağlantılı finansmanın yalnızca son yıllarla sınırlı olmadığını ortaya koydu. Pozitif Yaşam Derneğinin 2011, Lambdaİstanbul ile SPoD'un 2012 yılına kadar uzanan transfer kayıtları bulunduğu belirlendi. Eski kayıtlarda Pozitif Yaşam'a Avrupa Komisyonundan 47 bin 996,94 dolar, UNDP'den 2 bin 500 dolar ve Deutsche Gesellschaft bağlantılı kayıtlardan 5 işlemde 124 bin 786,02 dolar gönderildiği görüldü. SPoD'a ABD Dışişleri Bakanlığından farklı yıllarda 9 işlemle 113 bin 591,62 dolar, ILGA-Europe'tan 15 işlemle 61 bin 403,14 dolar ve EED/FEDEM'den 9 işlemle 167 bin 207,74 dolar aktarıldığı kaydedildi. MASAK TUTANAĞINDA ÇARPICI DEĞERLENDİRME MASAK verileri üzerinde hazırlanan inceleme tutanağında, söz konusu derneklere yurt dışı bağlantılı kişi ve kuruluşlar tarafından maddi destek sağlandığı belirtildi. Tutanakta, bu kaynaklar aracılığıyla cinsiyet değiştirmek isteyen kişilerin ameliyat masraflarının karşılandığı yönünde değerlendirmeye yer verildi. Derneklerin faaliyetleri dışında toplumsal yapının bozulmasına, toplum içerisinde görüş ayrılıklarının oluşmasına, aileler arasında kaygı meydana gelmesine, kamu düzeni ile toplumsal değerlere zarar verilmesine yönelik çalışmalar yürüttüğü iddiası da soruşturma kapsamında kayda geçirildi. Söz konusu ifadeler, soruşturma dosyasındaki inceleme ve değerlendirmeleri yansıtıyor. DERNEK HESAPLARINA MÜKERRER PARA AKIŞI Gerçek kişilerden yapılan para girişlerinin incelendiği ayrı analizde, gönderenlerin T.C. kimlik numarası kayıtları esas alındı ve aynı kişiye ait isim farklılıkları birleştirildi. En fazla işlem yapan isim, Lambdaİstanbul ile SPoD'a toplam 72 kez para gönderen Abdullah İkbal Arslanbaş oldu. Arslanbaş adına 37'si Lambda İstanbul'a, 35'i SPoD'a olmak üzere toplam 11 bin 535 liralık transfer kaydı bulundu. En fazla mükerrer işlem yapan kişiler şöyle sıralandı: Gönderen İşlem Toplam Dernek Abdullah İkbal Arslanbaş 72 11.535 TL Lambdaİstanbul ve SPoD Yasemin Öz 56 3.010 TL Lambdaİstanbul ve SPoD Aslı Meleş 54 25.324 TL LİSTAG Anıl Birkan 44 39.550 TL Pozitif İz Günseli Dum 40 5.680 TL LİSTAG Abdulkadir Öner Ceylan 38 21.146 TL Lambdaİstanbul ve LİSTAG Mesude Demirağ 36 46.600 TL LİSTAG Serpil Bilgin 33 7.510 TL LİSTAG Rezan Bekiroğlu 30 6.000 TL LİSTAG Cüneyt Orhan Yurtsever 28 8.400 TL LİSTAG Figen Yılmaz 27 21.800 TL LİSTAG Hasan Metehan Özkan 25 26.528,64 TL LİSTAG ve SPoD Can Candan 21 20.250 TL LİSTAG Osman Elbek 20 20.000 TL LİSTAG Yağmur Arığ 20 11.000 TL LİSTAG ve SPoD BİRDEN FAZLA DERNEĞE PARA GÖNDERENLER Aynı gerçek kişilerin birden fazla derneğin hesabında görülmesi de incelemede dikkat çeken başlıklardan biri oldu. Necla İclal Küneralp'in Lambda İstanbul'a 20 bin, LİSTAG'a 40 bin olmak üzere toplam 60 bin lira gönderdiği belirlendi. Turgay Bayındır'ın Lambdaİstanbul ve SPoD'a 19 işlemle toplam 52 bin 670 lira, Esra Banu Çırak'ın Lambdaİstanbul ile LİSTAG'a 40 bin lira aktardığı kaydedildi. Mihael Nahmias'ın Pozitif Yaşam ile Pozitif İz'e toplam 40 bin lira, Hasan Metehan Özkan'ın LİSTAG ile SPoD'a 25 işlemle 26 bin 528,64 lira gönderdiği tespit edildi. Abdulkadir Öner Ceylan'ın iki derneğe 38 işlemle 21 bin 146 lira, Abdullah İkbal Arslanbaş'ın ise iki derneğe 72 işlemle toplam 11 bin 535 lira aktardığı belirtildi. HEARTSTOPPER'IN YAZARI DA KAYITLARDA Gerçek kişilerden gelen transferler ile açık kaynak kayıtlarının karşılaştırıldığı analizde uluslararası alanda tanınan isimlerin de bulunduğu görüldü. MASAK kaydında karşı tarafın doğrudan "ALICE OSEMAN AUTHOR" olarak yer aldığı belirtildi. İngiltere'deki TSB Bank PLC London üzerinden Lambda İstanbul'a 663,37 sterlin gönderildiği ve işlem açıklamasında "DONATION OTHER" ifadesinin bulunduğu kaydedildi. İşlemin transfer tarihindeki TL karşılığı 12 bin 277,72 lira olarak hesaplandı. "Author" ibaresi, İngiltere bağlantısı ve ayırt edici isim nedeniyle kaydın, Heartstopper serisinin yaratıcısı, yazar ve senarist Alice Oseman ile eşleşme seviyesinin son derece yüksek olduğu değerlendirildi. SWIFT inceleme tutanağında aynı isme ait 2022 tarihli işlemin dolar karşılığı ise 904,10 dolar olarak yer aldı. TANINMIŞ İSİMLERİN TRANSFERLERİ Belgesel yönetmeni ve akademisyen Can Candan adına LİSTAG'a 21 ayrı işlemle toplam 20 bin 250 lira gönderildiği belirlendi. İşlem açıklamalarında düzenli şekilde "bağış", bir işlemde ise "aidat" ifadesinin bulunduğu kaydedildi. Oyuncu Ayça Damgacı adına LİSTAG hesabına tek işlemle 28 bin 513 lira aktarıldı. Ancak bu işlem "bağış" değil, "iade" açıklamasıyla kayıtlara geçti. Derya Seyhan Arman adına Lambda İstanbul'a 12 ayrı işlemle toplam 6 bin lira gönderildiği belirtildi. Banka kayıtlarında karşı tarafın "Derya Arman" , işlem açıklamalarında ise "Seyhan Arman" olarak yer aldığı aktarıldı. Hekim Osman Elbek adına LİSTAG'a 20 ayrı işlemle toplam 20 bin lira gönderildiği ve işlemlerde "bağış" açıklamasının bulunduğu kaydedildi. Çevirmen Amy Marie Spangler adına Lambda İstanbul'a 12 işlemle toplam 19 bin 700 lira gönderildi. Bazı işlemlerin açıklamasında doğrudan "bağış" ifadesinin yer aldığı belirtildi. Akademisyen Şemsa Özar adına SPoD'a "bağış" açıklamasıyla 5 bin liralık işlem bulunduğu kaydedildi. Ancak analizde, banka kaydındaki kişi ile kamuoyunca tanınan ismin aynı olduğunu gösteren ikinci bir kişisel tanımlayıcı bulunmadığı için bu eşleşmenin ihtiyatla değerlendirilmesi gerektiği vurgulandı. DERNEK YÖNETİCİLERİNDEN DERNEK HESAPLARINA PARA Bazı transfer sahiplerinin para gönderdikleri derneklerde yönetici veya çalışan olarak görev yaptığına ilişkin açık kaynak kayıtlarına da ulaşıldı. SPoD'un eski iletişim koordinatörü olarak eşleştirilen Erkan Çıvak adına iki bağış işleminde toplam 72 bin 830 lira para girişi bulundu. SPoD'un eski yönetim kurulu başkanı olduğu belirtilen Müge Akbasan adına 15 işlemle 49 bin 119,50 lira aktarıldı. Bu tutarın en az 35 bin 869,50 liralık bölümünün bağış veya aidat açıklaması taşıdığı kaydedildi. Derneğin yönetiminde sayman olarak yer aldığı belirtilen Ali Erdoğan adına 5 işlemle 39 bin 275,18 lira, Anıl Kocaoğulları adına ise 6 işlemle 24 bin 120 lira para girişi tespit edildi. SPoD'un denetleme kurulunda yer aldığı belirtilen Abdullah İkbal Arslanbaş, 72 işlemle gerçek kişiler arasındaki en yüksek transfer sayısına ulaştı. HER PARA GİRİŞİ BAĞIŞ DEĞİL Belgelerde, hesaplara giren brüt tutarların tamamının bağış olarak değerlendirilmemesi gerektiğine dikkat çekildi. HEVİ bağlantılı Osman Doğan adına 9 işlemle 101 bin 406,68 liralık brüt para girişi bulundu. Ancak bu tutarın 100 bin 206,68 liralık bölümünün huzur hakkı iadesi niteliğinde olduğu, bağış ve aidat olarak değerlendirilen kısmın yaklaşık bin 200 lira olduğu belirtildi. Zafer Rıfat Irmak adına görünen 93 bin 237,41 liralık para girişinin de 89 bin 853,41 liralık bölümünün huzur hakkı iadesi olduğu kaydedildi. Furkan Yurt adına görünen 61 bin liralık iki işlemin 60 bin liralık kısmının "maaş avans iadesi" açıklaması taşıdığı tespit edildi. Ayça Damgacı adına kaydedilen 28 bin 513 liralık işlem ile Selim Gültepe adına görünen 45 bin liralık işlemin de iade niteliğinde olduğu belirtildi. SORUŞTURMADA PARA TRAFİĞİ MERCEK ALTINDA Üç dosyanın birlikte değerlendirilmesi sonucunda, 6 derneğe uzanan yabancı finansman ağında uluslararası kuruluşların yanı sıra ABD Dışişleri Bakanlığı, Hollanda Dışişleri Bakanlığı, Almanya ve Fransa'nın diplomatik temsilcilikleri gibi yabancı kamu kurumlarının da bulunduğu tespit edildi. MASAK Veri İnceleme Tutanağında yer alan değerlendirmeler ile para transferlerinin hangi faaliyetlerde kullanıldığına ilişkin iddialar, İstanbul Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında inceleniyor. Belgelerde adı geçen kişiler ile kuruluşlar hakkındaki kayıtlar para transferlerini gösterirken, söz konusu hareketler tek başına suçun kesinleştiği anlamına gelmiyor. Dosyadaki iddia ve değerlendirmelere ilişkin adli süreç devam ediyor. Sosyal medyadaki sapkın içeriklere erişim engeli kararı! SOSYAL MEDYADAKİ SAPKIN İÇERİKLERE ERİŞİM ENGELİ KARARI! #MASAK LGBTİ Dernekleri Raporu #İstanbul Cumhuriyet Başsavcılığı LGBTİ Soruşturması Giriş Tarihi: 13 Eylül 2026 12:03 Son Güncelleme: 13 Eylül 2026 13:15 ahaber.com.tr Haber Merkezi Giriş Tarihi: 13 Eylül 2026 12:03 Son Güncelleme: 13 Eylül 2026 13:15 ahaber.com.tr Haber Merkezi İstanbul Cumhuriyet Başsavcılığının soruşturması kapsamında incelenen MASAK verileri, 6 LGBT derneğinin yurt dışı bağlantılı para trafiğini ortaya çıkardı. GİB SWIFT kayıtlarında derneklere gönderilen paranın dolar karşılığı 3 milyon 359 bin doları aşarken, 2021-2026 dönemindeki 209 yabancı kurumsal transferin işlem tarihlerindeki TL karşılığı 67,4 milyon liraya ulaştı. Para trafiğinde yabancı devlet kurumları, diplomatik misyonlar, uluslararası kuruluşlar ve bazı tanınmış isimler yer aldı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında gönderilen Mali Suçları Araştırma Kurulu verileri üzerinde yapılan inceleme, İstanbul merkezli 6 LGBT derneğinin yurt içi ve yurt dışı bağlantılı hesap hareketlerini gözler önüne serdi. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu'nun 226'ncı maddesi kapsamında yürütülen araştırmada; Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği, Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği, Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin hesapları mercek altına alındı. BAKAN GÜRLEK DUYURMUŞTU: İZMİR'DEKİ "AİLEM GÜVENDE" OPERASYONUNDAN GÖRÜNTÜLER! ahaber.com.tr'nin ulaştığı MASAK Veri İnceleme Tutanağı ile bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte incelendi. Belgelerde yabancı kuruluşlardan gelen fonlar, GİB SWIFT kayıtları, gerçek kişilerden yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketleri ayrıntılı şekilde sıralandı. 45 BİN 135 İŞLEM SATIRI İNCELENDİ "Bankacılık Transfer" tablosunda toplam 45 bin 135 işlem satırı bulunduğu belirtildi. Bu işlemlerin 13 bin 40'ının para girişi, 32 bin 95'inin ise para çıkışı olduğu kaydedildi. Para girişlerinden 218'inin doğrudan SWIFT alma işlemi olduğu tespit edildi. Gönderen adı, ülke bilgisi, SWIFT niteliği, banka ve işlem açıklamalarının birlikte değerlendirilmesi sonucunda 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan toplam 209 para girişi belirlendi. Bu işlemlerin transfer tarihlerindeki TL karşılıklarının toplamı yaklaşık 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde söz konusu rakamın paranın bugünkü değerini göstermediği, farklı tarihlerde gerçekleştirilen işlemlerin MASAK kayıtlarında bulunan TL karşılıklarının aritmetik toplamından oluştuğu vurgulandı. PARANIN YÜZDE 78'İ İKİ DERNEĞE GİTTİ 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinde SPoD ile HEVİ'nin belirgin şekilde öne çıktığı görüldü. Dernek İşlem sayısı Yabancı kaynak TL karşılığı SPoD 129 25 33.924.428,57 TL HEVİ 34 8 18.874.570,54 TL LİSTAG 19 8 8.231.662,68 TL Pozitif Yaşam 11 5 2.729.693,32 TL Lambda İstanbul 9 3 2.056.884,74 TL Pozitif-İz 7 3 1.577.322,83 TL Yabancı kurumsal para girişlerinin yaklaşık yüzde 50,3'ü SPoD'a, yüzde 28'i HEVİ'ye ve yüzde 12,2'si LİSTAG'a yöneldi. SPoD ile HEVİ'ye yapılan transferlerin işlem tarihlerindeki toplam TL karşılığı yaklaşık 52,8 milyon liraya ulaştı. Böylece iki dernek, 6 derneğe yönelen yabancı kurumsal finansmanın yaklaşık yüzde 78'ini aldı. SPoD'A 25 YABANCI KAYNAKTAN 33,9 MİLYON LİRA Yabancı kaynak çeşitliliği ve işlem hacmi bakımından ilk sırada SPoD yer aldı. Derneğin hesaplarına 25 farklı yabancı kaynaktan 129 işlemle yaklaşık 33 milyon 924 bin lira karşılığında para gönderildiği belirlendi. SPoD'a yapılan dikkat çekici transferler şöyle sıralandı: Women Win: 7 işlemde 320 bin 500 dolar Rainbow Railroad USA Inc: 3 işlemde 149 bin 794,86 dolar ILGA-Europe: 17 işlemde 104 bin 169,48 euro New Venture Fund: Tek işlemde 86 bin 400 dolar EED/FEDEM: 7 işlemde 76 bin 347,96 euro Regnbågsfonden: 6 işlemde 51 bin 840,34 euro ve 505 bin 84,50 İsveç kronu King Baudouin Foundation: Tek işlemde 25 bin dolar Almanya Federal Cumhuriyeti ve Başkonsolosluğu: 3 işlemde 42 bin 685 euro ABD Dışişleri Bakanlığı: 4 işlemde 38 bin 916,22 dolar Turkish Philanthropy Funds: 2 işlemde 23 bin 230,28 dolar German Marshall Fund: Tek işlemde 24 bin 839 dolar Fransa Büyükelçiliği: Tek işlemde 6 bin 505 euro OutRight Action International: 2 işlemde 6 bin 987 dolar International AIDS Society: 2 işlemde 2 bin 240 dolar ARACI BANKALARIN ARKASINDAKİ KAYNAK İncelemede, bazı banka kayıtlarında aracı finans kuruluşlarının gönderen olarak görünmesi nedeniyle gerçek fon sağlayıcısının ilk bakışta anlaşılamadığı tespit edildi. UK Online Giving Foundation kaynaklı çok sayıda işlemin karşı taraf bölümünde Bank of America veya Citibank Europe PLC'nin bulunduğu, ancak işlem açıklamalarında açıkça "UK ONLINE GIVING FOUNDATION" ve "POP GRANT DONATION FROM UKOGF" ifadelerinin yer aldığı kaydedildi. Bu nedenle 53 işlem aracı bankalara değil, nihai fon sağlayıcısı olarak değerlendirilen UK Online Giving Foundation'a atfedildi. Bu kapsamdaki son işlemin 27 Ağustos 2026 tarihinde gerçekleştirildiği belirtildi. HEVİ'YE 18,87 MİLYON LİRALIK YABANCI FON HEVİ'nin hesaplarına 8 yabancı kaynaktan 34 işlemle yaklaşık 18 milyon 874 bin lira karşılığında para gönderildiği belirlendi. Derneğin en büyük yabancı finansman kaynağının European Endowment for Democracy ve FEDEM kayıtları olduğu görüldü. Aynı finansman kaynağının farklı yazımlarla kaydedildiği belirtilirken 7 işlemde toplam 213 bin 930,27 euro gönderildiği tespit edildi. Bu işlemlerin transfer tarihlerindeki TL karşılığı 8 milyon 790 bin lirayı aştı. HEVİ'ye para gönderen diğer kaynaklar şöyle sıralandı: Wellspring Philanthropic Fund: 6 işlemde 200 bin 49 dolar ILGA-Europe: 11 işlemde 78 bin 910,98 euro Global Fund for Women: Tek işlemde 45 bin dolar Rosa-Luxemburg-Stiftung: 3 işlemde 19 bin 267,26 euro Fransa Büyükelçiliği: 2 işlemde 8 bin 361 euro Norveç Helsinki Komitesi: 3 işlemde 22 bin 453,12 dolar Front Line: Tek işlemde bin 815 euro LİSTAG'A YABANCI DEVLET VE DİPLOMATİK MİSYON PARASI LİSTAG'a 2021 sonrasında 8 farklı yabancı kaynaktan 19 işlemle yaklaşık 8 milyon 231 bin lira karşılığında para gönderildiği tespit edildi. Hollanda Dışişleri Bakanlığından 4 işlemde 89 bin 687 euro, Almanya Federal Cumhuriyeti ve Başkonsolosluğu bağlantılı kayıtlardan 6 işlemde 61 bin 413,92 euro gönderildiği belirlendi. Belgelerde adı eksik şekilde "Embassy of the Kingdom of..." olarak görünen kaynaktan 2 işlemle 38 bin 256 euro, European Endowment for Democracy'den ise 2 işlemle 25 bin euro aktarıldığı kaydedildi. LİSTAG'a yönelen finansmanın önemli bir bölümünün yabancı devlet kurumları ve diplomatik temsilciliklerle bağlantılı olduğu değerlendirmesine yer verildi. POZİTİF YAŞAM'A 2,73 MİLYON LİRA Pozitif Yaşam Derneğine 5 farklı kaynaktan 11 işlemle yaklaşık 2 milyon 729 bin lira karşılığında yabancı kurumsal para girişi tespit edildi. Charities Aid Foundation tarafından 2 işlemde 114 bin 310,30 euro, Gilead Sciences tarafından tek işlemde 33 bin dolar gönderildi. Bu iki kaynağın transfer tarihlerindeki toplam TL karşılığı 2,6 milyon lirayı aştı. German Marshall Fund'dan 13 bin 644 dolar, UK Online Giving Foundation üzerinden 6 işlemde toplam 4 bin 494,53 lira ve Posithiva Gruppen'den 195 euro aktarıldığı kaydedildi. POZİTİF İZ'E ABD VE FRANSA BAĞLANTILI TRANSFERLER Pozitif İz Derneğine 7 işlemle yaklaşık 1 milyon 577 bin lira karşılığında para gönderildiği belirlendi. International AIDS Society adına farklı yazımlarla görünen 4 transferin toplamı 30 bin 80 dolara ulaştı. Fransa Büyükelçiliğinden 10 bin 840 euro, ABD Dışişleri Bakanlığından ise 2 işlemde 7 bin 67,80 dolar gönderildiği tespit edildi. LAMBDA İSTANBUL'A ILGA-EUROPE'TAN 7 TRANSFER Lambda İstanbul'a 3 yabancı kurumsal kaynaktan 9 işlemle yaklaşık 2 milyon 56 bin lira karşılığında para girişi tespit edildi. ILGA-Europe tarafından 7 işlemde toplam 45 bin 532,01 euro gönderildi. Urgent Action Fund for Feminist kaynaklı kayıttan 6 bin dolar, IFLRY'den ise 300 euro aktarıldığı belirtildi. 3 Ağustos 2026 tarihinde İngiltere bağlantılı bir banka üzerinden "VACHINA" adına 500 euroluk transfer yapıldığı da görüldü. Ancak karşı tarafın tüzel bir kuruluş olup olmadığı kesinleştirilemediği için bu işlem kurumsal yabancı kaynak toplamına dahil edilmedi. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında gönderilen Mali Suçları Araştırma Kurulu verileri üzerinde yapılan inceleme, İstanbul merkezli 6 LGBT derneğinin yurt içi ve yurt dışı bağlantılı hesap hareketlerini gözler önüne serdi. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu'nun 226'ncı maddesi kapsamında yürütülen araştırmada; Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği, Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği, Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin hesapları mercek altına alındı. BAKAN GÜRLEK DUYURMUŞTU: İZMİR'DEKİ "AİLEM GÜVENDE" OPERASYONUNDAN GÖRÜNTÜLER! ahaber.com.tr'nin ulaştığı MASAK Veri İnceleme Tutanağı ile bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte incelendi. Belgelerde yabancı kuruluşlardan gelen fonlar, GİB SWIFT kayıtları, gerçek kişilerden yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketleri ayrıntılı şekilde sıralandı. 45 BİN 135 İŞLEM SATIRI İNCELENDİ "Bankacılık Transfer" tablosunda toplam 45 bin 135 işlem satırı bulunduğu belirtildi. Bu işlemlerin 13 bin 40'ının para girişi, 32 bin 95'inin ise para çıkışı olduğu kaydedildi. Para girişlerinden 218'inin doğrudan SWIFT alma işlemi olduğu tespit edildi. Gönderen adı, ülke bilgisi, SWIFT niteliği, banka ve işlem açıklamalarının birlikte değerlendirilmesi sonucunda 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan toplam 209 para girişi belirlendi. Bu işlemlerin transfer tarihlerindeki TL karşılıklarının toplamı yaklaşık 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde söz konusu rakamın paranın bugünkü değerini göstermediği, farklı tarihlerde gerçekleştirilen işlemlerin MASAK kayıtlarında bulunan TL karşılıklarının aritmetik toplamından oluştuğu vurgulandı. PARANIN YÜZDE 78'İ İKİ DERNEĞE GİTTİ 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinde SPoD ile HEVİ'nin belirgin şekilde öne çıktığı görüldü. Dernek İşlem sayısı Yabancı kaynak TL karşılığı SPoD 129 25 33.924.428,57 TL HEVİ 34 8 18.874.570,54 TL LİSTAG 19 8 8.231.662,68 TL Pozitif Yaşam 11 5 2.729.693,32 TL Lambda İstanbul 9 3 2.056.884,74 TL Pozitif-İz 7 3 1.577.322,83 TL Yabancı kurumsal para girişlerinin yaklaşık yüzde 50,3'ü SPoD'a, yüzde 28'i HEVİ'ye ve yüzde 12,2'si LİSTAG'a yöneldi. SPoD ile HEVİ'ye yapılan transferlerin işlem tarihlerindeki toplam TL karşılığı yaklaşık 52,8 milyon liraya ulaştı. Böylece iki dernek, 6 derneğe yönelen yabancı kurumsal finansmanın yaklaşık yüzde 78'ini aldı. SPoD'A 25 YABANCI KAYNAKTAN 33,9 MİLYON LİRA Yabancı kaynak çeşitliliği ve işlem hacmi bakımından ilk sırada SPoD yer aldı. Derneğin hesaplarına 25 farklı yabancı kaynaktan 129 işlemle yaklaşık 33 milyon 924 bin lira karşılığında para gönderildiği belirlendi. SPoD'a yapılan dikkat çekici transferler şöyle sıralandı: Women Win: 7 işlemde 320 bin 500 dolar Rainbow Railroad USA Inc: 3 işlemde 149 bin 794,86 dolar ILGA-Europe: 17 işlemde 104 bin 169,48 euro New Venture Fund: Tek işlemde 86 bin 400 dolar EED/FEDEM: 7 işlemde 76 bin 347,96 euro Regnbågsfonden: 6 işlemde 51 bin 840,34 euro ve 505 bin 84,50 İsveç kronu King Baudouin Foundation: Tek işlemde 25 bin dolar Almanya Federal Cumhuriyeti ve Başkonsolosluğu: 3 işlemde 42 bin 685 euro ABD Dışişleri Bakanlığı: 4 işlemde 38 bin 916,22 dolar Turkish Philanthropy Funds: 2 işlemde 23 bin 230,28 dolar German Marshall Fund: Tek işlemde 24 bin 839 dolar Fransa Büyükelçiliği: Tek işlemde 6 bin 505 euro OutRight Action International: 2 işlemde 6 bin 987 dolar International AIDS Society: 2 işlemde 2 bin 240 dolar ARACI BANKALARIN ARKASINDAKİ KAYNAK İncelemede, bazı banka kayıtlarında aracı finans kuruluşlarının gönderen olarak görünmesi nedeniyle gerçek fon sağlayıcısının ilk bakışta anlaşılamadığı tespit edildi. UK Online Giving Foundation kaynaklı çok sayıda işlemin karşı taraf bölümünde Bank of America veya Citibank Europe PLC'nin bulunduğu, ancak işlem açıklamalarında açıkça "UK ONLINE GIVING FOUNDATION" ve "POP GRANT DONATION FROM UKOGF" ifadelerinin yer aldığı kaydedildi. Bu nedenle 53 işlem aracı bankalara değil, nihai fon sağlayıcısı olarak değerlendirilen UK Online Giving Foundation'a atfedildi. Bu kapsamdaki son işlemin 27 Ağustos 2026 tarihinde gerçekleştirildiği belirtildi. HEVİ'YE 18,87 MİLYON LİRALIK YABANCI FON HEVİ'nin hesaplarına 8 yabancı kaynaktan 34 işlemle yaklaşık 18 milyon 874 bin lira karşılığında para gönderildiği belirlendi. Derneğin en büyük yabancı finansman kaynağının European Endowment for Democracy ve FEDEM kayıtları olduğu görüldü. Aynı finansman kaynağının farklı yazımlarla kaydedildiği belirtilirken 7 işlemde toplam 213 bin 930,27 euro gönderildiği tespit edildi. Bu işlemlerin transfer tarihlerindeki TL karşılığı 8 milyon 790 bin lirayı aştı. HEVİ'ye para gönderen diğer kaynaklar şöyle sıralandı: Wellspring Philanthropic Fund: 6 işlemde 200 bin 49 dolar ILGA-Europe: 11 işlemde 78 bin 910,98 euro Global Fund for Women: Tek işlemde 45 bin dolar Rosa-Luxemburg-Stiftung: 3 işlemde 19 bin 267,26 euro Fransa Büyükelçiliği: 2 işlemde 8 bin 361 euro Norveç Helsinki Komitesi: 3 işlemde 22 bin 453,12 dolar Front Line: Tek işlemde bin 815 euro LİSTAG'A YABANCI DEVLET VE DİPLOMATİK MİSYON PARASI LİSTAG'a 2021 sonrasında 8 farklı yabancı kaynaktan 19 işlemle yaklaşık 8 milyon 231 bin lira karşılığında para gönderildiği tespit edildi. Hollanda Dışişleri Bakanlığından 4 işlemde 89 bin 687 euro, Almanya Federal Cumhuriyeti ve Başkonsolosluğu bağlantılı kayıtlardan 6 işlemde 61 bin 413,92 euro gönderildiği belirlendi. Belgelerde adı eksik şekilde "Embassy of the Kingdom of..." olarak görünen kaynaktan 2 işlemle 38 bin 256 euro, European Endowment for Democracy'den ise 2 işlemle 25 bin euro aktarıldığı kaydedildi. LİSTAG'a yönelen finansmanın önemli bir bölümünün yabancı devlet kurumları ve diplomatik temsilciliklerle bağlantılı olduğu değerlendirmesine yer verildi. POZİTİF YAŞAM'A 2,73 MİLYON LİRA Pozitif Yaşam Derneğine 5 farklı kaynaktan 11 işlemle yaklaşık 2 milyon 729 bin lira karşılığında yabancı kurumsal para girişi tespit edildi. Charities Aid Foundation tarafından 2 işlemde 114 bin 310,30 euro, Gilead Sciences tarafından tek işlemde 33 bin dolar gönderildi. Bu iki kaynağın transfer tarihlerindeki toplam TL karşılığı 2,6 milyon lirayı aştı. German Marshall Fund'dan 13 bin 644 dolar, UK Online Giving Foundation üzerinden 6 işlemde toplam 4 bin 494,53 lira ve Posithiva Gruppen'den 195 euro aktarıldığı kaydedildi. POZİTİF İZ'E ABD VE FRANSA BAĞLANTILI TRANSFERLER Pozitif İz Derneğine 7 işlemle yaklaşık 1 milyon 577 bin lira karşılığında para gönderildiği belirlendi. International AIDS Society adına farklı yazımlarla görünen 4 transferin toplamı 30 bin 80 dolara ulaştı. Fransa Büyükelçiliğinden 10 bin 840 euro, ABD Dışişleri Bakanlığından ise 2 işlemde 7 bin 67,80 dolar gönderildiği tespit edildi. LAMBDA İSTANBUL'A ILGA-EUROPE'TAN 7 TRANSFER Lambda İstanbul'a 3 yabancı kurumsal kaynaktan 9 işlemle yaklaşık 2 milyon 56 bin lira karşılığında para girişi tespit edildi. ILGA-Europe tarafından 7 işlemde toplam 45 bin 532,01 euro gönderildi. Urgent Action Fund for Feminist kaynaklı kayıttan 6 bin dolar, IFLRY'den ise 300 euro aktarıldığı belirtildi. 3 Ağustos 2026 tarihinde İngiltere bağlantılı bir banka üzerinden "VACHINA" adına 500 euroluk transfer yapıldığı da görüldü. Ancak karşı tarafın tüzel bir kuruluş olup olmadığı kesinleştirilemediği için bu işlem kurumsal yabancı kaynak toplamına dahil edilmedi. AYNI KAYNAKLAR BİRDEN FAZLA DERNEĞİ FONLADI Üç dosyanın birlikte incelenmesi, bazı yabancı kaynakların birden fazla derneğe düzenli olarak para gönderdiğini ortaya koydu. EED/FEDEM'in HEVİ, LİSTAG ve SPoD'a 16 işlemde toplam 315 bin 278,23 euro gönderdiği belirlendi. İşlemlerin transfer tarihlerindeki toplam TL karşılığı yaklaşık 11,38 milyon lira olarak hesaplandı. ILGA-Europe'un HEVİ, Lambdaİstanbul, LİSTAG ve SPoD'a 37 işlemde toplam 234 bin 221,17 euro aktardığı kaydedildi. Bu işlemlerin TL karşılığının yaklaşık 7,69 milyon lira olduğu belirtildi. Diğer ortak finansman kaynakları ise şöyle sıralandı: Almanya Federal Cumhuriyeti ve Başkonsolosluğu: LİSTAG ve SPoD'a 9 işlemde 104 bin 98,92 euro Hollanda Dışişleri Bakanlığı: LİSTAG ve SPoD'a en az 5 işlemde 89 bin 687 euro ve 276 bin 500 lira ABD Dışişleri Bakanlığı: Pozitif- z ve SPoD'a 6 işlemde 45 bin 984,02 dolar Fransa Büyükelçiliği: HEVİ, Pozitif İz ve SPoD'a 4 işlemde 25 bin 706 euro German Marshall Fund: LİSTAG, Pozitif Yaşam ve SPoD'a 3 işlemde 63 bin 347 dolar International AIDS Society: Pozitif İz ve SPoD'a 6 işlemde 32 bin 320 dolar SWIFT KAYITLARINDA 3,3 MİLYON DOLARI AŞAN TRAFİK MASAK Veri İnceleme Tutanağındaki GİB SWIFT kayıtlarında, derneklerin farklı yıllara yayılan yurt dışı bağlantılı hesap hareketlerinin dolar karşılıklarına da yer verildi. Dernek İncelenen dönem Rapordaki toplam dolar karşılığı SPoD2012-2026 1.570.692,44 dolar HEVİ2018-2026 762.939,21 dolar Pozitif Yaşam-2011-20255 18.525,92 dolar LİSTAG2020-2026 314.220,89 dolar Lambdaİstanbul-2012-2026 103.650,93 dolar Pozitif İz-2022-2026 89.138,41 dolar Toplam3.359.167,80 dolar Böylece 6 derneğe ait GİB SWIFT kayıtlarında yer alan para hareketlerinin dolar karşılığı toplamı 3 milyon 359 bin 167,80 dolara ulaştı. Bu toplam, farklı yıllarda ve farklı para birimleriyle gerçekleştirilen işlemlerin tutanaktaki dolar karşılıklarından oluşuyor. 2021-2026 dönemine ilişkin 67,4 milyon liralık bankacılık analiziyle aynı kapsamı taşımadığı için iki rakamın birbirine eklenmemesi gerekiyor. PARA TRAFİĞİ 2011'E KADAR UZANDI SWIFT kayıtları, yurt dışı bağlantılı finansmanın yalnızca son yıllarla sınırlı olmadığını ortaya koydu. Pozitif Yaşam Derneğinin 2011, Lambdaİstanbul ile SPoD'un 2012 yılına kadar uzanan transfer kayıtları bulunduğu belirlendi. Eski kayıtlarda Pozitif Yaşam'a Avrupa Komisyonundan 47 bin 996,94 dolar, UNDP'den 2 bin 500 dolar ve Deutsche Gesellschaft bağlantılı kayıtlardan 5 işlemde 124 bin 786,02 dolar gönderildiği görüldü. SPoD'a ABD Dışişleri Bakanlığından farklı yıllarda 9 işlemle 113 bin 591,62 dolar, ILGA-Europe'tan 15 işlemle 61 bin 403,14 dolar ve EED/FEDEM'den 9 işlemle 167 bin 207,74 dolar aktarıldığı kaydedildi. MASAK TUTANAĞINDA ÇARPICI DEĞERLENDİRME MASAK verileri üzerinde hazırlanan inceleme tutanağında, söz konusu derneklere yurt dışı bağlantılı kişi ve kuruluşlar tarafından maddi destek sağlandığı belirtildi. Tutanakta, bu kaynaklar aracılığıyla cinsiyet değiştirmek isteyen kişilerin ameliyat masraflarının karşılandığı yönünde değerlendirmeye yer verildi. Derneklerin faaliyetleri dışında toplumsal yapının bozulmasına, toplum içerisinde görüş ayrılıklarının oluşmasına, aileler arasında kaygı meydana gelmesine, kamu düzeni ile toplumsal değerlere zarar verilmesine yönelik çalışmalar yürüttüğü iddiası da soruşturma kapsamında kayda geçirildi. Söz konusu ifadeler, soruşturma dosyasındaki inceleme ve değerlendirmeleri yansıtıyor. DERNEK HESAPLARINA MÜKERRER PARA AKIŞI Gerçek kişilerden yapılan para girişlerinin incelendiği ayrı analizde, gönderenlerin T.C. kimlik numarası kayıtları esas alındı ve aynı kişiye ait isim farklılıkları birleştirildi. En fazla işlem yapan isim, Lambdaİstanbul ile SPoD'a toplam 72 kez para gönderen Abdullah İkbal Arslanbaş oldu. Arslanbaş adına 37'si Lambda İstanbul'a, 35'i SPoD'a olmak üzere toplam 11 bin 535 liralık transfer kaydı bulundu. En fazla mükerrer işlem yapan kişiler şöyle sıralandı: Gönderen İşlem Toplam Dernek Abdullah İkbal Arslanbaş 72 11.535 TL Lambdaİstanbul ve SPoD Yasemin Öz 56 3.010 TL Lambdaİstanbul ve SPoD Aslı Meleş 54 25.324 TL LİSTAG Anıl Birkan 44 39.550 TL Pozitif İz Günseli Dum 40 5.680 TL LİSTAG Abdulkadir Öner Ceylan 38 21.146 TL Lambdaİstanbul ve LİSTAG Mesude Demirağ 36 46.600 TL LİSTAG Serpil Bilgin 33 7.510 TL LİSTAG Rezan Bekiroğlu 30 6.000 TL LİSTAG Cüneyt Orhan Yurtsever 28 8.400 TL LİSTAG Figen Yılmaz 27 21.800 TL LİSTAG Hasan Metehan Özkan 25 26.528,64 TL LİSTAG ve SPoD Can Candan 21 20.250 TL LİSTAG Osman Elbek 20 20.000 TL LİSTAG Yağmur Arığ 20 11.000 TL LİSTAG ve SPoD BİRDEN FAZLA DERNEĞE PARA GÖNDERENLER Aynı gerçek kişilerin birden fazla derneğin hesabında görülmesi de incelemede dikkat çeken başlıklardan biri oldu. Necla İclal Küneralp'in Lambda İstanbul'a 20 bin, LİSTAG'a 40 bin olmak üzere toplam 60 bin lira gönderdiği belirlendi. Turgay Bayındır'ın Lambdaİstanbul ve SPoD'a 19 işlemle toplam 52 bin 670 lira, Esra Banu Çırak'ın Lambdaİstanbul ile LİSTAG'a 40 bin lira aktardığı kaydedildi. Mihael Nahmias'ın Pozitif Yaşam ile Pozitif İz'e toplam 40 bin lira, Hasan Metehan Özkan'ın LİSTAG ile SPoD'a 25 işlemle 26 bin 528,64 lira gönderdiği tespit edildi. Abdulkadir Öner Ceylan'ın iki derneğe 38 işlemle 21 bin 146 lira, Abdullah İkbal Arslanbaş'ın ise iki derneğe 72 işlemle toplam 11 bin 535 lira aktardığı belirtildi. HEARTSTOPPER'IN YAZARI DA KAYITLARDA Gerçek kişilerden gelen transferler ile açık kaynak kayıtlarının karşılaştırıldığı analizde uluslararası alanda tanınan isimlerin de bulunduğu görüldü. MASAK kaydında karşı tarafın doğrudan "ALICE OSEMAN AUTHOR" olarak yer aldığı belirtildi. İngiltere'deki TSB Bank PLC London üzerinden Lambda İstanbul'a 663,37 sterlin gönderildiği ve işlem açıklamasında "DONATION OTHER" ifadesinin bulunduğu kaydedildi. İşlemin transfer tarihindeki TL karşılığı 12 bin 277,72 lira olarak hesaplandı. "Author" ibaresi, İngiltere bağlantısı ve ayırt edici isim nedeniyle kaydın</t>
+          <t>Antalya’da ambalaj ürünlerinin bulunduğu bir depoda çıkan yangın, bitişiğindeki depolar ile yakındaki bir eve sıçradı. Yaklaşık 2 saatte büyük ölçüde kontrol altına alınan yangında 5 depodaki ürünler yanarken, depo sahibi Arif Ordu, "Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. Antalya’da ambalaj ürünlerinin bulunduğu bir depoda çıkan yangın, bitişiğindeki depolar ile yakındaki bir eve sıçradı. Yaklaşık 2 saatte büyük ölçüde kontrol altına alınan yangında 5 depodaki ürünler yanarken, depo sahibi Arif Ordu, "Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. Antalya’da ambalaj ürünlerinin bulunduğu bir depoda çıkan yangın, bitişiğindeki depolar ile yakındaki bir eve sıçradı. Yaklaşık 2 saatte büyük ölçüde kontrol altına alınan yangında 5 depodaki ürünler yanarken, depo sahibi Arif Ordu, "Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. Turizm Aktüel -</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı MASAK verileri ortaya koydu! 6 derneğe yurt dışından 3,3 milyon dolar ve 67,4 milyon TL aktarımı A Haber İstanbul Cumhuriyet Başsavcılığının soruşturmasında MASAK verileri incelendi; 6 derneğe 2011-2026 döneminde yurt dışı bağlantılı milyonluk para girişleri ve 209 kurumsal transfer tespit edildi. AYNI KAYNAKLAR BİRDEN FAZLA DERNEĞİ FONLADI Üç dosyanın birlikte incelenmesi, bazı yabancı kaynakların birden fazla derneğe düzenli olarak para gönderdiğini ortaya koydu. EED/FEDEM'in HEVİ, LİSTAG ve SPoD'a 16 işlemde toplam 315 bin 278,23 euro gönderdiği belirlendi. İşlemlerin transfer tarihlerindeki toplam TL karşılığı yaklaşık 11,38 milyon lira olarak hesaplandı. ILGA-Europe'un HEVİ, Lambdaİstanbul, LİSTAG ve SPoD'a 37 işlemde toplam 234 bin 221,17 euro aktardığı kaydedildi. Bu işlemlerin TL karşılığının yaklaşık 7,69 milyon lira olduğu belirtildi. Diğer ortak finansman kaynakları ise şöyle sıralandı: Almanya Federal Cumhuriyeti ve Başkonsolosluğu: LİSTAG ve SPoD'a 9 işlemde 104 bin 98,92 euro Hollanda Dışişleri Bakanlığı: LİSTAG ve SPoD'a en az 5 işlemde 89 bin 687 euro ve 276 bin 500 lira ABD Dışişleri Bakanlığı: Pozitif- z ve SPoD'a 6 işlemde 45 bin 984,02 dolar Fransa Büyükelçiliği: HEVİ, Pozitif İz ve SPoD'a 4 işlemde 25 bin 706 euro German Marshall Fund: LİSTAG, Pozitif Yaşam ve SPoD'a 3 işlemde 63 bin 347 dolar International AIDS Society: Pozitif İz ve SPoD'a 6 işlemde 32 bin 320 dolar SWIFT KAYITLARINDA 3,3 MİLYON DOLARI AŞAN TRAFİK MASAK Veri İnceleme Tutanağındaki GİB SWIFT kayıtlarında, derneklerin farklı yıllara yayılan yurt dışı bağlantılı hesap hareketlerinin dolar karşılıklarına da yer verildi. Dernek İncelenen dönem Rapordaki toplam dolar karşılığı SPoD2012-2026 1.570.692,44 dolar HEVİ2018-2026 762.939,21 dolar Pozitif Yaşam-2011-20255 18.525,92 dolar LİSTAG2020-2026 314.220,89 dolar Lambdaİstanbul-2012-2026 103.650,93 dolar Pozitif İz-2022-2026 89.138,41 dolar Toplam3.359.167,80 dolar Böylece 6 derneğe ait GİB SWIFT kayıtlarında yer alan para hareketlerinin dolar karşılığı toplamı 3 milyon 359 bin 167,80 dolara ulaştı. Bu toplam, farklı yıllarda ve farklı para birimleriyle gerçekleştirilen işlemlerin tutanaktaki dolar karşılıklarından oluşuyor. 2021-2026 dönemine ilişkin 67,4 milyon liralık bankacılık analiziyle aynı kapsamı taşımadığı için iki rakamın birbirine eklenmemesi gerekiyor. PARA TRAFİĞİ 2011'E KADAR UZANDI SWIFT kayıtları, yurt dışı bağlantılı finansmanın yalnızca son yıllarla sınırlı olmadığını ortaya koydu. Pozitif Yaşam Derneğinin 2011, Lambdaİstanbul ile SPoD'un 2012 yılına kadar uzanan transfer kayıtları bulunduğu belirlendi. Eski kayıtlarda Pozitif Yaşam'a Avrupa Komisyonundan 47 bin 996,94 dolar, UNDP'den 2 bin 500 dolar ve Deutsche Gesellschaft bağlantılı kayıtlardan 5 işlemde 124 bin 786,02 dolar gönderildiği görüldü. SPoD'a ABD Dışişleri Bakanlığından farklı yıllarda 9 işlemle 113 bin 591,62 dolar, ILGA-Europe'tan 15 işlemle 61 bin 403,14 dolar ve EED/FEDEM'den 9 işlemle 167 bin 207,74 dolar aktarıldığı kaydedildi. MASAK TUTANAĞINDA ÇARPICI DEĞERLENDİRME MASAK verileri üzerinde hazırlanan inceleme tutanağında, söz konusu derneklere yurt dışı bağlantılı kişi ve kuruluşlar tarafından maddi destek sağlandığı belirtildi. Tutanakta, bu kaynaklar aracılığıyla cinsiyet değiştirmek isteyen kişilerin ameliyat masraflarının karşılandığı yönünde değerlendirmeye yer verildi. Derneklerin faaliyetleri dışında toplumsal yapının bozulmasına, toplum içerisinde görüş ayrılıklarının oluşmasına, aileler arasında kaygı meydana gelmesine, kamu düzeni ile toplumsal değerlere zarar verilmesine yönelik çalışmalar yürüttüğü iddiası da soruşturma kapsamında kayda geçirildi. Söz konusu ifadeler, soruşturma dosyasındaki inceleme ve değerlendirmeleri yansıtıyor. kimlik numarası kayıtları esas alındı ve aynı kişiye ait isim farklılıkları birleştirildi. En fazla işlem yapan isim, Lambdaİstanbul ile SPoD'a toplam 72 kez para gönderen Abdullah İkbal Arslanbaş oldu. Arslanbaş adına 37'si Lambda İstanbul'a, 35'i SPoD'a olmak üzere toplam 11 bin 535 liralık transfer kaydı bulundu. En fazla mükerrer işlem yapan kişiler şöyle sıralandı: Gönderen İşlem Toplam Dernek Abdullah İkbal Arslanbaş 72 11.535 TL Lambdaİstanbul ve SPoD Yasemin Öz 56 3.010 TL Lambdaİstanbul ve SPoD Aslı Meleş 54 25.324 TL LİSTAG Anıl Birkan 44 39.550 TL Pozitif İz Günseli Dum 40 5.680 TL LİSTAG Abdulkadir Öner Ceylan 38 21.146 TL Lambdaİstanbul ve LİSTAG Mesude Demirağ 36 46.600 TL LİSTAG Serpil Bilgin 33 7.510 TL LİSTAG Rezan Bekiroğlu 30 6.000 TL LİSTAG Cüneyt Orhan Yurtsever 28 8.400 TL LİSTAG Figen Yılmaz 27 21.800 TL LİSTAG Hasan Metehan Özkan 25 26.528,64 TL LİSTAG ve SPoD Can Candan 21 20.250 TL LİSTAG Osman Elbek 20 20.000 TL LİSTAG Yağmur Arığ 20 11.000 TL LİSTAG ve SPoD BİRDEN FAZLA DERNEĞE PARA GÖNDERENLER Aynı gerçek kişilerin birden fazla derneğin hesabında görülmesi de incelemede dikkat çeken başlıklardan biri oldu. Necla İclal Küneralp'in Lambda İstanbul'a 20 bin, LİSTAG'a 40 bin olmak üzere toplam 60 bin lira gönderdiği belirlendi. Abdulkadir Öner Ceylan'ın iki derneğe 38 işlemle 21 bin 146 lira, Abdullah İkbal Arslanbaş'ın ise iki derneğe 72 işlemle toplam 11 bin 535 lira aktardığı belirtildi. HEARTSTOPPER'IN YAZARI DA KAYITLARDA Gerçek kişilerden gelen transferler ile açık kaynak kayıtlarının karşılaştırıldığı analizde uluslararası alanda tanınan isimlerin de bulunduğu görüldü. MASAK kaydında karşı tarafın doğrudan "ALICE OSEMAN AUTHOR" olarak yer aldığı belirtildi. İngiltere'deki TSB Bank PLC London üzerinden Lambda İstanbul'a 663,37 sterlin gönderildiği ve işlem açıklamasında "DONATION OTHER" ifadesinin bulunduğu kaydedildi. SWIFT inceleme tutanağında aynı isme ait 2022 tarihli işlemin dolar karşılığı ise 904,10 dolar olarak yer aldı. Ancak bu işlem "bağış" değil, "iade" açıklamasıyla kayıtlara geçti. Derya Seyhan Arman adına Lambda İstanbul'a 12 ayrı işlemle toplam 6 bin lira gönderildiği belirtildi. Hekim Osman Elbek adına LİSTAG'a 20 ayrı işlemle toplam 20 bin lira gönderildiği ve işlemlerde "bağış" açıklamasının bulunduğu kaydedildi. Çevirmen Amy Marie Spangler adına Lambda İstanbul'a 12 işlemle toplam 19 bin 700 lira gönderildi. Bazı işlemlerin açıklamasında doğrudan "bağış" ifadesinin yer aldığı belirtildi. Akademisyen Şemsa Özar adına SPoD'a "bağış" açıklamasıyla 5 bin liralık işlem bulunduğu kaydedildi. DERNEK YÖNETİCİLERİNDEN DERNEK HESAPLARINA PARA Bazı transfer sahiplerinin para gönderdikleri derneklerde yönetici veya çalışan olarak görev yaptığına ilişkin açık kaynak kayıtlarına da ulaşıldı. SPoD'un eski yönetim kurulu başkanı olduğu belirtilen Müge Akbasan adına 15 işlemle 49 bin 119,50 lira aktarıldı. Bu tutarın en az 35 bin 869,50 liralık bölümünün bağış veya aidat açıklaması taşıdığı kaydedildi. SPoD'un denetleme kurulunda yer aldığı belirtilen Abdullah İkbal Arslanbaş, 72 işlemle gerçek kişiler arasındaki en yüksek transfer sayısına ulaştı. Ancak bu tutarın 100 bin 206,68 liralık bölümünün huzur hakkı iadesi niteliğinde olduğu, bağış ve aidat olarak değerlendirilen kısmın yaklaşık bin 200 lira olduğu belirtildi. Furkan Yurt adına görünen 61 bin liralık iki işlemin 60 bin liralık kısmının "maaş avans iadesi" açıklaması taşıdığı tespit edildi. SORUŞTURMADA PARA TRAFİĞİ MERCEK ALTINDA Üç dosyanın birlikte değerlendirilmesi sonucunda, 6 derneğe uzanan yabancı finansman ağında uluslararası kuruluşların yanı sıra ABD Dışişleri Bakanlığı, Hollanda Dışişleri Bakanlığı, Almanya ve Fransa'nın diplomatik temsilcilikleri gibi yabancı kamu kurumlarının da bulunduğu tespit edildi. MASAK Veri İnceleme Tutanağında yer alan değerlendirmeler ile para transferlerinin hangi faaliyetlerde kullanıldığına ilişkin iddialar, İstanbul Cumhuriyet Başsavcılığınca yürütülen soruşturma kapsamında inceleniyor. Belgelerde adı geçen kişiler ile kuruluşlar hakkındaki kayıtlar para transferlerini gösterirken, söz konusu hareketler tek başına suçun kesinleştiği anlamına gelmiyor. #MASAK LGBTİ Dernekleri Raporu #İstanbul Cumhuriyet Başsavcılığı LGBTİ Soruşturması Giriş Tarihi: 13 Eylül 2026 12:03 Son Güncelleme: 13 Eylül 2026 13:15 ahaber.com.tr Haber Merkezi Giriş Tarihi: 13 Eylül 2026 12:03 Son Güncelleme: 13 Eylül 2026 13:15 ahaber.com.tr Haber Merkezi İstanbul Cumhuriyet Başsavcılığının soruşturması kapsamında incelenen MASAK verileri, 6 LGBT derneğinin yurt dışı bağlantılı para trafiğini ortaya çıkardı. GİB SWIFT kayıtlarında derneklere gönderilen paranın dolar karşılığı 3 milyon 359 bin doları aşarken, 2021-2026 dönemindeki 209 yabancı kurumsal transferin işlem tarihlerindeki TL karşılığı 67,4 milyon liraya ulaştı. Para trafiğinde yabancı devlet kurumları, diplomatik misyonlar, uluslararası kuruluşlar ve bazı tanınmış isimler yer aldı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında gönderilen Mali Suçları Araştırma Kurulu verileri üzerinde yapılan inceleme, İstanbul merkezli 6 LGBT derneğinin yurt içi ve yurt dışı bağlantılı hesap hareketlerini gözler önüne serdi. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu'nun 226'ncı maddesi kapsamında yürütülen araştırmada; Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği, Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği, Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği, Pozitif Yaşam Derneği, Pozitif İz Derneği ile Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneğinin hesapları mercek altına alındı. BAKAN GÜRLEK DUYURMUŞTU: İZMİR'DEKİ "AİLEM GÜVENDE" OPERASYONUNDAN GÖRÜNTÜLER! ahaber.com.tr'nin ulaştığı MASAK Veri İnceleme Tutanağı ile bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte incelendi. Bu işlemlerin transfer tarihlerindeki TL karşılıklarının toplamı yaklaşık 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde söz konusu rakamın paranın bugünkü değerini göstermediği, farklı tarihlerde gerçekleştirilen işlemlerin MASAK kayıtlarında bulunan TL karşılıklarının aritmetik toplamından oluştuğu vurgulandı. PARANIN YÜZDE 78'İ İKİ DERNEĞE GİTTİ 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinde SPoD ile HEVİ'nin belirgin şekilde öne çıktığı görüldü. Dernek İşlem sayısı Yabancı kaynak TL karşılığı SPoD 129 25 33.924.428,57 TL HEVİ 34 8 18.874.570,54 TL LİSTAG 19 8 8.231.662,68 TL Pozitif Yaşam 11 5 2.729.693,32 TL Lambda İstanbul 9 3 2.056.884,74 TL Pozitif-İz 7 3 1.577.322,83 TL Yabancı kurumsal para girişlerinin yaklaşık yüzde 50,3'ü SPoD'a, yüzde 28'i HEVİ'ye ve yüzde 12,2'si LİSTAG'a yöneldi. SPoD ile HEVİ'ye yapılan transferlerin işlem tarihlerindeki toplam TL karşılığı yaklaşık 52,8 milyon liraya ulaştı. Böylece iki dernek, 6 derneğe yönelen yabancı kurumsal finansmanın yaklaşık yüzde 78'ini aldı. SPoD'A 25 YABANCI KAYNAKTAN 33,9 MİLYON LİRA Yabancı kaynak çeşitliliği ve işlem hacmi bakımından ilk sırada SPoD yer aldı. Derneğin hesaplarına 25 farklı yabancı kaynaktan 129 işlemle yaklaşık 33 milyon 924 bin lira karşılığında para gönderildiği belirlendi. SPoD'a yapılan dikkat çekici transferler şöyle sıralandı: Women Win: 7 işlemde 320 bin 500 dolar Rainbow Railroad USA Inc: 3 işlemde 149 bin 794,86 dolar ILGA-Europe: 17 işlemde 104 bin 169,48 euro New Venture Fund: Tek işlemde 86 bin 400 dolar EED/FEDEM: 7 işlemde 76 bin 347,96 euro Regnbågsfonden: 6 işlemde 51 bin 840,34 euro ve 505 bin 84,50 İsveç kronu King Baudouin Foundation: Tek işlemde 25 bin dolar Almanya Federal Cumhuriyeti ve Başkonsolosluğu: 3 işlemde 42 bin 685 euro ABD Dışişleri Bakanlığı: 4 işlemde 38 bin 916,22 dolar Turkish Philanthropy Funds: 2 işlemde 23 bin 230,28 dolar German Marshall Fund: Tek işlemde 24 bin 839 dolar Fransa Büyükelçiliği: Tek işlemde 6 bin 505 euro OutRight Action International: 2 işlemde 6 bin 987 dolar International AIDS Society: 2 işlemde 2 bin 240 dolar ARACI BANKALARIN ARKASINDAKİ KAYNAK İncelemede, bazı banka kayıtlarında aracı finans kuruluşlarının gönderen olarak görünmesi nedeniyle gerçek fon sağlayıcısının ilk bakışta anlaşılamadığı tespit edildi. HEVİ'YE 18,87 MİLYON LİRALIK YABANCI FON HEVİ'nin hesaplarına 8 yabancı kaynaktan 34 işlemle yaklaşık 18 milyon 874 bin lira karşılığında para gönderildiği belirlendi. Bu işlemlerin transfer tarihlerindeki TL karşılığı 8 milyon 790 bin lirayı aştı. HEVİ'ye para gönderen diğer kaynaklar şöyle sıralandı: Wellspring Philanthropic Fund: 6 işlemde 200 bin 49 dolar ILGA-Europe: 11 işlemde 78 bin 910,98 euro Global Fund for Women: Tek işlemde 45 bin dolar Rosa-Luxemburg-Stiftung: 3 işlemde 19 bin 267,26 euro Fransa Büyükelçiliği: 2 işlemde 8 bin 361 euro Norveç Helsinki Komitesi: 3 işlemde 22 bin 453,12 dolar Front Line: Tek işlemde bin 815 euro LİSTAG'A YABANCI DEVLET VE DİPLOMATİK MİSYON PARASI LİSTAG'a 2021 sonrasında 8 farklı yabancı kaynaktan 19 işlemle yaklaşık 8 milyon 231 bin lira karşılığında para gönderildiği tespit edildi. Belgelerde adı eksik şekilde "Embassy of the Kingdom of..." olarak görünen kaynaktan 2 işlemle 38 bin 256 euro, European Endowment for Democracy'den ise 2 işlemle 25 bin euro aktarıldığı kaydedildi. POZİTİF YAŞAM'A 2,73 MİLYON LİRA Pozitif Yaşam Derneğine 5 farklı kaynaktan 11 işlemle yaklaşık 2 milyon 729 bin lira karşılığında yabancı kurumsal para girişi tespit edildi. Charities Aid Foundation tarafından 2 işlemde 114 bin 310,30 euro, Gilead Sciences tarafından tek işlemde 33 bin dolar gönderildi. Bu iki kaynağın transfer tarihlerindeki toplam TL karşılığı 2,6 milyon lirayı aştı. German Marshall Fund'dan 13 bin 644 dolar, UK Online Giving Foundation üzerinden 6 işlemde toplam 4 bin 494,53 lira ve Posithiva Gruppen'den 195 euro aktarıldığı kaydedildi. POZİTİF İZ'E ABD VE FRANSA BAĞLANTILI TRANSFERLER Pozitif İz Derneğine 7 işlemle yaklaşık 1 milyon 577 bin lira karşılığında para gönderildiği belirlendi. International AIDS Society adına farklı yazımlarla görünen 4 transferin toplamı 30 bin 80 dolara ulaştı. Fransa Büyükelçiliğinden 10 bin 840 euro, ABD Dışişleri Bakanlığından ise 2 işlemde 7 bin 67,80 dolar gönderildiği tespit edildi. LAMBDA İSTANBUL'A ILGA-EUROPE'TAN 7 TRANSFER Lambda İstanbul'a 3 yabancı kurumsal kaynaktan 9 işlemle yaklaşık 2 milyon 56 bin lira karşılığında para girişi tespit edildi. Urgent Action Fund for Feminist kaynaklı kayıttan 6 bin dolar, IFLRY'den ise 300 euro aktarıldığı belirtildi. #MASAK LGBTİ Dernekleri Raporu #İstanbul Cumhuriyet Başsavcılığı LGBTİ Soruşturması Sonraki Haber Babülmendep krizi piyasaları alt üst etti! Petrol fiyatlarında artış altını baskıladı Mobil uygulamalarımızı indirin Günün Manşetleri İçin Tıklayın AYNI KAYNAKLAR BİRDEN FAZLA DERNEĞİ FONLADI Üç dosyanın birlikte incelenmesi, bazı yabancı kaynakların birden fazla derneğe düzenli olarak para gönderdiğini ortaya koydu.</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Turizm Aktüel Antalya’da ambalaj ürünlerinin bulunduğu bir depoda çıkan yangın, bitişiğindeki depolar ile yakındaki bir eve sıçradı. Yaklaşık 2 saatte büyük ölçüde kontrol altına alınan yangında 5 depodaki ürünler yanarken, depo sahibi Arif Ordu, "Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -3687,12 +3907,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.ahaber.com.tr/ozel-haberler/2026/09/13/lgbti-derneklerinin-karanlik-para-agi-desifre-oldu</t>
+          <t>https://www.turizmaktuel.com/haber/antalya-da-otel-malzemelerinin-bulundugu-5-depoda-yangin</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Antalya</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
@@ -3717,7 +3937,7 @@
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="n">
-        <v>115</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>12</v>
@@ -3726,27 +3946,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 06:08:08</t>
+          <t>2026-09-13 10:20:22</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15 ilde 'Ailem Güvende' operasyonu</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Dakika</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -3756,32 +3976,44 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv</t>
+          <t>Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Güncelleme: 13.09.2026 13:20 Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Kaynak: AA Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15 ilde 'Ailem Güvende' operasyonu 15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv 15 ilde 'Ailem Güvende' operasyonu | MASAK LGBTİ+ derneklerinin fonlarını deşifre etti Odatv</t>
+          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Dakika Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Güncelleme: 13.09.2026 13:20 Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Kaynak: AA Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.odatv.com/guncel/15-ilde-ailem-guvende-operasyonu-masak-lgbti-derneklerinin-fonlarini-desifre-etti-120162459</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>https://www.sondakika.com/amp/haber-bolu-gerede-deki-geri-donusum-deposunda-yangin-son-20233164/</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -3789,7 +4021,7 @@
       <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr"/>
@@ -3803,7 +4035,7 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="n">
-        <v>56.92</v>
+        <v>121.75</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>13</v>
@@ -3812,27 +4044,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:19:34</t>
+          <t>2026-09-13 10:19:26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi!</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -3842,32 +4074,44 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir</t>
+          <t>Ad Haberler - Gündem Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir LGBTİ+ derneklerine MASAK incelemesi: 'Batılı kurumlardan fonlu ameliyatlar' mercek altında Notbir</t>
+          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi Ad Haberler - Gündem Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor.</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTFd3TlNFT0JUb01yMmphNFBGcUc5dWl5NEkyZ25WcW5NdUwxbkVQQ0k0WERtUTJ3N3JfX3hlZnRqSWhBZjNSeWpNM0tFWkQxQVFRXzduUHk2UjdaQlVrdTFtbmJCN2tPdnVHYXNuSWhzX2V1SFlGTVRVNU16RWpOekxPMzRXWGRWSE5Kdms1M09Ld0NMTFBQckc2Q2JSVTV5bnZDaHhXY0ZIbFc2M1lHNmFKQXBrT2c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>https://www.sozcu.com.tr/amp/bolu-daki-depo-yangininda-son-durum-hasarin-boyutu-havadan-goruntulendi-p357811</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -3875,7 +4119,7 @@
       <c r="S15" s="2" t="inlineStr"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr"/>
@@ -3889,7 +4133,7 @@
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="n">
-        <v>86.98</v>
+        <v>117.5</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>14</v>
@@ -3898,27 +4142,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:07:34</t>
+          <t>2026-09-14 06:55:51</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>sahtecilik</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı!</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! SON TV</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -3928,32 +4172,44 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! SON TV</t>
+          <t>Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Güncelleme: 14.09.2026 09:55 Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı. Kaynak: İHA Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı! SON TV Dünyaca ünlü yazar ile oyuncu ve akademisyenlerin LGBT derneklerine para transferleri MASAK kayıtlarında çıktı!</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Güncelleme: 14.09.2026 09:55 Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Kaynak: İHA Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.son.tv/dunyaca-unlu-yazar-ile-oyuncu-ve-akademisyenlerin-lgbt-derneklerine-para-transferleri-masak-kayitlarinda-cikti/</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>https://www.sondakika.com/amp/haber-bilecik-bozuyuk-te-polis-banka-personelini-sahte-p-20234878/</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Bilecik</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Bozüyük</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -3961,7 +4217,7 @@
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr"/>
@@ -3975,7 +4231,7 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="n">
-        <v>102.18</v>
+        <v>116.25</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>15</v>
@@ -3984,27 +4240,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 20:23:48</t>
+          <t>2026-09-14 06:45:32</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı aksiyon.com.tr</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -4014,32 +4270,44 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa</t>
+          <t>Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Sahte para ve tespit yöntemleri: Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Vatandaşlara ve banka personeline öneriler: Polis ekipleri, iletişim yoluyla yapılan dolandırıcılıklara karşı tedbirli olunmasını, telefon veya e-posta yoluyla kişisel ve hesap bilgisi paylaşılmamasını vurguladı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. Yetkililer benzer uyarı ve eğitim faaliyetlerinin devam edeceğini belirtti. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI 1 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 2 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 3 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 4 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı 5 Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı 6 Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı 7 Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Polis ekipleri, iletişim yoluyla yapılan dolandırıcılıklara karşı tedbirli olunmasını, telefon veya e-posta yoluyla kişisel ve hesap bilgisi paylaşılmamasını vurguladı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. Yetkililer benzer uyarı ve eğitim faaliyetlerinin devam edeceğini belirtti. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI Ben Hüseyin Aydın, 34 yaşındayım, İstanbul'dayım. aksiyon.com.tr'nin Gündem ekibinde adliye ve hukuk muhabiriyim. Karmaşık dava dosyalarını alıp, herkesin anlayacağı şekilde sadeleştirmek benim işim. Detaylara çok önem veririm, titiz çalışırım. 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa Fenomen çifte MASAK kıskacı: Gelin Çağla Öz de yakalandı Söz Bursa</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı aksiyon.com.tr Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Sahte para ve tespit yöntemleri: Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI 1 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 2 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 3 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 4 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı 5 Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı 6 Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı 7 Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI Ben Hüseyin Aydın, 34 yaşındayım, İstanbul'dayım. Karmaşık dava dosyalarını alıp, herkesin anlayacağı şekilde sadeleştirmek benim işim. 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOd0N2UGZsdGF5RFhyX081cE5HLWdsQ0hEbXpHVExlS1FKS3k0OFVkMmJ0NWhJVU9wTTlpZzZNRjFtLXdvaUxZT2hMY2VoakFrdlVDaGV3TWFrTUNiSWI1cEtHRkNrYVpwM2JkY05SOVVWcVZFVzdyRlJNVnhrZmtMaGxLUTVFWExWSHJ6Y2xZUmpRZi01eEJUWjlhX2Ywc2FBajVpU3Z4SQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>https://www.aksiyon.com.tr/bilecik-te-bankacilara-sahte-para-ve-dolandiricilikla-mucadele-cagrisi-354075</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Adana | Aydın | Bartın | Bilecik | Düzce</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Köşk | Bozüyük | Mudurnu | Maltepe</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
@@ -4047,7 +4315,7 @@
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr"/>
@@ -4061,7 +4329,7 @@
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="n">
-        <v>53.16</v>
+        <v>105.25</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>16</v>
@@ -4070,7 +4338,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 08:33:15</t>
+          <t>2026-09-13 14:13:08</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -4085,12 +4353,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı!</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! SON TV</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -4106,25 +4374,29 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! SON TV</t>
+          <t>"Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! FLAŞ GELİŞME! MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı! SON TV MASAK incelemesinde 6 derneğin yurt dışından 3,3 milyon doları aşan para trafiği ortaya çıktı!</t>
+          <t>Van’da Düğün altınları için MASAK incelemesi Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.son.tv/flas-gelisme-masak-incelemesinde-dikkat-ceken-para-trafigi-6-dernege-yurt-disindan-33-milyon-dolari-asan-transfer-ortaya-cikti/</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>https://www.hakkarihabertv.com/vanda-dugun-altinlari-icin-masak-incelemesi-88464h.htm</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Van</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -4133,7 +4405,7 @@
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr"/>
@@ -4147,7 +4419,7 @@
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>58.92</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>17</v>
@@ -4156,7 +4428,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:13:08</t>
+          <t>2026-09-13 11:13:44</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -4171,12 +4443,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi</t>
+          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv</t>
+          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -4186,35 +4458,31 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
+          <t>enerji, masak</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>"Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. Mersin limanı’nda 350 kilogram kokain ele geçirildi Bingöl'de otomobil ile tır çarpıştı: 5 yaralı Van’da Düğün altınları için MASAK incelemesi Yayınlanma: 13 Eylül 2026 Pazar 17:13 Kaynak: Necmi Ertuş "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. Van Cumhuriyet Başsavcılığı tarafından Mehmet Fatih Tançalan hakkında sosyal medya platformlarında yapılan paylaşımlar nedeniyle "suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan soruşturma başlatıldı. Soruşturma kapsamında dün İstanbul'da gözaltına alınan Çağla Öz Tançalan'ın İstanbul Emniyet Müdürlüğü Mali Suçlarla Mücadele Şubesindeki işlemleri tamamlandı. Tançalan, işlemlerinin ardından Van Emniyet Müdürlüğüne götürüldü. Soruşturma kapsamında Van İl Emniyet Müdürlüğü Asayiş Şubesi ekipleri, Mehmet Fatih Tançalan'ı 8 Eylül'de Van'ın Muradiye ilçesindeki evinde gözaltına aldı. Emniyetteki işlemlerinin ardından adliyeye sevk edilen Tançalan, çıkarıldığı hakimlikçe "suçtan kaynaklanan malvarlığı değerlerini aklama" suçundan tutuklandı. Tançalan'ın sosyal medyaya yansıyan görüntüleri ile düğününde takıldığı belirtilen yüksek miktardaki altınlara ilişkin de mali araştırma başlatıldı ve Mali Suçları Araştırma Kurulundan (MASAK) inceleme talep edildi. Tançalan'ın düğününde eşi Çağla Öz Tançalan'a takılan ziynet eşyaları ve paralar, Muradiye'de bir ev ve eklentisinde yapılan aramada ele geçirildi. Aramanın gerçekleştirildiği evin sahibi de gözaltına alındı. HABERE YORUM KAT YASAL UYARI: Yazılan yoruml</t>
+          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. Mersin limanı’nda 350 kilogram kokain ele geçirildi Bingöl'de otomobil ile tır çarpıştı: 5 yaralı Van’da Düğün altınları için MASAK incelemesi Yayınlanma: 13 Eylül 2026 Pazar 17:13 Kaynak: Necmi Ertuş "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. Van Cumhuriyet Başsavcılığı tarafından Mehmet Fatih Tançalan hakkında sosyal medya platformlarında yapılan pay</t>
+          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5 Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_timeout</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakkarihabertv.com/vanda-dugun-altinlari-icin-masak-incelemesi-88464h.htm</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Bingöl | İstanbul | Van</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNcENzcjVCU05WeW5STWxZSnY5a1dWTnJfQ3p2S3ozZjc5TjJBSWVkdnlNdmFSWVBac29MQm1wM0NVTC1KWmZEbkdPbUFyQVlkcEdrLWFWWXdKUmZNM25mNm1FSjdUaFg0M3N6azZUQXJDZWtzZlhGYnZWbU5PZ01LcG04Qm9sU050NVNseDBDdnctWXNYU0xjeG4tZ3V4ZWtsbHIwRkhTR3Y1N29BdEVxYW9BcENMWjNWOEhOTGFGelFuZzlQWnhPcTJR?oc=5&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -4223,7 +4491,7 @@
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr"/>
@@ -4237,7 +4505,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="n">
-        <v>70.25</v>
+        <v>93.12</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>18</v>
@@ -4246,7 +4514,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 09:05:00</t>
+          <t>2026-09-13 12:22:00</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -4261,12 +4529,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı aydinlik.com.tr</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -4276,18 +4544,18 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
+          <t>masak, para transferi</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Vatan Partisi’nin dikkat çektiği küresel fon ağı MASAK raporuyla belgelendi. 6 LGBTİ+ derneğine Batı’dan 3,3 milyon doları aşkın kaynak aktarıldığı saptandı. 37 yabancı kurumdan sağlanan bu finansmanın cinsiyet değiştirme ameliyatları dahil çeşitli faaliyetlerde kullanıldığı belirlendi.</t>
+          <t>İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Gündem 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sevda Ecem Karapolat 13.09.2026 - 15:22 3 İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Soruşturma belgelerine dayandırılan bilgilere göre, 2021-2026 döneminde yabancı ve uluslararası kurumsal kaynaklardan yapılan 209 transferin işlem tarihlerindeki toplam karşılığı yaklaşık 67,4 milyon lira olarak hesaplandı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında, İstanbul merkezli 6 derneğin yurt içi ve yurt dışı bağlantılı para hareketleri incelemeye alındı. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu’nun 226’ncı maddesi kapsamında yürütülen araştırmada, MASAK Veri İnceleme Tutanağı ve bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte değerlendirildi. HANGİ DERNEKLERİN HESAPLARI İNCELENDİ? İnceleme kapsamında şu derneklerin hesap hareketleri ele alındı: Yemen’de çatışmalar şiddetlendi: İran destekli Husiler operasyon görüntülerini paylaştı İçeriği Görüntüle Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği (HEVİ) Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği Pozitif Yaşam Derneği Pozitif İz Derneği Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneği (SPoD) Belgelerde, yabancı kuruluşlardan gelen fonların yanı sıra GİB SWIFT kayıtları, gerçek kişiler tarafından yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketlerinin sıralandığı belirtildi. 45 BİN 135 İŞLEM KAYDI DEĞERLENDİRİLDİ İncelemeye ilişkin aktarılan bilgilere göre, “Bankacılık Transfer” tablosunda toplam 45 bin 135 işlem satırı bulunuyor. Bunların 13 bin 40’ını para girişleri , 32 bin 95’ini ise para çıkışları oluşturuyor. Para girişlerinin 218’inin doğrudan SWIFT alma işlemi olduğu kaydedildi. Gönderen adı, ülke bilgisi, işlemin SWIFT niteliği, banka ve açıklama bilgilerinin birlikte değerlendirilmesiyle yabancı kurumsal kaynaklardan gelen transferler ayrıca sınıflandırıldı. 37 KURUMSAL KAYNAKTAN 209 PARA GİRİŞİ 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan 209 para girişi belirlendiği aktarıldı. Bu işlemlerin gerçekleştirildikleri tarihlerdeki TL karşılıklarının toplamı 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde bu tutarın paranın bugünkü değerini ifade etmediği vurgulandı. Rakamın, farklı tarihlerde yapılan transferlerin MASAK kayıtlarındaki TL karşılıklarının aritmetik toplamından oluştuğu belirtildi. GİB SWIFT kayıtlarına ilişkin değerlendirmede ise derneklere gönderilen paranın dolar karşılığının 3 milyon 359 bin doları aştığı bilgisine yer verildi. YABANCI KURUMSAL GİRİŞLERİN YÜZDE 78’İ İKİ DERNEĞE Aktarılan inceleme bulgularına göre, 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinin yüzde 78’i SPoD ve HEVİ’ye yöneldi. Para hareketlerinde yabancı devlet kurumları, diplomatik misyonlar ve uluslararası kuruluşların yanı sıra gerçek kişilerden yapılan transferlerin de bulunduğu belirtildi. Paylaşılan bilgilerde, bu transferlerin suç oluşturduğuna ilişkin kesinleşmiş bir yargı kararına yer verilmedi. Kaynak: Haber Merkezi Editörün Seçtiği Benzine gece yarısı büyük zam geliyor: Ankara'da 80 liranın üzerine çıkacak! Editörün Seçtiği Kaşif Kozinoğlu'nun mezarı bugün açılacaktı: Feth-i kabir işlemi ertelendi! Editörün Seçtiği Kredi kartı limiti düşürülecek mi? İşte 2026 düzenlemesinin ayrıntıları... Editör Hakkında Sevda Ecem Karapolat Bunlar da ilginizi çekebilir Yemen’de çat</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı Vatan Partisi uyarmıştı, MASAK belgeledi: İşte LGBTİ+ derneklerinin küresel fon çarkı aydinlik.com.tr Vatan Partisi’nin dikkat çektiği küresel fon ağı MASAK raporuyla belgelendi. 6 LGBTİ+ derneğine Batı’dan 3,3 milyon doları aşkın kaynak aktarıldığı saptandı. 37 yabancı kurumdan sağlanan bu finansmanın cinsiyet değiştirme ameliyatları dahil çeşitli faaliyetlerde kullanıldığı belirlendi.</t>
+          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Gündem 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sevda Ecem Karapolat 13.09.2026 - 15:22 3 İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Soruşturma belgelerine dayandırılan bilgilere göre, 2021-2026 döneminde yabancı ve uluslararası kurumsal kaynaklardan yapılan 209 transferin işlem tarihlerindeki toplam karşılığı yaklaşık 67,4 milyon lira olarak hesaplandı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında, İstanbul merkezli 6 derneğin yurt içi ve yurt dışı bağlantılı para hareketleri incelemeye alındı. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu’nun 226’ncı maddesi kapsamında yürütülen araştırmada, MASAK Veri İnceleme Tutanağı ve bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte değerlendirildi. HANGİ DERNEKLERİN HESAPLARI İNCELENDİ? İnceleme kapsamında şu derneklerin hesap hareketleri ele alındı: Yemen’de çatışmalar şiddetlendi: İran destekli Husiler operasyon görüntülerini paylaştı İçeriği Görüntüle Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği (HEVİ) Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği Pozitif Yaşam Derneği Pozitif İz Derneği Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneği (SPoD) Belgelerde, yabancı kuruluşlardan gelen fonların yanı sıra GİB SWIFT kayıtları, gerçek kişiler tarafından yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketlerinin sıralandığı belirtildi. 45 BİN 135 İŞLEM KAYDI DEĞERLENDİRİLDİ İncelemeye ilişkin aktarılan bilgilere göre, “Bankacılık Transfer” tablosunda toplam 45 bin 135 işlem satırı bulunuyor. Bunların 13 bin 40’ını para girişleri , 32 bin 95’ini ise para çıkışları oluşturuyor. Para girişlerinin 218’inin doğrudan SWIFT alma işlemi olduğu kaydedildi. 37 KURUMSAL KAYNAKTAN 209 PARA GİRİŞİ 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan 209 para girişi belirlendiği aktarıldı. Rakamın, farklı tarihlerde yapılan transferlerin MASAK kayıtlarındaki TL karşılıklarının aritmetik toplamından oluştuğu belirtildi. GİB SWIFT kayıtlarına ilişkin değerlendirmede ise derneklere gönderilen paranın dolar karşılığının 3 milyon 359 bin doları aştığı bilgisine yer verildi. YABANCI KURUMSAL GİRİŞLERİN YÜZDE 78’İ İKİ DERNEĞE Aktarılan inceleme bulgularına göre, 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinin yüzde 78’i SPoD ve HEVİ’ye yöneldi. Para hareketlerinde yabancı devlet kurumları, diplomatik misyonlar ve uluslararası kuruluşların yanı sıra gerçek kişilerden yapılan transferlerin de bulunduğu belirtildi. Editörün Seçtiği Kaşif Kozinoğlu'nun mezarı bugün açılacaktı: Feth-i kabir işlemi ertelendi!</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -4297,10 +4565,14 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.aydinlik.com.tr/haber/vatan-partisi-uyarmisti-masak-belgeledi-iste-lgbti-derneklerinin-kuresel-fon-carki-589932</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>https://www.ankaranethaber.com/6-lgbt-dernegine-yurt-disindan-para-transferi-masak-incelemesinde-209-islem-belirlendi</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
@@ -4309,7 +4581,7 @@
       <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr"/>
@@ -4323,7 +4595,7 @@
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="n">
-        <v>86.62</v>
+        <v>111</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>19</v>
@@ -4332,27 +4604,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 06:35:00</t>
+          <t>2026-09-14 07:21:29</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti</t>
+          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Ege Telgraf</t>
+          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursada Bugün</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -4362,18 +4634,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>işletme, masak</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t>inşaat, şirket</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Gündem Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 13.09.2026 - 09:35 Okunma Süresi: 1 Dk Adalet Bakanı Akın Gürlek, İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonlarına ilişkin açıklamalarda bulundu. 5 il merkezli olarak 15 ili kapsayan operasyonlarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığı bildirildi. 162 ŞÜPHELİ HAKKINDA ADLİ SÜREÇ Emniyet ve Jandarma birimlerinin katılımıyla gerçekleştirilen operasyonlarda, 162 şüpheli hakkında adli işlem uygulandı. Soruşturmaların; fuhşa aracılık veya yer temini, müstehcen içeriklerin üretilmesi ve yayılması ile çocukların bu tür içeriklere maruz bırakılmasına yönelik faaliyetler üzerinde yoğunlaştığı belirtildi. Dolar 48 TL’yi aştı, Euro 56 TL seviyesinde! 13 Eylül güncel döviz kurları: Dolar kaç TL? Euro ne kadar? İçeriği Görüntüle Faaliyetlere ortam sağladığı değerlendirilen bazı işletmeler ile soruşturmaya konu edilen 9 dernek de incelemeye alındı. Toplam 13 işletme hakkında da adli işlem gerçekleştirildi. 15 İLDE EŞ ZAMANLI OPERASYON DÜZENLENDİ Soruşturma sürecinde gizli soruşturmacı görevlendirilmesinin yanı sıra teknik ve fiziki takip yapıldığı bildirildi. Tanık ifadeleri, dijital incelemeler ve görüntü kayıtlarından da yararlanıldığı aktarıldı. Elde edilen deliller doğrultusunda 15 ilde eş zamanlı gözaltı, arama ve el koyma işlemleri gerçekleştirildi. Operasyonlarda uyuşturucu maddeler ile çok sayıda dijital materyale el konuldu. SOSYAL MEDYA HESAPLARINA ERİŞİM ENGELİ Soruşturmalar kapsamında çok sayıda sosyal medya hesabı ve internet sitesi hakkında da erişimin engellenmesi tedbirinin uygulandığı açıklandı. MASAK'TAN FON HAREKETLERİNE İNCELEME Operasyonların mali boyutuna ilişkin yapılan incelemelerde ise MASAK'ın bazı derneklere yönelik para hareketlerini mercek altına aldığı belirtildi. Yapılan incelemelerde, bazı derneklere yurt dışında bulunan kamu kurumları ve yabancı kuruluşlardan yüksek miktarlarda fon aktarıldığının tespit edildiği aktarıldı. Söz konusu fonların kaynağı ile soruşturma kapsamında incelenen faaliyetler arasında herhangi bir bağlantı bulunup bulunmadığının araştırıldığı kaydedildi. Adalet Bakanı Akın Gürlek, açıklamasında çocukları, gençleri ve aileleri hedef alan suç yapılanmaları, istismar ağları ve yasa dışı faaliyetlere karşı müsamaha gösterilmeyeceğini ifade etti. Kaynak: HABER MERKEZİ Editörün Seçtiği Aydın’da ayakta kalan üç kuleden biri! Zindanından hamamına eksiksiz Ege’nin 200 yıllık az bilinen tarihi şatosu Editörün Seçtiği Ne Efes ne Bergama! 5 bin yıllık değişimin tanığı: İzmir’in kayıp ada kentinde binlerce boncuk bulundu Editörün Seçtiği Ne Efes ne Bergama! İZBAN’dan inip kralların tepesine çıkılıyor: İzmir’de üç saraylı antik kenti çoğu kişi bilmiyor Editör Hakkında Kader Ergin Bunlar da ilgini</t>
+          <t>Bursa'da Ankaş İnşaat ve E.A. A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da Ankaş İnşaat ve E.A. A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da Ankaş İnşaat ve E.A. A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursa'da konkordato kararı verilen şirket için 3 aylık mühlet Şirketin taşınır ve taşınmazlarının devrine kısıtlama 10 Eylül'den itibaren yeni icra ve iflas takibi yapılamayacak Konkordato komiseri görevlendirildi Alacaklılara itiraz için 7 günlük süre Konkordato sürecinde duruşma tarihi belirlenmedi Bursa'da Ankaş İnşaat ve E.A. A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da faaliyet gösteren Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. hakkında konkordato süreci başlatıldı. Bursa 1. Asliye Ticaret Mahkemesi, şirket ile davacılardan E. A. A. için 3 aylık geçici konkordato mühleti verilmesine karar verdi. Kararla birlikte borçluların mal varlıklarının devrine yönelik kısıtlamalar getirilirken, yeni icra ve iflas takiplerinin de önüne geçildi. Bursa 1. Asliye Ticaret Mahkemesi'nde görülen konkordato davasında önemli bir ara karar çıktı. 2026/678 Esas numarasıyla yürütülen dosyada, Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret Anonim Şirketi ile Emine Altun Anık hakkında geçici mühlet uygulanmasına hükmedildi. Mahkemenin 10 Eylül 2026 tarihli tensip kararları kapsamında verilen mühletin süresi üç ay olarak belirlendi. Böylece davacı-borçlular açısından konkordato hükümlerinin uygulanacağı yeni bir dönem başlamış oldu. Konkordato, borçlarını mevcut koşullar altında ödemekte zorlanan şirket veya kişilerin, alacaklılarıyla yeniden yapılandırma yoluna gitmesini sağlayan hukuki bir süreç olarak uygulanıyor. Bursa 1. Asliye Ticaret Mahkemesi de söz konusu dosyada geçici mühlet verilmesini uygun buldu. Karar doğrultusunda Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. ile E. A. A. için üç aylık geçici konkordato mühleti başladı. Geçici mühlet süresince borçluların mal varlıkları üzerinde yapabileceği bazı işlemler mahkeme denetimine tabi olacak. Özellikle şirketin faaliyetlerinin ve mevcut varlıklarının korunması amacıyla önemli sınırlamalar getirildi. Mahkeme kararıyla davacı-borçlular adına kayıtlı taşınır ve taşınmaz malların üçüncü kişilere devredilmesi, yeni bir karar verilinceye kadar yasaklandı. Bunun yanında borçluların mahkemenin izni olmadan belirli tasarruflarda bulunmasının da önüne geçildi. Konkordato mühleti boyunca borçluların rehin tesis etmesi, kefil olması veya taşınmazlarıyla işletmenin devamlı tesisatını kısmen ya da tamamen devretmesi mümkün olmayacak. Aynı şekilde bu varlıklar üzerinde kısıtlayıcı işlemler yapılması ve karşılıksız tasarruflarda bulunulması da mahkeme iznine bağlandı. Bu tedbirlerin temel amacı, konkordato sürecinde borçluların mevcut mal varlığının korunması ve alacaklıların haklarının zarar görmemesi olarak öne çıkıyor. Mahkemenin kararında konkordato mühletinin önemli sonuçlarından biri de icra ve iflas takipleri bakımından ortaya çıktı. İcra ve İflas Kanunu'nun ilgili hükümleri doğrultusunda 10 Eylül 2026 tarihinden itibaren davacı-borçlular hakkında yeni icra ve iflas takibi başlatılamayacak. Tedbir kararı yalnızca klasik icra işlemleriyle sınırlı kalmadı. Borçlular aleyhine yürütülebilecek takip işlemlerinin yanı sıra ihtiyati tedbir, ihtiyati haciz ve muhafaza işlemleri de karar kapsamında değerlendirildi. Bu süreçte davacıların mal varlığı üzerinde gerçekleştirilebilecek takip işlemlerine yönelik koruma sağlandı. Ancak mahkeme kararında, konkordato tedbirlerinin İcra ve İflas Kanunu'nun 206. maddesinin birinci sırasında yer alan imtiyazlı alacaklar ile rehinle güvence altına alınmış alacaklar bakımından geçerli olmayacağı da belirtildi. Mahkeme, üç aylık geçici mühlet döneminin denetimli şekilde yürütülmesi amacıyla konkordato komiseri de görevlendirdi. Dosyada mali konularda uzman komiser olarak Süreyyа Turhan atandı. Komiser, konkordato sürecinde borçluların mali durumunun değerlendirilmesi ve mahkemenin ihtiyaç duyduğu incelemelerin gerçekleştirilmesi bakımından görev yapacak. Komiserin atanmasıyla birlikte şirketin ve diğer davacı-borçlunun konkordato sürecindeki mali yapısının daha yakından incelenmesi bekleniyor. Mahkemenin ilanında, davacı-borçlulardan alacağı bulunduğunu ileri süren kişilere ve kurumlara da önemli bir süre tanındı. Buna göre alacaklı olduğunu iddia edenler, ilan tarihinden itibaren yedi gün içerisinde mahkemeye dilekçe sunarak itirazda bulunabilecek. İtiraz edecek kişilerin, konkordato mühleti verilmesini gerektiren koşulların bulunmadığını ileri sürmeleri ve iddialarını delilleriyle birlikte ortaya koymaları gerekiyor. Bu süre, konkordato sürecine ilişkin itirazların mahkeme tarafından değerlendirilmesi açısından önem taşıyor. Mahkeme tarafından geçici mühlet kararının ardından doğrudan bir duruşma günü belirlenmemesi de dikkat çekti. Bunun nedeni, geçici mühletin uzatılması veya sürenin tamamlanmasını beklemeden yeni bir karar alınmasını gerektirebilecek önemli gelişmelerin ortaya çıkabilmesi ihtimali olarak açıklandı. Dolayısıyla dosyada önümüzdeki dönemde şirketin mali durumu, konkordato sürecindeki gelişmeler ve mahkemenin yapacağı değerlendirmeler belirleyici olacak. Bursa'daki konkordato dosyası, 10 Eylül 2026 tarihli kararın ardından üç aylık geçici mühlet dönemiyle devam edecek. Bu süreçte şirketin mali yapısına ilişkin incelemeler sürdürülürken, alacaklıların itirazları ve komiser tarafından yapılacak çalışmalar da dosyanın geleceği açısından önem taşıyacak. Diğer Bursa Haberleri - Bölge Haberleri için tıklayın Türkiye bu olayı konuşuyor: 11 aylık Büşra'dan 4 gündür haber yok! Anne "satıldı" dedi, baba reddetti Cezaevinden çıkan Fatma Soydaş'ın son hali şaşırttı! İlk görüntüsü ortaya çıktı Bursa'da gözler bu toplantıda! Nilüfer'de tartışma yaratan imar planı gündemde... Bursa Orhangazi'de dev operasyon! 8 ton ele geçirildi... Kurtlar Vadisi sahneleri yeniden gündemde: Plakadaki detay dikkat çekti! Bursa'da vicdanları sızlatan görüntü!</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Ege Telgraf Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı Gündem Bakan Gürlek duyurdu: 9 dernek ve 13 işletme mercek altında, MASAK harekete geçti Adalet Bakanı Akın Gürlek, “Ailem Güvende” operasyonları kapsamında 5 il merkezli 15 ilde yürütülen soruşturmalarda 162 şüpheli ile 9 dernek ve 13 işletme hakkında adli işlem başlatıldığını açıkladı. Operasyonlarda çok sayıda dijital materyal ve uyuşturucu maddeye el konulurken, bazı sosyal medya hesapları ve internet siteleri için erişim engeli uygulandı</t>
+          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursada Bugün Bursa'da Ankaş İnşaat ve E.A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursa'da konkordato kararı verilen şirket için 3 aylık mühlet Şirketin taşınır ve taşınmazlarının devrine kısıtlama 10 Eylül'den itibaren yeni icra ve iflas takibi yapılamayacak Konkordato komiseri görevlendirildi Alacaklılara itiraz için 7 günlük süre Konkordato sürecinde duruşma tarihi belirlenmedi Bursa'da Ankaş İnşaat ve E.A. Bursa'da faaliyet gösteren Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. hakkında konkordato süreci başlatıldı. Asliye Ticaret Mahkemesi, şirket ile davacılardan E. için 3 aylık geçici konkordato mühleti verilmesine karar verdi. Kararla birlikte borçluların mal varlıklarının devrine yönelik kısıtlamalar getirilirken, yeni icra ve iflas takiplerinin de önüne geçildi. Asliye Ticaret Mahkemesi'nde görülen konkordato davasında önemli bir ara karar çıktı. 2026/678 Esas numarasıyla yürütülen dosyada, Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret Anonim Şirketi ile Emine Altun Anık hakkında geçici mühlet uygulanmasına hükmedildi. Böylece davacı-borçlular açısından konkordato hükümlerinin uygulanacağı yeni bir dönem başlamış oldu. Konkordato, borçlarını mevcut koşullar altında ödemekte zorlanan şirket veya kişilerin, alacaklılarıyla yeniden yapılandırma yoluna gitmesini sağlayan hukuki bir süreç olarak uygulanıyor. Asliye Ticaret Mahkemesi de söz konusu dosyada geçici mühlet verilmesini uygun buldu. Karar doğrultusunda Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. ile E. için üç aylık geçici konkordato mühleti başladı. Geçici mühlet süresince borçluların mal varlıkları üzerinde yapabileceği bazı işlemler mahkeme denetimine tabi olacak. Özellikle şirketin faaliyetlerinin ve mevcut varlıklarının korunması amacıyla önemli sınırlamalar getirildi. Bunun yanında borçluların mahkemenin izni olmadan belirli tasarruflarda bulunmasının da önüne geçildi. Konkordato mühleti boyunca borçluların rehin tesis etmesi, kefil olması veya taşınmazlarıyla işletmenin devamlı tesisatını kısmen ya da tamamen devretmesi mümkün olmayacak. Aynı şekilde bu varlıklar üzerinde kısıtlayıcı işlemler yapılması ve karşılıksız tasarruflarda bulunulması da mahkeme iznine bağlandı. Bu tedbirlerin temel amacı, konkordato sürecinde borçluların mevcut mal varlığının korunması ve alacaklıların haklarının zarar görmemesi olarak öne çıkıyor. Mahkemenin kararında konkordato mühletinin önemli sonuçlarından biri de icra ve iflas takipleri bakımından ortaya çıktı. İcra ve İflas Kanunu'nun ilgili hükümleri doğrultusunda 10 Eylül 2026 tarihinden itibaren davacı-borçlular hakkında yeni icra ve iflas takibi başlatılamayacak. Tedbir kararı yalnızca klasik icra işlemleriyle sınırlı kalmadı. Bu süreçte davacıların mal varlığı üzerinde gerçekleştirilebilecek takip işlemlerine yönelik koruma sağlandı. Ancak mahkeme kararında, konkordato tedbirlerinin İcra ve İflas Kanunu'nun 206. maddesinin birinci sırasında yer alan imtiyazlı alacaklar ile rehinle güvence altına alınmış alacaklar bakımından geçerli olmayacağı da belirtildi. Mahkeme, üç aylık geçici mühlet döneminin denetimli şekilde yürütülmesi amacıyla konkordato komiseri de görevlendirdi. Komiser, konkordato sürecinde borçluların mali durumunun değerlendirilmesi ve mahkemenin ihtiyaç duyduğu incelemelerin gerçekleştirilmesi bakımından görev yapacak. Komiserin atanmasıyla birlikte şirketin ve diğer davacı-borçlunun konkordato sürecindeki mali yapısının daha yakından incelenmesi bekleniyor. İtiraz edecek kişilerin, konkordato mühleti verilmesini gerektiren koşulların bulunmadığını ileri sürmeleri ve iddialarını delilleriyle birlikte ortaya koymaları gerekiyor. Bu süre, konkordato sürecine ilişkin itirazların mahkeme tarafından değerlendirilmesi açısından önem taşıyor. Mahkeme tarafından geçici mühlet kararının ardından doğrudan bir duruşma günü belirlenmemesi de dikkat çekti. Bunun nedeni, geçici mühletin uzatılması veya sürenin tamamlanmasını beklemeden yeni bir karar alınmasını gerektirebilecek önemli gelişmelerin ortaya çıkabilmesi ihtimali olarak açıklandı. Dolayısıyla dosyada önümüzdeki dönemde şirketin mali durumu, konkordato sürecindeki gelişmeler ve mahkemenin yapacağı değerlendirmeler belirleyici olacak. Bursa'daki konkordato dosyası, 10 Eylül 2026 tarihli kararın ardından üç aylık geçici mühlet dönemiyle devam edecek. Bu süreçte şirketin mali yapısına ilişkin incelemeler sürdürülürken, alacaklıların itirazları ve komiser tarafından yapılacak çalışmalar da dosyanın geleceği açısından önem taşıyacak. Diğer Bursa Haberleri - Bölge Haberleri için tıklayın Türkiye bu olayı konuşuyor: 11 aylık Büşra'dan 4 gündür haber yok! Anne "satıldı" dedi, baba reddetti Cezaevinden çıkan Fatma Soydaş'ın son hali şaşırttı! İlk görüntüsü ortaya çıktı Bursa'da gözler bu toplantıda! Bursa Orhangazi'de dev operasyon! Bursa'da vicdanları sızlatan görüntü!</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -4383,33 +4659,69 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.egetelgraf.com/bakan-gurlek-duyurdu-9-dernek-ve-13-isletme-mercek-altinda-masak-harekete-gecti</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>https://www.bursadabugun.com/haber/bursa-da-insaat-sirketi-icin-konkordato-sureci-basladi-mahkemeden-3-aylik-gecici-muhlet-karari-1948726.html</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Orhangazi</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr"/>
-      <c r="V21" s="2" t="inlineStr"/>
-      <c r="W21" s="2" t="inlineStr"/>
+          <t>faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş Orhangazi Bursa Türkiye</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Cargill Türkiye Bursa Orhangazi Mısır İşleme Tesisi</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Cargill Türkiye Bursa Orhangazi Mısır İşleme Tesisi</t>
+        </is>
+      </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr"/>
-      <c r="Z21" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>48.54368932038835</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>Ysf gida depo</t>
+        </is>
+      </c>
       <c r="AA21" s="2" t="n">
-        <v>94.75</v>
+        <v>199.75</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>20</v>
@@ -4418,27 +4730,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 07:18:00</t>
+          <t>2026-09-14 08:57:35</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında KARAR</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -4448,48 +4760,44 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonları 15 ili kapsadı. Fuhuş, müstehcenlik, uyuşturucu ve çocukların korunmasına ilişkin soruşturmalar kapsamında 162 şüpheli, 9 dernek ve 13 işletme hakkında adli işlem başlatıldı. Operasyonlarda çok sayıda uyuşturucu madde ve dijital materyale el konulurken, bazı sosyal medya hesapları ile internet siteleri hakkında da erişim engeli tedbiri uygulandı. İSTANBUL’DA 54 ADRESE OPERASYON İstanbul merkezli çalışmada İstanbul’un yanı sıra Ankara, Çanakkale, İzmir, Antalya, Ordu, Elazığ, Balıkesir, Aydın, Kırşehir, Iğdır ve Hatay’da operasyonlar düzenlendi. 38 şüpheliye yönelik adreslerde arama, yakalama ve el koyma işlemleri gerçekleştirilirken, İstanbul’da 10 işletme ile 6 LGBTİ+ derneğinin de aralarında bulunduğu toplam 54 iş yeri, ev ve dernekte arama yapıldı. UYUŞTURUCU, KAÇAK ALKOL VE RUHSATSIZ SİLAH ELE GEÇİRİLDİ Aramalarda 25 gram uyuşturucu ve uyarıcı madde, 10 gram kokain, 9 gram esrar, uyuşturucu olduğu değerlendirilen 10 sentetik hap, 7 enjektör ve iğnesi, yaklaşık 2 bin şişe kaçak alkol, ruhsatsız tabanca, 5 kamera kayıt cihazı ve 26 cep telefonu ele geçirildi. İstanbul'daki operasyonlarda 26 şüpheli gözaltına alınırken, diğer şüphelilerin yakalanmasına yönelik çalışmaların sürdüğü belirtildi. Bir işletme ise ruhsat faaliyetlerine aykırı hareket ettiği gerekçesiyle mühürlendi. MASAK İNCELEMESİNDE YÜKSEK TUTARLI FON AKTARIMI TESPİT EDİLDİ “Ailem Güvende” operasyonları kapsamında yürütülen soruşturmanın mali boyutunda MASAK incelemeleri dikkat çekti. Adalet Bakanı Akın Gürlek, bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığının tespit edildiğini açıkladı. Gürlek, söz konusu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısının araştırıldığını bildirdi. Gürlek'in açıklaması şöyle: "Cumhurbaşkanımız Recep Tayyip Erdoğan’ın ortaya koyduğu 2026-2035 Aile ve Nüfus On Yılı vizyonu ve 2026/4 Sayılı Cumhurbaşkanlığı Genelgesi doğrultusunda; çocuklarımızı, aile kurumunu ve toplum düzenini korumaya yönelik çalışmalarımızı kararlılıkla sürdürüyoruz. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımızın koordinasyonunda, Emniyet ve Jandarma teşkilatlarımızla birlikte başlatılan "Ailem Güvende" operasyonlarında, 5 il merkezli ve toplam 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletmeye yönelik adli işlemler gerçekleştirilmektedir. Soruşturmalarda; fuhşa aracılık veya yer temin eden kişiler, bu faaliyetlere ortam sağladığı değerlendirilen işletmeler, müstehcen içerik üreten ve yayan şüpheliler ile çocukların bu içeriklere maruz bırakılmasına yönelik faaliyetler incelenmiştir. Gizli soruşturmacı görevlendirilmesi, teknik ve fiziki takip, tanık beyanları, dijital incelemeler ve görüntü kayıtları sonucunda eş zamanlı gözaltı, arama ve el koyma işlemleri yapılmış; uyuşturucu maddeler ile çok sayıda dijital materyale el konulmuş, çok sayıda sosyal medya hesabı ve internet sitesine erişimin engellenmesi tedbiri uygulanmıştır. Soruşturmaların mali boyutunda ise LGBT ve ahlaksızlığı teşvik eden derneklere ilişkin; MASAK incelemelerinde bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığı tespit edilmiştir. Bu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısı araştırılmaktadır. Soruşturmaları titizlikle yürüten İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımıza, operasyonlarda görev alan Emniyet ve Jandarma teşkilatlarımızın kıymetli mensuplarına ve katkı sunan tüm kamu görevlilerimize teşekkür ediyorum. Anayasamızın aile ve çocukların korunmasına ilişkin devlete yüklediği sorumluluk çerçevesinde, çocuklarımızı, gençlerimizi ve ailelerimizi hedef alan hiçbir suç yapılanmasına, istismar ağına ve yasa dışı faaliyete müsamaha göstermeyeceğiz" ERİŞİM ENGELİ GETİRİLDİĞİ BELİRTİLEN 73 SİTE VE HESAP Soruşturma kapsamında erişim engeli getirildiği belirtilen site ve sosyal medya hesapları arasında LGBTİ+ alanında faaliyet gösteren dernek, oluşum ve platformların yanı sıra bazı akademik öğrenci toplulukları, medya platformları ve kişiler de yer aldı. Kaos GL SPoD LGBTİ+ Pembe Hayat LGBTİ+ Dayanışma Derneği ÜniKuir Derneği Lambdaistanbul LGBTİ+ Dayanışma Derneği 17 Mayıs Derneği HEVİ LGBTİ+ Derneği Kırmızı Şemsiye Derneği Genç LGBTİ+ Derneği Özgür Renkler Derneği Muamma LGBTİ+ Derneği Mersin 7 Renk Derneği Queer Adana Antalya BİZ Derneği Keskesor LGBTİ+ Cinsel Şiddetle Mücadele Derneği CETAD Velvele GZone Ayı Sözlük Boysan'ın Evi LGBTI News Turkey İstanbul LGBTİ+ Onur Haftası İstanbul Trans Onur Haftası Ankara Onur Haftası İzmir Onur Haftası ODTÜ LGBTİ+ Dayanışması Boğaziçi Üniversitesi LGBTİ+ Çalışmaları Kulübü Bilkent Renkli Düşün İstanbul Üniversitesi Radar Queer Deer – Hacettepe Üniversitesi Enes Hocaoğulları Yasemin Öz Ali Erol Ali Özbaş Zeynep Esmeray Özadikti Buse Kılıçkaya Şevval Kılıç Levent Pişkin Yıldız Tar İlker Hepkaner Mert Bell Mika Can Raun Seyhan Arman Kuir Tıp Öğrencileri Ağı Renkli Güvercin LGBTIQ GoFor Hormon Hakkım Kolektifi Kuir Baykuş GALA Derneği ÜniKuir2 Kuir Konya Eşitlik İçin Eğitimciler Kapsama Alanı Aşko Anlat Sportif Lezbon Arya'ya Ne Oldu Aforgütü Direnişin Renkleri Pozitif Dayanışma Bodrum Kadın Platformu Barış İçin LGBTİ+ Sivil Alan Araştırmaları Demos Araştırma Eşitlik İçin Kadın Platformu Qlub ÜniKuir Derste Zengiinn All Inclusive Mag LISTAG Boğaziçi LGBTİA İnter Dayanışma LGBT Türkiye 19:19 İstanbul'da yarın ulaşım ücretsiz: Sadece okul saatleri içerisinde 19:15 Trump, İran'la savaşın bitimine dair tarih verdi: Ara seçimler... 18:35 Suudi Arabistan'dan 'güvenlik' mesajı: İzin vermeyeceğiz 18:14 Trabzonspor’da Şenol Güneş sesleri 18:07 Yaz bitti mi, yağışlar başlıyor mu? Meteoroloji'den yeni hafta için 11 illik uyarı 18:04 Formula 1’in ilk Madrid yarışında tarihi zafer 17:54 TOKİ kiralık konut başvurusu ücretli mi? Bekarlar başvuru yapabilecek mi? Kiralık evler satın alınabilecek mi? 17:49 Osimhen için karar verildi: Dönüş tarihi belli oldu 17:38 Katılımevim’de yönetim değişti, Tera ile devir süreci sürüyor 17:38 Ankara’da yarın bazı yollar trafiğe kapatılacak 17:35 Irak, İran sınırındaki 3 sınır kapısını yeniden açıyor 17:34 Ünlülere yönelik uyuşturucu soruşturmasında yeni operasyon: Oyuncu Çağla Boz gözaltına alındı 17:32 Toprak Razgatlıoğlu San Marino’da 12. oldu 17:20 Uzaklaştırma kararı engel olmadı: Uzman çavuş eşini öldürüp intihar etti 17:13 Almanya'da aşırı sağ ve AfD’ye karşı protestolar artıyor MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. 13/09/2026 10:18 KAYNAK: Anadolu Ajansı (AA) İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonları 15 ili kapsadı. Fuhuş, müstehcenlik, uyuşturucu ve çocukların korunmasına ilişkin soruşturmalar kapsamında 162 şüpheli, 9 dernek ve 13 işletme hakkında adli işlem başlatıldı. Operasyonlarda çok sayıda uyuşturucu madde ve dijital materyale el konulurken, bazı sosyal medya hesapları ile internet siteleri hakkında da erişim engeli tedbiri uygulandı. İSTANBUL’DA 54 ADRESE OPERASYON İstanbul merkezli çalışmada İstanbul’un yanı sıra Ankara, Çanakkale, İzmir, Antalya, Ordu, Elazığ, Balıkesir, Aydın, Kırşehir, Iğdır ve Hatay’da operasyonlar düzenlendi. 38 şüpheliye yönelik adreslerde arama, yakalama ve el koyma işlemleri gerçekleştirilirken, İstanbul’da 10 işletme ile 6 LGBTİ+ derneğinin de aralarında bulunduğu toplam 54 iş yeri, ev ve dernekte arama yapıldı. UYUŞTURUCU, KAÇAK ALKOL VE RUHSATSIZ SİLAH ELE GEÇİRİLDİ Aramalarda 25 gram uyuşturucu ve uyarıcı madde, 10 gram kokain, 9 gram esrar, uyuşturucu olduğu değerlendirilen 10 sentetik hap, 7 enjektör ve iğnesi, yaklaşık 2 bin şişe kaçak alkol, ruhsatsız tabanca, 5 kamera kayıt cihazı ve 26 cep telefonu ele geçirildi. İstanbul'daki operasyonlarda 26 şüpheli gözaltına alınırken, diğer şüphelilerin yakalanmasına yönelik çalışmaların sürdüğü belirtildi. Bir işletme ise ruhsat faaliyetlerine aykırı hareket ettiği gerekçesiyle mühürlendi. MASAK İNCELEMESİNDE YÜKSEK TUTARLI FON AKTARIMI TESPİT EDİLDİ “Ailem Güvende” operasyonları kapsamında yürütülen soruşturmanın mali boyutunda MASAK incelemeleri dikkat çekti. Adalet Bakanı Akın Gürlek, bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığının tespit edildiğini açıkladı. Gürlek, söz konusu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısının araştırıldığını bildirdi. Gürlek'in açıklaması şöyle: "Cumhurbaşkanımız Recep Tayyip Erdoğan’ın ortaya koyduğu 2026-2035 Aile ve Nüfus On Yılı vizyonu ve 2026/4 Sayılı Cumhurbaşkanlığı Genelgesi doğrultusunda; çocuklarımızı, aile kurumunu ve toplum düzenini korumaya yönelik çalışmalarımızı kararlılıkla sürdürüyoruz. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımızın koordinasyonunda, Emniyet ve Jandarma teşkilatlarımızla birlikte başlatılan "Ailem Güvende" operasyonlarında, 5 il merkezli ve toplam 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletmeye yönelik adli işlemler gerçekleştirilmektedir. Soruşturmalarda; fuhşa aracılık veya yer temin eden kişiler, bu faaliyetlere ortam sağladığı değerlendirilen işletmeler, müstehcen içerik üreten ve yayan şüpheliler ile çocukların bu içeriklere maruz bırakılmasına yönelik faaliyetler incelenmiştir. Gizli soruşturmacı görevlendirilmesi, teknik ve fiziki takip, tanık beyanları, dijital incelemeler ve görüntü kayıtları sonucunda eş zamanlı gözaltı, arama ve el koyma işlemleri yapılmış; uyuşturucu maddeler ile çok sayıda dijital materyale el konulmuş, çok sayıda sosyal medya hesabı ve internet sitesine erişimin engellenmesi tedbiri uygulanmıştır. Soruşturmaların mali boyutunda ise LGBT ve ahlaksızlığı teşvik eden derneklere ilişkin; MASAK incelemelerinde bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığı tespit edilmiştir. Bu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısı araştırılmaktadır. Soruşturmaları titizlikle yürüten İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımıza, operasyonlarda görev alan Emniyet ve Jandarma teşkilatlarımızın kıymetli mensuplarına ve katkı sunan tüm kamu görevlilerimize teşekkür ediyorum. Anayasamızın aile ve çocukların korunmasına ilişkin devlete yüklediği sorumluluk çerçevesinde, çocuklarımızı, gençlerimizi ve ailelerimizi hedef alan hiçbir suç yapılanmasına, istismar ağına ve yasa dışı faaliyete müsamaha göstermeyeceğiz" ERİŞİM ENGELİ GETİRİLDİĞİ BELİRTİLEN 73 SİTE VE HESAP Soruşturma kapsamında erişim engeli getirildiği belirtilen site ve sosyal medya hesapları arasında LGBTİ+ alanında faaliyet gösteren dernek, oluşum ve platformların yanı sıra bazı akademik öğrenci toplulukları, medya platformları ve kişiler de yer aldı. Kaos GL SPoD LGBTİ+ Pembe Hayat LGBTİ+ Dayanışma Derneği ÜniKuir Derneği Lambdaistanbul LGBTİ+ Dayanışma Derneği 17 Mayıs Derneği HEVİ LGBTİ+ Derneği Kırmızı Şemsiye Derneği Genç LGBTİ+ Derneği Özgür Renkler Derneği Muamma LGBTİ+ Derneği Mersin 7 Renk Derneği Queer Adana Antalya BİZ Derneği Keskesor LGBTİ+ Cinsel Şiddetle Mücadele Derneği CETAD Velvele GZone Ayı Sözlük Boysan'ın Evi LGBTI News Turkey İstanbul LGBTİ+ Onur Haftası İstanbul Trans Onur Haftası Ankara Onur Haftası İzmir Onur Haftası ODTÜ LGBTİ+ Dayanışması Boğaziçi Üniversitesi LGBTİ+ Çalışmaları Kulübü Bilkent Renkli Düşün İstanbul Üniversitesi Radar Queer Deer – Hacettepe Üniversitesi Enes Hocaoğulları Yasemin Öz Ali Erol Ali Özbaş Zeynep Esmeray Özadikti Buse Kılıçkaya Şevval Kılıç Levent Pişkin Yıldız Tar İlker Hepkaner Mert Bell Mika Can Raun Seyhan Arman Kuir Tıp Öğrencileri Ağı Renkli Güvercin LGBTIQ GoFor Hormon Hakkım Kolektifi Kuir Baykuş GALA Derneği ÜniKuir2 Kuir Konya Eşitlik İçin Eğitimciler Kapsama Alanı Aşko Anlat Sportif Lezbon Arya'ya Ne Oldu Aforgütü Direnişin Renkleri Pozitif Dayanışma Bodrum Kadın Platformu Barış İçin LGBTİ+ Sivil Alan Araştırmaları Demos Araştırma Eşitlik İçin Kadın Platformu Qlub ÜniKuir Derste Zengiinn All Inclusive Mag LISTAG Boğaziçi LGBTİA İnter Dayanışma LGBT Türkiye YORUMLAR Diğer Haberler İstanbul'da yarın ulaşım ücretsiz Yaz bitti mi, yağışlar başlıyor mu? Meteoroloji'den yeni hafta için</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında KARAR İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. Operasyon kapsamında 73 site ve sosyal medya hesaplarına erişim engeli getirildi. MASAK incelemelerinde ise bazı derneklere yurt dışından yüksek tutarlı fonlar aktarıldığı tespit edildi. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonları 15 ili kapsadı. Fuhuş, müstehcenlik, uyuşturucu ve çocukların korunmasına ilişkin soruşturmalar kapsamında 162 şüpheli, 9 dernek ve 13 işletme hakkında adli işlem başlatıldı. Operasyonlarda çok sayıda uyuşturucu madde ve dijital materyale el konulurken, bazı sosyal medya hesapları ile internet siteleri hakkında da erişim engeli tedbiri uygulandı. İSTANBUL’DA 54 ADRESE OPERASYON İstanbul merkezli çalışmada İstanbul’un yanı sıra Ankara, Çanakkale, İzmir, Antalya, Ordu, Elazığ, Balıkesir, Aydın, Kırşehir, Iğdır ve Hatay’da operasyonlar düzenlendi. 38 şüpheliye yönelik adreslerde arama, yakalama ve el koyma işlemleri gerçekleştirilirken, İstanbul’da 10 işletme ile 6 LGBTİ+ derneğinin de aralarında bulunduğu toplam 54 iş yeri, ev ve dernekte arama yapıldı. İstanbul'daki operasyonlarda 26 şüpheli gözaltına alınırken, diğer şüphelilerin yakalanmasına yönelik çalışmaların sürdüğü belirtildi. MASAK İNCELEMESİNDE YÜKSEK TUTARLI FON AKTARIMI TESPİT EDİLDİ “Ailem Güvende” operasyonları kapsamında yürütülen soruşturmanın mali boyutunda MASAK incelemeleri dikkat çekti. Adalet Bakanı Akın Gürlek, bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığının tespit edildiğini açıkladı. Gürlek, söz konusu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısının araştırıldığını bildirdi. Gürlek'in açıklaması şöyle: "Cumhurbaşkanımız Recep Tayyip Erdoğan’ın ortaya koyduğu 2026-2035 Aile ve Nüfus On Yılı vizyonu ve 2026/4 Sayılı Cumhurbaşkanlığı Genelgesi doğrultusunda; çocuklarımızı, aile kurumunu ve toplum düzenini korumaya yönelik çalışmalarımızı kararlılıkla sürdürüyoruz. İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımızın koordinasyonunda, Emniyet ve Jandarma teşkilatlarımızla birlikte başlatılan "Ailem Güvende" operasyonlarında, 5 il merkezli ve toplam 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletmeye yönelik adli işlemler gerçekleştirilmektedir. Soruşturmalarda; fuhşa aracılık veya yer temin eden kişiler, bu faaliyetlere ortam sağladığı değerlendirilen işletmeler, müstehcen içerik üreten ve yayan şüpheliler ile çocukların bu içeriklere maruz bırakılmasına yönelik faaliyetler incelenmiştir. Gizli soruşturmacı görevlendirilmesi, teknik ve fiziki takip, tanık beyanları, dijital incelemeler ve görüntü kayıtları sonucunda eş zamanlı gözaltı, arama ve el koyma işlemleri yapılmış; uyuşturucu maddeler ile çok sayıda dijital materyale el konulmuş, çok sayıda sosyal medya hesabı ve internet sitesine erişimin engellenmesi tedbiri uygulanmıştır. Soruşturmaların mali boyutunda ise LGBT ve ahlaksızlığı teşvik eden derneklere ilişkin; MASAK incelemelerinde bazı derneklere yurt dışındaki kamu kurumları ve yabancı kuruluşlardan yüksek tutarlarda fon aktarıldığı tespit edilmiştir. Bu para hareketlerinin kaynağı ve soruşturmalara konu faaliyetlerle bağlantısı araştırılmaktadır. Soruşturmaları titizlikle yürüten İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarımıza, operasyonlarda görev alan Emniyet ve Jandarma teşkilatlarımızın kıymetli mensuplarına ve katkı sunan tüm kamu görevlilerimize teşekkür ediyorum. Anayasamızın aile ve çocukların korunmasına ilişkin devlete yüklediği sorumluluk çerçevesinde, çocuklarımızı, gençlerimizi ve ailelerimizi hedef alan hiçbir suç yapılanmasına, istismar ağına ve yasa dışı faaliyete müsamaha göstermeyeceğiz" ERİŞİM ENGELİ GETİRİLDİĞİ BELİRTİLEN 73 SİTE VE HESAP Soruşturma kapsamında erişim engeli getirildiği belirtilen site ve sosyal medya hesapları arasında LGBTİ+ alanında faaliyet gösteren dernek, oluşum ve platformların yanı sıra bazı akademik öğrenci toplulukları, medya platformları ve kişiler de yer aldı. Kaos GL SPoD LGBTİ+ Pembe Hayat LGBTİ+ Dayanışma Derneği ÜniKuir Derneği Lambdaistanbul LGBTİ+ Dayanışma Derneği 17 Mayıs Derneği HEVİ LGBTİ+ Derneği Kırmızı Şemsiye Derneği Genç LGBTİ+ Derneği Özgür Renkler Derneği Muamma LGBTİ+ Derneği Mersin 7 Renk Derneği Queer Adana Antalya BİZ Derneği Keskesor LGBTİ+ Cinsel Şiddetle Mücadele Derneği CETAD Velvele GZone Ayı Sözlük Boysan'ın Evi LGBTI News Turkey İstanbul LGBTİ+ Onur Haftası İstanbul Trans Onur Haftası Ankara Onur Haftası İzmir Onur Haftası ODTÜ LGBTİ+ Dayanışması Boğaziçi Üniversitesi LGBTİ+ Çalışmaları Kulübü Bilkent Renkli Düşün İstanbul Üniversitesi Radar Queer Deer – Hacettepe Üniversitesi Enes Hocaoğulları Yasemin Öz Ali Erol Ali Özbaş Zeynep Esmeray Özadikti Buse Kılıçkaya Şevval Kılıç Levent Pişkin Yıldız Tar İlker Hepkaner Mert Bell Mika Can Raun Seyhan Arman Kuir Tıp Öğrencileri Ağı Renkli Güvercin LGBTIQ GoFor Hormon Hakkım Kolektifi Kuir Baykuş GALA Derneği ÜniKuir2 Kuir Konya Eşitlik İçin Eğitimciler Kapsama Alanı Aşko Anlat Sportif Lezbon Arya'ya Ne Oldu Aforgütü Direnişin Renkleri Pozitif Dayanışma Bodrum Kadın Platformu Barış İçin LGBTİ+ Sivil Alan Araştırmaları Demos Araştırma Eşitlik İçin Kadın Platformu Qlub ÜniKuir Derste Zengiinn All Inclusive Mag LISTAG Boğaziçi LGBTİA İnter Dayanışma LGBT Türkiye 19:19 İstanbul'da yarın ulaşım ücretsiz: Sadece okul saatleri içerisinde 19:15 Trump, İran'la savaşın bitimine dair tarih verdi: Ara seçimler... 18:35 Suudi Arabistan'dan 'güvenlik' mesajı: İzin vermeyeceğiz 18:14 Trabzonspor’da Şenol Güneş sesleri 18:07 Yaz bitti mi, yağışlar başlıyor mu? Meteoroloji'den yeni hafta için 11 illik uyarı 18:04 Formula 1’in ilk Madrid yarışında tarihi zafer 17:54 TOKİ kiralık konut başvurusu ücretli mi? Bekarlar başvuru yapabilecek mi? 17:49 Osimhen için karar verildi: Dönüş tarihi belli oldu 17:38 Katılımevim’de yönetim değişti, Tera ile devir süreci sürüyor 17:38 Ankara’da yarın bazı yollar trafiğe kapatılacak 17:35 Irak, İran sınırındaki 3 sınır kapısını yeniden açıyor 17:34 Ünlülere yönelik uyuşturucu soruşturmasında yeni operasyon: Oyuncu Çağla Boz gözaltına alındı 17:32 Toprak Razgatlıoğlu San Marino’da 12. oldu 17:20 Uzaklaştırma kararı engel olmadı: Uzman çavuş eşini öldürüp intihar etti 17:13 Almanya'da aşırı sağ ve AfD’ye karşı protestolar artıyor MASAK’tan yüksek tutarlı para akışı tespiti: 73 sosyal medya hesabı engellendi, 162 şüpheli gözaltında İstanbul, Ankara, İzmir, Aydın ve Mersin merkezli yürütülen “Ailem Güvende” operasyonlarında fuhuş, müstehcenlik ve uyuşturucu iddialarına ilişkin soruşturmada 15 ili kapsayan çalışmalarda 162 şüpheli, 9 dernek ve 13 işletme hakkında işlem yapıldı. 13/09/2026 10:18 KAYNAK: Anadolu Ajansı (AA) İstanbul, Ankara, İzmir, Aydın ve Mersin Cumhuriyet Başsavcılıklarının koordinasyonunda yürütülen “Ailem Güvende” operasyonları 15 ili kapsadı.</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://www.karar.com/guncel-haberler/ailem-guvende-operasyonunda-yeni-gelisme-15-ilde-9-dernek-ve-13-2071591</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Ankara | Hatay | İstanbul | Mersin</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPUzE0Z0x2amtxSm0wTzh1MHFZQjI4OHZiOElkYl9naFJ3NnJONE9TeU5ldmZhY3NPYzBxaVZRRFR3d1VFcXVWcmNRdVZBN1p1Ul90VGxoMExRTEtzaEtOWUdDU1NXYXgzY1hkeER5Rm5nZEJNQk1EOXUxSmpxSHBoeENBU0tYZGtLbzNpWklEbUFIdVFjVjNTYTNyMEk?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>Levent</t>
-        </is>
-      </c>
+      <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr"/>
@@ -4503,7 +4811,7 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="n">
-        <v>141</v>
+        <v>61.08</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>21</v>
@@ -4512,27 +4820,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:22:00</t>
+          <t>2026-09-14 06:00:38</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -4542,18 +4850,22 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>masak, para transferi</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Gündem 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sevda Ecem Karapolat 13.09.2026 - 15:22 1 İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Soruşturma belgelerine dayandırılan bilgilere göre, 2021-2026 döneminde yabancı ve uluslararası kurumsal kaynaklardan yapılan 209 transferin işlem tarihlerindeki toplam karşılığı yaklaşık 67,4 milyon lira olarak hesaplandı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında, İstanbul merkezli 6 derneğin yurt içi ve yurt dışı bağlantılı para hareketleri incelemeye alındı. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu’nun 226’ncı maddesi kapsamında yürütülen araştırmada, MASAK Veri İnceleme Tutanağı ve bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte değerlendirildi. HANGİ DERNEKLERİN HESAPLARI İNCELENDİ? İnceleme kapsamında şu derneklerin hesap hareketleri ele alındı: Yemen’de çatışmalar şiddetlendi: İran destekli Husiler operasyon görüntülerini paylaştı İçeriği Görüntüle Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği (HEVİ) Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği Pozitif Yaşam Derneği Pozitif İz Derneği Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneği (SPoD) Belgelerde, yabancı kuruluşlardan gelen fonların yanı sıra GİB SWIFT kayıtları, gerçek kişiler tarafından yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketlerinin sıralandığı belirtildi. 45 BİN 135 İŞLEM KAYDI DEĞERLENDİRİLDİ İncelemeye ilişkin aktarılan bilgilere göre, “Bankacılık Transfer” tablosunda toplam 45 bin 135 işlem satırı bulunuyor. Bunların 13 bin 40’ını para girişleri , 32 bin 95’ini ise para çıkışları oluşturuyor. Para girişlerinin 218’inin doğrudan SWIFT alma işlemi olduğu kaydedildi. Gönderen adı, ülke bilgisi, işlemin SWIFT niteliği, banka ve açıklama bilgilerinin birlikte değerlendirilmesiyle yabancı kurumsal kaynaklardan gelen transferler ayrıca sınıflandırıldı. 37 KURUMSAL KAYNAKTAN 209 PARA GİRİŞİ 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan 209 para girişi belirlendiği aktarıldı. Bu işlemlerin gerçekleştirildikleri tarihlerdeki TL karşılıklarının toplamı 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde bu tutarın paranın bugünkü değerini ifade etmediği vurgulandı. Rakamın, farklı tarihlerde yapılan transferlerin MASAK kayıtlarındaki TL karşılıklarının aritmetik toplamından oluştuğu belirtildi. GİB SWIFT kayıtlarına ilişkin değerlendirmede ise derneklere gönderilen paranın dolar karşılığının 3 milyon 359 bin doları aştığı bilgisine yer verildi. YABANCI KURUMSAL GİRİŞLERİN YÜZDE 78’İ İKİ DERNEĞE Aktarılan inceleme bulgularına göre, 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinin yüzde 78’i SPoD ve HEVİ’ye yöneldi. Para hareketlerinde yabancı devlet kurumları, diplomatik misyonlar ve uluslararası kuruluşların yanı sıra gerçek kişilerden yapılan transferlerin de bulunduğu belirtildi. Paylaşılan bilgilerde, bu transferlerin suç oluşturduğuna ilişkin kesinleşmiş bir yargı kararına yer verilmedi. Kaynak: Haber Merkezi Editörün Seçtiği Benzine gece yarısı büyük zam geliyor: Ankara'da 80 liranın üzerine çıkacak! Editörün Seçtiği Kaşif Kozinoğlu'nun mezarı bugün açılacaktı: Feth-i kabir işlemi ertelendi! Editörün Seçtiği Kredi kartı limiti düşürülecek mi? İşte 2026 düzenlemesinin ayrıntıları... Editör Hakkında Sevda Ecem Karapolat Bunlar da ilginizi çekebilir Yemen’de çat</t>
+          <t>TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Anasayfa / Ekonomi / Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye'de İş Dünyası Ekonomi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Güncelleme: 14/09/2026 09:00 Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. 14/09/2026 09:00 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Bilsar Tekstil Muharrem Hilmi Kayhan Söktaş Tekstil İSO’da değişim sesleri yükseliyor Fotoğrafın 200. yılında sanat ile tasarım buluşuyor Mercedes-Benz Türk patent tescilinde tüm sektörlerin lideri oldu Türkiye’nin en büyük elektrikli araç sahipleri buluşması Yenikapı’da gerçekleşecek Ferrari’nin yeni kişiye özel modeli Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı SON DAKİKA HABERLERİ GÜNDEM KORİDORU 9 gün önce Resmi Gazete’de yayımlandı: Diyanet ve Dışişleri’nde kritik atamalar gerçekleşti EKONOMİ 12 gün önce KOSGEB’den KOBİ’lere 27,1 milyar liralık dev can suyu ALMANYA'DA İŞ DÜNYASI 12 gün önce Almanya’da Trilya yağına zararlı mineral yağ engeli: Raflardan toplatılıyor EKONOMİ 12 gün önce Eskişehir’de stratejik adım: Nadir elementler için dev kamulaştırma SPOR 12 gün önce Beşiktaş’ta beklenen ayrılık EKONOMİ 12 gün önce AFSİAD Başkanı Sayın’dan bankalara faiz ve teminat çağrısı EMLAK 12 gün önce Eylül ayı kira artış oranı için gözler TÜİK’te KATEGORİNİN POPÜLERLERİ 1 Gram altın tahminleri 2025 2 2026 gram altın fiyatı tahmini! Altın ne kadar olur? 3 Motosiklet fiyatlarına ek gümrük vergisi geldi! Scooterlara ne kadar zam geldi? 4 2025 çiğ süt satış fiyatı belli oldu 5 Kilis’in ihracatı ilk yarıda yüzde 13 artarak 69,2 milyon dolara ulaştı Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı Çerkezköy’de e-ticaret lojistiğine yeni merkez Yapay zekâ e-ihracatta KOBİ’lerin önünü açıyor Güneydoğu’nun ihracatı 8 ayda 8,2 milyar dolara ulaştı Otomotivde üretim frene bastı: 8 ayda 841 bin araç üretildi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı Çerkezköy’de e-ticaret lojistiğine yeni merkez Yapay zekâ e-ihracatta KOBİ’lerin önünü açıyor Güneydoğu’nun ihracatı 8 ayda 8,2 milyar dolara ulaştı Otomotivde üretim frene bastı: 8 ayda 841 bin araç üretildi</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Gündem 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sevda Ecem Karapolat 13.09.2026 - 15:22 1 İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Soruşturma belgelerine dayandırılan bilgilere göre, 2021-2026 döneminde yabancı ve uluslararası kurumsal kaynaklardan yapılan 209 transferin işlem tarihlerindeki toplam karşılığı yaklaşık 67,4 milyon lira olarak hesaplandı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında, İstanbul merkezli 6 derneğin yurt içi ve yurt dışı bağlantılı para hareketleri incelemeye alındı. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu’nun 226’ncı maddesi kapsamında yürütülen araştırmada, MASAK Veri İnceleme Tutanağı ve bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte değerlendirildi. HANGİ DERNEKLERİN HESAPLARI İNCELENDİ? İnceleme kapsamında şu derneklerin hesap hareketleri ele alındı: Yemen’de çatışmalar şiddetlendi: İran destekli Husiler operasyon görüntülerini paylaştı İçeriği Görüntüle Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği (HEVİ) Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği Pozitif Yaşam Derneği Pozitif İz Derneği Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneği (SPoD) Belgelerde, yabancı kuruluşlardan gelen fonların yanı sıra GİB SWIFT kayıtları, gerçek kişiler tarafından yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketlerinin sıralandığı belirtildi. 45 BİN 135 İŞLEM KAYDI DEĞERLENDİRİLDİ İncelemeye ilişkin aktarılan bilgilere göre, “Bankacılık Transfer” tablosunda toplam 45 bin 135 işlem satırı bulunuyor. Bunların 13 bin 40’ını para girişleri , 32 bin 95’ini ise para çıkışları oluşturuyor. Para girişlerinin 218’inin doğrudan SWIFT alma işlemi olduğu kaydedildi. 37 KURUMSAL KAYNAKTAN 209 PARA GİRİŞİ 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan 209 para girişi belirlendiği aktarıldı. Rakamın, farklı tarihlerde yapılan transferlerin MASAK kayıtlarındaki TL karşılıklarının aritmetik toplamından oluştuğu belirtildi. GİB SWIFT kayıtlarına ilişkin değerlendirmede ise derneklere gönderilen paranın dolar karşılığının 3 milyon 359 bin doları aştığı bilgisine yer verildi. YABANCI KURUMSAL GİRİŞLERİN YÜZDE 78’İ İKİ DERNEĞE Aktarılan inceleme bulgularına göre, 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinin yüzde 78’i SPoD ve HEVİ’ye yöneldi. Para hareketlerinde yabancı devlet kurumları, diplomatik misyonlar ve uluslararası kuruluşların yanı sıra gerçek kişilerden yapılan transferlerin de bulunduğu belirtildi. Editörün Seçtiği Kaşif Kozinoğlu'nun mezarı bugün açılacaktı: Feth-i kabir işlemi ertelendi!</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Anasayfa / Ekonomi / Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye'de İş Dünyası Ekonomi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Güncelleme: 14/09/2026 09:00 Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. 14/09/2026 09:00 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Bilsar Tekstil Muharrem Hilmi Kayhan Söktaş Tekstil İSO’da değişim sesleri yükseliyor Fotoğrafın 200. yılında sanat ile tasarım buluşuyor Mercedes-Benz Türk patent tescilinde tüm sektörlerin lideri oldu Türkiye’nin en büyük elektrikli araç sahipleri buluşması Yenikapı’da gerçekleşecek Ferrari’nin yeni kişiye özel modeli Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı SON DAKİKA HABERLERİ GÜNDEM KORİDORU 9 gün önce Resmi Gazete’de yayımlandı: Diyanet ve Dışişleri’nde kritik atamalar gerçekleşti EKONOMİ 12 gün önce KOSGEB’den KOBİ’lere 27,1 milyar liralık dev can suyu ALMANYA'DA İŞ DÜNYASI 12 gün önce Almanya’da Trilya yağına zararlı mineral yağ engeli: Raflardan toplatılıyor EKONOMİ 12 gün önce Eskişehir’de stratejik adım: Nadir elementler için dev kamulaştırma SPOR 12 gün önce Beşiktaş’ta beklenen ayrılık EKONOMİ 12 gün önce AFSİAD Başkanı Sayın’dan bankalara faiz ve teminat çağrısı EMLAK 12 gün önce Eylül ayı kira artış oranı için gözler TÜİK’te KATEGORİNİN POPÜLERLERİ 1 Gram altın tahminleri 2025 2 2026 gram altın fiyatı tahmini! 4 2025 çiğ süt satış fiyatı belli oldu 5 Kilis’in ihracatı ilk yarıda yüzde 13 artarak 69,2 milyon dolara ulaştı Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı Çerkezköy’de e-ticaret lojistiğine yeni merkez Yapay zekâ e-ihracatta KOBİ’lerin önünü açıyor Güneydoğu’nun ihracatı 8 ayda 8,2 milyar dolara ulaştı Otomotivde üretim frene bastı: 8 ayda 841 bin araç üretildi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı Çerkezköy’de e-ticaret lojistiğine yeni merkez Yapay zekâ e-ihracatta KOBİ’lerin önünü açıyor Güneydoğu’nun ihracatı 8 ayda 8,2 milyar dolara ulaştı Otomotivde üretim frene bastı: 8 ayda 841 bin araç üretildi</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -4563,15 +4875,19 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://www.ankaranethaber.com/6-lgbt-dernegine-yurt-disindan-para-transferi-masak-incelemesinde-209-islem-belirlendi</t>
+          <t>https://turkiyedeisdunyasi.com/gomlek-devinin-konkordato-ilan-etti-tusiad-eski-baskaninin-sirketinde-kredi-notu-dustu-132732/</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>Çorum | Eskişehir | Kilis | Aydın | İstanbul</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Söke | Beşiktaş | Çerkezköy</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
@@ -4579,7 +4895,7 @@
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr"/>
@@ -4593,7 +4909,7 @@
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="n">
-        <v>111</v>
+        <v>116.5</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>22</v>
@@ -4602,27 +4918,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:19:26</t>
+          <t>2026-09-14 09:46:30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi!</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -4632,44 +4948,32 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>gıda</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Ad Haberler - Gündem Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi.</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi Ad Haberler - Gündem Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor.</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.sozcu.com.tr/amp/bolu-daki-depo-yangininda-son-durum-hasarin-boyutu-havadan-goruntulendi-p357811</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+          <t>https://www.nefes.com.tr/turkiyenin-unlu-gida-markasi-iflastan-kurtuldu-alacaklilar-siraya-girdi-151173</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -4677,7 +4981,7 @@
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr"/>
@@ -4691,7 +4995,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="n">
-        <v>117.5</v>
+        <v>75.38</v>
       </c>
       <c r="AB24" s="2" t="n">
         <v>23</v>
@@ -4700,27 +5004,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 01:34:53</t>
+          <t>2026-09-14 06:22:37</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi Finans Gündem</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -4730,44 +5034,36 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>depo, fabrika</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>fabrika | depo</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda çıkan yangın kontrol altına alındı. Soğutma çalışmaları sürerken Valilik, olayda hafif yaralanan 2 kişinin tedavi edildiğini ve incelemelerin devam ettiğini açıkladı Bolu Gerede'deki geri dönüşüm deposunda çıkan yangın kontrol altına alındı. Soğutma çalışmaları...</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi Bolu Gerede'de fabrika deposundaki yangın kontrol altına alındı: 2 yaralı haberi Finans Gündem Bolu Gerede'deki geri dönüşüm deposunda çıkan yangın kontrol altına alındı. Soğutma çalışmaları sürerken Valilik, olayda hafif yaralanan 2 kişinin tedavi edildiğini ve incelemelerin devam ettiğini açıkladı Bolu Gerede'deki geri dönüşüm deposunda çıkan yangın kontrol altına alındı.</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi 58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber 58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://www.finansingundemi.com/haber/bolu-geredede-fabrika-deposundaki-yangin-kontrol-altina-alindi-2-yarali/1908123</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPanVHckV1ZE9YcmI0UGNQTXpvcWtOU01wSnhYaTA3c0d4eWwxOFlmWGZXUGxmODlIdzd6dmN4dWJPeXhMM0RjeXFRMGZDWDVYUFJydUhVTGwyeURrQlpZM1FHZEk1Q2pUYzFDdWt4NTBVcFNHdlh2RW1VMEloU0c4b055STAwYm9OS1U2QXdLQWRDd0IxZ2R2X19mRUc2TGpzYTAtejFNdllyOTlUUk8tLUwwcDFNZw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
       <c r="Q25" s="2" t="inlineStr"/>
@@ -4775,7 +5071,7 @@
       <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr"/>
@@ -4789,7 +5085,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="n">
-        <v>100.54</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>24</v>
@@ -4798,27 +5094,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 18:20:15</t>
+          <t>2026-09-13 15:39:00</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da depo yangını / Ek fotoğraflar</t>
+          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da depo yangını / Ek fotoğraflar Antalya İleri</t>
+          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı İstiklal Gazetesi</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -4828,37 +5124,37 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>firma</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da depo yangını / Ek fotoğraflar Antalya İleri</t>
+          <t>Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Anasayfa Ekonomi Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Yayınlanma: 13 Eylül 2026 Pazar 18:39 Havva İNCECİK Editör Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Türkiye tekstil sektörünün köklü kuruluşlarından Orta Anadolu Ticaret ve Sanayi İşletmesi T.A.Ş., 73 yıllık üretim faaliyetini sonlandırma kararı aldı. Şirketin Kayseri’deki üretim faaliyetleri 11 Eylül 2026 itibarıyla durdurulurken bütün üretim tesislerinin 12 Ekim 2026 tarihinde tamamen kapatılacağı açıklandı. Dünyaca ünlü markalara üretim yapıyordu 1953 yılında kurulan Orta Anadolu, 1986’dan bu yana dünyanın önde gelen moda markalarına premium denim kumaş tedarik ediyordu. Şirketin Levi’s, Mavi, Lee, Wrangler, Diesel, Replay ve Guess’in de aralarında bulunduğu 300’ün üzerinde markaya denim kumaş sağladığı belirtiliyor. Kapanma kararının gerekçeleri açıklandı Şirket yönetimi, küresel tekstil sektöründe yaşanan talep daralması, artan operasyon ve finansman maliyetleri, tedarik zincirindeki dalgalanmalar ile değişen ticaret koşullarının mevcut işletme modelini sürdürülemez hale getirdiğini bildirdi. Maliyetlerin azaltılması, verimliliğin artırılması ve şirketin yeniden yapılandırılması için kapsamlı çalışmalar yürütüldüğü ancak mevcut ekonomik koşullarda üretimin devam ettirilemediği belirtildi. Kararın geçici olmadığı belirtildi Şirketin yönetim kurulu tarafından alınan karar kapsamında Kayseri’deki üretimin kalıcı olarak sonlandırıldığı ifade edildi. Tesislerin kapatılmasına yönelik işlemler için 12 Ekim’e kadar sürecek bir takvim belirlendi. Şirket yönetimi, kapanış sürecinde çalışanlara, müşterilere, finans kuruluşlarına ve tedarikçilere yönelik ticari yükümlülüklerin şeffaflık ve sorumluluk anlayışıyla yerine getirileceğini açıkladı. Kaynak: Haber Merkezi HABERE YORUM KAT UYARI: Küfür, hakaret, rencide edici cümleler veya imalar, inançlara saldırı içeren, imla kuralları ile yazılmamış, Türkçe karakter kullanılmayan ve büyük harflerle yazılmış yor</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Antalya'da depo yangını / Ek fotoğraflar Antalya'da depo yangını / Ek fotoğraflar Antalya İleri Antalya'da depo yangını / Ek fotoğraflar Antalya İleri</t>
+          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı İstiklal Gazetesi Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Anasayfa Ekonomi Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Yayınlanma: 13 Eylül 2026 Pazar 18:39 Havva İNCECİK Editör Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Türkiye tekstil sektörünün köklü kuruluşlarından Orta Anadolu Ticaret ve Sanayi İşletmesi T.A.Ş., 73 yıllık üretim faaliyetini sonlandırma kararı aldı. Şirketin Kayseri’deki üretim faaliyetleri 11 Eylül 2026 itibarıyla durdurulurken bütün üretim tesislerinin 12 Ekim 2026 tarihinde tamamen kapatılacağı açıklandı. Dünyaca ünlü markalara üretim yapıyordu 1953 yılında kurulan Orta Anadolu, 1986’dan bu yana dünyanın önde gelen moda markalarına premium denim kumaş tedarik ediyordu. Şirketin Levi’s, Mavi, Lee, Wrangler, Diesel, Replay ve Guess’in de aralarında bulunduğu 300’ün üzerinde markaya denim kumaş sağladığı belirtiliyor. Kapanma kararının gerekçeleri açıklandı Şirket yönetimi, küresel tekstil sektöründe yaşanan talep daralması, artan operasyon ve finansman maliyetleri, tedarik zincirindeki dalgalanmalar ile değişen ticaret koşullarının mevcut işletme modelini sürdürülemez hale getirdiğini bildirdi. Maliyetlerin azaltılması, verimliliğin artırılması ve şirketin yeniden yapılandırılması için kapsamlı çalışmalar yürütüldüğü ancak mevcut ekonomik koşullarda üretimin devam ettirilemediği belirtildi. Kararın geçici olmadığı belirtildi Şirketin yönetim kurulu tarafından alınan karar kapsamında Kayseri’deki üretimin kalıcı olarak sonlandırıldığı ifade edildi. Tesislerin kapatılmasına yönelik işlemler için 12 Ekim’e kadar sürecek bir takvim belirlendi. Şirket yönetimi, kapanış sürecinde çalışanlara, müşterilere, finans kuruluşlarına ve tedarikçilere yönelik ticari yükümlülüklerin şeffaflık ve sorumluluk anlayışıyla yerine getirileceğini açıkladı.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE90d2U5TV9WcVhEeWsyNVEwRDI0QWZQaUg4ZXZNWnNmbzhCVUlpZ1R5X2VURWZvWjA3aWlYd0hid185U0wwSVZBby1GbW1RX2JWOHdkcHViQ0tFdXdYS3V4MGhJOWc5UmRza1AyaVJuYUx3QUxxdVZEOGh5eExiUQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.istiklal.com.tr/ekonomi/pes-pese-yasanan-iflas-ve-konkordato-dalgasina-dev-firma-da-katildi-1105108h</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Antalya</t>
+          <t>Kayseri</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
@@ -4883,7 +5179,7 @@
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="n">
-        <v>52.04</v>
+        <v>95.75</v>
       </c>
       <c r="AB26" s="2" t="n">
         <v>25</v>
@@ -4892,27 +5188,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:20:22</t>
+          <t>2026-09-14 07:27:00</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı!</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor sondakika.com</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4922,22 +5218,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Güncelleme: 13.09.2026 13:20 Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Kaynak: AA Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi.</t>
+          <t>Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. 14.09.2026 - 10:27 Yayınlanma — Paylaşım 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Kahramanmaraş Asliye Ticaret Mahkemesi’nin 2 Eylül 2026 tarihli kararı doğrultusunda, Germenicia Boya Tekstil Petrol İnşaat Sanayi ve Ticaret Limited Şirketi hakkında iflas kararı verildi. Mahkemenin 2025/22 Esas sayılı dosyasında verilen karara göre şirketin iflasına 2 Eylül 2026 saat 10.25 itibarıyla hükmedildi. Kararın ardından şirketin tasfiye işlemlerine başlandığı bildirildi. İflas kararının, İcra ve İflas Kanunu’nun 166. maddesi kapsamında ilan yoluyla tebliğ edildiği belirtildi. Germenicia Tekstil hakkında da iflas kararı Aynı mahkeme kararı kapsamında Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi hakkında da iflas işlemi başlatıldı. Bu şirketin de 2 Eylül 2026 tarihinde saat 10.25 itibarıyla iflasına karar verildiği duyuruldu. Mahkeme kararının ardından şirketin tasfiye sürecinin başlatıldığı ve kararın ilgili mevzuat gereğince ilan edildiği bildirildi. Konkordato sürecinde 2 aylık uzatma Kahramanmaraş Asliye Ticaret Mahkemesi’nde görülen bir başka konkordato dosyasında ise A.T., G.T., N.T. ile Maktes Isıtma ve Soğutma Sistemleri Taahhüt Makina Tesisat İnşaat Plan Proje Sanayi ve Ticaret Limited Şirketi hakkında yeni karar alındı. Benzin 80 TL’yi aştı! Gözler motorin zammında: 100 TL sınırına dayanacak İçeriği Görüntüle Mahkemenin 9 Eylül 2026 tarihli ara kararı doğrultusunda, 1 Ekim 2026 tarihinden itibaren geçerli olmak üzere kesin mühletin 2 ay süreyle uzatılmasına hükmedildi. Daha önce uygulanan kesin mühlete ilişkin tedbirlerin de devam etmesine karar verildi. Karar kapsamında, mahkemenin izni olmaksızın rehin, kefalet, devir, takyit ve ivazsız tasarruf işlemlerinin önlenmesine yönelik tedbirlerin sürdürüleceği bildirildi. Ayrıca her türlü ihtiyati tedbir ve ihtiyati haciz işlemleri ile muhafaza işlemleri dahil takip işlemlerinin de ihtiyati tedbir yoluyla durdurulmasına karar verildi. Alacaklılara 7 günlük itiraz süresi Mahkeme, konkordato sürecine ilişkin olarak alacaklılara da çağrıda bulundu. Buna göre alacaklıların, ilanın yayımlanmasından itibaren 7 gün içinde mahkeme dosyasına itiraz edebileceği bildirildi. Alacaklıların, konkordato mühleti verilmesini gerektiren bir durum bulunmadığını delilleriyle birlikte ortaya koyarak konkordato talebinin reddedilmesini isteme hakkı bulunduğu belirtildi. Editör Hakkında Editör 02 Bunlar da</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor sondakika.com Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Güncelleme: 13.09.2026 13:20 Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Kaynak: AA Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı.</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! 14.09.2026 - 10:27 Yayınlanma — Payl</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -4947,41 +5243,61 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.sondakika.com/amp/haber-bolu-gerede-deki-geri-donusum-deposunda-yangin-son-20233164/</t>
+          <t>https://www.edetv.com.tr/kahramanmarasta-iki-sirket-icin-iflas-karari-biri-icin-konkordatoda-muhlet-uzatildi</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+          <t>Kahramanmaraş</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi:raw_legal</t>
+        </is>
+      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr"/>
-      <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi Kahramanmaraş Türkiye</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="n">
-        <v>122.5</v>
+        <v>173.25</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>26</v>
@@ -4990,27 +5306,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:47:00</t>
+          <t>2026-09-13 20:52:25</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Depo’da korkutan yangın, mahalleli seferber oldu</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Depo’da korkutan yangın, mahalleli seferber oldu BursaVar</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -5020,22 +5336,18 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>turizm</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Depo’da korkutan yangın, mahalleli seferber oldu BursaVar</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Depo’da korkutan yangın, mahalleli seferber oldu Depo’da korkutan yangın, mahalleli seferber oldu BursaVar Depo’da korkutan yangın, mahalleli seferber oldu BursaVar</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -5045,7 +5357,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOYnkydTM5a0phbkY3cjNoSFV5MnBubnBoMXNTRHFla2ZaRGpOeU12OGx5RnZlT0d4c09sSVFFcTFTSEVXVVBJQUhXWkxjOWFGVVlyNGxMN20wTG5OSmlFX1p1enY3cjNmV0dWc1pfTkUxaklLNHNjaFJTYkw0Ym1NWXNNVHpLQ0RVNHpMS2Z4SdIBlAFBVV95cUxPTFJZc2NOUm9ReWY3eGEzeWhwOXJGbXZ4R25DOEdpd1RtNzdDYWY2TGFlYXpFbnRVZExMSlVzT3pacTVST2JucVJsb0YxM2h1allEcWg2Wk4xeDJacktzVjRndHkzQkFkUTRYMkIwMEdoU3dJdGlRYnBRYkpWNGZRWVJMS2NuWFczaTAwNHVjMG1hVS11?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOYnVoWnhPQXR6MDdHdkRVTWhLZDF5YTRTSmNJSmtpbVJacEVmRUEtelBJSmtwN2ZWeTFBbG9acUFROXRQVWZ3WVN2SEN1UGQtX0QwT3pKUldzQlJOZGZxcnptSU5taUpMQjR4dmVRZHVlN0w3Wm5GM2kwQUpKVnZIQWpPVXVSUzAteHdXWndFNUFEbnFtS3k4bU5xNU9pS0V5QUw0NldB?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr"/>
@@ -5071,7 +5383,7 @@
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="n">
-        <v>46.82</v>
+        <v>68.42</v>
       </c>
       <c r="AB28" s="2" t="n">
         <v>27</v>
@@ -5080,27 +5392,27 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 17:42:00</t>
+          <t>2026-09-13 14:39:00</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne?</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı!</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? politikam.com</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -5110,22 +5422,18 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>turizm</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Olay yerinden ilk detaylar haberimizde. Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Olay yerinden ilk detaylar haberimizde. Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Olay yerinden ilk detaylar haberimizde. Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Olay yerinden ilk detaylar haberimizde. Kevser Yoldaş Editör 12.09.2026 - 20:42 Yayınlanma — Paylaşım 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Antalya’nın Muratpaşa ilçesinde akşam saatlerinde hareketli dakikalar yaşandı. Yenigöl Mahallesi Lavanta Sokak üzerinde bulunan bir ambalaj deposunda henüz belirlenemeyen bir nedenle yangın çıktı. Depoda bulunan plastik ve ambalaj malzemelerinin tutuşmasıyla alevler kısa sürede büyüyerek kontrolden çıktı. Rüzgarın ve yanıcı maddelerin etkisiyle şiddetini artıran alevler, deponun hemen bitişiğinde yer alan müstakil bir eve sıçradı. İtfaiye, Polis ve Sağlık Ekipleri Alarmda Sokaktan yükselen dumanları ve alevleri gören mahalle sakinlerinin ihbarı üzerine bölgeye çok sayıda itfaiye, polis ve 112 Acil Sağlık ekibi sevk edildi. Olay yerine kısa sürede ulaşan emniyet güçleri çevrede güvenlik önlemleri alarak sokağı trafiğe ve yaya geçişine kapatırken, sağlık ekipleri de olası yaralanma ve dumandan etkilenme ihtimallerine karşı hazır bekletilmeye başlandı. Söndürme Çalışmaları Devam Ediyor İtfaiye ekipleri, hem ambalaj deposunu saran alevleri kontrol altına almak hem de eve sıçrayan yangının diğer yapılara yayılmasını önlemek için yoğun bir çalışma yürütüyor. Yangının çıkış nedeninin belirlenmesi amacıyla söndürme işlemlerinin tamamlanmasının ardından inceleme başlatılacak. Kaynak: Anadolu Ajansı Editör Kevser Yoldaş Bu</t>
+          <t>Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. VİB Turizm'den dolandırıcılık uyarısı! Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Haber Merkezi Editör 13.09.2026 - 17:39 Yayınlanma — P</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Son Durum Ne? politikam.com Antalya Muratpaşa'da ambalaj deposunda çıkan ve eve sıçrayan yangına itfaiye ekipleri müdahale ediyor. Antalya Muratpaşa'da Yangın Paniği: Ambalaj Deposu Ve Yanındaki Ev Alevlere Teslim Oldu! Kevser Yoldaş Editör 12.09.2026 - 20:42 Yayınlanma —</t>
+          <t>VİB Turizm'den dolandırıcılık uyarısı! VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. VİB Turizm'den dolandırıcılık uyarısı!</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -5135,61 +5443,33 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.politikam.com/antalya-muratpasada-yangin-panigi-ambalaj-deposu-ve-yanindaki-ev-alevlere-teslim-oldu-son-durum-ne</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>Antalya</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Muratpaşa</t>
-        </is>
-      </c>
+          <t>https://www.bizimsakarya.com.tr/vib-turizmden-dolandiricilik-uyarisi</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>Ambalaj Deposu</t>
-        </is>
-      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>Ambalaj Deposu Muratpaşa Antalya Türkiye</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Ambalaj Ticaret | Balcı Ambalaj | Doğuş Ambalaj | Gürbüz Ambalaj toptan parekende | Antalya Ambalaj</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>Ambalaj Ticaret</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr">
-        <is>
-          <t>66.66666666666666 | 70.0 | 81.48148148148148 | 66.66666666666666 | 66.66666666666666</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
       <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="n">
-        <v>205</v>
+        <v>54.14</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>28</v>
@@ -5198,12 +5478,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:00:14</t>
+          <t>2026-09-14 08:14:01</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>borç krizi</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -5213,12 +5493,12 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti</t>
+          <t>AirBaltic'te finansal kriz: ABD'de iflas koruması başvurusunda bulundu</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti Samanyolu Haber</t>
+          <t>AirBaltic'te finansal kriz: ABD'de iflas koruması başvurusunda bulundu İstanbul Ticaret Gazetesi</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -5228,22 +5508,18 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>inşaat, şirket</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>ticaret</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler İzmir’de 35 yıldır faaliyet gösteren İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında iflas kararı verildi. Şirketin iflasına, İzmir 3. Asliye Ticaret Mahkemesi tarafından hükmedildi. Mahkemenin 23 Ocak 2026 tarihli kararıyla iflasına karar verilen şirketin alacaklılarına ilişkin ek sıra cetveli de hazırlandı. Ege’de Son Söz’de yer alan habere göre, İzmir İflas Dairesi tarafından yayımlanan ilana göre, iflas masasına alacak kaydı yaptıranların kayıt, kabul, ret ve sıralarını gösteren 8 Eylül 2026 tarihli ek sıra cetveli, aynı gün İzmir İflas Müdürlüğü divanhanesine asıldı. İlanda, sıra cetvelinde yer alan alacakların esasına ilişkin itirazların en geç 15 gün içerisinde İzmir Asliye Ticaret Mahkemelerinde yapılabileceği belirtildi. Alacakların sırasına ilişkin itirazların ise en geç 7 gün içerisinde İzmir İcra Hukuk Mahkemelerinde dava açılarak yapılabileceği bildirildi. İzmir İflas Dairesi, söz konusu sürelere ilişkin duyuruyu İcra ve İflas Kanunu’nun ilgili maddeleri kapsamında tebliğ ve ilan etti. İFLAS DUYURUSU Duyuru şu şekilde: “İzmi</t>
+          <t>Borç yükünü yönetmekte zorlanan Letonya'nın ulusal hava yolu şirketi AirBaltic, mali yapılandırma kapsamında ABD'de iflas koruması başvurusunda bulunurken, 350 milyon avroluk finansmanla operasyonların süreceğini açıkladı. Borç yükünü yönetmekte zorlanan Letonya'nın ulusal hava yolu şirketi AirBaltic, mali yapılandırma kapsamında ABD'de iflas koruması başvurusunda… Borç yükünü yönetmekte zorlanan Letonya'nın ulusal hava yolu şirketi AirBaltic, mali yapılandırma kapsamında ABD'de iflas koruması başvurusunda bulunurken, 350 milyon avroluk finansmanla operasyonların süreceğini açıkladı.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti Alacaklılar kapıya dayandı: 35 yıllık Türk inşaat şirketi iflas etti Samanyolu Haber Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler Samanyolu Haber: Son Dakika ve En Son Haberler İzmir’de 35 yıldır faaliyet gösteren İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş. hakkında iflas kararı verildi. Şirketin iflasına, İzmir 3. Asliye Ticaret Mahkemesi tarafından hükmedildi. Mahkemenin 23 Ocak 2026 tarihli kararıyla iflasına karar verilen şirketin alacaklılarına ilişkin ek sıra cetveli de hazırlandı. Ege’de Son Söz’de yer alan habere göre, İzmir İflas Dairesi tarafından yayımlanan ilana göre, iflas masasına alacak kaydı yaptıranların kayıt, kabul, ret ve sıralarını gösteren 8 Eylül 2026 tarihli ek sıra cetveli, aynı gün İzmir İflas Müdürlüğü divanhanesine asıldı. İlanda, sıra cetvelinde yer alan alacakların esasına ilişkin itirazların en geç 15 gün içerisinde İzmir Asliye Ticaret Mahkemelerinde yapılabileceği belirtildi. Alacakların sırasına ilişkin itirazların ise en geç 7 gün içerisinde İzmir İcra Hukuk Mahkemelerinde dava açılarak yapılabileceği bildirildi. İzmir İflas Dairesi, söz konusu sürelere ilişkin duyuruyu İcra ve İflas Kanunu’nun ilgili maddeleri kapsamında tebliğ ve ilan etti.</t>
+          <t>AirBaltic'te finansal kriz: ABD'de iflas koruması başvurusunda bulundu AirBaltic'te finansal kriz: ABD'de iflas koruması başvurusunda bulundu İstanbul Ticaret Gazetesi Borç yükünü yönetmekte zorlanan Letonya'nın ulusal hava yolu şirketi AirBaltic, mali yapılandırma kapsamında ABD'de iflas koruması başvurusunda bulunurken, 350 milyon avroluk finansmanla operasyonların süreceğini açıkladı. Borç yükünü yönetmekte zorlanan Letonya'nın ulusal hava yolu şirketi AirBaltic, mali yapılandırma kapsamında ABD'de iflas koruması başvurusunda… Borç yükünü yönetmekte zorlanan Letonya'nın ulusal hava yolu şirketi AirBaltic, mali yapılandırma kapsamında ABD'de iflas koruması başvurusunda bulunurken, 350 milyon avroluk finansmanla operasyonların süreceğini açıkladı.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -5253,46 +5529,42 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://www.samanyoluhaber.com/alacaklilar-kapiya-dayandi-35-yillik-turk-insaat-sirketi-iflas-etti-haberi/1492579</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+          <t>https://istanbulticaretgazetesi.com/airbalticte-finansal-kriz-abdde-iflas-korumasi-basvurusunda-bulundu</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş</t>
+          <t>İstanbul Ticaret</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş:57:body | İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş:raw_legal</t>
+          <t>İstanbul Ticaret:166:body+summary</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>İzmer İnşaat Sanayi Ticaret ve Turizm A.Ş İzmir Türkiye</t>
+          <t>İstanbul Ticaret Türkiye</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>İzmer</t>
+          <t>İstanbul Ticaret Üniversitesi | İstanbul Ticaret Merkezi | İstanbul Ticaret İş Güvenliği ve Endüstriyel Ürünler San. A.Ş | İstanbul Ticaret Üniversitesi Küçükyalı Kampüsü | İstanbul Ticaret Borsası</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>İzmer</t>
+          <t>İstanbul Ticaret Üniversitesi</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
@@ -5302,16 +5574,12 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="Z30" s="2" t="inlineStr">
-        <is>
-          <t>İzmer Ege Yapı Kimyasalları | İz-Mer Mermer Granit</t>
-        </is>
-      </c>
+          <t>100.0 | 100.0 | 100.0 | 100.0 | 100.0</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr"/>
       <c r="AA30" s="2" t="n">
-        <v>180.38</v>
+        <v>186.9</v>
       </c>
       <c r="AB30" s="2" t="n">
         <v>29</v>
@@ -5320,7 +5588,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 06:18:00</t>
+          <t>2026-09-14 09:58:46</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -5335,12 +5603,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!”</t>
+          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara</t>
+          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti Sözcü Gazetesi</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -5350,35 +5618,35 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>firma</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>tekstil</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara</t>
+          <t>Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. Google algoritmasına bırakmayın, okuyacağınız haberi siz seçin! Tıkla ve ekle Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. 2019’da faaliyetlerine başlayan şirket, tekstil üretiminin yanı sıra otelcilik sektöründe de faaliyet gösteriyordu. Kahramanmaraş İcra Dairesi, şirket hakkında verilen iflas kararının ardından iflasın açılmasına ilişkin işlemleri uygulamaya aldı. ŞİRKETİN ÜRETİM KAPASİTESİ NE KADARDI? Günün Trend Haberleri Germenicia Boya Tekstil’in boyahane bölümünde yıllık 5 milyon 400 bin kilogram üretim kapasitesi bulunuyordu. Örgü bölümünün yıllık üretim kapasitesi ise 5 milyon kilogram seviyesindeydi. Yaklaşık 200 kişinin çalıştığı şirket, tekstil sektöründeki faaliyetlerini Kahramanmaraş merkezli olarak sürdürüyordu. OTELCİLİK SEKTÖRÜNDE DE FAALİYET GÖSTERİYORDU Şirketin tekstilin yanı sıra turizm sektöründe de yatırımı bulunuyordu. İstanbul’da Germenicia Hotel adıyla faaliyet gösteren bir işletmesi vardı. Şirketin finansal darboğazın ardından konkordato sürecinden başarıyla çıkamaması üzerine iflas kararı verildi. Şirketin vergi levhasındaki bilgilere göre 2024 ve 2025 yıllarında vergi matrahı oluşmadı. 2023 yılında ise 2 milyon 362 bin 651 TL matrah ve 590 bin 662 TL vergi tahakkuku kaydedilmişti. Kahramanmaraş İcra Dairesi, verilen iflas kararının ardından şirket hakkında ilgili iflas işlemlerini başlattı. www.sozcu.com.tr internet sitesinde yayınlanan yazı, haber ve fotoğrafların her türlü telif hakkı Mega Ajans ve Rek. Tic. A.Ş'ye aittir. İzin alınmadan, kaynak gösterilerek dahi iktibas edilemez. Bu habere emoji ile tepki ver 2019’da faaliyetlerine başlayan şirket, tekstil üretiminin yanı sıra otelcilik sektöründe de faaliyet gösteriyordu. Kahramanmaraş İcra Dairesi, şirket hakkında verilen iflas kararının ardından iflasın açılmasına ilişkin işlemleri uygulamaya aldı. ŞİRKETİN ÜRETİM KAPASİTESİ NE KADARDI? Günün Trend Haberleri Germenicia Boya Tekstil’in boyahane bölümünde yıllık 5 milyon 400 bin kilogram üretim kapasitesi bulunuyordu. Örgü bölümünün yıllık üretim kapasitesi ise 5 milyon kilogram seviyesindeydi. Yaklaşık 200 kişinin çalıştığı şirket, tekstil sektöründeki faaliyetlerini Kahramanmaraş merkezli olarak sürdürüyordu. OTELCİLİK SEKTÖRÜNDE DE FAALİYET GÖSTERİYORDU Şirketin tekstilin yanı sıra turizm sektöründe de yatırımı bulunuyordu. İstanbul’da Germenicia Hotel adıyla faaliyet gösteren bir işletmesi vardı. Şirketin finansal darboğazın ardından konkordato sürecinden başarıyla çıkamaması üzerine iflas kararı verildi. Şirketin vergi levhasındaki bilgilere göre 2024 ve 2025 yıllarında vergi matrahı oluşmadı. 2023 yılında ise 2 milyon 362 bin 651 TL matrah ve 590 bin 662 TL vergi tahakkuku kaydedilmişti. Kahramanmaraş İcra Dairesi, verilen iflas kararının ardından şirket hakkında ilgili iflas işlemlerini başlattı. DOLAR 48,62 0,10 (%0,20) EURO 56,15 -0,17 (%-0,31) Haber Merkezi Facebook ile paylaş Messenger ile gönd</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara Ekonomist Şirin’den faiz değerlendirmesi: “Birçok firmada iflas var!” Yeni Ankara</t>
+          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti Yüzlerce çalışanı olan Türk tekstil devi iflas etti Sözcü Gazetesi Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. Google algoritmasına bırakmayın, okuyacağınız haberi siz seçin! Tıkla ve ekle Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. 2019’da faaliyetlerine başlayan şirket, tekstil üretiminin yanı sıra otelcilik sektöründe de faaliyet gösteriyordu. Kahramanmaraş İcra Dairesi, şirket hakkında verilen iflas kararının ardından iflasın açılmasına ilişkin işlemleri uygulamaya aldı. ŞİRKETİN ÜRETİM KAPASİTESİ NE KADARDI? Günün Trend Haberleri Germenicia Boya Tekstil’in boyahane bölümünde yıllık 5 milyon 400 bin kilogram üretim kapasitesi bulunuyordu. Örgü bölümünün yıllık üretim kapasitesi ise 5 milyon kilogram seviyesindeydi. Yaklaşık 200 kişinin çalıştığı şirket, tekstil sektöründeki faaliyetlerini Kahramanmaraş merkezli olarak sürdürüyordu. OTELCİLİK SEKTÖRÜNDE DE FAALİYET GÖSTERİYORDU Şirketin tekstilin yanı sıra turizm sektöründe de yatırımı bulunuyordu. İstanbul’da Germenicia Hotel adıyla faaliyet gösteren bir işletmesi vardı. Şirketin finansal darboğazın ardından konkordato sürecinden başarıyla çıkamaması üzerine iflas kararı verildi. Şirketin vergi levhasındaki bilgilere göre 2024 ve 2025 yıllarında vergi matrahı oluşmadı. Kahramanmaraş İcra Dairesi, verilen iflas kararının ardından şirket hakkında ilgili iflas işlemlerini başlattı. İzin alınmadan, kaynak gösterilerek dahi iktibas edilemez. Bu habere emoji ile tepki ver 2019’da faaliyetlerine başlayan şirket, tekstil üretiminin yanı sıra otelcilik sektöründe de faaliyet gösteriyordu.</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.yeniankara.com.tr/ekonomi/ekonomist-sirinden-faiz-degerlendirmesi-bircok-firmada-iflas-var-182562</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>https://www.sozcu.com.tr/yuzlerce-calisani-olan-turk-tekstil-devi-iflas-etti-p358094</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Kahramanmaraş</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
@@ -5387,7 +5655,7 @@
       <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr"/>
@@ -5401,7 +5669,7 @@
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="n">
-        <v>61.56</v>
+        <v>75</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>30</v>
@@ -5410,7 +5678,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 18:50:00</t>
+          <t>2026-09-14 07:12:00</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -5425,12 +5693,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Yıldırım Gazetesi</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -5450,12 +5718,12 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı. Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı. Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı. BURSA Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Bursa 1. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı.</t>
+          <t>www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Yıldırım Gazetesi Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı. Asliye Ticaret Mahkemesi’nde görülecek davanın duruşma tarihi belli olurken, alacaklılara da itiraz ve davaya katılmaları için 15 günlük süre tanındı. BURSA Bursa’da bir şirket için daha iflas talebi! Mahkeme tarihi belli oldu Bursa’da faaliyet gösteren ES Pet Plastik Ambalaj Gıda Sanayi Ticaret Limited Şirketi hakkında iflas talebiyle dava açıldı.</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Doğrulama başarılı.</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -5465,15 +5733,19 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.yildirimgazetesi.com/bursada-bir-sirket-icin-daha-iflas-talebi-mahkeme-tarihi-belli-oldu</t>
+          <t>https://www.kocaelibarisgazetesi.com/amp/gundem/gebzede-iflas-eden-sirket-icin-alacaklilara-cagri-1-ay-sure-verildi-h160416</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>Kocaeli</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Gebze</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -5481,7 +5753,7 @@
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
@@ -5495,7 +5767,7 @@
       <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr"/>
       <c r="AA32" s="2" t="n">
-        <v>94.36</v>
+        <v>107.49</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>31</v>
@@ -5504,12 +5776,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 01:09:00</t>
+          <t>2026-09-14 08:07:27</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -5519,12 +5791,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Ege Gıda Meşrubat, konkordato süreci başlattı</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak?</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Ege Gıda Meşrubat, konkordato süreci başlattı egealternatif.com</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -5534,18 +5806,22 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>gıda</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi, Edirne 2’nci Asliye Hukuk Mahkemesi tarafından konkordato ilan etti ve 3 aylık geçici mühlet aldı. Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi, Edirne 2’nci Asliye Hukuk Mahkemesi tarafından konkordato ilan etti ve 3 aylık geçici mühlet aldı. Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi, Edirne 2’nci Asliye Hukuk Mahkemesi tarafından konkordato ilan etti ve 3 aylık geçici mühlet aldı.</t>
+          <t>Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Yeni müşterilere özel avantajlı ihtiyaç kredisi! Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. TÜM UÇUŞLARIN PLANLANDIĞI ŞEKİLDE KESİNTİSİZ SÜRECEĞİ BELİRTİLDİ AirBaltic, ABD'de iflas koruması başvurusunda bulundu! AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Açıklamada, yasal sürecin yolcuları ve günlük ticari faaliyetleri etkilemeyeceği, tüm uçuşların planlandığı şekilde kesintisiz süreceği, bilet ile rezervasyonların geçerliliğini koruyacağı vurgulandı. Bu arada, iflas koruması başvurusu kararı, şirketin 380 milyon avro değerindeki tahvillerin sahiplerinin alternatif bir ara finansman teklifini oylayacağ kritik toplantıdan bir gün önce geldi. Jet yakıtı fiyatlarındaki artış öncesinde de mali zorluk yaşayan hava yolunun, 2026-2027 dönemini finanse etmek için nakit girişine ihtiyaç duyduğu biliniyordu. Sürecin, Letonya 'da yaklaşan parlamento seçimlerinin hemen öncesine denk gelmesi de dikkati çekti. Hisselerinin yüzde 88,4'ü Letonya devletine ait olan AirBaltic'in yüzde 10 hissesi ise geçen yıl Alman hava yolu firması Lufthansa AG tarafından satın alınmıştı. Kaynak: AA | Bu içerik Hande Dağ tarafından yayına alınmıştır</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Ege Gıda Meşrubat, konkordato süreci başlattı Ege Gıda Meşrubat, konkordato süreci başlattı egealternatif.com Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi, Edirne 2’nci Asliye Hukuk Mahkemesi tarafından konkordato ilan etti ve 3 aylık geçici mühlet aldı.</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Yeni müşterilere özel avantajlı ihtiyaç kredisi! Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? TÜM UÇUŞLARIN PLANLANDIĞI ŞEKİLDE KESİNTİSİZ SÜRECEĞİ BELİRTİLDİ AirBaltic, ABD'de iflas koruması başvurusunda bulundu! AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Açıklamada, yasal sürecin yolcuları ve günlük ticari faaliyetleri etkilemeyeceği, tüm uçuşların planlandığı şekilde kesintisiz süreceği, bilet ile rezervasyonların geçerliliğini koruyacağı vurgulandı. Bu arada, iflas koruması başvurusu kararı, şirketin 380 milyon avro değerindeki tahvillerin sahiplerinin alternatif bir ara finansman teklifini oylayacağ kritik toplantıdan bir gün önce geldi. Jet yakıtı fiyatlarındaki artış öncesinde de mali zorluk yaşayan hava yolunun, 2026-2027 dönemini finanse etmek için nakit girişine ihtiyaç duyduğu biliniyordu. Sürecin, Letonya 'da yaklaşan parlamento seçimlerinin hemen öncesine denk gelmesi de dikkati çekti. Hisselerinin yüzde 88,4'ü Letonya devletine ait olan AirBaltic'in yüzde 10 hissesi ise geçen yıl Alman hava yolu firması Lufthansa AG tarafından satın alınmıştı.</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -5555,7 +5831,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.egealternatif.com/haber/ege-gida-mesrubat-konkordato-sureci-baslatti_92480/</t>
+          <t>https://www.mynet.com/amp/unlu-hava-yolu-sirketinden-iflas-koruma-basvurusu-biletler-ne-olacak-finans-574454</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
@@ -5563,49 +5839,25 @@
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>Ege Gıda:292:body+summary+title | Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi:raw_legal</t>
-        </is>
-      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>Ege Gıda Meşrubat Sanayi ve Ticaret Limited Şirketi Türkiye</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Ege Gıda Sanayi ve Ticaret Limited Şirketi | EGE EXPORT GIDA SANAYİ VE TİCARET LİMİTED ṢİRKETİ | EGE GRUP GIDA DIS TICARET ANONIM SIRKETI | Ege Gıda Meşrubat San</t>
-        </is>
-      </c>
-      <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>Ege Gıda Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t>100.0 | 67.3076923076923 | 75.0 | 100</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
       <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" s="2" t="n">
-        <v>156.8</v>
+        <v>99</v>
       </c>
       <c r="AB33" s="2" t="n">
         <v>32</v>
@@ -5614,12 +5866,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:08:44</t>
+          <t>2026-09-14 07:23:36</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>tasfiye</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5629,12 +5881,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı...</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek enerjifm.com.tr</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5644,18 +5896,22 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>enerji</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+          <t>tekstil, şirket</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. Resmi Gazete'de yayımlanan "2027-2029 Dönemi Bütçe Çağrısı" ile ka 2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. Resmi Gazete'de yayımlanan "2027-2029 Dönemi Bütçe Çağrısı" ile ka 2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. Resmi Gazete'de yayımlanan "2027-2029 Dönemi Bütçe Çağrısı" ile kamu idarelerinin yeni dönem bütçe çalışmalarında izleyeceği...Devamı için tıklayınız Şarkı İsteği Gönder DJ'e şarkı isteğinizi iletin İsteğiniz Alındı! DJ en kısa sürede isteğinizi değerlendirecektir. Kapat CANLI Yükleniyor... Enerji FM 100.5 Alemin En kral Radyosu Dinle Kamuda ihtiyaç fazlası araçlar tasfiye edilecek İçerikle ilgili telif hakkı ihlali veya başka bir itirazınız varsa aşağıdaki formu doldurun. En kısa sürede değerlendirip gerekli işlemi yapacağız. DJ'e şarkı isteğinizi iletin DJ en kısa sürede isteğinizi değerlendirecektir.</t>
+          <t>Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil sektöründe faaliyet gösteren bir şirketin devam eden iflas tasfiyesinde yeni bir aşamaya geçildi. Bursa İflas Dairesi’nin 2025/10 İflas sayılı dosyası kapsamında, Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında basit tasfiyede ek sıra cetveli ilanı yayımlandı. ŞİRKETİN İFLASINA 2025 YILINDA KARAR VERİLMİŞTİ İlanda yer alan bilgilere göre Bursa 1. Asliye Ticaret Mahkemesi, 14 Ağustos 2025 tarihli ve 2025/490 Esas sayılı kararıyla şirketin iflasına hükmetti. Şirketin iflası aynı gün saat 14.57 itibarıyla açılırken, tasfiye işlemlerinin basit usulde gerçekleştirilmesine karar verildi. KESTEL'DEKİ TEKSTİL ŞİRKETİ İflas ilanında şirketin adresi de ayrıntılı şekilde yer aldı. Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi'nin adresi Ahmet Vefik Paşa OSB Mahallesi, Yeniyol Caddesi, MNG Tekstil Ltd. Sitesi, MNG Tekstil No:10, Kestel/Bursa olarak belirtildi. ALACAK KAYIT TALEPLERİ İNCELENDİ Bursa İflas Dairesi tarafından yürütülen tasfiye kapsamında iflas dosyasına yapılan alacak kayıt taleplerinin incelendiği ve alacaklar hakkında karar verildiği bildirildi. İcra ve İflas Kanunu hükümlerine göre hazırlanan ek sıra cetveli, ilgililerin incelemesine sunulmak üzere iflas dosyasında hazır tutuluyor. Sıra cetveli, iflas tasfiyesinde alacaklıların taleplerinin hangi kapsamda değerlendirildiği ve alacakların sıralamasına ilişkin süreç açısından önem taşıyor. ALACAKLILAR DİKKAT: 15 VE 7 GÜNLÜK İTİRAZ SÜRESİ İlanda alacaklıların itiraz haklarına ilişkin kritik süreler de açıklandı. Buna göre alacağın esasına ve miktarına yönelik itirazların 15 gün içerisinde, Bursa İflas Dairesi'nin bulunduğu yerdeki Ticaret Mahkemesi'nde dava konusu edilmesi gerekiyor. Sıraya ilişkin itirazlar için ise 7 günlük süre bulunuyor. Bu kapsamdaki itirazların şikâyet yoluyla İcra Mahkemesi'ne taşınabileceği belirtildi. Söz konusu süreler ilan tarihine bağlı hukuki süreler olduğundan, ilgililerin resmi ilandaki tarih ve usulleri esas alması önem taşıyor.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Kamuda ihtiyaç fazlası araçlar tasfiye edilecek Kamuda ihtiyaç fazlası araçlar tasfiye edilecek enerjifm.com.tr 2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. Resmi Gazete'de yayımlanan "2027-2029 Dönemi Bütçe Çağrısı" ile ka 2027-2029 dönemini kapsayan Merkezi Yönetim Bütçesi hazırlık süreci başladı. DJ en kısa sürede isteğinizi değerlendirecektir. Enerji FM 100.5 Alemin En kral Radyosu Dinle Kamuda ihtiyaç fazlası araçlar tasfiye edilecek İçerikle ilgili telif hakkı ihlali veya başka bir itirazınız varsa aşağıdaki formu doldurun. En kısa sürede değerlendirip gerekli işlemi yapacağız. DJ'e şarkı isteğinizi iletin DJ en kısa sürede isteğinizi değerlendirecektir.</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’da tekstil sektöründe faaliyet gösteren bir şirketin devam eden iflas tasfiyesinde yeni bir aşamaya geçildi. Bursa İflas Dairesi’nin 2025/10 İflas sayılı dosyası kapsamında, Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında basit tasfiyede ek sıra cetveli ilanı yayımlandı. ŞİRKETİN İFLASINA 2025 YILINDA KARAR VERİLMİŞTİ İlanda yer alan bilgilere göre Bursa 1. Asliye Ticaret Mahkemesi, 14 Ağustos 2025 tarihli ve 2025/490 Esas sayılı kararıyla şirketin iflasına hükmetti. Şirketin iflası aynı gün saat 14.57 itibarıyla açılırken, tasfiye işlemlerinin basit usulde gerçekleştirilmesine karar verildi. KESTEL'DEKİ TEKSTİL ŞİRKETİ İflas ilanında şirketin adresi de ayrıntılı şekilde yer aldı. Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi'nin adresi Ahmet Vefik Paşa OSB Mahallesi, Yeniyol Caddesi, MNG Tekstil Ltd. Sitesi, MNG Tekstil No:10, Kestel/Bursa olarak belirtildi. ALACAK KAYIT TALEPLERİ İNCELENDİ Bursa İflas Dairesi tarafından yürütülen tasfiye kapsamında iflas dosyasına yapılan alacak kayıt taleplerinin incelendiği ve alacaklar hakkında karar verildiği bildirildi. İcra ve İflas Kanunu hükümlerine göre hazırlanan ek sıra cetveli, ilgililerin incelemesine sunulmak üzere iflas dosyasında hazır tutuluyor. Sıra cetveli, iflas tasfiyesinde alacaklıların taleplerinin hangi kapsamda değerlendirildiği ve alacakların sıralamasına ilişkin süreç açısından önem taşıyor. ALACAKLILAR DİKKAT: 15 VE 7 GÜNLÜK İTİRAZ SÜRESİ İlanda alacaklıların itiraz haklarına ilişkin kritik süreler de açıklandı. Buna göre alacağın esasına ve miktarına yönelik itirazların 15 gün içerisinde, Bursa İflas Dairesi'nin bulunduğu yerdeki Ticaret Mahkemesi'nde dava konusu edilmesi gerekiyor. Sıraya ilişkin itirazlar için ise 7 günlük süre bulunuyor. Bu kapsamdaki itirazların şikâyet yoluyla İcra Mahkemesi'ne taşınabileceği belirtildi. Söz konusu süreler ilan tarihine bağlı hukuki süreler olduğundan, ilgililerin resmi ilandaki tarih ve usulleri esas alması önem taşıyor.</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -5665,19 +5921,35 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://enerjifm.com.tr/haber/23335/kamuda-ihtiyac-fazlasi-araclar-tasfiye-edilecek</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
+          <t>https://www.bursahakimiyet.com.tr/bursa/bursa-da-tekstil-sirketinin-iflasinda-yeni-gelisme-alacaklilar-icin-sure-basladi-1709285</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Kestel</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Ahmet Vefik Paşa OSB Mahallesi | adresi Ahmet Vefik Paşa OSB</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Yeniyol Caddesi</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr"/>
@@ -5691,7 +5963,7 @@
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="n">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="AB34" s="2" t="n">
         <v>33</v>
@@ -5700,27 +5972,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 17:51:00</t>
+          <t>2026-09-14 09:53:53</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınına müdahale sürüyor</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınına müdahale sürüyor Güneydoğu Ekspres</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -5730,22 +6002,22 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Bolu Fabrika yangınına müdahale sürüyor Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Ali Abbas YILMAZ 12.09.2026 - 20:51 Okunma Süresi: 1 Dk Trafik ışıklarında feci kaza yaşandı İçeriği Görüntüle Bolu’nun Gerede ilçesinde organize sanayi bölgesinde faaliyet gösteren bir geri dönüşüm fabrikasında henüz belirlenemeyen nedenle yangın çıktı. Haber verilmesi üzerine bölgeye itfaiye ekipleri sevk edildi. Yangın nedeniyle bölgede yoğun duman oluşurken, fabrikadan patlama sesleri duyuluyor. Ekiplerin yangını söndürme çalışmaları sürüyor. Kaynak: MA Editörün Seçtiği Sabahattin Ali’nin öyküleri Kürtçeye çevrildi Editörün Seçtiği Köyden kente geliyor, sabah saatlerinde tükeniyor Editörün Seçtiği Gastronomi araştırmacısı Mehmet Kudat: Diyarbakır tandır kültür yeniden canlandırılmalı Editör Hakkında Ali Abbas YILMAZ B</t>
+          <t>Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. DOLAR 48,62 0,20% EURO 56,15 -0,30% ALTIN 6621,33 0,00% BIST 100 13821,97 0,49% TRY 0.0230 USD 0.0193 EUR Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Edip Üçok 14 Eylül 2026 | 12:54 AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu. 13:17 Bagajınızda bunlar yoksa cezası var: 2026'nın zorunlu araç gereçleri listelendi 13:11 Tüketici temsilcileri uyardı: Kırtasiye alışverişinde "Popüler Ürün" tuzağına düşmeyin 12:54 Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu 12:41 "İran'ın komşularıyla, özellikle de Türkiye ile ilişkisi istenilen düzeyde" 12:31 Net Global halka arz sonuçları açıklandı: Bireysele kaç lot düştü? 12:22 AJet'in yurt içi uçuşlarda indirim kampanyası başladı 12:18 Otomotivde 8 aylık tablo belli oldu: Adetler düştü, ihracat geliri yükseldi 12:01 Ankara bir zamanlar deniz miydi? Külhöyük’te 66 milyon yıllık keşif 11:47 Türkiye sermaye piyasaları büyüyor: Menkul kıymetler 38 trilyon liraya ulaştı, yatırımcı sayısı 40 milyona yaklaştı 11:32 Evlilik desteği projesi yaygınlaşıyor: Yerel ve ulusal firma sayısı artışta USD/TRY 30 dk 1 saat 1 gün USD/TRY EURO/TRY ALTIN/TRY BITCOIN/TRY Döviz Çevirici TRY 0.0230 USD 0.0193 EUR Hesapla Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınına müdahale sürüyor Fabrika yangınına müdahale sürüyor Güneydoğu Ekspres Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor. Bolu Fabrika yangınına müdahale sürüyor Bolu’nun Gerede ilçesinde bir geri dönüşüm fabrikasında çıkan yangın söndürülmeye çalışırken fabrikadan patlama sesleri yükseliyor.</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. DOLAR 48,62 0,20% EURO 56,15 -0,30% ALTIN 6621,33 0,00% BIST 100 13821,97 0,49% TRY 0.0230 USD 0.0193 EUR Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Edip Üçok 14 Eylül 2026 | 12:54 AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu. 13:17 Bagajınızda bunlar yoksa cezası var: 2026'nın zorunlu araç gereçleri listelendi 13:11 Tüketici temsilcileri uyardı: Kırtasiye alışverişinde "Popüler Ürün" tuzağına düşmeyin 12:54 Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu 12:41 "İran'ın komşularıyla, özellikle de Türkiye ile ilişkisi istenilen düzeyde" 12:31 Net Global halka arz sonuçları açıklandı: Bireysele kaç lot düştü? 12:22 AJet'in yurt içi uçuşlarda indirim kampanyası başladı 12:18 Otomotivde 8 aylık tablo belli oldu: Adetler düştü, ihracat geliri yükseldi 12:01 Ankara bir zamanlar deniz miydi? Külhöyük’te 66 milyon yıllık keşif 11:47 Türkiye sermaye piyasaları büyüyor: Menkul kıymetler 38 trilyon liraya ulaştı, yatırımcı sayısı 40 milyona yaklaştı 11:32 Evlilik desteği projesi yaygınlaşıyor: Yerel ve ulusal firma sayısı artışta USD/TRY 30 dk 1 saat 1 gün USD/TRY EURO/TRY ALTIN/TRY BITCOIN/TRY Döviz Çevirici TRY 0.0230 USD 0.0193 EUR Hesapla Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5755,19 +6027,11 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.guneydoguekspres.com/fabrika-yanginina-mudahale-suruyor-1</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+          <t>https://www.ekonomist.com.tr/dunya/savasin-maliyetine-dayanamadi-dev-havayolu-sirketi-iflas-korumasi-basvurusunda-bulundu-78706</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr"/>
@@ -5775,7 +6039,7 @@
       <c r="S35" s="2" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr"/>
@@ -5789,7 +6053,7 @@
       <c r="Y35" s="2" t="inlineStr"/>
       <c r="Z35" s="2" t="inlineStr"/>
       <c r="AA35" s="2" t="n">
-        <v>79.56999999999999</v>
+        <v>98.75</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>34</v>
@@ -5798,7 +6062,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 18:58:00</t>
+          <t>2026-09-13 20:36:11</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -5813,12 +6077,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı</t>
+          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Zonguldak Pusula Son Dakika Haberleri</t>
+          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor aksiyon.com.tr</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -5838,12 +6102,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi.</t>
+          <t>Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Gece yarısı Düzce Door fabrikasında yangın Düzce D-100 karayolu kenarında bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında başlayan yangın, kısa sürede büyüyerek fabrikayı etkisi altına aldı. Olay yerine intikal eden Düzce Belediye ekipleri ve itfaiye müdahalesi ile alevleri kontrol altına almak için çalışma başlattı. Olay yeri ve müdahale: İlk ihbarın D-100 karayolundan görüldüğü için geldiğini belirten yetkililer, itfaiye ekiplerinin bölgeye yönlendirildiğini söyledi. Ahşap ve Amerikan panel üretimi yapan fabrikanın malzeme yapısı nedeniyle yangının kısa sürede yayıldığı bildirildi. Belediye ekipleri yangına müdahale ederken öncelik olarak personel güvenliği ve çevredeki yapıların korunması hedeflendi. Başkan Özlü'nün açıklamaları: Düzce Belediye Başkanı Dr. Faruk Özlü , olay yerinde yaptığı açıklamada ekiplere tüm imkanların seferber edildiğini ve yangının en kısa sürede kontrol altına alınmasının amaçlandığını söyledi. Özlü, ilk bildirimde gecikme olduğunu düşündüğünü, bazı komşuların fabrikada zaman zaman küçük çaplı yangınlar yaşandığını ifade ettiğini aktardı. Başkan Özlü, "İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra uzmanlarımız çıkış sebebi üzerinde çalışacaklar" diyerek, fabrikanın yapısal özellikleri nedeniyle alevlerin hızla yayıldığını vurguladı. Ayrıca can kaybı olmadığını belirterek, fabrika sahiplerine ve Düzce halkına geçmiş olsun dileğinde bulundu. Yetkililer, söndürme çalışmalarının bu akşam tamamlanmasının hedeflendiğini, yangının kesin çıkış nedeninin ise inceleme sonrası netleşeceğini bildirdi. Düzce Belediye Başkanı Faruk Özlü yangını en kısa sürede söndürmeye çalıştıklarını söyledi 1 Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı 2 Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada 3 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 4 Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı 5 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 6 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 7 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor Gece yarısı Düzce Door fabrikasında yangın Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Düzce D-100 karayolu kenarında bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında başlayan yangın, kısa sürede büyüyerek fabrikayı etkisi altına aldı. Olay yerine intikal eden Düzce Belediye ekipleri ve itfaiye müdahalesi ile alevleri kontrol altına almak için çalışma başlattı. İlk ihbarın D-100 karayolundan görüldüğü için geldiğini belirten yetkililer, itfaiye ekiplerinin bölgeye yönlendirildiğini söyledi. Ahşap ve Amerikan panel üretimi yapan fabrikanın malzeme yapısı nedeniyle yangının kısa sürede yayıldığı bildirildi. Belediye ekipleri yangına müdahale ederken öncelik olarak personel güvenliği ve çevredeki yapıların korunması hedeflendi. Düzce Belediye Başkanı Dr. Faruk Özlü , olay yerinde yaptığı açıklamada ekiplere tüm imkanların seferber edildiğini ve yangının en kısa sürede kontrol altına alınmasının amaçlandığını söyledi. Özlü, ilk bildirimde gecikme olduğunu düşündüğünü, bazı komşuların fabrikada zaman zaman küçük çaplı yangınlar yaşandığını ifade ettiğini aktardı. Başkan Özlü, "İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra uzmanlarımız çıkış sebebi üzerinde çalışacaklar" diyerek, fabrikanın yapısal özellikleri nedeniyle alevlerin hızla yayıldığını vurguladı. Ayrıca can kaybı olmadığını belirterek, fabrika sahiplerine ve Düzce halkına geçmiş olsun dileğinde bulundu. Yetkililer, söndürme çalışmalarının bu akşam tamamlanmasının hedeflendiğini, yangının kesin çıkış nedeninin ise inceleme sonrası netleşeceğini bildirdi. Düzce Belediye Başkanı Faruk Özlü yangını en kısa sürede söndürmeye çalıştıklarını söyledi Ben Ahmet Demir, 30 yaşındayım, İstanbul. aksiyon.com.tr Gündem ekibinin 'son d</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Zonguldak Pusula Son Dakika Haberleri Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi.</t>
+          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor aksiyon.com.tr Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Gece yarısı Düzce Door fabrikasında yangın Düzce D-100 karayolu kenarında bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında başlayan yangın, kısa sürede büyüyerek fabrikayı etkisi altına aldı. Olay yerine intikal eden Düzce Belediye ekipleri ve itfaiye müdahalesi ile alevleri kontrol altına almak için çalışma başlattı. Olay yeri ve müdahale: İlk ihbarın D-100 karayolundan görüldüğü için geldiğini belirten yetkililer, itfaiye ekiplerinin bölgeye yönlendirildiğini söyledi. Ahşap ve Amerikan panel üretimi yapan fabrikanın malzeme yapısı nedeniyle yangının kısa sürede yayıldığı bildirildi. Belediye ekipleri yangına müdahale ederken öncelik olarak personel güvenliği ve çevredeki yapıların korunması hedeflendi. Başkan Özlü'nün açıklamaları: Düzce Belediye Başkanı Dr. Faruk Özlü , olay yerinde yaptığı açıklamada ekiplere tüm imkanların seferber edildiğini ve yangının en kısa sürede kontrol altına alınmasının amaçlandığını söyledi. Özlü, ilk bildirimde gecikme olduğunu düşündüğünü, bazı komşuların fabrikada zaman zaman küçük çaplı yangınlar yaşandığını ifade ettiğini aktardı. Başkan Özlü, "İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra uzmanlarımız çıkış sebebi üzerinde çalışacaklar" diyerek, fabrikanın yapısal özellikleri nedeniyle alevlerin hızla yayıldığını vurguladı. Ayrıca can kaybı olmadığını belirterek, fabrika sahiplerine ve Düzce halkına geçmiş olsun dileğinde bulundu. Yetkililer, söndürme çalışmalarının bu akşam tamamlanmasının hedeflendiğini, yangının kesin çıkış nedeninin ise inceleme sonrası netleşeceğini bildirdi. Düzce Belediye Başkanı Faruk Özlü yangını en kısa sürede söndürmeye çalıştıklarını söyledi 1 Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı 2 Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada 3 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 4 Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı 5 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 6 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 7 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor Gece yarısı Düzce Door fabrikasında yangın Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Düzce D-100 karayolu kenarında bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında başlayan yangın, kısa sürede büyüyerek fabrikayı etkisi altına aldı. İlk ihbarın D-100 karayolundan görüldüğü için geldiğini belirten yetkililer, itfaiye ekiplerinin bölgeye yönlendirildiğini söyledi. Düzce Belediye Başkanı Dr. Düzce Belediye Başkanı Faruk Özlü yangını en kısa sürede söndürmeye çalıştıklarını söyledi Ben Ahmet Demir, 30 yaşındayım, İstanbul.</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -5853,15 +6117,19 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.pusulagazetesi.com.tr/fabrika-yangininda-yaklasik-4-saat-geride-kaldi-1-yarali</t>
+          <t>https://www.aksiyon.com.tr/gece-yarisi-duzce-door-fabrikasinda-cikan-yangina-itfaiye-mudahale-ediyor-353989</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>Adana | Bilecik | Düzce | Iğdır | Zonguldak</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Köşk | Mudurnu</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -5869,7 +6137,7 @@
       <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr"/>
@@ -5883,7 +6151,7 @@
       <c r="Y36" s="2" t="inlineStr"/>
       <c r="Z36" s="2" t="inlineStr"/>
       <c r="AA36" s="2" t="n">
-        <v>84.98999999999999</v>
+        <v>117.5</v>
       </c>
       <c r="AB36" s="2" t="n">
         <v>35</v>
@@ -5892,12 +6160,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 17:37:21</t>
+          <t>2026-09-13 20:44:00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>usulsüzlük</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -5907,12 +6175,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü</t>
+          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Bursa Saati</t>
+          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Cumhuriyet</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5922,22 +6190,22 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>imalat, imalathane</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>üretim tesisi</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Asayiş Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. 12.09.2026 - 20:37 12.09.2026 - 20:37 Loading... Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Edinilen bilgiye göre, ilçeye bağlı Sanayi Mahallesi Osman Kavuncu Bulvarı üzerinde bulunan bir avize imalathanesinin çatısında henüz bilinmeyen bir sebeple yangın çıktı. İhbar üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin müdahalesiyle yangın söndürülürken, iş yerinin çatısında hasar meydana geldi. Olayla ilgili soruşturma başlatıldı. B</t>
+          <t>Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Edinilen bilgiye göre, saat 21.40 sıralarında Door Kapı Fabrikası'nda henüz belirlenemeyen bir nedenle yangın çıktı. Alevler kısa sürede fabrikanın geniş bir bölümüne yayılırken, yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. İhbar üzerine bölgeye çok sayıda itfaiye, sağlık ve güvenlik ekibi sevk edildi. Yangının büyüklüğü nedeniyle Düzce'nin ilçelerinden itfaiye ekipleri bölgeye yönlendirilirken, Bolu'dan da takviye ekipler sevk edildi. Dron ile havadan kaydedilen görüntülerde fabrikanın büyük bölümünü saran alevler ve bölgeden yükselen yoğun duman dikkat çekti. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Yangının çıkış nedeninin ise söndürme çalışmalarının ardından yapılacak incelemeyle belirlenmesi bekleniyor. BELEDİYE BAŞKANINDAN AÇIKLAMA: 'ÖNEMLİ OLAN CAN KAYBININ OLMAMASI' Düzce Belediye Başkanı Faruk Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirtti. Başkan Özlü, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Ama gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce'mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. Düzce’de kapı fabrikasında yangın Müdahale sürüyor, belediye başkanından açıklama geldi "Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" https://t.co/FX7LXZRI1N pic.twitter.com/0q2oeam7me — Cumhuriyet (@cumhuriyetgzt1) September 13, 2026 Hava Durumu Namaz Vakitleri Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Takip Et: Paylaş:</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Bursa Saati Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. Asayiş Kayseri'de avize imalathanesinin çatısında çıkan yangın söndürüldü Kayseri'nin Kocasinan ilçesinde bir avize imalathanesinin çatı kısımda çıkan yangın itfaiye ekiplerinin müdahalesiyle söndürüldü. 12.09.2026 - 20:37 12.09.2026 - 20:37 Loading... Edinilen bilgiye göre, ilçeye bağlı Sanayi Mahallesi Osman Kavuncu Bulvarı üzerinde bulunan bir avize imalathanesinin çatısında henüz bilinmeyen bir sebeple yangın çıktı. İhbar üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Polis ekipleri çevrede güvenlik önlemi alırken, itfaiye ekipleri de yangına müdahale etti. Ekiplerin müdahalesiyle yangın söndürülürken, iş yerinin çatısında hasar meydana geldi. Olayla ilgili soruşturma başlatıldı.</t>
+          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Cumhuriyet Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Edinilen bilgiye göre, saat 21.40 sıralarında Door Kapı Fabrikası'nda henüz belirlenemeyen bir nedenle yangın çıktı. Alevler kısa sürede fabrikanın geniş bir bölümüne yayılırken, yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. İhbar üzerine bölgeye çok sayıda itfaiye, sağlık ve güvenlik ekibi sevk edildi. Yangının büyüklüğü nedeniyle Düzce'nin ilçelerinden itfaiye ekipleri bölgeye yönlendirilirken, Bolu'dan da takviye ekipler sevk edildi. Dron ile havadan kaydedilen görüntülerde fabrikanın büyük bölümünü saran alevler ve bölgeden yükselen yoğun duman dikkat çekti. Yangının çıkış nedeninin ise söndürme çalışmalarının ardından yapılacak incelemeyle belirlenmesi bekleniyor. BELEDİYE BAŞKANINDAN AÇIKLAMA: 'ÖNEMLİ OLAN CAN KAYBININ OLMAMASI' Düzce Belediye Başkanı Faruk Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirtti. Başkan Özlü, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce'mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. Düzce’de kapı fabrikasında yangın Müdahale sürüyor, belediye başkanından açıklama geldi "Önemli olan can kaybının olmaması. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" https://t.co/FX7LXZRI1N pic.twitter.com/0q2oeam7me — Cumhuriyet (@cumhuriyetgzt1) September 13, 2026 Hava Durumu Namaz Vakitleri Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Takip Et: Paylaş:</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -5947,35 +6215,27 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.bursasaati.com.tr/kayseride-avize-imalathanesinin-catisinda-cikan-yangin-sonduruldu/amp</t>
+          <t>https://www.cumhuriyet.com.tr/turkiye/duzce-de-kapi-fabrikasinda-yangin-mudahale-suruyor-belediye-baskanindan-aciklama-geldi-2537255</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Kayseri</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>Kocasinan</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>ilçeye bağlı Sanayi Mahallesi</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>Sanayi Mahallesi Osman Kavuncu Bulvarı</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr"/>
+          <t>Bolu | Düzce</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>Door Kapı Fabrikası</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr"/>
@@ -5989,7 +6249,7 @@
       <c r="Y37" s="2" t="inlineStr"/>
       <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="n">
-        <v>134.72</v>
+        <v>133.75</v>
       </c>
       <c r="AB37" s="2" t="n">
         <v>36</v>
@@ -5998,12 +6258,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 19:04:58</t>
+          <t>2026-09-13 21:48:26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>yolsuzluk</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -6013,12 +6273,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Aksiyon.com.TR</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -6028,18 +6288,22 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. yangın sürüyor, söndürme çalışmaları devam ediyorBolu'nun Gerede ilçesinde bulunan Gerede Karma Organize Sanayi Bölgesi (OSB) içindeki geri dönüşüm tesisinde saat 19.00 civarında henüz belirlenemeyen nedenle yangın başladı. Kısa sürede fabrikaya yayılan alevler, ekiplerin yoğun çalışmasına rağmen yaklaşık 4 saattir kontrol… HABERİN DEVAMI Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı.</t>
+          <t>Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Aksiyon.com.TR Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. yangın sürüyor, söndürme çalışmaları devam ediyorBolu'nun Gerede ilçesinde bulunan Gerede Karma Organize Sanayi Bölgesi (OSB) içindeki geri dönüşüm tesisinde saat 19.00 civarında henüz belirlenemeyen nedenle yangın başladı. Kısa sürede fabrikaya yayılan alevler, ekiplerin yoğun çalışmasına rağmen yaklaşık 4 saattir kontrol… HABERİN DEVAMI Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı. Gerede'de geri dönüşüm tesisinde çıkan yangın müdahale süresini 4 saate taşıdı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangına yaklaşık 4 saattir itfaiye müdahale ediyor; 1 işçi hafif yaralandı ve hastaneye kaldırıldı.</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -6049,7 +6313,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.aksiyon.com.tr/gerede-de-geri-donusum-tesisinde-cikan-yangin-mudahale-suresini-4-saate-tasidi-353480/amp</t>
+          <t>https://www.sondakika.com/amp/haber-duzce-hacialiler-koyundeki-fabrika-yanginina-sakar-20234469/</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -6057,11 +6321,7 @@
           <t>Bolu</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -6069,7 +6329,7 @@
       <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr"/>
@@ -6083,7 +6343,7 @@
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="n">
-        <v>117.63</v>
+        <v>96.03</v>
       </c>
       <c r="AB38" s="2" t="n">
         <v>37</v>
@@ -6092,27 +6352,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:39:00</t>
+          <t>2026-09-13 20:36:42</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı!</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6122,28 +6382,32 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>turizm</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. VİB Turizm'den dolandırıcılık uyarısı! Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Haber Merkezi Editör 13.09.2026 - 17:39 Yayınlanma — P</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı! VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. VİB Turizm'den dolandırıcılık uyarısı!</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.bizimsakarya.com.tr/vib-turizmden-dolandiricilik-uyarisi</t>
+          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOWFBIUXlRV3gyZy1XMnUzM3d5R3YtcDlaSjdiQlNXalhVMTAwSHhhZWtKSHVkTzVMd09OMWxZbVlheGI1dmthNkZXVTM5RXRjUkduanpSX3NRN0JRa0c0dEo3MTFPVmdzemJSLTNNMnFDc0JSM0ZOVldLUWM5X2tZUkF5c0pCdHY2WHE1M2NCdTdGWlVzV192S1FEdUJtYlQ3ai1WbUpoX1BKdXNSRWJRb190OG9EbWZsVmhWaXJ5OUdEazNLVTZlMFNtR0dILTltdkxkYkN1SDNtUWFCX0FXMEZ5OERZMk1HWjdzM0diNjBodVFfYjlvZEVhVQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
@@ -6169,7 +6433,7 @@
       <c r="Y39" s="2" t="inlineStr"/>
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="n">
-        <v>54.14</v>
+        <v>118.1</v>
       </c>
       <c r="AB39" s="2" t="n">
         <v>38</v>
@@ -6178,27 +6442,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 00:03:35</t>
+          <t>2026-09-13 19:48:24</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada aksiyon.com.tr</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -6208,32 +6472,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>enerji</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr"/>
+          <t>tesis, üretim, üretim tesisi</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>üretim tesisi</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr</t>
+          <t>Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. olay yerine intikal ve müdahale: Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. alevler ve dumanın görünürlüğü: Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. müdahalenin sürdüğü bildirildi: Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. 1 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 2 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 3 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 4 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı 5 Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı 6 Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı 7 Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada olay yerine intikal ve müdahale: Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. Ben Mehmet Yılmaz, 28 yaşındayım. İstanbul'dayım. aksiyon.com.tr Gündem ekibinin hırslı araştırmacı gazetecisiyim. Masa başında durmayı sevmem; sahada, meclis koridorlarında, siyasi kulislerde gerçeklerin peşindeyim. İdealist biriyim ve işimi ciddiyetle yaparım. 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr Yeni dolandırıcılık yöntemi: Sistem güncellemesi! Piyasanın çok altındaki ev ilanlarına dikkat enerjifm.com.tr</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada aksiyon.com.tr Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. olay yerine intikal ve müdahale: Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. alevler ve dumanın görünürlüğü: Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. müdahalenin sürdüğü bildirildi: Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. 1 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 2 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 3 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 4 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı 5 Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı 6 Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı 7 Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada olay yerine intikal ve müdahale: Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Ben Mehmet Yılmaz, 28 yaşındayım. Masa başında durmayı sevmem; sahada, meclis koridorlarında, siyasi kulislerde gerçeklerin peşindeyim. 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOa0FHZTR5WWlLWURTM3dxOVl2T1pPNTJVWGRscEloTnBweGxJZDdzNXlqX09SUUdiTnRlMTZHUkV1UkNiZ1R0MFV0Wm1Dd3k0Q2x4VmFhOHdTRWxhNEx1STV6eXNKaTdNRjVzSDVOTlFza2N1ZEs2RjkyRk5MYlc4Tk5aWDVKOGtRem5yVjNlQy1zVUJ0d2twZjhZQmQ2VHhPT3JoT1BULS1kTkR2czdWT3Q2ei1FNjlBYzVlUmNCZUQyY0ZPZVJn?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>https://www.aksiyon.com.tr/duzce-de-uretim-tesisinde-yangin-alarmi-itfaiye-ekipleri-sahada-353976</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Adana | Aydın | Bartın | Düzce | Iğdır</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Köşk | Mudurnu | Maltepe</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -6241,7 +6517,7 @@
       <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr"/>
@@ -6255,7 +6531,7 @@
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="n">
-        <v>91.59999999999999</v>
+        <v>102.75</v>
       </c>
       <c r="AB40" s="2" t="n">
         <v>39</v>
@@ -6264,27 +6540,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:10:48</t>
+          <t>2026-09-14 07:27:59</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı duzcegazeteefsane.com</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6294,35 +6570,39 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem</t>
+          <t>Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem LGBT derneklerine bağışa soruşturma! 45 bin banka hesabına inceleme haberi Finans Gündem</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı duzcegazeteefsane.com Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPeXNpNGNCMnJGZDc4ZFk5SWZ4Nmx0TEhETXNqc2EycnhaVGx6VWNSUWtDelJSTmRMOW5yZ3Z2RGxDYkkxeUdiTVZ4R2JSUjdId1hzak50cklfdkxTVS1tTVVxN1Zaakl0dWRmcElXdnBTZEVxNHQxRFRCTHpTTktjdTg5azFadm80TW1uZXNIVzg3VE9KNzg4NHFpdGlaN215c2w4eWdyVVprMG9DZmQySnBR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>https://www.duzcegazeteefsane.com/duzce-belediyesi-gundem-duzce-haberleri/15394-saniyelerle-yarisildi:-duzcedeki-fabrika-yanginina-hizli-mudahale-ve-ekiplerin-zaman-cizelgesi-aciklandi</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
@@ -6331,7 +6611,7 @@
       <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr"/>
@@ -6345,7 +6625,7 @@
       <c r="Y41" s="2" t="inlineStr"/>
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="n">
-        <v>65.88</v>
+        <v>115.01</v>
       </c>
       <c r="AB41" s="2" t="n">
         <v>40</v>
@@ -6354,27 +6634,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:52:00</t>
+          <t>2026-09-13 14:06:00</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>banka hesabına bloke</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama!</t>
+          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com</t>
+          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı yeniadimgazetesi.com</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6384,22 +6664,22 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Emekli Maaşlarına Ek Zam: Seyyanen Zam İçin Gözler Kritik Kararda! İçeriği Görüntüle Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Vatandaşların hukuki süreçlerde en sık karşılaştığı ve kafa karışıklığı yaşadığı konuların başında, maaşın işveren tarafından bankaya yatırılmasından sonraki hukuki statüsü gelmektedir. Maaş kesintisi doğrudan işyeri üzerinden icra dairesi kanalıyla yapılırken, banka hesaplarına uygulanan e-haciz işlemleri Doğrudan banka blokajı olarak gerçekleşmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Bu durum, banka hesabında bloke bulunan vatandaşların işlem türünü doğru tespit etmesini zorunlu kılmaktadır. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. Uygulanan işlemin bir maaş haczi mi yoksa banka mevduat haczi mi olduğunun icra dosyasından doğrulanması gerekmektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Akseki Aksu Alanya Demre Döşemealtı Elmalı Finike Gazipaşa Gündoğmuş İbradı Kaş Kemer Kepez Konyaaltı Korkuteli Kumluca Manavgat Muratpaşa Serik 30 ° C Web sitemizden ayrılıyorsunuz Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor. Sayfada Kal Devam Et Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. Vatandaşların hukuki süreçlerde en sık karşılaştığı ve kafa karışıklığı yaşadığı konuların başında, maaşın işveren tarafından bankaya yatırılmasından sonraki hukuki statüsü gelmektedir. Maaş kesintisi doğrudan işyeri üzerinden icra dairesi kanalıyla yapılırken, banka hesaplarına uygulanan e-haciz işlemleri Doğrudan banka blokajı olarak gerçekleşmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Bu durum, banka hesabında bloke bulunan vatandaşların işlem türünü doğru tespit etmesini zorunlu kılmaktadır. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. Uygulanan işlemin bir maaş haczi mi yoksa banka mevduat haczi mi olduğunun icra dosyasından doğrulanması gerekmektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Antalya Hakkında'nın sponsor olduğu yayıncılar Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor.</t>
+          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Yükleniyor... Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Sercan Yıldırım Editör 13.09.2026 - 17:06 Yayınlanma 13.09.2026 - 17:06 Güncelleme —</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Emekli Maaşlarına Ek Zam: Seyyanen Zam İçin Gözler Kritik Kararda! İçeriği Görüntüle Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Akseki Aksu Alanya Demre Döşemealtı Elmalı Finike Gazipaşa Gündoğmuş İbradı Kaş Kemer Kepez Konyaaltı Korkuteli Kumluca Manavgat Muratpaşa Serik 30 ° C Web sitemizden ayrılıyorsunuz Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor. Sayfada Kal Devam Et Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Antalya Hakkında'nın sponsor olduğu yayıncılar Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor.</t>
+          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı yeniadimgazetesi.com Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. Sercan Yıldırım Editör 13.09.2026 - 17:06 Yayınlanma 13.09.2026 - 17:06 Güncelleme —</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -6409,10 +6689,14 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://www.antalyahakkinda.com/maasiniz-hesaba-yatinca-bu-para-kesilecek-bankalardan-kritik-uygulama</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>https://www.yeniadimgazetesi.com/boludaki-fabrika-yangininda-yaklasik-4-saat-geride-kaldi-1-yarali</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
@@ -6421,7 +6705,7 @@
       <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr"/>
@@ -6435,7 +6719,7 @@
       <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr"/>
       <c r="AA42" s="2" t="n">
-        <v>79.25</v>
+        <v>92.16</v>
       </c>
       <c r="AB42" s="2" t="n">
         <v>41</v>
@@ -6444,27 +6728,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 06:39:00</t>
+          <t>2026-09-14 07:51:05</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>şüpheli işlem</t>
+          <t>mali suç</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -6474,18 +6758,18 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>şüpheli işlem</t>
+          <t>para transferi</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci Adalet Bakanı Gürlek: 15 ilde 'Ailem Güvende' operasyonunda 162 şüpheli işlem gördü Gerçek Haberci</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -6495,7 +6779,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOXzhXNnZwbnFrUHFHNnZac2ZnMmZoUXNLYnJnVkN5SlczZmZKeEQ4cEZNTEVhQjFrYUl5TF9YMDRyaWY4SkhFaWpTNlplWnJKZVFNOVJxcUxTdXRibVpqMnR5QjRyNWRxOVJaZ2Y1end0d3EyeVJtYksyOG00b2F1cVBPMmNTeVJMNjgtUG5aSGFYa3U3TUxVaVZsb0RJSUVVZTFxT2pCNDZETUxWTmktUHJoMERFdVBSNzNjV3ZDRG0yUdIBxwFBVV95cUxObmxnU2JUTWwyZ0I4Mm1oTEc2cDBaZGREUW5LcHMxVG0tOW13OGhjTm1KOTFBLWsxUm1TNEtnWmhOX0VpMHd0SkNJMjhaVzlka2tFeHBBRHlaeEQ1cDVUbE9RcVNoWlZpQWxzQlJBajFrWG1GZC01WDJvaDNLMWVDb0xSRTFRV0RocmJ1cldmWlhrQ3ZiZUpzZGoyQW9tNmpLOEtuWmpGOXNuMENUdG1iSjBqVWZnLUEwY3g4cXhIek43dDFkTlo4?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNVkNOMFRrcXVpWXRrTzRGc3UzVzRUX0FVYU9qRDB6RXZrUV94bl95QUF2Ykh3bGdia0FTMm1mdk1lbE9SVlEtTjlGRlp3SzY1VkpVLTZ0cHRFb1dQV2JNMnZwSndTTTQ1RWRTbjk5ZG1NeG9YWWxRTEZLRVgzQm5maENHSzhRUTVXTXVsamZCaFExZVpiT0E4TWpWTU56dzdwU2c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
@@ -6521,7 +6805,7 @@
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="n">
-        <v>82.98</v>
+        <v>59.8</v>
       </c>
       <c r="AB43" s="2" t="n">
         <v>42</v>
@@ -6530,27 +6814,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 04:52:14</t>
+          <t>2026-09-14 06:20:02</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>soruşturma</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı</t>
+          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı 10haber.net</t>
+          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -6560,22 +6844,18 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>holding</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>işletme</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini […] Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini […] Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini bu sarsıntıya bağladı. Ancak dün ortaya çıkan ve henüz bütün boyutları bilinmeyen bir gelişme, gerçeğin farklı olabileceğini ima ediyor. Cumartesi günü İstanbul Cumhuriyet Başsavcılığı’nın Tera tarafından devralınmak üzere olan, hatta devir görüşmelerinin tamamlandığı açıklanan Pusula Holding’in en azından bazı yöneticileri ve patronları hakkında soruşturma yürüttüğü ortaya çıktı. Buna göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, Pusula Holding’in bir parçası olan KatılımEvim yönetim kurulu üyesi Serdar Turhan ve tamamen ayrı bir şirket olan Destek Yatırım’ın hakim ortağı Altunç Kumova savcılık tarafından soruşturuluyor, hatta iddiaya göre bu isimler hakkında tedbir kararları alınmış durumda. Gazeteci İsmail Saymaz’ın sosyal medyadan yazdığına göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, cep telefonunu Türkiye’de bırakarak Marmaris’ten bir tekneyle Yunanistan’a geçti. Bu gelişme sonrası Katılımevim Yönetim Kurulu üyesi Serdar Turhan ve Destek Yatırım’ın sahibi Altunç Kumova için de yurt dışı çıkış yas ağı getirildi ve tedbir uygulandı. Savcılıktan henüz bir açıklama yapılmadığı için, Pusula ile ilgili bir soruşturma olup olmadığı, varsa bunun kapsamı ve konusu hakkında pek az bilgi var. Ancak cumartesi günü çıkan bu haberler üstüne gerek Tera Holding, gerekse Pusula Holding açıklamalar yaparak devralınma sürecinin bu soruşturmadan bağımsız olarak devam ettiğini bildirdiler. Günün 10 Haberi Yok artık daha neler… 11 aylık bebeklerini satmışlar, ‘Kayboldu’ demişler Şimşek vergi denetimini anlattı: ‘Büyük ve yüksek gelirli mükellefler mercek altında’ Özgür Özel’den seçim mesajı: ‘Butlancılar ve darbeciler otokratın safında’ Yapay zeka devleri birden insafa geldi: Evet, gelişme hızımızı yavaşlatmalıyız “Kıyamet” ne kadar yakın? Dünyanın sonunu yapay zeka mı siyaset mi getirecek? Kahve erkeklerde testosteronu arttırıyormuş Bermuda Şeytan Üçgeni’nin büyük gizemi: Batık şehir izine rastlandı Nurgül Yeşilçay: Şehirde gençler yaşasın, biz değil Trabzonspor’da Burak Yılmaz iddiası: Galatasaray derbisinde takımın başında olabilir İspanya, üç yazıyla Arda Güler’i göklere çıkardı: ‘Mourinho’ya kendisini 15 dakikada hatırlattı’ Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini bu sarsıntıya bağladı. Ancak dün ortaya çıkan ve henüz bütün boyutları bilinmeyen bir gelişme, gerçeğin farklı olabileceğini ima ediyor. Cumartesi günü İstanbul Cumhuriyet Başsavcılığı’nın Tera tarafından devralınmak üzere olan, hatta devir görüşmelerinin tamamlandığı açıklanan Pusula Holding’in en azından bazı yöneticileri ve patronları hakkında soruşturma yürüttüğü ortaya çıktı. Buna göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, Pusula Holding’in bir parçası olan KatılımEvim yönetim kurulu üyesi Serdar Turhan ve tamamen ayrı bir şirket olan Destek Yatırım’ın hakim ortağı Altunç Kumova savcılık tarafından soruşturuluyor, hatta iddiaya göre bu isimler hakkında tedbir kararları alınmış durumda. Gazeteci İsmail Saymaz’ın sosyal medyadan yazdığına göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, cep telefonunu Türkiye’de bırakarak Marmaris’ten bir tekneyle Yunanistan’a geçti. Bu gelişme sonrası Katılımevim Yönetim Kurulu üyesi Serdar Turhan ve Destek Yatırım’ın sahibi Altunç Kumova için de yurt dışı çıkış yas ağı getirildi ve tedbir uygulandı. Savcılıktan henüz bir açıklama yapılmadığı için, Pusula ile ilgili bir soruşturma olup olmadığı, varsa bunun kapsamı ve konusu hakkında pek az bilgi var. Ancak cumartesi günü çıkan bu haberler üstüne gerek Tera Holding, gerekse Pusula Holding açıklamalar yaparak devralınma sürecinin bu soruşturmadan bağımsız olarak devam ettiğini bildirdiler. Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı İstanbul’da Cumhuriyet Savcılığı’nın Pusula Holding ve ona bağlı şirketler için soruşturma yürüttüğü, holdinge bağlı bazı şirketlerin patronlarının yurt dışına kaçtığı ortaya çıktı. Tam da bugünlerde Terra Holding, Pusula’yı satın almak için görüşmeleri tamamlamıştı. 10Haber bültenine üye olun, gündem özeti her sabah mailinize gelsin. Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini bu sarsıntıya bağladı. Ancak dün ortaya çıkan ve henüz bütün boyutları bilinmeyen bir gelişme, gerçeğin farklı olabileceğini ima ediyor. Cumartesi günü İstanbul Cumhuriyet Başsavcılığı’nın Tera tarafından devralınmak üzere olan, hatta devir görüşmelerinin tamamlandığı açıklanan Pusula Holding’in en azından bazı yöneticileri ve patronları hakkında soruşturma yürüttüğü ortaya çıktı. Buna göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, Pusula Holding’in bir parçası olan KatılımEvim yönetim kurulu üyesi Serdar Turhan ve tamamen ayrı bir şirket olan Destek Yatırım’ın hakim ortağı Altunç Kumova savcılık tarafından soruşturuluyor, hatta iddiaya göre bu isimler hakkında tedbir kararları alınmış durumda. Gazeteci İsmail Saymaz’ın sosyal medyadan yazdığına göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, cep telefonunu Türkiye’de bırakarak Marmaris’ten bir tekneyle Yunanistan’a geçti. Bu gelişme sonrası Katılımevim Yönetim Kurulu üyesi Serdar Turhan ve Destek Yatırım’ın sahibi Altunç Kumova için de yurt dışı çıkış yas ağı getirildi ve tedbir uygulandı. Savcılıktan henüz bir açıklama yapılmadığı için, Pusula ile ilgili bir soruşturma olup olmadığı, varsa bunun kapsamı ve konusu hakkında pek az bilgi var. Ancak cumartesi günü çıkan bu haberler üstüne gerek Tera Holding, gerekse Pusula Holding açıklamalar yaparak devralınma sürecinin bu soruşturmadan bağımsız olarak devam ettiğini bildirdiler.</t>
+          <t>... Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işlet Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işlet ASAYİŞ - 14 Eylül 2026 Pazartesi 09:20 Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu A A A Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işletmesinde saat 03.30 sıralarında meydana geldi. İşletmeden yükselen alev ve dumanları görenlerin ihbarı üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. 17 itfaiye aracıyla müdahale Yangına Bursa Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekiplerin yanı sıra farklı birimlerden de destek gönderildi. Söndürme çalışmalarında 17 itfaiye aracı ve 1 insansız hava aracı (dron) ekibi görev aldı. Ayrıca Park ve Bahçeler Şube Müdürlüğü/Tarım AŞ’ye ait 3 su tankeri, Yol Bakım ve Onarım Şube Müdürlüğü’ne ait 1 su tankeri ile Nilüfer Belediyesi’ne ait 1 kepçe çalışmalara destek verdi. Çok sayıda ekibin müdahale etmesiyle yangın çok geçmeden kontrol altına alındı. Soğutma çalışmaları devam ederken, olayla ilgili tahkikat başlatıldı. Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işletmesinde saat 03.30 sıralarında meydana geldi. İşletmeden yükselen alev ve dumanları görenlerin ihbarı üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. 17 itfaiye aracıyla müdahale Yangına Bursa Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekiplerin yanı sıra farklı birimlerden de destek gönderildi. Söndürme çalışmalarında 17 itfaiye aracı ve 1 insansız hava aracı (dron) ekibi görev aldı. Ayrıca Park ve Bahçeler Şube Müdürlüğü/Tarım AŞ’ye ait 3 su tankeri, Yol Bakım ve Onarım Şube Müdürlüğü’ne ait 1 su tankeri ile Nilüfer Belediyesi’ne ait 1 kepçe çalışmalara destek verdi. Çok sayıda ekibin müdahale etmesiyle yangın çok geçmeden kontrol altına alındı. Soğutma çalışmaları devam ederken, olayla ilgili tahkikat başlatıldı. Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işletmesinde saat 03.30 sıralarında meydana geldi. İşletmeden yükselen alev ve dumanları görenlerin ihbarı üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. 17 itfaiye aracıyla müdahale Yangına Bursa Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekiplerin yanı sıra farklı birimlerden de destek gönderildi. Söndürme çalışmalarında 17 itfaiye aracı ve 1 insansız hava aracı (dron) ekibi görev aldı. Ayrıca Park ve Bahçeler Şube Müdürlüğü/Tarım AŞ’ye ait 3 su tankeri, Yol Bakım ve Onarım Şube Müdürlüğü’ne ait 1 su tankeri ile Nilüfer Belediyesi’ne ait 1 kepçe çalışmalara destek verdi. Çok sayıda ekibin müdahale etmesiyle yangın çok geçmeden kontrol altına alındı. Soğutma çalışmaları devam ederken, olayla ilgili tahkikat başlatıldı.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>» Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı » Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı 10haber.net Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini […] Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Herkes, fon piyasasının en büyük oyuncularından olan ama fonlar dışında pek çok başka alanda da şirketleri bulunan Tera Holding’in aynı piyasanın bir başka oyuncusu olan Pusula Holding’i devralma girişimini bu sarsıntıya bağladı. Ancak dün ortaya çıkan ve henüz bütün boyutları bilinmeyen bir gelişme, gerçeğin farklı olabileceğini ima ediyor. Cumartesi günü İstanbul Cumhuriyet Başsavcılığı’nın Tera tarafından devralınmak üzere olan, hatta devir görüşmelerinin tamamlandığı açıklanan Pusula Holding’in en azından bazı yöneticileri ve patronları hakkında soruşturma yürüttüğü ortaya çıktı. Buna göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, Pusula Holding’in bir parçası olan KatılımEvim yönetim kurulu üyesi Serdar Turhan ve tamamen ayrı bir şirket olan Destek Yatırım’ın hakim ortağı Altunç Kumova savcılık tarafından soruşturuluyor, hatta iddiaya göre bu isimler hakkında tedbir kararları alınmış durumda. Gazeteci İsmail Saymaz’ın sosyal medyadan yazdığına göre Pusula Portföy Yönetim Kurulu Başkanı Muhammed Yarız, cep telefonunu Türkiye’de bırakarak Marmaris’ten bir tekneyle Yunanistan’a geçti. Bu gelişme sonrası Katılımevim Yönetim Kurulu üyesi Serdar Turhan ve Destek Yatırım’ın sahibi Altunç Kumova için de yurt dışı çıkış yas ağı getirildi ve tedbir uygulandı. Savcılıktan henüz bir açıklama yapılmadığı için, Pusula ile ilgili bir soruşturma olup olmadığı, varsa bunun kapsamı ve konusu hakkında pek az bilgi var. Ancak cumartesi günü çıkan bu haberler üstüne gerek Tera Holding, gerekse Pusula Holding açıklamalar yaparak devralınma sürecinin bu soruşturmadan bağımsız olarak devam ettiğini bildirdiler. Günün 10 Haberi Yok artık daha neler… 11 aylık bebeklerini satmışlar, ‘Kayboldu’ demişler Şimşek vergi denetimini anlattı: ‘Büyük ve yüksek gelirli mükellefler mercek altında’ Özgür Özel’den seçim mesajı: ‘Butlancılar ve darbeciler otokratın safında’ Yapay zeka devleri birden insafa geldi: Evet, gelişme hızımızı yavaşlatmalıyız “Kıyamet” ne kadar yakın? Dünyanın sonunu yapay zeka mı siyaset mi getirecek? Kahve erkeklerde testosteronu arttırıyormuş Bermuda Şeytan Üçgeni’nin büyük gizemi: Batık şehir izine rastlandı Nurgül Yeşilçay: Şehirde gençler yaşasın, biz değil Trabzonspor’da Burak Yılmaz iddiası: Galatasaray derbisinde takımın başında olabilir İspanya, üç yazıyla Arda Güler’i göklere çıkardı: ‘Mourinho’ya kendisini 15 dakikada hatırlattı’ Sermaye Piyasası Kurulu’nun kısa süre önce yatırım fonlarıyla ilgili yaptığı köklü düzenleme, İstanbul Borsasında bir süredir devasa boyutlara gelen bu fon piyasasında bazı sarsıntılara neden oldu. Piyasa fena karıştı: Tam Tera Grubu Pusula’yı alıyordu, savcılık Pusula Holding’e soruşturma başlattı, patronları kaçtı İstanbul’da Cumhuriyet Savcılığı’nın Pusula Holding ve ona bağlı şirketler için soruşturma yürüttüğü, holdinge bağlı bazı şirketlerin patronlarının yurt dışına kaçtığı ortaya çıktı. Tam da bugünlerde Terra Holding, Pusula’yı satın almak için görüşmeleri tamamlamıştı.</t>
+          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı İhlas Haber Ajansı Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işlet Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işlet ASAYİŞ - 14 Eylül 2026 Pazartesi 09:20 Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu A A A Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işletmesinde saat 03.30 sıralarında meydana geldi. İşletmeden yükselen alev ve dumanları görenlerin ihbarı üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. 17 itfaiye aracıyla müdahale Yangına Bursa Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekiplerin yanı sıra farklı birimlerden de destek gönderildi. Söndürme çalışmalarında 17 itfaiye aracı ve 1 insansız hava aracı (dron) ekibi görev aldı. Ayrıca Park ve Bahçeler Şube Müdürlüğü/Tarım AŞ’ye ait 3 su tankeri, Yol Bakım ve Onarım Şube Müdürlüğü’ne ait 1 su tankeri ile Nilüfer Belediyesi’ne ait 1 kepçe çalışmalara destek verdi. Çok sayıda ekibin müdahale etmesiyle yangın çok geçmeden kontrol altına alındı. Soğutma çalışmaları devam ederken, olayla ilgili tahkikat başlatıldı. Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -6585,17 +6865,17 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://10haber.net/ekonomi/piyasa-fena-karisti-tam-tera-grubu-pusulayi-aliyordu-savcilik-pusula-holdinge-sorusturma-baslatti-patronlari-kacti-736955/</t>
+          <t>https://www.iha.com.tr/bursa-haberleri/komur-isletmesinde-gece-yarisi-yangin-panigi-ekipler-seferber-oldu-485164420</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>İstanbul | Muğla</t>
+          <t>Bursa</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Marmaris</t>
+          <t>Nilüfer</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
@@ -6603,12 +6883,12 @@
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>Pusula Holding</t>
+          <t>Tarım AŞ</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Pusula Holding:292:body+summary+title</t>
+          <t>Tarım AŞ:63:body | Tarım AŞ:raw_legal</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -6618,17 +6898,17 @@
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>Pusula Holding Marmaris İstanbul Türkiye</t>
+          <t>Tarım AŞ Nilüfer Bursa Türkiye</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Pusula Yatırım Menkul Değerler A.Ş | Pusula Portföy Yönetimi A.Ş | Pusula Uluslararası Ticaret A.Ş | Pusula Enerji | Pusula</t>
+          <t>TARIM PEYZAJ A.Ş. Bursa Tarım Hayvancılık Peyzaj Çevre İnş. San. Tic. A.Ş</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>Pusula Yatırım Menkul Değerler A.Ş</t>
+          <t>TARIM PEYZAJ A.Ş. Bursa Tarım Hayvancılık Peyzaj Çevre İnş. San. Tic. A.Ş</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
@@ -6638,12 +6918,12 @@
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>100 | 100 | 100 | 100 | 100.0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" s="2" t="n">
-        <v>258.75</v>
+        <v>206.85</v>
       </c>
       <c r="AB44" s="2" t="n">
         <v>43</v>
@@ -6652,7 +6932,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:33:00</t>
+          <t>2026-09-14 09:20:28</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -6667,12 +6947,12 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Sanayideki Yangın Büyümeden Söndürüldü</t>
+          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV</t>
+          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı aksiyon.com.tr</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6682,18 +6962,22 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>sanayi</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr"/>
+          <t>depo</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>depo</t>
+        </is>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. +1 Haber albümü için resme tıklayın Bugün öğleden sonra Konacık Sanayi Sitesi'ndeki otluk alanda yangın başladı. Alevleri fark eden sanayi esnafı, hortum ve yangın tüpleriyle alevlere müdahale etti. İhbarın ardından Bodrum İtfaiye Grup Amirliği ekipleri de olay yerine geldi. Vatandaşlar ve ekiplerin müdahalesiyle yangın büyümeden söndürüldü. Yangının otluk alana atılan sigara izmaritinden çıktığı sanılıyor. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 - Asayiş Sanayideki Yangın Büyümeden Söndürüldü Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. +1 Haber albümü için resme tıklayın Bugün öğleden sonra Konacık Sanayi Sitesi'ndeki otluk alanda yangın başladı. Alevleri fark eden sanayi esnafı, hortum ve yangın tüpleriyle alevlere müdahale etti. İhbarın ardından Bodrum İtfaiye Grup Amirliği ekipleri de olay yerine geldi. Vatandaşlar ve ekiplerin müdahalesiyle yangın büyümeden söndürüldü. Yangının otluk alana atılan sigara izmaritinden çıktığı sanılıyor. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 Muğla / Bodrum - Asayiş Yazdır GİRİŞ YAP Yorum yazarak Bodrum Kent Tv Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yoruml</t>
+          <t>Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Olayın gelişimi: Mardin'in Kızıltepe ilçesinde, Atatürk Mahallesi yakınlarında hurda araçların bulunduğu bir alanda yangın çıktı. Yangının henüz belirlenemeyen nedenle başladığı bildirildi. Bölgedeki vatandaşların durumu fark ederek ihbarda bulunmasının ardından yetkililer alarma geçti. Müdahale ve söndürme çalışmaları: İhbar üzerine bölgeye sevk edilen itfaiye ekipleri kısa sürede olay yerine ulaşarak müdahaleye başladı. Ekiplerin çalışmasıyla yangın kısa sürede kontrol altına alınarak söndürüldü. Çevrede ek güvenlik önlemleri alındı ve yangının yayılmasının önüne geçildi. Hasar ve soruşturma: Yangında hurda araçlarda maddi hasar meydana geldi. Olayla ilgili olarak yetkililer tarafından inceleme başlatıldı; yangının çıkış nedeni ile hasarın boyutuna ilişkin tespit çalışmalarının sürdüğü bildirildi. MARDİN'İN KIZILTEPE İLÇESİNDE HURDA ARAÇLARIN BULUNDUĞU ALANDA ÇIKAN YANGIN İTFAİYE EKİPLERİNİN MÜDAHALESİYLE SÖNDÜRÜLDÜ. 1 Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı 2 Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada 3 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 4 Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı 5 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 6 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 7 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Mardin'de hurda araç deposunda yangın kontrol altına alındı Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Mardin'in Kızıltepe ilçesinde, Atatürk Mahallesi yakınlarında hurda araçların bulunduğu bir alanda yangın çıktı. Yangının henüz belirlenemeyen nedenle başladığı bildirildi. Bölgedeki vatandaşların durumu fark ederek ihbarda bulunmasının ardından yetkililer alarma geçti. İhbar üzerine bölgeye sevk edilen itfaiye ekipleri kısa sürede olay yerine ulaşarak müdahaleye başladı. Ekiplerin çalışmasıyla yangın kısa sürede kontrol altına alınarak söndürüldü. Çevrede ek güvenlik önlemleri alındı ve yangının yayılmasının önüne geçildi. Yangında hurda araçlarda maddi hasar meydana geldi. Olayla ilgili olarak yetkililer tarafından inceleme başlatıldı; yangının çıkış nedeni ile hasarın boyutuna ilişkin tespit çalışmalarının sürdüğü bildirildi. MARDİN'İN KIZILTEPE İLÇESİNDE HURDA ARAÇLARIN BULUNDUĞU ALANDA ÇIKAN YANGIN İTFAİYE EKİPLERİNİN MÜDAHALESİYLE SÖNDÜRÜLDÜ. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. aksiyon.com.tr Gündem'deyim ama spesifik olarak eğitim ve sağlık politikalarındaki güncel gelişmelere odaklanıyorum. Öğrenmeye açık, meraklı ve enerjik bir yapım var. Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Sanayideki Yangın Büyümeden Söndürüldü Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. +1 Haber albümü için resme tıklayın Bugün öğleden sonra Konacık Sanayi Sitesi'ndeki otluk alanda yangın başladı. Alevleri fark eden sanayi esnafı, hortum ve yangın tüpleriyle alevlere müdahale etti. İhbarın ardından Bodrum İtfaiye Grup Amirliği ekipleri de olay yerine geldi. Vatandaşlar ve ekiplerin müdahalesiyle yangın büyümeden söndürüldü. Yangının otluk alana atılan sigara izmaritinden çıktığı sanılıyor. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 - Asayiş Sanayideki Yangın Büyümeden Söndürüldü Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 Muğla / Bodrum - Asayiş Yazdır GİRİŞ YAP Yorum yazarak Bodrum Kent Tv Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
+          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı Mardin'de hurda araç deposunda yangın kontrol altına alındı aksiyon.com.tr Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Olayın gelişimi: Mardin'in Kızıltepe ilçesinde, Atatürk Mahallesi yakınlarında hurda araçların bulunduğu bir alanda yangın çıktı. Yangının henüz belirlenemeyen nedenle başladığı bildirildi. Bölgedeki vatandaşların durumu fark ederek ihbarda bulunmasının ardından yetkililer alarma geçti. Müdahale ve söndürme çalışmaları: İhbar üzerine bölgeye sevk edilen itfaiye ekipleri kısa sürede olay yerine ulaşarak müdahaleye başladı. Ekiplerin çalışmasıyla yangın kısa sürede kontrol altına alınarak söndürüldü. Çevrede ek güvenlik önlemleri alındı ve yangının yayılmasının önüne geçildi. Hasar ve soruşturma: Yangında hurda araçlarda maddi hasar meydana geldi. Olayla ilgili olarak yetkililer tarafından inceleme başlatıldı; yangının çıkış nedeni ile hasarın boyutuna ilişkin tespit çalışmalarının sürdüğü bildirildi. MARDİN'İN KIZILTEPE İLÇESİNDE HURDA ARAÇLARIN BULUNDUĞU ALANDA ÇIKAN YANGIN İTFAİYE EKİPLERİNİN MÜDAHALESİYLE SÖNDÜRÜLDÜ. 1 Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı 2 Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada 3 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 4 Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı 5 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 6 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 7 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Mardin'de hurda araç deposunda yangın kontrol altına alındı Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Mardin'in Kızıltepe ilçesinde, Atatürk Mahallesi yakınlarında hurda araçların bulunduğu bir alanda yangın çıktı. İhbar üzerine bölgeye sevk edilen itfaiye ekipleri kısa sürede olay yerine ulaşarak müdahaleye başladı. Yangında hurda araçlarda maddi hasar meydana geldi. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -6703,22 +6987,22 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://kenttv.net/haber/28692971/sanayideki-yangin-buyumeden-sonduruldu</t>
+          <t>https://www.aksiyon.com.tr/mardin-de-hurda-arac-deposunda-yangin-kontrol-altina-alindi-354264</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Muğla</t>
+          <t>Adana | Bilecik | Bursa | Düzce | Iğdır</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bodrum</t>
+          <t>Köşk | Mudurnu | Kızıltepe</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>da sanayi sitesi</t>
+          <t>Atatürk Mahallesi</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr"/>
@@ -6741,7 +7025,7 @@
       <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="n">
-        <v>105.25</v>
+        <v>121</v>
       </c>
       <c r="AB45" s="2" t="n">
         <v>44</v>
@@ -6750,27 +7034,27 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:50:46</t>
+          <t>2026-09-13 22:01:00</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>soruşturma</t>
+          <t>bankaya soruşturma</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor</t>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -6780,85 +7064,453 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>ticaret</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+          <t>İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor. İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor. İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor.</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPczREcWt4bVUtWHhXU0d2Qzh0cklpYTJpbDR1RkdPQ05kOGNfUWRvT1gzNHE3NFY2V1R3a0RyeHFsbER3bXBMRkJCd2NoLUVHNjNTV1VLcGlzZHJxcEVOcV9uVzlfNmwycTdIVnY1STE4blpLcXVKUzR4elVIUnRkWmxKbjhVdXFCcXBDb3c2Y1VJUnVXSkRPNmlYRDEwZlp6a040aEVnLUQxc082WWVES2FQVGpUTF9Ca3N4UjQ5SGxZcDdmRnZFOGlR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>https://www.toplumsal.com.tr/haber/izmir-deki-banka-subesinde-rehin-alan-supheli-teslim-oldu_25400/</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
       <c r="Q46" s="2" t="inlineStr"/>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret:161:body+summary</t>
-        </is>
-      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret Türkiye</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret Üniversitesi | İstanbul Ticaret Merkezi | İstanbul Ticaret İş Güvenliği ve Endüstriyel Ürünler San. A.Ş | İstanbul Ticaret Üniversitesi Küçükyalı Kampüsü | İstanbul Ticaret Borsası</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret Üniversitesi</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t>100.0 | 100.0 | 100.0 | 100.0 | 100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr"/>
       <c r="AA46" s="2" t="n">
-        <v>200.96</v>
+        <v>60.14</v>
       </c>
       <c r="AB46" s="2" t="n">
         <v>45</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 08:43:00</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>banka hesapları bloke</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Diğer</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>el konuldu</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Güncel İran'da çok sayıda kişinin mal varlıklarına el konuldu İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Mehmet TÜRK 14.09.2026 - 11:43 Okunma Süresi: 1 Dk Türkşeker 182 işçi alımı başvuruları başladı: İŞKUR başvuru şartları neler, son başvuru tarihi ne zaman? İçeriği Görüntüle İran Yargı Erki, el konulan mülkler, bloke edilen banka hesaplarına dair raporunu açıkladı. Mizan Haber Ajansı’nda yer alan habere göre, aralarında gazetecilerin, aktivistlerin, akademisyenlerin olduğu yüzlerce kişinin mal varlıklarına ve banka hesaplarına el konul konuldu. El konulan mal varlıklarının 143’ü Tahran’da bulunuyor. Habere göre, 182 kişinin banka hesapları bloke edildi, 2 binden fazla kişinin ise banka hesapları için incelemeler devam ediyor. Haberde, el konulan varlıkların İran halkı için kullanılacağı iddia edildi. Kaynak: MA Editörün Seçtiği Diyarbakır’da okullar açıldı, yol çalışması trafiği vurdu! Editörün Seçtiği Daha 17 17. bölüm fragmanı yayınlandı mı, ne zaman yayınlanacak? Aras ve Teoman arasında yeni dönem! Editörün Seçtiği Dayik Qurban, Gift Orban Editör Hakkında Mehmet TÜRK Bunlar da</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Güncel İran'da çok sayıda kişinin mal varlıklarına el konuldu İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.guneydoguekspres.com/iranda-cok-sayida-kisinin-mal-varliklarina-el-konuldu</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="AB47" s="2" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 10:52:00</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>banka hesaplarına bloke</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama!</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Yükleniyor... Emekli Maaşlarına Ek Zam: Seyyanen Zam İçin Gözler Kritik Kararda! İçeriği Görüntüle Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Vatandaşların hukuki süreçlerde en sık karşılaştığı ve kafa karışıklığı yaşadığı konuların başında, maaşın işveren tarafından bankaya yatırılmasından sonraki hukuki statüsü gelmektedir. Maaş kesintisi doğrudan işyeri üzerinden icra dairesi kanalıyla yapılırken, banka hesaplarına uygulanan e-haciz işlemleri Doğrudan banka blokajı olarak gerçekleşmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Bu durum, banka hesabında bloke bulunan vatandaşların işlem türünü doğru tespit etmesini zorunlu kılmaktadır. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. Uygulanan işlemin bir maaş haczi mi yoksa banka mevduat haczi mi olduğunun icra dosyasından doğrulanması gerekmektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Akseki Aksu Alanya Demre Döşemealtı Elmalı Finike Gazipaşa Gündoğmuş İbradı Kaş Kemer Kepez Konyaaltı Korkuteli Kumluca Manavgat Muratpaşa Serik 30 ° C Web sitemizden ayrılıyorsunuz Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor. Sayfada Kal Devam Et Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. Vatandaşların hukuki süreçlerde en sık karşılaştığı ve kafa karışıklığı yaşadığı konuların başında, maaşın işveren tarafından bankaya yatırılmasından sonraki hukuki statüsü gelmektedir. Maaş kesintisi doğrudan işyeri üzerinden icra dairesi kanalıyla yapılırken, banka hesaplarına uygulanan e-haciz işlemleri Doğrudan banka blokajı olarak gerçekleşmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Bu durum, banka hesabında bloke bulunan vatandaşların işlem türünü doğru tespit etmesini zorunlu kılmaktadır. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. Uygulanan işlemin bir maaş haczi mi yoksa banka mevduat haczi mi olduğunun icra dosyasından doğrulanması gerekmektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Antalya Hakkında'nın sponsor olduğu yayıncılar Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor.</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Emekli Maaşlarına Ek Zam: Seyyanen Zam İçin Gözler Kritik Kararda! İçeriği Görüntüle Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Akseki Aksu Alanya Demre Döşemealtı Elmalı Finike Gazipaşa Gündoğmuş İbradı Kaş Kemer Kepez Konyaaltı Korkuteli Kumluca Manavgat Muratpaşa Serik 30 ° C Web sitemizden ayrılıyorsunuz Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor. Sayfada Kal Devam Et Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Antalya Hakkında'nın sponsor olduğu yayıncılar Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.antalyahakkinda.com/maasiniz-hesaba-yatinca-bu-para-kesilecek-bankalardan-kritik-uygulama</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="AB48" s="2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:23:00</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>banka soruşturma</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası Samsun Gazetesi</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Pusula Finans Holding ve Katılımevim'in de gündemde olduğu soruşturmada bazı isimler hakkında yakalama ve yurt dışı yasağı iddiaları gündeme geldi. Pusula Finans Holding ve Katılımevim'in de gündemde olduğu soruşturmada bazı isimler hakkında yakalama ve yurt dışı yasağı iddiaları gündeme geldi. Pusula Finans Holding ve Katılımevim'in de gündemde olduğu soruşturmada bazı isimler hakkında yakalama ve yurt dışı yasağı iddiaları gündeme geldi. Dev finans şirketinde soruşturma: Yakalama kararı iddiası Pusula Finans Holding ve Katılımevim'in de adının geçtiği soruşturmayla ilgili yeni iddialar gündeme geldi. Pusula Portföy Yönetim Kurulu Başkanı Muhammet Yarız'ın yurt dışına çıktığı ve hakkında yakalama kararı verildiği öne sürülürken, bazı isimler hakkında da yurt dışına çıkış yasağı uygulandığı iddia edildi. Yunus Emre Purç Editör 13.09.2026 - 16:23 Yayınlanma 0 Paylaşım 2 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Yükleniyor... Finans sektöründe Pusula Finans Holding ve bünyesindeki şirketleri ilgilendiren gelişmeler gündemdeki yerini koruyor. Pusula Finans Holding'in, portföyünde Katılımevim'in çoğunluk hisselerini bulundurduğu ve Tera Grubu'na devri konusunda tarafların anlaşmaya vardığı açıklanmıştı. Devir işleminin tamamlanabilmesi için Sermaye Piyasası Kurulu (SPK), Bankacılık Düzenleme ve Denetleme Kurumu (BDDK) ve Rekabet Kurulu başta olmak üzere gerekli izinlerin alınması beklenirken, soruşturmayla ilgili yeni iddialar ortaya atıldı. MUHAMMET YARIZ'IN YURT DIŞINA ÇIKTIĞI ÖNE SÜRÜLDÜ Soruşturma kapsamında adı geçen Pusula Portföy Yönetim Kurulu Başkanı Muhammet Yarız'ın yurt dışına çıktığı iddia edildi. Yarız'ın cep telefonunu ofisinde bırakarak Marmaris'ten tekneyle yurt dışına gittiği ve Yunanistan'da bulunduğu öne sürüldü. Gazeteci İsmail Saymaz da konuya ilişkin benzer iddiaları gündeme getirdi. Faizsiz 100 bin TL kredi fırsatı: Bankalar tek tek açıkladı İçeriği Görüntüle YARIZ HAKKINDA YAKALAMA KARARI İDDİASI Soruşturmayla ilgili ortaya atılan bir diğer iddia ise Muhammet Yarız hakkında yakalama kararı çıkarıldığı yönünde oldu. İstanbul Cumhuriyet Başsavcılığı tarafından Yarız hakkında yakalama kararı verildiği, ayrıca mal varlığı ve banka hesaplarına tedbir konulduğu öne sürüldü. SERDAR TURHAN İÇİN DE YURT DIŞI YASAĞI İDDİASI Soruşturmada adı geçen isimlerden birinin de Katılımevim Yönetim Kurulu Başkanı Serdar Turhan olduğu ileri sürüldü. Turhan hakkında yurt dışına çıkış yasağı kararı verildiği iddia edilirken, yurt dışında bulunan mal varlığına ilişkin çeşitli bilgilerin de soruşturma kapsamında gündeme geldiği öne sürüldü. ALTUNÇ KUMOVA HAKKINDA DA KARAR İDDİASI Soruşturma kapsamında hakkında tedbir uygulandığı öne sürülen bir diğer isim ise Destek Yatırım'ın hakim ortağı ve Yönetim Kurulu Başkanı Altunç Kumova oldu. Kumova hakkında da yurt dışına çıkış yasağı kararı verildiği iddia edildi. GÖZLER PUSULA'NIN TERA'YA DEVRİNDE Yaşanan gelişmelerin ardından Pusula Finans Holding'in Tera Grubu'na devrinin nasıl ilerleyeceği merak konusu oldu. Tera tarafından yapılan açıklamada, kamuoyuna yansıyan gelişmelerin Pusula Finans Holding ve bünyesindeki şirketlerin tüzel kişiliklerinden, faaliyetlerinden ve kurumsal yapılarından bağımsız olduğu belirtildi. Şirket, daha önce duyurulan anlaşma doğrultusunda devralma sürecinin devam ettiğini bildirdi. DEVİR İÇİN GEREKLİ ONAYLAR BEKLENİYOR Pusula Finans Holding'in Tera Grubu'na devrinin tamamlanması için ilgili düzenleyici kurumların gerekli izin ve onaylarının alınması gerekiyor. Tera, söz konusu gelişmelere rağmen finans sektöründeki faaliyetlerini genişletmeye yönelik uzun vadeli stratejisinde değişiklik bulunmadığını açıkladı. KATILIMEVİM HİSSELERİ DE GÜNDEMDE Pusula Finans Holding ile ilgili gelişmeler, holdingin bünyesinde bulunan ve Borsa İstanbul'da KTLEV koduyla işlem gören Katılımevim açısından da yakından takip ediliyor. Katılımevim hisselerinde daha önce yaşanan hareketlilik de dikkat çekmişti. Satış anlaşmasının açıklanmasının ardından hisselerde üst üste yükselişler görülmüştü. İDDİALARIN ODAĞINDAKİ ŞİRKET: KATILIMEVİM Katılımevim, tasarruf finansman sektöründe faaliyet gösteriyor. Şirket; konut, araç ve çatılı iş yeri edinmek isteyen müşterilere tasarruf finansman modeli kapsamında hizmet sunuyor. Pusula Finans Holding'in Katılımevim'deki çoğunluk hisseleriyle bağlantısı nedeniyle holding hakkında yaşanan gelişmelerin şirket açısından da önem taşıdığı belirtiliyor. Not: Haberde yer alan yurt dışına kaçış, yakalama kararı ve yurt dışı çıkış yasağına ilişkin bilgiler, kaynakta yer alan iddialara dayanmaktadır. Kaynak: HABERLER Yükleniyor... Editörün Seçtiği Geri ödeme olmadan 5 bin lira veriliyor! Editörün Seçtiği Taraftarın Sesi Kanal S ekranlarında sizlerle 22 Ocak Pazartesi Editörün Seçtiği Samsun'da FETÖ'cü akrabası başını yaktı! Karar belli oldu Editör Hakkında Yunus Emre Purç Bunlar da ilginizi çekebil</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası Dev finans şirketinde soruşturma: Yakalama kararı iddiası Samsun Gazetesi Pusula Finans Holding ve Katılımevim'in de gündemde olduğu soruşturmada bazı isimler hakkında yakalama ve yurt dışı yasağı iddiaları gündeme geldi. Dev finans şirketinde soruşturma: Yakalama kararı iddiası Pusula Finans Holding ve Katılımevim'in de adının geçtiği soruşturmayla ilgili yeni iddialar gündeme geldi. Pusula Portföy Yönetim Kurulu Başkanı Muhammet Yarız'ın yurt dışına çıktığı ve hakkında yakalama kararı verildiği öne sürülürken, bazı isimler hakkında da yurt dışına çıkış yasağı uygulandığı iddia edildi. Finans sektöründe Pusula Finans Holding ve bünyesindeki şirketleri ilgilendiren gelişmeler gündemdeki yerini koruyor. Pusula Finans Holding'in, portföyünde Katılımevim'in çoğunluk hisselerini bulundurduğu ve Tera Grubu'na devri konusunda tarafların anlaşmaya vardığı açıklanmıştı. Devir işleminin tamamlanabilmesi için Sermaye Piyasası Kurulu (SPK), Bankacılık Düzenleme ve Denetleme Kurumu (BDDK) ve Rekabet Kurulu başta olmak üzere gerekli izinlerin alınması beklenirken, soruşturmayla ilgili yeni iddialar ortaya atıldı. MUHAMMET YARIZ'IN YURT DIŞINA ÇIKTIĞI ÖNE SÜRÜLDÜ Soruşturma kapsamında adı geçen Pusula Portföy Yönetim Kurulu Başkanı Muhammet Yarız'ın yurt dışına çıktığı iddia edildi. Yarız'ın cep telefonunu ofisinde bırakarak Marmaris'ten tekneyle yurt dışına gittiği ve Yunanistan'da bulunduğu öne sürüldü. Faizsiz 100 bin TL kredi fırsatı: Bankalar tek tek açıkladı İçeriği Görüntüle YARIZ HAKKINDA YAKALAMA KARARI İDDİASI Soruşturmayla ilgili ortaya atılan bir diğer iddia ise Muhammet Yarız hakkında yakalama kararı çıkarıldığı yönünde oldu. İstanbul Cumhuriyet Başsavcılığı tarafından Yarız hakkında yakalama kararı verildiği, ayrıca mal varlığı ve banka hesaplarına tedbir konulduğu öne sürüldü. SERDAR TURHAN İÇİN DE YURT DIŞI YASAĞI İDDİASI Soruşturmada adı geçen isimlerden birinin de Katılımevim Yönetim Kurulu Başkanı Serdar Turhan olduğu ileri sürüldü. Turhan hakkında yurt dışına çıkış yasağı kararı verildiği iddia edilirken, yurt dışında bulunan mal varlığına ilişkin çeşitli bilgilerin de soruşturma kapsamında gündeme geldiği öne sürüldü. ALTUNÇ KUMOVA HAKKINDA DA KARAR İDDİASI Soruşturma kapsamında hakkında tedbir uygulandığı öne sürülen bir diğer isim ise Destek Yatırım'ın hakim ortağı ve Yönetim Kurulu Başkanı Altunç Kumova oldu. Kumova hakkında da yurt dışına çıkış yasağı kararı verildiği iddia edildi. GÖZLER PUSULA'NIN TERA'YA DEVRİNDE Yaşanan gelişmelerin ardından Pusula Finans Holding'in Tera Grubu'na devrinin nasıl ilerleyeceği merak konusu oldu. Tera tarafından yapılan açıklamada, kamuoyuna yansıyan gelişmelerin Pusula Finans Holding ve bünyesindeki şirketlerin tüzel kişiliklerinden, faaliyetlerinden ve kurumsal yapılarından bağımsız olduğu belirtildi. Şirket, daha önce duyurulan anlaşma doğrultusunda devralma sürecinin devam ettiğini bildirdi. DEVİR İÇİN GEREKLİ ONAYLAR BEKLENİYOR Pusula Finans Holding'in Tera Grubu'na devrinin tamamlanması için ilgili düzenleyici kurumların gerekli izin ve onaylarının alınması gerekiyor. Tera, söz konusu gelişmelere rağmen finans sektöründeki faaliyetlerini genişletmeye yönelik uzun vadeli stratejisinde değişiklik bulunmadığını açıkladı. KATILIMEVİM HİSSELERİ DE GÜNDEMDE Pusula Finans Holding ile ilgili gelişmeler, holdingin bünyesinde bulunan ve Borsa İstanbul'da KTLEV koduyla işlem gören Katılımevim açısından da yakından takip ediliyor. Katılımevim hisselerinde daha önce yaşanan hareketlilik de dikkat çekmişti. Satış anlaşmasının açıklanmasının ardından hisselerde üst üste yükselişler görülmüştü. İDDİALARIN ODAĞINDAKİ ŞİRKET: KATILIMEVİM Katılımevim, tasarruf finansman sektöründe faaliyet gösteriyor. Şirket; konut, araç ve çatılı iş yeri edinmek isteyen müşterilere tasarruf finansman modeli kapsamında hizmet sunuyor. Pusula Finans Holding'in Katılımevim'deki çoğunluk hisseleriyle bağlantısı nedeniyle holding hakkında yaşanan gelişmelerin şirket açısından da önem taşıdığı belirtiliyor. Not: Haberde yer alan yurt dışına kaçış, yakalama kararı ve yurt dışı çıkış yasağına ilişkin bilgiler, kaynakta yer alan iddialara dayanmaktadır. Editörün Seçtiği Taraftarın Sesi Kanal S ekranlarında sizlerle 22 Ocak Pazartesi Editörün Seçtiği Samsun'da FETÖ'cü akrabası başını yaktı!</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.samsungazetesi.com/dev-finans-sirketinde-sorusturma-yakalama-karari-iddiasi</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Samsun | Muğla</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Marmaris</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="AB49" s="2" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 11:50:46</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>soruşturma</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>ticaret</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi ve içerik paylaşan sosyal medya hesapları hakkında soruşturma başlattı. Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi… Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi ve içerik paylaşan sosyal medya hesapları hakkında soruşturma başlattı.</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi ve içerik paylaşan sosyal medya hesapları hakkında soruşturma başlattı. Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi… Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi ve içerik paylaşan sosyal medya hesapları hakkında soruşturma başlattı.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>https://istanbulticaretgazetesi.com/sosyal-medyada-yaniltici-borsa-paylasimlarina-sorusturma-suphelilerin-kimlikleri-arastiriliyor</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret:84:summary</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Türkiye</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi | İstanbul Ticaret Merkezi | İstanbul Ticaret İş Güvenliği ve Endüstriyel Ürünler San. A.Ş | İstanbul Ticaret Üniversitesi Küçükyalı Kampüsü | İstanbul Ticaret Borsası</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>100.0 | 100.0 | 100.0 | 100.0 | 100.0</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="n">
+        <v>192.64</v>
+      </c>
+      <c r="AB50" s="2" t="n">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB46"/>
+  <autoFilter ref="A1:AB50"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -6905,6 +7557,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:42:00</t>
+          <t>2026-09-13 21:35:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü</t>
+          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Bursada Bugün</t>
+          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı A Haber</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -537,14 +537,10 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Bursa | Düzce</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Orhangazi</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
@@ -556,22 +552,22 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 23:31:00</t>
+          <t>2026-09-14 06:49:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce Postası</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği Ege Telgraf</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -579,11 +575,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
@@ -596,22 +588,22 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:03:00</t>
+          <t>2026-09-14 07:49:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi</t>
+          <t>8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Ege Alternatif</t>
+          <t>8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği Ulusal Kanal</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -619,11 +611,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -636,22 +624,22 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:49:00</t>
+          <t>2026-09-13 23:08:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği</t>
+          <t>Düzce’de kapı fabrikasında yangın</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği egetelgraf.com</t>
+          <t>Düzce’de kapı fabrikasında yangın Milliyet</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -659,35 +647,47 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Bolu | Düzce | İstanbul | Mardin</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Bahçelievler</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>KZB Yangın Söndürme Sistemleri</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:19:31</t>
+          <t>2026-09-13 19:18:13</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti!</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! Düzce Gazete Efsane</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -695,7 +695,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
@@ -708,22 +712,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:33:00</t>
+          <t>2026-09-13 21:12:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı surmelihaber.com</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -731,20 +735,32 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>İlamet Metal Ltd Şti</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:18:13</t>
+          <t>2026-09-14 09:11:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -754,12 +770,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti!</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! duzcegazeteefsane.com</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -769,22 +785,30 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Düzce</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>Antalya | Bursa</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Alanya</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Toptancı Hali</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:12:00</t>
+          <t>2026-09-13 20:07:54</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -794,12 +818,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın turizmaktuel.com</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -809,30 +833,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Nova Orman Ürünleri - Bolu Fabrika</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:45:00</t>
+          <t>2026-09-14 10:17:58</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -842,12 +858,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi</t>
+          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber</t>
+          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı bolgegundemi.com</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -855,11 +871,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
@@ -872,22 +884,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:41:26</t>
+          <t>2026-09-14 12:09:13</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü</t>
+          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü kocatepegazetesi.com</t>
+          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu İlke TV</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -895,16 +907,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Ankara | Eskişehir | Manisa</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Demirci</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
@@ -916,22 +920,22 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:11:00</t>
+          <t>2026-09-14 11:18:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Demirtaş Mahallesi'nde saman deposu yangını</t>
+          <t>Vanlı Kara Haydar'ın akılalmaz görüntüsü ortaya çıktı! Bankada bile bu kadar para yoktur</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya</t>
+          <t>Vanlı Kara Haydar'ın akılalmaz görüntüsü ortaya çıktı! Bankada bile bu kadar para yoktur Halk TV</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -939,47 +943,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Antalya | Bursa</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Alanya</t>
-        </is>
-      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Demirtaş Toptancı Hali</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:07:54</t>
+          <t>2026-09-14 11:11:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın</t>
+          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Turizm Aktüel</t>
+          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -989,7 +981,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Antalya</t>
+          <t>Van</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1004,22 +996,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:20:22</t>
+          <t>2026-09-14 06:55:51</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Dakika</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1029,12 +1021,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
+          <t>Bilecik</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Gerede</t>
+          <t>Bozüyük</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -1048,22 +1040,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:19:26</t>
+          <t>2026-09-14 06:45:32</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi!</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1073,12 +1065,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
+          <t>Bilecik | Bursa | Denizli | Düzce | Eskişehir</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Gerede</t>
+          <t>Bozüyük | Silivri | Ereğli | Yeşilyurt</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
@@ -1092,22 +1084,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:55:51</t>
+          <t>2026-09-13 22:32:41</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı</t>
+          <t>Düzce’de fabrika yangını büyüdü! Alevlerle savaşan 1 itfaiye eri yaralandı</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika</t>
+          <t>Düzce’de fabrika yangını büyüdü! Alevlerle savaşan 1 itfaiye eri yaralandı Takvim</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1117,14 +1109,10 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Bilecik</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Bozüyük</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr">
@@ -1136,22 +1124,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:45:32</t>
+          <t>2026-09-14 08:44:22</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı</t>
+          <t>Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı aksiyon.com.tr</t>
+          <t>Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Son Dakika</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1161,14 +1149,10 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Adana | Aydın | Bartın | Bilecik | Düzce</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Köşk | Bozüyük | Mudurnu | Maltepe</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
       <c r="J17" s="2" t="inlineStr">
@@ -1180,22 +1164,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:13:08</t>
+          <t>2026-09-13 22:33:16</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi</t>
+          <t>Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv</t>
+          <t>Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1203,11 +1187,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul | Van</t>
-        </is>
-      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1220,22 +1200,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:13:44</t>
+          <t>2026-09-13 22:32:24</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi</t>
+          <t>Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5</t>
+          <t>Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Son Dakika</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1243,7 +1223,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1256,22 +1240,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:22:00</t>
+          <t>2026-09-13 21:48:26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1281,7 +1265,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Bolu | Düzce</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1296,22 +1280,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:21:29</t>
+          <t>2026-09-14 07:27:59</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursada Bugün</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı Düzce Gazete Efsane</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1321,49 +1305,37 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Orhangazi</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Cargill Türkiye Bursa Orhangazi Mısır İşleme Tesisi</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:57:35</t>
+          <t>2026-09-13 19:48:24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1371,8 +1343,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Denizli | Düzce | Eskişehir | İstanbul</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Silivri | Ereğli | Yeşilyurt</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
@@ -1384,22 +1364,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:00:38</t>
+          <t>2026-09-13 19:45:00</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1409,14 +1389,10 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Çorum | Eskişehir | Kilis | Aydın | İstanbul</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Söke | Beşiktaş | Çerkezköy</t>
-        </is>
-      </c>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
@@ -1428,22 +1404,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:46:30</t>
+          <t>2026-09-13 20:49:00</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi</t>
+          <t>Başkan Özlü’den fabrika yangını açıklaması</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
+          <t>Başkan Özlü’den fabrika yangını açıklaması Düzce Postası</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1451,7 +1427,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1464,22 +1444,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:22:37</t>
+          <t>2026-09-13 22:33:20</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi</t>
+          <t>Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
+          <t>Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti havadis.com</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1487,7 +1467,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1500,22 +1484,22 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:39:00</t>
+          <t>2026-09-14 07:28:44</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı</t>
+          <t>İnegöl OSB’de tekstil fabrikasında yangın</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı İstiklal Gazetesi</t>
+          <t>İnegöl OSB’de tekstil fabrikasında yangın İnegöl Yerel Haber</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1525,10 +1509,14 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Kayseri</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>İnegöl</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
@@ -1540,22 +1528,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:27:00</t>
+          <t>2026-09-13 20:48:21</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı!</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız"</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" Mersin Haber</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1563,47 +1551,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş</t>
-        </is>
-      </c>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:52:25</t>
+          <t>2026-09-14 14:23:02</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı</t>
+          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
+          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1611,8 +1587,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Denizli | Düzce | Eskişehir | İstanbul</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Silivri | Ereğli | Yeşilyurt</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
@@ -1624,7 +1608,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:39:00</t>
+          <t>2026-09-14 14:22:08</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1634,12 +1618,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı!</t>
+          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi</t>
+          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede havadis.com</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1647,7 +1631,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1704,7 +1692,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:58:46</t>
+          <t>2026-09-14 09:05:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1714,12 +1702,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti</t>
+          <t>Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu!</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti Sözcü Gazetesi</t>
+          <t>Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu! babaocagi.com.tr</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1727,11 +1715,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul | Kahramanmaraş</t>
-        </is>
-      </c>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1744,7 +1728,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:12:00</t>
+          <t>2026-09-14 14:29:33</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1754,12 +1738,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti Tek Referans</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1767,16 +1751,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Kocaeli</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Gebze</t>
-        </is>
-      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
@@ -1788,7 +1764,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:07:27</t>
+          <t>2026-09-14 07:30:52</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1798,12 +1774,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak?</t>
+          <t>Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet</t>
+          <t>Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı Bursada Bugün</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1811,8 +1787,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | İstanbul</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Kestel</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
@@ -1824,7 +1808,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:23:36</t>
+          <t>2026-09-14 10:32:55</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1834,12 +1818,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı...</t>
+          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet</t>
+          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı | Türkiye Ekonomisi Haberleri GZT</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1847,17 +1831,13 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Kestel</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Boya Tekstil</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -1868,7 +1848,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:53:53</t>
+          <t>2026-09-14 06:12:39</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1878,12 +1858,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu</t>
+          <t>Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi...</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist</t>
+          <t>Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1891,35 +1871,43 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:36:11</t>
+          <t>2026-09-14 06:00:38</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor aksiyon.com.tr</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1929,12 +1917,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Adana | Bilecik | Düzce | Iğdır | Zonguldak</t>
+          <t>Çorum | Eskişehir | Kilis | Aydın | İstanbul</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Köşk | Mudurnu</t>
+          <t>Söke | Beşiktaş</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -1948,22 +1936,22 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:44:00</t>
+          <t>2026-09-14 09:46:30</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Cumhuriyet</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1971,11 +1959,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Bolu | Düzce</t>
-        </is>
-      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
@@ -1988,22 +1972,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:48:26</t>
+          <t>2026-09-14 12:51:00</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti</t>
+          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika</t>
+          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -2013,7 +1997,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
+          <t>Kahramanmaraş</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -2028,22 +2012,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:36:42</t>
+          <t>2026-09-14 11:31:46</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı</t>
+          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı</t>
+          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Merhaba Gazetesi</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2051,7 +2035,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Konya</t>
+        </is>
+      </c>
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2064,22 +2052,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:48:24</t>
+          <t>2026-09-14 06:22:37</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada aksiyon.com.tr</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2087,16 +2075,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Adana | Aydın | Bartın | Düzce | Iğdır</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Köşk | Mudurnu | Maltepe</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
@@ -2108,22 +2088,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:27:59</t>
+          <t>2026-09-13 20:52:25</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı duzcegazeteefsane.com</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2131,11 +2111,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2148,22 +2124,22 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:06:00</t>
+          <t>2026-09-14 07:27:00</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı!</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı yeniadimgazetesi.com</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2173,37 +2149,45 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
+          <t>Kahramanmaraş</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:51:05</t>
+          <t>2026-09-14 09:53:53</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2224,22 +2208,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:20:02</t>
+          <t>2026-09-14 07:12:00</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı İhlas Haber Ajansı</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2249,49 +2233,41 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Kocaeli</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Nilüfer</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Tarım AŞ</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>TARIM PEYZAJ A.Ş. Bursa Tarım Hayvancılık Peyzaj Çevre İnş. San. Tic. A.Ş</t>
-        </is>
-      </c>
+          <t>Gebze</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:20:28</t>
+          <t>2026-09-14 15:56:00</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı aksiyon.com.tr</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku yildirimgazetesi.com</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2299,16 +2275,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Adana | Bilecik | Bursa | Düzce | Iğdır</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Köşk | Mudurnu | Kızıltepe</t>
-        </is>
-      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
@@ -2320,22 +2288,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 22:01:00</t>
+          <t>2026-09-14 10:10:00</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu</t>
+          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber</t>
+          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti Ekonomim</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2343,11 +2311,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2360,22 +2324,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:43:00</t>
+          <t>2026-09-14 08:07:27</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak?</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2396,22 +2360,22 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:52:00</t>
+          <t>2026-09-14 07:23:36</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama!</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı...</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2419,8 +2383,16 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Kestel</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
@@ -2432,22 +2404,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:23:00</t>
+          <t>2026-09-14 07:51:05</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası Samsun Gazetesi</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2455,16 +2427,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul | Samsun | Muğla</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Marmaris</t>
-        </is>
-      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
@@ -2476,49 +2440,281 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:50:46</t>
+          <t>2026-09-14 11:31:11</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
+          <t>Fiziksel Risk / Yangın</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Muğla</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Bodrum</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 06:35:00</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Fiziksel Risk / Yangın</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Bursa’da kömür işletmesinde korkutan yangın!</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Bursa’da kömür işletmesinde korkutan yangın! bursatv.com.tr</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Nilüfer</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:44:15</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Diğer</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza borsatek.com</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 08:43:00</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Diğer</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:55:08</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir. Vietnam.vn</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:01:00</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:21:32</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>Habere Git</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret Üniversitesi</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>firma adı + güvenli maps adayı var</t>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı İhlas Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J50"/>
+  <autoFilter ref="A1:J56"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2569,6 +2765,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2580,7 +2782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB50"/>
+  <dimension ref="A1:AB56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2758,12 +2960,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:42:00</t>
+          <t>2026-09-13 21:35:12</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>üretim tesisi yangını</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2773,12 +2975,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü</t>
+          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Bursada Bugün</t>
+          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı A Haber</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2798,12 +3000,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Düzce'de fabrika yangını için çok sayıda ekip sevk edildi Ahşap malzemeler alevlerin kısa sürede büyümesine neden oldu Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Yangın, Düzce merkeze bağlı Hacıdayı mevkisinde faaliyet gösteren ahşap kapı fabrikasında meydana geldi. Fabrikadan yükselen alevleri ve dumanları görenlerin durumu yetkililere bildirmesi üzerine bölgeye geniş kapsamlı ekip sevkiyatı yapıldı. İlk belirlemelere göre henüz çıkış nedeni netleşmeyen yangın, fabrikada bulunan ahşap ve diğer yanıcı malzemelerin etkisiyle kısa süre içerisinde geniş bir alana yayıldı. Alevlerin büyümesi üzerine yangına müdahale için kent merkezinin yanı sıra ilçelerden ve çevre illerden de itfaiye ekipleri bölgeye gönderildi. İhbarın ardından olay yerine ulaşan itfaiye ekipleri, fabrikadaki yangının daha fazla alana yayılmasını önlemek amacıyla çalışma başlattı. Yangının üretim yapılan bölümde bulunan yanıcı malzemeler nedeniyle hızlı şekilde büyümesi, müdahalenin kapsamının genişletilmesine neden oldu. Bölgeye sevk edilen ekipler, farklı noktalardan alevlere müdahale ederek yangını kontrol altına almaya çalışıyor. Düzce fabrika yangını nedeniyle ekiplerin bölgede yoğun çalışması sürerken, çevrede de güvenlik tedbirleri alındı. Yangının çıkış noktası ve büyüklüğünün net olarak belirlenmesine yönelik çalışmalar da devam ediyor. İtfaiye ekiplerinin müdahalesinin ardından yangının çıkış nedeninin belirlenmesi için gerekli incelemelerin yapılması bekleniyor. Yangının meydana geldiği fabrikanın ahşap kapı imalatı yapılan bir tesis olması nedeniyle içeride bulunan malzemelerin alevlerin yayılma hızını artırdığı belirtildi. Yangının başlamasının ardından kısa süre içerisinde yoğun duman ve alevlerin yükselmesi üzerine bölgeye daha fazla ekip takviyesi gerçekleştirildi. İtfaiye ekipleri, bir yandan alevleri bastırmaya çalışırken diğer yandan yangının fabrikanın diğer bölümlerine ve çevredeki alanlara sıçramaması için müdahalelerini sürdürüyor. Çalışmalar sırasında ekiplerin koordineli şekilde hareket ettiği görüldü. Diğer Güncel Haberler için tıklayın Türkiye bu olayı konuşuyor: 11 aylık Büşra'dan 4 gündür haber yok! Anne "satıldı" dedi, baba reddetti Cezaevinden çıkan Fatma Soydaş'ın son hali şaşırttı! İlk görüntüsü ortaya çıktı Bursa'da gözler bu toplantıda! Nilüfer'de tartışma yaratan imar planı gündemde... Bursa Orhangazi'de dev operasyon! 8 ton ele geçirildi... Kurtlar Vadisi sahneleri yeniden gündemde: Plakadaki detay dikkat çekti! Bursa'da vicdanları sızlatan görüntü!</t>
+          <t>Düzce'de Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken 1 itfaiye eri yaralandı. Düzce'de Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken 1 itfaiye eri yaralandı. Düzce'de Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken 1 itfaiye eri yaralandı. Giriş Tarihi: 14 Eylül 2026 00:35 Son Güncelleme: 14 Eylül 2026 02:12 ahaber.com.tr Haber Merkezi Giriş Tarihi: 14 Eylül 2026 00:35 Son Güncelleme: 14 Eylül 2026 02:12 ahaber.com.tr Haber Merkezi Düzce'de merkeze bağlı Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken, 1 itfaiye eri yanan çatının üzerine düşerek yaralandı. Yaralı itfaiye eri olay yerindeki ilk müdahalenin ardından hastaneye kaldırılırken, yangın kontrol altına alındı. DÜZCE'DE AHŞAP KAPI FABRİKASINDA YANGIN! Düzce D-100 kara yolu üzerinde bulunan Hacıdayı mevkiindeki Düzce Door isimli fabrikada bilinmeyen nedenle yangın çıktı. Alevler, yanıcı maddeler nedeniyle kısa sürede büyürken ihbar üzerine kent merkezi, ilçeler ve çevre illerden itfaiye ekipleri bölgeye sevk edildi. Yangına müdahale eden 1 itfaiye eri yaralanarak hastaneye kaldırıldı. (Foto: İHA) İTFAİYE ERİ YARALANDI Yangına müdahale eden 1 itfaiye eri, yanan çatının üzerine düşmesi sonucu yaralandı. Olay yerinde ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. "CAN KAYBI YOK" Düzce Belediye Başkanı Faruk Özlü, yangının çıktığı fabrikada söndürme çalışmalarına ilişkin son durumu payla</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Bursada Bugün Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yanıcı malzemelerin bulunduğu tesiste alevlerin kısa sürede büyümesi üzerine bölgeye çok sayıda itfaiye ekibi yönlendirildi. Ekiplerin yangını kontrol altına alma çalışmaları devam ediyor. Düzce'de ahşap kapı fabrikasında yangın paniği! Alevler kısa sürede büyüdü Düzce'de fabrika yangını için çok sayıda ekip sevk edildi Ahşap malzemeler alevlerin kısa sürede büyümesine neden oldu Düzce'de ahşap kapı üretimi gerçekleştirilen bir fabrikada henüz belirlenemeyen nedenle yangın çıktı. Yangın, Düzce merkeze bağlı Hacıdayı mevkisinde faaliyet gösteren ahşap kapı fabrikasında meydana geldi. Fabrikadan yükselen alevleri ve dumanları görenlerin durumu yetkililere bildirmesi üzerine bölgeye geniş kapsamlı ekip sevkiyatı yapıldı. İlk belirlemelere göre henüz çıkış nedeni netleşmeyen yangın, fabrikada bulunan ahşap ve diğer yanıcı malzemelerin etkisiyle kısa süre içerisinde geniş bir alana yayıldı. Alevlerin büyümesi üzerine yangına müdahale için kent merkezinin yanı sıra ilçelerden ve çevre illerden de itfaiye ekipleri bölgeye gönderildi. İhbarın ardından olay yerine ulaşan itfaiye ekipleri, fabrikadaki yangının daha fazla alana yayılmasını önlemek amacıyla çalışma başlattı. Yangının üretim yapılan bölümde bulunan yanıcı malzemeler nedeniyle hızlı şekilde büyümesi, müdahalenin kapsamının genişletilmesine neden oldu. Bölgeye sevk edilen ekipler, farklı noktalardan alevlere müdahale ederek yangını kontrol altına almaya çalışıyor. Düzce fabrika yangını nedeniyle ekiplerin bölgede yoğun çalışması sürerken, çevrede de güvenlik tedbirleri alındı. Yangının çıkış noktası ve büyüklüğünün net olarak belirlenmesine yönelik çalışmalar da devam ediyor. İtfaiye ekiplerinin müdahalesinin ardından yangının çıkış nedeninin belirlenmesi için gerekli incelemelerin yapılması bekleniyor. Yangının meydana geldiği fabrikanın ahşap kapı imalatı yapılan bir tesis olması nedeniyle içeride bulunan malzemelerin alevlerin yayılma hızını artırdığı belirtildi. Yangının başlamasının ardından kısa süre içerisinde yoğun duman ve alevlerin yükselmesi üzerine bölgeye daha fazla ekip takviyesi gerçekleştirildi. İtfaiye ekipleri, bir yandan alevleri bastırmaya çalışırken diğer yandan yangının fabrikanın diğer bölümlerine ve çevredeki alanlara sıçramaması için müdahalelerini sürdürüyor. Çalışmalar sırasında ekiplerin koordineli şekilde hareket ettiği görüldü. Anne "satıldı" dedi, baba reddetti Cezaevinden çıkan Fatma Soydaş'ın son hali şaşırttı! İlk görüntüsü ortaya çıktı Bursa'da gözler bu toplantıda! Bursa Orhangazi'de dev operasyon! Bursa'da vicdanları sızlatan görüntü!</t>
+          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı A Haber Düzce'de Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken 1 itfaiye eri yaralandı. Giriş Tarihi: 14 Eylül 2026 00:35 Son Güncelleme: 14 Eylül 2026 02:12 ahaber.com.tr Haber Merkezi Giriş Tarihi: 14 Eylül 2026 00:35 Son Güncelleme: 14 Eylül 2026 02:12 ahaber.com.tr Haber Merkezi Düzce'de merkeze bağlı Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken, 1 itfaiye eri yanan çatının üzerine düşerek yaralandı. Yaralı itfaiye eri olay yerindeki ilk müdahalenin ardından hastaneye kaldırılırken, yangın kontrol altına alındı. DÜZCE'DE AHŞAP KAPI FABRİKASINDA YANGIN! Düzce D-100 kara yolu üzerinde bulunan Hacıdayı mevkiindeki Düzce Door isimli fabrikada bilinmeyen nedenle yangın çıktı. Alevler, yanıcı maddeler nedeniyle kısa sürede büyürken ihbar üzerine kent merkezi, ilçeler ve çevre illerden itfaiye ekipleri bölgeye sevk edildi. Yangına müdahale eden 1 itfaiye eri yaralanarak hastaneye kaldırıldı. (Foto: İHA) İTFAİYE ERİ YARALANDI Yangına müdahale eden 1 itfaiye eri, yanan çatının üzerine düşmesi sonucu yaralandı. Olay yerinde ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. "CAN KAYBI YOK" Düzce Belediye Başkanı Faruk Özlü, yangının çıktığı fabrikada söndürme çalışmalarına ilişkin son durumu payla</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -2813,27 +3015,27 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>https://www.bursadabugun.com/haber/duzce-de-ahsap-kapi-fabrikasinda-yangin-panigi-alevler-kisa-surede-buyudu-1948671.html</t>
+          <t>https://www.ahaber.com.tr/yasam/2026/09/14/duzcede-kapi-fabrikasinda-yangin</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Bursa | Düzce</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Orhangazi</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Alevler kısa sürede tesisi</t>
+        </is>
+      </c>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr"/>
@@ -2847,7 +3049,7 @@
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="n">
-        <v>118</v>
+        <v>102.5</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -2856,27 +3058,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 23:31:00</t>
+          <t>2026-09-14 06:49:00</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>MASAK raporu</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce Postası</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği Ege Telgraf</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2886,22 +3088,18 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci hastaneye kaldırıldı. Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci h... Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci hastaneye kaldırıldı. Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale eden bir itfaiye eri, üzerine çatı düşmesi sonucu yaralandı. D-100 kara yolu üzerinde bulunan Düzce Door isimli fabrikada çıkan yangın kısa sürede fabrikayı sardı. Yangına müdahale eden itfaiye ekiplerinin çalışmaları sırasında bir itfaiye erinin üzerine yanan çatı düştü. Çatı parçalarının altında kalan itfaiye eri yaralandı. Olay yerinde sağlık ekipleri tarafından ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci hastaneye kaldırıldı. Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale eden bir itfaiye eri, üzerine çatı düşmesi sonucu yaralandı. D-100 kara yolu üzerinde bulunan Düzce Door isimli fabrikada çıkan yangın kısa sürede fabrikayı sardı. Yangına müdahale eden itfaiye ekiplerinin çalışmaları sırasında bir itfaiye erinin üzerine yanan çatı düştü. Çatı parçalarının altında kalan itfaiye eri yaralandı. Olay yerinde sağlık ekipleri tarafından ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. 14 Eyl 2026 - 02:31 İHA Düzce - Asayiş Yazdır Mahreç İhlas Haber Ajansı Yorum yazarak Düzce Postası Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yo</t>
+          <t>8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Güncel 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 14.09.2026 - 09:49 Okunma Süresi: 1 Dk İçişleri Bakanlığı, yasa dışı bahis organizasyonlarına yönelik 8 ilde kapsamlı operasyonlar gerçekleştirildiğini açıkladı. Mali Suçları Araştırma Kurulu (MASAK) raporları doğrultusunda yürütülen çalışmalarda, hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edilen 177 şüpheli hakkında adli işlem başlatıldı. 8 İLDE EŞ ZAMANLI OPERASYON Yasa dışı bahis suçuna yönelik operasyonlar 8 ilde düzenlendi. Ekiplerin çalışmaları kapsamında şüphelilerin banka hesapları ve para hareketleri mercek altına alındı. Türkiye’den 45 dakikada gidiliyor, turistler akın ediyor! Samos’ta pasaport kuyruğu bitmiyor! İçeriği Görüntüle MASAK RAPORLARI HAREKETLİLİĞİ ORTAYA ÇIKARDI Operasyonların önemli dayanaklarından biri MASAK tarafından hazırlanan raporlar oldu. Yapılan incelemelerde, şüphelilerin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği bulunduğu belirlendi. 177 ŞÜPHELİ HAKKINDA ADLİ İŞLEM Soruşturma kapsamında yasa dışı bahis faaliyetleriyle bağlantılı olduğu değerlendirilen 177 şüpheli hakkında adli işlem başlatıldı. Güvenlik güçlerinin operasyonlarla yasa dışı bahis ağlarına yönelik mücadelesini sürdürdüğü bildirildi. Kaynak: HABER MERKEZİ Editörün Seçtiği Ne Çeşme ne Foça! İzmir’in gizli koyunda su hala yüzmeye çağırıyor: Berraklığı gören gözlerine inanamıyor Editörün Seçtiği Ne Çeşme ne Foça! İzmir’in kimsenin bilmediği koy: İncecik sahili ve berrak suyuyla yaz bitmeden çağırıyor Editörün Seçtiği İzmir’de yaz bitmeden görülmesi gereken beyaz koy! Deniz cam, gören kendini Maldivler’de sanıyor Editör Hakkında Kader Ergin Bunlar da ilgi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce Postası Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci hastaneye kaldırıldı. Çatı parçalarının üzerine düşmesi sonucu yaralanan itfaiyeci h... Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale eden bir itfaiye eri, üzerine çatı düşmesi sonucu yaralandı. D-100 kara yolu üzerinde bulunan Düzce Door isimli fabrikada çıkan yangın kısa sürede fabrikayı sardı. Yangına müdahale eden itfaiye ekiplerinin çalışmaları sırasında bir itfaiye erinin üzerine yanan çatı düştü. Çatı parçalarının altında kalan itfaiye eri yaralandı. Olay yerinde sağlık ekipleri tarafından ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. Düzce’de fabrikadaki yangında üzerine çatı düşen itfaiyeci yaralandı Düzce’de kapı üretimi yapan fabrikada çıkan yangına müdahale sırasında bir itfaiye eri yaralandı. 14 Eyl 2026 - 02:31 İHA Düzce - Asayiş Yazdır Mahreç İhlas Haber Ajansı Yorum yazarak Düzce Postası Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
+          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği Ege Telgraf 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Güncel 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -2911,14 +3109,10 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>https://www.duzcepostasi.com/haber/28694684/duzcede-fabrikadaki-yanginda-uzerine-cati-dusen-itfaiyeci-yaralandi</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+          <t>https://www.egetelgraf.com/8-ilde-yasa-disi-bahis-operasyonu-masak-raporu-ortaya-cikardi-17-milyar-750-milyon-tllik-para-trafigi</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
@@ -2927,7 +3121,7 @@
       <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr"/>
@@ -2941,7 +3135,7 @@
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
       <c r="AA3" s="2" t="n">
-        <v>95.5</v>
+        <v>112</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>2</v>
@@ -2950,27 +3144,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:03:00</t>
+          <t>2026-09-14 07:49:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>MASAK raporu</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi</t>
+          <t>8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Ege Alternatif</t>
+          <t>8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği Ulusal Kanal</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -2980,52 +3174,40 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. ASAYİŞ Yayınlanma : 14 Eylül 2026 09:03 Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'de bir kapı imalat fabrikasında çıkan yangın tamamen söndürüldü. Yangının ardından fabrikanın durumu havadan görüntülendi. Yangın anında büyük hasar oluştu Düzce Gökçeköy mevkisinde bulunan Düzce Door isimli fabrikada, dün akşam 21.30 sıralarında başlayan yangın, içerideki kimyasal, ahşap ve plastik maddelerin etkisiyle hızla yayıldı ve tüm tesisi sardı. Yangın, 4 saatlik bir mücadelenin ardından kontrol altına alındı ve sabaha karşı tamamen söndürüldü. Detaylı inceleme yapılacak Fabrikanın son hali havadan görüntülenirken, yangının etkisiyle tamamen kullanılmaz hale geldiği ve bazı bölümlerden hala dumanların yükseldiği görüldü. İlerleyen saatlerde, yangının çıkış nedeni hakkında detaylı bir inceleme yapılması planlanıyor. #Düzce #Yangın İHA Pay</t>
+          <t>8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği Ulusal Kanal</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Ege Alternatif Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Yangın tamamen söndürüldü, ancak bazı bölümlerden hala dumanlar yükseliyor. ASAYİŞ Yayınlanma : 14 Eylül 2026 09:03 Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'deki kapı fabrikasında çıkan yangın sonrası fabrikanın durumu havadan görüntülendi. Düzce'deki kapı fabrikasındaki yangın havadan görüntülendi Düzce'de bir kapı imalat fabrikasında çıkan yangın tamamen söndürüldü. Yangının ardından fabrikanın durumu havadan görüntülendi. Yangın anında büyük hasar oluştu Düzce Gökçeköy mevkisinde bulunan Düzce Door isimli fabrikada, dün akşam 21.30 sıralarında başlayan yangın, içerideki kimyasal, ahşap ve plastik maddelerin etkisiyle hızla yayıldı ve tüm tesisi sardı. Yangın, 4 saatlik bir mücadelenin ardından kontrol altına alındı ve sabaha karşı tamamen söndürüldü. Detaylı inceleme yapılacak Fabrikanın son hali havadan görüntülenirken, yangının etkisiyle tamamen kullanılmaz hale geldiği ve bazı bölümlerden hala dumanların yükseldiği görüldü. İlerleyen saatlerde, yangının çıkış nedeni hakkında detaylı bir inceleme yapılması planlanıyor.</t>
+          <t>8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği 8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği Ulusal Kanal 8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği Ulusal Kanal</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>https://www.egealternatif.com/haber/duzce-deki-kapi-fabrikasindaki-yangin-havadan-goruntulendi_92660/</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOTjQzOEEyN3dWWk5JTnBoQlpyMFVodE10dGhsd3JPLVg1Y1VQVkJlbmhQZnQwa3k2RFAxSjZKT1pIOU81MkpNal8wd3RxMkxhSk9kem5QMjB4bUEtUW5tdGVFZlFBd3ZhUnJFQ0xVOVV6X1lIMUk4RnBqeEpUWXdFRko0aGxrOWMwTUFwVVJOVDIydVc0YTBrWHNYT015bTZBN2dZWmotZFRwWWF0Y3RMTzBkMUtZYmZfVElDVndWblhQUW8tZm9BTjBQcmhpeDhmSDUxUHFma9IB3AFBVV95cUxQa2l0RlFKNlA3RnFEbWYtdGFieVFKMm9RSUQtTUh3WVVwMTRPRTBURnR5MS1OMlFkNHRHVkZCZF9HeFVYN19la1dKVm9aTVBLUnNvWUdtOFhFTTdteEpjZ1NOeXNvU3dfdDQyMEdfZXU4N3pGS2V4OWkzWDlHWGVCVy1KRS1VWld5OU9LTVBBUmk0dE5BM3gxVXdqdU1OVzVUeC0yS3ZpWGdKR3A1cHJLbnhuLTZIblFSUnVNbE5xR2tpZnpaWlZMaXRDTnB3ZzQwMG92RVM0VlVSOHRj?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>ve tüm tesisi</t>
-        </is>
-      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr"/>
@@ -3039,7 +3221,7 @@
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
       <c r="AA4" s="2" t="n">
-        <v>104.25</v>
+        <v>96.14</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>3</v>
@@ -3048,27 +3230,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:49:00</t>
+          <t>2026-09-13 23:08:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>MASAK raporu</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği</t>
+          <t>Düzce’de kapı fabrikasında yangın</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği egetelgraf.com</t>
+          <t>Düzce’de kapı fabrikasında yangın Milliyet</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -3078,18 +3260,22 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Güncel 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + 14.09.2026 - 09:49 Okunma Süresi: 1 Dk İçişleri Bakanlığı, yasa dışı bahis organizasyonlarına yönelik 8 ilde kapsamlı operasyonlar gerçekleştirildiğini açıkladı. Mali Suçları Araştırma Kurulu (MASAK) raporları doğrultusunda yürütülen çalışmalarda, hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edilen 177 şüpheli hakkında adli işlem başlatıldı. 8 İLDE EŞ ZAMANLI OPERASYON Yasa dışı bahis suçuna yönelik operasyonlar 8 ilde düzenlendi. Ekiplerin çalışmaları kapsamında şüphelilerin banka hesapları ve para hareketleri mercek altına alındı. İzmirliler dikkat! Termometreler önce yükselecek, ardından sıcaklık hızla düşecek İçeriği Görüntüle MASAK RAPORLARI HAREKETLİLİĞİ ORTAYA ÇIKARDI Operasyonların önemli dayanaklarından biri MASAK tarafından hazırlanan raporlar oldu. Yapılan incelemelerde, şüphelilerin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği bulunduğu belirlendi. 177 ŞÜPHELİ HAKKINDA ADLİ İŞLEM Soruşturma kapsamında yasa dışı bahis faaliyetleriyle bağlantılı olduğu değerlendirilen 177 şüpheli hakkında adli işlem başlatıldı. Güvenlik güçlerinin operasyonlarla yasa dışı bahis ağlarına yönelik mücadelesini sürdürdüğü bildirildi. Kaynak: HABER MERKEZİ Editörün Seçtiği Aydın’da ayakta kalan üç kuleden biri! Zindanından hamamına eksiksiz Ege’nin 200 yıllık az bilinen tarihi şatosu Editörün Seçtiği Ne Efes ne Bergama! 5 bin yıllık değişimin tanığı: İzmir’in kayıp ada kentinde binlerce boncuk bulundu Editörün Seçtiği Ne Efes ne Bergama! İZBAN’dan inip kralların tepesine çıkılıyor: İzmir’de üç saraylı antik kenti çoğu kişi bilmiyor Editör Hakkında Kader Ergin Bunlar da ilgi</t>
+          <t>Düzce’de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yoğun müdahalesi sonrası yangın kontrol altına alındı. Düzce’de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yoğun müdahalesi sonrası yangın kontrol altına alındı. Düzce’de faaliyet gösteren kapı üretim fabrikas... 00:29 MSB, yerli mühimmat atışlarına ilişkin görüntüleri paylaştı 02:02 Haysiyet'teki o sahne gerçek mi, yapay zekâ mı? 00:37 İstanbul'da orman yangını! Alevlere havadan müdahale başladı 01:44 Piyasalarda haftanın kazananı ve kaybedeni belli oldu! Altın yatırımcısı dikkat 02:05 AK Parti Sözcüsü Çelik’ten Özgür Özel’e sert tepki: Kendisini siyaset adabına davet ediyoruz 02:33 Teoman gerçeği öğrenecek mi? İki kardeş kavuşacak mı? 01:02 İstanbul Havalimanı’nın yeni pisti için geri sayım... 00:25 Vanlı Kara Haydar'ın eşi Çağla Öz'le ilgili yeni gelişme 03:59 Serhat kaderini kendi çizdi 00:52 İstanbul’da kiralık TOKİ evleri için başvurular yarın başlıyor! Bakan Kurum’dan örnek daire paylaşımı 00:59 Yeni eğitim öğretim yılı öncesi güvenlik önlemleri! 81 ilde 31 bin okul bahçe görevlisi 00:18 Kontrolsüz şekilde tali yola dönen otomobile arkadan gelen motosiklet çarptı 01:27 Vanuatu açıklarında feribot battı: 1 ölü, 30 kayıp 01:25 Okulların açıldığı güne dikkat! İstanbul’da hava değişiyor: AKOM saat verdi 02:49 Dev çekirgeler Van’ı sardı! Boyları 20 santimetreye yaklaşabiliyor: Bizi tedirgin ediyor 01:08 Genel müdürünün sözleriyle hayatı değişti! Kurumsal kariyerini bıraktı, Ironman şampiyonu oldu 00:45 2026 Yılı Kırsal Kalkınma Yatırım Programı başvuru sonuçları açıklandı 00:12 'Ailem Güvende' operasyonu! 15 ilde düğmeye basıldı: 162 şüpheli hakkında adli işlem 00:43 Deniz Türüç, TFF Temsilcisiyle tartıştı 00:13 Sanal medya ünlüsü Semih Varol gözaltına alındı 03:10 100 yaşındaki Ali Gül uzun yaşamın sırrını açıkladı! 'Ömrümde doktora sadece bir kere gittim' 00:25 Tarım işçilerini taşıyan minibüs, park halindeki traktöre çarptı! 10 kişinin yaralandığı kaza kamerada 00:09 'Vanlı Kara Haydar’ Mehmet Fatih Tançalan’ın eşi Çağla Öz İstanbul’da gözaltına alındı 00:57 AK Parti'nin 25. yılına özel 'Türkiye Bülteni' yayımlandı 03:57 Arif Ahmet Denizolgun'un ölümüne ilişkin soruşturma! Tanıktan şoke eden ifade: Beni belki de zehirlerler 02:42 İlim Yayma Vakfı Mütevelli Heyeti Başkanı Bilal Erdoğan: İyiliğin egemen geleceği bir dünyada yaşamak mümkün 00:27 Mardin’de TEKNOFEST İnsansız Kara Aracı Yarışması tamamlandı 03:01 Kiracıları tarafından öldürülen ev sahibi çift son yolculuğuna uğurlandı: Geride 5 yetim çocuk bıraktı 01:40 İstanbul Bahçelievler'de 5 katlı binanın istinat duvarı çöktü 01:53 Cemre Baysel: İlk bölümümüz şahane ; Oynatma Listesi HABERLER Düzce’de kapı fabrikasında yangın Düzce ’de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yoğun müdahalesi sonrası yangın kontrol altına alındı. Merkeze bağlı Hacialiler köyü mevkisinde bulunan kapı fabrikasında, saat 22.00 sıralarında yangın çıktı. Yangın kısa sürede büyüyerek fabrikayı sardı. İhbar üzerine bölgeye itfaiyeleri sevk edildi. İtfaiye erleri, yangına müdahale ederken Sakarya ve Bolu’dan da itfaiye ekipleri destek için bölgeye gönderildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. BAŞKAN ÖZLÜ: ÖNEMLİ OLAN CAN KAYBININ OLMAMASI Kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürerken, Düzce Belediye Başkanı Faruk Özlü de bölgeye gelerek çalışmalar hakkında bilgiler aldı. Başkan Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirterek, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Ama gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce'mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. İTFAİYE ERİ YARALANDI Öte yandan yangın söndürme çalışmalarında görev alan bir itfaiye eri ise, üzerine çatıdan parçaların düşmesi sonucu yaralandı. İtfaiye eri, sağlık ekibi tarafından ambulansla Düzce Atatürk Devlet Hastanesi’ne kaldırıldı. KONTROL ALTINA ALINDI Düzce’de kapı fabrikasında saat 21.30 sıralarında çıkan yangın, itfaiye ekiplerinin çalışmalarıyla saat 01.30 sıralarında kontrol altına alındı. Fabrikada soğutma çalışmaları sürerken, yangınla ilgili soruşturma başlatıldı. GÜNCELLEME 14.09.2026 - 02:15 Düzce Yangın Kapı Fabrikası İtfaiye Müdahalesi DETAYLARI GÖSTER PAYLAŞ Sitene Ekle Aşağıdaki kodu kopyalayıp sitenize ekleyebilirsiniz &lt;iframe src="https://www.milliyet.com.tr/video/embed/?vid=7659809&amp;resizable=1&amp;autostart=true" width="584px" height="326px" frameborder="0" scrolling="0" allow="autoplay; fullscreen" allowfullscreen&gt;&lt;/iframe&gt; Video Otomatik Olarak Başlasın Otomatik Boyut Genişlik: Yükseklik: X Sitene Ekle Aşağıdaki kodu kopyalayıp sitenize ekleyebilirsiniz &lt;iframe src="https://www.milliyet.com.tr/video/embed/?vid=7659809&amp;resizable=1&amp;autostart=true" width="584px" height="326px" frameborder="0" scrolling="0" allow="autoplay; fullscreen" allowfullscreen&gt;&lt;/iframe&gt; Video Otomatik Olarak Başlasın Otomatik Boyut Genişlik: Yükseklik: X Haberler Video Haberler Düzce’de kapı fabrikasında yangın Düzce’de kapı fabrikasında yangın Merkeze bağlı Hacialiler köyü mevkisinde bulunan kapı fabrikasında, saat 22.00 sıralarında yangın çıktı. Yangın kısa sürede büyüyerek fabrikayı sardı. İhbar üzerine bölgeye itfaiyeleri sevk edildi. İtfaiye erleri, yangına müdahale ederken Sakarya ve Bolu’dan da itfaiye ekipleri destek için bölgeye gönderildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. BAŞKAN ÖZLÜ: ÖNEMLİ OLAN CAN KAYBININ OLMAMASI Kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürerken, Düzce Belediye Başkanı Faruk Özlü de bölgeye gelerek çalışmalar hakkında bilgiler aldı. Başkan Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirterek, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Ama gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce'mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. Öte yandan yangın söndürme çalışmalarında görev alan bir itfaiye eri ise, üzerine çatıdan parçaların düşmesi sonucu yaralandı. İtfaiye eri, sağlık ekibi tarafından ambulansla Düzce Atatürk Devlet Hastanesi’ne kaldırıldı. Düzce’de kapı fabrikasında saat 21.30 sıralarında çıkan yangın, itfaiye ekiplerinin çalışmalarıyla saat 01.30 sıralarında kontrol altına alındı. Fabrikada soğutma çalışmaları sürerken, yangınla ilgili soruşturma başlatıldı.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği egetelgraf.com 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi Güncel 8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği 8 ilde yasa dışı bahis operasyonu düzenlendi. MASAK raporlarıyla yapılan incelemelerde, 177 şüphelinin hesaplarında toplam 17 milyar 750 milyon liralık para hareketliliği tespit edildi</t>
+          <t>Düzce’de kapı fabrikasında yangın Düzce’de kapı fabrikasında yangın Milliyet Düzce’de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yoğun müdahalesi sonrası yangın kontrol altına alındı. Düzce’de faaliyet gösteren kapı üretim fabrikas... 00:37 İstanbul'da orman yangını! Alevlere havadan müdahale başladı 01:44 Piyasalarda haftanın kazananı ve kaybedeni belli oldu! Altın yatırımcısı dikkat 02:05 AK Parti Sözcüsü Çelik’ten Özgür Özel’e sert tepki: Kendisini siyaset adabına davet ediyoruz 02:33 Teoman gerçeği öğrenecek mi? 01:02 İstanbul Havalimanı’nın yeni pisti için geri sayım... 00:25 Vanlı Kara Haydar'ın eşi Çağla Öz'le ilgili yeni gelişme 03:59 Serhat kaderini kendi çizdi 00:52 İstanbul’da kiralık TOKİ evleri için başvurular yarın başlıyor! İstanbul’da hava değişiyor: AKOM saat verdi 02:49 Dev çekirgeler Van’ı sardı! Boyları 20 santimetreye yaklaşabiliyor: Bizi tedirgin ediyor 01:08 Genel müdürünün sözleriyle hayatı değişti! Kurumsal kariyerini bıraktı, Ironman şampiyonu oldu 00:45 2026 Yılı Kırsal Kalkınma Yatırım Programı başvuru sonuçları açıklandı 00:12 'Ailem Güvende' operasyonu! 15 ilde düğmeye basıldı: 162 şüpheli hakkında adli işlem 00:43 Deniz Türüç, TFF Temsilcisiyle tartıştı 00:13 Sanal medya ünlüsü Semih Varol gözaltına alındı 03:10 100 yaşındaki Ali Gül uzun yaşamın sırrını açıkladı! 'Ömrümde doktora sadece bir kere gittim' 00:25 Tarım işçilerini taşıyan minibüs, park halindeki traktöre çarptı! 10 kişinin yaralandığı kaza kamerada 00:09 'Vanlı Kara Haydar’ Mehmet Fatih Tançalan’ın eşi Çağla Öz İstanbul’da gözaltına alındı 00:57 AK Parti'nin 25. yılına özel 'Türkiye Bülteni' yayımlandı 03:57 Arif Ahmet Denizolgun'un ölümüne ilişkin soruşturma! Tanıktan şoke eden ifade: Beni belki de zehirlerler 02:42 İlim Yayma Vakfı Mütevelli Heyeti Başkanı Bilal Erdoğan: İyiliğin egemen geleceği bir dünyada yaşamak mümkün 00:27 Mardin’de TEKNOFEST İnsansız Kara Aracı Yarışması tamamlandı 03:01 Kiracıları tarafından öldürülen ev sahibi çift son yolculuğuna uğurlandı: Geride 5 yetim çocuk bıraktı 01:40 İstanbul Bahçelievler'de 5 katlı binanın istinat duvarı çöktü 01:53 Cemre Baysel: İlk bölümümüz şahane ; Oynatma Listesi HABERLER Düzce’de kapı fabrikasında yangın Düzce ’de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. Merkeze bağlı Hacialiler köyü mevkisinde bulunan kapı fabrikasında, saat 22.00 sıralarında yangın çıktı. Yangın kısa sürede büyüyerek fabrikayı sardı. İtfaiye erleri, yangına müdahale ederken Sakarya ve Bolu’dan da itfaiye ekipleri destek için bölgeye gönderildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. BAŞKAN ÖZLÜ: ÖNEMLİ OLAN CAN KAYBININ OLMAMASI Kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürerken, Düzce Belediye Başkanı Faruk Özlü de bölgeye gelerek çalışmalar hakkında bilgiler aldı. Başkan Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirterek, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce'mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. İTFAİYE ERİ YARALANDI Öte yandan yangın söndürme çalışmalarında görev alan bir itfaiye eri ise, üzerine çatıdan parçaların düşmesi sonucu yaralandı. İtfaiye eri, sağlık ekibi tarafından ambulansla Düzce Atatürk Devlet Hastanesi’ne kaldırıldı. KONTROL ALTINA ALINDI Düzce’de kapı fabrikasında saat 21.30 sıralarında çıkan yangın, itfaiye ekiplerinin çalışmalarıyla saat 01.30 sıralarında kontrol altına alındı. Fabrikada soğutma çalışmaları sürerken, yangınla ilgili soruşturma başlatıldı. GÜNCELLEME 14.09.2026 - 02:15 Düzce Yangın Kapı Fabrikası İtfaiye Müdahalesi DETAYLARI GÖSTER PAYLAŞ Sitene Ekle Aşağıdaki kodu kopyalayıp sitenize ekleyebilirsiniz &lt;iframe src="https://www.milliyet.com.tr/video/embed/?vid=7659809&amp;resizable=1&amp;autostart=true" width="584px" height="326px" frameborder="0" scrolling="0" allow="autoplay; fullscreen" allowfullscreen&gt;&lt;/iframe&gt; Video Otomatik Olarak Başlasın Otomatik Boyut Genişlik: Yükseklik: X Sitene Ekle Aşağıdaki kodu kopyalayıp sitenize ekleyebilirsiniz &lt;iframe src="https://www.milliyet.com.tr/video/embed/?vid=7659809&amp;resizable=1&amp;autostart=true" width="584px" height="326px" frameborder="0" scrolling="0" allow="autoplay; fullscreen" allowfullscreen&gt;&lt;/iframe&gt; Video Otomatik Olarak Başlasın Otomatik Boyut Genişlik: Yükseklik: X Haberler Video Haberler Düzce’de kapı fabrikasında yangın Düzce’de kapı fabrikasında yangın Merkeze bağlı Hacialiler köyü mevkisinde bulunan kapı fabrikasında, saat 22.00 sıralarında yangın çıktı. Öte yandan yangın söndürme çalışmalarında görev alan bir itfaiye eri ise, üzerine çatıdan parçaların düşmesi sonucu yaralandı. Düzce’de kapı fabrikasında saat 21.30 sıralarında çıkan yangın, itfaiye ekiplerinin çalışmalarıyla saat 01.30 sıralarında kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -3099,33 +3285,61 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>https://www.egetelgraf.com/8-ilde-yasa-disi-bahis-operasyonu-masak-raporu-ortaya-cikardi-17-milyar-750-milyon-tllik-para-trafigi</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>https://www.milliyet.com.tr/milliyet-tv/duzcede-kapi-fabrikasinda-yangin-video-7659809</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Bolu | Düzce | İstanbul | Mardin</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Bahçelievler</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Yangın Kapı Fabrikası</t>
+        </is>
+      </c>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
+          <t>firma yok</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Yangın Kapı Fabrikası Bahçelievler Bolu Türkiye</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>KZB Yangın Söndürme Sistemleri | KÖROĞLU ELEKTRİK, YANGIN, HAVALANDIRMA, OTOMASYON SİSTEMLERİ | KZB - Bolu Yangın Söndürme Sistemleri</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>KZB Yangın Söndürme Sistemleri</t>
+        </is>
+      </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>47.05882352941177 | 44.44444444444444 | 44.44444444444444</t>
+        </is>
+      </c>
       <c r="Z5" s="2" t="inlineStr"/>
       <c r="AA5" s="2" t="n">
-        <v>112.75</v>
+        <v>144</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>4</v>
@@ -3134,27 +3348,27 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:19:31</t>
+          <t>2026-09-13 19:18:13</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>para aklama</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti!</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! Düzce Gazete Efsane</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -3164,44 +3378,52 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn</t>
+          <t>Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi. Vietnam.vn Çinli adam bankaya yatırdığı parayla dolu iki bavul taşıyordu ama parayı geri götüremedi.</t>
+          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! Düzce Gazete Efsane Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWUdoUHJCRWZaZEdNanVFWHRsZFp3QnNMNWlEeWI0X3p4MEJSalFXY1YxcDN2cUNETm5tdl90cGpaVVJtSkp2WXRJajd6THVlNk9pOU5PODNLTl9KQXhhbV9QMTAxNmdrVTYtS09EZXR4N0lfci10azVOUjRINFJ2OE53enFLM3NpbXc4dlRDUkpTcF9aekFrNVNuaWRfUEhvNk5POXVJMkxhRlJaSkFfNA?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>https://www.duzcegazeteefsane.com/asayis-duzce-haberleri/15389-duzcede-gece-yarisi-korku-dolu-anlar:-fabrikada-cikan-yangin-gokyuzunu-alevlere-teslim-etti!</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Kısa sürede tüm tesisi</t>
+        </is>
+      </c>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr"/>
@@ -3215,7 +3437,7 @@
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr"/>
       <c r="AA6" s="2" t="n">
-        <v>76.5</v>
+        <v>129.57</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>5</v>
@@ -3224,27 +3446,27 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:33:00</t>
+          <t>2026-09-13 21:12:00</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>para aklama</t>
+          <t>tesis yangını</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı surmelihaber.com</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -3254,22 +3476,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>banka, banka hesabı</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Yozgat Bozok Üniversitesi Ziraat Fakültesi Dekanlığı, son dönemde üniversite öğrencilerini hedef alan banka hesabı ve IBAN dolandırıcılığı vakalarındaki artışa dikkat çekerek öğrencilere yasal uyarıda bulundu. Yozgat Bozok Üniversitesi Ziraat Fakültesi Dekanlığı, son dönemde üniversite öğrencilerini hedef alan banka hesabı ve IBAN dolandırıcılığı vakalarındaki artışa dikkat çekerek öğrencilere yasal uyarıda bulundu. Yozgat Bozok Üniversitesi Ziraat Fakültesi Dekanlığı, son dönemde üniversite öğrencilerini hedef alan banka hesabı ve IBAN dolandırıcılığı vakalarındaki artışa dikkat çekerek öğrencilere yasal uyarıda bulundu.</t>
+          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Val... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. 5 SAAT SÜREN ZORLU MÜCADELE Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı 5 SAAT SÜREN ZORLU MÜCADELE BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. 13 Eyl 2026 - 12:55 Bolu - Asayiş Yazdır Yorum yazarak Bolu Gündem Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yorumlarda</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı Yozgat Bozok Üniversitesinden Banka Hesabı Dolandırıcılığı Uyarısı surmelihaber.com Yozgat Bozok Üniversitesi Ziraat Fakültesi Dekanlığı, son dönemde üniversite öğrencilerini hedef alan banka hesabı ve IBAN dolandırıcılığı vakalarındaki artışa dikkat çekerek öğrencilere yasal uyarıda bulundu.</t>
+          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. 5 SAAT SÜREN ZORLU MÜCADELE Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı 5 SAAT SÜREN ZORLU MÜCADELE BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. 13 Eyl 2026 - 12:55 Bolu - Asayiş Yazdır Yorum yazarak Bolu Gündem Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -3279,33 +3501,69 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>https://surmelihaber.com/gundem/yozgat-bozok-universitesinden-banka-hesabi-dolandiriciligi-uyarisi-25494h</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
+          <t>https://www.bolugundem.com/haber/28691580/boluda-5-saatlik-yangin-kabusu-geri-donusum-fabrikasi-alevlere-teslim-oldu-3-kisi-yaralandi</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Gerede</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>00 sıralarında Karma Organize Sanayi</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Geri dönüşüm fabrikası | başlayan ve tesisi</t>
+        </is>
+      </c>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
+          <t>firma yok</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>Geri dönüşüm fabrikası 00 sıralarında Karma Organize Sanayi Gerede Bolu Türkiye</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>İlamet Metal Ltd Şti | Nova Orman Ürünleri - Bolu Fabrika | Gerede Deri Sanayi Sitesi</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>İlamet Metal Ltd Şti</t>
+        </is>
+      </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>35.8974358974359 | 51.851851851851855 | 37.2093023255814</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>Gerede Organize Sanayi Bölgesi | Gerede Deri İhtisas OSB</t>
+        </is>
+      </c>
       <c r="AA7" s="2" t="n">
-        <v>66.04000000000001</v>
+        <v>220.5</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>6</v>
@@ -3314,12 +3572,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:18:13</t>
+          <t>2026-09-14 09:11:00</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3329,12 +3587,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti!</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! duzcegazeteefsane.com</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -3344,22 +3602,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd</t>
+          <t>Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Demirtaş Mahallesi'nde saman deposu yangını Alanya'nın Demirtaş Mahallesi'ndeki bir depolama alanında çıkan yangında çok sayıda saman balyası yandı. İtfaiyenin müdahalesiyle alevler söndürüldü. 14.09.2026 - 12:11 Yayınlanma Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Alanya’da 75 bin öğrenci derslere başlıyor İçeriği Görüntüle Alanya'nın Demirtaş Mahallesi'nde yer alan bir saman depolama alanında henüz belirlenemeyen bir nedenle yangın çıktı. Çevredekilerin ihbarı üzerine, olay yerine hızla Antalya Büyükşehir Belediyesi Alanya İtfaiye Müdürlüğü ekipleri sevk edildi. İtfaiye personelinin zamanında müdahalesi sayesinde alevler daha geniş bir alana yayılmadan kontrol altına alındı. Yerel haber kaynaklarının aktardığına göre, söndürme işlemlerinin ardından depolama alanında bulunan çok sayıda saman balyası yandı. SOĞUTMA VE İNCELEME SÜRECİ BAŞLADI Bölgede alevlerin tamamen bastırılmasının ardından itfaiye ekipleri tarafından bir süre daha soğutma çalışmaları gerçekleştirildi. Yangının tam olarak hangi sebeple başladığını tespit etmek amacıyla ilgili birimler tarafından resmi inceleme süreci başlatıldı. TARIMSAL DEPOLAMADA GÜVENLİK ÖNLEMİ Saman balyası gibi kuru tarım ürünlerinin istiflendiği alanlar, materyalin yapısı gereği yüksek tutuşma potansiyeli barındırıyor. Bu tür depolama noktalarında yeterli havalandırmanın sağlanması ve temel yangın söndürme teçhizatının bulundurulması, olası maddi kayıpların büyümesini engellemek için standart bir gereksinim olarak öne çıkıyor. Kaynak: Haber Merkezi Editörün Seçtiği Antalya S Tipi Cezaevi'nde işkence iddiası Meclis'e taşındı Editörün Seçtiği 5 milyon TL’de mevduat ve konut hesabı değişti Editörün Seçtiği 10 Yaşındaki İki Arkadaş Limonata Satarak Harçlık Biriktiriyor Bunlar da</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! duzcegazeteefsane.com Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd Düzce'de faaliyet gösteren bir fabrikada henüz belirlenemeyen bir sebepten dolayı alevler yükseldi. Kısa sürede tüm tesisi saran yangın, gecenin karanlığını ayd</t>
+          <t>Demirtaş Mahallesi'nde saman deposu yangını Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Demirtaş Mahallesi'nde saman deposu yangını Alanya'nın Demirtaş Mahallesi'ndeki bir depolama alanında çıkan yangında çok sayıda saman balyası yandı. İtfaiyenin müdahalesiyle alevler söndürüldü. 14.09.2026 - 12:11 Yayınlanma P</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -3369,41 +3627,69 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>https://www.duzcegazeteefsane.com/asayis-duzce-haberleri/15389-duzcede-gece-yarisi-korku-dolu-anlar:-fabrikada-cikan-yangin-gokyuzunu-alevlere-teslim-etti!</t>
+          <t>https://www.yenialanya.com/demirtas-mahallesinde-saman-deposu-yangini</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Düzce</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
+          <t>Antalya | Bursa</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Alanya</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş | Demirtaş Mahallesi | saman deposu yangını Demirtaş Mahallesi | Yeni Alanya Alanya Demirtaş Mahallesi | nın Demirtaş Mahallesi</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Kısa sürede tüm tesisi</t>
+          <t>nde saman deposu</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr"/>
-      <c r="V8" s="2" t="inlineStr"/>
-      <c r="W8" s="2" t="inlineStr"/>
+          <t>firma yok</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>nde saman deposu Demirtaş Alanya Antalya Türkiye</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Toptancı Hali | Demirtaş Mermer</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Demirtaş Toptancı Hali</t>
+        </is>
+      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr"/>
+          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>36.8421052631579 | 38.70967741935484</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>ALANYA BELEDİYESİ DEMİRTAŞ HAYVAN BARINAĞI</t>
+        </is>
+      </c>
       <c r="AA8" s="2" t="n">
-        <v>130.07</v>
+        <v>174.25</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>7</v>
@@ -3412,12 +3698,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:12:00</t>
+          <t>2026-09-13 20:07:54</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3427,12 +3713,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın turizmaktuel.com</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -3442,94 +3728,62 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo, turizm</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Val... Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. 5 SAAT SÜREN ZORLU MÜCADELE Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı 5 SAAT SÜREN ZORLU MÜCADELE BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. 13 Eyl 2026 - 12:55 Bolu - Asayiş Yazdır Yorum yazarak Bolu Gündem Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yorumlarda</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın turizmaktuel.com</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Valilik 3 kişinin yaralandığını duyurdu. Bolu'nun Gerede ilçesinde dün saat 19.00 sıralarında Karma Organize Sanayi Bölgesi'ndeki (OSB) bir geri dönüşüm fabrikasında başlayan ve tesisi alev topuna çeviren büyük yangın, itfaiye ekiplerinin yaklaşık 5 saat süren yoğun mücadelesi sonucu kontrol altına alındı. Bolu Valiliği'nden yapılan resmi açıklamaya göre, zaman zaman patlamaların da yaşandığı olayda üç kişi yaralandı. 5 SAAT SÜREN ZORLU MÜCADELE Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Gökyüzünü kaplayan yoğun duman ve art arda duyulan patlama sesleri üzerine bölgeye çok sayıda itfaiye, jandarma ve sağlık ekibi sevk edildi. Ekiplerin alevleri kırmak ve yangının çevre tesislere sıçramasını önlemek için başlattığı yoğun çalışma yaklaşık 5 saat boyunca kesintisiz devam etti. BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaralı işçi, olay yerinde bekleyen ambulanslarda yapılan ilk müdahalenin ardından hastaneye sevk edildi. İlerleyen saatlerde Bolu Valiliği tarafından yapılan resmi açıklamada, yangının tamamen kontrol altın a alındığı müjdelenirken, olayda 2 kişinin daha yaralandığı ve toplam yaralı sayısının 3'e yükseldiği bildirildi. TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. Dev alevlerin kırılmasının ardından itfaiye ekipleri, içten yanma ve yeniden alevlenme riskine karşı bölgede kapsamlı bir söndürme ve soğutma çalışması yürütülürdü. Jandarma ekipleri çevredeki güvenlik önlemlerini sürdürürken, yangının kesin çıkış nedenini belirlemek üzere geniş çaplı bir soruşturma başlatıldı. Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı 5 SAAT SÜREN ZORLU MÜCADELE BOLU VALİLİĞİ'NDEN YARALI AÇIKLAMASI TESİS AĞIR HASAR ALDI, SOĞUTMA ÇALIŞMALARI SÜRÜYOR Bolu'nun Gerede ilçesindeki geri dönüşüm tesisinde saat 19.00'da başlayan ve patlamalara sahne olan dev yangın, 5 saatlik mücadeleyle kontrol altına alındı. Akşam saat 19.00 sularında tesis içerisinde henüz belirlenemeyen bir nedenle başlayan alevler, içerideki malzemelerin de etkisiyle kısa sürede büyüyerek fabrikanın büyük bir bölümünü sardı. Yangının ilk anlarında alevlere müdahale etmeye çalışan 1 fabrika işçisi hafif şekilde yaralandı. Yaklaşık 5 saat alev alev yanan geri dönüşüm fabrikasında büyük çapta maddi hasar meydana geldi. 13 Eyl 2026 - 12:55 Bolu - Asayiş Yazdır Yorum yazarak Bolu Gündem Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
+          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın turizmaktuel.com Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın turizmaktuel.com</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bolugundem.com/haber/28691580/boluda-5-saatlik-yangin-kabusu-geri-donusum-fabrikasi-alevlere-teslim-oldu-3-kisi-yaralandi</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQNERNUWxFV2dtNG4tQXdUdzNTQmJDb2o1bWVWTkZpdGZucEFCbW9FWXl2UkNLZzZRRDV6XzI5WkU5MVBqMUIwZ2QxN1ZUU0MxYkpOOXRFMTFFN3FzMVB2SlhTNHRLcFk3dVlER3FPYmhrSm9PZi1QY09JdTl0bXo4VDNmMHo3ekFUSlFYcXEtM295aGt2NUE?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>00 sıralarında Karma Organize Sanayi</t>
-        </is>
-      </c>
+          <t>Antalya</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Geri dönüşüm fabrikası | başlayan ve tesisi</t>
-        </is>
-      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>Geri dönüşüm fabrikası 00 sıralarında Karma Organize Sanayi Gerede Bolu Türkiye</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Nova Orman Ürünleri - Bolu Fabrika | İlamet Metal Ltd Şti | An-Ker-San Kereste Fabrikası Gerede OSB</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Nova Orman Ürünleri - Bolu Fabrika</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>51.851851851851855 | 35.8974358974359 | 58.064516129032256</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>Gerede Organize Sanayi Bölgesi | Gerede Deri İhtisas OSB</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" s="2" t="n">
-        <v>220.5</v>
+        <v>64.98</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>8</v>
@@ -3538,12 +3792,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:45:00</t>
+          <t>2026-09-14 10:17:58</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>depo yangını</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3553,12 +3807,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi</t>
+          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber</t>
+          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı bolgegundemi.com</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -3568,22 +3822,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>depo</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. 13 Eylül 2026 - 22:45 - Güncellenme: 13 Eylül 2026 - 23:29 G: 13 Eylül 2026 - 23:29 Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. Editör Haber Merkezi 0 Paylaşım 0 Paylaşım Google Kaynaklara Ekle A − A + Düzce'de Door Kapı Fabrikası'nda çıkan yangın fabrikanın geniş bir bölümüne yayıldı. Yangının büyüklüğü nedeniyle Düzce'nin ilçelerinden itfaiye ekipleri bölgeye yönlendirilirken, Bolu'dan da takviye ekip sevk edildi. Edinilen bilgilere göre yangın saat 21.40 sıralarında henüz belirlenemeyen bir nedenle çıktı. Kısa sürede yayılan alevlerin ardından bölgeye çok sayıda itfaiye, sağlık ve güvenlik ekibi gönderildi. Bolu'dan takviye ekip sevk edildi Yangının geniş bir alana yayılması üzerine Düzce'nin ilçelerindeki itfaiye ekipleri de bölgeye yönlendirildi. Söndürme çalışmalarına destek amacıyla Bolu'dan takviye ekip sevk edildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. Yangının boyutu dronla görüntülendi Door Kapı Fabrikası'ndaki yangın dronla havadan görüntülendi. Havadan kaydedilen görüntülerde fabrikanın büyük bölümünü saran alevler ile bölgeden yükselen yoğun duman yer aldı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Yangının çıkış nedeninin, söndürme çalışmalarının ardından yapılacak incelemeyle belirlenmesi bekleniyor. Düzce / Merkez #düzce yangın #düzce fabrika yangını #düzce door yangın Y</t>
+          <t>www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. 13 Eylül 2026 - 22:45 - Güncellenme: 13 Eylül 2026 - 23:29 G: 13 Eylül 2026 - 23:29 Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi.</t>
+          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı bolgegundemi.com www.bolgegundemi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.bolgegundemi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -3593,27 +3847,23 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>https://www.duzcehurhaber.com/duzcede-kapi-fabrikasinda-buyuk-yangin-alevler-sehrin-ust-kesimlerinden-goruldu-4205470</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
+          <t>https://www.bolgegundemi.com/antalya/alanyadaki-saman-deposu-yangini-sonrasi-resmi-inceleme-baslatildi-178510.html</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>deki Door Kapı Fabrikası</t>
+          <t>daki Saman Deposu</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
+          <t>il yok | ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr"/>
@@ -3627,7 +3877,7 @@
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
       <c r="AA10" s="2" t="n">
-        <v>119.25</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>9</v>
@@ -3636,27 +3886,27 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:41:26</t>
+          <t>2026-09-14 12:09:13</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü</t>
+          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü kocatepegazetesi.com</t>
+          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu İlke TV</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -3666,40 +3916,32 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>tesis</t>
+          <t>el konuldu, mal varlığı</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Haberler Asayiş Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. asayiş PAYLAŞ 13.09.2026 14:41 Güncelleme: 13.09.2026 14:41 İHA İhlas Haber Ajansı TAKİP ET Kocatepe Gazetesi kaynağını Google'da tercih edilen kaynak olarak ekleyin! Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. asayiş İHA PAYLAŞ İlk Yorum Yazan Sen Ol! Kocatepe Gazetesi - Bizi Sosyal Medyada Takip Edin! Facebook X.com Instagram Bakmadan Geçme Başkan Demirci’den ‘Öğretmen Emeği’ Vurgusu Başkan Arslan Takdir Etti; Taleplerini Gündeme Getirdi Bilgi Ailesinin Acı Günü: Hasibe Bilgi Vefat Etti Afyon'un Komşusu O İlde Milletvekili Vali'den Şikayetçi: Vekil Ankara'dan Koruma Talep Etti Afyon'da Seçim Gündemi Hareketleniyor. Ticaret Borsası'nda Mühsürler'e Muhalif Hareketlenme Okullar Açılırken Önemli Uyarı: Bu Ürünler Denetlenmeli Haberler Asayiş Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. asayiş PAYLAŞ 13.09.2026 14:41 Güncelleme: 13.09.2026 14:41 İHA İhlas Haber Ajansı TAKİP ET Kocatepe Gazetesi kaynağını Google'da tercih edilen kaynak olarak ekleyin! Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. asayiş İHA PAYLAŞ İlk Yorum Yazan Sen Ol! Kocatepe Gazetesi - Bizi Sosyal Medyada Takip Edin! Facebook X.com Instagram Bakmadan Geçme Başkan Demirci’den ‘Öğretmen Emeği’ Vurgusu Başkan Arslan Takdir Etti; Taleplerini Gündeme Getirdi Bilgi Ailesinin Acı Günü: Hasibe Bilgi Vefat Etti Afyon'un Komşusu O İlde Milletvekili Vali'den Şikayetçi: Vekil Ankara'dan Koruma Talep Etti Afyon'da Seçim Gündemi Hareketleniyor. Ticaret Borsası'nda Mühsürler'e Muhalif Hareketlenme Okullar Açılırken Önemli Uyarı: Bu Ürünler Denetlenmeli Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü https://www.kocatepegazetesi.com/geri-donusum-tesisinde-korkutan-yangin-alevler-buyumeden-sonduruldu/409832/ Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. Yukarıdaki arama formları aracılığı ile Kocatepe Gazetesi arşivinde kelime, içerik, konu araması yapabilir veya gün-ay-yıl formatında tarih girerek tarihe göre haberleri listeleyebilirsiniz.</t>
+          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu İlke TV</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü kocatepegazetesi.com Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Haberler Asayiş Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü Eskişehir'de bir geri dönüşüm tesisinde çıkan yangın, itfaiye ekiplerinin müdahalesiyle kontrol altına alınarak söndürüldü. Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Tesis içerisinden yükselen dumanları görenlerin ihbarı üzerine bölgeye polis ve itfaiye ekipleri sevk edildi. Olay yerine gelen Eskişehir Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı ekipleri alevlere hızla müdahale etti. Ekiplerin yürüttüğü çalışma sonucunda yangın diğer alanlara sıçramadan kontrol altına alınarak tamamen söndürüldü. Yangının çıkış nedeninin belirlenmesi için inceleme başlatıldı. Facebook X.com Instagram Bakmadan Geçme Başkan Demirci’den ‘Öğretmen Emeği’ Vurgusu Başkan Arslan Takdir Etti; Taleplerini Gündeme Getirdi Bilgi Ailesinin Acı Günü: Hasibe Bilgi Vefat Etti Afyon'un Komşusu O İlde Milletvekili Vali'den Şikayetçi: Vekil Ankara'dan Koruma Talep Etti Afyon'da Seçim Gündemi Hareketleniyor. Ticaret Borsası'nda Mühsürler'e Muhalif Hareketlenme Okullar Açılırken Önemli Uyarı: Bu Ürünler Denetlenmeli Haberler Asayiş Geri Dönüşüm Tesisinde Korkutan Yangın! Ticaret Borsası'nda Mühsürler'e Muhalif Hareketlenme Okullar Açılırken Önemli Uyarı: Bu Ürünler Denetlenmeli Geri Dönüşüm Tesisinde Korkutan Yangın! Alevler Büyümeden Söndürüldü https://www.kocatepegazetesi.com/geri-donusum-tesisinde-korkutan-yangin-alevler-buyumeden-sonduruldu/409832/ Edinilen bilgilere göre; kentte faaliyet gösteren bir geri dönüşüm tesisinde henüz belirlenemeyen bir nedenle yangın çıktı. Geri Dönüşüm Tesisinde Korkutan Yangın!</t>
+          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu İlke TV İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu İlke TV</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>https://www.kocatepegazetesi.com/geri-donusum-tesisinde-korkutan-yangin-alevler-buyumeden-sonduruldu/409832/</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Ankara | Eskişehir | Manisa</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Demirci</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPVDAwVHJ6dGFnTkl2NGxnNzdCb0JqNjRoLVF3eG5wcHIxRTc3cF9aeFVSTDI3RGNYNnM1bzJxbTJzdkcwdXlUNjRvbkk3U3AzOVJnUVByamVoMHlxaWZVQWd0NDY1YmJaalRtNWlOd0lVaUttZDByZjROUVlUS215VTRlSzRlT2hJYlpwbW1aMkVuVEIxTEF5bllrSGpRMXhhZ0pN?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -3707,7 +3949,7 @@
       <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr"/>
@@ -3721,7 +3963,7 @@
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" s="2" t="n">
-        <v>115.25</v>
+        <v>68.88</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>10</v>
@@ -3730,27 +3972,27 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:11:00</t>
+          <t>2026-09-14 11:18:00</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>kara para</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Demirtaş Mahallesi'nde saman deposu yangını</t>
+          <t>Vanlı Kara Haydar'ın akılalmaz görüntüsü ortaya çıktı! Bankada bile bu kadar para yoktur</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya</t>
+          <t>Vanlı Kara Haydar'ın akılalmaz görüntüsü ortaya çıktı! Bankada bile bu kadar para yoktur Halk TV</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -3760,22 +4002,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Demirtaş Mahallesi'nde saman deposu yangını Alanya'nın Demirtaş Mahallesi'ndeki bir depolama alanında çıkan yangında çok sayıda saman balyası yandı. İtfaiyenin müdahalesiyle alevler söndürüldü. 14.09.2026 - 12:11 Yayınlanma Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Alanya’da 75 bin öğrenci derslere başlıyor İçeriği Görüntüle Alanya'nın Demirtaş Mahallesi'nde yer alan bir saman depolama alanında henüz belirlenemeyen bir nedenle yangın çıktı. Çevredekilerin ihbarı üzerine, olay yerine hızla Antalya Büyükşehir Belediyesi Alanya İtfaiye Müdürlüğü ekipleri sevk edildi. İtfaiye personelinin zamanında müdahalesi sayesinde alevler daha geniş bir alana yayılmadan kontrol altına alındı. Yerel haber kaynaklarının aktardığına göre, söndürme işlemlerinin ardından depolama alanında bulunan çok sayıda saman balyası yandı. SOĞUTMA VE İNCELEME SÜRECİ BAŞLADI Bölgede alevlerin tamamen bastırılmasının ardından itfaiye ekipleri tarafından bir süre daha soğutma çalışmaları gerçekleştirildi. Yangının tam olarak hangi sebeple başladığını tespit etmek amacıyla ilgili birimler tarafından resmi inceleme süreci başlatıldı. TARIMSAL DEPOLAMADA GÜVENLİK ÖNLEMİ Saman balyası gibi kuru tarım ürünlerinin istiflendiği alanlar, materyalin yapısı gereği yüksek tutuşma potansiyeli barındırıyor. Bu tür depolama noktalarında yeterli havalandırmanın sağlanması ve temel yangın söndürme teçhizatının bulundurulması, olası maddi kayıpların büyümesini engellemek için standart bir gereksinim olarak öne çıkıyor. Kaynak: Haber Merkezi Editörün Seçtiği Antalya S Tipi Cezaevi'nde işkence iddiası Meclis'e taşındı Editörün Seçtiği 5 milyon TL’de mevduat ve konut hesabı değişti Editörün Seçtiği 10 Yaşındaki İki Arkadaş Limonata Satarak Harçlık Biriktiriyor Bunlar da</t>
+          <t>“Vanlı Kara Haydar” lakaplı Mehmet Fatih Tançalan’ın döviz desteleri ve para balyalarıyla çekildiği öne sürülen yeni görüntüleri ortaya çıktı. “Vanlı Kara Haydar” lakaplı Mehmet Fatih Tançalan’ın döviz desteleri ve para balyalarıyla çekildiği öne sürülen yeni görüntüleri ortaya çıktı. “Vanlı Kara Haydar” lakaplı Mehmet Fatih Tançalan’ın döviz desteleri ve para balyalarıyla çekildiği öne sürülen yeni görüntüleri ortaya çıktı.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Demirtaş Mahallesi'nde saman deposu yangını Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya Alanya Demirtaş Mahallesi’nde saman deposunda çıkan yangında çok sayıda balya yandı. Antalya BB itfaiyesi alevleri söndürdü, inceleme başladı. Demirtaş Mahallesi'nde saman deposu yangını Alanya'nın Demirtaş Mahallesi'ndeki bir depolama alanında çıkan yangında çok sayıda saman balyası yandı. İtfaiyenin müdahalesiyle alevler söndürüldü. 14.09.2026 - 12:11 Yayınlanma P</t>
+          <t>Vanlı Kara Haydar'ın akılalmaz görüntüsü ortaya çıktı! Bankada bile bu kadar para yoktur Vanlı Kara Haydar'ın akılalmaz görüntüsü ortaya çıktı! Bankada bile bu kadar para yoktur Halk TV “Vanlı Kara Haydar” lakaplı Mehmet Fatih Tançalan’ın döviz desteleri ve para balyalarıyla çekildiği öne sürülen yeni görüntüleri ortaya çıktı.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -3785,65 +4027,33 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>https://www.yenialanya.com/demirtas-mahallesinde-saman-deposu-yangini</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Antalya | Bursa</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Alanya</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Demirtaş | Demirtaş Mahallesi | saman deposu yangını Demirtaş Mahallesi | Yeni Alanya Alanya Demirtaş Mahallesi | nın Demirtaş Mahallesi</t>
-        </is>
-      </c>
+          <t>https://halktv.com.tr/turkiye/vanli-kara-haydarin-akilalmaz-goruntusu-ortaya-cikti-bankada-bile-bu-kadar-para-yoktur-1054959h</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>nde saman deposu</t>
-        </is>
-      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="2" t="inlineStr"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>firma yok</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>nde saman deposu Demirtaş Alanya Antalya Türkiye</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Demirtaş Toptancı Hali</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>Demirtaş Toptancı Hali</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>36.8421052631579</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
       <c r="AA12" s="2" t="n">
-        <v>174.25</v>
+        <v>78.28</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>11</v>
@@ -3852,27 +4062,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:07:54</t>
+          <t>2026-09-14 11:11:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>MASAK</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın</t>
+          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Turizm Aktüel</t>
+          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -3882,22 +4092,18 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>depo, turizm</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>depo</t>
-        </is>
-      </c>
+          <t>masak</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Antalya’da ambalaj ürünlerinin bulunduğu bir depoda çıkan yangın, bitişiğindeki depolar ile yakındaki bir eve sıçradı. Yaklaşık 2 saatte büyük ölçüde kontrol altına alınan yangında 5 depodaki ürünler yanarken, depo sahibi Arif Ordu, "Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. Antalya’da ambalaj ürünlerinin bulunduğu bir depoda çıkan yangın, bitişiğindeki depolar ile yakındaki bir eve sıçradı. Yaklaşık 2 saatte büyük ölçüde kontrol altına alınan yangında 5 depodaki ürünler yanarken, depo sahibi Arif Ordu, "Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. Antalya’da ambalaj ürünlerinin bulunduğu bir depoda çıkan yangın, bitişiğindeki depolar ile yakındaki bir eve sıçradı. Yaklaşık 2 saatte büyük ölçüde kontrol altına alınan yangında 5 depodaki ürünler yanarken, depo sahibi Arif Ordu, "Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi. Turizm Aktüel -</t>
+          <t>Van’da “Vanlı Kara Haydar” lakabıyla tanınan Mehmet Fatih Tançalan hakkında yürütülen malvarlığı soruşturması sürerken yeni görüntüler ortaya çıktı. Görüntülerde Tançalan’ın, farklı para birimlerinden oluşan çok sayıda döviz destesinin bulunduğu bir ortamda olduğu görülüyor.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın Turizm Aktüel Antalya’da ambalaj ürünlerinin bulunduğu bir depoda çıkan yangın, bitişiğindeki depolar ile yakındaki bir eve sıçradı. Yaklaşık 2 saatte büyük ölçüde kontrol altına alınan yangında 5 depodaki ürünler yanarken, depo sahibi Arif Ordu, "Maddi kaybımız çok büyük, can kaybımız yok ona şükrediyoruz" dedi.</t>
+          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor Yeniçağ Gazetesi Van’da “Vanlı Kara Haydar” lakabıyla tanınan Mehmet Fatih Tançalan hakkında yürütülen malvarlığı soruşturması sürerken yeni görüntüler ortaya çıktı. Görüntülerde Tançalan’ın, farklı para birimlerinden oluşan çok sayıda döviz destesinin bulunduğu bir ortamda olduğu görülüyor.</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -3907,12 +4113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.turizmaktuel.com/haber/antalya-da-otel-malzemelerinin-bulundugu-5-depoda-yangin</t>
+          <t>https://www.yenicaggazetesi.com/kara-haydarin-bu-kezde-dolar-goruntuleri-ortaya-cikti-masak-115-milyonu-izliyor-1071680h.htm</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Antalya</t>
+          <t>Van</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
@@ -3937,7 +4143,7 @@
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
       <c r="AA13" s="2" t="n">
-        <v>72.68000000000001</v>
+        <v>93.75</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>12</v>
@@ -3946,27 +4152,27 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:20:22</t>
+          <t>2026-09-14 06:55:51</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>sahtecilik</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Dakika</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -3976,22 +4182,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Güncelleme: 13.09.2026 13:20 Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Kaynak: AA Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi.</t>
+          <t>Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Güncelleme: 14.09.2026 09:55 Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı. Kaynak: İHA Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Dakika Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri soğutma çalışmalarını sürdürürken yanan malzemeler iş makineleriyle dışarı taşınıyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Son Güncelleme: 13.09.2026 13:20 Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı. Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Kaynak: AA Bolu 'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Bolu Gerede'deki geri dönüşüm deposunda yangın sonrası soğutma çalışması sürüyor Bolu'nun Gerede ilçesindeki bir fabrikanın geri dönüşüm deposinde çıkan yangın gece kontrol altına alındı.</t>
+          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Güncelleme: 14.09.2026 09:55 Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Kaynak: İHA Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi.</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -4001,17 +4207,17 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.sondakika.com/amp/haber-bolu-gerede-deki-geri-donusum-deposunda-yangin-son-20233164/</t>
+          <t>https://www.sondakika.com/amp/haber-bilecik-bozuyuk-te-polis-banka-personelini-sahte-p-20234878/</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
+          <t>Bilecik</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Gerede</t>
+          <t>Bozüyük</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
@@ -4035,7 +4241,7 @@
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
       <c r="AA14" s="2" t="n">
-        <v>121.75</v>
+        <v>116.25</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>13</v>
@@ -4044,27 +4250,27 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:19:26</t>
+          <t>2026-09-14 06:45:32</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>depo yangını</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi!</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -4074,22 +4280,22 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>banka</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>finansal kuruluş</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Ad Haberler - Gündem Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi.</t>
+          <t>Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Sahte para ve tespit yöntemleri: Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Vatandaşlara ve banka personeline öneriler: Polis ekipleri, iletişim yoluyla yapılan dolandırıcılıklara karşı tedbirli olunmasını, telefon veya e-posta yoluyla kişisel ve hesap bilgisi paylaşılmamasını vurguladı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. Yetkililer benzer uyarı ve eğitim faaliyetlerinin devam edeceğini belirtti. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI 1 Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi 2 Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını 3 Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor 4 Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı 5 Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı 6 Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı 7 Ereğli'de tanker şarampole devrildi: 1 yaralı Ereğli'de tanker şarampole devrildi: 1 yaralı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Polis ekipleri, iletişim yoluyla yapılan dolandırıcılıklara karşı tedbirli olunmasını, telefon veya e-posta yoluyla kişisel ve hesap bilgisi paylaşılmamasını vurguladı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. Yetkililer benzer uyarı ve eğitim faaliyetlerinin devam edeceğini belirtti. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI Ben Hüseyin Aydın, 34 yaşındayım, İstanbul'dayım. aksiyon.com.tr'nin Gündem ekibinde adliye ve hukuk muhabiriyim. Karmaşık dava dosyalarını alıp, herkesin anlayacağı şekilde sadeleştirmek benim işim. Detaylara çok önem veririm, titiz çalışırım. İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Sözcü Gazetesi Ad Haberler - Gündem Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Bolu'nun Gerede ilçesindeki bir fabrikaya ait geri dönüşüm deposunda dün başlayan yangının ardından sahada soğutma ve tahliye çalışmaları aralıksız sürüyor. Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Gerede ilçesine bağlı Yazıkara köyü sınırları içerisinde faaliyet gösteren bir fabrikanın geri dönüşüm deposunda çıkan ve gece saatlerinde kontrol altına alınan yangın alanında ekipler çalışma yapıyor. Depodaki yanan geri dönüşüm malzemesi iş makineleriyle dışarı çıkarılarak konteyner ve kamyonlara taşınıyor. Depo ve çevresinde bulunan, yangında zarar görmeyen malzemeler ise işçiler tarafından güvenli alana taşınıyor. Gerede Belediyesi İtfaiye Müdürlüğü ekipleri de soğutma çalışmalarını sürdürüyor. Yangında zarar gören alan dronla görüntülendi. Bolu'daki depo yangınında son durum: Hasarın boyutu havadan görüntülendi! Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Yayınlanma: 13 Eylül 2026 - 13:19 Güncellenme: Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor. Bolu'da dün yangın çıkan geri dönüşüm malzemenin bulunduğu depoda soğutma çalışmaları devam ediyor.</t>
+          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Aksiyon.com.TR Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Sahte para ve tespit yöntemleri: Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI 1 Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi 2 Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını 3 Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor 4 Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı 5 Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı 6 Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı 7 Ereğli'de tanker şarampole devrildi: 1 yaralı Ereğli'de tanker şarampole devrildi: 1 yaralı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI Ben Hüseyin Aydın, 34 yaşındayım, İstanbul'dayım. Karmaşık dava dosyalarını alıp, herkesin anlayacağı şekilde sadeleştirmek benim işim. İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -4099,17 +4305,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://www.sozcu.com.tr/amp/bolu-daki-depo-yangininda-son-durum-hasarin-boyutu-havadan-goruntulendi-p357811</t>
+          <t>https://www.aksiyon.com.tr/bilecik-te-bankacilara-sahte-para-ve-dolandiricilikla-mucadele-cagrisi-354075</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
+          <t>Bilecik | Bursa | Denizli | Düzce | Eskişehir</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Gerede</t>
+          <t>Bozüyük | Silivri | Ereğli | Yeşilyurt</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
@@ -4133,7 +4339,7 @@
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
       <c r="AA15" s="2" t="n">
-        <v>117.5</v>
+        <v>105.25</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>14</v>
@@ -4142,27 +4348,27 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:55:51</t>
+          <t>2026-09-13 22:32:41</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>sahtecilik</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı</t>
+          <t>Düzce’de fabrika yangını büyüdü! Alevlerle savaşan 1 itfaiye eri yaralandı</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika</t>
+          <t>Düzce’de fabrika yangını büyüdü! Alevlerle savaşan 1 itfaiye eri yaralandı Takvim</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -4172,22 +4378,22 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Güncelleme: 14.09.2026 09:55 Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı. Kaynak: İHA Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Ekipler ayrıca genel güvenlik konularında uyarılarda bulunarak bilgilendirici broşürler dağıttı.</t>
+          <t>Düzce D-100 kara yolu üzerindeki kapı fabrikasında çıkan yangın kısa sürede büyüdü. Müdahale sırasında yaralanan itfaiye eri hastaneye kaldırıldı. Düzce D-100 kara yolu üzerindeki kapı fabrikasında çıkan yangın kısa sürede büyüdü. Müdahale sırasında yaralanan itfaiye eri hastaneye kaldırıldı. Düzce D-100 kara yolu üzerindeki kapı fabrikasında çıkan yangın kısa sürede büyüdü. Müdahale sırasında yaralanan itfaiye eri hastaneye kaldırıldı. Düzce’de alevler geceyi aydınlattı! Kapı fabrikasındaki yangında korkutan anlar kamerada Düzce’de gece saatlerinde yükselen alevler kısa sürede kapı fabrikasını sardı. Ekiplerin yoğun müdahalesiyle yangın kontrol altına alınırken, yaşanan korkutan anlar kameralara yansıdı. Takvim.com.tr Giriş Tarihi: 14 Eylül 2026 01:32 Güncelleme Tarihi: 14 Eylül 2026 05:49 Facebook X NSosyal Linki Kopyala Yazı Boyutu Takvim'i Google'a ekleyin, doğru kaynaktan haberi alın! Düzce'de kapı üretimi yapan fabrikadaki yangına müdahale eden 1 itfaiye eri yaralandı. Yangın ekiplerin yoğun mücadelesinin ardından söndürüldü. Düzce’de kapı fabrikasında yangın! Düzce D-100 kara yolu üzerinde bulunan Düzce Door isimli fabrikada meydana gelen yangın, hızla tüm fabrikayı sardı. Kapı üretimi yapan fabrikada yangın çıktı. (Fotoğraflar: Takvim Foto Arşivi ve İHA) Yangına müdahale eden 1 itfaiye eri, yanan çatının üzerine düşmesi sonucu yaralandı. Bir itfaiye eri yaralandı Olay yerinde ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. KONTROL ALTINA ALINDI İtfaiye ekiplerinin çalışmalarıyla kontrol altına alındı. Fabrikada soğutma çalışmaları sürerken, yangınla ilgili soruşturma başlatıldı. TAKVİM UYGULAMASINI İNDİRMEK İÇİN TIKLAYIN SONRAKİ HABER Başakşehir'de boş arazi, Fatih'te surlar Simla Öğütcü Takvim.com.tr Yaşam Günün Ma</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Ekipler sahtecilik yöntemleri ve iletişim yoluyla dolandırıcılık hakkında bilgi verip broşür dağıttı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Güncelleme: 14.09.2026 09:55 Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi. Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik'in Bozüyük ilçesinde polis ekipleri, bankalarda görev yapan personel ve vatandaşları sahte para ve dolandırıcılık konusunda bilgilendirdi. Bozüyük Toplum Destekli Polislik Büro Amirliği ekiplerince ilçede bulunan bankalar ziyaret edildi. Gerçekleştirilen bilgilendirme çalışmasında sahte para ve sahtecilik yöntemleri, dolandırıcılık, iletişim yoluyla dolandırıcılık ve dolandırıcılık çeşitleri hakkında bilgi verildi. Kaynak: İHA Bilecik 'te sahte para ve dolandırıcılık uyarısı yapıldı. Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Bilecik'in Bozüyük ilçesinde polis ekipleri, banka personeli ve vatandaşları sahte para ile dolandırıcılık konusunda bilgilendirdi.</t>
+          <t>Düzce’de fabrika yangını büyüdü! Alevlerle savaşan 1 itfaiye eri yaralandı Düzce’de fabrika yangını büyüdü! Alevlerle savaşan 1 itfaiye eri yaralandı Takvim Düzce D-100 kara yolu üzerindeki kapı fabrikasında çıkan yangın kısa sürede büyüdü. Müdahale sırasında yaralanan itfaiye eri hastaneye kaldırıldı. Düzce’de alevler geceyi aydınlattı! Kapı fabrikasındaki yangında korkutan anlar kamerada Düzce’de gece saatlerinde yükselen alevler kısa sürede kapı fabrikasını sardı. Ekiplerin yoğun müdahalesiyle yangın kontrol altına alınırken, yaşanan korkutan anlar kameralara yansıdı. Takvim.com.tr Giriş Tarihi: 14 Eylül 2026 01:32 Güncelleme Tarihi: 14 Eylül 2026 05:49 Facebook X NSosyal Linki Kopyala Yazı Boyutu Takvim'i Google'a ekleyin, doğru kaynaktan haberi alın! Düzce'de kapı üretimi yapan fabrikadaki yangına müdahale eden 1 itfaiye eri yaralandı. Yangın ekiplerin yoğun mücadelesinin ardından söndürüldü. Düzce’de kapı fabrikasında yangın! Düzce D-100 kara yolu üzerinde bulunan Düzce Door isimli fabrikada meydana gelen yangın, hızla tüm fabrikayı sardı. Kapı üretimi yapan fabrikada yangın çıktı. (Fotoğraflar: Takvim Foto Arşivi ve İHA) Yangına müdahale eden 1 itfaiye eri, yanan çatının üzerine düşmesi sonucu yaralandı. Bir itfaiye eri yaralandı Olay yerinde ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. Fabrikada soğutma çalışmaları sürerken, yangınla ilgili soruşturma başlatıldı.</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -4197,19 +4403,15 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>https://www.sondakika.com/amp/haber-bilecik-bozuyuk-te-polis-banka-personelini-sahte-p-20234878/</t>
+          <t>https://www.takvim.com.tr/yasam/2026/09/13/duzcede-kapi-fabrikasinda-yangin-cikti</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Bilecik</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Bozüyük</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -4217,7 +4419,7 @@
       <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr"/>
@@ -4231,7 +4433,7 @@
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" s="2" t="n">
-        <v>116.25</v>
+        <v>98.25</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>15</v>
@@ -4240,27 +4442,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:45:32</t>
+          <t>2026-09-14 08:44:22</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>dolandırıcılık</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı</t>
+          <t>Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı aksiyon.com.tr</t>
+          <t>Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Son Dakika</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -4270,22 +4472,22 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Sahte para ve tespit yöntemleri: Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Vatandaşlara ve banka personeline öneriler: Polis ekipleri, iletişim yoluyla yapılan dolandırıcılıklara karşı tedbirli olunmasını, telefon veya e-posta yoluyla kişisel ve hesap bilgisi paylaşılmamasını vurguladı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. Yetkililer benzer uyarı ve eğitim faaliyetlerinin devam edeceğini belirtti. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI 1 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 2 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 3 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 4 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı 5 Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı 6 Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı 7 Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Polis ekipleri, iletişim yoluyla yapılan dolandırıcılıklara karşı tedbirli olunmasını, telefon veya e-posta yoluyla kişisel ve hesap bilgisi paylaşılmamasını vurguladı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. Yetkililer benzer uyarı ve eğitim faaliyetlerinin devam edeceğini belirtti. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI Ben Hüseyin Aydın, 34 yaşındayım, İstanbul'dayım. aksiyon.com.tr'nin Gündem ekibinde adliye ve hukuk muhabiriyim. Karmaşık dava dosyalarını alıp, herkesin anlayacağı şekilde sadeleştirmek benim işim. Detaylara çok önem veririm, titiz çalışırım. 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
+          <t>Düzce'de Hacıdayı mevkisindeki ahşap kapı fabrikasında çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri gece boyu süren soğutma çalışmalarını tamamladı, olası olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Düzce'de Hacıdayı mevkisindeki ahşap kapı fabrikasında çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri gece boyu süren soğutma çalışmalarını tamamladı, olası olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Düzce'de Hacıdayı mevkisindeki ahşap kapı fabrikasında çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri gece boyu süren soğutma çalışmalarını tamamladı, olası olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Son Güncelleme: 14.09.2026 11:44 Düzce'de Hacıdayı mevkisindeki ahşap kapı fabrikasında çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri gece boyu süren soğutma çalışmalarını tamamladı, olası olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Düzce 'de yangın çıkan ahşap kapı fabrikasında ekipler soğutma çalışmalarını tamamladı. Merkeze bağlı Hacıdayı mevkisinde faaliyet gösteren bir ahşap kapı fabrikasında çıkan ve gece kontrol altına alınan yangını söndürme çalışmaları sabah saatlerine kadar sürdü. Fabrika ve eklentilerinde yanan malzemeler dışarıya çıkarıldı, yangında zarar görmeyen materyaller ise işçiler tarafından güvenli alana taşındı. Düzce Belediyesi İtfaiye Müdürlüğü ekipleri, gece boyu süren soğutma çalışmalarını tamamladı. Muhtemel olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Bu arada, yangında zarar gören alan dronla görüntülendi. Kaynak: AA Düzce 'de yangın çıkan ahşap kapı fabrikasında ekipler soğutma çalışmalarını tamamladı. Merkeze bağlı Hacıdayı mevkisinde faaliyet gösteren bir ahşap kapı fabrikasında çıkan ve gece kontrol altına alınan yangını söndürme çalışmaları sabah saatlerine kadar sürdü. Fabrika ve eklentilerinde yanan malzemeler dışarıya çıkarıldı, yangında zarar görmeyen materyaller ise işçiler tarafından güvenli alana taşındı. Düzce Belediyesi İtfaiye Müdürlüğü ekipleri, gece boyu süren soğutma çalışmalarını tamamladı. Muhtemel olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Bu arada, yangında zarar gören alan dronla görüntülendi. Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Düzce'de Hacıdayı mevkisindeki ahşap kapı fabrikasında çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri gece boyu süren soğutma çalışmalarını tamamladı, olası olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Düzce 'de yangın çıkan ahşap kapı fabrikasında ekipler soğutma çalışmalarını tamamladı. Merkeze bağlı Hacıdayı mevkisinde faaliyet gösteren bir ahşap kapı fabrikasında çıkan ve gece kontrol altına alınan yangını söndürme çalışmaları sabah saatlerine kadar sürdü. Fabrika ve eklentilerinde yanan malzemeler dışarıya çıkarıldı, yangında zarar görmeyen materyaller ise işçiler tarafından güvenli alana taşındı. Düzce Belediyesi İtfaiye Müdürlüğü ekipleri, gece boyu süren soğutma çalışmalarını tamamladı. Muhtemel olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Bu arada, yangında zarar gören alan dronla görüntülendi.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı aksiyon.com.tr Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. Bozüyük Toplum Destekli Polislik Büro Amirliği tarafından gerçekleştirilen ziyaretlerde, risklere karşı dikkat edilmesi gereken hususlar aktarıldı ve bilgilendirici materyaller dağıtıldı. Sahte para ve tespit yöntemleri: Ziyaretler sırasında polis ekipleri, banknotlarda dikkat edilecek temel göstergeler ile sahtecilik belirtilerine ilişkin genel bilgiler paylaştı. Personellere; banknotların dokusu, su işareti, emniyet şeridi ve baskı kalitesindeki farklılıklara dikkat edilmesi gerektiği hatırlatıldı. Ayrıca şüpheli görülen banknotların nasıl izole edileceği ve hangi birimlere bildirileceği konusunda prosedürler ele alındı. Banka çalışanlarına işlem sırasında çift kontrol uygulamaları, şüpheli işlemlerde yöneticilere haber verme ve müşteriyi sakinleştirerek prosedürleri işletme önerileri aktarıldı. Ekipler ayrıca genel güvenlik uyarılarıyla birlikte bilgilendirici broşürler dağıtarak farkındalığı artırmayı hedefledi. Bozüyük Toplum Destekli Polislik Büro Amirliği'nin çalışması, hem finans kuruluşlarında hem de toplumda sahte para ve dolandırıcılık vakalarının önlenmesine yönelik adımların parçası olarak değerlendiriliyor. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI 1 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 2 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 3 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 4 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı 5 Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı 6 Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı 7 Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankalarda sahte para ve dolandırıcılık bilgilendirmesi Bilecik'in Bozüyük ilçesinde polis, bankalarda çalışanlar ve vatandaşları sahte para ile iletişim yoluyla yapılan dolandırıcılıklara karşı bilgilendirdi. Bozüyük ilçesinde görevli polis ekipleri, bankalarda görev yapan personel ile vatandaşları sahte para ve çeşitli dolandırıcılık yöntemleri konusunda uyardı. BANKALARA SAHTE PARA VE DOLANDIRICILIK UYARISI Ben Hüseyin Aydın, 34 yaşındayım, İstanbul'dayım. Karmaşık dava dosyalarını alıp, herkesin anlayacağı şekilde sadeleştirmek benim işim. 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
+          <t>Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Son Dakika Düzce'de Hacıdayı mevkisindeki ahşap kapı fabrikasında çıkan yangın gece kontrol altına alındı. İtfaiye ekipleri gece boyu süren soğutma çalışmalarını tamamladı, olası olumsuzluklara karşı 2 itfaiye aracı bölgede bekletiliyor. Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Son Güncelleme: 14.09.2026 11:44 Düzce'de Hacıdayı mevkisindeki ahşap kapı fabrikasında çıkan yangın gece kontrol altına alındı. Düzce 'de yangın çıkan ahşap kapı fabrikasında ekipler soğutma çalışmalarını tamamladı. Merkeze bağlı Hacıdayı mevkisinde faaliyet gösteren bir ahşap kapı fabrikasında çıkan ve gece kontrol altına alınan yangını söndürme çalışmaları sabah saatlerine kadar sürdü. Fabrika ve eklentilerinde yanan malzemeler dışarıya çıkarıldı, yangında zarar görmeyen materyaller ise işçiler tarafından güvenli alana taşındı. Düzce Belediyesi İtfaiye Müdürlüğü ekipleri, gece boyu süren soğutma çalışmalarını tamamladı. Bu arada, yangında zarar gören alan dronla görüntülendi. Kaynak: AA Düzce 'de yangın çıkan ahşap kapı fabrikasında ekipler soğutma çalışmalarını tamamladı. Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Düzce'de Hacıdayı mevkisindeki ahşap kapı fabrikasında çıkan yangın gece kontrol altına alındı.</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -4295,27 +4497,27 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>https://www.aksiyon.com.tr/bilecik-te-bankacilara-sahte-para-ve-dolandiricilikla-mucadele-cagrisi-354075</t>
+          <t>https://www.sondakika.com/amp/haber-duzce-deki-ahsap-kapi-fabrikasi-yangininda-sogutma-20235476/</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Adana | Aydın | Bartın | Bilecik | Düzce</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Köşk | Bozüyük | Mudurnu | Maltepe</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>deki ahşap kapı fabrikası</t>
+        </is>
+      </c>
       <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr"/>
@@ -4329,7 +4531,7 @@
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
       <c r="AA17" s="2" t="n">
-        <v>105.25</v>
+        <v>105.5</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>16</v>
@@ -4338,27 +4540,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:13:08</t>
+          <t>2026-09-13 22:33:16</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi</t>
+          <t>Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv</t>
+          <t>Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -4368,18 +4570,22 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>masak</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>"Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü. "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü.</t>
+          <t>Düzce Gökçeköy'de 21.30'da başlayan kapı fabrikası yangını sürüyor; itfaiye, belediye ve orman ekipleri evlere sıçramaması için soğutma çalışması yapıyor. Düzce Gökçeköy'de 21.30'da başlayan kapı fabrikası yangını sürüyor; itfaiye, belediye ve orman ekipleri evlere sıçramaması için soğutma çalışması yapıyor. kısa bilgi:Akşam saatlerinde Düzce D100 Karayolu Gökçeköy mevkiinde bulunan ahşap kapı üretimi yapan fabrikada çıkan yangın devam ediyor. 21.30 civarında başlayan ve kısa sürede büyüyen alevlere karşı müdahale sürüyor; yangının çıkış nedeni henüz belirlenemedi.yangına müdahale:Müdahale çalışmalarına Düzce Belediyesi başta olmak… HABERİN DEVAMI Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Düzce Gökçeköy'de 21.30'da başlayan kapı fabrikası yangını sürüyor; itfaiye, belediye ve orman ekipleri evlere sıçramaması için soğutma çalışması yapıyor. Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Düzce Gökçeköy'de 21.30'da başlayan kapı fabrikası yangını sürüyor; itfaiye, belediye ve orman ekipleri evlere sıçramaması için soğutma çalışması yapıyor.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Van’da Düğün altınları için MASAK incelemesi Van’da Düğün altınları için MASAK incelemesi Hakkari Haber Tv "Vanlı Kara Haydar" olarak bilinen Mehmet Fatih Tançalan'ın eşi Çağla Öz Tançalan, hakkında yürütülen soruşturma kapsamında İstanbul'da gözaltına alınmasının ardından Van'a götürüldü.</t>
+          <t>Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Aksiyon.com.TR Düzce Gökçeköy'de 21.30'da başlayan kapı fabrikası yangını sürüyor; itfaiye, belediye ve orman ekipleri evlere sıçramaması için soğutma çalışması yapıyor. kısa bilgi:Akşam saatlerinde Düzce D100 Karayolu Gökçeköy mevkiinde bulunan ahşap kapı üretimi yapan fabrikada çıkan yangın devam ediyor. 21.30 civarında başlayan ve kısa sürede büyüyen alevlere karşı müdahale sürüyor; yangının çıkış nedeni henüz belirlenemedi.yangına müdahale:Müdahale çalışmalarına Düzce Belediyesi başta olmak… HABERİN DEVAMI Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Düzce Gökçeköy'de 21.30'da başlayan kapı fabrikası yangını sürüyor; itfaiye, belediye ve orman ekipleri evlere sıçramaması için soğutma çalışması yapıyor. Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Düzce Gökçeköy'de 21.30'da başlayan kapı fabrikası yangını sürüyor; itfaiye, belediye ve orman ekipleri evlere sıçramaması için soğutma çalışması yapıyor.</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -4389,23 +4595,23 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://www.hakkarihabertv.com/vanda-dugun-altinlari-icin-masak-incelemesi-88464h.htm</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul | Van</t>
-        </is>
-      </c>
+          <t>https://www.aksiyon.com.tr/duzce-gokcekoy-de-kapi-fabrikasi-yangini-ekipler-cevredeki-evleri-korumaya-calisiyor-354004/amp</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>de kapı fabrikası | da başlayan kapı fabrikası</t>
+        </is>
+      </c>
       <c r="R18" s="2" t="inlineStr"/>
       <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr"/>
@@ -4419,7 +4625,7 @@
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
       <c r="AA18" s="2" t="n">
-        <v>58.92</v>
+        <v>118.87</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>17</v>
@@ -4428,27 +4634,27 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:13:44</t>
+          <t>2026-09-13 22:32:24</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi</t>
+          <t>Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5</t>
+          <t>Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Son Dakika</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -4458,31 +4664,39 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>enerji, masak</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5</t>
+          <t>Düzce'de bir kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi. Düzce'de bir kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi. Düzce'de bir kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi. Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Son Güncelleme: 14.09.2026 01:32 Düzce'de bir kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi. YANAN FABRİKA DRONLA GÖRÜNTÜLENDİ Düzce 'de, kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi. Musa KESKİN/DÜZCE, Kaynak: DHA YANAN FABRİKA DRONLA GÖRÜNTÜLENDİ Düzce 'de, kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi. Musa KESKİN/DÜZCE, Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Düzce'de bir kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi. YANAN FABRİKA DRONLA GÖRÜNTÜLENDİ Düzce 'de, kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5 Ailem Güvende soruşturmasında MASAK kayıtları: 6 derneğe 3,3 milyon dolarlık yurt dışı transferi Enerji FM 100.5</t>
+          <t>Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Son Dakika Düzce'de bir kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Yanan fabrika dronla görüntülendi. Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Son Güncelleme: 14.09.2026 01:32 Düzce'de bir kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. YANAN FABRİKA DRONLA GÖRÜNTÜLENDİ Düzce 'de, kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Musa KESKİN/DÜZCE, Kaynak: DHA YANAN FABRİKA DRONLA GÖRÜNTÜLENDİ Düzce 'de, kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor. Musa KESKİN/DÜZCE, Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Düzce'de bir kapı fabrikasında çıkan yangını söndürmek için ekiplerin müdahalesi sürüyor.</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>browser_timeout</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNcENzcjVCU05WeW5STWxZSnY5a1dWTnJfQ3p2S3ozZjc5TjJBSWVkdnlNdmFSWVBac29MQm1wM0NVTC1KWmZEbkdPbUFyQVlkcEdrLWFWWXdKUmZNM25mNm1FSjdUaFg0M3N6azZUQXJDZWtzZlhGYnZWbU5PZ01LcG04Qm9sU050NVNseDBDdnctWXNYU0xjeG4tZ3V4ZWtsbHIwRkhTR3Y1N29BdEVxYW9BcENMWjNWOEhOTGFGelFuZzlQWnhPcTJR?oc=5&amp;hl=en-US&amp;gl=US&amp;ceid=US:en</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>https://www.sondakika.com/amp/haber-duzce-de-kapi-fabrikasindaki-yangina-mudahale-suru-20234494/</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -4491,7 +4705,7 @@
       <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr"/>
@@ -4505,7 +4719,7 @@
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
       <c r="AA19" s="2" t="n">
-        <v>93.12</v>
+        <v>108.31</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>18</v>
@@ -4514,27 +4728,27 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:22:00</t>
+          <t>2026-09-13 21:48:26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MASAK</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -4544,18 +4758,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>masak, para transferi</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Gündem 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sevda Ecem Karapolat 13.09.2026 - 15:22 3 İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Soruşturma belgelerine dayandırılan bilgilere göre, 2021-2026 döneminde yabancı ve uluslararası kurumsal kaynaklardan yapılan 209 transferin işlem tarihlerindeki toplam karşılığı yaklaşık 67,4 milyon lira olarak hesaplandı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında, İstanbul merkezli 6 derneğin yurt içi ve yurt dışı bağlantılı para hareketleri incelemeye alındı. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu’nun 226’ncı maddesi kapsamında yürütülen araştırmada, MASAK Veri İnceleme Tutanağı ve bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte değerlendirildi. HANGİ DERNEKLERİN HESAPLARI İNCELENDİ? İnceleme kapsamında şu derneklerin hesap hareketleri ele alındı: Yemen’de çatışmalar şiddetlendi: İran destekli Husiler operasyon görüntülerini paylaştı İçeriği Görüntüle Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği (HEVİ) Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği Pozitif Yaşam Derneği Pozitif İz Derneği Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneği (SPoD) Belgelerde, yabancı kuruluşlardan gelen fonların yanı sıra GİB SWIFT kayıtları, gerçek kişiler tarafından yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketlerinin sıralandığı belirtildi. 45 BİN 135 İŞLEM KAYDI DEĞERLENDİRİLDİ İncelemeye ilişkin aktarılan bilgilere göre, “Bankacılık Transfer” tablosunda toplam 45 bin 135 işlem satırı bulunuyor. Bunların 13 bin 40’ını para girişleri , 32 bin 95’ini ise para çıkışları oluşturuyor. Para girişlerinin 218’inin doğrudan SWIFT alma işlemi olduğu kaydedildi. Gönderen adı, ülke bilgisi, işlemin SWIFT niteliği, banka ve açıklama bilgilerinin birlikte değerlendirilmesiyle yabancı kurumsal kaynaklardan gelen transferler ayrıca sınıflandırıldı. 37 KURUMSAL KAYNAKTAN 209 PARA GİRİŞİ 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan 209 para girişi belirlendiği aktarıldı. Bu işlemlerin gerçekleştirildikleri tarihlerdeki TL karşılıklarının toplamı 67 milyon 394 bin 563 lira olarak hesaplandı. Belgelerde bu tutarın paranın bugünkü değerini ifade etmediği vurgulandı. Rakamın, farklı tarihlerde yapılan transferlerin MASAK kayıtlarındaki TL karşılıklarının aritmetik toplamından oluştuğu belirtildi. GİB SWIFT kayıtlarına ilişkin değerlendirmede ise derneklere gönderilen paranın dolar karşılığının 3 milyon 359 bin doları aştığı bilgisine yer verildi. YABANCI KURUMSAL GİRİŞLERİN YÜZDE 78’İ İKİ DERNEĞE Aktarılan inceleme bulgularına göre, 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinin yüzde 78’i SPoD ve HEVİ’ye yöneldi. Para hareketlerinde yabancı devlet kurumları, diplomatik misyonlar ve uluslararası kuruluşların yanı sıra gerçek kişilerden yapılan transferlerin de bulunduğu belirtildi. Paylaşılan bilgilerde, bu transferlerin suç oluşturduğuna ilişkin kesinleşmiş bir yargı kararına yer verilmedi. Kaynak: Haber Merkezi Editörün Seçtiği Benzine gece yarısı büyük zam geliyor: Ankara'da 80 liranın üzerine çıkacak! Editörün Seçtiği Kaşif Kozinoğlu'nun mezarı bugün açılacaktı: Feth-i kabir işlemi ertelendi! Editörün Seçtiği Kredi kartı limiti düşürülecek mi? İşte 2026 düzenlemesinin ayrıntıları... Editör Hakkında Sevda Ecem Karapolat Bunlar da ilginizi çekebilir Yemen’de çat</t>
+          <t>Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Güncelleme: 14.09.2026 00:48 Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. DÜZCE'de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangına müdahalesi sürüyor. Merkeze bağlı Hacialiler köyü mevkisinde bulunan kapı fabrikasında, saat 22.00 sıralarında yangın çıktı. Yangın kısa sürede büyüyerek fabrikayı sardı. İhbar üzerine bölgeye itfaiyeleri sevk edildi. İtfaiye erleri, yangına müdahale ederken Sakarya ve Bolu 'dan da itfaiye ekipleri destek için bölgeye gönderildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. Ekiplerin yangını kontrol altına almak için çalışmaları devam ediyor. Kaynak: DHA DÜZCE'de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangına müdahalesi sürüyor. Merkeze bağlı Hacialiler köyü mevkisinde bulunan kapı fabrikasında, saat 22.00 sıralarında yangın çıktı. Yangın kısa sürede büyüyerek fabrikayı sardı. İhbar üzerine bölgeye itfaiyeleri sevk edildi. İtfaiye erleri, yangına müdahale ederken Sakarya ve Bolu 'dan da itfaiye ekipleri destek için bölgeye gönderildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. Ekiplerin yangını kontrol altına almak için çalışmaları devam ediyor. Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. DÜZCE'de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangına müdahalesi sürüyor. Merkeze bağlı Hacialiler köyü mevkisinde bulunan kapı fabrikasında, saat 22.00 sıralarında yangın çıktı. Yangın kısa sürede büyüyerek fabrikayı sardı. İhbar üzerine bölgeye itfaiyeleri sevk edildi. İtfaiye erleri, yangına müdahale ederken Sakarya ve Bolu 'dan da itfaiye ekipleri destek için bölgeye gönderildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. Ekiplerin yangını kontrol altına almak için çalışmaları devam ediyor.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi ankaranethaber.com İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Gündem 6 LGBT derneğine yurt dışından para transferi: MASAK incelemesinde 209 işlem belirlendi İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Sevda Ecem Karapolat 13.09.2026 - 15:22 3 İstanbul Cumhuriyet Başsavcılığının yürüttüğü soruşturma kapsamında, 6 LGBT derneğinin hesap hareketlerine ilişkin MASAK verileri incelendi. Soruşturma belgelerine dayandırılan bilgilere göre, 2021-2026 döneminde yabancı ve uluslararası kurumsal kaynaklardan yapılan 209 transferin işlem tarihlerindeki toplam karşılığı yaklaşık 67,4 milyon lira olarak hesaplandı. İstanbul Cumhuriyet Başsavcılığının 2026/143015 sayılı soruşturması kapsamında, İstanbul merkezli 6 derneğin yurt içi ve yurt dışı bağlantılı para hareketleri incelemeye alındı. 5253 sayılı Dernekler Kanunu ile Türk Ceza Kanunu’nun 226’ncı maddesi kapsamında yürütülen araştırmada, MASAK Veri İnceleme Tutanağı ve bankacılık transferlerine ilişkin iki ayrı analiz dosyası birlikte değerlendirildi. HANGİ DERNEKLERİN HESAPLARI İNCELENDİ? İnceleme kapsamında şu derneklerin hesap hareketleri ele alındı: Yemen’de çatışmalar şiddetlendi: İran destekli Husiler operasyon görüntülerini paylaştı İçeriği Görüntüle Hak Eşitlik Varoluş İçin Lezbiyen Gey Biseksüel Transseksüel İnterseksüel Derneği (HEVİ) Lambda İstanbul Lezbiyen Gey Biseksüel Trans İnterseks Artı Dayanışma Derneği Lezbiyen Gey Biseksüel Trans İnterseks Artı Aileleri ve Yakınları Derneği Pozitif Yaşam Derneği Pozitif İz Derneği Sosyal Politika Cinsiyet Kimliği ve Cinsel Yönelim Çalışmaları Derneği (SPoD) Belgelerde, yabancı kuruluşlardan gelen fonların yanı sıra GİB SWIFT kayıtları, gerçek kişiler tarafından yapılan mükerrer transferler ve derneklerle bağlantılı isimlerin hesap hareketlerinin sıralandığı belirtildi. 45 BİN 135 İŞLEM KAYDI DEĞERLENDİRİLDİ İncelemeye ilişkin aktarılan bilgilere göre, “Bankacılık Transfer” tablosunda toplam 45 bin 135 işlem satırı bulunuyor. Bunların 13 bin 40’ını para girişleri , 32 bin 95’ini ise para çıkışları oluşturuyor. Para girişlerinin 218’inin doğrudan SWIFT alma işlemi olduğu kaydedildi. 37 KURUMSAL KAYNAKTAN 209 PARA GİRİŞİ 2021-2026 yılları arasında yabancı veya uluslararası nitelikteki 37 farklı kurumsal kaynak ve kamu misyonundan 209 para girişi belirlendiği aktarıldı. Rakamın, farklı tarihlerde yapılan transferlerin MASAK kayıtlarındaki TL karşılıklarının aritmetik toplamından oluştuğu belirtildi. GİB SWIFT kayıtlarına ilişkin değerlendirmede ise derneklere gönderilen paranın dolar karşılığının 3 milyon 359 bin doları aştığı bilgisine yer verildi. YABANCI KURUMSAL GİRİŞLERİN YÜZDE 78’İ İKİ DERNEĞE Aktarılan inceleme bulgularına göre, 2021-2026 döneminde tespit edilen yabancı kurumsal para girişlerinin yüzde 78’i SPoD ve HEVİ’ye yöneldi. Para hareketlerinde yabancı devlet kurumları, diplomatik misyonlar ve uluslararası kuruluşların yanı sıra gerçek kişilerden yapılan transferlerin de bulunduğu belirtildi. Editörün Seçtiği Kaşif Kozinoğlu'nun mezarı bugün açılacaktı: Feth-i kabir işlemi ertelendi!</t>
+          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Güncelleme: 14.09.2026 00:48 Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. DÜZCE'de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangına müdahalesi sürüyor. Merkeze bağlı Hacialiler köyü mevkisinde bulunan kapı fabrikasında, saat 22.00 sıralarında yangın çıktı. Yangın kısa sürede büyüyerek fabrikayı sardı. İtfaiye erleri, yangına müdahale ederken Sakarya ve Bolu 'dan da itfaiye ekipleri destek için bölgeye gönderildi. Fabrikadan yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. Ekiplerin yangını kontrol altına almak için çalışmaları devam ediyor. Kaynak: DHA DÜZCE'de faaliyet gösteren kapı üretim fabrikasında yangın çıktı. Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı.</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -4565,12 +4783,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://www.ankaranethaber.com/6-lgbt-dernegine-yurt-disindan-para-transferi-masak-incelemesinde-209-islem-belirlendi</t>
+          <t>https://www.sondakika.com/amp/haber-duzce-hacialiler-koyundeki-fabrika-yanginina-sakar-20234469/</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>İstanbul</t>
+          <t>Bolu | Düzce</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -4595,7 +4813,7 @@
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
       <c r="AA20" s="2" t="n">
-        <v>111</v>
+        <v>102.25</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>19</v>
@@ -4604,27 +4822,27 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:21:29</t>
+          <t>2026-09-14 07:27:59</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursada Bugün</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı Düzce Gazete Efsane</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -4634,22 +4852,22 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>inşaat, şirket</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da Ankaş İnşaat ve E.A. A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da Ankaş İnşaat ve E.A. A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da Ankaş İnşaat ve E.A. A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursa'da konkordato kararı verilen şirket için 3 aylık mühlet Şirketin taşınır ve taşınmazlarının devrine kısıtlama 10 Eylül'den itibaren yeni icra ve iflas takibi yapılamayacak Konkordato komiseri görevlendirildi Alacaklılara itiraz için 7 günlük süre Konkordato sürecinde duruşma tarihi belirlenmedi Bursa'da Ankaş İnşaat ve E.A. A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da faaliyet gösteren Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. hakkında konkordato süreci başlatıldı. Bursa 1. Asliye Ticaret Mahkemesi, şirket ile davacılardan E. A. A. için 3 aylık geçici konkordato mühleti verilmesine karar verdi. Kararla birlikte borçluların mal varlıklarının devrine yönelik kısıtlamalar getirilirken, yeni icra ve iflas takiplerinin de önüne geçildi. Bursa 1. Asliye Ticaret Mahkemesi'nde görülen konkordato davasında önemli bir ara karar çıktı. 2026/678 Esas numarasıyla yürütülen dosyada, Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret Anonim Şirketi ile Emine Altun Anık hakkında geçici mühlet uygulanmasına hükmedildi. Mahkemenin 10 Eylül 2026 tarihli tensip kararları kapsamında verilen mühletin süresi üç ay olarak belirlendi. Böylece davacı-borçlular açısından konkordato hükümlerinin uygulanacağı yeni bir dönem başlamış oldu. Konkordato, borçlarını mevcut koşullar altında ödemekte zorlanan şirket veya kişilerin, alacaklılarıyla yeniden yapılandırma yoluna gitmesini sağlayan hukuki bir süreç olarak uygulanıyor. Bursa 1. Asliye Ticaret Mahkemesi de söz konusu dosyada geçici mühlet verilmesini uygun buldu. Karar doğrultusunda Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. ile E. A. A. için üç aylık geçici konkordato mühleti başladı. Geçici mühlet süresince borçluların mal varlıkları üzerinde yapabileceği bazı işlemler mahkeme denetimine tabi olacak. Özellikle şirketin faaliyetlerinin ve mevcut varlıklarının korunması amacıyla önemli sınırlamalar getirildi. Mahkeme kararıyla davacı-borçlular adına kayıtlı taşınır ve taşınmaz malların üçüncü kişilere devredilmesi, yeni bir karar verilinceye kadar yasaklandı. Bunun yanında borçluların mahkemenin izni olmadan belirli tasarruflarda bulunmasının da önüne geçildi. Konkordato mühleti boyunca borçluların rehin tesis etmesi, kefil olması veya taşınmazlarıyla işletmenin devamlı tesisatını kısmen ya da tamamen devretmesi mümkün olmayacak. Aynı şekilde bu varlıklar üzerinde kısıtlayıcı işlemler yapılması ve karşılıksız tasarruflarda bulunulması da mahkeme iznine bağlandı. Bu tedbirlerin temel amacı, konkordato sürecinde borçluların mevcut mal varlığının korunması ve alacaklıların haklarının zarar görmemesi olarak öne çıkıyor. Mahkemenin kararında konkordato mühletinin önemli sonuçlarından biri de icra ve iflas takipleri bakımından ortaya çıktı. İcra ve İflas Kanunu'nun ilgili hükümleri doğrultusunda 10 Eylül 2026 tarihinden itibaren davacı-borçlular hakkında yeni icra ve iflas takibi başlatılamayacak. Tedbir kararı yalnızca klasik icra işlemleriyle sınırlı kalmadı. Borçlular aleyhine yürütülebilecek takip işlemlerinin yanı sıra ihtiyati tedbir, ihtiyati haciz ve muhafaza işlemleri de karar kapsamında değerlendirildi. Bu süreçte davacıların mal varlığı üzerinde gerçekleştirilebilecek takip işlemlerine yönelik koruma sağlandı. Ancak mahkeme kararında, konkordato tedbirlerinin İcra ve İflas Kanunu'nun 206. maddesinin birinci sırasında yer alan imtiyazlı alacaklar ile rehinle güvence altına alınmış alacaklar bakımından geçerli olmayacağı da belirtildi. Mahkeme, üç aylık geçici mühlet döneminin denetimli şekilde yürütülmesi amacıyla konkordato komiseri de görevlendirdi. Dosyada mali konularda uzman komiser olarak Süreyyа Turhan atandı. Komiser, konkordato sürecinde borçluların mali durumunun değerlendirilmesi ve mahkemenin ihtiyaç duyduğu incelemelerin gerçekleştirilmesi bakımından görev yapacak. Komiserin atanmasıyla birlikte şirketin ve diğer davacı-borçlunun konkordato sürecindeki mali yapısının daha yakından incelenmesi bekleniyor. Mahkemenin ilanında, davacı-borçlulardan alacağı bulunduğunu ileri süren kişilere ve kurumlara da önemli bir süre tanındı. Buna göre alacaklı olduğunu iddia edenler, ilan tarihinden itibaren yedi gün içerisinde mahkemeye dilekçe sunarak itirazda bulunabilecek. İtiraz edecek kişilerin, konkordato mühleti verilmesini gerektiren koşulların bulunmadığını ileri sürmeleri ve iddialarını delilleriyle birlikte ortaya koymaları gerekiyor. Bu süre, konkordato sürecine ilişkin itirazların mahkeme tarafından değerlendirilmesi açısından önem taşıyor. Mahkeme tarafından geçici mühlet kararının ardından doğrudan bir duruşma günü belirlenmemesi de dikkat çekti. Bunun nedeni, geçici mühletin uzatılması veya sürenin tamamlanmasını beklemeden yeni bir karar alınmasını gerektirebilecek önemli gelişmelerin ortaya çıkabilmesi ihtimali olarak açıklandı. Dolayısıyla dosyada önümüzdeki dönemde şirketin mali durumu, konkordato sürecindeki gelişmeler ve mahkemenin yapacağı değerlendirmeler belirleyici olacak. Bursa'daki konkordato dosyası, 10 Eylül 2026 tarihli kararın ardından üç aylık geçici mühlet dönemiyle devam edecek. Bu süreçte şirketin mali yapısına ilişkin incelemeler sürdürülürken, alacaklıların itirazları ve komiser tarafından yapılacak çalışmalar da dosyanın geleceği açısından önem taşıyacak. Diğer Bursa Haberleri - Bölge Haberleri için tıklayın Türkiye bu olayı konuşuyor: 11 aylık Büşra'dan 4 gündür haber yok! Anne "satıldı" dedi, baba reddetti Cezaevinden çıkan Fatma Soydaş'ın son hali şaşırttı! İlk görüntüsü ortaya çıktı Bursa'da gözler bu toplantıda! Nilüfer'de tartışma yaratan imar planı gündemde... Bursa Orhangazi'de dev operasyon! 8 ton ele geçirildi... Kurtlar Vadisi sahneleri yeniden gündemde: Plakadaki detay dikkat çekti! Bursa'da vicdanları sızlatan görüntü!</t>
+          <t>Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursada Bugün Bursa'da Ankaş İnşaat ve E.A. için 3 aylık geçici konkordato mühleti verildi. Mahkeme, 10 Eylül 2026'dan itibaren yeni icra takibini durdurup komiser atadı. Bursa'da inşaat şirketi için konkordato süreci başladı! Mahkemeden 3 aylık geçici mühlet kararı Bursa'da konkordato kararı verilen şirket için 3 aylık mühlet Şirketin taşınır ve taşınmazlarının devrine kısıtlama 10 Eylül'den itibaren yeni icra ve iflas takibi yapılamayacak Konkordato komiseri görevlendirildi Alacaklılara itiraz için 7 günlük süre Konkordato sürecinde duruşma tarihi belirlenmedi Bursa'da Ankaş İnşaat ve E.A. Bursa'da faaliyet gösteren Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. hakkında konkordato süreci başlatıldı. Asliye Ticaret Mahkemesi, şirket ile davacılardan E. için 3 aylık geçici konkordato mühleti verilmesine karar verdi. Kararla birlikte borçluların mal varlıklarının devrine yönelik kısıtlamalar getirilirken, yeni icra ve iflas takiplerinin de önüne geçildi. Asliye Ticaret Mahkemesi'nde görülen konkordato davasında önemli bir ara karar çıktı. 2026/678 Esas numarasıyla yürütülen dosyada, Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret Anonim Şirketi ile Emine Altun Anık hakkında geçici mühlet uygulanmasına hükmedildi. Böylece davacı-borçlular açısından konkordato hükümlerinin uygulanacağı yeni bir dönem başlamış oldu. Konkordato, borçlarını mevcut koşullar altında ödemekte zorlanan şirket veya kişilerin, alacaklılarıyla yeniden yapılandırma yoluna gitmesini sağlayan hukuki bir süreç olarak uygulanıyor. Asliye Ticaret Mahkemesi de söz konusu dosyada geçici mühlet verilmesini uygun buldu. Karar doğrultusunda Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. ile E. için üç aylık geçici konkordato mühleti başladı. Geçici mühlet süresince borçluların mal varlıkları üzerinde yapabileceği bazı işlemler mahkeme denetimine tabi olacak. Özellikle şirketin faaliyetlerinin ve mevcut varlıklarının korunması amacıyla önemli sınırlamalar getirildi. Bunun yanında borçluların mahkemenin izni olmadan belirli tasarruflarda bulunmasının da önüne geçildi. Konkordato mühleti boyunca borçluların rehin tesis etmesi, kefil olması veya taşınmazlarıyla işletmenin devamlı tesisatını kısmen ya da tamamen devretmesi mümkün olmayacak. Aynı şekilde bu varlıklar üzerinde kısıtlayıcı işlemler yapılması ve karşılıksız tasarruflarda bulunulması da mahkeme iznine bağlandı. Bu tedbirlerin temel amacı, konkordato sürecinde borçluların mevcut mal varlığının korunması ve alacaklıların haklarının zarar görmemesi olarak öne çıkıyor. Mahkemenin kararında konkordato mühletinin önemli sonuçlarından biri de icra ve iflas takipleri bakımından ortaya çıktı. İcra ve İflas Kanunu'nun ilgili hükümleri doğrultusunda 10 Eylül 2026 tarihinden itibaren davacı-borçlular hakkında yeni icra ve iflas takibi başlatılamayacak. Tedbir kararı yalnızca klasik icra işlemleriyle sınırlı kalmadı. Bu süreçte davacıların mal varlığı üzerinde gerçekleştirilebilecek takip işlemlerine yönelik koruma sağlandı. Ancak mahkeme kararında, konkordato tedbirlerinin İcra ve İflas Kanunu'nun 206. maddesinin birinci sırasında yer alan imtiyazlı alacaklar ile rehinle güvence altına alınmış alacaklar bakımından geçerli olmayacağı da belirtildi. Mahkeme, üç aylık geçici mühlet döneminin denetimli şekilde yürütülmesi amacıyla konkordato komiseri de görevlendirdi. Komiser, konkordato sürecinde borçluların mali durumunun değerlendirilmesi ve mahkemenin ihtiyaç duyduğu incelemelerin gerçekleştirilmesi bakımından görev yapacak. Komiserin atanmasıyla birlikte şirketin ve diğer davacı-borçlunun konkordato sürecindeki mali yapısının daha yakından incelenmesi bekleniyor. İtiraz edecek kişilerin, konkordato mühleti verilmesini gerektiren koşulların bulunmadığını ileri sürmeleri ve iddialarını delilleriyle birlikte ortaya koymaları gerekiyor. Bu süre, konkordato sürecine ilişkin itirazların mahkeme tarafından değerlendirilmesi açısından önem taşıyor. Mahkeme tarafından geçici mühlet kararının ardından doğrudan bir duruşma günü belirlenmemesi de dikkat çekti. Bunun nedeni, geçici mühletin uzatılması veya sürenin tamamlanmasını beklemeden yeni bir karar alınmasını gerektirebilecek önemli gelişmelerin ortaya çıkabilmesi ihtimali olarak açıklandı. Dolayısıyla dosyada önümüzdeki dönemde şirketin mali durumu, konkordato sürecindeki gelişmeler ve mahkemenin yapacağı değerlendirmeler belirleyici olacak. Bursa'daki konkordato dosyası, 10 Eylül 2026 tarihli kararın ardından üç aylık geçici mühlet dönemiyle devam edecek. Bu süreçte şirketin mali yapısına ilişkin incelemeler sürdürülürken, alacaklıların itirazları ve komiser tarafından yapılacak çalışmalar da dosyanın geleceği açısından önem taşıyacak. Diğer Bursa Haberleri - Bölge Haberleri için tıklayın Türkiye bu olayı konuşuyor: 11 aylık Büşra'dan 4 gündür haber yok! Anne "satıldı" dedi, baba reddetti Cezaevinden çıkan Fatma Soydaş'ın son hali şaşırttı! İlk görüntüsü ortaya çıktı Bursa'da gözler bu toplantıda! Bursa Orhangazi'de dev operasyon! Bursa'da vicdanları sızlatan görüntü!</t>
+          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı Düzce Gazete Efsane Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -4659,69 +4877,37 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>https://www.bursadabugun.com/haber/bursa-da-insaat-sirketi-icin-konkordato-sureci-basladi-mahkemeden-3-aylik-gecici-muhlet-karari-1948726.html</t>
+          <t>https://www.duzcegazeteefsane.com/duzce-belediyesi-gundem-duzce-haberleri/15394-saniyelerle-yarisildi:-duzcedeki-fabrika-yanginina-hizli-mudahale-ve-ekiplerin-zaman-cizelgesi-aciklandi</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Orhangazi</t>
-        </is>
-      </c>
+          <t>Düzce</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
       <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş:raw_legal</t>
-        </is>
-      </c>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş Orhangazi Bursa Türkiye</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Cargill Türkiye Bursa Orhangazi Mısır İşleme Tesisi</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>Cargill Türkiye Bursa Orhangazi Mısır İşleme Tesisi</t>
-        </is>
-      </c>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t>48.54368932038835</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t>Ysf gida depo</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
       <c r="AA21" s="2" t="n">
-        <v>199.75</v>
+        <v>114.51</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>20</v>
@@ -4730,27 +4916,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:57:35</t>
+          <t>2026-09-13 19:48:24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -4760,36 +4946,44 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>tesis, üretim, üretim tesisi</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>üretim tesisi</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com</t>
+          <t>Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. olay yerine intikal ve müdahale: Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. alevler ve dumanın görünürlüğü: Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. müdahalenin sürdüğü bildirildi: Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. 1 Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi 2 Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını 3 Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor 4 Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı 5 Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı 6 Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı 7 Ereğli'de tanker şarampole devrildi: 1 yaralı Ereğli'de tanker şarampole devrildi: 1 yaralı Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada olay yerine intikal ve müdahale: Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. Ben Mehmet Yılmaz, 28 yaşındayım. İstanbul'dayım. aksiyon.com.tr Gündem ekibinin hırslı araştırmacı gazetecisiyim. Masa başında durmayı sevmem; sahada, meclis koridorlarında, siyasi kulislerde gerçeklerin peşindeyim. İdealist biriyim ve işimi ciddiyetle yaparım. 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti tekreferans.com</t>
+          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Aksiyon.com.TR Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. olay yerine intikal ve müdahale: Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. alevler ve dumanın görünürlüğü: Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. müdahalenin sürdüğü bildirildi: Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. 1 Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi 2 Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını 3 Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor 4 Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı 5 Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı 6 Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı 7 Ereğli'de tanker şarampole devrildi: 1 yaralı Ereğli'de tanker şarampole devrildi: 1 yaralı Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada olay yerine intikal ve müdahale: Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Ben Mehmet Yılmaz, 28 yaşındayım. Masa başında durmayı sevmem; sahada, meclis koridorlarında, siyasi kulislerde gerçeklerin peşindeyim. 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPUzE0Z0x2amtxSm0wTzh1MHFZQjI4OHZiOElkYl9naFJ3NnJONE9TeU5ldmZhY3NPYzBxaVZRRFR3d1VFcXVWcmNRdVZBN1p1Ul90VGxoMExRTEtzaEtOWUdDU1NXYXgzY1hkeER5Rm5nZEJNQk1EOXUxSmpxSHBoeENBU0tYZGtLbzNpWklEbUFIdVFjVjNTYTNyMEk?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>https://www.aksiyon.com.tr/duzce-de-uretim-tesisinde-yangin-alarmi-itfaiye-ekipleri-sahada-353976</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Denizli | Düzce | Eskişehir | İstanbul</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Silivri | Ereğli | Yeşilyurt</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
@@ -4797,7 +4991,7 @@
       <c r="S22" s="2" t="inlineStr"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr"/>
@@ -4811,7 +5005,7 @@
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
       <c r="AA22" s="2" t="n">
-        <v>61.08</v>
+        <v>102.75</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>21</v>
@@ -4820,27 +5014,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:00:38</t>
+          <t>2026-09-13 19:45:00</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -4850,22 +5044,22 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Anasayfa / Ekonomi / Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye'de İş Dünyası Ekonomi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Güncelleme: 14/09/2026 09:00 Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. 14/09/2026 09:00 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Bilsar Tekstil Muharrem Hilmi Kayhan Söktaş Tekstil İSO’da değişim sesleri yükseliyor Fotoğrafın 200. yılında sanat ile tasarım buluşuyor Mercedes-Benz Türk patent tescilinde tüm sektörlerin lideri oldu Türkiye’nin en büyük elektrikli araç sahipleri buluşması Yenikapı’da gerçekleşecek Ferrari’nin yeni kişiye özel modeli Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı SON DAKİKA HABERLERİ GÜNDEM KORİDORU 9 gün önce Resmi Gazete’de yayımlandı: Diyanet ve Dışişleri’nde kritik atamalar gerçekleşti EKONOMİ 12 gün önce KOSGEB’den KOBİ’lere 27,1 milyar liralık dev can suyu ALMANYA'DA İŞ DÜNYASI 12 gün önce Almanya’da Trilya yağına zararlı mineral yağ engeli: Raflardan toplatılıyor EKONOMİ 12 gün önce Eskişehir’de stratejik adım: Nadir elementler için dev kamulaştırma SPOR 12 gün önce Beşiktaş’ta beklenen ayrılık EKONOMİ 12 gün önce AFSİAD Başkanı Sayın’dan bankalara faiz ve teminat çağrısı EMLAK 12 gün önce Eylül ayı kira artış oranı için gözler TÜİK’te KATEGORİNİN POPÜLERLERİ 1 Gram altın tahminleri 2025 2 2026 gram altın fiyatı tahmini! Altın ne kadar olur? 3 Motosiklet fiyatlarına ek gümrük vergisi geldi! Scooterlara ne kadar zam geldi? 4 2025 çiğ süt satış fiyatı belli oldu 5 Kilis’in ihracatı ilk yarıda yüzde 13 artarak 69,2 milyon dolara ulaştı Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı Çerkezköy’de e-ticaret lojistiğine yeni merkez Yapay zekâ e-ihracatta KOBİ’lerin önünü açıyor Güneydoğu’nun ihracatı 8 ayda 8,2 milyar dolara ulaştı Otomotivde üretim frene bastı: 8 ayda 841 bin araç üretildi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı Çerkezköy’de e-ticaret lojistiğine yeni merkez Yapay zekâ e-ihracatta KOBİ’lerin önünü açıyor Güneydoğu’nun ihracatı 8 ayda 8,2 milyar dolara ulaştı Otomotivde üretim frene bastı: 8 ayda 841 bin araç üretildi</t>
+          <t>Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi. Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Anasayfa / Ekonomi / Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye'de İş Dünyası Ekonomi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Güncelleme: 14/09/2026 09:00 Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. 14/09/2026 09:00 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Bilsar Tekstil Muharrem Hilmi Kayhan Söktaş Tekstil İSO’da değişim sesleri yükseliyor Fotoğrafın 200. yılında sanat ile tasarım buluşuyor Mercedes-Benz Türk patent tescilinde tüm sektörlerin lideri oldu Türkiye’nin en büyük elektrikli araç sahipleri buluşması Yenikapı’da gerçekleşecek Ferrari’nin yeni kişiye özel modeli Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı SON DAKİKA HABERLERİ GÜNDEM KORİDORU 9 gün önce Resmi Gazete’de yayımlandı: Diyanet ve Dışişleri’nde kritik atamalar gerçekleşti EKONOMİ 12 gün önce KOSGEB’den KOBİ’lere 27,1 milyar liralık dev can suyu ALMANYA'DA İŞ DÜNYASI 12 gün önce Almanya’da Trilya yağına zararlı mineral yağ engeli: Raflardan toplatılıyor EKONOMİ 12 gün önce Eskişehir’de stratejik adım: Nadir elementler için dev kamulaştırma SPOR 12 gün önce Beşiktaş’ta beklenen ayrılık EKONOMİ 12 gün önce AFSİAD Başkanı Sayın’dan bankalara faiz ve teminat çağrısı EMLAK 12 gün önce Eylül ayı kira artış oranı için gözler TÜİK’te KATEGORİNİN POPÜLERLERİ 1 Gram altın tahminleri 2025 2 2026 gram altın fiyatı tahmini! 4 2025 çiğ süt satış fiyatı belli oldu 5 Kilis’in ihracatı ilk yarıda yüzde 13 artarak 69,2 milyon dolara ulaştı Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı Çerkezköy’de e-ticaret lojistiğine yeni merkez Yapay zekâ e-ihracatta KOBİ’lerin önünü açıyor Güneydoğu’nun ihracatı 8 ayda 8,2 milyar dolara ulaştı Otomotivde üretim frene bastı: 8 ayda 841 bin araç üretildi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Güneşin enerjisinin elektrik üretimindeki payı 28 kat arttı Çerkezköy’de e-ticaret lojistiğine yeni merkez Yapay zekâ e-ihracatta KOBİ’lerin önünü açıyor Güneydoğu’nun ihracatı 8 ayda 8,2 milyar dolara ulaştı Otomotivde üretim frene bastı: 8 ayda 841 bin araç üretildi</t>
+          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber Düzce'deki Door Kapı Fabrikası'nda çıkan yangına ilçelerden ve Bolu'dan takviye ekipler sevk edildi. Fabrikayı saran alevler dronla havadan görüntülendi.</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -4875,27 +5069,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>https://turkiyedeisdunyasi.com/gomlek-devinin-konkordato-ilan-etti-tusiad-eski-baskaninin-sirketinde-kredi-notu-dustu-132732/</t>
+          <t>https://www.duzcehurhaber.com/duzcede-kapi-fabrikasinda-buyuk-yangin-alevler-sehrin-ust-kesimlerinden-goruldu-4205470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Çorum | Eskişehir | Kilis | Aydın | İstanbul</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>Söke | Beşiktaş | Çerkezköy</t>
-        </is>
-      </c>
+          <t>Bolu</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>deki Door Kapı Fabrikası</t>
+        </is>
+      </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr"/>
@@ -4909,7 +5103,7 @@
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
       <c r="AA23" s="2" t="n">
-        <v>116.5</v>
+        <v>108.86</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>22</v>
@@ -4918,27 +5112,27 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:46:30</t>
+          <t>2026-09-13 20:49:00</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi</t>
+          <t>Başkan Özlü’den fabrika yangını açıklaması</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
+          <t>Başkan Özlü’den fabrika yangını açıklaması Düzce Postası</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -4948,31 +5142,39 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>gıda</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
+          <t>fabrika</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>fabrika</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
+          <t>Düzce’de kapı üretimi yapan bir fabrikada çıkan yangına ilişkin açıklamalarda bulunan Düzce Belediye Başkanı Dr. Faruk Özlü, ekiplerin yangını kontrol altına almak için yoğun şekilde çalıştığını söyledi. Özlü, yangının çıkış nedeninin söndürme çalışmalarının ardından yapılacak incelemelerle belirleneceğini ifade etti. Düzce’de kapı üretimi yapan bir fabrikada çıkan yangına ilişkin açıklamalarda bulunan Düzce Belediye Başkanı Dr. Faruk Özlü, ekiplerin yangını kontrol altına al... Düzce’de kapı üretimi yapan bir fabrikada çıkan yangına ilişkin açıklamalarda bulunan Düzce Belediye Başkanı Dr. Faruk Özlü, ekiplerin yangını kontrol altına almak için yoğun şekilde çalıştığını söyledi. Özlü, yangının çıkış nedeninin söndürme çalışmalarının ardından yapılacak incelemelerle belirleneceğini ifade etti. Düzce’de meydana gelen fabrika yangınının ardından olay yerinde açıklamalarda bulunan Düzce Belediye Başkanı Dr. Faruk Özlü, yangına ilişkin değerlendirmelerde bulundu. Yangının ilk ihbarının D-100 Karayolu’ndan geçen vatandaşlar tarafından belediyeye yapıldığını belirten Özlü, ihbarın ardından itfaiye ekiplerinin bölgeye sevk edildiğini söyledi. Başkan Özlü, “Şu anda bütün ekiplerimiz burada yangını söndürme çalışmalarını yürütüyorlar. Bize gelen ilk ihbar D-100 Karayolu’na yakın olduğu için karayolundan geçenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Bütün gücümüzle bu yangını söndürmeye çalışıyoruz” dedi. “Düzce Belediyesi bölgesinin en güçlü itfaiyesidir” Düzce Belediyesi İtfaiyesi’nin bölgedeki güçlü ekiplerden biri olduğunu vurgulayan Özlü, yangının belediyeye bildirilmesinde gecikme yaşandığı kanaatinde olduğunu dile getirdi. Özlü, “Düzce Belediyesi, her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım” ifadelerini kullandı. Fabrikanın çevresindeki vatandaşlarla da görüştüğünü belirten Özlü, bölgede daha önce de küçük çaplı yangınlar çıktığı yönünde bilgiler aldıklarını aktardı. Bu haberi kaçırmayın Düzce'de ahşap kapı fabrikasında büyük yangın kontrol altına alındı Devamını Oku Yangının çıkış nedeni araştırılacak Yangının neden çıktığının henüz bilinmediğini belirten Özlü, önceliğin yangının tamamen söndürülmesi olduğunu söyledi. Özlü, “Şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış nedeni üzerinde çalışacaklar, raporlarını hazırlayacaklar” dedi. Fabrikanın ahşap ve Amerikan panel üretimi gerçekleştirmesi nedeniyle yangının kısa sürede yayıldığını ifade eden Özlü, “Gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim” diye konuştu. “Önemli olan can kaybının olmaması” Yangında herhangi bir can kaybının bulunmadığını belirten Başkan Özlü, fabrika sahiplerine ve Düzce’ye geçmiş olsun dileklerini iletti. Özlü açıklamasını şu sözlerle tamamladı: “Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız.” Başkan Özlü’den fabrika yangını açıklaması “Düzce Belediyesi bölgesinin en güçlü itfaiyesidir” Yangının çıkış nedeni araştırılacak “Önemli olan can kaybının olmaması” Düzce’de kapı üretimi yapan bir fabrikada çıkan yangına ilişkin açıklamalarda bulunan Düzce Belediye Başkanı Dr. Faruk Özlü, ekiplerin yangını kontrol altına almak için yoğun şekilde çalıştığını söyledi. Özlü, yangının çıkış nedeninin söndürme çalışmalarının ardından yapılacak incelemelerle belirleneceğini ifade etti. Düzce’de meydana gelen fabrika yangınının ardından olay yerinde açıklamalarda bulunan Düzce Belediye Başkanı Dr. Faruk Özlü, yangına ilişkin değerlendirmelerde bulundu. Yangının ilk ihbarının D-100 Karayolu’ndan geçen vatandaşlar tarafından belediyeye yapıldığını belirten Özlü, ihbarın ardından itfaiye ekiplerinin bölgeye sevk edildiğini söyledi. Başkan Özlü, “Şu anda bütün ekiplerimiz burada yangını söndürme çalışmalarını yürütüyorlar. Bize gelen ilk ihbar D-100 Karayolu’na yakın olduğu için karayolundan geçenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Bütün gücümüzle bu yangını söndürmeye çalışıyoruz” dedi. Düzce Belediyesi İtfaiyesi’nin bölgedeki güçlü ekiplerden biri olduğunu vurgulayan Özlü, yangının belediyeye bildirilmesinde gecikme yaşandığı kanaatinde olduğunu dile getirdi. Özlü, “Düzce Belediyesi, her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım” ifadelerini kullandı. Fabrikanın çevresindeki vatandaşlarla da görüştüğünü belirten Özlü, bölgede daha önce de küçük çaplı yangınlar çıktığı yönünde bilgiler aldıklarını aktardı. Yangının neden çıktığının henüz bilinmediğini belirten Özlü, önceliğin yangının tamamen söndürülmesi olduğunu söyledi. Özlü, “Şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış nedeni üzerinde çalışacaklar, raporlarını hazırlayacaklar” dedi. Fabrikanın ahşap ve Amerikan panel üretimi gerçekleştirmesi nedeniyle yangının kısa sürede yayıldığını ifade eden Özlü, “Gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim” diye konuştu. Yangında herhangi bir can kaybının bulunmadığını belirten Başkan Özlü, fabrika sahiplerine ve Düzce’ye geçmiş olsun dileklerini iletti. Özlü açıklamasını şu sözlerle tamamladı: “Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız.” 13 Eyl 2026 - 23:49 Düzce / Düzce - Asayiş Yazdır Yorum yazarak Düzce Postası Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yoru</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
+          <t>Başkan Özlü’den fabrika yangını açıklaması Başkan Özlü’den fabrika yangını açıklaması Düzce Postası Düzce’de kapı üretimi yapan bir fabrikada çıkan yangına ilişkin açıklamalarda bulunan Düzce Belediye Başkanı Dr. Faruk Özlü, ekiplerin yangını kontrol altına almak için yoğun şekilde çalıştığını söyledi. Özlü, yangının çıkış nedeninin söndürme çalışmalarının ardından yapılacak incelemelerle belirleneceğini ifade etti. Faruk Özlü, ekiplerin yangını kontrol altına al... Düzce’de meydana gelen fabrika yangınının ardından olay yerinde açıklamalarda bulunan Düzce Belediye Başkanı Dr. Faruk Özlü, yangına ilişkin değerlendirmelerde bulundu. Yangının ilk ihbarının D-100 Karayolu’ndan geçen vatandaşlar tarafından belediyeye yapıldığını belirten Özlü, ihbarın ardından itfaiye ekiplerinin bölgeye sevk edildiğini söyledi. Başkan Özlü, “Şu anda bütün ekiplerimiz burada yangını söndürme çalışmalarını yürütüyorlar. Bütün gücümüzle bu yangını söndürmeye çalışıyoruz” dedi. “Düzce Belediyesi bölgesinin en güçlü itfaiyesidir” Düzce Belediyesi İtfaiyesi’nin bölgedeki güçlü ekiplerden biri olduğunu vurgulayan Özlü, yangının belediyeye bildirilmesinde gecikme yaşandığı kanaatinde olduğunu dile getirdi. Özlü, “Düzce Belediyesi, her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım” ifadelerini kullandı. Fabrikanın çevresindeki vatandaşlarla da görüştüğünü belirten Özlü, bölgede daha önce de küçük çaplı yangınlar çıktığı yönünde bilgiler aldıklarını aktardı. Bu haberi kaçırmayın Düzce'de ahşap kapı fabrikasında büyük yangın kontrol altına alındı Devamını Oku Yangının çıkış nedeni araştırılacak Yangının neden çıktığının henüz bilinmediğini belirten Özlü, önceliğin yangının tamamen söndürülmesi olduğunu söyledi. Özlü, “Şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış nedeni üzerinde çalışacaklar, raporlarını hazırlayacaklar” dedi. Fabrikanın ahşap ve Amerikan panel üretimi gerçekleştirmesi nedeniyle yangının kısa sürede yayıldığını ifade eden Özlü, “Gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim” diye konuştu. “Önemli olan can kaybının olmaması” Yangında herhangi bir can kaybının bulunmadığını belirten Başkan Özlü, fabrika sahiplerine ve Düzce’ye geçmiş olsun dileklerini iletti. Özlü açıklamasını şu sözlerle tamamladı: “Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız.” Başkan Özlü’den fabrika yangını açıklaması “Düzce Belediyesi bölgesinin en güçlü itfaiyesidir” Yangının çıkış nedeni araştırılacak “Önemli olan can kaybının olmaması” Düzce’de kapı üretimi yapan bir fabrikada çıkan yangına ilişkin açıklamalarda bulunan Düzce Belediye Başkanı Dr. Düzce Belediyesi İtfaiyesi’nin bölgedeki güçlü ekiplerden biri olduğunu vurgulayan Özlü, yangının belediyeye bildirilmesinde gecikme yaşandığı kanaatinde olduğunu dile getirdi. Yangının neden çıktığının henüz bilinmediğini belirten Özlü, önceliğin yangının tamamen söndürülmesi olduğunu söyledi. Yangında herhangi bir can kaybının bulunmadığını belirten Başkan Özlü, fabrika sahiplerine ve Düzce’ye geçmiş olsun dileklerini iletti. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız.” 13 Eyl 2026 - 23:49 Düzce / Düzce - Asayiş Yazdır Yorum yazarak Düzce Postası Gazetesi Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>https://www.nefes.com.tr/turkiyenin-unlu-gida-markasi-iflastan-kurtuldu-alacaklilar-siraya-girdi-151173</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>https://www.duzcepostasi.com/haber/28694540/baskan-ozluden-fabrika-yangini-aciklamasi</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
@@ -4981,7 +5183,7 @@
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr"/>
@@ -4995,7 +5197,7 @@
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
       <c r="AA24" s="2" t="n">
-        <v>75.38</v>
+        <v>68</v>
       </c>
       <c r="AB24" s="2" t="n">
         <v>23</v>
@@ -5004,27 +5206,27 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:22:37</t>
+          <t>2026-09-13 22:33:20</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi</t>
+          <t>Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
+          <t>Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti havadis.com</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -5034,22 +5236,22 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
+          <t>Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti havadis.com</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi 58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber 58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
+          <t>Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti havadis.com Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti havadis.com</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -5059,10 +5261,14 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPanVHckV1ZE9YcmI0UGNQTXpvcWtOU01wSnhYaTA3c0d4eWwxOFlmWGZXUGxmODlIdzd6dmN4dWJPeXhMM0RjeXFRMGZDWDVYUFJydUhVTGwyeURrQlpZM1FHZEk1Q2pUYzFDdWt4NTBVcFNHdlh2RW1VMEloU0c4b055STAwYm9OS1U2QXdLQWRDd0IxZ2R2X19mRUc2TGpzYTAtejFNdllyOTlUUk8tLUwwcDFNZw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOOVJ3cTZrTXh2bmtCV0x2MHlQdkYtZldpc0txMTZKc0RiMFc1d004TXVTbHVtMUludFgwQzdWZGVIYzlIZjF1cU9Sd1h2SElRNV9JbGE1aVdkeGJKTDRTZDhnQzZRLXQ2TDdmVmV3VUdDZURFeE1mTW9hUFc4bVZ3c1NFU2pSdDRIYjQwZVVDY0JjcWNqekpwcUc2Rlc0UEdvY1B2aHBuaTAxOFpneE9FbGd1MW5MMTdfclBF?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
@@ -5071,7 +5277,7 @@
       <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr"/>
@@ -5085,7 +5291,7 @@
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
       <c r="AA25" s="2" t="n">
-        <v>87.54000000000001</v>
+        <v>91.44</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>24</v>
@@ -5094,27 +5300,27 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 15:39:00</t>
+          <t>2026-09-14 07:28:44</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı</t>
+          <t>İnegöl OSB’de tekstil fabrikasında yangın</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı İstiklal Gazetesi</t>
+          <t>İnegöl OSB’de tekstil fabrikasında yangın İnegöl Yerel Haber</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -5124,48 +5330,56 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>firma</t>
+          <t>fabrika, osb, tekstil</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Anasayfa Ekonomi Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Yayınlanma: 13 Eylül 2026 Pazar 18:39 Havva İNCECİK Editör Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Türkiye tekstil sektörünün köklü kuruluşlarından Orta Anadolu Ticaret ve Sanayi İşletmesi T.A.Ş., 73 yıllık üretim faaliyetini sonlandırma kararı aldı. Şirketin Kayseri’deki üretim faaliyetleri 11 Eylül 2026 itibarıyla durdurulurken bütün üretim tesislerinin 12 Ekim 2026 tarihinde tamamen kapatılacağı açıklandı. Dünyaca ünlü markalara üretim yapıyordu 1953 yılında kurulan Orta Anadolu, 1986’dan bu yana dünyanın önde gelen moda markalarına premium denim kumaş tedarik ediyordu. Şirketin Levi’s, Mavi, Lee, Wrangler, Diesel, Replay ve Guess’in de aralarında bulunduğu 300’ün üzerinde markaya denim kumaş sağladığı belirtiliyor. Kapanma kararının gerekçeleri açıklandı Şirket yönetimi, küresel tekstil sektöründe yaşanan talep daralması, artan operasyon ve finansman maliyetleri, tedarik zincirindeki dalgalanmalar ile değişen ticaret koşullarının mevcut işletme modelini sürdürülemez hale getirdiğini bildirdi. Maliyetlerin azaltılması, verimliliğin artırılması ve şirketin yeniden yapılandırılması için kapsamlı çalışmalar yürütüldüğü ancak mevcut ekonomik koşullarda üretimin devam ettirilemediği belirtildi. Kararın geçici olmadığı belirtildi Şirketin yönetim kurulu tarafından alınan karar kapsamında Kayseri’deki üretimin kalıcı olarak sonlandırıldığı ifade edildi. Tesislerin kapatılmasına yönelik işlemler için 12 Ekim’e kadar sürecek bir takvim belirlendi. Şirket yönetimi, kapanış sürecinde çalışanlara, müşterilere, finans kuruluşlarına ve tedarikçilere yönelik ticari yükümlülüklerin şeffaflık ve sorumluluk anlayışıyla yerine getirileceğini açıkladı. Kaynak: Haber Merkezi HABERE YORUM KAT UYARI: Küfür, hakaret, rencide edici cümleler veya imalar, inançlara saldırı içeren, imla kuralları ile yazılmamış, Türkçe karakter kullanılmayan ve büyük harflerle yazılmış yor</t>
+          <t>İnegöl OSB’de tekstil fabrikasında yangın İnegöl Yerel Haber</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı İstiklal Gazetesi Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Şirkete ait bütün üretim tesisleri 12 Ekim 2026’da tamamen kapatılacak. Anasayfa Ekonomi Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Peş peşe yaşanan iflas ve konkordato dalgasına dev firma da katıldı Yayınlanma: 13 Eylül 2026 Pazar 18:39 Havva İNCECİK Editör Premium denim üreticisi Orta Anadolu, Kayseri’de üretimi durdurdu. Türkiye tekstil sektörünün köklü kuruluşlarından Orta Anadolu Ticaret ve Sanayi İşletmesi T.A.Ş., 73 yıllık üretim faaliyetini sonlandırma kararı aldı. Şirketin Kayseri’deki üretim faaliyetleri 11 Eylül 2026 itibarıyla durdurulurken bütün üretim tesislerinin 12 Ekim 2026 tarihinde tamamen kapatılacağı açıklandı. Dünyaca ünlü markalara üretim yapıyordu 1953 yılında kurulan Orta Anadolu, 1986’dan bu yana dünyanın önde gelen moda markalarına premium denim kumaş tedarik ediyordu. Şirketin Levi’s, Mavi, Lee, Wrangler, Diesel, Replay ve Guess’in de aralarında bulunduğu 300’ün üzerinde markaya denim kumaş sağladığı belirtiliyor. Kapanma kararının gerekçeleri açıklandı Şirket yönetimi, küresel tekstil sektöründe yaşanan talep daralması, artan operasyon ve finansman maliyetleri, tedarik zincirindeki dalgalanmalar ile değişen ticaret koşullarının mevcut işletme modelini sürdürülemez hale getirdiğini bildirdi. Maliyetlerin azaltılması, verimliliğin artırılması ve şirketin yeniden yapılandırılması için kapsamlı çalışmalar yürütüldüğü ancak mevcut ekonomik koşullarda üretimin devam ettirilemediği belirtildi. Kararın geçici olmadığı belirtildi Şirketin yönetim kurulu tarafından alınan karar kapsamında Kayseri’deki üretimin kalıcı olarak sonlandırıldığı ifade edildi. Tesislerin kapatılmasına yönelik işlemler için 12 Ekim’e kadar sürecek bir takvim belirlendi. Şirket yönetimi, kapanış sürecinde çalışanlara, müşterilere, finans kuruluşlarına ve tedarikçilere yönelik ticari yükümlülüklerin şeffaflık ve sorumluluk anlayışıyla yerine getirileceğini açıkladı.</t>
+          <t>İnegöl OSB’de tekstil fabrikasında yangın İnegöl OSB’de tekstil fabrikasında yangın İnegöl Yerel Haber İnegöl OSB’de tekstil fabrikasında yangın İnegöl Yerel Haber</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>https://www.istiklal.com.tr/ekonomi/pes-pese-yasanan-iflas-ve-konkordato-dalgasina-dev-firma-da-katildi-1105108h</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxObDhJSHJRQmI1b1pwYzNzMFc1YnVaanVoSWswM09ISGV1aE9QWXF6aVJwbjJ0bzBnaUlaTHk5QlNLLWdGZzhoaENBeVVtbVVTamplSm1fNE9DNkFnTlEyWjdRa3MzckltVTdPRVRGczZfTlhxSWJxY2FfN3RsLVVnZjM2Um5qcVU50gGOAUFVX3lxTE13M05uTzVKTlZYSFFoX0s0UGVzeEZKV21SSjJCUEFSVVBrNGx0N242R0RfaVliRGxJY2VleDI5ZVB4VEcydG4yZnJ4YXlTNGdTbnpoRE5OUU1yYm5FQ1l5aG53ZkNwSGhvSHdYeG0zdjlYdTVkVERXRTFNaG40UUJSQ09Vb2NPV0l5dXAwTXc?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Kayseri</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>İnegöl</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>İnegöl OSB | tekstil fabrikasında yangın İnegöl OSB</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr"/>
@@ -5179,7 +5393,7 @@
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" s="2" t="n">
-        <v>95.75</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AB26" s="2" t="n">
         <v>25</v>
@@ -5188,27 +5402,27 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:27:00</t>
+          <t>2026-09-13 20:48:21</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>fabrika yangını</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı!</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız"</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" Mersin Haber</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -5218,22 +5432,22 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>şirket / firma</t>
+          <t>fabrika</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. 14.09.2026 - 10:27 Yayınlanma — Paylaşım 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Kahramanmaraş Asliye Ticaret Mahkemesi’nin 2 Eylül 2026 tarihli kararı doğrultusunda, Germenicia Boya Tekstil Petrol İnşaat Sanayi ve Ticaret Limited Şirketi hakkında iflas kararı verildi. Mahkemenin 2025/22 Esas sayılı dosyasında verilen karara göre şirketin iflasına 2 Eylül 2026 saat 10.25 itibarıyla hükmedildi. Kararın ardından şirketin tasfiye işlemlerine başlandığı bildirildi. İflas kararının, İcra ve İflas Kanunu’nun 166. maddesi kapsamında ilan yoluyla tebliğ edildiği belirtildi. Germenicia Tekstil hakkında da iflas kararı Aynı mahkeme kararı kapsamında Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi hakkında da iflas işlemi başlatıldı. Bu şirketin de 2 Eylül 2026 tarihinde saat 10.25 itibarıyla iflasına karar verildiği duyuruldu. Mahkeme kararının ardından şirketin tasfiye sürecinin başlatıldığı ve kararın ilgili mevzuat gereğince ilan edildiği bildirildi. Konkordato sürecinde 2 aylık uzatma Kahramanmaraş Asliye Ticaret Mahkemesi’nde görülen bir başka konkordato dosyasında ise A.T., G.T., N.T. ile Maktes Isıtma ve Soğutma Sistemleri Taahhüt Makina Tesisat İnşaat Plan Proje Sanayi ve Ticaret Limited Şirketi hakkında yeni karar alındı. Benzin 80 TL’yi aştı! Gözler motorin zammında: 100 TL sınırına dayanacak İçeriği Görüntüle Mahkemenin 9 Eylül 2026 tarihli ara kararı doğrultusunda, 1 Ekim 2026 tarihinden itibaren geçerli olmak üzere kesin mühletin 2 ay süreyle uzatılmasına hükmedildi. Daha önce uygulanan kesin mühlete ilişkin tedbirlerin de devam etmesine karar verildi. Karar kapsamında, mahkemenin izni olmaksızın rehin, kefalet, devir, takyit ve ivazsız tasarruf işlemlerinin önlenmesine yönelik tedbirlerin sürdürüleceği bildirildi. Ayrıca her türlü ihtiyati tedbir ve ihtiyati haciz işlemleri ile muhafaza işlemleri dahil takip işlemlerinin de ihtiyati tedbir yoluyla durdurulmasına karar verildi. Alacaklılara 7 günlük itiraz süresi Mahkeme, konkordato sürecine ilişkin olarak alacaklılara da çağrıda bulundu. Buna göre alacaklıların, ilanın yayımlanmasından itibaren 7 gün içinde mahkeme dosyasına itiraz edebileceği bildirildi. Alacaklıların, konkordato mühleti verilmesini gerektiren bir durum bulunmadığını delilleriyle birlikte ortaya koyarak konkordato talebinin reddedilmesini isteme hakkı bulunduğu belirtildi. Editör Hakkında Editör 02 Bunlar da</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" Düzce Belediye Başkanı Faruk Özlü, kapı fabrikasındaki yangına ilişkin, "Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. 13 Eylül 2026 @mersinhaber 'i takip et Düzce D-100 kara yolu üzerinde bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında çıkan yangın devam ediyor. Söndürme çalışmalarını incelemek için olay yerine gelen Düzce Belediye Başkanı Faruk Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirtti. Başkan Özlü, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Ama gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. Düzce D-100 kara yolu üzerinde bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında çıkan yangın devam ediyor. Söndürme çalışmalarını incelemek için olay yerine gelen Düzce Belediye Başkanı Faruk Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirtti. Başkan Özlü, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Ama gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. 13 Eylül 2026 @mersinhaber 'i takip et Düzce D-100 kara yolu üzerinde bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında çıkan yangın devam ediyor. Söndürme çalışmalarını incelemek için olay yerine gelen Düzce Belediye Başkanı Faruk Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirtti. Başkan Özlü, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Ama gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" Düzce Belediye Başkanı Faruk Özlü, kapı fabrikasındaki yangına ilişkin, "Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! 14.09.2026 - 10:27 Yayınlanma — Payl</t>
+          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" Mersin Haber Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" Düzce Belediye Başkanı Faruk Özlü, kapı fabrikasındaki yangına ilişkin, "Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. 13 Eylül 2026 @mersinhaber 'i takip et Düzce D-100 kara yolu üzerinde bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında çıkan yangın devam ediyor. Söndürme çalışmalarını incelemek için olay yerine gelen Düzce Belediye Başkanı Faruk Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirtti. Başkan Özlü, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce’mize geçmiş olsun diliyorum. Düzce D-100 kara yolu üzerinde bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında çıkan yangın devam ediyor.</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -5243,61 +5457,33 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://www.edetv.com.tr/kahramanmarasta-iki-sirket-icin-iflas-karari-biri-icin-konkordatoda-muhlet-uzatildi</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş</t>
-        </is>
-      </c>
+          <t>https://www.mersinhaber.com/amp/haber/774512</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
       <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi:raw_legal</t>
-        </is>
-      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi Kahramanmaraş Türkiye</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr"/>
       <c r="AA27" s="2" t="n">
-        <v>173.25</v>
+        <v>115.75</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>26</v>
@@ -5306,27 +5492,27 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:52:25</t>
+          <t>2026-09-14 14:23:02</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>konkordato</t>
+          <t>dolandırıcılık</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı</t>
+          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
+          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı Aksiyon.com.TR</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -5336,32 +5522,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>turizm</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
+          <t>Eskişehir Emniyet'in 'KAPTIRMA' projesiyle 90 şubeden 150 banka çalışanına şüpheli para işlemleri, iletişim ve anlık ihbar yöntemleri anlatıldı. Eskişehir Emniyet'in 'KAPTIRMA' projesiyle 90 şubeden 150 banka çalışanına şüpheli para işlemleri, iletişim ve anlık ihbar yöntemleri anlatıldı. Eskişehir Emniyet'in 'KAPTIRMA' projesiyle 90 şubeden 150 banka çalışanına şüpheli para işlemleri, iletişim ve anlık ihbar yöntemleri anlatıldı. Eskişehir polisinden banka personeline yönelik bilgilendirme Eskişehir İl Emniyet Müdürlüğü tarafından dolandırıcılık suçlarıyla mücadele kapsamında hayata geçirilen 'KAPTIRMA' projesi çerçevesinde kent genelindeki banka yöneticileri ve özel güvenlik görevlilerine yönelik kapsamlı bir bilgilendirme toplantısı düzenlendi. Toplantı, İl Emniyet Müdürlüğü yerleşkesinde Asayiş Şube Müdürlüğü koordinesinde gerçekleştirildi. Programa, Eskişehir genelinde faaliyet gösteren yaklaşık 90 banka şubesinden 150 yönetici ve özel güvenlik görevlisi katılım sağladı. Toplantının içeriği: Programda son dönemde artış gösteren dolandırıcılık yöntemleri ile şüpheli finansal işlemler ayrıntılı olarak ele alındı. Katılımcılara, banka şubelerinde gözlemlenebilecek risk senaryoları ve uyarı işaretleri hakkında kapsamlı bilgi verildi. Şüpheli işlemler ve anlık iletişim: Bilgilendirme oturumlarında, şüpheli para çekme ve havale/EFT işlemlerinde izlenmesi gereken adımlar , panik veya baskı altındaki vatandaşlara yönelik doğru iletişim yaklaşımları ve emniyet birimleriyle kurulacak anlık ihbar mekanizmaları detaylandırıldı. Eğitimler, banka personeli ile emniyet güçleri arasındaki koordinasyonun önemine vurgu yapıldı. Toplantıda ayrıca; vatandaşların maddi mağduriyet yaşamasının önüne geçilmesinin hedeflendiği, farkındalık oluşturma ve denetim çalışmalarının kararlılıkla devam edeceği bildirildi. ESKİŞEHİR İL EMNİYET MÜDÜRLÜĞÜ TARAFINDAN DOLANDIRICILIK SUÇLARIYLA MÜCADELE ÇERÇEVESİNDE HAYATA GEÇİRİLEN "KAPTIRMA" PROJESİ KAPSAMINDA, KENT GENELİNDEKİ BANKA YÖNETİCİLERİ VE GÜVENLİK PERSONELİNE YÖNELİK KAPSAMLI BİR BİLGİLENDİRME TOPLANTISI DÜZENLENDİ. 1 Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi 2 Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını 3 Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor 4 Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı 5 Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı 6 Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı 7 Ereğli'de tanker şarampole devrildi: 1 yaralı Ereğli'de tanker şarampole devrildi: 1 yaralı Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı Eskişehir polisinden banka personeline yönelik bilgilendirme Eskişehir Emniyet'in 'KAPTIRMA' projesiyle 90 şubeden 150 banka çalışanına şüpheli para işlemleri, iletişim ve anlık ihbar yöntemleri anlatıldı. Eskişehir İl Emniyet Müdürlüğü tarafından dolandırıcılık suçlarıyla mücadele kapsamında hayata geçirilen 'KAPTIRMA' projesi çerçevesinde kent genelindeki banka yöneticileri ve özel güvenlik görevlilerine yönelik kapsamlı bir bilgilendirme toplantısı düzenlendi. Toplantı, İl Emniyet Müdürlüğü yerleşkesinde Asayiş Şube Müdürlüğü koordinesinde gerçekleştirildi. Programa, Eskişehir genelinde faaliyet gösteren yaklaşık 90 banka şubesinden 150 yönetici ve özel güvenlik görevlisi katılım sağladı. Programda son dönemde artış gösteren dolandırıcılık yöntemleri ile şüpheli finansal işlemler ayrıntılı olarak ele alındı. Katılımcılara, banka şubelerinde gözlemlenebilecek risk senaryoları ve uyarı işaretleri hakkında kapsamlı bilgi verildi. Bilgilendirme oturumlarında, şüpheli para çekme ve havale/EFT işlemlerinde izlenmesi gereken adımlar , panik veya baskı altındaki vatandaşlara yönelik doğru iletişim yaklaşımları ve emniyet birimleriyle kurulacak anlık ihbar mekanizmaları detaylandırıldı. Eğitimler, banka personeli ile emniyet güçleri arasındaki koordinasyonun önemine vurgu yapıldı. Toplantıda ayrıca; vatandaşların maddi mağduriyet yaşamasının önüne geçilmesinin hedeflendiği, farkındalık oluşturma ve denetim çalışmalarının kararlılıkla devam edeceği bildirildi. ESKİŞEHİR İL EMNİYET MÜDÜRLÜĞÜ TARAFINDAN DOLANDIRICILIK SUÇLARIYLA MÜCADELE ÇERÇEVESİNDE HAYATA GEÇİRİLEN "KAPTIRMA" PROJESİ KAPSAMINDA, KENT GENELİNDEKİ BANKA YÖNETİCİLERİ VE GÜVENLİK PERSONELİNE YÖNELİK KAPSAMLI BİR BİLGİLENDİRME TOPLANTISI DÜZENLENDİ. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. aksiyon.com.tr Gündem'deyim ama spesifik olarak eğitim ve sağlık politikalarındaki güncel gelişmelere odaklanıyorum. Öğrenmeye açık, meraklı ve enerjik bir yapım var. 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
+          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı Aksiyon.com.TR Eskişehir Emniyet'in 'KAPTIRMA' projesiyle 90 şubeden 150 banka çalışanına şüpheli para işlemleri, iletişim ve anlık ihbar yöntemleri anlatıldı. Eskişehir polisinden banka personeline yönelik bilgilendirme Eskişehir İl Emniyet Müdürlüğü tarafından dolandırıcılık suçlarıyla mücadele kapsamında hayata geçirilen 'KAPTIRMA' projesi çerçevesinde kent genelindeki banka yöneticileri ve özel güvenlik görevlilerine yönelik kapsamlı bir bilgilendirme toplantısı düzenlendi. Toplantı, İl Emniyet Müdürlüğü yerleşkesinde Asayiş Şube Müdürlüğü koordinesinde gerçekleştirildi. Programa, Eskişehir genelinde faaliyet gösteren yaklaşık 90 banka şubesinden 150 yönetici ve özel güvenlik görevlisi katılım sağladı. Toplantının içeriği: Programda son dönemde artış gösteren dolandırıcılık yöntemleri ile şüpheli finansal işlemler ayrıntılı olarak ele alındı. Katılımcılara, banka şubelerinde gözlemlenebilecek risk senaryoları ve uyarı işaretleri hakkında kapsamlı bilgi verildi. Şüpheli işlemler ve anlık iletişim: Bilgilendirme oturumlarında, şüpheli para çekme ve havale/EFT işlemlerinde izlenmesi gereken adımlar , panik veya baskı altındaki vatandaşlara yönelik doğru iletişim yaklaşımları ve emniyet birimleriyle kurulacak anlık ihbar mekanizmaları detaylandırıldı. Eğitimler, banka personeli ile emniyet güçleri arasındaki koordinasyonun önemine vurgu yapıldı. Toplantıda ayrıca; vatandaşların maddi mağduriyet yaşamasının önüne geçilmesinin hedeflendiği, farkındalık oluşturma ve denetim çalışmalarının kararlılıkla devam edeceği bildirildi. ESKİŞEHİR İL EMNİYET MÜDÜRLÜĞÜ TARAFINDAN DOLANDIRICILIK SUÇLARIYLA MÜCADELE ÇERÇEVESİNDE HAYATA GEÇİRİLEN "KAPTIRMA" PROJESİ KAPSAMINDA, KENT GENELİNDEKİ BANKA YÖNETİCİLERİ VE GÜVENLİK PERSONELİNE YÖNELİK KAPSAMLI BİR BİLGİLENDİRME TOPLANTISI DÜZENLENDİ. 1 Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi Gölyazı'da geceyi aydınlatan alevler itfaiyeyi alarma geçirdi 2 Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını Zirvede inanç ve zorluk: Ulu Baba Dağı'na yaz akını 3 Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor Denizli'de Yeşilyurt'ta kaybolan 67 yaşındaki Alzheimer hastası için aramalar sürüyor 4 Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı Eskişehir’de NATO karşıtı izinsiz eyleme müdahale: 35 gözaltı 5 Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı Silivri'de elektrik direği kesimi sırasında çıkan yangın ekili arazilere sıçradı 6 Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı Bursa’da otluk alanda çıkan yangın itfaiye müdahalesiyle kontrol altına alındı 7 Ereğli'de tanker şarampole devrildi: 1 yaralı Ereğli'de tanker şarampole devrildi: 1 yaralı Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı Eskişehir polisinden banka personeline yönelik bilgilendirme Eskişehir Emniyet'in 'KAPTIRMA' projesiyle 90 şubeden 150 banka çalışanına şüpheli para işlemleri, iletişim ve anlık ihbar yöntemleri anlatıldı. Eskişehir İl Emniyet Müdürlüğü tarafından dolandırıcılık suçlarıyla mücadele kapsamında hayata geçirilen 'KAPTIRMA' projesi çerçevesinde kent genelindeki banka yöneticileri ve özel güvenlik görevlilerine yönelik kapsamlı bir bilgilendirme toplantısı düzenlendi. Programda son dönemde artış gösteren dolandırıcılık yöntemleri ile şüpheli finansal işlemler ayrıntılı olarak ele alındı. Bilgilendirme oturumlarında, şüpheli para çekme ve havale/EFT işlemlerinde izlenmesi gereken adımlar , panik veya baskı altındaki vatandaşlara yönelik doğru iletişim yaklaşımları ve emniyet birimleriyle kurulacak anlık ihbar mekanizmaları detaylandırıldı. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Taşacak Bu Deniz 13. Valilik ve Meteoroloji Açıklamaları 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOYnVoWnhPQXR6MDdHdkRVTWhLZDF5YTRTSmNJSmtpbVJacEVmRUEtelBJSmtwN2ZWeTFBbG9acUFROXRQVWZ3WVN2SEN1UGQtX0QwT3pKUldzQlJOZGZxcnptSU5taUpMQjR4dmVRZHVlN0w3Wm5GM2kwQUpKVnZIQWpPVXVSUzAteHdXWndFNUFEbnFtS3k4bU5xNU9pS0V5QUw0NldB?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>https://www.aksiyon.com.tr/bankalara-yonelik-kaptirma-egitimleriyle-dolandiriciliga-karsi-onlem-artirildi-354593</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | Denizli | Düzce | Eskişehir | İstanbul</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Silivri | Ereğli | Yeşilyurt</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -5369,7 +5567,7 @@
       <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr"/>
@@ -5383,7 +5581,7 @@
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
       <c r="AA28" s="2" t="n">
-        <v>68.42</v>
+        <v>112.75</v>
       </c>
       <c r="AB28" s="2" t="n">
         <v>27</v>
@@ -5392,7 +5590,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:39:00</t>
+          <t>2026-09-14 14:22:08</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -5407,12 +5605,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı!</t>
+          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi</t>
+          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede havadis.com</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -5422,18 +5620,22 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>turizm</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. VİB Turizm'den dolandırıcılık uyarısı! Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. Haber Merkezi Editör 13.09.2026 - 17:39 Yayınlanma — P</t>
+          <t>Eskişehir Emniyeti, artan dolandırıcılık vakalarına karşı banka çalışanlarını birer savunma hattına dönüştürüyor. Eskişehir Emniyeti, artan dolandırıcılık vakalarına karşı banka çalışanlarını birer savunma hattına dönüştürüyor. Eskişehir Emniyeti, artan dolandırıcılık vakalarına karşı banka çalışanlarını birer savunma hattına dönüştürüyor. Eskişehir Emniyeti, artan dolandırıcılık vakalarına karşı banka çalışanlarını birer savunma hattına dönüştürüyor. KAPTIRMA projesiyle 90 şubeden 150 görevli, şüpheli işlemleri anında tespit edip emniyetle koordineli hareket etmek üzere özel bir eğitimden geçirildi. Facebook'ta Paylaş X'de Paylaş Whatsapp'tan Gönder YAYINLAMA: 14 Eylül 2026 - 17:22 EDİTÖR: Havadis KAYNAK: İhlas Haber Ajansı Eskişehir İl Emniyet Müdürlüğü, vatandaşların birikimlerini hedef alan dolandırıcılık şebekelerine karşı oldukça kapsamlı ve stratejik bir savunma mekanizması geliştirdi. Asayiş Şube Müdürlüğü tarafından yürütülen çalışmalar kapsamında, kent genelinde faaliyet gösteren yaklaşık 90 farklı banka şubesinden 150 yönetici ve özel güvenlik görevlisi, emniyet yerleşkesinde düzenlenen özel bir bilgilendirme toplantısında bir araya getirildi. KAPTIRMA ismi verilen bu yeni proje, finansal kurumların dolandırıcılıkla mücadeledeki rolünü güçlendirmeyi hedefliyor. Banka çalışanları artık ilk savunma hattı Düzenlenen eğitim programında, son dönemde sıkça karşılaşılan ve vatandaşları ciddi maddi kayıplara uğratan dolandırıcılık yöntemleri detaylı bir şekilde masaya yatırıldı. Özellikle panik halindeki müşterilerin gerçekleştirdiği şüpheli para çekme, havale veya EFT işlemleri üzerinde duruldu. Banka personeline, bu tür durumlarda müşterinin üzerindeki baskıyı nasıl fark edebilecekleri ve bu kişilere nasıl yaklaşmaları gerektiği konusunda profesyonel iletişim teknikleri aktarıldı. Emniyet yetkilileri, banka çalışanlarının bu noktada kritik bir gözlemci rolü üstlendiğini belirtti. Anlık ihbar mekanizması kuruldu Projenin en önemli ayağını ise emniyet birimleri ile bankalar arasında kurulan hızlı iletişim ağı oluşturuyor. Şüpheli bir işlemle karşılaşıldığında, banka görevlilerinin vakit kaybetmeden emniyet güçlerine haber verebilmesi için geliştirilen anlık ihbar mekanizması, mağduriyetlerin henüz gerçekleşmeden önlenmesini amaçlıyor. Bu koordinasyonun, dolandırıcıların vatandaşları ikna ederek gerçekleştirdiği hızlı para transferlerini durdurmak adına hayati bir önem taşıdığı vurgulandı. Kararlılıkla sürecek denetimler Eskişehir Emniyeti, bu projenin sadece bir bilgilendirme toplantısıyla sınırlı kalmayacağını, vatandaşların birikimlerini korumak adına benzer denetim ve eğitim çalışmalarının kararlılıkla devam edeceğini duyurdu. Banka çalışanlarının dolandırıcılık olaylarına karşı daha duyarlı hale getirilmesiyle, suçluların finansal sistem üzerinden gerçekleştirdiği faaliyetlerin büyük ölçüde engellenmesi hedefleniyor. Emniyet yetkilileri, banka personeli ile emniyet güçleri arasındaki bu iş birliğinin, suçla mücadelede yeni bir dönemi başlattığını ifade etti. Suikast iddiasıyla başlayan davada sürpriz karar: 6 sanık için tahliye yolu açıldı #İstanbul / 14 Eylül 2026 Balıkesir'de yeşil devrim: 33 futbol sahası büyüklüğünde nefes alanı oluşturuldu #Yaşam / 14 Eylül 2026 Malatya'da korkutan kaza: Çarpışmanın şiddetiyle araç ters döndü #Asayiş / 14 Eylül 2026 Yoru</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm'den dolandırıcılık uyarısı! VİB Turizm'den dolandırıcılık uyarısı! Bizim Sakarya Gazetesi Sakarya Vib Turizm Yönetim Kurulu Başkanı Suat Akın, kendi ismi ve telefon numarası kullanılarak vatandaşlardan para talep edildiğini belirterek acil bir dolandırıcılık uyarısı yayımladı. Akın, kendi adına gelen hiçbir para talebine itibar edilmemesi gerektiğini vurguladı. VİB Turizm'den dolandırıcılık uyarısı!</t>
+          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede havadis.com Eskişehir Emniyeti, artan dolandırıcılık vakalarına karşı banka çalışanlarını birer savunma hattına dönüştürüyor. KAPTIRMA projesiyle 90 şubeden 150 görevli, şüpheli işlemleri anında tespit edip emniyetle koordineli hareket etmek üzere özel bir eğitimden geçirildi.</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -5443,10 +5645,14 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.bizimsakarya.com.tr/vib-turizmden-dolandiricilik-uyarisi</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>https://www.havadis.com/asayis/eskisehir-de-bankalara-dolandiricilik-kalkani-kaptirma-projesi-devrede/499303</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Eskişehir</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
@@ -5455,7 +5661,7 @@
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr"/>
@@ -5469,7 +5675,7 @@
       <c r="Y29" s="2" t="inlineStr"/>
       <c r="Z29" s="2" t="inlineStr"/>
       <c r="AA29" s="2" t="n">
-        <v>54.14</v>
+        <v>87.25</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>28</v>
@@ -5483,7 +5689,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>borç krizi</t>
+          <t>mali kriz</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -5559,7 +5765,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>İstanbul Ticaret Üniversitesi | İstanbul Ticaret Merkezi | İstanbul Ticaret İş Güvenliği ve Endüstriyel Ürünler San. A.Ş | İstanbul Ticaret Üniversitesi Küçükyalı Kampüsü | İstanbul Ticaret Borsası</t>
+          <t>İstanbul Ticaret Üniversitesi | İstanbul Ticaret Merkezi | İstanbul Ticaret İş Güvenliği ve Endüstriyel Ürünler San. A.Ş | İstanbul Ticaret İl Müdürlüğü | İstanbul Ticaret Üniversitesi Küçükyalı Kampüsü</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -5588,12 +5794,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:58:46</t>
+          <t>2026-09-14 09:05:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>mali kriz</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -5603,12 +5809,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti</t>
+          <t>Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu!</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti Sözcü Gazetesi</t>
+          <t>Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu! babaocagi.com.tr</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -5618,35 +5824,35 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>tekstil</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. Google algoritmasına bırakmayın, okuyacağınız haberi siz seçin! Tıkla ve ekle Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. 2019’da faaliyetlerine başlayan şirket, tekstil üretiminin yanı sıra otelcilik sektöründe de faaliyet gösteriyordu. Kahramanmaraş İcra Dairesi, şirket hakkında verilen iflas kararının ardından iflasın açılmasına ilişkin işlemleri uygulamaya aldı. ŞİRKETİN ÜRETİM KAPASİTESİ NE KADARDI? Günün Trend Haberleri Germenicia Boya Tekstil’in boyahane bölümünde yıllık 5 milyon 400 bin kilogram üretim kapasitesi bulunuyordu. Örgü bölümünün yıllık üretim kapasitesi ise 5 milyon kilogram seviyesindeydi. Yaklaşık 200 kişinin çalıştığı şirket, tekstil sektöründeki faaliyetlerini Kahramanmaraş merkezli olarak sürdürüyordu. OTELCİLİK SEKTÖRÜNDE DE FAALİYET GÖSTERİYORDU Şirketin tekstilin yanı sıra turizm sektöründe de yatırımı bulunuyordu. İstanbul’da Germenicia Hotel adıyla faaliyet gösteren bir işletmesi vardı. Şirketin finansal darboğazın ardından konkordato sürecinden başarıyla çıkamaması üzerine iflas kararı verildi. Şirketin vergi levhasındaki bilgilere göre 2024 ve 2025 yıllarında vergi matrahı oluşmadı. 2023 yılında ise 2 milyon 362 bin 651 TL matrah ve 590 bin 662 TL vergi tahakkuku kaydedilmişti. Kahramanmaraş İcra Dairesi, verilen iflas kararının ardından şirket hakkında ilgili iflas işlemlerini başlattı. www.sozcu.com.tr internet sitesinde yayınlanan yazı, haber ve fotoğrafların her türlü telif hakkı Mega Ajans ve Rek. Tic. A.Ş'ye aittir. İzin alınmadan, kaynak gösterilerek dahi iktibas edilemez. Bu habere emoji ile tepki ver 2019’da faaliyetlerine başlayan şirket, tekstil üretiminin yanı sıra otelcilik sektöründe de faaliyet gösteriyordu. Kahramanmaraş İcra Dairesi, şirket hakkında verilen iflas kararının ardından iflasın açılmasına ilişkin işlemleri uygulamaya aldı. ŞİRKETİN ÜRETİM KAPASİTESİ NE KADARDI? Günün Trend Haberleri Germenicia Boya Tekstil’in boyahane bölümünde yıllık 5 milyon 400 bin kilogram üretim kapasitesi bulunuyordu. Örgü bölümünün yıllık üretim kapasitesi ise 5 milyon kilogram seviyesindeydi. Yaklaşık 200 kişinin çalıştığı şirket, tekstil sektöründeki faaliyetlerini Kahramanmaraş merkezli olarak sürdürüyordu. OTELCİLİK SEKTÖRÜNDE DE FAALİYET GÖSTERİYORDU Şirketin tekstilin yanı sıra turizm sektöründe de yatırımı bulunuyordu. İstanbul’da Germenicia Hotel adıyla faaliyet gösteren bir işletmesi vardı. Şirketin finansal darboğazın ardından konkordato sürecinden başarıyla çıkamaması üzerine iflas kararı verildi. Şirketin vergi levhasındaki bilgilere göre 2024 ve 2025 yıllarında vergi matrahı oluşmadı. 2023 yılında ise 2 milyon 362 bin 651 TL matrah ve 590 bin 662 TL vergi tahakkuku kaydedilmişti. Kahramanmaraş İcra Dairesi, verilen iflas kararının ardından şirket hakkında ilgili iflas işlemlerini başlattı. DOLAR 48,62 0,10 (%0,20) EURO 56,15 -0,17 (%-0,31) Haber Merkezi Facebook ile paylaş Messenger ile gönd</t>
+          <t>Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu! babaocagi.com.tr</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Yüzlerce çalışanı olan Türk tekstil devi iflas etti Yüzlerce çalışanı olan Türk tekstil devi iflas etti Sözcü Gazetesi Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. Yaklaşık 200 çalışanı bulunan ve yıllık 5 milyon kilogramın üzerinde üretim kapasitesine sahip şirket için iflas işlemleri başlatıldı. Google algoritmasına bırakmayın, okuyacağınız haberi siz seçin! Tıkla ve ekle Türkiye’de tekstil sektöründe faaliyet gösteren Kahramanmaraş merkezli Germenicia Boya Tekstil’in iflas ettiği açıklandı. 2019’da faaliyetlerine başlayan şirket, tekstil üretiminin yanı sıra otelcilik sektöründe de faaliyet gösteriyordu. Kahramanmaraş İcra Dairesi, şirket hakkında verilen iflas kararının ardından iflasın açılmasına ilişkin işlemleri uygulamaya aldı. ŞİRKETİN ÜRETİM KAPASİTESİ NE KADARDI? Günün Trend Haberleri Germenicia Boya Tekstil’in boyahane bölümünde yıllık 5 milyon 400 bin kilogram üretim kapasitesi bulunuyordu. Örgü bölümünün yıllık üretim kapasitesi ise 5 milyon kilogram seviyesindeydi. Yaklaşık 200 kişinin çalıştığı şirket, tekstil sektöründeki faaliyetlerini Kahramanmaraş merkezli olarak sürdürüyordu. OTELCİLİK SEKTÖRÜNDE DE FAALİYET GÖSTERİYORDU Şirketin tekstilin yanı sıra turizm sektöründe de yatırımı bulunuyordu. İstanbul’da Germenicia Hotel adıyla faaliyet gösteren bir işletmesi vardı. Şirketin finansal darboğazın ardından konkordato sürecinden başarıyla çıkamaması üzerine iflas kararı verildi. Şirketin vergi levhasındaki bilgilere göre 2024 ve 2025 yıllarında vergi matrahı oluşmadı. Kahramanmaraş İcra Dairesi, verilen iflas kararının ardından şirket hakkında ilgili iflas işlemlerini başlattı. İzin alınmadan, kaynak gösterilerek dahi iktibas edilemez. Bu habere emoji ile tepki ver 2019’da faaliyetlerine başlayan şirket, tekstil üretiminin yanı sıra otelcilik sektöründe de faaliyet gösteriyordu.</t>
+          <t>Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu! Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu! babaocagi.com.tr Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu!</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://www.sozcu.com.tr/yuzlerce-calisani-olan-turk-tekstil-devi-iflas-etti-p358094</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul | Kahramanmaraş</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPRkpIQ3BETW1aMTI1ZkF3T2xGSGRCaGNRa2sxVjRGWi1DakxUNXZZcTBQdjVDamY1aTBWWW9XN0ZGMWtickdOODRNQ3hTLXQ3MVQ4YXB3bk15ZEFoYUFxdkp3aUVXY01ROFZZWllzRDRZZnpPc3JWb2N4X0lzR3o0QWRnNVNXRTBVckRPN1lweS1XVUljY3NZVVBSY2JVVlB2LU5wZg?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
@@ -5655,7 +5861,7 @@
       <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr"/>
@@ -5669,7 +5875,7 @@
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="n">
-        <v>75</v>
+        <v>77.42</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>30</v>
@@ -5678,12 +5884,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:12:00</t>
+          <t>2026-09-14 14:29:33</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -5693,12 +5899,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti Tek Referans</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -5718,34 +5924,26 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti Tek Referans</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Doğrulama başarılı.</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti Tek Referans İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti Tek Referans</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://www.kocaelibarisgazetesi.com/amp/gundem/gebzede-iflas-eden-sirket-icin-alacaklilara-cagri-1-ay-sure-verildi-h160416</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>Kocaeli</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>Gebze</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPUzE0Z0x2amtxSm0wTzh1MHFZQjI4OHZiOElkYl9naFJ3NnJONE9TeU5ldmZhY3NPYzBxaVZRRFR3d1VFcXVWcmNRdVZBN1p1Ul90VGxoMExRTEtzaEtOWUdDU1NXYXgzY1hkeER5Rm5nZEJNQk1EOXUxSmpxSHBoeENBU0tYZGtLbzNpWklEbUFIdVFjVjNTYTNyMEk?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -5753,7 +5951,7 @@
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
@@ -5767,7 +5965,7 @@
       <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr"/>
       <c r="AA32" s="2" t="n">
-        <v>107.49</v>
+        <v>52.3</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>31</v>
@@ -5776,7 +5974,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:07:27</t>
+          <t>2026-09-14 07:30:52</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -5791,12 +5989,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak?</t>
+          <t>Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet</t>
+          <t>Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı Bursada Bugün</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -5806,7 +6004,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
+          <t>tekstil, şirket</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -5816,12 +6014,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Yeni müşterilere özel avantajlı ihtiyaç kredisi! Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. TÜM UÇUŞLARIN PLANLANDIĞI ŞEKİLDE KESİNTİSİZ SÜRECEĞİ BELİRTİLDİ AirBaltic, ABD'de iflas koruması başvurusunda bulundu! AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Açıklamada, yasal sürecin yolcuları ve günlük ticari faaliyetleri etkilemeyeceği, tüm uçuşların planlandığı şekilde kesintisiz süreceği, bilet ile rezervasyonların geçerliliğini koruyacağı vurgulandı. Bu arada, iflas koruması başvurusu kararı, şirketin 380 milyon avro değerindeki tahvillerin sahiplerinin alternatif bir ara finansman teklifini oylayacağ kritik toplantıdan bir gün önce geldi. Jet yakıtı fiyatlarındaki artış öncesinde de mali zorluk yaşayan hava yolunun, 2026-2027 dönemini finanse etmek için nakit girişine ihtiyaç duyduğu biliniyordu. Sürecin, Letonya 'da yaklaşan parlamento seçimlerinin hemen öncesine denk gelmesi de dikkati çekti. Hisselerinin yüzde 88,4'ü Letonya devletine ait olan AirBaltic'in yüzde 10 hissesi ise geçen yıl Alman hava yolu firması Lufthansa AG tarafından satın alınmıştı. Kaynak: AA | Bu içerik Hande Dağ tarafından yayına alınmıştır</t>
+          <t>Bursa'da tekstil sektöründe faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında iflas kararı verildi. Kestel'de faaliyet gösteren şirketin iflası, Bursa 1. Asliye Ticaret Mahkemesi'nin kararıyla 14 Ağustos 2025 tarihinde açıldı. İflas işlemlerinin basit tasfiye usulüyle yürütüldüğü dosyada, alacak kayıtlarına ilişkin incelemelerin tamamlanmasının ardından ek sıra cetveli hazırlandı. Bursa'da tekstil sektöründe faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında iflas kararı verildi. Kestel'de faaliyet gösteren şirketin iflası, Bursa 1. Asliye Ticaret Mahkemesi'nin kararıyla 14 Ağustos 2025 tarihinde açıldı. İflas işlemlerinin basit tasfiye usulüyle yürütüldüğü dosyada, alacak kayıtlarına ilişkin incelemelerin tamamlanmasının ardından ek sıra cetveli hazırlandı. Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı Bursa'da alevler bir anda yükseldi! Mahalle sakinleri s... Bakanlık harekete geçti! Çocuklar ve gençler için 81 il... Bir meslekten daha yeşil pasaport talebi! "15-20 yılını... Bursa'da Artık Olmayan 10 Bina! Bir Zamanlar Şehrin İçi... Türkiye'yi sarsan operasyon! Ortaya çıkan görüntüler se... Savcılık paylaşımların peşine düştü! Kimlikleri tek tek... Petrol piyasası alev aldı! Benzine gece yarısı zam geliyor Kozinoğlu soruşturması "Kurtlar Vadisi'ne" sıçradı! İfa... Bursaspor, Esenler Erokspor'u konuk edecek! Hedef 3 pua... Bakan Fidan mesajı Suriye'den verdi! Bir an önce hayata... Bursa'da o yolda çalışma tamamlandı! Samanlı Çevre Bağl... TCMB'den 5 ve 50 TL banknotlar için yeni karar: Değişik... Bursa'da yürek yakan kaza! Bebeğini kucağına almasına s... Atatürk'ün "Bize bir ordu kadar yardım etti" dediği ism... MHP Bursa'da Özcanbaz dönemi: İşte yeni yönetim Gelinin mehir şartını duyan damat kendini tutamadı! Kayıp 11 aylık Büşra bebekle ilgili vahim iddia! Bursa'daki yangın hızla yayılmıştı! Sevindiren haber ge... Bursa'da eski okul yıkıldı, yerine yenisi geliyor! 32 d... Bursa'da 3 büfe kiraya çıkıyor! Aylık kira bedelleri be... Milyonlarca öğrenciyi ilgilendiren karar! Okulların açı... Bursa'da restoran yangını! Dumanlar gökyüzünü kapladı... Bursa'da motosiklet aydınlatma direğine çarptı! Ağır ya... Uluslararası uyuşturucu baronu İstanbul'da yakalandı! Gökçek'in soruşturma ifadesi ortaya çıktı! Gayrimenkul ... Yıllar sonra yeniden ekranlarda! Çocuklar Duymasın'ın D... Bursa'da yeni haftaya sürpriz başlangıç! Yola çıkarken ... Bursa'da bir şirket için daha iflas talebi! Mahkeme tar... Trabzonspor'da Konya hüsranı sonrası deprem! "Gerekirse... Son dakika! Fenerbahçe'de İsmail Kartal istifa etti! Kamu görevlileri de listede! Türkiye güne operasyonla b... 9 ayda 6 zam birden! Mutfak tüpünün fiyatını duyanlar ş... Bursa'da korkunç kaza: 'Dümdüz vurmuş...' Tekstil sektöründe deprem etkisi yaratan karar! 73 yıll... Devriye görevinde acı haber! 1 asker şehit oldu... Bursa'da adı değişen yerler! Eski isimlerini bugün nere... Gülistan Doku soruşturmasında 6. dalga! 7 ilde eş zaman... Doğal diye satılan ünlü maden sularında skandal Bursa'da tarım işçilerini taşıyan araç kaza yaptı! 10 k... Bursa'da 2 gencin öldüğü kazada kahreden detay! Bursaspor-Esenler Erokspor maçının ardından: 'Üzgünüz...' Bursalılar dikkat! Nilüfer'in bazı mahallelerinde sular... Geçmeyen öksürüğünün nedeni akıllara durgunluk verdi! 4... Bursa'da polislerin okul seferberliği başladı! Ekipler ... MHP Bursa'da bayrak değişimi! Yeni il başkanı belli oldu 147 proje arasından seçildi! Bursa'daki tarihi Romangal... 3 bin TL'lik sipariş sonrası hesabını kontrol etti, gör... Dönme dolapta cinsel ilişkiye girdi! Takvim belli oldu: Cepleri yakacak bir zam daha geliyor! Türk ordusu tarafından eğitildiler! Ülkenin liderinden ... Firari fenomenin eski görüntüleri ortaya çıktı! "Bu hay... Bursa minibüslerinde para uzatma devrini bitirecek haml... Üniversiteli kızlar, kaldıkları otelde yan odadan gelen... Bursa'daki ölümlü kaza ile ilgili son dakika! Sürücü gö... Belediye başkanı hakkında skandal ifadeler! Gizli oda, ... Bu saate dikkat! Altın yatırımcısının beklediği gün gel... Bursa'da yaza elveda! Önümüzdeki hafta işler değişiyor... Bursa'da doğalgaz paniği! 6 katlı apartman tahliye edildi Tarihi kırılma! 3 ülke Birleşik Krallık'tan ayrılmak iç... "Mesajlar elimde" Ferdi Tayfur'un damadından Vanlı Kara... Bursa'da bugün hava nasıl olacak? Meteoroloji saat vere... Bursa'yı da yakından ilgilendiriyor! Uzman isimden mily... Altın piyasasında neler oluyor? 20 yıldır böylesi yaşan... Bursa'da iki ilçeyi birbirine bağlayan köprü ortadan ik... Petrol fiyatları çıldırdı, Trump'tan yeni "savaş" sözle... Cumhurbaşkanı Erdoğan: "Türkiye'nin ayağa kalkmasından ... Bursa'da ters yöne giren tır faciaya neden oldu! 2 kiş... Milyonlarca emekliyi ilgilendiriyor! Yeni destek modell... Kaşif Kozinoğlu'nun mezarı açıldı: Ceset bütünlüğü bozu... Arazi anlaşmazlığı kanlı bitti: Kardeşini öldürüp yeğen... Kapıkule'ye nefes aldıracak proje! Türkiye-Bulgaristan ... İadesi kabul edilmedi, markette dehşet saçtı! Kasiyeri ... Bursa'da TEKNOSAB nedeniyle bir mahallenin yolu değişiyor! Bursa'nın en çok vergi ödeyen dev şirketleri açıklandı! Bursa'da gece yarısı gerilim tırmandı! Polislere de sal... "Vanlı Kara Haydar" hakkında çok ağır iddialar! Çalışanların maaşından 991 lira kesilecekti! Flaş geliş... Bursa'da toplu ulaşımda değişiklik! 20/A artık buradan ... Bursa'da 3 yıllığına kiraya verilecek! Tahmini bedeli 7... Savaş dev havayolunu şirketini fena vurdu! İflas bayrağ... Kaçırılmayacak iş fırsatı! 182 kişi alınacak 40 Bin Bursasporlu tek ses oldu! Tribünlerde 106 desibe... Bursa'da o yol kapatıldı! Sürücüler alternatif şeride y... Türk devletleri arasında yeni dönem: TÜRKPOL geliyor, k... Milyonlarca özel sektör çalışanını ilgilendiriyor! Yarg... Bugün resmen başladı! Haberi duyan kayıt için e-Devlet'... Bahis operasyonu Bursa'ya da uzandı! Çok sayıda kişi gö... Bursa'da 1 kilo zeytin 77 bin liraya satıldı! Bursa'da alevler ağaçlara sıçradı! Kırsalda korkutan ya... Bursa'da herkes uykudayken yangın çıktı! Ekipler alarma... Bursa'dan Bosna Hersek'e uzanan görev! Yeniden atandı... Gönül Dağı Yusuf kimdir, Gönül Dağı Veysel'in oğlu Yusu... Bursa'da yolcu taşırken canlı yayın yaptı! Cezası ağır ... Bursa'da trafiğin kilit noktalarından birinde değişim! Feci çarpışma can aldı! Elektrikli motosikletteki yaşlı... Ağabeyinin arkadaşıyla evlendi, düştüğü tek cümlelik no... 2026'yı nokta atışı bilmişti! 2027 asgari ücret tahmini... Kurtlar Vadisi sahneleri yeniden gündemde: Plakadaki de... 2027 Emekli maaşı ne kadar olacak? Sigara içenler dikkat! Bakanlığın yeni taslağında yok y... Ebeveynler dikkat! Sağlığı tehdit eden ürün toplatılıyor Galatasaray'a Barcelona maçı öncesi Osimhen'den haber! Bursa'da tarihi Şifa Hamamı yeniden hayat buluyor! 8 mi... Daha 1 yaşında bile değil! Çadırda sır olay... Bursa'da herkes bunu bekliyordu ama tam tersi oldu! Ace... Bursa'da kedilere 5 yıldızlı 'TOKİ'! Her gün tek tek il... Türkiye güne operasyonla başladı! Listede 162 şüpheli v... Cezaevinde yasak aşk skandalı! Gardiyanın gizli görüntü... Dev ortakların ayrılma kararı aldığı Togg'da teslimat k... Bursa'da yürekleri ağza getiren anlar! 6 katlı bina san... Her detayı kan donduruyor! Büşra bebeğin annesinin ifad... Kurtlar Vadisi'nin yönetmeni Osman Sınav'ın mezara götü... Bursa'da taraftarları sevindiren görüntü! Timsah heykel... Daireyi gezerken banyoya girdi, çıktığı yere inanamadı! Türkiye için tarihi mesaj! Her an hazırız diyerek duyur... Bursa'nın hızlı tren hayalinde gerilim yükseldi! 2 maha... Tezgahının başında sinirlendi! Sonrasında yaptıkları gü... Bursa'da gece yarısı kahreden kaza! Belediye personeli ... Çocukların yardım çığlığı faciayla bitti: Apartman göre... Bursa'da çevreyolunu dumanlar kapladı! Alevler hızla ya... Firari uyuşturucu baronu İstanbul'da yakalandı! Örgütü ... CHP Bursa'da flaş değişim! İl Başkanı görevden alındı Bursaspor'dan maçlık transfer açıklaması: "Süre uzatıldı" Bursalılar yola çıkarken haritaya bakın! Ulaşım iki yön... Kayıp Büşra'nın annesi cinayeti itiraf etti: "Babası öl... Nefes alamıyordu! Yoldan geçen görevlinin müdahalesi ha... Bursaspor kazanırsa liderlik koltuğunu devralacak! MAÇ ... Ülke genelinde eş zamanlı operasyon! Listede yüzlerce k... Adana'dan Bursa'ya uzanan suç örgütü soruşturması! Bağ ... Bursa'da işten çıkarma krizi! Çalışanlar neye uğradığın... Nev Sağlık Grubu hakkındaki iddialara Ergin Kopal'dan n... Bursa, Arap coğrafyasının en büyük fuarında yerini aldı! Vanlı Kara Haydar'ın eşi ile ilgili flaş gelişme! Mahke... Yanan yolcu otobüsünde baba herkesi kurtardı, kızını ku... Bursa'da otobüs kabini talebi: 'Caddeye çıkmak zorunda ... Bursa'da vicdanları sızlatan görüntü! Bursa'nın ticaretinde 102 yıllık gurur! Geçmişten gelec... Meteoroloji açıkladı! Bursa'da ağustos ayında termometr... İki ayrı suç örgütüne operasyon! Evlerinden çıkanlar şa... Bursa'da saniyeler içinde oldu! 2 kişi yola savruldu 1974'te rafa kaldırıldı, Bursa'da yıllar sonra servet d... Serhat Kılıç'ın son isteği yerine getirildi! Vasiyeti a... Rakam 32 milyon TL...Türkiye'yi sarsan operasyon! Valil... Bursa bugün kurtuluşunu kutladı! 104. yıl coşkusu Bursa'da yürekleri ağza getiren kaza! Kontrolden çıkan ... Bursa'da aracını kontrol ederken fark etti! Lastiğin üz... Bursa'da can pazarı! Kamyon devrildi, ölü ve yaralı var... 3 ilde okulları kana bulayacaklardı! Saldırı hazırlığın... Bursa'da okul kapısında izdiham! Veliler çözüm bekliyor... Bursalı mühendis, uluslararası arenada 'Geleceğin Lider... Şeftali fiyatı dip yaptı, belediye başkanı "Gerekirse d... Çöplükten define bulan Sivaslı, verilen ödülü beğenmeyi... Hastalara cinsel içerikli film izletilen hastaneden açı... Milyonlarca kişinin aldığı ürün için yeni karar! Artık ... Yeraltı dizisinin setinden olay yaratan kareler! Oyuncu... Bursa Milletvekili Varank'tan maç sonrası dikkat çeken ... Atatürk'e benzeyen şahısların kavgası Cumhurbaşkanı Erdoğan'dan Bursa'nın gurur günü için öze... Bursa'da kahreden olay! Genç kız balkondan düşerek haya... Kayınpederi çıldırtan yazı! Damadı hastanelik etti... Vanlı Kara Haydar ve Çağla Öz'ün düğün takıları bulundu... Bakan Gürlek duyurdu: Bursa'daki 6 yıllık faili meçhul ... Bursa'dan yola çıkan otobüste skandal görüntüler! Arka ... Bursalı milli futbolcu kararını açıkladı: Akademisini k... Bursaspor'un Esenler Erokspor maçı 11'i belli oldu! Bursa'da otomobil takla attı! 2 kişi ölümden döndü... Son dakika! İş insanına ait jet Libya'da kaza yaptı Benzin zamlandı, Bursa'da tabelalar değişti! İşte yeni ... 5 kişiyi rehin almıştı: Bankaya silahlı baskının arkası... Bursa'da 14 yaşındaki kayıp çocuktan haber var! Bursa'da bu gelenek tam 103 yıldır yaşatılıyor! Türk sanayisinin devi kapılarını kapattı! Türk yolcuları da ilgilendiriyor! 9 Avrupa ülkesinden s... Balkonda kadına sopalı dehşet kamerada! Çığlıkları böyl... "Yurt dışına kaçtı" denilen patron konuştu! Dev şirkett... Bursa'da ışık ihlali iddiası faciaya dönüştü! 1 ölü, 1 ... Bursa'da yüzlerce yıllık tarihi hamamın şaşırtan dönüşü... Ünlü şarkıcının ölümünde şoke eden detay! Doktorlar çar... Bursaspor'a Manisa deplasmanı sonrası şok ceza! PFDK ka... Bursa'da tekstil şirketi iflas etti! Alacaklılar için k... İstanbul'da bir daire parasına koskoca köyü satın aldı! Bursa'da film gibi anlar! Bayılma numarası yaptı, yola ... Otobüsle 6 saat sürüyordu! Yeni yolculuk süresi şaşırtacak Türkiye bu olayı konuşuyor: 11 aylık Büşra'dan 4 gündür... Bursa'da okul yollarında köprü engeli: Mahalleli açılma... Veliaht Prens'ten Trump'a acil telefon: Onları bir an ö... Bursa'da yaşayan herkesi ilgilendiriyor! Ulaşım ücretle... 25 bin lira ek ödeme gündemde! Emekliler bu ayrıntıya d... Bursa'da spor camiasını yasa boğan haber! Ölü bulundu Onur Market'ten Mega Kampanya! Bursa'da sahilde erkek cesedi bulundu Türkiye yağışa doydu, Bursa geride kaldı! Dikkat çeken ... Maltepe'deki dehşette 500 bin dolar detayı! Nedeni akıl... 15'inci kattan kendini boşluğa attı! Korkunç tesadüf ik... Bursa Acemler'de korkutan yangın! Ekipler kısa sürede m... Bursa'da Mümin Canbaz Fen Lisesi'nde başarı ödüllendiri... Bursalılar dikkat! Bir ürün riskli bulundu, sahiplerine... Bursa'da ekipler dere yatağına indi! Mihraplı Deresi'nd... Bursa'da 196 bina tarihe karıştı! Yerine yenileri geliyor Bursa'da üretilen otomobil devine sürpriz talip! Daha y... Kaçarken saklamışlar! Bursa'da yunan askerlerinin gizle... Bursa'da başkanın evi alevlere teslim oldu! Dudak dudağa görüntü paylaştı! İşte Midyeci Ahmet'in il... Bursa'da yola çıkacaklar dikkat! O güzergahta trafik de... Ece Erken'den ücretli abonelik açıklaması! Özel fotoğra... Tartıştığı eşini öldürdü, ardından canına kıydı: Dehşet... Seçil Erzan davasında flaş gelişme! Mahkeme kararını verdi Motorine zam kapıda! Sürücülerin gözü salı gününde Bursa'nın vergi rekortmenleri belli oldu! Zirvedeki isi... Altın ve gümüş için kritik hafta! İslam Memiş'ten dikka... Bursa'nın meşhur çeşmesinde yoğunluk! Sırada tek bir ku... Bursasporlu futbolcular maçı değerlendirdi: 'Memnun değ... Domuz sürüsü mahalleye indi, kafalarına göre dolaştılar... Yangın bir anda büyüdü! Mahsur kalanlar kurtulmak için ... Bursaspor taraftarından Kırdar eşliğinde 'Cendere' şov! Gemlik'te zeytin sezonu böyle başladı! İlk ürünler dual... Bursa'da 14 yaşındaki çocuk kayıp! Ailesi her yerde onu... Araç sahipleri dikkat! Trafik sigortasında yeni fiyatla... Davutoğlu'nun oğlunun nikahında dikkat çeken detay! 2 aydır cezaevindeydi! Sosyal medya fenomeni için flaş ... Bursa'da gözler bu toplantıda! Nilüfer'de tartışma yara... Günlerdir aranıyordu! Kara Haydar'ın eşiyle ilgili geli... Zekeriya Öz ve 20 isim için kritik gelişme! Sınıf annesinin WhatsApp grubuna yazdığı mesaj ortalığı... Feci kaza sonrası otobüs alev alev yandı: Ölü ve yaralı... Bursa'da heba olan hayatlar! Ne yaptılarsa ayıltamadıla... Filenin Efeleri Şampiyonadaki İkinci Sınavına Çıkıyor: ... Yunanistan'dan İznik'e inanç turizmi çıkarması Bursa'da zincirleme kaza! Karşı şeride geçen otomobil o... Bursaspor Esenler Erokspor maçında puanlar paylaşıldı... Düğün başına 30 bin TL! Atatürk'e benzediği iddia edile... Bursa'da yangın paniği! Alevler bir anda yükseldi, vata... Bursa'da orman yangını! Zamanla yarış sürüyor... Bursa'da yazdan kalma hafta sonu! Meteoroloji 5 günlük ... Rakam verdi ve uyardı! "Ciddi anlamda çarşı pazar karışır" Kenan Evren'in hüküm giydiği anların görüntüleri ortaya... Bursa'da tekstil sektöründe faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında iflas kararı verildi. Kestel'de faaliyet gösteren şirketin iflası, Bursa 1. Asliye Ticaret Mahkemesi'nin kararıyla 14 Ağustos 2025 tarihinde açıldı. İflas işlemlerinin basit tasfiye usulüyle yürütüldüğü dosyada, alacak kayıtlarına ilişkin incelemelerin tamamlanmasının ardından ek sıra cetveli hazırlandı. Bursa'daki tekstil sektörünü ilgilendiren iflas sürecinde yeni bir aşamaya geçildi. Bursa İflas Dairesi tarafından yayımlanan ilana göre, Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında yürütülen iflas dosyasında alacak kayıt talepleri incelendi ve yapılan değerlendirmeler doğrultusunda sıra cetveli oluşturuldu. Şirketin iflasına ilişkin süreç, Bursa 1. Asliye Ticaret Mahkemesi'nin 2025/490 Esas sayılı dosyası kapsamında verilen kararla başladı. Mahkeme, 14 Ağustos 2025 tarihinde şirketin iflasına hükmetti. İflas aynı gün saat 14.57'de açıldı. Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi, Bursa'nın Kestel ilçesindeki Ahmet Vefik Paşa Organize Sanayi Bölgesi'nde faaliyet gösteriyordu. Şirketin Bursa Ticaret Sicil Müdürlüğü'ndeki kayıt numarası ise 112160 olarak açıklandı. İflas kararının ardından dosyanın Bursa İflas Dairesi tarafından yürütüldüğü belirtildi. Tasfiyenin basit usulde yapılmasına karar verilmesiyle birlikte şirketin alacak ve borç durumuna ilişkin işlemler de iflas mevzuatı çerçevesinde sürdürülüyor. İflas dosyasına alacaklılar tarafından yapılan başvuruların incelenmesinin ardından alacaklara ilişkin kararların verildiği bildirildi. Hazırlanan sıra cetveli ise ilgililerin incelemesine sunuldu. İflas sürecinin önemli aşamalarından biri olan sıra cetveli, iflas masasına bildirilen alacakların durumunun ve sıralamasının ortaya konulması açısından önem taşıyor. Bursa İflas Dairesi tarafından yayımlanan yeni ilan, dosyada ek sıra cetvelinin hazırlandığını duyuruyor. Böylece iflas dosyasındaki alacak kayıtlarına yönelik değerlendirmeler sonucunda ortaya çıkan yeni durum da ilgililerin bilgisine sunulmuş oldu. Sıra cetvelinin, Bursa İflas Dairesi'nde incelemeye açık şekilde tutulduğu belirtildi. Dosyada alacağı bulunan kişiler ve diğer ilgililer, kendi alacaklarıyla ilgili yapılan değerlendirmeleri inceleyebilecek. İflas dosyasındaki alacağın esasına veya miktarına itiraz etmek isteyenler açısından önemli bir süre bulunuyor. İlanda yer alan bilgilere göre, alacağın varlığına, niteliğine veya belirlenen miktarına yönelik itirazların 15 gün içerisinde yapılması gerekiyor. Bu itirazların, iflas dairesinin bulunduğu yerdeki Ticaret Mahkemesi'nde dava konusu edilmesi gerekiyor. Dolayısıyla sıra cetvelinde kendi alacağının yanlış değerlendirildiğini düşünen alacaklıların belirtilen süre içerisinde hukuki yollara başvurması önem taşıyor. Sıra cetvelindeki alacağın miktarı veya esasından farklı olarak, alacağın sırasına yönelik itirazlar için ise daha kısa bir süre öngörülüyor. İlana göre sıra bakımından itirazda bulunmak isteyenlerin 7 gün içerisinde İcra Mahkemesi nezdinde şikayet yoluna başvurması gerekiyor. Bu nedenle iflas dosyasında alacağı bulunan kişilerin yalnızca alacak miktarını değil, sıra cetvelinde alacaklarının hangi sırada yer aldığını da kontrol etmesi gerekiyor. İlanla birlikte öngörülen yasal sürelerin geçirilmesi, hak kayıpları açısından önem taşıyor. Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi'nin iflasına ilişkin süreç, mahkemenin 14 Ağustos 2025 tarihli kararıyla başlamıştı. İflasın aynı gün saat 14.57'de açılmasının ardından dosyanın basit tasfiye yöntemiyle yürütülmesine karar verilmişti. Gelinen aşamada alacak kayıt taleplerinin incelenmesi tamamlanırken, sıra cetveline ilişkin işlemler de ilan aşamasına taşındı. Bursa İflas Dairesi'nin 2025/10 İflas sayılı dosyasında yayımlanan ek sıra cetveli, şirketten alacaklı olduğunu belirten tarafların haklarını takip edebilmesi açısından önem taşıyor. İlgililerin, sıra cetvelini Bursa İflas Dairesi'nde inceleyerek kendileriyle ilgili değerlendirmeleri kontrol edebileceği ve itiraz hakkı bulunan durumlarda ilgili mahkemelere yasal süreler içerisinde başvurabileceği bildirildi. Bursa Bölge , 2026.09.14 10:30</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Yeni müşterilere özel avantajlı ihtiyaç kredisi! Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? TÜM UÇUŞLARIN PLANLANDIĞI ŞEKİLDE KESİNTİSİZ SÜRECEĞİ BELİRTİLDİ AirBaltic, ABD'de iflas koruması başvurusunda bulundu! AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Açıklamada, yasal sürecin yolcuları ve günlük ticari faaliyetleri etkilemeyeceği, tüm uçuşların planlandığı şekilde kesintisiz süreceği, bilet ile rezervasyonların geçerliliğini koruyacağı vurgulandı. Bu arada, iflas koruması başvurusu kararı, şirketin 380 milyon avro değerindeki tahvillerin sahiplerinin alternatif bir ara finansman teklifini oylayacağ kritik toplantıdan bir gün önce geldi. Jet yakıtı fiyatlarındaki artış öncesinde de mali zorluk yaşayan hava yolunun, 2026-2027 dönemini finanse etmek için nakit girişine ihtiyaç duyduğu biliniyordu. Sürecin, Letonya 'da yaklaşan parlamento seçimlerinin hemen öncesine denk gelmesi de dikkati çekti. Hisselerinin yüzde 88,4'ü Letonya devletine ait olan AirBaltic'in yüzde 10 hissesi ise geçen yıl Alman hava yolu firması Lufthansa AG tarafından satın alınmıştı.</t>
+          <t>Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı Bursada Bugün Bursa'da tekstil sektöründe faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında iflas kararı verildi. Kestel'de faaliyet gösteren şirketin iflası, Bursa 1. Asliye Ticaret Mahkemesi'nin kararıyla 14 Ağustos 2025 tarihinde açıldı. İflas işlemlerinin basit tasfiye usulüyle yürütüldüğü dosyada, alacak kayıtlarına ilişkin incelemelerin tamamlanmasının ardından ek sıra cetveli hazırlandı. Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı Bursa'da alevler bir anda yükseldi! Çocuklar ve gençler için 81 il... Bir meslekten daha yeşil pasaport talebi! Bursa'da Artık Olmayan 10 Bina! Türkiye'yi sarsan operasyon! Petrol piyasası alev aldı! Benzine gece yarısı zam geliyor Kozinoğlu soruşturması "Kurtlar Vadisi'ne" sıçradı! Bursaspor, Esenler Erokspor'u konuk edecek! Bursa'da o yolda çalışma tamamlandı! Bursa'da yürek yakan kaza! Bebeğini kucağına almasına s... Atatürk'ün "Bize bir ordu kadar yardım etti" dediği ism... MHP Bursa'da Özcanbaz dönemi: İşte yeni yönetim Gelinin mehir şartını duyan damat kendini tutamadı! Bursa'daki yangın hızla yayılmıştı! Bursa'da eski okul yıkıldı, yerine yenisi geliyor! Bursa'da 3 büfe kiraya çıkıyor! Bursa'da restoran yangını! Bursa'da motosiklet aydınlatma direğine çarptı! Uluslararası uyuşturucu baronu İstanbul'da yakalandı! Gökçek'in soruşturma ifadesi ortaya çıktı! Çocuklar Duymasın'ın D... Bursa'da yeni haftaya sürpriz başlangıç! Bursa'da bir şirket için daha iflas talebi! Trabzonspor'da Konya hüsranı sonrası deprem! Fenerbahçe'de İsmail Kartal istifa etti! Türkiye güne operasyonla b... Bursa'da korkunç kaza: 'Dümdüz vurmuş...' Tekstil sektöründe deprem etkisi yaratan karar! Bursa'da adı değişen yerler! Gülistan Doku soruşturmasında 6. Doğal diye satılan ünlü maden sularında skandal Bursa'da tarım işçilerini taşıyan araç kaza yaptı! Bursa'da 2 gencin öldüğü kazada kahreden detay! Bursaspor-Esenler Erokspor maçının ardından: 'Üzgünüz...' Bursalılar dikkat! Bursa'da polislerin okul seferberliği başladı! MHP Bursa'da bayrak değişimi! Yeni il başkanı belli oldu 147 proje arasından seçildi! Bursa'daki tarihi Romangal... 3 bin TL'lik sipariş sonrası hesabını kontrol etti, gör... Bursa minibüslerinde para uzatma devrini bitirecek haml... Belediye başkanı hakkında skandal ifadeler! Bursa'da doğalgaz paniği! Bursa'da bugün hava nasıl olacak? Bursa'yı da yakından ilgilendiriyor! Altın piyasasında neler oluyor? 20 yıldır böylesi yaşan... Bursa'da iki ilçeyi birbirine bağlayan köprü ortadan ik... Petrol fiyatları çıldırdı, Trump'tan yeni "savaş" sözle... Cumhurbaşkanı Erdoğan: "Türkiye'nin ayağa kalkmasından ... Bursa'da ters yöne giren tır faciaya neden oldu! Kaşif Kozinoğlu'nun mezarı açıldı: Ceset bütünlüğü bozu... Arazi anlaşmazlığı kanlı bitti: Kardeşini öldürüp yeğen... Bursa'da TEKNOSAB nedeniyle bir mahallenin yolu değişiyor! Bursa'nın en çok vergi ödeyen dev şirketleri açıklandı! Bursa'da gece yarısı gerilim tırmandı! Çalışanların maaşından 991 lira kesilecekti! Bursa'da toplu ulaşımda değişiklik! Bursa'da 3 yıllığına kiraya verilecek! Savaş dev havayolunu şirketini fena vurdu! 182 kişi alınacak 40 Bin Bursasporlu tek ses oldu! Bursa'da o yol kapatıldı! Türk devletleri arasında yeni dönem: TÜRKPOL geliyor, k... Bahis operasyonu Bursa'ya da uzandı! Bursa'da 1 kilo zeytin 77 bin liraya satıldı! Bursa'da alevler ağaçlara sıçradı! Bursa'da herkes uykudayken yangın çıktı! Bursa'dan Bosna Hersek'e uzanan görev! Bursa'da yolcu taşırken canlı yayın yaptı! Bursa'da trafiğin kilit noktalarından birinde değişim! Elektrikli motosikletteki yaşlı... Ağabeyinin arkadaşıyla evlendi, düştüğü tek cümlelik no... 2027 asgari ücret tahmini... 2027 Emekli maaşı ne kadar olacak? Bakanlığın yeni taslağında yok y... Bursa'da tarihi Şifa Hamamı yeniden hayat buluyor! Daha 1 yaşında bile değil! Bursa'da herkes bunu bekliyordu ama tam tersi oldu!</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -5831,11 +6029,19 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>https://www.mynet.com/amp/unlu-hava-yolu-sirketinden-iflas-koruma-basvurusu-biletler-ne-olacak-finans-574454</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>https://m.bursadabugun.com/haber/amp-bursa-da-tekstil-sirketi-iflas-etti-alacaklilar-icin-kritik-sure-basladi-1948730.html</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Bursa | İstanbul</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Kestel</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr"/>
@@ -5843,7 +6049,7 @@
       <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr"/>
@@ -5857,7 +6063,7 @@
       <c r="Y33" s="2" t="inlineStr"/>
       <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" s="2" t="n">
-        <v>99</v>
+        <v>117.25</v>
       </c>
       <c r="AB33" s="2" t="n">
         <v>32</v>
@@ -5866,12 +6072,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:23:36</t>
+          <t>2026-09-14 10:32:55</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -5881,12 +6087,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı...</t>
+          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet</t>
+          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı | Türkiye Ekonomisi Haberleri GZT</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5896,60 +6102,48 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>tekstil, şirket</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>tekstil</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil sektöründe faaliyet gösteren bir şirketin devam eden iflas tasfiyesinde yeni bir aşamaya geçildi. Bursa İflas Dairesi’nin 2025/10 İflas sayılı dosyası kapsamında, Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında basit tasfiyede ek sıra cetveli ilanı yayımlandı. ŞİRKETİN İFLASINA 2025 YILINDA KARAR VERİLMİŞTİ İlanda yer alan bilgilere göre Bursa 1. Asliye Ticaret Mahkemesi, 14 Ağustos 2025 tarihli ve 2025/490 Esas sayılı kararıyla şirketin iflasına hükmetti. Şirketin iflası aynı gün saat 14.57 itibarıyla açılırken, tasfiye işlemlerinin basit usulde gerçekleştirilmesine karar verildi. KESTEL'DEKİ TEKSTİL ŞİRKETİ İflas ilanında şirketin adresi de ayrıntılı şekilde yer aldı. Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi'nin adresi Ahmet Vefik Paşa OSB Mahallesi, Yeniyol Caddesi, MNG Tekstil Ltd. Sitesi, MNG Tekstil No:10, Kestel/Bursa olarak belirtildi. ALACAK KAYIT TALEPLERİ İNCELENDİ Bursa İflas Dairesi tarafından yürütülen tasfiye kapsamında iflas dosyasına yapılan alacak kayıt taleplerinin incelendiği ve alacaklar hakkında karar verildiği bildirildi. İcra ve İflas Kanunu hükümlerine göre hazırlanan ek sıra cetveli, ilgililerin incelemesine sunulmak üzere iflas dosyasında hazır tutuluyor. Sıra cetveli, iflas tasfiyesinde alacaklıların taleplerinin hangi kapsamda değerlendirildiği ve alacakların sıralamasına ilişkin süreç açısından önem taşıyor. ALACAKLILAR DİKKAT: 15 VE 7 GÜNLÜK İTİRAZ SÜRESİ İlanda alacaklıların itiraz haklarına ilişkin kritik süreler de açıklandı. Buna göre alacağın esasına ve miktarına yönelik itirazların 15 gün içerisinde, Bursa İflas Dairesi'nin bulunduğu yerdeki Ticaret Mahkemesi'nde dava konusu edilmesi gerekiyor. Sıraya ilişkin itirazlar için ise 7 günlük süre bulunuyor. Bu kapsamdaki itirazların şikâyet yoluyla İcra Mahkemesi'ne taşınabileceği belirtildi. Söz konusu süreler ilan tarihine bağlı hukuki süreler olduğundan, ilgililerin resmi ilandaki tarih ve usulleri esas alması önem taşıyor.</t>
+          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı | Türkiye Ekonomisi Haberleri GZT</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’da tekstil sektöründe faaliyet gösteren bir şirketin devam eden iflas tasfiyesinde yeni bir aşamaya geçildi. Bursa İflas Dairesi’nin 2025/10 İflas sayılı dosyası kapsamında, Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında basit tasfiyede ek sıra cetveli ilanı yayımlandı. ŞİRKETİN İFLASINA 2025 YILINDA KARAR VERİLMİŞTİ İlanda yer alan bilgilere göre Bursa 1. Asliye Ticaret Mahkemesi, 14 Ağustos 2025 tarihli ve 2025/490 Esas sayılı kararıyla şirketin iflasına hükmetti. Şirketin iflası aynı gün saat 14.57 itibarıyla açılırken, tasfiye işlemlerinin basit usulde gerçekleştirilmesine karar verildi. KESTEL'DEKİ TEKSTİL ŞİRKETİ İflas ilanında şirketin adresi de ayrıntılı şekilde yer aldı. Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi'nin adresi Ahmet Vefik Paşa OSB Mahallesi, Yeniyol Caddesi, MNG Tekstil Ltd. Sitesi, MNG Tekstil No:10, Kestel/Bursa olarak belirtildi. ALACAK KAYIT TALEPLERİ İNCELENDİ Bursa İflas Dairesi tarafından yürütülen tasfiye kapsamında iflas dosyasına yapılan alacak kayıt taleplerinin incelendiği ve alacaklar hakkında karar verildiği bildirildi. İcra ve İflas Kanunu hükümlerine göre hazırlanan ek sıra cetveli, ilgililerin incelemesine sunulmak üzere iflas dosyasında hazır tutuluyor. Sıra cetveli, iflas tasfiyesinde alacaklıların taleplerinin hangi kapsamda değerlendirildiği ve alacakların sıralamasına ilişkin süreç açısından önem taşıyor. ALACAKLILAR DİKKAT: 15 VE 7 GÜNLÜK İTİRAZ SÜRESİ İlanda alacaklıların itiraz haklarına ilişkin kritik süreler de açıklandı. Buna göre alacağın esasına ve miktarına yönelik itirazların 15 gün içerisinde, Bursa İflas Dairesi'nin bulunduğu yerdeki Ticaret Mahkemesi'nde dava konusu edilmesi gerekiyor. Sıraya ilişkin itirazlar için ise 7 günlük süre bulunuyor. Bu kapsamdaki itirazların şikâyet yoluyla İcra Mahkemesi'ne taşınabileceği belirtildi. Söz konusu süreler ilan tarihine bağlı hukuki süreler olduğundan, ilgililerin resmi ilandaki tarih ve usulleri esas alması önem taşıyor.</t>
+          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı | Türkiye Ekonomisi Haberleri GZT Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı | Türkiye Ekonomisi Haberleri GZT</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>https://www.bursahakimiyet.com.tr/bursa/bursa-da-tekstil-sirketinin-iflasinda-yeni-gelisme-alacaklilar-icin-sure-basladi-1709285</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Kestel</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Ahmet Vefik Paşa OSB Mahallesi | adresi Ahmet Vefik Paşa OSB</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>Yeniyol Caddesi</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOUnFRYnN6a2lIanlpblFXQng1cm9BTElmRWw5elZQUTIyS194VV9wd2pxUXlWQnR4UjFRMHMwMkxfS1hxcUNud3hsaWZhaU1ORUlSSXgxVlBVV1YzcTdZLU5XMjFuRDg4UEF6cGJnclIwN2Q4bnZDcmRHNTUwdkpIb1BCckEwNnZaRHcxRTlwTW80VTRJa1M4eW10NUhkVkFKUEM3Nm8wZlJtNnNlb0p2MGJ0bDRzOEZuNXlQOUZn?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
       <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Boya Tekstil</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Boya Tekstil:292:body+summary+title</t>
+        </is>
+      </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr"/>
@@ -5963,7 +6157,7 @@
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr"/>
       <c r="AA34" s="2" t="n">
-        <v>160</v>
+        <v>154.2</v>
       </c>
       <c r="AB34" s="2" t="n">
         <v>33</v>
@@ -5972,12 +6166,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:53:53</t>
+          <t>2026-09-14 06:12:39</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>iflas</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -5987,12 +6181,12 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu</t>
+          <t>Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi...</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist</t>
+          <t>Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -6012,48 +6206,68 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. DOLAR 48,62 0,20% EURO 56,15 -0,30% ALTIN 6621,33 0,00% BIST 100 13821,97 0,49% TRY 0.0230 USD 0.0193 EUR Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Edip Üçok 14 Eylül 2026 | 12:54 AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu. 13:17 Bagajınızda bunlar yoksa cezası var: 2026'nın zorunlu araç gereçleri listelendi 13:11 Tüketici temsilcileri uyardı: Kırtasiye alışverişinde "Popüler Ürün" tuzağına düşmeyin 12:54 Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu 12:41 "İran'ın komşularıyla, özellikle de Türkiye ile ilişkisi istenilen düzeyde" 12:31 Net Global halka arz sonuçları açıklandı: Bireysele kaç lot düştü? 12:22 AJet'in yurt içi uçuşlarda indirim kampanyası başladı 12:18 Otomotivde 8 aylık tablo belli oldu: Adetler düştü, ihracat geliri yükseldi 12:01 Ankara bir zamanlar deniz miydi? Külhöyük’te 66 milyon yıllık keşif 11:47 Türkiye sermaye piyasaları büyüyor: Menkul kıymetler 38 trilyon liraya ulaştı, yatırımcı sayısı 40 milyona yaklaştı 11:32 Evlilik desteği projesi yaygınlaşıyor: Yerel ve ulusal firma sayısı artışta USD/TRY 30 dk 1 saat 1 gün USD/TRY EURO/TRY ALTIN/TRY BITCOIN/TRY Döviz Çevirici TRY 0.0230 USD 0.0193 EUR Hesapla Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu.</t>
+          <t>Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi... Bursa’da faaliyet gösteren Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. ile Emine Altun Anık’ın konkordato talebinde yeni gelişme yaşandı. Bursa 1. Asliye Ticaret Mahkemesi, davacılar hakkında 3 aylık geçici konkordato mühleti verirken, mal varlıklarının devrine ve yeni icra-iflas takiplerine yönelik önemli tedbir kararları aldı. Bursa iş dünyasını ilgilendiren konkordato ilanlarına bir yenisi daha eklendi. Bursa 1. Asliye Ticaret Mahkemesi Başkanlığı, 2026/678 Esas sayılı konkordato dosyasında Emine Altun Anık ile Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret Anonim Şirketi hakkında karar verdi. Mahkemenin 10 Eylül 2026 tarihli tensip kararıyla davacılara 3 aylık geçici konkordato mühleti verildi. TAŞINIR VE TAŞINMAZLARIN DEVRİ YASAKLANDI Mahkeme tarafından alınan tedbirler kapsamında davacı borçlular adına kayıtlı tüm taşınır ve taşınmaz malların üçüncü kişilere devri, ikinci bir karara kadar yasaklandı. Borçluların mahkeme izni olmaksızın mühlet kararından itibaren rehin tesis edemeyeceği, kefil olamayacağı, taşınmazlarını ve işletmenin devamlı tesisatını kısmen dahi olsa devredemeyeceği veya takyit edemeyeceği belirtildi. Ayrıca ivazsız tasarruflarda bulunulamayacağı bildirildi. YENİ İCRA VE İFLAS TAKİBİ YAPILAMAYACAK Kararın en dikkat çeken bölümlerinden biri de icra ve iflas takiplerine ilişkin oldu. Mahkeme, geçici mühlet içerisinde davacılar aleyhine, 6183 sayılı Kanun kapsamında yapılan takipler de dahil olmak üzere, hangi nedene dayanırsa dayansın ihtiyati tedbir, ihtiyati haciz ve muhafaza işlemleri dahil takip işlemlerinin yapılmaması yönünde ihtiyati tedbir kararı verdi. Buna göre 10 Eylül 2026 tarihinden itibaren yeni icra ve iflas takibi yapılamayacak. İlanda, söz konusu tedbirlerin İcra ve İflas Kanunu'nun 206'ncı maddesinin birinci sırasında belirtilen imtiyazlı alacaklar ile rehinle temin edilmiş alacaklar bakımından hüküm ifade etmeyeceği de kaydedildi. KONKORDATO KOMİSERİ ATANDI Üç aylık geçici mühlet süresince görev yapmak üzere konkordato komiseri de belirlendi. Mahkeme tarafından alacaklı sayısı ve alacak miktarı dikkate alınarak mali konularda uzman Süreyya Turhan konkordato komiseri olarak atandı. ALACAKLILARA 7 GÜNLÜK İTİRAZ SÜRESİ Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. ile Emine Altun Anık'tan alacaklı olduğunu ileri süren kişiler için de önemli bir süre bulunuyor. Mahkeme ilanına göre alacaklılar, ilanın yayımlandığı tarihten itibaren 7 günlük kesin süre içerisinde dilekçeyle itiraz edebilecek. Alacaklılar, konkordato mühleti verilmesini gerektiren bir durum bulunmadığını delilleriyle birlikte ileri sürebilecek. DURUŞMA GÜNÜ BELİRLENMEDİ Mahkeme, geçici mühletin uzatılması veya süre sona ermeden önce önemli nedenlerin ortaya çıkması ihtimalini dikkate alarak şimdilik duruşma günü belirlemedi. Böylece Bursa 1. Asliye Ticaret Mahkemesi'nin kararı doğrultusunda şirket ve diğer davacı bakımından üç aylık geçici konkordato süreci başlamış oldu.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. DOLAR 48,62 0,20% EURO 56,15 -0,30% ALTIN 6621,33 0,00% BIST 100 13821,97 0,49% TRY 0.0230 USD 0.0193 EUR Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Edip Üçok 14 Eylül 2026 | 12:54 AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu. 13:17 Bagajınızda bunlar yoksa cezası var: 2026'nın zorunlu araç gereçleri listelendi 13:11 Tüketici temsilcileri uyardı: Kırtasiye alışverişinde "Popüler Ürün" tuzağına düşmeyin 12:54 Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu 12:41 "İran'ın komşularıyla, özellikle de Türkiye ile ilişkisi istenilen düzeyde" 12:31 Net Global halka arz sonuçları açıklandı: Bireysele kaç lot düştü? 12:22 AJet'in yurt içi uçuşlarda indirim kampanyası başladı 12:18 Otomotivde 8 aylık tablo belli oldu: Adetler düştü, ihracat geliri yükseldi 12:01 Ankara bir zamanlar deniz miydi? Külhöyük’te 66 milyon yıllık keşif 11:47 Türkiye sermaye piyasaları büyüyor: Menkul kıymetler 38 trilyon liraya ulaştı, yatırımcı sayısı 40 milyona yaklaştı 11:32 Evlilik desteği projesi yaygınlaşıyor: Yerel ve ulusal firma sayısı artışta USD/TRY 30 dk 1 saat 1 gün USD/TRY EURO/TRY ALTIN/TRY BITCOIN/TRY Döviz Çevirici TRY 0.0230 USD 0.0193 EUR Hesapla Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11.</t>
+          <t>Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi... Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi... Bursa Hakimiyet Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi... Bursa’da faaliyet gösteren Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. ile Emine Altun Anık’ın konkordato talebinde yeni gelişme yaşandı. Asliye Ticaret Mahkemesi, davacılar hakkında 3 aylık geçici konkordato mühleti verirken, mal varlıklarının devrine ve yeni icra-iflas takiplerine yönelik önemli tedbir kararları aldı. Bursa iş dünyasını ilgilendiren konkordato ilanlarına bir yenisi daha eklendi. Asliye Ticaret Mahkemesi Başkanlığı, 2026/678 Esas sayılı konkordato dosyasında Emine Altun Anık ile Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret Anonim Şirketi hakkında karar verdi. Mahkemenin 10 Eylül 2026 tarihli tensip kararıyla davacılara 3 aylık geçici konkordato mühleti verildi. TAŞINIR VE TAŞINMAZLARIN DEVRİ YASAKLANDI Mahkeme tarafından alınan tedbirler kapsamında davacı borçlular adına kayıtlı tüm taşınır ve taşınmaz malların üçüncü kişilere devri, ikinci bir karara kadar yasaklandı. Borçluların mahkeme izni olmaksızın mühlet kararından itibaren rehin tesis edemeyeceği, kefil olamayacağı, taşınmazlarını ve işletmenin devamlı tesisatını kısmen dahi olsa devredemeyeceği veya takyit edemeyeceği belirtildi. Ayrıca ivazsız tasarruflarda bulunulamayacağı bildirildi. YENİ İCRA VE İFLAS TAKİBİ YAPILAMAYACAK Kararın en dikkat çeken bölümlerinden biri de icra ve iflas takiplerine ilişkin oldu. Mahkeme, geçici mühlet içerisinde davacılar aleyhine, 6183 sayılı Kanun kapsamında yapılan takipler de dahil olmak üzere, hangi nedene dayanırsa dayansın ihtiyati tedbir, ihtiyati haciz ve muhafaza işlemleri dahil takip işlemlerinin yapılmaması yönünde ihtiyati tedbir kararı verdi. Buna göre 10 Eylül 2026 tarihinden itibaren yeni icra ve iflas takibi yapılamayacak. İlanda, söz konusu tedbirlerin İcra ve İflas Kanunu'nun 206'ncı maddesinin birinci sırasında belirtilen imtiyazlı alacaklar ile rehinle temin edilmiş alacaklar bakımından hüküm ifade etmeyeceği de kaydedildi. KONKORDATO KOMİSERİ ATANDI Üç aylık geçici mühlet süresince görev yapmak üzere konkordato komiseri de belirlendi. Mahkeme tarafından alacaklı sayısı ve alacak miktarı dikkate alınarak mali konularda uzman Süreyya Turhan konkordato komiseri olarak atandı. ALACAKLILARA 7 GÜNLÜK İTİRAZ SÜRESİ Ankaş İnşaat Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş. ile Emine Altun Anık'tan alacaklı olduğunu ileri süren kişiler için de önemli bir süre bulunuyor. Alacaklılar, konkordato mühleti verilmesini gerektiren bir durum bulunmadığını delilleriyle birlikte ileri sürebilecek. DURUŞMA GÜNÜ BELİRLENMEDİ Mahkeme, geçici mühletin uzatılması veya süre sona ermeden önce önemli nedenlerin ortaya çıkması ihtimalini dikkate alarak şimdilik duruşma günü belirlemedi. Asliye Ticaret Mahkemesi'nin kararı doğrultusunda şirket ve diğer davacı bakımından üç aylık geçici konkordato süreci başlamış oldu.</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_full_article_dom</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.ekonomist.com.tr/dunya/savasin-maliyetine-dayanamadi-dev-havayolu-sirketi-iflas-korumasi-basvurusunda-bulundu-78706</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>https://www.bursahakimiyet.com.tr/bursa/bursa-da-bir-sirket-daha-konkordato-surecinde-mal-varliklarinin-devrine-yasak-getirildi-1709234</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
       <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
-      <c r="S35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş:raw_legal</t>
+        </is>
+      </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş Bursa Türkiye</t>
+        </is>
+      </c>
       <c r="V35" s="2" t="inlineStr"/>
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr"/>
-      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>Kuzey Sera Sistemleri Bursa | SPORGIDA &amp; VOİT SHOP</t>
+        </is>
+      </c>
       <c r="AA35" s="2" t="n">
-        <v>98.75</v>
+        <v>147.25</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>34</v>
@@ -6062,27 +6276,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:36:11</t>
+          <t>2026-09-14 06:00:38</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor aksiyon.com.tr</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -6092,22 +6306,22 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Gece yarısı Düzce Door fabrikasında yangın Düzce D-100 karayolu kenarında bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında başlayan yangın, kısa sürede büyüyerek fabrikayı etkisi altına aldı. Olay yerine intikal eden Düzce Belediye ekipleri ve itfaiye müdahalesi ile alevleri kontrol altına almak için çalışma başlattı. Olay yeri ve müdahale: İlk ihbarın D-100 karayolundan görüldüğü için geldiğini belirten yetkililer, itfaiye ekiplerinin bölgeye yönlendirildiğini söyledi. Ahşap ve Amerikan panel üretimi yapan fabrikanın malzeme yapısı nedeniyle yangının kısa sürede yayıldığı bildirildi. Belediye ekipleri yangına müdahale ederken öncelik olarak personel güvenliği ve çevredeki yapıların korunması hedeflendi. Başkan Özlü'nün açıklamaları: Düzce Belediye Başkanı Dr. Faruk Özlü , olay yerinde yaptığı açıklamada ekiplere tüm imkanların seferber edildiğini ve yangının en kısa sürede kontrol altına alınmasının amaçlandığını söyledi. Özlü, ilk bildirimde gecikme olduğunu düşündüğünü, bazı komşuların fabrikada zaman zaman küçük çaplı yangınlar yaşandığını ifade ettiğini aktardı. Başkan Özlü, "İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra uzmanlarımız çıkış sebebi üzerinde çalışacaklar" diyerek, fabrikanın yapısal özellikleri nedeniyle alevlerin hızla yayıldığını vurguladı. Ayrıca can kaybı olmadığını belirterek, fabrika sahiplerine ve Düzce halkına geçmiş olsun dileğinde bulundu. Yetkililer, söndürme çalışmalarının bu akşam tamamlanmasının hedeflendiğini, yangının kesin çıkış nedeninin ise inceleme sonrası netleşeceğini bildirdi. Düzce Belediye Başkanı Faruk Özlü yangını en kısa sürede söndürmeye çalıştıklarını söyledi 1 Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı 2 Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada 3 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 4 Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı 5 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 6 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 7 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor Gece yarısı Düzce Door fabrikasında yangın Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Düzce D-100 karayolu kenarında bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında başlayan yangın, kısa sürede büyüyerek fabrikayı etkisi altına aldı. Olay yerine intikal eden Düzce Belediye ekipleri ve itfaiye müdahalesi ile alevleri kontrol altına almak için çalışma başlattı. İlk ihbarın D-100 karayolundan görüldüğü için geldiğini belirten yetkililer, itfaiye ekiplerinin bölgeye yönlendirildiğini söyledi. Ahşap ve Amerikan panel üretimi yapan fabrikanın malzeme yapısı nedeniyle yangının kısa sürede yayıldığı bildirildi. Belediye ekipleri yangına müdahale ederken öncelik olarak personel güvenliği ve çevredeki yapıların korunması hedeflendi. Düzce Belediye Başkanı Dr. Faruk Özlü , olay yerinde yaptığı açıklamada ekiplere tüm imkanların seferber edildiğini ve yangının en kısa sürede kontrol altına alınmasının amaçlandığını söyledi. Özlü, ilk bildirimde gecikme olduğunu düşündüğünü, bazı komşuların fabrikada zaman zaman küçük çaplı yangınlar yaşandığını ifade ettiğini aktardı. Başkan Özlü, "İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra uzmanlarımız çıkış sebebi üzerinde çalışacaklar" diyerek, fabrikanın yapısal özellikleri nedeniyle alevlerin hızla yayıldığını vurguladı. Ayrıca can kaybı olmadığını belirterek, fabrika sahiplerine ve Düzce halkına geçmiş olsun dileğinde bulundu. Yetkililer, söndürme çalışmalarının bu akşam tamamlanmasının hedeflendiğini, yangının kesin çıkış nedeninin ise inceleme sonrası netleşeceğini bildirdi. Düzce Belediye Başkanı Faruk Özlü yangını en kısa sürede söndürmeye çalıştıklarını söyledi Ben Ahmet Demir, 30 yaşındayım, İstanbul. aksiyon.com.tr Gündem ekibinin 'son d</t>
+          <t>TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Anasayfa / Ekonomi / Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye'de İş Dünyası Ekonomi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Güncelleme: 14/09/2026 09:00 Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. 14/09/2026 09:00 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Bilsar Tekstil Muharrem Hilmi Kayhan Söktaş Tekstil Sanayici ve ihracatçılar için “Dönüşüme Değer” iş birliği Yıldız yaratan turnuvada final heyecanı Migros, meyve ve sebzedeki pestisit analiz sonuçlarını Migros Sanal Market’te yayınlamaya başladı Şirketlerde yeni unvan dönemi Sessiz ilerleyen hastalığa karşı 5 kritik uyarı Kule vinç sektöründe Türkiye’nin üretim potansiyeli öne çıkıyor SON DAKİKA HABERLERİ GÜNDEM KORİDORU 10 gün önce Resmi Gazete’de yayımlandı: Diyanet ve Dışişleri’nde kritik atamalar gerçekleşti EKONOMİ 12 gün önce KOSGEB’den KOBİ’lere 27,1 milyar liralık dev can suyu ALMANYA'DA İŞ DÜNYASI 12 gün önce Almanya’da Trilya yağına zararlı mineral yağ engeli: Raflardan toplatılıyor EKONOMİ 12 gün önce Eskişehir’de stratejik adım: Nadir elementler için dev kamulaştırma SPOR 12 gün önce Beşiktaş’ta beklenen ayrılık EKONOMİ 12 gün önce AFSİAD Başkanı Sayın’dan bankalara faiz ve teminat çağrısı EMLAK 12 gün önce Eylül ayı kira artış oranı için gözler TÜİK’te KATEGORİNİN POPÜLERLERİ 1 Gram altın tahminleri 2025 2 2026 gram altın fiyatı tahmini! Altın ne kadar olur? 3 Motosiklet fiyatlarına ek gümrük vergisi geldi! Scooterlara ne kadar zam geldi? 4 2025 çiğ süt satış fiyatı belli oldu 5 Kilis’in ihracatı ilk yarıda yüzde 13 artarak 69,2 milyon dolara ulaştı Türkiye’nin sivil havacılık filosunda araç sayısında dikkat çeken artış Jimmy Key yurt dışında 17 mağazaya ulaştı Ahilik Haftası’nda esnafa finansman desteği Tarımda iklim riski büyüyor, sigortanın önemi artıyor Egeli ihracatçılardan Karadeniz için güvenli koridor talebi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Türkiye’nin sivil havacılık filosunda araç sayısında dikkat çeken artış Jimmy Key yurt dışında 17 mağazaya ulaştı Ahilik Haftası’nda esnafa finansman desteği Tarımda iklim riski büyüyor, sigortanın önemi artıyor Egeli ihracatçılardan Karadeniz için güvenli koridor talebi</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor aksiyon.com.tr Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Gece yarısı Düzce Door fabrikasında yangın Düzce D-100 karayolu kenarında bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında başlayan yangın, kısa sürede büyüyerek fabrikayı etkisi altına aldı. Olay yerine intikal eden Düzce Belediye ekipleri ve itfaiye müdahalesi ile alevleri kontrol altına almak için çalışma başlattı. Olay yeri ve müdahale: İlk ihbarın D-100 karayolundan görüldüğü için geldiğini belirten yetkililer, itfaiye ekiplerinin bölgeye yönlendirildiğini söyledi. Ahşap ve Amerikan panel üretimi yapan fabrikanın malzeme yapısı nedeniyle yangının kısa sürede yayıldığı bildirildi. Belediye ekipleri yangına müdahale ederken öncelik olarak personel güvenliği ve çevredeki yapıların korunması hedeflendi. Başkan Özlü'nün açıklamaları: Düzce Belediye Başkanı Dr. Faruk Özlü , olay yerinde yaptığı açıklamada ekiplere tüm imkanların seferber edildiğini ve yangının en kısa sürede kontrol altına alınmasının amaçlandığını söyledi. Özlü, ilk bildirimde gecikme olduğunu düşündüğünü, bazı komşuların fabrikada zaman zaman küçük çaplı yangınlar yaşandığını ifade ettiğini aktardı. Başkan Özlü, "İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra uzmanlarımız çıkış sebebi üzerinde çalışacaklar" diyerek, fabrikanın yapısal özellikleri nedeniyle alevlerin hızla yayıldığını vurguladı. Ayrıca can kaybı olmadığını belirterek, fabrika sahiplerine ve Düzce halkına geçmiş olsun dileğinde bulundu. Yetkililer, söndürme çalışmalarının bu akşam tamamlanmasının hedeflendiğini, yangının kesin çıkış nedeninin ise inceleme sonrası netleşeceğini bildirdi. Düzce Belediye Başkanı Faruk Özlü yangını en kısa sürede söndürmeye çalıştıklarını söyledi 1 Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı 2 Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada 3 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 4 Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı 5 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 6 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 7 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Gece yarısı Düzce Door fabrikasında çıkan yangına itfaiye müdahale ediyor Gece yarısı Düzce Door fabrikasında yangın Düzce'de Düzce Door kapı fabrikasında 21.30'da başlayan yangına belediye itfaiyesi müdahale etti; Faruk Özlü can kaybı olmadığını ve söndürme çalışmalarının sürdüğünü açıkladı. Düzce D-100 karayolu kenarında bulunan Düzce Door isimli kapı fabrikasında saat 21.30 sıralarında başlayan yangın, kısa sürede büyüyerek fabrikayı etkisi altına aldı. İlk ihbarın D-100 karayolundan görüldüğü için geldiğini belirten yetkililer, itfaiye ekiplerinin bölgeye yönlendirildiğini söyledi. Düzce Belediye Başkanı Dr. Düzce Belediye Başkanı Faruk Özlü yangını en kısa sürede söndürmeye çalıştıklarını söyledi Ben Ahmet Demir, 30 yaşındayım, İstanbul.</t>
+          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Çorum’da faaliyet gösteren Bilsar’ın ödeme güçlüğüne düşmesi, Aydın Söke’de üretim yapan Söktaş Tekstil’in ticari alacaklarını ve finansal görünümünü etkiledi. TÜSİAD’ın eski başkanlarından Muharrem Hilmi Kayhan ile kardeşi Eyüp Hilmi Kayhan’ın büyük ortakları arasında bulunduğu Söktaş Tekstil’in kredi notu, JCR Avrasya Derecelendirme tarafından aşağı çekildi. KREDİ NOTU B SEVİYESİNE İNDİRİLDİ JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Şirketin görünümü de “Negatif” olarak revize edildi. Not indiriminin gerekçeleri arasında Söktaş’ın 2025 yılında kaldıraç ve borç karşılama göstergelerinde yaşanan belirgin bozulma gösterildi. Derecelendirme kuruluşuna göre, 2026’nın ilk yarısında da şirketin finansal görünümündeki zayıflık sürdü. Söktaş’ın üretim ve satış hacimlerinde hem 2025 yılında hem de 2026’nın ilk altı ayında gerileme yaşandığı belirtildi. Ayrıca şirketin 1 Eylül 2026 itibarıyla gecikme kayıtlarının oluşması ve bu durumun güncel olarak devam etmesi de not indiriminde etkili oldu. ÖDENMEYEN SENETLERİN KAYNAĞINI AÇIKLADI Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Şirket, söz konusu gecikmelerin kendi borç ödeme kapasitesindeki bir sorundan veya doğrudan üstlendiği yükümlülüklerden kaynaklanmadığını bildirdi. Şirketin açıklamasına göre sorun, Bilsar Tekstil’den tahsilat karşılığında alınan ve ticari borçların ödenmesinde kullanılan senetlerden kaynaklandı. Bilsar’ın ödeme güçlüğüne düşmesi ve ardından konkordato başvurusunda bulunması nedeniyle bu senetlerin vadelerinde tahsil edilemediği belirtildi. Söktaş, yaşanan gelişmenin kambiyo mevzuatı kapsamında kendisine “ciranta” sıfatıyla yüklenen müteselsil sorumluluk nedeniyle finansal sistemlere gecikme kaydı olarak yansıdığını ifade etti. HUKUKİ SÜREÇ BAŞLATILDI Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Şirket ayrıca yaşanan gelişmenin nakit akışı ve finansal yapısı üzerindeki etkisini sınırlamak amacıyla likidite ve nakit yönetimi tedbirlerinin uygulamaya alındığını açıkladı. Söktaş, ticari alacaklardan kaynaklanan risklerin yakından takip edildiğini ve finansal yapının korunmasına yönelik önlemlerin sürdürüldüğünü bildirdi. BİLSAR AVRUPA’NIN ÖNEMLİ ÜRETİCİLERİNDENDİ Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Mahkeme, şirket sahipleri ile birlikte Bilsar Tekstil ve Bilsar Dış Ticaret hakkında 3 aylık geçici mühlet kararı vermişti. Bir dönem yıllık yaklaşık 2,5 milyon gömlek üretim kapasitesine ulaşan Bilsar, Avrupa’nın en büyük gömlek üreticileri arasında gösteriliyordu. Şirketin yaşadığı ödeme sıkıntısının, ticari ilişkide bulunduğu diğer tekstil şirketlerine de yansıması sektördeki finansal baskının boyutunu ortaya koydu. Anasayfa / Ekonomi / Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye'de İş Dünyası Ekonomi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Güncelleme: 14/09/2026 09:00 Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. TÜSİAD eski Başkanı Muharrem Hilmi Kayhan’ın büyük ortakları arasında yer aldığı Söktaş’ın kredi notu JCR Avrasya tarafından BBB- (tr)’den B (tr)’ye indirildi. Şirketin görünümü ise “Negatif” olarak belirlendi. 14/09/2026 09:00 0 Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. Bilsar Tekstil Muharrem Hilmi Kayhan Söktaş Tekstil Sanayici ve ihracatçılar için “Dönüşüme Değer” iş birliği Yıldız yaratan turnuvada final heyecanı Migros, meyve ve sebzedeki pestisit analiz sonuçlarını Migros Sanal Market’te yayınlamaya başladı Şirketlerde yeni unvan dönemi Sessiz ilerleyen hastalığa karşı 5 kritik uyarı Kule vinç sektöründe Türkiye’nin üretim potansiyeli öne çıkıyor SON DAKİKA HABERLERİ GÜNDEM KORİDORU 10 gün önce Resmi Gazete’de yayımlandı: Diyanet ve Dışişleri’nde kritik atamalar gerçekleşti EKONOMİ 12 gün önce KOSGEB’den KOBİ’lere 27,1 milyar liralık dev can suyu ALMANYA'DA İŞ DÜNYASI 12 gün önce Almanya’da Trilya yağına zararlı mineral yağ engeli: Raflardan toplatılıyor EKONOMİ 12 gün önce Eskişehir’de stratejik adım: Nadir elementler için dev kamulaştırma SPOR 12 gün önce Beşiktaş’ta beklenen ayrılık EKONOMİ 12 gün önce AFSİAD Başkanı Sayın’dan bankalara faiz ve teminat çağrısı EMLAK 12 gün önce Eylül ayı kira artış oranı için gözler TÜİK’te KATEGORİNİN POPÜLERLERİ 1 Gram altın tahminleri 2025 2 2026 gram altın fiyatı tahmini! 4 2025 çiğ süt satış fiyatı belli oldu 5 Kilis’in ihracatı ilk yarıda yüzde 13 artarak 69,2 milyon dolara ulaştı Türkiye’nin sivil havacılık filosunda araç sayısında dikkat çeken artış Jimmy Key yurt dışında 17 mağazaya ulaştı Ahilik Haftası’nda esnafa finansman desteği Tarımda iklim riski büyüyor, sigortanın önemi artıyor Egeli ihracatçılardan Karadeniz için güvenli koridor talebi Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Çorum merkezli Bilsar Tekstil’in konkordato sürecine girmesi, ticari ilişkide bulunduğu Söktaş Tekstil’i de finansal açıdan etkiledi. Türkiye’nin önde gelen gömlek üreticileri arasında yer alan Bilsar Tekstil’in konkordato süreci, sektördeki başka bir önemli şirketi de finansal açıdan zor durumda bıraktı. JCR Avrasya, Söktaş Tekstil’in uzun vadeli ulusal kredi notunu BBB- (tr)’den B (tr)’ye düşürdü. Söktaş ise derecelendirme raporunda yer alan “gecikme kayıtları” ifadesine ilişkin açıklama yaptı. Ödenmeyen senetler konusunda gerekli hukuki ve yasal işlemlerin başlatıldığı açıklanırken, Söktaş’ın hem keşideci hem de borçlu konumundaki üçüncü şirketler hakkında takip süreçlerini devreye aldığı belirtildi. Çorum’da Bil’s markasıyla gömlek üretimi gerçekleştiren Bilsar Tekstil’in sahipleri Selman Safi Bilal ve Süha Bilal, ağustos ayının sonunda konkordato talebinde bulunmuştu. Türkiye’nin sivil havacılık filosunda araç sayısında dikkat çeken artış Jimmy Key yurt dışında 17 mağazaya ulaştı Ahilik Haftası’nda esnafa finansman desteği Tarımda iklim riski büyüyor, sigortanın önemi artıyor Egeli ihracatçılardan Karadeniz için güvenli koridor talebi</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -6117,17 +6331,17 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.aksiyon.com.tr/gece-yarisi-duzce-door-fabrikasinda-cikan-yangina-itfaiye-mudahale-ediyor-353989</t>
+          <t>https://turkiyedeisdunyasi.com/gomlek-devinin-konkordato-ilan-etti-tusiad-eski-baskaninin-sirketinde-kredi-notu-dustu-132732/</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Adana | Bilecik | Düzce | Iğdır | Zonguldak</t>
+          <t>Çorum | Eskişehir | Kilis | Aydın | İstanbul</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Köşk | Mudurnu</t>
+          <t>Söke | Beşiktaş</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -6151,7 +6365,7 @@
       <c r="Y36" s="2" t="inlineStr"/>
       <c r="Z36" s="2" t="inlineStr"/>
       <c r="AA36" s="2" t="n">
-        <v>117.5</v>
+        <v>116.5</v>
       </c>
       <c r="AB36" s="2" t="n">
         <v>35</v>
@@ -6160,27 +6374,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:44:00</t>
+          <t>2026-09-14 09:46:30</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Cumhuriyet</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -6190,52 +6404,40 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>gıda</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Edinilen bilgiye göre, saat 21.40 sıralarında Door Kapı Fabrikası'nda henüz belirlenemeyen bir nedenle yangın çıktı. Alevler kısa sürede fabrikanın geniş bir bölümüne yayılırken, yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. İhbar üzerine bölgeye çok sayıda itfaiye, sağlık ve güvenlik ekibi sevk edildi. Yangının büyüklüğü nedeniyle Düzce'nin ilçelerinden itfaiye ekipleri bölgeye yönlendirilirken, Bolu'dan da takviye ekipler sevk edildi. Dron ile havadan kaydedilen görüntülerde fabrikanın büyük bölümünü saran alevler ve bölgeden yükselen yoğun duman dikkat çekti. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Yangının çıkış nedeninin ise söndürme çalışmalarının ardından yapılacak incelemeyle belirlenmesi bekleniyor. BELEDİYE BAŞKANINDAN AÇIKLAMA: 'ÖNEMLİ OLAN CAN KAYBININ OLMAMASI' Düzce Belediye Başkanı Faruk Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirtti. Başkan Özlü, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Ama gerçekten çok üzücü bir olayla karşı karşıyayız. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce'mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. Düzce’de kapı fabrikasında yangın Müdahale sürüyor, belediye başkanından açıklama geldi "Önemli olan can kaybının olmaması. Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" https://t.co/FX7LXZRI1N pic.twitter.com/0q2oeam7me — Cumhuriyet (@cumhuriyetgzt1) September 13, 2026 Hava Durumu Namaz Vakitleri Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Takip Et: Paylaş:</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Cumhuriyet Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. İtfaiye ekiplerinin yangını kontrol altına almak için çalışmaları sürüyor. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Düzce’de faaliyet gösteren bir kapı üretim fabrikasında yangın çıktı. Düzce Belediye Başkanı Faruk Özlü yaptığı açıklamada Edinilen bilgiye göre, saat 21.40 sıralarında Door Kapı Fabrikası'nda henüz belirlenemeyen bir nedenle yangın çıktı. Alevler kısa sürede fabrikanın geniş bir bölümüne yayılırken, yükselen yoğun duman ve alevler kentin birçok noktasından görüldü. İhbar üzerine bölgeye çok sayıda itfaiye, sağlık ve güvenlik ekibi sevk edildi. Yangının büyüklüğü nedeniyle Düzce'nin ilçelerinden itfaiye ekipleri bölgeye yönlendirilirken, Bolu'dan da takviye ekipler sevk edildi. Dron ile havadan kaydedilen görüntülerde fabrikanın büyük bölümünü saran alevler ve bölgeden yükselen yoğun duman dikkat çekti. Yangının çıkış nedeninin ise söndürme çalışmalarının ardından yapılacak incelemeyle belirlenmesi bekleniyor. BELEDİYE BAŞKANINDAN AÇIKLAMA: 'ÖNEMLİ OLAN CAN KAYBININ OLMAMASI' Düzce Belediye Başkanı Faruk Özlü, yangını en kısa sürede kontrol altına almayı hedeflediklerini belirtti. Başkan Özlü, "Ekiplerimiz burada yangını söndürme çalışmalarına girişiyorlar. Bize gelen ilk ihbar D-100 kara yoluna yakın olduğu için D-100 kara yolundan görenlerin belediyemize bildirmesiyle itfaiye ekiplerimiz buraya geldi. Biliyorsunuz bütün gücümüzle bu yangını söndürmeye çalışıyoruz. Düzce Belediyesi her zaman söylediğim gibi bölgesinin en güçlü itfaiyesidir. Fakat bize yangının bildirilmesinde biraz gecikme olduğu inancındayım. Burada bulunan arkadaşlarla, burada bulunan komşularla görüştüğümüzde bu fabrikada zaman zaman ufak çaplı yangınların olduğunu ifade ettiler. Tabii şu anda sebebini bilmiyoruz. İlk aşamada amacımız yangının söndürülmesi. Yangının söndürülmesinden sonra bizim uzmanlarımız yangının çıkış sebebi üzerinde çalışacaklar. Bir kapı fabrikasının tamamen yanmakta olduğunu, yandığını görüyoruz. Ahşap ve Amerikan panel üreten bir fabrika olduğu için bu yangının çok çabuk yayıldığını, çok çabuk etrafı sardığını ifade etmek isterim. Fabrika sahiplerine ve Düzce'mize geçmiş olsun diliyorum. Önemli olan can kaybının olmaması. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" dedi. Düzce’de kapı fabrikasında yangın Müdahale sürüyor, belediye başkanından açıklama geldi "Önemli olan can kaybının olmaması. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" https://t.co/FX7LXZRI1N pic.twitter.com/0q2oeam7me — Cumhuriyet (@cumhuriyetgzt1) September 13, 2026 Hava Durumu Namaz Vakitleri Düzce’de kapı fabrikasında yangın: Müdahale sürüyor, belediye başkanından açıklama geldi Takip Et: Paylaş:</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.cumhuriyet.com.tr/turkiye/duzce-de-kapi-fabrikasinda-yangin-mudahale-suruyor-belediye-baskanindan-aciklama-geldi-2537255</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Bolu | Düzce</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPOG5TR1RJU1k4eEZxcUtOSVAzNkZoWmJEUmY4bVpNN2lqRHJjYi1FOWxwbmpXYmRsSWVzU244ZXVSQUk2WlNKVTlJdnR4TzhNZVM3NHRYclR1MVFPMTdzdXdrWUNrdllFRDlGQ1VFSXowR3dHSW1KYkhnZk43dGlHQ2hqREFuQWJaWkJqX0toRU9KcGRDU2F1cFY1cmc5djVuSWdFWndR?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>Door Kapı Fabrikası</t>
-        </is>
-      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr"/>
@@ -6249,7 +6451,7 @@
       <c r="Y37" s="2" t="inlineStr"/>
       <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" s="2" t="n">
-        <v>133.75</v>
+        <v>75.38</v>
       </c>
       <c r="AB37" s="2" t="n">
         <v>36</v>
@@ -6258,27 +6460,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:48:26</t>
+          <t>2026-09-14 12:51:00</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti</t>
+          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika</t>
+          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek Yeniçağ Gazetesi</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -6288,22 +6490,22 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>firma, tekstil</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü. Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü.</t>
+          <t>Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil resmen iflas etti. Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil resmen iflas etti. Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil resmen iflas etti. Türkiye'nin önemli tekstil merkezlerinden Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil, içine girdiği mali darboğazı aşamayarak iflas etti. Başvurduğu konkordato sürecinden olumlu bir sonuç alamayan şirket için Kahramanmaraş İcra Dairesi tarafından iflas işlemleri resmen başlatıldı. 2019 yılında kurulan ve bölgede yaklaşık 200 kişiye istihdam sağlayan şirket, tekstil sektöründe oldukça iddialı bir üretim hacmine sahipti. Tesisin yıllık kapasite verileri sektördeki ağırlığını net bir şekilde yansıtıyordu. Fabrikanın boyahane bölümü yıllık 5 milyon 400 bin kilogram üretim kapasitesiyle çalışırken, örgü bölümünün yıllık üretim kapasitesi 5 milyon kilogram seviyesindeydi. Ancak firmanın farklı sektörlere yayılmış bu yatırım yapısı da ne yazık ki yaşanan derin finansal krizden çıkış için yeterli olmadı. Şirketin adım adım iflasa giden süreci, son yıllardaki vergi kayıtlarına da yansıdı. Üretim ve kârlılıktaki duraklama, mali tablolar üzerinden açıkça görülebiliyor. 2023 yılında 2 milyon 362 bin 651 TL vergi matrahı üzerinden 590 bin 662 TL vergi tahakkuku sağlayan şirketin, mali krizin giderek derinleşmesiyle birlikte 2024 ve 2025 yıllarında herhangi bir vergi matrahı oluşmadı. Yaşanan bu finansal tıkanıklık, sürecin nihai olarak iflas kararıyla sonuçlanmasına neden oldu. Ekonomik dalgalanmaların tekstil gibi yoğun istihdam sağlayan köklü sektörler üzerindeki yıkıcı etkisi son dönemde giderek daha belirgin hale geliyor. Sizce yerel üreticileri bu tür mali krizlerden korumak ve istihdam kaybını önlemek adına sektörel bazda ne gibi destek mekanizmaları devreye sokulabilir? Türkiye'nin önemli tekstil merkezlerinden Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil, içine girdiği mali darboğazı aşamayarak iflas etti. Başvurduğu konkordato sürecinden olumlu bir sonuç alamayan şirket için Kahramanmaraş İcra Dairesi tarafından iflas işlemleri resmen başlatıldı. 1 8 2019 yılında kurulan ve bölgede yaklaşık 200 kişiye istihdam sağlayan şirket, tekstil sektöründe oldukça iddialı bir üretim hacmine sahipti. 2 8 Tesisin yıllık kapasite verileri sektördeki ağırlığını net bir şekilde yansıtıyordu. Fabrikanın boyahane bölümü yıllık 5 milyon 400 bin kilogram üretim kapasitesiyle çalışırken, örgü bölümünün yıllık üretim kapasitesi 5 milyon kilogram seviyesindeydi. 3 8 Ancak firmanın farklı sektörlere yayılmış bu yatırım yapısı da ne yazık ki yaşanan derin finansal krizden çıkış için yeterli olmadı. Şirketin adım adım iflasa giden süreci, son yıllardaki vergi kayıtlarına da yansıdı. Üretim ve kârlılıktaki duraklama, mali tablolar üzerinden açıkça görülebiliyor. 5 8 2023 yılında 2 milyon 362 bin 651 TL vergi matrahı üzerinden 590 bin 662 TL vergi tahakkuku sağlayan şirketin, mali krizin giderek derinleşmesiyle birlikte 2024 ve 2025 yıllarında herhangi bir vergi matrahı oluşmadı. 6 8 Yaşanan bu finansal tıkanıklık, sürecin nihai olarak iflas kararıyla sonuçlanmasına neden oldu. Ekonomik dalgalanmaların tekstil gibi yoğun istihdam sağlayan köklü sektörler üzerindeki yıkıcı etkisi son dönemde giderek daha belirgin hale geliyor. 7 8 Sizce yerel üreticileri bu tür mali krizlerden korumak ve istihdam kaybını önlemek adına sektörel bazda ne gibi destek mekanizmaları devreye sokulabilir? 8 8 Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil resmen iflas etti. Yeniçağ Gazetesi mobil uygulamasını hemen indirin. QR kodu tarayarak hızlıca mağazaya ulaşın.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika Düzce merkeze bağlı Hacialiler köyü mevkisindeki kapı fabrikasında saat 22.00 sıralarında yangın çıktı ve kısa sürede tüm fabrikayı sardı. İtfaiyenin müdahalesi sürerken Sakarya ve Bolu'dan da destek ekipleri bölgeye sevk edildi, fabrikadan yükselen alevler kentin birçok noktasından görüldü.</t>
+          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek Yeniçağ Gazetesi Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil resmen iflas etti. Türkiye'nin önemli tekstil merkezlerinden Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil, içine girdiği mali darboğazı aşamayarak iflas etti. Başvurduğu konkordato sürecinden olumlu bir sonuç alamayan şirket için Kahramanmaraş İcra Dairesi tarafından iflas işlemleri resmen başlatıldı. 2019 yılında kurulan ve bölgede yaklaşık 200 kişiye istihdam sağlayan şirket, tekstil sektöründe oldukça iddialı bir üretim hacmine sahipti. Tesisin yıllık kapasite verileri sektördeki ağırlığını net bir şekilde yansıtıyordu. Fabrikanın boyahane bölümü yıllık 5 milyon 400 bin kilogram üretim kapasitesiyle çalışırken, örgü bölümünün yıllık üretim kapasitesi 5 milyon kilogram seviyesindeydi. Ancak firmanın farklı sektörlere yayılmış bu yatırım yapısı da ne yazık ki yaşanan derin finansal krizden çıkış için yeterli olmadı. Şirketin adım adım iflasa giden süreci, son yıllardaki vergi kayıtlarına da yansıdı. Üretim ve kârlılıktaki duraklama, mali tablolar üzerinden açıkça görülebiliyor. 2023 yılında 2 milyon 362 bin 651 TL vergi matrahı üzerinden 590 bin 662 TL vergi tahakkuku sağlayan şirketin, mali krizin giderek derinleşmesiyle birlikte 2024 ve 2025 yıllarında herhangi bir vergi matrahı oluşmadı. Yaşanan bu finansal tıkanıklık, sürecin nihai olarak iflas kararıyla sonuçlanmasına neden oldu. Sizce yerel üreticileri bu tür mali krizlerden korumak ve istihdam kaybını önlemek adına sektörel bazda ne gibi destek mekanizmaları devreye sokulabilir? 1 8 2019 yılında kurulan ve bölgede yaklaşık 200 kişiye istihdam sağlayan şirket, tekstil sektöründe oldukça iddialı bir üretim hacmine sahipti. 2 8 Tesisin yıllık kapasite verileri sektördeki ağırlığını net bir şekilde yansıtıyordu. 3 8 Ancak firmanın farklı sektörlere yayılmış bu yatırım yapısı da ne yazık ki yaşanan derin finansal krizden çıkış için yeterli olmadı. 5 8 2023 yılında 2 milyon 362 bin 651 TL vergi matrahı üzerinden 590 bin 662 TL vergi tahakkuku sağlayan şirketin, mali krizin giderek derinleşmesiyle birlikte 2024 ve 2025 yıllarında herhangi bir vergi matrahı oluşmadı. 6 8 Yaşanan bu finansal tıkanıklık, sürecin nihai olarak iflas kararıyla sonuçlanmasına neden oldu. 7 8 Sizce yerel üreticileri bu tür mali krizlerden korumak ve istihdam kaybını önlemek adına sektörel bazda ne gibi destek mekanizmaları devreye sokulabilir? 8 8 Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek Kahramanmaraş'ta faaliyet gösteren Germenicia Boya Tekstil resmen iflas etti. Yeniçağ Gazetesi mobil uygulamasını hemen indirin. QR kodu tarayarak hızlıca mağazaya ulaşın.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -6313,12 +6515,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.sondakika.com/amp/haber-duzce-hacialiler-koyundeki-fabrika-yanginina-sakar-20234469/</t>
+          <t>https://www.yenicaggazetesi.com/tekstil-sektorunun-iddiali-firmasi-iflas-etti-200-calisan-kara-kara-dusunecek-1071744h.htm</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
+          <t>Kahramanmaraş</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
@@ -6343,7 +6545,7 @@
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr"/>
       <c r="AA38" s="2" t="n">
-        <v>96.03</v>
+        <v>103.75</v>
       </c>
       <c r="AB38" s="2" t="n">
         <v>37</v>
@@ -6352,27 +6554,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:36:42</t>
+          <t>2026-09-14 11:31:46</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı</t>
+          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı</t>
+          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Merhaba Gazetesi</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -6382,44 +6584,52 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>firma, organize sanayi, sanayi</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı</t>
+          <t>Endüstriyel mutfak ekipmanları üretip, dünyaya satan Konyalı firmayla ilgili yeni bir haber duyuruldu. Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat San. ve Tic. Ltd. Şti ile ilgili kritik 2 ay başladı Endüstriyel mutfak ekipmanları üretip, dünyaya satan Konyalı firmayla ilgili yeni bir haber duyuruldu. Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat San. ve Tic. Ltd. Şti ile ilgili kritik 2 ay başladı Endüstriyel mutfak ekipmanları üretip, dünyaya satan Konyalı firmayla ilgili yeni bir haber duyuruldu. Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat San. ve Tic. Ltd. Şti ile ilgili kritik 2 ay başladı Anasayfa Ekonomi Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Yayınlanma: 14 Eylül 2026 Pazartesi 14:31 Endüstriyel mutfak ekipmanları üretip, dünyaya satan Konyalı firmayla ilgili yeni bir haber duyuruldu. Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat San. ve Tic. Ltd. Şti ile ilgili kritik 2 ay başladı 2015 yılında Konya'da küçük bir atölyede hamur yoğurma ve hamur açma makineleri üreterek faaliyetlerine başlayan, zamanla dünyaya açılan ve sektörde bir dönem ihracat rekoru kıran Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat Sanayi ve Ticaret Limited Şirketi, bu yılın haziran ayında konkordato başvurusu yapmıştı. 2. Organize Sanayi Bölgesinde faaliyet gösteren, lüks ve donanımlı bir fabrikada üretim yapan firmaya 3 ay süre ile geçici mühlet kararı ve ihtiyati tedbir kararı verilmişti. Bu süreç ile ilgili yeni bir gelişme daha yaşandı. Osimo; hamur yoğurma makinesi, et kıyma makinesi, endüstriyel fırın, patates soyma makinesi başta olmak üzere, birçok alanda ürünün üretimini yapıyordu. Firmanın üretim tesisi ise 2. Organize Sanayi Bölgesinde yer alıyor. 2 AYLIK UZATMA VERİLDİ Konya 3. Asliye Ticaret Mahkemesi tarafından şunlar belirtildi: “Davacı Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat Sanayi ve Ticaret Limited Şirketi - (Selçuk Vergi Dairesi Vergi No:648***…. - Konya Ticaret Sicil No:486..) tarafından hasımsız olarak açılan Mahkememizde görülmekte olan Konkordato (Adi Konkordatodan Kaynaklanan (İİK 285 İla 308/h)) davasının 04.09.2026 tarihli duruşması sırasında verilen ara karar gereğince; Davacı Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat Sanayi ve Ticaret Limited Şirketi - (Selçuk Vergi Dairesi Vergi No:648***…. - Konya Ticaret Sicil No:486..) hakkında 17.06.2026 tarihinden itibaren verilen 3 aylık konkordato geçici mühletinin, 17.09.2026 tarihinden itibaren 2 AY DAHA UZATILMASINA, 17.06.2026 gün ve 2026/505 Esas sayılı ara kararında verilen ihtiyati tedbir kararlarının aynen DEVAMINA, 382818**** T.C. kimlik numaralı Serbest Muhasebeci Mali Müşavir Hüseyin SEZEN'in Geçici Konkordato Komiseri olarak görevinin DEVAMINA, karar verildiği İLAN OLUNUR.” Konkordatoda 2 aylık uzatma kararı, 3 aylık "geçici mühlet" süresinin yetersiz kalması ve sürecin başarıyla tamamlanabilmesi için ek zamana ihtiyaç duyulması nedeniyle verilir. Kaynak: Haber Merkezi HABERE YORUM KAT UYARI: Küfür, hakaret, rencide edici cümleler veya imalar, inançlara saldırı içeren, imla kuralları ile yazılmamış, Türkçe karakter kullanılmayan ve büyük harflerle yazılmış yorumlar onaylanmama</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" İhlas Haber Ajansı İhlas Haber Ajansı</t>
+          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Merhaba Gazetesi Endüstriyel mutfak ekipmanları üretip, dünyaya satan Konyalı firmayla ilgili yeni bir haber duyuruldu. Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat San. Ltd. Şti ile ilgili kritik 2 ay başladı Endüstriyel mutfak ekipmanları üretip, dünyaya satan Konyalı firmayla ilgili yeni bir haber duyuruldu. Ltd. Şti ile ilgili kritik 2 ay başladı Anasayfa Ekonomi Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Yayınlanma: 14 Eylül 2026 Pazartesi 14:31 Endüstriyel mutfak ekipmanları üretip, dünyaya satan Konyalı firmayla ilgili yeni bir haber duyuruldu. Ltd. Şti ile ilgili kritik 2 ay başladı 2015 yılında Konya'da küçük bir atölyede hamur yoğurma ve hamur açma makineleri üreterek faaliyetlerine başlayan, zamanla dünyaya açılan ve sektörde bir dönem ihracat rekoru kıran Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat Sanayi ve Ticaret Limited Şirketi, bu yılın haziran ayında konkordato başvurusu yapmıştı. Organize Sanayi Bölgesinde faaliyet gösteren, lüks ve donanımlı bir fabrikada üretim yapan firmaya 3 ay süre ile geçici mühlet kararı ve ihtiyati tedbir kararı verilmişti. Bu süreç ile ilgili yeni bir gelişme daha yaşandı. Osimo; hamur yoğurma makinesi, et kıyma makinesi, endüstriyel fırın, patates soyma makinesi başta olmak üzere, birçok alanda ürünün üretimini yapıyordu. Firmanın üretim tesisi ise 2. Organize Sanayi Bölgesinde yer alıyor. 2 AYLIK UZATMA VERİLDİ Konya 3. Asliye Ticaret Mahkemesi tarafından şunlar belirtildi: “Davacı Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat Sanayi ve Ticaret Limited Şirketi - (Selçuk Vergi Dairesi Vergi No:648***…. - Konya Ticaret Sicil No:486..) tarafından hasımsız olarak açılan Mahkememizde görülmekte olan Konkordato (Adi Konkordatodan Kaynaklanan (İİK 285 İla 308/h)) davasının 04.09.2026 tarihli duruşması sırasında verilen ara karar gereğince; Davacı Osimo Endüstriyel Mutfak Ekipmanları İthalat İhracat Sanayi ve Ticaret Limited Şirketi - (Selçuk Vergi Dairesi Vergi No:648***…. - Konya Ticaret Sicil No:486..) hakkında 17.06.2026 tarihinden itibaren verilen 3 aylık konkordato geçici mühletinin, 17.09.2026 tarihinden itibaren 2 AY DAHA UZATILMASINA, 17.06.2026 gün ve 2026/505 Esas sayılı ara kararında verilen ihtiyati tedbir kararlarının aynen DEVAMINA, 382818**** T.C. kimlik numaralı Serbest Muhasebeci Mali Müşavir Hüseyin SEZEN'in Geçici Konkordato Komiseri olarak görevinin DEVAMINA, karar verildiği İLAN OLUNUR.” Konkordatoda 2 aylık uzatma kararı, 3 aylık "geçici mühlet" süresinin yetersiz kalması ve sürecin başarıyla tamamlanabilmesi için ek zamana ihtiyaç duyulması nedeniyle verilir.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxOWFBIUXlRV3gyZy1XMnUzM3d5R3YtcDlaSjdiQlNXalhVMTAwSHhhZWtKSHVkTzVMd09OMWxZbVlheGI1dmthNkZXVTM5RXRjUkduanpSX3NRN0JRa0c0dEo3MTFPVmdzemJSLTNNMnFDc0JSM0ZOVldLUWM5X2tZUkF5c0pCdHY2WHE1M2NCdTdGWlVzV192S1FEdUJtYlQ3ai1WbUpoX1BKdXNSRWJRb190OG9EbWZsVmhWaXJ5OUdEazNLVTZlMFNtR0dILTltdkxkYkN1SDNtUWFCX0FXMEZ5OERZMk1HWjdzM0diNjBodVFfYjlvZEVhVQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>https://www.merhabahaber.com/konya-organize-sanayideki-dev-firma-konkordato-ilan-etti-2-ay-sure-basladi-1952300h.htm</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Konya</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>Firmanın üretim tesisi</t>
+        </is>
+      </c>
       <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>ilçe yok | firma yok</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr"/>
@@ -6433,7 +6643,7 @@
       <c r="Y39" s="2" t="inlineStr"/>
       <c r="Z39" s="2" t="inlineStr"/>
       <c r="AA39" s="2" t="n">
-        <v>118.1</v>
+        <v>125.5</v>
       </c>
       <c r="AB39" s="2" t="n">
         <v>38</v>
@@ -6442,27 +6652,27 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:48:24</t>
+          <t>2026-09-14 06:22:37</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada aksiyon.com.tr</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -6472,44 +6682,36 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>tesis, üretim, üretim tesisi</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>üretim tesisi</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. olay yerine intikal ve müdahale: Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. alevler ve dumanın görünürlüğü: Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. müdahalenin sürdüğü bildirildi: Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. 1 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 2 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 3 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 4 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı 5 Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı 6 Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı 7 Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada olay yerine intikal ve müdahale: Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. Ben Mehmet Yılmaz, 28 yaşındayım. İstanbul'dayım. aksiyon.com.tr Gündem ekibinin hırslı araştırmacı gazetecisiyim. Masa başında durmayı sevmem; sahada, meclis koridorlarında, siyasi kulislerde gerçeklerin peşindeyim. İdealist biriyim ve işimi ciddiyetle yaparım. 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada aksiyon.com.tr Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. olay yerine intikal ve müdahale: Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. İhbar üzerine bölgeye çok sayıda itfaiye ekibi sevk edildi ve ekiplerin yangına müdahalesi sürüyor. alevler ve dumanın görünürlüğü: Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Olayın büyüklüğü ve dumanın yüksekliği nedeniyle çevrede gözle görülür bir etkilenme kaydedildi. müdahalenin sürdüğü bildirildi: Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Olayla ilgili soruşturma ve hasar tespit çalışmaları yangın söndürüldükten sonra yapılacak. DÜZCE’DE FAALİYET GÖSTEREN DÜZCE DOOR KAPI FABRİKASINDA YANGIN ÇIKTI. KISA SÜREDE BÜYÜYEN YANGIN NEDENİYLE FABRİKA ALEVLERE TESLİM OLURKEN, BÖLGEYE ÇOK SAYIDA İTFAİYE EKİBİ SEVK EDİLDİ. 1 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 2 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 3 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 4 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı 5 Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı Maltepe'de dükkanında ölü bulunan kuyumcu için inceleme başlatıldı 6 Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı Aydın'da ÇEMBER-141 operasyonu: 2 günde 24 aranan şahıs yakalandı 7 Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Bartın'da yağmura rağmen ilköğretim haftası kutlaması kararlılıkla sürdü Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada olay yerine intikal ve müdahale: Düzce Door Kapı fabrikasında kısa sürede büyüyen yangın şehrin üst kesimlerinden de görüldü; çok sayıda itfaiye ekibi olay yerine yönlendirildi. Düzce’de faaliyet gösteren Düzce Door Kapı fabrikasında başlayan yangın, edinilen bilgilere göre kısa sürede büyüyerek geniş bir alana yayıldı. Alev topuna dönen fabrikadan yükselen yoğun duman ve alevler, şehrin üst kesimlerinden de görüldü. Yetkililer, itfaiye ekiplerinin yangını kontrol altına almak ve büyümesini engellemek için çalışmalarını sürdürdüğünü bildirdi. Ben Mehmet Yılmaz, 28 yaşındayım. Masa başında durmayı sevmem; sahada, meclis koridorlarında, siyasi kulislerde gerçeklerin peşindeyim. 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
+          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi 58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber 58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://www.aksiyon.com.tr/duzce-de-uretim-tesisinde-yangin-alarmi-itfaiye-ekipleri-sahada-353976</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Adana | Aydın | Bartın | Düzce | Iğdır</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>Köşk | Mudurnu | Maltepe</t>
-        </is>
-      </c>
+          <t>https://tasinmazhaber.com/58-yillik-meyve-suyu-sirketi-konkordatodan-cikti-aroma-bursa-konkordato-sureci-sona-erdi/</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -6517,7 +6719,7 @@
       <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr"/>
@@ -6531,7 +6733,7 @@
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr"/>
       <c r="AA40" s="2" t="n">
-        <v>102.75</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="AB40" s="2" t="n">
         <v>39</v>
@@ -6540,27 +6742,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:27:59</t>
+          <t>2026-09-13 20:52:25</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı duzcegazeteefsane.com</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6570,39 +6772,31 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>turizm</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı duzcegazeteefsane.com Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların Düzce'nin Hacı Aliler Köyü D-100 Karayolu üzerinde bulunan bir kapı fabrikasında gece saatlerinde meydana gelen ve korku dolu anlar yaşatan yangın, kurumların</t>
+          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://www.duzcegazeteefsane.com/duzce-belediyesi-gundem-duzce-haberleri/15394-saniyelerle-yarisildi:-duzcedeki-fabrika-yanginina-hizli-mudahale-ve-ekiplerin-zaman-cizelgesi-aciklandi</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+          <t>https://tasinmazhaber.com/vib-turizm-konkordato-surecine-girdi-mahkemeden-3-aylik-gecici-muhlet-karari/</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
@@ -6611,7 +6805,7 @@
       <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr"/>
@@ -6625,7 +6819,7 @@
       <c r="Y41" s="2" t="inlineStr"/>
       <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" s="2" t="n">
-        <v>115.01</v>
+        <v>68.42</v>
       </c>
       <c r="AB41" s="2" t="n">
         <v>40</v>
@@ -6634,27 +6828,27 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 14:06:00</t>
+          <t>2026-09-14 07:27:00</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>fabrika yangını</t>
+          <t>konkordato</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı!</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı yeniadimgazetesi.com</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -6664,22 +6858,22 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Yükleniyor... Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Sercan Yıldırım Editör 13.09.2026 - 17:06 Yayınlanma 13.09.2026 - 17:06 Güncelleme —</t>
+          <t>Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. 14.09.2026 - 10:27 Yayınlanma — Paylaşım 1 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Kahramanmaraş Asliye Ticaret Mahkemesi’nin 2 Eylül 2026 tarihli kararı doğrultusunda, Germenicia Boya Tekstil Petrol İnşaat Sanayi ve Ticaret Limited Şirketi hakkında iflas kararı verildi. Mahkemenin 2025/22 Esas sayılı dosyasında verilen karara göre şirketin iflasına 2 Eylül 2026 saat 10.25 itibarıyla hükmedildi. Kararın ardından şirketin tasfiye işlemlerine başlandığı bildirildi. İflas kararının, İcra ve İflas Kanunu’nun 166. maddesi kapsamında ilan yoluyla tebliğ edildiği belirtildi. Germenicia Tekstil hakkında da iflas kararı Aynı mahkeme kararı kapsamında Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi hakkında da iflas işlemi başlatıldı. Bu şirketin de 2 Eylül 2026 tarihinde saat 10.25 itibarıyla iflasına karar verildiği duyuruldu. Mahkeme kararının ardından şirketin tasfiye sürecinin başlatıldığı ve kararın ilgili mevzuat gereğince ilan edildiği bildirildi. Konkordato sürecinde 2 aylık uzatma Kahramanmaraş Asliye Ticaret Mahkemesi’nde görülen bir başka konkordato dosyasında ise A.T., G.T., N.T. ile Maktes Isıtma ve Soğutma Sistemleri Taahhüt Makina Tesisat İnşaat Plan Proje Sanayi ve Ticaret Limited Şirketi hakkında yeni karar alındı. Benzin 80 TL’yi aştı! Gözler motorin zammında: 100 TL sınırına dayanacak İçeriği Görüntüle Mahkemenin 9 Eylül 2026 tarihli ara kararı doğrultusunda, 1 Ekim 2026 tarihinden itibaren geçerli olmak üzere kesin mühletin 2 ay süreyle uzatılmasına hükmedildi. Daha önce uygulanan kesin mühlete ilişkin tedbirlerin de devam etmesine karar verildi. Karar kapsamında, mahkemenin izni olmaksızın rehin, kefalet, devir, takyit ve ivazsız tasarruf işlemlerinin önlenmesine yönelik tedbirlerin sürdürüleceği bildirildi. Ayrıca her türlü ihtiyati tedbir ve ihtiyati haciz işlemleri ile muhafaza işlemleri dahil takip işlemlerinin de ihtiyati tedbir yoluyla durdurulmasına karar verildi. Alacaklılara 7 günlük itiraz süresi Mahkeme, konkordato sürecine ilişkin olarak alacaklılara da çağrıda bulundu. Buna göre alacaklıların, ilanın yayımlanmasından itibaren 7 gün içinde mahkeme dosyasına itiraz edebileceği bildirildi. Alacaklıların, konkordato mühleti verilmesini gerektiren bir durum bulunmadığını delilleriyle birlikte ortaya koyarak konkordato talebinin reddedilmesini isteme hakkı bulunduğu belirtildi. Editör Hakkında Editör 02 Bunlar da</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı yeniadimgazetesi.com Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. 1 fabrika işçisinin hafif şekilde yaralandığı fabrika yangınına müdahale anları havadan görüntülendi. Bolu'daki fabrika yangınında yaklaşık 4 saat geride kaldı: 1 yaralı Bolu'nun Gerede ilçesindeki geri dönüşüm fabrikasında çıkan yangının söndürme çalışmalarında yaklaşık 4 saat geride kaldı. Sercan Yıldırım Editör 13.09.2026 - 17:06 Yayınlanma 13.09.2026 - 17:06 Güncelleme —</t>
+          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV Kahramanmaraş’ta ticari faaliyet yürüten iki şirket hakkında mahkeme tarafından iflas kararı verildi. Kentte bir şirket ve üç kişiyle ilgili devam eden konkordato sürecinde ise kesin mühletin 2 ay süreyle uzatılmasına karar verildi. Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! 14.09.2026 - 10:27 Yayınlanma — Payl</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -6689,37 +6883,61 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://www.yeniadimgazetesi.com/boludaki-fabrika-yangininda-yaklasik-4-saat-geride-kaldi-1-yarali</t>
+          <t>https://www.edetv.com.tr/kahramanmarasta-iki-sirket-icin-iflas-karari-biri-icin-konkordatoda-muhlet-uzatildi</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Bolu</t>
+          <t>Kahramanmaraş</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr"/>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi:raw_legal</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr"/>
-      <c r="V42" s="2" t="inlineStr"/>
-      <c r="W42" s="2" t="inlineStr"/>
+          <t>ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi Kahramanmaraş Türkiye</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr"/>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="Z42" s="2" t="inlineStr"/>
       <c r="AA42" s="2" t="n">
-        <v>92.16</v>
+        <v>173.25</v>
       </c>
       <c r="AB42" s="2" t="n">
         <v>41</v>
@@ -6728,27 +6946,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:51:05</t>
+          <t>2026-09-14 09:53:53</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>mali suç</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -6758,28 +6976,32 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>para transferi</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
+          <t>Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. DOLAR 48,61 0,20% EURO 56,23 -0,16% ALTIN 6660,55 -0,02% BIST 100 13821,97 0,49% Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Edip Üçok 14 Eylül 2026 | 12:54 AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu. 17:30 "Türkiye'nin ilk Ay görevi kapsamında geliştirilen uzay aracının üretimi tamamlandı" 17:10 En çok tercih edilen 2. ülke: AB'li turistin rotası Türkiye 16:51 "Yapay zeka denetimine ABD ve Çin de katılmalı" 16:40 Karada, denizde ve insansız sistemlerde caydırıcı ateş gücü oluyor 16:29 Konak Rıhtımı'nın özelleştirme ihalesi iptal edildi 16:19 "Türkiye ekonomik gelişme hızıyla rol model olarak takip edilen bir ülke konumuna yükseldi" 16:06 TOKİ kiralık sosyal konut projesinde başvurular bugün başladı: Teslimat ne zaman, kiralar kaç liradan başlıyor? İşte örnek daireler... 15:35 AB güvenlik standartlarından taviz vermiyor: Yükümlülük yapay zeka şirketlerinde olacak 15:08 Kontrolsüz hızın getirdiği riskler: Yapay zekada ilerleme hızı nasıl dizginlenecek? 14:51 Sivil havacılık filosu büyüyor: Hava araçlarının sayısı 1772'ye ulaştı USD/TRY 30 dk 1 saat 1 gün USD/TRY EURO/TRY ALTIN/TRY BITCOIN/TRY Döviz Çevirici TRY USD EUR Hesapla Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
+          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. DOLAR 48,61 0,20% EURO 56,23 -0,16% ALTIN 6660,55 -0,02% BIST 100 13821,97 0,49% Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Edip Üçok 14 Eylül 2026 | 12:54 AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Şirket tarafından yapılan açıklamada, ABD ile Iran arasındaki çatışmaların jet yakıtı fiyatlarını ikiye katladığı ve havacılık sektörünü Kovid-19 pandemisinden bu yana en ağır krizle karşı karşıya bıraktığı belirtildi. 350 milyon Euro'luk yeni finansman paketi Yeniden yapılandırma sürecinde operasyonlarını kesintisiz sürdürmeyi hedefleyen airBaltic; Barclays, Morgan Stanley, Strategic Value Partners, Hayfin Capital Management ve Oaktree Capital Management’ın aralarında bulunduğu kredi veren gruptan 350 milyon Euro tutarında finansman taahhüdü sağladığını duyurdu. Çoğunluk hissesi Letonya hükümetine ait olan havayolu şirketi, mahkeme denetimindeki bu sürecin alacaklılara karşı koruma sağlama amacı taşıdığını ve tüm uçuşların planlandığı şekilde devam edeceğini vurguladı. Savaşın havacılıktaki ikinci kurbanı Nisan ayında Letonya hükümetinden 30 milyon avroluk devlet kredisi almasına rağmen artan yakıt masrafları nedeniyle nakit akışı daha da bozulan AirBaltic, ABD’li indirimli havayolu Spirit Airlines’ın Mayıs ayındaki çöküşünün ardından savaşla bağlantılı ikinci büyük havayolu şirketi oldu. Uzmanlar ve yatırımcılar, zayıf bilançoya sahip ve petrol fiyatlarındaki dalgalanmalara açık şirketlerin bu krizden en ağır darbeyi alacağı konusunda uyarılarda bulunuyordu. 17:30 "Türkiye'nin ilk Ay görevi kapsamında geliştirilen uzay aracının üretimi tamamlandı" 17:10 En çok tercih edilen 2. 15:35 AB güvenlik standartlarından taviz vermiyor: Yükümlülük yapay zeka şirketlerinde olacak 15:08 Kontrolsüz hızın getirdiği riskler: Yapay zekada ilerleme hızı nasıl dizginlenecek? 14:51 Sivil havacılık filosu büyüyor: Hava araçlarının sayısı 1772'ye ulaştı USD/TRY 30 dk 1 saat 1 gün USD/TRY EURO/TRY ALTIN/TRY BITCOIN/TRY Döviz Çevirici TRY USD EUR Hesapla Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11.</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>browser_failed</t>
+          <t>browser_full_article</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNVkNOMFRrcXVpWXRrTzRGc3UzVzRUX0FVYU9qRDB6RXZrUV94bl95QUF2Ykh3bGdia0FTMm1mdk1lbE9SVlEtTjlGRlp3SzY1VkpVLTZ0cHRFb1dQV2JNMnZwSndTTTQ1RWRTbjk5ZG1NeG9YWWxRTEZLRVgzQm5maENHSzhRUTVXTXVsamZCaFExZVpiT0E4TWpWTU56dzdwU2c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+          <t>https://www.ekonomist.com.tr/dunya/savasin-maliyetine-dayanamadi-dev-havayolu-sirketi-iflas-korumasi-basvurusunda-bulundu-78706</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
@@ -6805,7 +7027,7 @@
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" s="2" t="n">
-        <v>59.8</v>
+        <v>98.75</v>
       </c>
       <c r="AB43" s="2" t="n">
         <v>42</v>
@@ -6814,27 +7036,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:20:02</t>
+          <t>2026-09-14 07:12:00</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı İhlas Haber Ajansı</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -6844,18 +7066,22 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>işletme</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>... Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işlet Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işlet ASAYİŞ - 14 Eylül 2026 Pazartesi 09:20 Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu A A A Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işletmesinde saat 03.30 sıralarında meydana geldi. İşletmeden yükselen alev ve dumanları görenlerin ihbarı üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. 17 itfaiye aracıyla müdahale Yangına Bursa Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekiplerin yanı sıra farklı birimlerden de destek gönderildi. Söndürme çalışmalarında 17 itfaiye aracı ve 1 insansız hava aracı (dron) ekibi görev aldı. Ayrıca Park ve Bahçeler Şube Müdürlüğü/Tarım AŞ’ye ait 3 su tankeri, Yol Bakım ve Onarım Şube Müdürlüğü’ne ait 1 su tankeri ile Nilüfer Belediyesi’ne ait 1 kepçe çalışmalara destek verdi. Çok sayıda ekibin müdahale etmesiyle yangın çok geçmeden kontrol altına alındı. Soğutma çalışmaları devam ederken, olayla ilgili tahkikat başlatıldı. Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işletmesinde saat 03.30 sıralarında meydana geldi. İşletmeden yükselen alev ve dumanları görenlerin ihbarı üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. 17 itfaiye aracıyla müdahale Yangına Bursa Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekiplerin yanı sıra farklı birimlerden de destek gönderildi. Söndürme çalışmalarında 17 itfaiye aracı ve 1 insansız hava aracı (dron) ekibi görev aldı. Ayrıca Park ve Bahçeler Şube Müdürlüğü/Tarım AŞ’ye ait 3 su tankeri, Yol Bakım ve Onarım Şube Müdürlüğü’ne ait 1 su tankeri ile Nilüfer Belediyesi’ne ait 1 kepçe çalışmalara destek verdi. Çok sayıda ekibin müdahale etmesiyle yangın çok geçmeden kontrol altına alındı. Soğutma çalışmaları devam ederken, olayla ilgili tahkikat başlatıldı. Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işletmesinde saat 03.30 sıralarında meydana geldi. İşletmeden yükselen alev ve dumanları görenlerin ihbarı üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. 17 itfaiye aracıyla müdahale Yangına Bursa Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekiplerin yanı sıra farklı birimlerden de destek gönderildi. Söndürme çalışmalarında 17 itfaiye aracı ve 1 insansız hava aracı (dron) ekibi görev aldı. Ayrıca Park ve Bahçeler Şube Müdürlüğü/Tarım AŞ’ye ait 3 su tankeri, Yol Bakım ve Onarım Şube Müdürlüğü’ne ait 1 su tankeri ile Nilüfer Belediyesi’ne ait 1 kepçe çalışmalara destek verdi. Çok sayıda ekibin müdahale etmesiyle yangın çok geçmeden kontrol altına alındı. Soğutma çalışmaları devam ederken, olayla ilgili tahkikat başlatıldı.</t>
+          <t>www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. Doğrulama başarılı. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Doğrulama başarılı. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu İhlas Haber Ajansı İhlas Haber Ajansı Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işlet Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işlet ASAYİŞ - 14 Eylül 2026 Pazartesi 09:20 Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu A A A Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü. Yangın, Nilüfer ilçesinde bulunan bir kömür işletmesinde saat 03.30 sıralarında meydana geldi. İşletmeden yükselen alev ve dumanları görenlerin ihbarı üzerine olay yerine çok sayıda itfaiye ekibi sevk edildi. 17 itfaiye aracıyla müdahale Yangına Bursa Büyükşehir Belediyesi İtfaiye Dairesi Başkanlığı’na bağlı ekiplerin yanı sıra farklı birimlerden de destek gönderildi. Söndürme çalışmalarında 17 itfaiye aracı ve 1 insansız hava aracı (dron) ekibi görev aldı. Ayrıca Park ve Bahçeler Şube Müdürlüğü/Tarım AŞ’ye ait 3 su tankeri, Yol Bakım ve Onarım Şube Müdürlüğü’ne ait 1 su tankeri ile Nilüfer Belediyesi’ne ait 1 kepçe çalışmalara destek verdi. Çok sayıda ekibin müdahale etmesiyle yangın çok geçmeden kontrol altına alındı. Soğutma çalışmaları devam ederken, olayla ilgili tahkikat başlatıldı. Kömür işletmesinde gece yarısı yangın paniği: Ekipler seferber oldu Bursa’da bir kömür işletmesinde gece saatlerinde çıkan yangın çok sayıda ekibin müdahalesiyle söndürüldü.</t>
+          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Bu web sitesi, kötü niyetli botlara karşı korunmak için bir güvenlik hizmeti kullanıyor. Web sitesi bir bot olmadığınızı doğrularken bu sayfa görüntülenir. www.kocaelibarisgazetesi.com adresinin yanıt vermesi bekleniyor www.kocaelibarisgazetesi.com Güvenlik doğrulaması yapılıyor Doğrulama başarılı.</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -6865,65 +7091,41 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>https://www.iha.com.tr/bursa-haberleri/komur-isletmesinde-gece-yarisi-yangin-panigi-ekipler-seferber-oldu-485164420</t>
+          <t>https://www.kocaelibarisgazetesi.com/amp/gundem/gebzede-iflas-eden-sirket-icin-alacaklilara-cagri-1-ay-sure-verildi-h160416</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Kocaeli</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Nilüfer</t>
+          <t>Gebze</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
       <c r="Q44" s="2" t="inlineStr"/>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>Tarım AŞ</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>Tarım AŞ:63:body | Tarım AŞ:raw_legal</t>
-        </is>
-      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>Tarım AŞ Nilüfer Bursa Türkiye</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>TARIM PEYZAJ A.Ş. Bursa Tarım Hayvancılık Peyzaj Çevre İnş. San. Tic. A.Ş</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>TARIM PEYZAJ A.Ş. Bursa Tarım Hayvancılık Peyzaj Çevre İnş. San. Tic. A.Ş</t>
-        </is>
-      </c>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
       <c r="Z44" s="2" t="inlineStr"/>
       <c r="AA44" s="2" t="n">
-        <v>206.85</v>
+        <v>107.49</v>
       </c>
       <c r="AB44" s="2" t="n">
         <v>43</v>
@@ -6932,27 +7134,27 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:20:28</t>
+          <t>2026-09-14 15:56:00</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>yangın</t>
+          <t>tasfiye</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı aksiyon.com.tr</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku yildirimgazetesi.com</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6962,56 +7164,44 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>tekstil, turizm, şirket</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>depo</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Olayın gelişimi: Mardin'in Kızıltepe ilçesinde, Atatürk Mahallesi yakınlarında hurda araçların bulunduğu bir alanda yangın çıktı. Yangının henüz belirlenemeyen nedenle başladığı bildirildi. Bölgedeki vatandaşların durumu fark ederek ihbarda bulunmasının ardından yetkililer alarma geçti. Müdahale ve söndürme çalışmaları: İhbar üzerine bölgeye sevk edilen itfaiye ekipleri kısa sürede olay yerine ulaşarak müdahaleye başladı. Ekiplerin çalışmasıyla yangın kısa sürede kontrol altına alınarak söndürüldü. Çevrede ek güvenlik önlemleri alındı ve yangının yayılmasının önüne geçildi. Hasar ve soruşturma: Yangında hurda araçlarda maddi hasar meydana geldi. Olayla ilgili olarak yetkililer tarafından inceleme başlatıldı; yangının çıkış nedeni ile hasarın boyutuna ilişkin tespit çalışmalarının sürdüğü bildirildi. MARDİN'İN KIZILTEPE İLÇESİNDE HURDA ARAÇLARIN BULUNDUĞU ALANDA ÇIKAN YANGIN İTFAİYE EKİPLERİNİN MÜDAHALESİYLE SÖNDÜRÜLDÜ. 1 Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı 2 Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada 3 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 4 Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı 5 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 6 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 7 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Mardin'de hurda araç deposunda yangın kontrol altına alındı Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Mardin'in Kızıltepe ilçesinde, Atatürk Mahallesi yakınlarında hurda araçların bulunduğu bir alanda yangın çıktı. Yangının henüz belirlenemeyen nedenle başladığı bildirildi. Bölgedeki vatandaşların durumu fark ederek ihbarda bulunmasının ardından yetkililer alarma geçti. İhbar üzerine bölgeye sevk edilen itfaiye ekipleri kısa sürede olay yerine ulaşarak müdahaleye başladı. Ekiplerin çalışmasıyla yangın kısa sürede kontrol altına alınarak söndürüldü. Çevrede ek güvenlik önlemleri alındı ve yangının yayılmasının önüne geçildi. Yangında hurda araçlarda maddi hasar meydana geldi. Olayla ilgili olarak yetkililer tarafından inceleme başlatıldı; yangının çıkış nedeni ile hasarın boyutuna ilişkin tespit çalışmalarının sürdüğü bildirildi. MARDİN'İN KIZILTEPE İLÇESİNDE HURDA ARAÇLARIN BULUNDUĞU ALANDA ÇIKAN YANGIN İTFAİYE EKİPLERİNİN MÜDAHALESİYLE SÖNDÜRÜLDÜ. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. aksiyon.com.tr Gündem'deyim ama spesifik olarak eğitim ve sağlık politikalarındaki güncel gelişmelere odaklanıyorum. Öğrenmeye açık, meraklı ve enerjik bir yapım var. Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. bölüm neden yok? TRT 1, 2 Ocak yayın planını değiştirdi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku yildirimgazetesi.com</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Mardin'de hurda araç deposunda yangın kontrol altına alındı Mardin'de hurda araç deposunda yangın kontrol altına alındı aksiyon.com.tr Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Olayın gelişimi: Mardin'in Kızıltepe ilçesinde, Atatürk Mahallesi yakınlarında hurda araçların bulunduğu bir alanda yangın çıktı. Yangının henüz belirlenemeyen nedenle başladığı bildirildi. Bölgedeki vatandaşların durumu fark ederek ihbarda bulunmasının ardından yetkililer alarma geçti. Müdahale ve söndürme çalışmaları: İhbar üzerine bölgeye sevk edilen itfaiye ekipleri kısa sürede olay yerine ulaşarak müdahaleye başladı. Ekiplerin çalışmasıyla yangın kısa sürede kontrol altına alınarak söndürüldü. Çevrede ek güvenlik önlemleri alındı ve yangının yayılmasının önüne geçildi. Hasar ve soruşturma: Yangında hurda araçlarda maddi hasar meydana geldi. Olayla ilgili olarak yetkililer tarafından inceleme başlatıldı; yangının çıkış nedeni ile hasarın boyutuna ilişkin tespit çalışmalarının sürdüğü bildirildi. MARDİN'İN KIZILTEPE İLÇESİNDE HURDA ARAÇLARIN BULUNDUĞU ALANDA ÇIKAN YANGIN İTFAİYE EKİPLERİNİN MÜDAHALESİYLE SÖNDÜRÜLDÜ. 1 Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı 2 Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada 3 Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi Mudurnu'da soda taşıyan tırın devrilmesi yolu kilitledi 4 Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı Zonguldak'ta minibüsün altında kalan kadın vatandaşların müdahalesiyle kurtarıldı 5 Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı Iğdır'da Doğubayazıt kaynaklı sevkiyat engellendi: iki şüpheli tutuklandı 6 Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi Köşk'te yol uygulamasında faturasız 630 bin makaron ve 87,5 kg tütün ele geçirildi 7 Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Sopa görüntülere yansıdı: Adana'da birliktelik yaşadığı kadını darp eden kişi gözaltına alındı Mardin'de hurda araç deposunda yangın kontrol altına alındı Kızıltepe'de hurda araç deposunda çıkan yangın, itfaiye ekiplerinin erken müdahalesiyle söndürüldü; maddi hasar tespit edildi, inceleme başlatıldı. Mardin'in Kızıltepe ilçesinde, Atatürk Mahallesi yakınlarında hurda araçların bulunduğu bir alanda yangın çıktı. İhbar üzerine bölgeye sevk edilen itfaiye ekipleri kısa sürede olay yerine ulaşarak müdahaleye başladı. Yangında hurda araçlarda maddi hasar meydana geldi. Ben Meryem Özdemir, 24 yaşındayım, Bursa'dan çalışıyorum. Market poşeti fiyatı 2026'da 1 TL oldu — 1 Ocak 2026'da yürürlüğe giren tarife Taşacak Bu Deniz 13. TRT 1, 2 Ocak yayın planını değiştirdi 2026 Zorunlu Trafik Sigortası: SEDDK Teminat Limitlerini ve Çoklu Araç Tarifesini Yeniden Belirledi 2026 Ehliyet, Pasaport ve Kimlik Kartı Harçları Resmileşti: Yeni Tarifeler ve Geçerlilik Tarihi 1 Ocak'ta İstanbul'da Toplu Taşıma Ücretsiz: İBB Metro, Metrobüs ve Otobüs Ek Seferlerini Açıkladı Emekliye 60.000 TL'ye Kadar Paketler: Bankaların Güncel Promosyon ve Ek Avantajları 29 Aralık: Van, Zonguldak, Karabük, Bolu ve Düzce'de okullar tatil — Üniversiteler ne durumda? 29 Aralık İstanbul'da Okullar Tatil mi? Valilik ve Meteoroloji Açıklamaları İstanbul'da simit fiyatları fiilen yükseldi: Resmi tarife 15 TL, satışlar 20-25 TL'ye çıktı Resmi Gazete'de yayımlandı: 66 meslekte Mesleki Yeterlilik Belgesi zorunluluğu 26-27 Aralık Hava Durumu: İstanbul, Ankara ve Yalova için Kar Tahminleri 2026 Sosyal Destek Zamları: Evde Bakım, 65 Yaş ve Engelli Maaşlarında Yeni Tahminler</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku yildirimgazetesi.com Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku yildirimgazetesi.com</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>https://www.aksiyon.com.tr/mardin-de-hurda-arac-deposunda-yangin-kontrol-altina-alindi-354264</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Adana | Bilecik | Bursa | Düzce | Iğdır</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>Köşk | Mudurnu | Kızıltepe</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>Atatürk Mahallesi</t>
-        </is>
-      </c>
+          <t>https://www.yildirimgazetesi.com/yatirimlariyla-dikkat-cekiyordu-tekstil-ve-turizm-sirketine-iflas-soku-1</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr"/>
@@ -7025,7 +7215,7 @@
       <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
       <c r="AA45" s="2" t="n">
-        <v>121</v>
+        <v>75.42</v>
       </c>
       <c r="AB45" s="2" t="n">
         <v>44</v>
@@ -7034,27 +7224,27 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 22:01:00</t>
+          <t>2026-09-14 10:10:00</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>bankaya soruşturma</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu</t>
+          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber</t>
+          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti Ekonomim</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -7064,39 +7254,35 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>tekstil, şirket</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor. İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor. İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor.</t>
+          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti Ekonomim</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor.</t>
+          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti 2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti Ekonomim 2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti Ekonomim</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>https://www.toplumsal.com.tr/haber/izmir-deki-banka-subesinde-rehin-alan-supheli-teslim-oldu_25400/</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPdll1RkxqNURhd3g0c2xqZGdKbDVqTXZNRG40SUdWcVd4VW85Z200VzlTSkg0Yk5OaVRTcVlkZExaNlNkLTJ1Wm83MDVNajR4RmQxQjgzOFg1U01CY3p5SUk2V3JFX0laTndlbVdQTUxnZmlUS3dSLW5obWFqMUVzU3JuY1AxTVUwZUZDRWxvMFJvLVJsN1pkRjVUVkxWSTBBYUNsQmtrVHNNTGtNeGxKY2hn0gG3AUFVX3lxTE1Hd1VpTmQ3U2RyMkhkbmxveW5RaWRVUi1zVklrV3Q2TElJSHF1b1VfV3BOYUhUcklIWmtHcG1Tblh3akVkYXMwSS1iX3VhNHRqa2hxWWtBcEFyQklXVnVJS0JOcHNLZHBCcllWa3l0Ty1QM0JUVDZEVm56b2JBX3VRWWI3SS1CNTl4dWlsMDJ4YV81RjRHVWpyd2MzeDJNZEJHRWFBeUJVc0Z1MzJmWWFYT05RbFBXVQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
@@ -7105,7 +7291,7 @@
       <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr"/>
@@ -7119,7 +7305,7 @@
       <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr"/>
       <c r="AA46" s="2" t="n">
-        <v>60.14</v>
+        <v>58.98</v>
       </c>
       <c r="AB46" s="2" t="n">
         <v>45</v>
@@ -7128,27 +7314,27 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:43:00</t>
+          <t>2026-09-14 08:07:27</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>banka hesapları bloke</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak?</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -7158,18 +7344,22 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>el konuldu</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
+          <t>şirket</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>şirket / firma</t>
+        </is>
+      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Güncel İran'da çok sayıda kişinin mal varlıklarına el konuldu İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Mehmet TÜRK 14.09.2026 - 11:43 Okunma Süresi: 1 Dk Türkşeker 182 işçi alımı başvuruları başladı: İŞKUR başvuru şartları neler, son başvuru tarihi ne zaman? İçeriği Görüntüle İran Yargı Erki, el konulan mülkler, bloke edilen banka hesaplarına dair raporunu açıkladı. Mizan Haber Ajansı’nda yer alan habere göre, aralarında gazetecilerin, aktivistlerin, akademisyenlerin olduğu yüzlerce kişinin mal varlıklarına ve banka hesaplarına el konul konuldu. El konulan mal varlıklarının 143’ü Tahran’da bulunuyor. Habere göre, 182 kişinin banka hesapları bloke edildi, 2 binden fazla kişinin ise banka hesapları için incelemeler devam ediyor. Haberde, el konulan varlıkların İran halkı için kullanılacağı iddia edildi. Kaynak: MA Editörün Seçtiği Diyarbakır’da okullar açıldı, yol çalışması trafiği vurdu! Editörün Seçtiği Daha 17 17. bölüm fragmanı yayınlandı mı, ne zaman yayınlanacak? Aras ve Teoman arasında yeni dönem! Editörün Seçtiği Dayik Qurban, Gift Orban Editör Hakkında Mehmet TÜRK Bunlar da</t>
+          <t>Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Yeni müşterilere özel avantajlı ihtiyaç kredisi! Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. TÜM UÇUŞLARIN PLANLANDIĞI ŞEKİLDE KESİNTİSİZ SÜRECEĞİ BELİRTİLDİ AirBaltic, ABD'de iflas koruması başvurusunda bulundu! AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Açıklamada, yasal sürecin yolcuları ve günlük ticari faaliyetleri etkilemeyeceği, tüm uçuşların planlandığı şekilde kesintisiz süreceği, bilet ile rezervasyonların geçerliliğini koruyacağı vurgulandı. Bu arada, iflas koruması başvurusu kararı, şirketin 380 milyon avro değerindeki tahvillerin sahiplerinin alternatif bir ara finansman teklifini oylayacağ kritik toplantıdan bir gün önce geldi. Jet yakıtı fiyatlarındaki artış öncesinde de mali zorluk yaşayan hava yolunun, 2026-2027 dönemini finanse etmek için nakit girişine ihtiyaç duyduğu biliniyordu. Sürecin, Letonya 'da yaklaşan parlamento seçimlerinin hemen öncesine denk gelmesi de dikkati çekti. Hisselerinin yüzde 88,4'ü Letonya devletine ait olan AirBaltic'in yüzde 10 hissesi ise geçen yıl Alman hava yolu firması Lufthansa AG tarafından satın alınmıştı. Kaynak: AA | Bu içerik Hande Dağ tarafından yayına alınmıştır</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Güncel İran'da çok sayıda kişinin mal varlıklarına el konuldu İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi.</t>
+          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet Letonya'nın ulusal hava yolu şirketi AirBaltic, borç yükümlülüklerini yeniden yapılandırmak amacıyla ABD'de iflas koruması başvurusunda bulundu. Yeni müşterilere özel avantajlı ihtiyaç kredisi! Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? TÜM UÇUŞLARIN PLANLANDIĞI ŞEKİLDE KESİNTİSİZ SÜRECEĞİ BELİRTİLDİ AirBaltic, ABD'de iflas koruması başvurusunda bulundu! AirBaltic'ten yapılan açıklamada, borçların yeniden yapılandırılması için ABD İflas Kanunu'nun 11. Bölümü (Chapter 11) kapsamında alacaklı koruması talebiyle resmi başvurunun yapıldığı belirtilerek, şirketin bu süreçte operasyonlarını sürdürebilmek için 350 milyon avroluk "süreç içi borçlanma" finansman taahhüdü sağladığı bildirildi. Açıklamada, yasal sürecin yolcuları ve günlük ticari faaliyetleri etkilemeyeceği, tüm uçuşların planlandığı şekilde kesintisiz süreceği, bilet ile rezervasyonların geçerliliğini koruyacağı vurgulandı. Bu arada, iflas koruması başvurusu kararı, şirketin 380 milyon avro değerindeki tahvillerin sahiplerinin alternatif bir ara finansman teklifini oylayacağ kritik toplantıdan bir gün önce geldi. Jet yakıtı fiyatlarındaki artış öncesinde de mali zorluk yaşayan hava yolunun, 2026-2027 dönemini finanse etmek için nakit girişine ihtiyaç duyduğu biliniyordu. Sürecin, Letonya 'da yaklaşan parlamento seçimlerinin hemen öncesine denk gelmesi de dikkati çekti. Hisselerinin yüzde 88,4'ü Letonya devletine ait olan AirBaltic'in yüzde 10 hissesi ise geçen yıl Alman hava yolu firması Lufthansa AG tarafından satın alınmıştı.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -7179,7 +7369,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>https://www.guneydoguekspres.com/iranda-cok-sayida-kisinin-mal-varliklarina-el-konuldu</t>
+          <t>https://www.mynet.com/amp/unlu-hava-yolu-sirketinden-iflas-koruma-basvurusu-biletler-ne-olacak-finans-574454</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr"/>
@@ -7205,7 +7395,7 @@
       <c r="Y47" s="2" t="inlineStr"/>
       <c r="Z47" s="2" t="inlineStr"/>
       <c r="AA47" s="2" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="AB47" s="2" t="n">
         <v>46</v>
@@ -7214,27 +7404,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 10:52:00</t>
+          <t>2026-09-14 07:23:36</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>banka hesaplarına bloke</t>
+          <t>iflas</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama!</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı...</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -7244,22 +7434,22 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>banka</t>
+          <t>tekstil, şirket</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>finansal kuruluş</t>
+          <t>şirket / firma</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Yükleniyor... Emekli Maaşlarına Ek Zam: Seyyanen Zam İçin Gözler Kritik Kararda! İçeriği Görüntüle Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Vatandaşların hukuki süreçlerde en sık karşılaştığı ve kafa karışıklığı yaşadığı konuların başında, maaşın işveren tarafından bankaya yatırılmasından sonraki hukuki statüsü gelmektedir. Maaş kesintisi doğrudan işyeri üzerinden icra dairesi kanalıyla yapılırken, banka hesaplarına uygulanan e-haciz işlemleri Doğrudan banka blokajı olarak gerçekleşmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Bu durum, banka hesabında bloke bulunan vatandaşların işlem türünü doğru tespit etmesini zorunlu kılmaktadır. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. Uygulanan işlemin bir maaş haczi mi yoksa banka mevduat haczi mi olduğunun icra dosyasından doğrulanması gerekmektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Akseki Aksu Alanya Demre Döşemealtı Elmalı Finike Gazipaşa Gündoğmuş İbradı Kaş Kemer Kepez Konyaaltı Korkuteli Kumluca Manavgat Muratpaşa Serik 30 ° C Web sitemizden ayrılıyorsunuz Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor. Sayfada Kal Devam Et Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. Vatandaşların hukuki süreçlerde en sık karşılaştığı ve kafa karışıklığı yaşadığı konuların başında, maaşın işveren tarafından bankaya yatırılmasından sonraki hukuki statüsü gelmektedir. Maaş kesintisi doğrudan işyeri üzerinden icra dairesi kanalıyla yapılırken, banka hesaplarına uygulanan e-haciz işlemleri Doğrudan banka blokajı olarak gerçekleşmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Bu durum, banka hesabında bloke bulunan vatandaşların işlem türünü doğru tespit etmesini zorunlu kılmaktadır. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. Uygulanan işlemin bir maaş haczi mi yoksa banka mevduat haczi mi olduğunun icra dosyasından doğrulanması gerekmektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Antalya Hakkında'nın sponsor olduğu yayıncılar Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor.</t>
+          <t>Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil sektöründe faaliyet gösteren bir şirketin devam eden iflas tasfiyesinde yeni bir aşamaya geçildi. Bursa İflas Dairesi’nin 2025/10 İflas sayılı dosyası kapsamında, Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında basit tasfiyede ek sıra cetveli ilanı yayımlandı. ŞİRKETİN İFLASINA 2025 YILINDA KARAR VERİLMİŞTİ İlanda yer alan bilgilere göre Bursa 1. Asliye Ticaret Mahkemesi, 14 Ağustos 2025 tarihli ve 2025/490 Esas sayılı kararıyla şirketin iflasına hükmetti. Şirketin iflası aynı gün saat 14.57 itibarıyla açılırken, tasfiye işlemlerinin basit usulde gerçekleştirilmesine karar verildi. KESTEL'DEKİ TEKSTİL ŞİRKETİ İflas ilanında şirketin adresi de ayrıntılı şekilde yer aldı. Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi'nin adresi Ahmet Vefik Paşa OSB Mahallesi, Yeniyol Caddesi, MNG Tekstil Ltd. Sitesi, MNG Tekstil No:10, Kestel/Bursa olarak belirtildi. ALACAK KAYIT TALEPLERİ İNCELENDİ Bursa İflas Dairesi tarafından yürütülen tasfiye kapsamında iflas dosyasına yapılan alacak kayıt taleplerinin incelendiği ve alacaklar hakkında karar verildiği bildirildi. İcra ve İflas Kanunu hükümlerine göre hazırlanan ek sıra cetveli, ilgililerin incelemesine sunulmak üzere iflas dosyasında hazır tutuluyor. Sıra cetveli, iflas tasfiyesinde alacaklıların taleplerinin hangi kapsamda değerlendirildiği ve alacakların sıralamasına ilişkin süreç açısından önem taşıyor. ALACAKLILAR DİKKAT: 15 VE 7 GÜNLÜK İTİRAZ SÜRESİ İlanda alacaklıların itiraz haklarına ilişkin kritik süreler de açıklandı. Buna göre alacağın esasına ve miktarına yönelik itirazların 15 gün içerisinde, Bursa İflas Dairesi'nin bulunduğu yerdeki Ticaret Mahkemesi'nde dava konusu edilmesi gerekiyor. Sıraya ilişkin itirazlar için ise 7 günlük süre bulunuyor. Bu kapsamdaki itirazların şikâyet yoluyla İcra Mahkemesi'ne taşınabileceği belirtildi. Söz konusu süreler ilan tarihine bağlı hukuki süreler olduğundan, ilgililerin resmi ilandaki tarih ve usulleri esas alması önem taşıyor.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! antalyahakkinda.com Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Emekli Maaşlarına Ek Zam: Seyyanen Zam İçin Gözler Kritik Kararda! İçeriği Görüntüle Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. İcra ve İflas Kanunu kapsamında belirlenen esaslara göre bir çalışanın aylık kazancının tamamına el konulması hukuken mümkün değildir. Borçlu bireylerin mağduriyet yaşamaması adına yasalarla koruma altına alınan bu süreçte, genel borçlar için uygulanacak azami kesinti oranı maaşın %25,00 kadarı olarak belirlenmiştir. Bu oran çalışanın rızası olmadıkça artırılamaz ve işverenler tarafından doğrudan maaş bordrosuna yansıtılarak icra dairesine aktarılır. Bununla birlikte borcun niteliği kesinti oranları ve öncelik sıralaması üzerinde belirleyici bir rol oynamaktadır. Örneğin aile hukukundan doğan nafaka alacakları, genel kredi borçları veya bireysel ihtiyaç kredilerinden farklı bir hukuki statüye sahiptir. Mahkeme tarafından hükmedilen cari nafaka borçlarında %25,00 sınırı uygulanmaz ve hakim kararıyla belirlenen aylık tutarın tamamı maaştan kesilir. Çalışanların kendilerine tebliğ edilen icra ödeme emirlerini dikkatle incelemesi ve borç türüne göre uygulanan kesintilerin mevzuata uygun olup olmadığını kontrol etmesi gerekmektedir. İşveren tarafından %25,00 oranı kesildikten sonra çalışanın hesabına yatırılan net tutar, artık hukuki olarak maaş niteliğinden çıkıp genel mevduat bakiyesi olarak değerlendirilebilmektedir. Banka hesabına konulan blokelerin maaş hesabından kaynaklandığını belirten borçluların, sadece banka şubesine şifahi beyanda bulunmaları işlemi kaldırmaya yetmemektedir. İşveren tarafından kesinti yapıldıktan sonra hesaba yatan kalan paranın tamamına banka tarafından e-haciz uygulanması durumunda, borçlunun icra müdürlüğüne başvurarak mesken ve geçim şartlarına aykırılık gerekçesiyle şikayet hakkını kullanması icap etmektedir. Aksi takdirde hesaptaki bakiyenin tamamı borç karşılığında icra dosyasına aktarılabilmektedir. Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. Hakkında icra takibi başlatılan bir çalışanın maaşının tamamına el konulması yasal olarak imkansızdır. Ancak borçlu bireyin icra dairesinde bilerek veya bilmeyerek maaşının tamamının kesilmesine muvafakat etmesi halinde bu koruma zırhı ortadan kalkmaktadır. Bu nedenle icra evraklarına imza atarken verilen taahhütlerin içeriğine ve yazılan maddelere son derece dikkat edilmesi hayati önem taşımaktadır. İcra tebligatının çalışana ulaşmasıyla başlayan yasal süreler, itiraz ve şikayet haklarının kullanımı açısından belirleyicidir. Kendisine ulaşan ödeme emrini teslim alan vatandaşların 7 gün içinde ilgili icra dairesine başvurarak borca veya ferilerine itiraz etme hakkı bulunmaktadır. İtiraz edilmeyen takiplerde borç kesinleşmekte ve işyerine maaş haczi müzekkeresi gönderilmektedir. Sürecin her aşamasında hak kaybı yaşanmaması, haksız kesintilerin önüne geçilmesi ve e-haciz blokelerinin kaldırılması adına uzman bir hukukçudan profesyonel destek alınması önerilmektedir. İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Müzekkereyi tebellüğ eden işveren veya insan kaynakları birimi, 7 gün içerisinde icra dairesine cevap vermek ve çalışanın maaşından yapılacak kesinti oranını bildirmek zorundadır. Şirketlerin icra dairesinden gelen bu resmi yazıları cevapsız bırakması veya kesinti yapmayı reddetmesi halinde, borç tutarı doğrudan işverenin şahsi veya kurumsal sorumluluğuna girmektedir. İşverenler, çalışanın maaşından her ay düzenli olarak %25,00 oranındaki kesintiyi yapmak ve belirlenen icra dairesi hesabına yatırmakla mükelleftir. Birden fazla icra dosyası bulunan çalışanlar için sıraya koyma ilkesi geçerlidir ve ilk gelen icra dosyası kapanmadan ikinci icra dosyası için kesinti yapılamamaktadır. Ancak nafaka alacakları bu kuralın istisnasını oluşturmakta ve her zaman ilk sırada yer almaktadır. İşverenlerin kanuna uygun hareket etmesi, hem şirket içi hukuki riskleri ortadan kaldırmakta hem de çalışanın yasal haklarının korunmasına zemin hazırlamaktadır. Akseki Aksu Alanya Demre Döşemealtı Elmalı Finike Gazipaşa Gündoğmuş İbradı Kaş Kemer Kepez Konyaaltı Korkuteli Kumluca Manavgat Muratpaşa Serik 30 ° C Web sitemizden ayrılıyorsunuz Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor. Sayfada Kal Devam Et Maaşınız Hesaba Yatınca Bu Para Kesilecek: Bankalardan Kritik Uygulama! Banka Hesaplarındaki Haciz İşlemleri Ve Maaş Hesabı Ayrımı Borçlu Çalışanların İcra Sürecinde Haklarını Koruma Yolları İşverenlerin Maaş Haczi Müzekkerelerine Karşı Yasal Sorumlulukları Çalışma hayatında borç ilişkileri nedeniyle gündeme gelen maaş haczi uygulamalarında yasal sınırlar ve borçluların hakları büyük önem taşımaktadır. Kredi kartı ekstreleri, tüketici kredileri veya şahsi borçlar nedeniyle icra takibi ile karşı karşıya kalan çalışanların hak kaybına uğramamak adına atması gereken kritik adımlar bulunmaktadır. İcra daireleri tarafından işyerlerine gönderilen maaş haczi yazıları, işverenler açısından yasal bir zorunluluk teşkil etmekte ve belirli yükümlülükler getirmektedir. Antalya Hakkında'nın sponsor olduğu yayıncılar Bu bağlantı sizi https://www.antalyahakkinda.com dışındaki bir siteye yönlendiriyor.</t>
+          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet Bursa’nın Kestel ilçesinde faaliyet gösteren Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi’nin iflas sürecinde ek sıra cetveli ilan edildi. Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa’da tekstil sektöründe faaliyet gösteren bir şirketin devam eden iflas tasfiyesinde yeni bir aşamaya geçildi. Bursa İflas Dairesi’nin 2025/10 İflas sayılı dosyası kapsamında, Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi hakkında basit tasfiyede ek sıra cetveli ilanı yayımlandı. ŞİRKETİN İFLASINA 2025 YILINDA KARAR VERİLMİŞTİ İlanda yer alan bilgilere göre Bursa 1. Asliye Ticaret Mahkemesi, 14 Ağustos 2025 tarihli ve 2025/490 Esas sayılı kararıyla şirketin iflasına hükmetti. Şirketin iflası aynı gün saat 14.57 itibarıyla açılırken, tasfiye işlemlerinin basit usulde gerçekleştirilmesine karar verildi. KESTEL'DEKİ TEKSTİL ŞİRKETİ İflas ilanında şirketin adresi de ayrıntılı şekilde yer aldı. Mihenk Boya Tekstil Kumaş Sanayi ve Dış Ticaret Limited Şirketi'nin adresi Ahmet Vefik Paşa OSB Mahallesi, Yeniyol Caddesi, MNG Tekstil Ltd. Sitesi, MNG Tekstil No:10, Kestel/Bursa olarak belirtildi. ALACAK KAYIT TALEPLERİ İNCELENDİ Bursa İflas Dairesi tarafından yürütülen tasfiye kapsamında iflas dosyasına yapılan alacak kayıt taleplerinin incelendiği ve alacaklar hakkında karar verildiği bildirildi. İcra ve İflas Kanunu hükümlerine göre hazırlanan ek sıra cetveli, ilgililerin incelemesine sunulmak üzere iflas dosyasında hazır tutuluyor. Sıra cetveli, iflas tasfiyesinde alacaklıların taleplerinin hangi kapsamda değerlendirildiği ve alacakların sıralamasına ilişkin süreç açısından önem taşıyor. ALACAKLILAR DİKKAT: 15 VE 7 GÜNLÜK İTİRAZ SÜRESİ İlanda alacaklıların itiraz haklarına ilişkin kritik süreler de açıklandı. Buna göre alacağın esasına ve miktarına yönelik itirazların 15 gün içerisinde, Bursa İflas Dairesi'nin bulunduğu yerdeki Ticaret Mahkemesi'nde dava konusu edilmesi gerekiyor. Sıraya ilişkin itirazlar için ise 7 günlük süre bulunuyor. Bu kapsamdaki itirazların şikâyet yoluyla İcra Mahkemesi'ne taşınabileceği belirtildi. Söz konusu süreler ilan tarihine bağlı hukuki süreler olduğundan, ilgililerin resmi ilandaki tarih ve usulleri esas alması önem taşıyor.</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -7269,19 +7459,35 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>https://www.antalyahakkinda.com/maasiniz-hesaba-yatinca-bu-para-kesilecek-bankalardan-kritik-uygulama</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr"/>
+          <t>https://www.bursahakimiyet.com.tr/bursa/bursa-da-tekstil-sirketinin-iflasinda-yeni-gelisme-alacaklilar-icin-sure-basladi-1709285</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Kestel</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Ahmet Vefik Paşa OSB Mahallesi | adresi Ahmet Vefik Paşa OSB</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Yeniyol Caddesi</t>
+        </is>
+      </c>
       <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+          <t>firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr"/>
@@ -7295,7 +7501,7 @@
       <c r="Y48" s="2" t="inlineStr"/>
       <c r="Z48" s="2" t="inlineStr"/>
       <c r="AA48" s="2" t="n">
-        <v>79.25</v>
+        <v>160</v>
       </c>
       <c r="AB48" s="2" t="n">
         <v>47</v>
@@ -7304,27 +7510,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 13:23:00</t>
+          <t>2026-09-14 07:51:05</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>banka soruşturma</t>
+          <t>mali suç</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası Samsun Gazetesi</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -7334,44 +7540,32 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>şirket</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>şirket / firma</t>
-        </is>
-      </c>
+          <t>para transferi</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Pusula Finans Holding ve Katılımevim'in de gündemde olduğu soruşturmada bazı isimler hakkında yakalama ve yurt dışı yasağı iddiaları gündeme geldi. Pusula Finans Holding ve Katılımevim'in de gündemde olduğu soruşturmada bazı isimler hakkında yakalama ve yurt dışı yasağı iddiaları gündeme geldi. Pusula Finans Holding ve Katılımevim'in de gündemde olduğu soruşturmada bazı isimler hakkında yakalama ve yurt dışı yasağı iddiaları gündeme geldi. Dev finans şirketinde soruşturma: Yakalama kararı iddiası Pusula Finans Holding ve Katılımevim'in de adının geçtiği soruşturmayla ilgili yeni iddialar gündeme geldi. Pusula Portföy Yönetim Kurulu Başkanı Muhammet Yarız'ın yurt dışına çıktığı ve hakkında yakalama kararı verildiği öne sürülürken, bazı isimler hakkında da yurt dışına çıkış yasağı uygulandığı iddia edildi. Yunus Emre Purç Editör 13.09.2026 - 16:23 Yayınlanma 0 Paylaşım 2 Dk Okunma Süresi Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Yükleniyor... Finans sektöründe Pusula Finans Holding ve bünyesindeki şirketleri ilgilendiren gelişmeler gündemdeki yerini koruyor. Pusula Finans Holding'in, portföyünde Katılımevim'in çoğunluk hisselerini bulundurduğu ve Tera Grubu'na devri konusunda tarafların anlaşmaya vardığı açıklanmıştı. Devir işleminin tamamlanabilmesi için Sermaye Piyasası Kurulu (SPK), Bankacılık Düzenleme ve Denetleme Kurumu (BDDK) ve Rekabet Kurulu başta olmak üzere gerekli izinlerin alınması beklenirken, soruşturmayla ilgili yeni iddialar ortaya atıldı. MUHAMMET YARIZ'IN YURT DIŞINA ÇIKTIĞI ÖNE SÜRÜLDÜ Soruşturma kapsamında adı geçen Pusula Portföy Yönetim Kurulu Başkanı Muhammet Yarız'ın yurt dışına çıktığı iddia edildi. Yarız'ın cep telefonunu ofisinde bırakarak Marmaris'ten tekneyle yurt dışına gittiği ve Yunanistan'da bulunduğu öne sürüldü. Gazeteci İsmail Saymaz da konuya ilişkin benzer iddiaları gündeme getirdi. Faizsiz 100 bin TL kredi fırsatı: Bankalar tek tek açıkladı İçeriği Görüntüle YARIZ HAKKINDA YAKALAMA KARARI İDDİASI Soruşturmayla ilgili ortaya atılan bir diğer iddia ise Muhammet Yarız hakkında yakalama kararı çıkarıldığı yönünde oldu. İstanbul Cumhuriyet Başsavcılığı tarafından Yarız hakkında yakalama kararı verildiği, ayrıca mal varlığı ve banka hesaplarına tedbir konulduğu öne sürüldü. SERDAR TURHAN İÇİN DE YURT DIŞI YASAĞI İDDİASI Soruşturmada adı geçen isimlerden birinin de Katılımevim Yönetim Kurulu Başkanı Serdar Turhan olduğu ileri sürüldü. Turhan hakkında yurt dışına çıkış yasağı kararı verildiği iddia edilirken, yurt dışında bulunan mal varlığına ilişkin çeşitli bilgilerin de soruşturma kapsamında gündeme geldiği öne sürüldü. ALTUNÇ KUMOVA HAKKINDA DA KARAR İDDİASI Soruşturma kapsamında hakkında tedbir uygulandığı öne sürülen bir diğer isim ise Destek Yatırım'ın hakim ortağı ve Yönetim Kurulu Başkanı Altunç Kumova oldu. Kumova hakkında da yurt dışına çıkış yasağı kararı verildiği iddia edildi. GÖZLER PUSULA'NIN TERA'YA DEVRİNDE Yaşanan gelişmelerin ardından Pusula Finans Holding'in Tera Grubu'na devrinin nasıl ilerleyeceği merak konusu oldu. Tera tarafından yapılan açıklamada, kamuoyuna yansıyan gelişmelerin Pusula Finans Holding ve bünyesindeki şirketlerin tüzel kişiliklerinden, faaliyetlerinden ve kurumsal yapılarından bağımsız olduğu belirtildi. Şirket, daha önce duyurulan anlaşma doğrultusunda devralma sürecinin devam ettiğini bildirdi. DEVİR İÇİN GEREKLİ ONAYLAR BEKLENİYOR Pusula Finans Holding'in Tera Grubu'na devrinin tamamlanması için ilgili düzenleyici kurumların gerekli izin ve onaylarının alınması gerekiyor. Tera, söz konusu gelişmelere rağmen finans sektöründeki faaliyetlerini genişletmeye yönelik uzun vadeli stratejisinde değişiklik bulunmadığını açıkladı. KATILIMEVİM HİSSELERİ DE GÜNDEMDE Pusula Finans Holding ile ilgili gelişmeler, holdingin bünyesinde bulunan ve Borsa İstanbul'da KTLEV koduyla işlem gören Katılımevim açısından da yakından takip ediliyor. Katılımevim hisselerinde daha önce yaşanan hareketlilik de dikkat çekmişti. Satış anlaşmasının açıklanmasının ardından hisselerde üst üste yükselişler görülmüştü. İDDİALARIN ODAĞINDAKİ ŞİRKET: KATILIMEVİM Katılımevim, tasarruf finansman sektöründe faaliyet gösteriyor. Şirket; konut, araç ve çatılı iş yeri edinmek isteyen müşterilere tasarruf finansman modeli kapsamında hizmet sunuyor. Pusula Finans Holding'in Katılımevim'deki çoğunluk hisseleriyle bağlantısı nedeniyle holding hakkında yaşanan gelişmelerin şirket açısından da önem taşıdığı belirtiliyor. Not: Haberde yer alan yurt dışına kaçış, yakalama kararı ve yurt dışı çıkış yasağına ilişkin bilgiler, kaynakta yer alan iddialara dayanmaktadır. Kaynak: HABERLER Yükleniyor... Editörün Seçtiği Geri ödeme olmadan 5 bin lira veriliyor! Editörün Seçtiği Taraftarın Sesi Kanal S ekranlarında sizlerle 22 Ocak Pazartesi Editörün Seçtiği Samsun'da FETÖ'cü akrabası başını yaktı! Karar belli oldu Editör Hakkında Yunus Emre Purç Bunlar da ilginizi çekebil</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Dev finans şirketinde soruşturma: Yakalama kararı iddiası Dev finans şirketinde soruşturma: Yakalama kararı iddiası Samsun Gazetesi Pusula Finans Holding ve Katılımevim'in de gündemde olduğu soruşturmada bazı isimler hakkında yakalama ve yurt dışı yasağı iddiaları gündeme geldi. Dev finans şirketinde soruşturma: Yakalama kararı iddiası Pusula Finans Holding ve Katılımevim'in de adının geçtiği soruşturmayla ilgili yeni iddialar gündeme geldi. Pusula Portföy Yönetim Kurulu Başkanı Muhammet Yarız'ın yurt dışına çıktığı ve hakkında yakalama kararı verildiği öne sürülürken, bazı isimler hakkında da yurt dışına çıkış yasağı uygulandığı iddia edildi. Finans sektöründe Pusula Finans Holding ve bünyesindeki şirketleri ilgilendiren gelişmeler gündemdeki yerini koruyor. Pusula Finans Holding'in, portföyünde Katılımevim'in çoğunluk hisselerini bulundurduğu ve Tera Grubu'na devri konusunda tarafların anlaşmaya vardığı açıklanmıştı. Devir işleminin tamamlanabilmesi için Sermaye Piyasası Kurulu (SPK), Bankacılık Düzenleme ve Denetleme Kurumu (BDDK) ve Rekabet Kurulu başta olmak üzere gerekli izinlerin alınması beklenirken, soruşturmayla ilgili yeni iddialar ortaya atıldı. MUHAMMET YARIZ'IN YURT DIŞINA ÇIKTIĞI ÖNE SÜRÜLDÜ Soruşturma kapsamında adı geçen Pusula Portföy Yönetim Kurulu Başkanı Muhammet Yarız'ın yurt dışına çıktığı iddia edildi. Yarız'ın cep telefonunu ofisinde bırakarak Marmaris'ten tekneyle yurt dışına gittiği ve Yunanistan'da bulunduğu öne sürüldü. Faizsiz 100 bin TL kredi fırsatı: Bankalar tek tek açıkladı İçeriği Görüntüle YARIZ HAKKINDA YAKALAMA KARARI İDDİASI Soruşturmayla ilgili ortaya atılan bir diğer iddia ise Muhammet Yarız hakkında yakalama kararı çıkarıldığı yönünde oldu. İstanbul Cumhuriyet Başsavcılığı tarafından Yarız hakkında yakalama kararı verildiği, ayrıca mal varlığı ve banka hesaplarına tedbir konulduğu öne sürüldü. SERDAR TURHAN İÇİN DE YURT DIŞI YASAĞI İDDİASI Soruşturmada adı geçen isimlerden birinin de Katılımevim Yönetim Kurulu Başkanı Serdar Turhan olduğu ileri sürüldü. Turhan hakkında yurt dışına çıkış yasağı kararı verildiği iddia edilirken, yurt dışında bulunan mal varlığına ilişkin çeşitli bilgilerin de soruşturma kapsamında gündeme geldiği öne sürüldü. ALTUNÇ KUMOVA HAKKINDA DA KARAR İDDİASI Soruşturma kapsamında hakkında tedbir uygulandığı öne sürülen bir diğer isim ise Destek Yatırım'ın hakim ortağı ve Yönetim Kurulu Başkanı Altunç Kumova oldu. Kumova hakkında da yurt dışına çıkış yasağı kararı verildiği iddia edildi. GÖZLER PUSULA'NIN TERA'YA DEVRİNDE Yaşanan gelişmelerin ardından Pusula Finans Holding'in Tera Grubu'na devrinin nasıl ilerleyeceği merak konusu oldu. Tera tarafından yapılan açıklamada, kamuoyuna yansıyan gelişmelerin Pusula Finans Holding ve bünyesindeki şirketlerin tüzel kişiliklerinden, faaliyetlerinden ve kurumsal yapılarından bağımsız olduğu belirtildi. Şirket, daha önce duyurulan anlaşma doğrultusunda devralma sürecinin devam ettiğini bildirdi. DEVİR İÇİN GEREKLİ ONAYLAR BEKLENİYOR Pusula Finans Holding'in Tera Grubu'na devrinin tamamlanması için ilgili düzenleyici kurumların gerekli izin ve onaylarının alınması gerekiyor. Tera, söz konusu gelişmelere rağmen finans sektöründeki faaliyetlerini genişletmeye yönelik uzun vadeli stratejisinde değişiklik bulunmadığını açıkladı. KATILIMEVİM HİSSELERİ DE GÜNDEMDE Pusula Finans Holding ile ilgili gelişmeler, holdingin bünyesinde bulunan ve Borsa İstanbul'da KTLEV koduyla işlem gören Katılımevim açısından da yakından takip ediliyor. Katılımevim hisselerinde daha önce yaşanan hareketlilik de dikkat çekmişti. Satış anlaşmasının açıklanmasının ardından hisselerde üst üste yükselişler görülmüştü. İDDİALARIN ODAĞINDAKİ ŞİRKET: KATILIMEVİM Katılımevim, tasarruf finansman sektöründe faaliyet gösteriyor. Şirket; konut, araç ve çatılı iş yeri edinmek isteyen müşterilere tasarruf finansman modeli kapsamında hizmet sunuyor. Pusula Finans Holding'in Katılımevim'deki çoğunluk hisseleriyle bağlantısı nedeniyle holding hakkında yaşanan gelişmelerin şirket açısından da önem taşıdığı belirtiliyor. Not: Haberde yer alan yurt dışına kaçış, yakalama kararı ve yurt dışı çıkış yasağına ilişkin bilgiler, kaynakta yer alan iddialara dayanmaktadır. Editörün Seçtiği Taraftarın Sesi Kanal S ekranlarında sizlerle 22 Ocak Pazartesi Editörün Seçtiği Samsun'da FETÖ'cü akrabası başını yaktı!</t>
+          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>browser_full_article</t>
+          <t>browser_failed</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>https://www.samsungazetesi.com/dev-finans-sirketinde-sorusturma-yakalama-karari-iddiasi</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul | Samsun | Muğla</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>Marmaris</t>
-        </is>
-      </c>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNVkNOMFRrcXVpWXRrTzRGc3UzVzRUX0FVYU9qRDB6RXZrUV94bl95QUF2Ykh3bGdia0FTMm1mdk1lbE9SVlEtTjlGRlp3SzY1VkpVLTZ0cHRFb1dQV2JNMnZwSndTTTQ1RWRTbjk5ZG1NeG9YWWxRTEZLRVgzQm5maENHSzhRUTVXTXVsamZCaFExZVpiT0E4TWpWTU56dzdwU2c?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
       <c r="Q49" s="2" t="inlineStr"/>
@@ -7379,7 +7573,7 @@
       <c r="S49" s="2" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>firma yok | faaliyet/tesis yok</t>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr"/>
@@ -7393,7 +7587,7 @@
       <c r="Y49" s="2" t="inlineStr"/>
       <c r="Z49" s="2" t="inlineStr"/>
       <c r="AA49" s="2" t="n">
-        <v>87.75</v>
+        <v>59.8</v>
       </c>
       <c r="AB49" s="2" t="n">
         <v>48</v>
@@ -7402,27 +7596,27 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 11:50:46</t>
+          <t>2026-09-14 11:31:11</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>soruşturma</t>
+          <t>yangın</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor</t>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi</t>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -7432,18 +7626,18 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>ticaret</t>
+          <t>sanayi</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi ve içerik paylaşan sosyal medya hesapları hakkında soruşturma başlattı. Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi… Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi ve içerik paylaşan sosyal medya hesapları hakkında soruşturma başlattı.</t>
+          <t>Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Anasayfa / Video Galeri / Asayiş - 13 Eyl 2026 - 16:33 G üncelleme : 14 Eyl 2026 - 14:31 Sanayideki Yangın Büyümeden Söndürüldü Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. +1 Büyütmek için resme tıklayın Bugün öğleden sonra Konacık Sanayi Sitesi'ndeki otluk alanda yangın başladı. Alevleri fark eden sanayi esnafı, hortum ve yangın tüpleriyle alevlere müdahale etti. İhbarın ardından Bodrum İtfaiye Grup Amirliği ekipleri de olay yerine geldi. Vatandaşlar ve ekiplerin müdahalesiyle yangın büyümeden söndürüldü. Yangının otluk alana atılan sigara izmaritinden çıktığı sanılıyor. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 Muğla / Bodrum - Asayiş Yazdır GİRİŞ YAP Yorum yazarak Bodrum Kent Tv Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz. Yazılan yoru</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor Sosyal medyada yanıltıcı borsa paylaşımlarına soruşturma: Şüphelilerin kimlikleri araştırılıyor İstanbul Ticaret Gazetesi Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi ve içerik paylaşan sosyal medya hesapları hakkında soruşturma başlattı. Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi… Bakırköy Cumhuriyet Başsavcılığı, sermaye piyasası araçlarının fiyatlarını, değerlerini veya yatırımcıların kararlarını etkilemeye yönelik yanıltıcı bilgi ve içerik paylaşan sosyal medya hesapları hakkında soruşturma başlattı.</t>
+          <t>Sanayideki Yangın Büyümeden Söndürüldü Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. Anasayfa / Video Galeri / Asayiş - 13 Eyl 2026 - 16:33 G üncelleme : 14 Eyl 2026 - 14:31 Sanayideki Yangın Büyümeden Söndürüldü Bodrum'da sanayi sitesi içerisindeki otluk alanda çıkan yangın, büyümeden söndürüldü. +1 Büyütmek için resme tıklayın Bugün öğleden sonra Konacık Sanayi Sitesi'ndeki otluk alanda yangın başladı. Alevleri fark eden sanayi esnafı, hortum ve yangın tüpleriyle alevlere müdahale etti. İhbarın ardından Bodrum İtfaiye Grup Amirliği ekipleri de olay yerine geldi. Vatandaşlar ve ekiplerin müdahalesiyle yangın büyümeden söndürüldü. Yangının otluk alana atılan sigara izmaritinden çıktığı sanılıyor. Kaynak: Bodrum Kent TV # yangın , itfaiye 13 Eyl 2026 - 16:33 Muğla / Bodrum - Asayiş Yazdır GİRİŞ YAP Yorum yazarak Bodrum Kent Tv Topluluk Kuralları’nı kabul etmiş bulunuyor ve yorumunuzla ilgili doğrudan veya dolaylı tüm sorumluluğu tek başınıza üstleniyorsunuz.</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -7453,64 +7647,596 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>https://istanbulticaretgazetesi.com/sosyal-medyada-yaniltici-borsa-paylasimlarina-sorusturma-suphelilerin-kimlikleri-arastiriliyor</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
-      <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
+          <t>https://kenttv.net/video/28692971/sanayideki-yangin-buyumeden-sonduruldu</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Muğla</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Bodrum</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>da sanayi sitesi</t>
+        </is>
+      </c>
       <c r="P50" s="2" t="inlineStr"/>
       <c r="Q50" s="2" t="inlineStr"/>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret:84:summary</t>
-        </is>
-      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret Türkiye</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret Üniversitesi | İstanbul Ticaret Merkezi | İstanbul Ticaret İş Güvenliği ve Endüstriyel Ürünler San. A.Ş | İstanbul Ticaret Üniversitesi Küçükyalı Kampüsü | İstanbul Ticaret Borsası</t>
-        </is>
-      </c>
-      <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret Üniversitesi</t>
-        </is>
-      </c>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
-        </is>
-      </c>
-      <c r="Y50" s="2" t="inlineStr">
-        <is>
-          <t>100.0 | 100.0 | 100.0 | 100.0 | 100.0</t>
-        </is>
-      </c>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
       <c r="Z50" s="2" t="inlineStr"/>
       <c r="AA50" s="2" t="n">
-        <v>192.64</v>
+        <v>101.82</v>
       </c>
       <c r="AB50" s="2" t="n">
         <v>49</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 06:35:00</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>yangın</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Fiziksel Risk / Yangın</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Bursa’da kömür işletmesinde korkutan yangın!</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Bursa’da kömür işletmesinde korkutan yangın! bursatv.com.tr</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>işletme</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Bursa’nın Nilüfer ilçesinde bir kömür işletmesinde gece saatlerinde yangın çıktı. Alevleri görenlerin ihbarı üzerine bölgeye çok sayıda itfaiye ekibi sevk edilirken, yangın yoğun müdahalenin ardından kontrol altına alındı. Bursa’nın Nilüfer ilçesinde bir kömür işletmesinde gece saatlerinde yangın çıktı. Alevleri görenlerin ihbarı üzerine bölgeye çok sayıda itfaiye ekibi sevk edilirken, yangın yoğun müdahalenin ardından kontrol altına alındı. Bursa’nın Nilüfer ilçesinde bir kömür işletmesinde gece saatlerinde yangın çıktı. Alevleri görenlerin ihbarı üzerine bölgeye çok sayıda itfaiye ekibi sevk edilirken, yangın yoğun müdahalenin ardından kontrol altına alındı.</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Bursa’da kömür işletmesinde korkutan yangın! Bursa’da kömür işletmesinde korkutan yangın! bursatv.com.tr Bursa’nın Nilüfer ilçesinde bir kömür işletmesinde gece saatlerinde yangın çıktı. Alevleri görenlerin ihbarı üzerine bölgeye çok sayıda itfaiye ekibi sevk edilirken, yangın yoğun müdahalenin ardından kontrol altına alındı.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bursatv.com.tr/bursada-komur-isletmesinde-korkutan-yangin</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Bursa</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Nilüfer</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="n">
+        <v>79.43000000000001</v>
+      </c>
+      <c r="AB51" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 15:44:15</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>vergi incelemesi</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Diğer</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza borsatek.com</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>gıda</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda, 2024 hesap dönemine ilişkin vergi incelemesi sonucunda 6,2 milyon TL vergi aslı ve 12,2 milyon TL vergi ve gecikme cezası ile karşı karşıya kaldı. Ersu Meyve ve Gıda, 2024 hesap dönemine ilişkin vergi incelemesi sonucunda 6,2 milyon TL vergi aslı ve 12,2 milyon TL vergi ve gecikme cezası ile karşı karşıya kaldı. Ersu Meyve ve Gıda, 2024 hesap dönemine ilişkin vergi incelemesi sonucunda 6,2 milyon TL vergi aslı ve 12,2 milyon TL vergi ve gecikme cezası ile karşı karşıya kaldı. Borsa, halka arzlar, döviz, kripto para, hisse önerileri Ersu Meyve ve Gıda Sanayii (ERSU), 2024 hesap dönemine ilişkin yürütülen sınırlı vergi incelemesi sonucunda vergi/ceza ihbarnameleri aldı. Borsatek'i Facebook'ta takip et Facebook'ta takip et Hazine ve Maliye Bakanlığı Vergi Denetim Kurulu Başkanlığı tarafından gerçekleştirilen inceleme, şirketin 2024 hesap döneminde gerçekleştirdiği taşınmaz satışından doğan kazanca ilişkin uygulanan kurumlar vergisi istisnası kapsamında yürütüldü. Vergi/ceza ihbarnameleri kapsamında: 2024 hesap dönemi kurumlar vergisi yönünden 6.237.842,65 TL vergi aslı ve 6.292.932,72 TL vergi ziyaı cezası 2024 yılı geçici vergilendirme dönemi yönünden 5.943.608,63 TL vergi ziyaı cezası tarh/tahakkuk ettirildi. Geçici vergi yönünden raporda hesaplanan 5.942.318,81 TL geçici vergi aslı, mahsup döneminin geçmiş olması nedeniyle ilgili mevzuat uyarınca tahakkuk ettirilmeyecek. Söz konusu tutar üzerinden ilgili dönem için gecikme faizi hesaplanabilecek. Ersu Meyve ve Gıda, vergi inceleme raporları ve ihbarnamelere ilişkin yasal haklarını değerlendirmekte olup, idari ve/veya hukuki süreçlere başvurulması halinde gelişmeler kamuoyu ile</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza borsatek.com Ersu Meyve ve Gıda, 2024 hesap dönemine ilişkin vergi incelemesi sonucunda 6,2 milyon TL vergi aslı ve 12,2 milyon TL vergi ve gecikme cezası ile karşı karşıya kaldı. Borsa, halka arzlar, döviz, kripto para, hisse önerileri Ersu Meyve ve Gıda Sanayii (ERSU), 2024 hesap dönemine ilişkin yürütülen sınırlı vergi incelemesi sonucunda vergi/ceza ihbarnameleri aldı. Borsatek'i Facebook'ta takip et Facebook'ta takip et Hazine ve Maliye Bakanlığı Vergi Denetim Kurulu Başkanlığı tarafından gerçekleştirilen inceleme, şirketin 2024 hesap döneminde gerçekleştirdiği taşınmaz satışından doğan kazanca ilişkin uygulanan kurumlar vergisi istisnası kapsamında yürütüldü. Vergi/ceza ihbarnameleri kapsamında: 2024 hesap dönemi kurumlar vergisi yönünden 6.237.842,65 TL vergi aslı ve 6.292.932,72 TL vergi ziyaı cezası 2024 yılı geçici vergilendirme dönemi yönünden 5.943.608,63 TL vergi ziyaı cezası tarh/tahakkuk ettirildi. Geçici vergi yönünden raporda hesaplanan 5.942.318,81 TL geçici vergi aslı, mahsup döneminin geçmiş olması nedeniyle ilgili mevzuat uyarınca tahakkuk ettirilmeyecek. Söz konusu tutar üzerinden ilgili dönem için gecikme faizi hesaplanabilecek. Ersu Meyve ve Gıda, vergi inceleme raporları ve ihbarnamelere ilişkin yasal haklarını değerlendirmekte olup, idari ve/veya hukuki süreçlere başvurulması halinde gelişmeler kamuoyu ile</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borsatek.com/ersu-vergi-incelemesi-ceza/</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda:292:body+summary+title</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="n">
+        <v>155.25</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 08:43:00</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>banka hesapları bloke</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Diğer</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>el konuldu</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Güncel İran'da çok sayıda kişinin mal varlıklarına el konuldu İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Paylaş Linkedin Pinterest Telegram Yazdır Kopyala A - A + Mehmet TÜRK 14.09.2026 - 11:43 Okunma Süresi: 1 Dk Türkşeker 182 işçi alımı başvuruları başladı: İŞKUR başvuru şartları neler, son başvuru tarihi ne zaman? İçeriği Görüntüle İran Yargı Erki, el konulan mülkler, bloke edilen banka hesaplarına dair raporunu açıkladı. Mizan Haber Ajansı’nda yer alan habere göre, aralarında gazetecilerin, aktivistlerin, akademisyenlerin olduğu yüzlerce kişinin mal varlıklarına ve banka hesaplarına el konul konuldu. El konulan mal varlıklarının 143’ü Tahran’da bulunuyor. Habere göre, 182 kişinin banka hesapları bloke edildi, 2 binden fazla kişinin ise banka hesapları için incelemeler devam ediyor. Haberde, el konulan varlıkların İran halkı için kullanılacağı iddia edildi. Kaynak: MA Editörün Seçtiği Diyarbakır’da okullar açıldı, yol çalışması trafiği vurdu! Editörün Seçtiği Daha 17 17. bölüm fragmanı yayınlandı mı, ne zaman yayınlanacak? Aras ve Teoman arasında yeni dönem! Editörün Seçtiği Dayik Qurban, Gift Orban Editör Hakkında Mehmet TÜRK Bunlar da</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi. Güncel İran'da çok sayıda kişinin mal varlıklarına el konuldu İran’da, “vatana ve halka ihanet”, “casusluk” iddiasıyla 240 kişinin mal varlıklarına, 182 kişinin banka hesapları bloke edildi.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.guneydoguekspres.com/iranda-cok-sayida-kisinin-mal-varliklarina-el-konuldu</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="AB53" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:55:08</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>bankaya soruşturma</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir. Vietnam.vn</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir. Vietnam.vn</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir. Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir. Vietnam.vn Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>browser_failed</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdjRmSmtRVVQ3cm84cHItZGRXVE1HVGctemU4bDNSN3FFVDdtdDc4djROdnUxSzZWWlRZRzZnOWdXUHlZRzRLNnRfem5wMzVBRXp0M2NuTWpiQnhlRU5KclotSzhqQ2Q5TWkwZm1CUmxSM0ZIaXdlcHdCcEFzb2k5aXp6S2dYN2xlZHlXZXh3XzU4dUVCbkRHdmRLeWVvUnhLN2NGc0NYaw?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="AB54" s="2" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:01:00</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>bankaya soruşturma</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>banka</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>finansal kuruluş</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor. İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor. İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor.</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber İzmir'de bir banka şubesinde rehin alınan 5 çalışan, güvenlik güçlerinin müzakereleri sonucu sağlıklı bir şekilde kurtarıldı. Şüpheli Can Aydın teslim oldu ve geçmişi inceleniyor.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>browser_full_article</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.toplumsal.com.tr/haber/izmir-deki-banka-subesinde-rehin-alan-supheli-teslim-oldu_25400/</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="AB55" s="2" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14 12:21:32</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>gözaltı</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı İhlas Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>maden</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı İhlas Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı İhlas Haber Ajansı Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı İhlas Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>browser_failed</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOS195ZE5BeGRkS2doS1BQRmptWGRPTnl3VnBSUHZSeVFUWjdRdEFkNC04dFZtbDMwUGZBVWhjY25FODdpRURXT0VtTU1rdEZfcE41QmRDR1N3Y0g5N29jaVBzS2UyNGZMeU1jSl9Db2FnZ2NIUzdUUmdEd1loSkphaEhtRjBNRFZxZUR1UUxlLU4wQQ?oc=5&amp;hl=tr&amp;gl=TR&amp;ceid=TR:tr</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>il yok | ilçe yok | firma yok | faaliyet/tesis yok</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="n">
+        <v>43.98</v>
+      </c>
+      <c r="AB56" s="2" t="n">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB50"/>
+  <autoFilter ref="A1:AB56"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -7561,6 +8287,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/haberler_final.xlsx
+++ b/data/haberler_final.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw_Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kontrol_Listesi'!$A$1:$J$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Raw_Data'!$A$1:$AB$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:35:12</t>
+          <t>2026-09-15 09:30:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı</t>
+          <t>Madran Dağı alarm veriyor: Yangın felaketi yetmezmiş gibi Madran’da bir maden daha kapasite arttırıyor</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı A Haber</t>
+          <t>Madran Dağı alarm veriyor: Yangın felaketi yetmezmiş gibi Madran’da bir maden daha kapasite arttırıyor Evrensel.net</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -537,37 +537,49 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Düzce</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>Aydın | Burdur | Bursa | Isparta | Kırklareli</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Bozdoğan | Çine | Yenipazar | İznik</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Akmin Endüstri Mineralleri Sanayi ve Ticaret A.Ş</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>AKFELD MADENCİLİK SANAYİ VE TİCARET A.Ş</t>
+        </is>
+      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:49:00</t>
+          <t>2026-09-14 21:56:30</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği</t>
+          <t>Tarım arazilerinde bulunan depolar ve fabrikalarda proaktif yangın önleme tedbirleri uygulanmalıdır.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>8 ilde yasa dışı bahis operasyonu! MASAK raporu ortaya çıkardı: 17 Milyar 750 Milyon TL’lik para trafiği Ege Telgraf</t>
+          <t>Tarım arazilerinde bulunan depolar ve fabrikalarda proaktif yangın önleme tedbirleri uygulanmalıdır. vietnam.vn</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -581,29 +593,29 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>maps sonucu düşük güven nedeniyle elendi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:49:00</t>
+          <t>2026-09-14 14:03:15</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği</t>
+          <t>Düzce’de yangın çıkan ahşap kapı fabrikasında soğutma çalışmaları tamamlandı</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8 ilde dev yasa dışı bahis operasyonu! MASAK raporu dudak uçuklattı: 17,7 milyar liralık para trafiği Ulusal Kanal</t>
+          <t>Düzce’de yangın çıkan ahşap kapı fabrikasında soğutma çalışmaları tamamlandı Safranbolu Birlik Haber</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -611,7 +623,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Düzce</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -624,7 +640,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 23:08:00</t>
+          <t>2026-09-15 03:46:00</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -634,12 +650,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de kapı fabrikasında yangın</t>
+          <t>Düzce'deki fabrika yangında zarar gördü</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de kapı fabrikasında yangın Milliyet</t>
+          <t>Düzce'deki fabrika yangında zarar gördü toplumsal.com.tr</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -647,32 +663,20 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Bolu | Düzce | İstanbul | Mardin</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Bahçelievler</t>
-        </is>
-      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>KZB Yangın Söndürme Sistemleri</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:18:13</t>
+          <t>2026-09-14 17:53:45</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -682,12 +686,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti!</t>
+          <t>Arazi kullanımı, inşaat yönetmelikleri ve yangın önleme ve kontrolü ile ilgili ihlallerin ele alınması.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Gece Yarısı Korku Dolu Anlar: Fabrikada Çıkan Yangın Gökyüzünü Alevlere Teslim Etti! Düzce Gazete Efsane</t>
+          <t>Arazi kullanımı, inşaat yönetmelikleri ve yangın önleme ve kontrolü ile ilgili ihlallerin ele alınması. vietnam.vn</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -695,11 +699,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:12:00</t>
+          <t>2026-09-14 10:17:58</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı</t>
+          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bolu'da 5 saatlik yangın kabusu: Geri dönüşüm fabrikası alevlere teslim oldu, 3 kişi yaralandı Bolu Gündem</t>
+          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı bolgegundemi.com</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -735,47 +735,35 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Gerede</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>İlamet Metal Ltd Şti</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:11:00</t>
+          <t>2026-09-15 08:11:47</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Demirtaş Mahallesi'nde saman deposu yangını</t>
+          <t>İran'da 240 muhalif ve gazetecinin mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Demirtaş Mahallesi'nde saman deposu yangını Yeni Alanya</t>
+          <t>İran'da 240 muhalif ve gazetecinin mal varlığına el konuldu Euronews.com</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -785,45 +773,37 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Antalya | Bursa</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Alanya</t>
-        </is>
-      </c>
+          <t>İzmir</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Demirtaş Toptancı Hali</t>
-        </is>
-      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>firma adı yok, tesis/lokasyon ile maps tahmini var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:07:54</t>
+          <t>2026-09-14 12:09:13</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın</t>
+          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Antalya’da otel malzemelerinin bulunduğu 5 depoda yangın turizmaktuel.com</t>
+          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu İlke TV</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -831,11 +811,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Antalya</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
@@ -848,22 +824,22 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 10:17:58</t>
+          <t>2026-09-14 18:31:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı</t>
+          <t>﻿Görkemli takı töreni MASAK'a takılmıştı: ''Kara Haydar''ın eşi Çağla Öz tutuklandı</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Alanya’daki Saman Deposu Yangını Sonrası Resmi İnceleme Başlatıldı bolgegundemi.com</t>
+          <t>﻿Görkemli takı töreni MASAK'a takılmıştı: ''Kara Haydar''ın eşi Çağla Öz tutuklandı STAR - Haberler</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -871,7 +847,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Van</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
@@ -884,22 +864,22 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 12:09:13</t>
+          <t>2026-09-14 11:11:00</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Kara Para / MASAK / Bahis</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu</t>
+          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>İran’da 100 kişi hakkında idam kararı: Yüzlerce kişinin mal varlığına el konuldu İlke TV</t>
+          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor yenicaggazetesi.com</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -907,7 +887,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Van</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
@@ -956,22 +940,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:11:00</t>
+          <t>2026-09-14 16:54:06</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor</t>
+          <t>Bankalara sahte para ve dolandırıcılık uyarısı</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Kara Haydar'ın bu kezde dolar görüntüleri ortaya çıktı: MASAK 115 milyonu izliyor Yeniçağ Gazetesi</t>
+          <t>Bankalara sahte para ve dolandırıcılık uyarısı Medya Midas</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -979,11 +963,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Van</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
@@ -996,22 +976,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:55:51</t>
+          <t>2026-09-15 08:15:13</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı</t>
+          <t>Ho Chi Minh Şehri polisi, yeni üniversite öğrencilerini hedef alan ve onları kiralık oda depozitolarını ödemeye ikna etmeyi amaçlayan dolandırıcılık yöntemlerine karşı uyarıda bulundu.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Bilecik Bozüyük'te polis, banka personelini sahte para ve dolandırıcılığa karşı uyardı Son Dakika</t>
+          <t>Ho Chi Minh Şehri polisi, yeni üniversite öğrencilerini hedef alan ve onları kiralık oda depozitolarını ödemeye ikna etmeyi amaçlayan dolandırıcılık yöntemlerine karşı uyarıda bulundu. vietnam.vn</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1019,16 +999,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Bilecik</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Bozüyük</t>
-        </is>
-      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
@@ -1040,22 +1012,22 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:45:32</t>
+          <t>2026-09-14 14:23:02</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı</t>
+          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Bilecik'te bankacılara sahte para ve dolandırıcılıkla mücadele çağrısı Aksiyon.com.TR</t>
+          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı aksiyon.com.tr</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1065,14 +1037,10 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Bilecik | Bursa | Denizli | Düzce | Eskişehir</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Bozüyük | Silivri | Ereğli | Yeşilyurt</t>
-        </is>
-      </c>
+          <t>Bursa | Düzce | Erzurum | İstanbul | Tokat</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
@@ -1084,22 +1052,22 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 22:32:41</t>
+          <t>2026-09-15 05:56:41</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de fabrika yangını büyüdü! Alevlerle savaşan 1 itfaiye eri yaralandı</t>
+          <t>Eskişehir’de Bankacılara ‘KAPTIRMA’ Projesi Anlatıldı</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de fabrika yangını büyüdü! Alevlerle savaşan 1 itfaiye eri yaralandı Takvim</t>
+          <t>Eskişehir’de Bankacılara ‘KAPTIRMA’ Projesi Anlatıldı Eskişehir Durum</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1109,7 +1077,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Düzce</t>
+          <t>Eskişehir</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1124,22 +1092,22 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:44:22</t>
+          <t>2026-09-14 14:22:08</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Dolandırıcılık / Sahtecilik</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı</t>
+          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki ahşap kapı fabrikası yangınında soğutma tamamlandı Son Dakika</t>
+          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede havadis.com</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1149,7 +1117,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Düzce</t>
+          <t>Eskişehir</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1164,22 +1132,22 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 22:33:16</t>
+          <t>2026-09-15 09:03:00</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor</t>
+          <t>Sebze-Meyve Sektörüne Operasyon: 41 Şirket Yöneticisi Hakkında Gözaltı Kararı</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Düzce Gökçeköy'de kapı fabrikası yangını: ekipler çevredeki evleri korumaya çalışıyor Aksiyon.com.TR</t>
+          <t>Sebze-Meyve Sektörüne Operasyon: 41 Şirket Yöneticisi Hakkında Gözaltı Kararı 5 Ocak Gazetesi</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1200,22 +1168,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 22:32:24</t>
+          <t>2026-09-15 07:03:42</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi</t>
+          <t>Ankara- Sebze ve meyvede fahiş fiyat operasyonu; 41 firmanın yöneticisi hakkında gözaltı kararı</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de kapı fabrikasındaki yangına müdahale sürüyor, yanan fabrika dronla görüntülendi Son Dakika</t>
+          <t>Ankara- Sebze ve meyvede fahiş fiyat operasyonu; 41 firmanın yöneticisi hakkında gözaltı kararı Milliyet</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1225,7 +1193,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Düzce</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
@@ -1240,22 +1208,22 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:48:26</t>
+          <t>2026-09-14 13:34:13</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti</t>
+          <t>Letonya’nın havayolu şirketi AirBaltic jet yakıtı krizi nedeniyle ABD’de iflas koruması başvurusunda bulundu</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Düzce Hacıaliler köyündeki fabrika yangınına Sakarya ve Bolu'dan itfaiye gitti Son Dakika</t>
+          <t>Letonya’nın havayolu şirketi AirBaltic jet yakıtı krizi nedeniyle ABD’de iflas koruması başvurusunda bulundu Patronlar Dünyası</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1263,11 +1231,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Bolu | Düzce</t>
-        </is>
-      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1280,22 +1244,22 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:27:59</t>
+          <t>2026-09-15 09:20:12</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı</t>
+          <t>İngiltere Merkez Bankası tahvil satışlarını durdurmaya hazırlanıyor</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Saniyelerle Yarışıldı: Düzce'deki Fabrika Yangınına Hızlı Müdahale ve Ekiplerin Zaman Çizelgesi Açıklandı Düzce Gazete Efsane</t>
+          <t>İngiltere Merkez Bankası tahvil satışlarını durdurmaya hazırlanıyor Investing.com Türkiye</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1303,11 +1267,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1320,22 +1280,22 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:48:24</t>
+          <t>2026-09-15 07:17:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada</t>
+          <t>Konkordato isteyen firmanın alacaklılarına çağrı</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Düzce’de üretim tesisinde yangın alarmı: itfaiye ekipleri sahada Aksiyon.com.TR</t>
+          <t>Konkordato isteyen firmanın alacaklılarına çağrı Akyazı Haber Akyazı'nın Bir Numaralı Haber Sitesi</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1345,41 +1305,49 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Bursa | Denizli | Düzce | Eskişehir | İstanbul</t>
+          <t>Sakarya</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Silivri | Ereğli | Yeşilyurt</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>Akyazı | Ferizli</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Monosteel Makine Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Monosteel Production Facility</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 19:45:00</t>
+          <t>2026-09-14 23:15:32</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi</t>
+          <t>Konkordato alırım, "bankalara faizi sildiririm" diyenlere dikkat!</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Düzce'deki fabrika yangını büyüdü: Bolu'dan takviye ekip gönderildi Düzce Hür Haber</t>
+          <t>Konkordato alırım, "bankalara faizi sildiririm" diyenlere dikkat! Para Analiz</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1387,11 +1355,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Bolu</t>
-        </is>
-      </c>
+      <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1404,22 +1368,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:49:00</t>
+          <t>2026-09-15 06:19:39</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Başkan Özlü’den fabrika yangını açıklaması</t>
+          <t>İstanbul'da üç şirket iflas etti: Amper Elektrik, Forend Elektrik ve Protart için karar</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Başkan Özlü’den fabrika yangını açıklaması Düzce Postası</t>
+          <t>İstanbul'da üç şirket iflas etti: Amper Elektrik, Forend Elektrik ve Protart için karar | Türkiye Ekonomisi Haberleri GZT</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1429,37 +1393,45 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Düzce</t>
+          <t>İstanbul</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Amper Elektrik İnşaat ve Sanayi Anonim Şirketi | Forend Elektrik Malzemeleri ve Dış Ticaret Anonim Şirketi</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>AMPER Enerji Teknik Kontrol Ölçüm Test ve Analiz A.Ş</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 22:33:20</t>
+          <t>2026-09-15 06:58:00</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti</t>
+          <t>Üç şirket için iflas kararı! 54 yıllık şirket de iflas edenler arasında</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de geceyi aydınlatan alevler: Fabrika yangını yerleşim yerlerini tehdit etti havadis.com</t>
+          <t>Üç şirket için iflas kararı! 54 yıllık şirket de iflas edenler arasında Türkinform</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1467,39 +1439,43 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Düzce</t>
-        </is>
-      </c>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Amper Elektrik İnşaat ve Sanayi AŞ</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>AMPER Enerji Teknik Kontrol Ölçüm Test ve Analiz A.Ş</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:28:44</t>
+          <t>2026-09-15 09:04:21</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>İnegöl OSB’de tekstil fabrikasında yangın</t>
+          <t>Bir değil, iki değil... Üç şirket için iflas kararı... Batık kredi alarmı</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>İnegöl OSB’de tekstil fabrikasında yangın İnegöl Yerel Haber</t>
+          <t>Bir değil, iki değil... Üç şirket için iflas kararı... Batık kredi alarmı Odatv</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1507,16 +1483,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>İnegöl</t>
-        </is>
-      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
@@ -1528,22 +1496,22 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:48:21</t>
+          <t>2026-09-14 14:29:33</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız"</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Düzce Belediye Başkanı Özlü: "Bir can kaybı yok. Fabrikadaki yangın söndürme işlemlerini inşallah bu akşam tamamlayacağız" Mersin Haber</t>
+          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti Tek Referans</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1564,22 +1532,22 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:23:02</t>
+          <t>2026-09-14 09:46:30</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Banka / Finansal Kuruluş</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Bankalara yönelik 'KAPTIRMA' eğitimleriyle dolandırıcılığa karşı önlem artırıldı Aksiyon.com.TR</t>
+          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1587,16 +1555,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Bursa | Denizli | Düzce | Eskişehir | İstanbul</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Silivri | Ereğli | Yeşilyurt</t>
-        </is>
-      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
@@ -1608,22 +1568,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:22:08</t>
+          <t>2026-09-14 10:32:55</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Dolandırıcılık / Sahtecilik</t>
+          <t>İflas / Konkordato / Mali Sorun</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede</t>
+          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Eskişehir'de bankalara dolandırıcılık kalkanı: KAPTIRMA projesi devrede havadis.com</t>
+          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı | Türkiye Ekonomisi Haberleri GZT</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1631,13 +1591,13 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Eskişehir</t>
-        </is>
-      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Boya Tekstil</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -1648,7 +1608,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:14:01</t>
+          <t>2026-09-14 13:15:00</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1658,12 +1618,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>AirBaltic'te finansal kriz: ABD'de iflas koruması başvurusunda bulundu</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>AirBaltic'te finansal kriz: ABD'de iflas koruması başvurusunda bulundu İstanbul Ticaret Gazetesi</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku Yıldırım Gazetesi</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1671,28 +1631,24 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Kahramanmaraş</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>İstanbul Ticaret Üniversitesi</t>
-        </is>
-      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:05:00</t>
+          <t>2026-09-15 08:00:00</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1702,12 +1658,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu!</t>
+          <t>İstanbul'da oteli de olan tekstil şirketi iflasını açıkladı</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Dev havayolu şirketi iflas korumasına başvurdu: Savaş ve yakıt krizi vurdu! babaocagi.com.tr</t>
+          <t>İstanbul'da oteli de olan tekstil şirketi iflasını açıkladı Turizm Güncel</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1715,7 +1671,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1728,7 +1688,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:29:33</t>
+          <t>2026-09-14 12:51:00</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1738,12 +1698,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti</t>
+          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>İnşaat şirketine mahkemeden şok karar… Konkordato talebini reddetti Tek Referans</t>
+          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek yenicaggazetesi.com</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1764,7 +1724,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:30:52</t>
+          <t>2026-09-14 11:31:46</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1774,12 +1734,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı</t>
+          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Bursa'da tekstil şirketi iflas etti! Alacaklılar için kritik süre başladı Bursada Bugün</t>
+          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Merhaba Gazetesi</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1789,14 +1749,10 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Bursa | İstanbul</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Kestel</t>
-        </is>
-      </c>
+          <t>Konya</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr">
@@ -1808,7 +1764,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 10:32:55</t>
+          <t>2026-09-15 05:58:02</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1818,12 +1774,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı</t>
+          <t>1978 yılından bu yana inşaat sektöründeydi! Dildar İnşaat'a 6 ay geçici konkordato koruması!</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Germenicia Boya Tekstil ve Germenicia Hotel iflas etti: Konkordato sürecinden çıkamadı | Türkiye Ekonomisi Haberleri GZT</t>
+          <t>1978 yılından bu yana inşaat sektöründeydi! Dildar İnşaat'a 6 ay geçici konkordato koruması! emlakkulisi.com</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1835,20 +1791,24 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Germenicia Boya Tekstil</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t>Dildar İnşaat Turizm Yatırım ve İşletmeleri A.Ş</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Dildar İnşaat</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:12:39</t>
+          <t>2026-09-15 09:07:00</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1858,12 +1818,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi...</t>
+          <t>Kahramanmaraş’ta İki Firma İçin İflas Kararı: Tasfiye Başladı</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da bir şirket daha konkordato sürecinde! Mal varlıklarının devrine yasak getirildi... Bursa Hakimiyet</t>
+          <t>Kahramanmaraş’ta İki Firma İçin İflas Kararı: Tasfiye Başladı Haber 46</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1873,26 +1833,30 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
+          <t>Kahramanmaraş</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Gıda Spor Tesisleri Seracılık Sanayi ve Ticaret A.Ş</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
+          <t>Germenicia Tekstil San. ve Tic. Ltd. Şti</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>maps sonucu düşük güven nedeniyle elendi</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:00:38</t>
+          <t>2026-09-14 15:22:00</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1902,12 +1866,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü</t>
+          <t>Kocaeli'deki şirket iflas etti: Alacaklılara çağrı!</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Gömlek devinin konkordato ilan etti: TÜSİAD eski başkanının şirketinde kredi notu düştü Türkiye İş Dünyası Haberleri</t>
+          <t>Kocaeli'deki şirket iflas etti: Alacaklılara çağrı! kocaeligazetesi.com.tr</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1917,12 +1881,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Çorum | Eskişehir | Kilis | Aydın | İstanbul</t>
+          <t>Kocaeli</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Söke | Beşiktaş</t>
+          <t>Gebze</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
@@ -1936,7 +1900,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:46:30</t>
+          <t>2026-09-14 15:56:00</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1946,12 +1910,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Türkiye’nin ünlü gıda markası iflastan kurtuldu. Alacaklılar sıraya girdi Nefes Gazetesi</t>
+          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku Yıldırım Gazetesi</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1972,22 +1936,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:00</t>
+          <t>2026-09-15 07:47:16</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek</t>
+          <t>Tadilattaki petrol istasyonunda yangın İhlas Haber Ajansı</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Tekstil sektörünün iddialı firması iflas etti: 200 çalışan kara kara düşünecek Yeniçağ Gazetesi</t>
+          <t>Tadilattaki petrol istasyonunda yangın İhlas Haber Ajansı iha.com.tr</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1997,10 +1961,14 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>Siirt</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Kurtalan</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
@@ -2012,22 +1980,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:31:46</t>
+          <t>2026-09-15 05:53:00</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Fiziksel Risk / Yangın</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı</t>
+          <t>Pendik’te ambalaj fabrikasında yangın: Ekipler seferber oldu!</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Konya organize sanayideki dev firma konkordato ilan etti! 2 ay süre başladı Merhaba Gazetesi</t>
+          <t>Pendik’te ambalaj fabrikasında yangın: Ekipler seferber oldu! babaocagi.com.tr</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -2037,10 +2005,14 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Konya</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Pendik</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
@@ -2052,7 +2024,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:22:37</t>
+          <t>2026-09-15 06:00:00</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2062,12 +2034,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi</t>
+          <t>Otel yatırımı da kurtaramadı: Şirket resmen iflas etti</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>58 Yıllık Meyve Suyu Şirketi Konkordatodan Çıktı! Aroma Bursa Konkordato Süreci Sona Erdi Taşınmaz Haber</t>
+          <t>Otel yatırımı da kurtaramadı: Şirket resmen iflas etti Turizm Ajansı</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -2088,7 +2060,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:52:25</t>
+          <t>2026-09-14 15:55:46</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2098,12 +2070,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı</t>
+          <t>Cambium Networks’ün yan kuruluşu iflas sürecine girdi, şirket işgücünün %53,6’sını kesti</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>VİB Turizm Konkordato Sürecine Girdi! Mahkemeden 3 Aylık Geçici Mühlet Kararı Taşınmaz Haber</t>
+          <t>Cambium Networks’ün yan kuruluşu iflas sürecine girdi, şirket işgücünün %53,6’sını kesti Investing.com Türkiye</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2124,7 +2096,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:27:00</t>
+          <t>2026-09-14 10:10:00</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2134,12 +2106,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı!</t>
+          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Kahramanmaraş’ta İki Şirket İçin İflas Kararı, Biri İçin Konkordatoda Mühlet Uzatıldı! ede TV</t>
+          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti Ekonomim</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2147,32 +2119,20 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Kahramanmaraş</t>
-        </is>
-      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Germenicia Group Kumaş Boya İşletmesi (Germenicia Tekstil Sanayi ve Ticaret Limited Şirketi</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>firma adı + güvenli maps adayı var</t>
+          <t>maps araması yapılmadı</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 09:53:53</t>
+          <t>2026-09-14 15:47:43</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2182,12 +2142,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu</t>
+          <t>ABD Başkanı Trump: İran ekonomik olarak iflas yolunda</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Savaşın maliyetine dayanamadı: Dev havayolu şirketi iflas koruması başvurusunda bulundu Ekonomist</t>
+          <t>ABD Başkanı Trump: İran ekonomik olarak iflas yolunda İstanbul Ticaret Gazetesi</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2197,18 +2157,26 @@
       </c>
       <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
-      <c r="I43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul Ticaret Üniversitesi</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:12:00</t>
+          <t>2026-09-14 11:06:00</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2218,12 +2186,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi</t>
+          <t>Dünyaca ünlü havayolu şirketinden iflas etti: Savaş havacılığı vurdu</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Gebze’de iflas eden şirket için alacaklılara çağrı: 1 ay süre verildi Kocaeli Barış Gazetesi</t>
+          <t>Dünyaca ünlü havayolu şirketinden iflas etti: Savaş havacılığı vurdu yenicaggazetesi.com</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2231,16 +2199,8 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Kocaeli</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Gebze</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
@@ -2252,7 +2212,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:56:00</t>
+          <t>2026-09-14 21:13:42</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2262,12 +2222,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku</t>
+          <t>15 milyon kişiyi ilgilendiriyor! Şirket iflas etti, datalar satılabilir</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Yatırımlarıyla dikkat çekiyordu! Tekstil ve turizm şirketine iflas şoku yildirimgazetesi.com</t>
+          <t>15 milyon kişiyi ilgilendiriyor! Şirket iflas etti, datalar satılabilir magazinlife.com</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2288,22 +2248,22 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 10:10:00</t>
+          <t>2026-09-14 18:15:09</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti</t>
+          <t>Kırıkkale’de yasa dışı bahse 56 milyonluk darbe: Banka hesaplarından kriptoya uzanan para trafiği ortaya çıktı!</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2 yıldır zarar ediyordu: Tekstil ve otelcilik şirketi iflas etti Ekonomim</t>
+          <t>Kırıkkale’de yasa dışı bahse 56 milyonluk darbe: Banka hesaplarından kriptoya uzanan para trafiği ortaya çıktı! SON TV</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2311,7 +2271,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Kırıkkale</t>
+        </is>
+      </c>
       <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2324,22 +2288,22 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:07:27</t>
+          <t>2026-09-15 07:49:23</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak?</t>
+          <t>Gıda tedarik firmalarına operasyon: 41 dağıtıcı şirketin 41 yöneticisine gözaltı</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Ünlü hava yolu şirketinden iflas koruma başvurusu: Biletler ne olacak? - Finans haberlerinin doğru adresi - Mynet Finans Haber Mynet</t>
+          <t>Gıda tedarik firmalarına operasyon: 41 dağıtıcı şirketin 41 yöneticisine gözaltı Ensonhaber</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2347,35 +2311,51 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul | Uşak | Antalya | Konya</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Ilgın</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>EREN TARIM ÜRN. LTD. ŞTİ | TOPÇUOĞULLARI SARRAF TAR.ÜR. LTD.ŞTİ | FATİH TARIMSAL ÜRÜNLER SANAYİ TİCARET LTD.ŞTİ | ALTUNPUL TARIM ÜRÜNLERİ TİCARET LİMİTED ŞİRKETİ | KÜTMEY SANAYİ VE TİCARET ANONİM ŞİRKETİ | AYDAŞ ORGANİK TARIM İTHALAT VE İHRACAT LİMİTED ŞİRKETİ | BETA TROPİKAL MEYVE TİCARET VE PAZARLAMA LİMİTED ŞİRKETİ</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>EREN Packing House (EREN TARIM</t>
+        </is>
+      </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>maps araması yapılmadı</t>
+          <t>firma adı + güvenli maps adayı var</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:23:36</t>
+          <t>2026-09-15 08:28:23</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>İflas / Konkordato / Mali Sorun</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı...</t>
+          <t>Sebze ve meyve hallerindeki 41 dağıtıcı firmaya fahiş fiyat operasyonu: 33 gözaltı</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da tekstil şirketinin iflasında yeni gelişme! Alacaklılar için süre başladı... Bursa Hakimiyet</t>
+          <t>Sebze ve meyve hallerindeki 41 dağıtıcı firmaya fahiş fiyat operasyonu: 33 gözaltı Egeli Gazete</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2385,14 +2365,10 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Kestel</t>
-        </is>
-      </c>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
@@ -2404,22 +2380,22 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 07:51:05</t>
+          <t>2026-09-15 06:16:30</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Kara Para / MASAK / Bahis</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe</t>
+          <t>Son Dakika... Sebze ve meyve fiyatlarını manipüle eden firmalara operasyon: 41 gözaltı kararı</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Jandarma Operasyonu: Yasa Dışı Bahis ve Para Transferine Darbe Haber S Balıkesir</t>
+          <t>Son Dakika... Sebze ve meyve fiyatlarını manipüle eden firmalara operasyon: 41 gözaltı kararı 12punto</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2427,7 +2403,11 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2440,22 +2420,22 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 11:31:11</t>
+          <t>2026-09-15 07:15:00</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Sanayideki Yangın Büyümeden Söndürüldü</t>
+          <t>Tarladan markete fiyat operasyonu nedir, kimler gözaltına alındı? Hangi firmalar var?</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Sanayideki Yangın Büyümeden Söndürüldü Bodrum Kent TV</t>
+          <t>Tarladan markete fiyat operasyonu nedir, kimler gözaltına alındı? Hangi firmalar var? Antalya Körfez Gazetesi</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -2465,12 +2445,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Muğla</t>
+          <t>Antalya | İstanbul</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Bodrum</t>
+          <t>Kepez</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -2484,22 +2464,22 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 06:35:00</t>
+          <t>2026-09-14 15:44:15</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Fiziksel Risk / Yangın</t>
+          <t>Diğer</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da kömür işletmesinde korkutan yangın!</t>
+          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Bursa’da kömür işletmesinde korkutan yangın! bursatv.com.tr</t>
+          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza borsatek.com</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -2507,17 +2487,13 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Nilüfer</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Ersu Meyve ve Gıda</t>
+        </is>
+      </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -2528,22 +2504,22 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 15:44:15</t>
+          <t>2026-09-15 07:42:51</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Operasyon / Soruşturma / Suç</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza</t>
+          <t>Yaş sebze ve meyvede fahiş fiyatla dağıtım yapanlara operasyon: 41 şirket yöneticisine gözaltı</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Ersu Meyve ve Gıda’ya 2024 vergi incelemesinden 12,5 milyon TL vergi ve ceza borsatek.com</t>
+          <t>Yaş sebze ve meyvede fahiş fiyatla dağıtım yapanlara operasyon: 41 şirket yöneticisine gözaltı Haberiniz</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -2553,11 +2529,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Ersu Meyve ve Gıda</t>
-        </is>
-      </c>
+      <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -2568,22 +2540,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 08:43:00</t>
+          <t>2026-09-14 14:55:08</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Diğer</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu</t>
+          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>İran'da çok sayıda kişinin mal varlıklarına el konuldu Güneydoğu Ekspres</t>
+          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir. vietnam.vn</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -2604,7 +2576,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:55:08</t>
+          <t>2026-09-15 05:39:00</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2614,12 +2586,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir.</t>
+          <t>Türk banka denmişti Rus bankaya ABD yaptırımı geldi</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Kişilerin banka hesaplarını satmamaları, kiralamamaları veya ödünç vermemeleri şiddetle tavsiye edilir. Vietnam.vn</t>
+          <t>Türk banka denmişti Rus bankaya ABD yaptırımı geldi Haber Hürriyeti</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -2640,7 +2612,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 22:01:00</t>
+          <t>2026-09-15 08:00:11</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2650,12 +2622,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu</t>
+          <t>AI Ajanları Ödeme Sistemlerine Giriyor Bankacılığın Yeni Arayüzü AI mı Olacak?</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>İzmir'deki banka şubesinde rehin alan şüpheli teslim oldu Toplumsal Haber</t>
+          <t>AI Ajanları Ödeme Sistemlerine Giriyor Bankacılığın Yeni Arayüzü AI mı Olacak? FintekWins</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -2663,11 +2635,7 @@
           <t>Habere Git</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>İzmir</t>
-        </is>
-      </c>
+      <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
@@ -2680,22 +2648,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 12:21:32</t>
+          <t>2026-09-14 18:33:31</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Operasyon / Soruşturma / Suç</t>
+          <t>Banka / Finansal Kuruluş</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı</t>
+          <t>8 Büyük Bankacılık Kuruluşu, Kripto Paralar İçin Boğa Lehine Clarity Act'e Karşı Sıcak Bildiri Yayınladı!</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Ruhsatsız madendeki ölüme 5 gözaltı İhlas Haber Ajansı İhlas Haber Ajansı</t>
+          <t>8 Büyük Bankacılık Kuruluşu, Kripto Paralar İçin Boğa Lehine Clarity Act'e Karşı Sıcak Bildiri Yayınladı! Bitcoin Sistemi</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2713,8 +2681,236 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:00:00</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Diğer</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Çiçek başına 10 kuruş: Ağaç A.Ş.'de rüşvet tarifesi</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Çiçek başına 10 kuruş: Ağaç A.Ş.'de rüşvet tarifesi Yeni Şafak</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Ağaç ve Peyzaj A.Ş</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>İSTANBUL AĞAÇ A.Ş</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>firma adı + güvenli maps adayı var</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:45:00</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Gıda tedarikçilerine 22 ilde operasyon: 41 gözaltı kararı</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Gıda tedarikçilerine 22 ilde operasyon: 41 gözaltı kararı kutahyaekspres.com</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:47:18</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul merkezli 22 farklı ilde gıdada fahiş fiyat operasyonu: 33 gözaltı İhlas Haber Ajansı</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul merkezli 22 farklı ilde gıdada fahiş fiyat operasyonu: 33 gözaltı İhlas Haber Ajansı iha.com.tr</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>İstanbul</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:44:36</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Operasyon / Soruşturma / Suç</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Fahiş fiyat operasyonu! Adalet Bakanı Gürlek: 41 firmanın 41 yöneticisine gözaltı kararı</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Fahiş fiyat operasyonu! Adalet Bakanı Gürlek: 41 firmanın 41 yöneticisine gözaltı kararı Milliyet</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:59:53</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh Şehri polisi, 70'ten fazla banka hesabına para transferi yapmaları için kandırılan kişileri arıyor.</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Ho Chi Minh Şehri polisi, 70'ten fazla banka hesabına para transferi yapmaları için kandırılan kişileri arıyor. vietnam.vn</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:43:17</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Banka / Finansal Kuruluş</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>SHB, çevrimiçi para transferi işlemlerinde güvenlik önlemlerini güçlendiriyor.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>SHB, çevrimiçi para transferi işlemlerinde güvenlik önlemlerini güçlendiriyor. vietnam.vn</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Habere Git</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>maps araması yapılmadı</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J56"/>
+  <autoFilter ref="A1:J62"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
@@ -2771,6 +2967,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2782,7 +2984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB56"/>
+  <dimension ref="A1:AB62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2960,12 +3162,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-13 21:35:12</t>
+          <t>2026-09-15 09:30:00</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>tesis yangını</t>
+          <t>üretim tesisi yangını</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2975,12 +3177,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı</t>
+          <t>Madran Dağı alarm veriyor: Yangın felaketi yetmezmiş gibi Madran’da bir maden daha kapasite arttırıyor</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı A Haber</t>
+          <t>Madran Dağı alarm veriyor: Yangın felaketi yetmezmiş gibi Madran’da bir maden daha kapasite arttırıyor Evrensel.net</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -2990,22 +3192,18 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>fabrika</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>fabrika</t>
-        </is>
-      </c>
+          <t>maden</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken 1 itfaiye eri yaralandı. Düzce'de Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken 1 itfaiye eri yaralandı. Düzce'de Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken 1 itfaiye eri yaralandı. Giriş Tarihi: 14 Eylül 2026 00:35 Son Güncelleme: 14 Eylül 2026 02:12 ahaber.com.tr Haber Merkezi Giriş Tarihi: 14 Eylül 2026 00:35 Son Güncelleme: 14 Eylül 2026 02:12 ahaber.com.tr Haber Merkezi Düzce'de merkeze bağlı Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken, 1 itfaiye eri yanan çatının üzerine düşerek yaralandı. Yaralı itfaiye eri olay yerindeki ilk müdahalenin ardından hastaneye kaldırılırken, yangın kontrol altına alındı. DÜZCE'DE AHŞAP KAPI FABRİKASINDA YANGIN! Düzce D-100 kara yolu üzerinde bulunan Hacıdayı mevkiindeki Düzce Door isimli fabrikada bilinmeyen nedenle yangın çıktı. Alevler, yanıcı maddeler nedeniyle kısa sürede büyürken ihbar üzerine kent merkezi, ilçeler ve çevre illerden itfaiye ekipleri bölgeye sevk edildi. Yangına müdahale eden 1 itfaiye eri yaralanarak hastaneye kaldırıldı. (Foto: İHA) İTFAİYE ERİ YARALANDI Yangına müdahale eden 1 itfaiye eri, yanan çatının üzerine düşmesi sonucu yaralandı. Olay yerinde ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. "CAN KAYBI YOK" Düzce Belediye Başkanı Faruk Özlü, yangının çıktığı fabrikada söndürme çalışmalarına ilişkin son durumu payla</t>
+          <t>Büyük bir yangın atlatan Aydın Madran Dağı’nda yeni bir maden projesi için ÇED süreci başlatıldı. Yaklaşık 47 bin ağacın kesilmesini öngören kapasite artışı, su kaynaklarını, yerleşim yerlerini ve 8 bin yıllık kaya resimlerini tehdit ediyor. Büyük bir yangın atlatan Aydın Madran Dağı’nda yeni bir maden projesi için ÇED süreci başlatıldı. Yaklaşık 47 bin ağacın kesilmesini öngören kapasite artışı, su kaynaklarını, yerleşim yerlerini ve 8 bin yıllık kaya resimlerini tehdit ediyor. Fotoğraf: Özer Akdemir Yurt genelinde parçalı bulutlu hava etkisini sürdürürken; İstanbul ve Kırklareli'de öğle, İzmir ve Manisa'da gece saatlerinde gök gürültülü sağanak geçişleri yaşanacak. Fotoğraf: Alvin Leopold/Unsplash Küresel çip krizi ve artan maliyetler nedeniyle akıllı telefon fiyatlarında yeni artışlar bekleniyor. MOBİSAD Başkanı Turnacı, yeni zamların gelebileceğini söyledi. Fotoğraf: Pixabay Brent petrolün yükselişi sürüyor. Varil fiyatı, bugün saat 09.37 itibarıyla kapanışa göre yüzde 1,7 artarak 107,52 dolar oldu. Temsili görsel | Fotoğraf: Pixabay Bursa'nın İznik ilçesinde bir soğuk hava deposunda gece saatlerinde çıkan yangın kontrol altına alınarak söndürüldü. Fotoğraf: DHA Antalya kavşağında iki minibüsün çarpışması sonucu 2'si Afgan, 10 tarım işçisi kadın yaralandı. Fotoğraf: DHA Motorinin litre fiyatına yapılan 6,62 liralık zam, Isparta'da pompaya yansıdı. Yurttaşlar ve sektör temsilcileri, artan akaryakıt maliyetlerinin bütçelerini ve işlerini olumsuz etkilediğini söyledi. Fotoğraf: ANKA İçerik yükleniyor... (Haber Merkezi) Devamını Oku İçerik yükleniyor... (Ekonomi Servisi) Devamını Oku İçerik yükleniyor... (AA) İçerik yükleniyor... (İşçi Sendika Servisi) İçerik yükleniyor... (ANKA) Madran Dağı alarm veriyor: Yangın felaketi yetmezmiş gibi Madran’da bir maden daha kapasite arttırıyor Büyük bir yangın atlatan Aydın Madran Dağı’nda yeni bir maden projesi için ÇED süreci başlatıldı. Yaklaşık 47 bin ağacın kesilmesini öngören kapasite artışı, su kaynaklarını, yerleşim yerlerini ve 8 bin yıllık kaya resimlerini tehdit ediyor. Serin hava geliyor: Meteoroloji'den İstanbul dahil birçok ilde sağanak yağış uyarısı Yurt genelinde parçalı bulutlu hava etkisini sürdürürken; İstanbul ve Kırklareli'de öğle, İzmir ve Manisa'da gece saatlerinde gök gürültülü sağanak geçişleri yaşanacak. Akıllı telefonlarda yeni zam dalgası yolda: 'İmkanı olan ertelemesin' Küresel çip krizi ve artan maliyetler nedeniyle akıllı telefon fiyatlarında yeni artışlar bekleniyor. MOBİSAD Başkanı Turnacı, yeni zamların gelebileceğini söyledi. Brent petrolün yükselişi sürüyor: Varil fiyatı yüzde 1,7 artarak 107,52 dolar oldu Brent petrolün yükselişi sürüyor. Varil fiyatı, bugün saat 09.37 itibarıyla kapanışa göre yüzde 1,7 artarak 107,52 dolar oldu. Bursa'da soğuk hava deposunda çıkan yangın söndürüldü Bursa'nın İznik ilçesinde bir soğuk hava deposunda gece saatlerinde çıkan yangın kontrol altına alınarak söndürüldü. Burdur'da minibüsler çarpıştı: 10 tarım işçisi kadın yaralandı, sürücüler gözaltında Antalya kavşağında iki minibüsün çarpışması sonucu 2'si Afgan, 10 tarım işçisi kadın yaralandı. Isparta'da vatandaşlardan motorin zammına tepki: Cebimize giren depoya gidiyor Motorinin litre fiyatına yapılan 6,62 liralık zam, Isparta'da pompaya yansıdı. Yurttaşlar ve sektör temsilcileri, artan akaryakıt maliyetlerinin bütçelerini ve işlerini olumsuz etkilediğini söyledi. Özer Akdemir ozerakdemir@gmail.com Aydın - Aydın'ın Çine ve Yenipazar ilçeleri sınırlarında kalan Madran Dağı, adeta feldspat ve kuvars madenciliği yürüten şirketlerin istilası altında. Geçtiğimiz haftalarda çok büyük bir yangın felaketi yaşayan Madran’da yangından bir hafta önce Aktaş maden işletmesinin feldispat-kuvars madeni faaliyetlerine başlamıştı. Dağda şimdi de Akmin Endüstri Mineralleri Sanayi ve Ticaret A.Ş. tarafından Aydın ili Çine ilçesi Topçam Mahallesi ile Yenipazar ilçesi Paşaköy ve Karacaören Mahalleleri mevkisinde feldspat ve kuvars ocağı kapasite artışı ile kırma-eleme tesisi projesine ilişkin ÇED başvurusu yapıldı. Yangında onbinlerce ağacın yandığı Madran Dağı’nda Akmin madencilik kapasite artışında da yaklaşık 467 bir ağacın kesilmesi planlanıyor. Madran Dağı sınırları içerisindeki proje kapsamında işletmenin mevcut faaliyetlerine ilave olarak yeni ÇED poligonlarının eklenmesi hedefleniyor. ÇED başvuru dosyasındaki bilgilere göre, işletmenin ruhsat sahasında yer alan ikinci poligondaki 16,45 hektarlık alanda yıllık 120 bin tonluk kuvars ocağı ve kırma-eleme tesisi faaliyeti aynen sürdürülüyor. Birinci ruhsat poligonunda planlanan ilave 3 adet ÇED alanında ise yıllık 390 bin ton toplam kazı yapılması ve 195 bin ton feldspat ile 195 bin ton pasa üretilmesi öngörülüyor. Proje genelinde toplam kazı kapasitesinin yıllık 590 bin tona çıkarılması ve yıllık 315 bin ton tüvenan cevher elde edilmesi planlanıyor. İlave ÇED poligonlarında yeni bir kırma-eleme tesisi kurulmayacağı ve delme-patlatma işlemi yapılmaksızın iş makineleri aracılığıyla mekanik üretim gerçekleştirileceği ileri sürülüyor. Başvuru dosyasında yer alan mesafe tablolarına göre proje sahası Aydın il merkezine 29 kilometre, Çine ilçe merkezine 14 kilometre, Yenipazar ilçe merkezine 9 kilometre ve Bozdoğan ilçe merkezine 15 kilometre uzaklıkta bulunuyor. Hassas alıcılar ve yerleşim yerleri bağlamında yapılan ölçümlerde, planlanan ÇED-2 alanının Karacaören Mahallesi'ne sadece 112 metre mesafede kaldığı görülüyor. Aynı zamanda ÇED-1 alanının Karacaören'e 500 metre, ÇED-3 alanının Paşaköy'e 740 metre ve Hacıköseler Mahallesi'ne 1,5 kilometre mesafede konumlandığı belirtiliyor. Mevcut ÇED alanına en yakın yapıların ise 700 ila 1200 metre mesafelerde yer aldığı kaydediliyor. Saha çevresindeki su varlıkları incelendiğinde, Madran Çayı'nın ÇED alanlarına en yakın 705 metre mesafeden aktığı ve Karacaören Göleti'nin 720 metre uzaklıkta bulunduğu göze çarpıyor. Bölgedeki en yakın korunan alan olarak 7,4 kilometre mesafedeki Şarlan Tabiat Parkı gösterilirken, saha içerisinde sulak alan bulunmadığı aktarılıyor. Türkiye'nin en kaliteli kaynak sularının çıktığı ve 500 yılı aşkın geçmişe sahip Topçam su kaynakları madencilik faaliyetlerinin doğrudan hedefi haline geliyor. Maden ocaklarında gerçekleştirilen dinamitli patlatmalar yeraltı su damarlarını patlatırken açılan devasa maden çukurlarına biriken içme suları pompalarla dışarı tahliye ediliyor ve bu durum köylülerin içme suyuna erişimini kısıtlıyor. Aynı zamanda yöre halkının ana geçim kaynağını oluşturan fıstık çamı yetiştiriciliği, zeytincilik, arıcılık ve bağ-bahçecilik faaliyetleri madenlerden yayılan toz emisyonu, erozyon ve taş fırlamaları sebebiyle ağır zarar görüyor. Patlatmalar sırasında savrulan kaya parçaları fıstık çamlarının dallarını koparırken tarlaları ve verimli tarım arazilerini kullanılamaz hale getiriyor. Madran Dağı üzerindeki madencilik projeleri ve kapasite artışı çalışmaları çerçevesinde hazırlanan ÇED dosyalarındaki orman amenajman verilerine göre proje sahalarında toplam 46 bin 668 adet ağacın kesilmesi öngörülüyor. Kesilmesi planlanan ağaçlar arasında kayın, meşe, sarıçam, karaçam, ladin, sedir ve göknarın yanı sıra bölge ekosisteminin ana omurgasını oluşturan kızılçam ile fıstık çamları yer alıyor. Yaklaşık 152 hektarlık orman alanını kapsayan bu kesimlerin yanında Akmin Endüstri Mineralleri ÇED başvuru dosyasında da talep edilen yeni ÇED poligonlarının orman arazileri üzerinde kaldığı ve bitkisel toprağın sıyrılacağı ifade ediliyor. Feldspat ve kuvars madenciliği esnasındaki açık ocak kırma-eleme faaliyetleri ve patlatmalar sonucu ortama yayılan tozlar kristalen silika içeriyor. Bu toksik toza uzun süreli maruz kalmak, maden çalışanlarının yanı sıra civar köylerde yaşayan insanlarda da tedavisi bulunmayan ölümcül silikozis hastalığı riskini doğuruyor. ÇED dosyalarında en yakın sit alanının uzak mesafelerde olduğu iddia edilse de Madran Dağı'nın gnays kayalıkları içinde yer alan 8 bin yıllık antik kaya resimleri ile yığma antik mezarlar, şiddetli patlatmaların yarattığı sarsıntılar yüzünden tamamen yok olma tehlikesi taşıyor. Bununla birlikte geniş çaplı orman kıyımı ve bitkisel toprak sıyırma işlemleri dağdaki yaban hayatı ile koruma altındaki türleri yaşam alanlarından mahrum bırakarak bölgenin biyolojik çeşitliliğine ağır darbeler vuruyor. 31 yıldır emeğin sesi olan Evrensel, gücünü sadece okurlarından alıyor. Emeğin sesinin daha gür çıkması için sen de güç ver. Fotoğraf: Alvin Leopold/Unsplash Önemli haberlerden ve gelişmelerden haberdar olmak ister misiniz?</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı Düzce'de kapı fabrikasında yangın! 1 itfaiye eri yaralandı A Haber Düzce'de Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken 1 itfaiye eri yaralandı. Giriş Tarihi: 14 Eylül 2026 00:35 Son Güncelleme: 14 Eylül 2026 02:12 ahaber.com.tr Haber Merkezi Giriş Tarihi: 14 Eylül 2026 00:35 Son Güncelleme: 14 Eylül 2026 02:12 ahaber.com.tr Haber Merkezi Düzce'de merkeze bağlı Hacıdayı mevkiinde bulunan ahşap kapı fabrikasında yangın çıktı. Alevler kısa sürede tesisi tamamen sararken, 1 itfaiye eri yanan çatının üzerine düşerek yaralandı. Yaralı itfaiye eri olay yerindeki ilk müdahalenin ardından hastaneye kaldırılırken, yangın kontrol altına alındı. DÜZCE'DE AHŞAP KAPI FABRİKASINDA YANGIN! Düzce D-100 kara yolu üzerinde bulunan Hacıdayı mevkiindeki Düzce Door isimli fabrikada bilinmeyen nedenle yangın çıktı. Alevler, yanıcı maddeler nedeniyle kısa sürede büyürken ihbar üzerine kent merkezi, ilçeler ve çevre illerden itfaiye ekipleri bölgeye sevk edildi. Yangına müdahale eden 1 itfaiye eri yaralanarak hastaneye kaldırıldı. (Foto: İHA) İTFAİYE ERİ YARALANDI Yangına müdahale eden 1 itfaiye eri, yanan çatının üzerine düşmesi sonucu yaralandı. Olay yerinde ilk müdahalesi yapılan yaralı itfaiye eri, Düzce Atatürk Devlet Hastanesine kaldırılarak tedavi altına alındı. "CAN KAYBI YOK" Düzce Belediye Başkanı Faruk Özlü, yangının çıktığı fabrikada söndürme çalışmalarına ilişkin son durumu payla</t>
+          <t>Madran Dağı alarm veriyor: Yangın felaketi yetmezmiş gibi Madran’da bir maden daha kapasite arttırıyor Madran Dağı alarm veriyor: Yangın felaketi yetmezmiş gibi Madran’da bir maden daha kapasite arttırıyor Evrensel.net Büyük bir yangın atlatan Aydın Madran Dağı’nda yeni bir maden projesi için ÇED süreci başlatıldı. Yaklaşık 47 bin ağacın kesilmesini öngören kapasite artışı, su kaynaklarını, yerleşim yerlerini ve 8 bin yıllık kaya resimlerini tehdit ediyor. Fotoğraf: Özer Akdemir Yurt genelinde parçalı bulutlu hava etkisini sürdürürken; İstanbul ve Kırklareli'de öğle, İzmir ve Manisa'da gece saatlerinde gök gürültülü sağanak geçişleri yaşanacak. Fotoğraf: Alvin Leopold/Unsplash Küresel çip krizi ve artan maliyetler nedeniyle akıllı telefon fiyatlarında yeni artışlar bekleniyor. MOBİSAD Başkanı Turnacı, yeni zamların gelebileceğini söyledi. Fotoğraf: Pixabay Brent petrolün yükselişi sürüyor. Varil fiyatı, bugün saat 09.37 itibarıyla kapanışa göre yüzde 1,7 artarak 107,52 dolar oldu. Temsili görsel | Fotoğraf: Pixabay Bursa'nın İznik ilçesinde bir soğuk hava deposunda gece saatlerinde çıkan yangın kontrol altına alınarak söndürüldü. Fotoğraf: DHA Antalya kavşağında iki minibüsün çarpışması sonucu 2'si Afgan, 10 tarım işçisi kadın yaralandı. Fotoğraf: DHA Motorinin litre fiyatına yapılan 6,62 liralık zam, Isparta'da pompaya yansıdı. Yurttaşlar ve sektör temsilcileri, artan akaryakıt maliyetlerinin bütçelerini ve işlerini olumsuz etkilediğini söyledi. (İşçi Sendika Servisi) İçerik yükleniyor... (ANKA) Madran Dağı alarm veriyor: Yangın felaketi yetmezmiş gibi Madran’da bir maden daha kapasite arttırıyor Büyük bir yangın atlatan Aydın Madran Dağı’nda yeni bir maden projesi için ÇED süreci başlatıldı. Serin hava geliyor: Meteoroloji'den İstanbul dahil birçok ilde sağanak yağış uyarısı Yurt genelinde parçalı bulutlu hava etkisini sürdürürken; İstanbul ve Kırklareli'de öğle, İzmir ve Manisa'da gece saatlerinde gök gürültülü sağanak geçişleri yaşanacak. Akıllı telefonlarda yeni zam dalgası yolda: 'İmkanı olan ertelemesin' Küresel çip krizi ve artan maliyetler nedeniyle akıllı telefon fiyatlarında yeni artışlar bekleniyor. Bursa'da soğuk hava deposunda çıkan yangın söndürüldü Bursa'nın İznik ilçesinde bir soğuk hava deposunda gece saatlerinde çıkan yangın kontrol altına alınarak söndürüldü. Burdur'da minibüsler çarpıştı: 10 tarım işçisi kadın yaralandı, sürücüler gözaltında Antalya kavşağında iki minibüsün çarpışması sonucu 2'si Afgan, 10 tarım işçisi kadın yaralandı. Isparta'da vatandaşlardan motorin zammına tepki: Cebimize giren depoya gidiyor Motorinin litre fiyatına yapılan 6,62 liralık zam, Isparta'da pompaya yansıdı. Özer Akdemir ozerakdemir@gmail.com Aydın - Aydın'ın Çine ve Yenipazar ilçeleri sınırlarında kalan Madran Dağı, adeta feldspat ve kuvars madenciliği yürüten şirketlerin istilası altında. Geçtiğimiz haftalarda çok büyük bir yangın felaketi yaşayan Madran’da yangından bir hafta önce Aktaş maden işletmesinin feldispat-kuvars madeni faaliyetlerine başlamıştı. Dağda şimdi de Akmin Endüstri Mineralleri Sanayi ve Ticaret A.Ş. tarafından Aydın ili Çine ilçesi Topçam Mahallesi ile Yenipazar ilçesi Paşaköy ve Karacaören Mahalleleri mevkisinde feldspat ve kuvars ocağı kapasite artışı ile kırma-eleme tesisi projesine ilişkin ÇED başvurusu yapıldı. Yangında onbinlerce ağacın yandığı Madran Dağı’nda Akmin madencilik kapasite artışında da yaklaşık 467 bir ağacın kesilmesi planlanıyor. Madran Dağı sınırları içerisindeki proje kapsamında işletmenin mevcut faaliyetlerine ilave olarak yeni ÇED poligonlarının eklenmesi hedefleniyor. ÇED başvuru dosyasındaki bilgilere göre, işletmenin ruhsat sahasında yer alan ikinci poligondaki 16,45 hektarlık alanda yıllık 120 bin tonluk kuvars ocağı ve kırma-eleme tesisi faaliyeti aynen sürdürülüyor. Birinci ruhsat poligonunda planlanan ilave 3 adet ÇED alanında ise yıllık 390 bin ton toplam kazı yapılması ve 195 bin ton feldspat ile 195 bin ton pasa üretilmesi öngörülüyor. Proje genelinde toplam kazı kapasitesi